--- a/EconJM_status.xlsx
+++ b/EconJM_status.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/jjgecon_dat/Dropbox/Work/Job Search/2025 EconJM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A616927B-FF54-2A4B-A2B5-B8A8F6A959A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44A5C9A7-34AD-1A45-AE23-FA855FF4BF5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{6FE48536-7E5C-BF4C-9490-2A6392576298}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="sum" sheetId="1" r:id="rId1"/>
+    <sheet name="timeline" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -36,14 +37,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="32">
   <si>
     <t>add_id</t>
   </si>
   <si>
-    <t>add_title</t>
-  </si>
-  <si>
     <t>add_category</t>
   </si>
   <si>
@@ -65,40 +63,103 @@
     <t>WOO_letter_status</t>
   </si>
   <si>
-    <t>add_description_file</t>
-  </si>
-  <si>
     <t>app_status</t>
   </si>
   <si>
-    <t>institution_mission</t>
-  </si>
-  <si>
-    <t>collab_name</t>
-  </si>
-  <si>
-    <t>collab_reason</t>
-  </si>
-  <si>
-    <t>add_url</t>
-  </si>
-  <si>
     <t>add_how_apply</t>
   </si>
   <si>
     <t>institution</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>app_id</t>
+  </si>
+  <si>
+    <t>comment</t>
+  </si>
+  <si>
+    <t>simon_frazer_1</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Burnaby, Canada</t>
+  </si>
+  <si>
+    <t>deadline_target</t>
+  </si>
+  <si>
+    <t>add_rank</t>
+  </si>
+  <si>
+    <t>assistant</t>
+  </si>
+  <si>
+    <t>add_field</t>
+  </si>
+  <si>
+    <t>Simon Fraser University</t>
+  </si>
+  <si>
+    <t>add_posting</t>
+  </si>
+  <si>
+    <t>EJM</t>
+  </si>
+  <si>
+    <t>McMaster University</t>
+  </si>
+  <si>
+    <t>macmaster_1</t>
+  </si>
+  <si>
+    <t>Hamilton, Canada</t>
+  </si>
+  <si>
+    <t>applied micro</t>
+  </si>
+  <si>
+    <t>research</t>
+  </si>
+  <si>
+    <t>teaching</t>
+  </si>
+  <si>
+    <t>gathering info</t>
+  </si>
+  <si>
+    <t>prep docs</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -119,13 +180,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -458,76 +526,206 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7772053-9363-CA4A-A53F-040B7C700753}">
-  <dimension ref="A1:Q1"/>
+  <dimension ref="A1:P3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="1" max="1" width="19.6640625" customWidth="1"/>
     <col min="2" max="2" width="18.33203125" customWidth="1"/>
     <col min="3" max="3" width="37.33203125" customWidth="1"/>
-    <col min="4" max="4" width="19.33203125" customWidth="1"/>
-    <col min="5" max="5" width="39.33203125" customWidth="1"/>
-    <col min="6" max="6" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.33203125" customWidth="1"/>
-    <col min="11" max="11" width="19.83203125" customWidth="1"/>
-    <col min="12" max="13" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="26.1640625" customWidth="1"/>
-    <col min="17" max="17" width="32.6640625" customWidth="1"/>
+    <col min="4" max="6" width="19.5" customWidth="1"/>
+    <col min="7" max="8" width="19.33203125" customWidth="1"/>
+    <col min="9" max="9" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="21.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:16" s="3" customFormat="1" ht="22" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
         <v>16</v>
       </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="1">
+        <v>45931</v>
+      </c>
+      <c r="I2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2">
         <v>1</v>
       </c>
-      <c r="F1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" s="1">
+        <v>45931</v>
+      </c>
+      <c r="I3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{2FD67E99-97D4-6F4F-9C23-F094A4E233EB}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{C466BD2C-2D71-FD47-B267-C9470B42EAAE}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923E81FA-B875-3C4E-A189-1A21268FA086}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="32.83203125" customWidth="1"/>
+    <col min="2" max="2" width="33" customWidth="1"/>
+    <col min="3" max="3" width="25.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" s="3" customFormat="1" ht="22" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
+        <v>45909</v>
+      </c>
+      <c r="B2" t="s">
         <v>14</v>
       </c>
-      <c r="H1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K1" t="s">
-        <v>5</v>
-      </c>
-      <c r="L1" t="s">
-        <v>6</v>
-      </c>
-      <c r="M1" t="s">
-        <v>7</v>
-      </c>
-      <c r="N1" t="s">
-        <v>8</v>
-      </c>
-      <c r="O1" t="s">
-        <v>11</v>
-      </c>
-      <c r="P1" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>13</v>
+      <c r="C2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>45909</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/EconJM_status.xlsx
+++ b/EconJM_status.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/jjgecon_dat/Dropbox/Work/Job Search/2025 EconJM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44A5C9A7-34AD-1A45-AE23-FA855FF4BF5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81F6EDF3-CBC6-784A-9C4C-827DB84885BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{6FE48536-7E5C-BF4C-9490-2A6392576298}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="64">
   <si>
     <t>add_id</t>
   </si>
@@ -45,15 +45,6 @@
     <t>add_category</t>
   </si>
   <si>
-    <t>needed_cover_letter</t>
-  </si>
-  <si>
-    <t>needed_RS</t>
-  </si>
-  <si>
-    <t>needed_TS</t>
-  </si>
-  <si>
     <t>OMER_letter_status</t>
   </si>
   <si>
@@ -132,7 +123,112 @@
     <t>gathering info</t>
   </si>
   <si>
-    <t>prep docs</t>
+    <t>need_cover_letter</t>
+  </si>
+  <si>
+    <t>need_RS</t>
+  </si>
+  <si>
+    <t>need_TS</t>
+  </si>
+  <si>
+    <t>need_diversity</t>
+  </si>
+  <si>
+    <t>generating docs</t>
+  </si>
+  <si>
+    <t>usydney_1</t>
+  </si>
+  <si>
+    <t>University of Sydney</t>
+  </si>
+  <si>
+    <t>Sydney, Asutralia</t>
+  </si>
+  <si>
+    <t>postdoc</t>
+  </si>
+  <si>
+    <t>culture</t>
+  </si>
+  <si>
+    <t>good_match</t>
+  </si>
+  <si>
+    <t>getting info</t>
+  </si>
+  <si>
+    <t>nova_lisboa_1</t>
+  </si>
+  <si>
+    <t>University Nova Lisboa</t>
+  </si>
+  <si>
+    <t>Cascais, Portugal</t>
+  </si>
+  <si>
+    <t>environmental</t>
+  </si>
+  <si>
+    <t>Williamstown, United States</t>
+  </si>
+  <si>
+    <t>Williams College</t>
+  </si>
+  <si>
+    <t>will_college_1</t>
+  </si>
+  <si>
+    <t>https://apply.interfolio.com/171825</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/posts/nicholascmartin_ai-fellows-12-month-lte-activity-7372630155451637760-Sn6h/?utm_source=share&amp;utm_medium=member_ios&amp;rcm=ACoAAABLNkkBpy5X7ZG5OxHeOGF5LMwJFpHvX2Q</t>
+  </si>
+  <si>
+    <t>aist_1</t>
+  </si>
+  <si>
+    <t>Touluse, France</t>
+  </si>
+  <si>
+    <t>Institute For Advanced Study</t>
+  </si>
+  <si>
+    <t>fellowship</t>
+  </si>
+  <si>
+    <t>waseda_1</t>
+  </si>
+  <si>
+    <t>Waseda University</t>
+  </si>
+  <si>
+    <t>Waseda, Japan</t>
+  </si>
+  <si>
+    <t>JOE</t>
+  </si>
+  <si>
+    <t>https://www.wasedapse.jp/en/fpse2/eng_input.php</t>
+  </si>
+  <si>
+    <t>other_link</t>
+  </si>
+  <si>
+    <t>https://www.waseda.jp/fpse/pse/news-en/2025/08/05/24591/</t>
+  </si>
+  <si>
+    <t>penn_state_1</t>
+  </si>
+  <si>
+    <t>Pennsylvania State University</t>
+  </si>
+  <si>
+    <t>University Park, United States</t>
+  </si>
+  <si>
+    <t>https://psu.wd1.myworkdayjobs.com/en-US/PSU_Academic/details/Assistant-Professor-of-Economics_REQ_0000071571-1</t>
   </si>
 </sst>
 </file>
@@ -526,160 +622,455 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7772053-9363-CA4A-A53F-040B7C700753}">
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:S9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" customWidth="1"/>
-    <col min="2" max="2" width="18.33203125" customWidth="1"/>
-    <col min="3" max="3" width="37.33203125" customWidth="1"/>
-    <col min="4" max="6" width="19.5" customWidth="1"/>
-    <col min="7" max="8" width="19.33203125" customWidth="1"/>
-    <col min="9" max="9" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.1640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="21.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="19.6640625" customWidth="1"/>
+    <col min="3" max="3" width="18.33203125" customWidth="1"/>
+    <col min="4" max="4" width="37.33203125" customWidth="1"/>
+    <col min="5" max="7" width="19.5" customWidth="1"/>
+    <col min="8" max="9" width="19.33203125" customWidth="1"/>
+    <col min="10" max="10" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.1640625" customWidth="1"/>
+    <col min="13" max="13" width="23.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="21.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="3" customFormat="1" ht="22" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" s="3" customFormat="1" ht="22" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="G1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S1" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2" s="1">
+        <v>45931</v>
+      </c>
+      <c r="J2" t="s">
         <v>20</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I1" s="3" t="s">
+      <c r="K2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="O2">
+        <v>1</v>
+      </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>22</v>
       </c>
-      <c r="J1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="C3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" t="s">
         <v>16</v>
       </c>
-      <c r="E2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H2" s="1">
+      <c r="G3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" s="1">
         <v>45931</v>
       </c>
-      <c r="I2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="J3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3">
+        <v>1</v>
+      </c>
+      <c r="O3">
+        <v>1</v>
+      </c>
+      <c r="P3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H4" t="s">
         <v>25</v>
       </c>
-      <c r="B3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="I4" s="1">
+        <v>45978</v>
+      </c>
+      <c r="J4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" t="s">
+        <v>43</v>
+      </c>
+      <c r="H5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I5" s="1">
+        <v>45978</v>
+      </c>
+      <c r="J5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K5" t="s">
+        <v>20</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" t="s">
         <v>24</v>
       </c>
-      <c r="D3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G3" t="s">
-        <v>29</v>
-      </c>
-      <c r="H3" s="1">
-        <v>45931</v>
-      </c>
-      <c r="I3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J3" t="s">
-        <v>23</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
+      <c r="H6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" s="1">
+        <v>45971</v>
+      </c>
+      <c r="J6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="L6" s="2"/>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" t="s">
+        <v>52</v>
+      </c>
+      <c r="H7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" s="1">
+        <v>45971</v>
+      </c>
+      <c r="K7" t="s">
+        <v>48</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="1">
+        <v>45940</v>
+      </c>
+      <c r="J8" t="s">
+        <v>56</v>
+      </c>
+      <c r="K8" t="s">
+        <v>57</v>
+      </c>
+      <c r="L8" t="s">
+        <v>59</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E9" t="s">
+        <v>62</v>
+      </c>
+      <c r="F9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" s="1">
+        <v>45971</v>
+      </c>
+      <c r="J9" t="s">
+        <v>20</v>
+      </c>
+      <c r="K9" t="s">
+        <v>63</v>
+      </c>
+      <c r="M9">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{2FD67E99-97D4-6F4F-9C23-F094A4E233EB}"/>
-    <hyperlink ref="C3" r:id="rId2" xr:uid="{C466BD2C-2D71-FD47-B267-C9470B42EAAE}"/>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{2FD67E99-97D4-6F4F-9C23-F094A4E233EB}"/>
+    <hyperlink ref="D3" r:id="rId2" xr:uid="{C466BD2C-2D71-FD47-B267-C9470B42EAAE}"/>
+    <hyperlink ref="D4" r:id="rId3" xr:uid="{7E4575FB-8BA7-8343-9270-E933C2CF052A}"/>
+    <hyperlink ref="D5" r:id="rId4" xr:uid="{7DE2DCC0-6910-AF4A-ADA1-2F0A7CE7A46A}"/>
+    <hyperlink ref="D6" r:id="rId5" xr:uid="{9F5721B0-AA94-954A-B077-53D294EE0006}"/>
+    <hyperlink ref="K6" r:id="rId6" xr:uid="{E9AC54D1-D414-9A4A-8F10-99810DECDF26}"/>
+    <hyperlink ref="D7" r:id="rId7" xr:uid="{3DA7C680-99C0-9744-A5E3-8B70509CE1C7}"/>
+    <hyperlink ref="D8" r:id="rId8" xr:uid="{F2E0FCCF-BB13-0240-931E-487798981CC9}"/>
+    <hyperlink ref="D9" r:id="rId9" xr:uid="{DF00AD54-0273-B54C-B9CE-46119BBDF932}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -687,7 +1078,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923E81FA-B875-3C4E-A189-1A21268FA086}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="32.83203125" customWidth="1"/>
@@ -697,13 +1088,13 @@
   <sheetData>
     <row r="1" spans="1:3" s="3" customFormat="1" ht="22" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -711,10 +1102,10 @@
         <v>45909</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -722,10 +1113,21 @@
         <v>45909</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>45910</v>
+      </c>
+      <c r="B4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/EconJM_status.xlsx
+++ b/EconJM_status.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/jjgecon_dat/Dropbox/Work/Job Search/2025 EconJM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81F6EDF3-CBC6-784A-9C4C-827DB84885BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D65141B-4883-524A-8E44-F821B95E8907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{6FE48536-7E5C-BF4C-9490-2A6392576298}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="104">
   <si>
     <t>add_id</t>
   </si>
@@ -120,9 +120,6 @@
     <t>teaching</t>
   </si>
   <si>
-    <t>gathering info</t>
-  </si>
-  <si>
     <t>need_cover_letter</t>
   </si>
   <si>
@@ -156,9 +153,6 @@
     <t>good_match</t>
   </si>
   <si>
-    <t>getting info</t>
-  </si>
-  <si>
     <t>nova_lisboa_1</t>
   </si>
   <si>
@@ -183,9 +177,6 @@
     <t>https://apply.interfolio.com/171825</t>
   </si>
   <si>
-    <t>https://www.linkedin.com/posts/nicholascmartin_ai-fellows-12-month-lte-activity-7372630155451637760-Sn6h/?utm_source=share&amp;utm_medium=member_ios&amp;rcm=ACoAAABLNkkBpy5X7ZG5OxHeOGF5LMwJFpHvX2Q</t>
-  </si>
-  <si>
     <t>aist_1</t>
   </si>
   <si>
@@ -229,6 +220,135 @@
   </si>
   <si>
     <t>https://psu.wd1.myworkdayjobs.com/en-US/PSU_Academic/details/Assistant-Professor-of-Economics_REQ_0000071571-1</t>
+  </si>
+  <si>
+    <t>https://www.iast.fr/research-fellowships</t>
+  </si>
+  <si>
+    <t>american_u_1</t>
+  </si>
+  <si>
+    <t>American University</t>
+  </si>
+  <si>
+    <t>Washington, DC</t>
+  </si>
+  <si>
+    <t>development</t>
+  </si>
+  <si>
+    <t>https://american.wd1.myworkdayjobs.com/en-US/AU/job/Assistant-Professor--Tenure-Track----Department-of-Environment--Development---Health_R2984</t>
+  </si>
+  <si>
+    <t>how_to_rec_letters</t>
+  </si>
+  <si>
+    <t>american_u_2</t>
+  </si>
+  <si>
+    <t>https://american.wd1.myworkdayjobs.com/AU/job/Main-Campus-Washington-DC/Assistant-Professor--Tenure-Track----Department-of-Politics--Governance---Economics_R2983-1</t>
+  </si>
+  <si>
+    <t>analysis_1</t>
+  </si>
+  <si>
+    <t>https://associatecareers-analysisgroup.icims.com/jobs/2388/associate---generalist-%28phd%29-%282026-start-date%29/job?mobile=false&amp;width=1150&amp;height=500&amp;bga=true&amp;needsRedirect=false&amp;jan1offset=-360&amp;jun1offset=-300</t>
+  </si>
+  <si>
+    <t>analysis_2</t>
+  </si>
+  <si>
+    <t>https://associatecareers-analysisgroup.icims.com/jobs/2760/associate---generalist---montreal---toronto-%282026-start-date%29/job</t>
+  </si>
+  <si>
+    <t>consulting</t>
+  </si>
+  <si>
+    <t>Analysis Group</t>
+  </si>
+  <si>
+    <t>US</t>
+  </si>
+  <si>
+    <t>Montreal</t>
+  </si>
+  <si>
+    <t>babson_1</t>
+  </si>
+  <si>
+    <t>Babson College</t>
+  </si>
+  <si>
+    <t>Wellesley, Massachusetts</t>
+  </si>
+  <si>
+    <t>adjunct</t>
+  </si>
+  <si>
+    <t>https://babson.peopleadmin.com/postings/6541</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t>babson_2</t>
+  </si>
+  <si>
+    <t>macroeconomics</t>
+  </si>
+  <si>
+    <t>https://babson.peopleadmin.com/postings/6545</t>
+  </si>
+  <si>
+    <t>bates_1</t>
+  </si>
+  <si>
+    <t>Bates College</t>
+  </si>
+  <si>
+    <t>Lewiston, Maine</t>
+  </si>
+  <si>
+    <t>https://apply.interfolio.com/173570</t>
+  </si>
+  <si>
+    <t>gathering info from AEA JOE, stopped @ Bates College</t>
+  </si>
+  <si>
+    <t>uc3_1</t>
+  </si>
+  <si>
+    <t>Universidad Carlos III</t>
+  </si>
+  <si>
+    <t>Getafe, Spain</t>
+  </si>
+  <si>
+    <t>https://econjobmarket.org/positions/11791/1/0</t>
+  </si>
+  <si>
+    <t>Texas A&amp;M</t>
+  </si>
+  <si>
+    <t>tamu_1</t>
+  </si>
+  <si>
+    <t>College Station, Texas</t>
+  </si>
+  <si>
+    <t>https://apply.interfolio.com/173294</t>
+  </si>
+  <si>
+    <t>gathering the applications that I'm most interested in</t>
+  </si>
+  <si>
+    <t>rovira_1</t>
+  </si>
+  <si>
+    <t>Universitat Rovira i Virgili</t>
+  </si>
+  <si>
+    <t>Reus, Spain</t>
   </si>
 </sst>
 </file>
@@ -259,12 +379,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -280,12 +406,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -622,7 +755,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7772053-9363-CA4A-A53F-040B7C700753}">
-  <dimension ref="A1:S9"/>
+  <dimension ref="A1:T19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -633,21 +766,22 @@
     <col min="10" max="10" width="14.5" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18.1640625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18.1640625" customWidth="1"/>
-    <col min="13" max="13" width="23.5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="17" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="21.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23.5" customWidth="1"/>
+    <col min="14" max="14" width="23.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="22.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="23.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="21.83203125" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="3" customFormat="1" ht="22" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" s="3" customFormat="1" ht="22" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>5</v>
@@ -677,36 +811,39 @@
         <v>6</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="M1" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="P1" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="S1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="T1" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>18</v>
@@ -732,9 +869,6 @@
       <c r="K2" t="s">
         <v>20</v>
       </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
       <c r="N2">
         <v>1</v>
       </c>
@@ -744,13 +878,16 @@
       <c r="P2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="Q2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>21</v>
@@ -776,9 +913,6 @@
       <c r="K3" t="s">
         <v>20</v>
       </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
       <c r="N3">
         <v>1</v>
       </c>
@@ -788,28 +922,31 @@
       <c r="P3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="Q3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" t="s">
         <v>34</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>35</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>36</v>
-      </c>
-      <c r="G4" t="s">
-        <v>37</v>
       </c>
       <c r="H4" t="s">
         <v>25</v>
@@ -823,11 +960,8 @@
       <c r="K4" t="s">
         <v>20</v>
       </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
       <c r="N4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4">
         <v>0</v>
@@ -835,25 +969,28 @@
       <c r="P4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="Q4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" t="s">
         <v>40</v>
-      </c>
-      <c r="C5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E5" t="s">
-        <v>42</v>
       </c>
       <c r="F5" t="s">
         <v>16</v>
       </c>
       <c r="G5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H5" t="s">
         <v>25</v>
@@ -867,11 +1004,8 @@
       <c r="K5" t="s">
         <v>20</v>
       </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
       <c r="N5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5">
         <v>0</v>
@@ -879,19 +1013,22 @@
       <c r="P5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="Q5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F6" t="s">
         <v>16</v>
@@ -909,40 +1046,40 @@
         <v>20</v>
       </c>
       <c r="K6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="L6" s="2"/>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" t="s">
         <v>47</v>
       </c>
-      <c r="L6" s="2"/>
-      <c r="M6">
-        <v>1</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>1</v>
-      </c>
-      <c r="P6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+      <c r="F7" t="s">
         <v>49</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E7" t="s">
-        <v>50</v>
-      </c>
-      <c r="F7" t="s">
-        <v>52</v>
       </c>
       <c r="H7" t="s">
         <v>25</v>
@@ -951,13 +1088,10 @@
         <v>45971</v>
       </c>
       <c r="K7" t="s">
-        <v>48</v>
-      </c>
-      <c r="M7">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7">
         <v>0</v>
@@ -965,22 +1099,25 @@
       <c r="P7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="Q7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E8" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F8" t="s">
         <v>16</v>
@@ -995,42 +1132,42 @@
         <v>45940</v>
       </c>
       <c r="J8" t="s">
+        <v>53</v>
+      </c>
+      <c r="K8" t="s">
+        <v>54</v>
+      </c>
+      <c r="L8" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="K8" t="s">
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
         <v>57</v>
       </c>
-      <c r="L8" t="s">
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" t="s">
         <v>59</v>
-      </c>
-      <c r="M8">
-        <v>1</v>
-      </c>
-      <c r="N8">
-        <v>1</v>
-      </c>
-      <c r="O8">
-        <v>1</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>60</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E9" t="s">
-        <v>62</v>
       </c>
       <c r="F9" t="s">
         <v>16</v>
@@ -1045,19 +1182,423 @@
         <v>20</v>
       </c>
       <c r="K9" t="s">
+        <v>60</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="M9">
-        <v>1</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <v>0</v>
+      <c r="E10" t="s">
+        <v>64</v>
+      </c>
+      <c r="F10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" t="s">
+        <v>65</v>
+      </c>
+      <c r="H10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10" s="1">
+        <v>45931</v>
+      </c>
+      <c r="J10" t="s">
+        <v>66</v>
+      </c>
+      <c r="N10">
+        <v>1</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>1</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E11" t="s">
+        <v>64</v>
+      </c>
+      <c r="F11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" s="1">
+        <v>45931</v>
+      </c>
+      <c r="J11" t="s">
+        <v>69</v>
+      </c>
+      <c r="N11">
+        <v>1</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>1</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E12" t="s">
+        <v>76</v>
+      </c>
+      <c r="H12" t="s">
+        <v>74</v>
+      </c>
+      <c r="I12" s="1">
+        <v>45962</v>
+      </c>
+      <c r="J12" t="s">
+        <v>71</v>
+      </c>
+      <c r="N12">
+        <v>1</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E13" t="s">
+        <v>77</v>
+      </c>
+      <c r="H13" t="s">
+        <v>74</v>
+      </c>
+      <c r="I13" s="1">
+        <v>45962</v>
+      </c>
+      <c r="J13" t="s">
+        <v>73</v>
+      </c>
+      <c r="N13">
+        <v>1</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E14" t="s">
+        <v>80</v>
+      </c>
+      <c r="F14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H14" t="s">
+        <v>26</v>
+      </c>
+      <c r="I14" s="1">
+        <v>45940</v>
+      </c>
+      <c r="J14" t="s">
+        <v>82</v>
+      </c>
+      <c r="N14">
+        <v>1</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>1</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="S14" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="T14" s="6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>84</v>
+      </c>
+      <c r="C15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E15" t="s">
+        <v>80</v>
+      </c>
+      <c r="F15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G15" t="s">
+        <v>85</v>
+      </c>
+      <c r="H15" t="s">
+        <v>25</v>
+      </c>
+      <c r="I15" s="1">
+        <v>45940</v>
+      </c>
+      <c r="J15" t="s">
+        <v>86</v>
+      </c>
+      <c r="N15">
+        <v>1</v>
+      </c>
+      <c r="O15">
+        <v>1</v>
+      </c>
+      <c r="P15">
+        <v>1</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E16" t="s">
+        <v>89</v>
+      </c>
+      <c r="F16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" t="s">
+        <v>24</v>
+      </c>
+      <c r="H16" t="s">
+        <v>25</v>
+      </c>
+      <c r="I16" s="1">
+        <v>45962</v>
+      </c>
+      <c r="J16" t="s">
+        <v>90</v>
+      </c>
+      <c r="N16">
+        <v>1</v>
+      </c>
+      <c r="O16">
+        <v>1</v>
+      </c>
+      <c r="P16">
+        <v>1</v>
+      </c>
+      <c r="Q16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E17" t="s">
+        <v>94</v>
+      </c>
+      <c r="F17" t="s">
+        <v>16</v>
+      </c>
+      <c r="H17" t="s">
+        <v>25</v>
+      </c>
+      <c r="I17" s="1">
+        <v>45971</v>
+      </c>
+      <c r="J17" t="s">
+        <v>95</v>
+      </c>
+      <c r="N17">
+        <v>1</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>97</v>
+      </c>
+      <c r="C18" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E18" t="s">
+        <v>98</v>
+      </c>
+      <c r="F18" t="s">
+        <v>16</v>
+      </c>
+      <c r="G18" t="s">
+        <v>24</v>
+      </c>
+      <c r="H18" t="s">
+        <v>25</v>
+      </c>
+      <c r="I18" s="1">
+        <v>45962</v>
+      </c>
+      <c r="J18" t="s">
+        <v>99</v>
+      </c>
+      <c r="N18">
+        <v>1</v>
+      </c>
+      <c r="O18">
+        <v>1</v>
+      </c>
+      <c r="P18">
+        <v>1</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>101</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E19" t="s">
+        <v>103</v>
+      </c>
+      <c r="F19" t="s">
+        <v>16</v>
+      </c>
+      <c r="I19" s="1">
+        <v>45940</v>
+      </c>
+      <c r="J19" t="s">
+        <v>20</v>
+      </c>
+      <c r="N19">
+        <v>1</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="T19" s="6" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -1071,6 +1612,17 @@
     <hyperlink ref="D7" r:id="rId7" xr:uid="{3DA7C680-99C0-9744-A5E3-8B70509CE1C7}"/>
     <hyperlink ref="D8" r:id="rId8" xr:uid="{F2E0FCCF-BB13-0240-931E-487798981CC9}"/>
     <hyperlink ref="D9" r:id="rId9" xr:uid="{DF00AD54-0273-B54C-B9CE-46119BBDF932}"/>
+    <hyperlink ref="D10" r:id="rId10" display="American Uiversity" xr:uid="{4368F24E-5E4F-B944-AB45-4045D2296D5A}"/>
+    <hyperlink ref="D11" r:id="rId11" display="American Uiversity" xr:uid="{0B28A4E3-9367-5B4E-821E-8878EF62879B}"/>
+    <hyperlink ref="L8" r:id="rId12" xr:uid="{F8BB08B3-A5E4-0244-9B87-74DC5560EA9C}"/>
+    <hyperlink ref="D12" r:id="rId13" xr:uid="{1A802253-386D-0248-869E-8A0EA127D432}"/>
+    <hyperlink ref="D13" r:id="rId14" xr:uid="{D10E5030-47DD-F84B-A85A-CB7F9EEF20B4}"/>
+    <hyperlink ref="D14" r:id="rId15" xr:uid="{AF10C3AC-DC3E-8F4B-A325-8137F8872365}"/>
+    <hyperlink ref="D15" r:id="rId16" xr:uid="{DAADFE53-28FB-BF47-B382-1AE9637B0AC9}"/>
+    <hyperlink ref="D16" r:id="rId17" xr:uid="{055B8A95-C64C-8344-8D9A-88ADC3E4C5A7}"/>
+    <hyperlink ref="D17" r:id="rId18" xr:uid="{557D8143-61B7-124A-9EC7-930988E1B3DE}"/>
+    <hyperlink ref="D18" r:id="rId19" xr:uid="{0B9459D2-C194-B546-B890-EDF488B5E508}"/>
+    <hyperlink ref="D19" r:id="rId20" xr:uid="{3E8CCC0C-C03D-0642-8D93-6D5E4E29B155}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1083,7 +1635,7 @@
   <cols>
     <col min="1" max="1" width="32.83203125" customWidth="1"/>
     <col min="2" max="2" width="33" customWidth="1"/>
-    <col min="3" max="3" width="25.83203125" customWidth="1"/>
+    <col min="3" max="3" width="58.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" s="3" customFormat="1" ht="22" x14ac:dyDescent="0.3">
@@ -1099,36 +1651,22 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
-        <v>45909</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
+        <v>45930</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
-        <v>45909</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
+        <v>45931</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" s="1">
-        <v>45910</v>
-      </c>
-      <c r="B4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4" t="s">
-        <v>27</v>
-      </c>
+      <c r="A4" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/EconJM_status.xlsx
+++ b/EconJM_status.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/jjgecon_dat/Dropbox/Work/Job Search/2025 EconJM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D65141B-4883-524A-8E44-F821B95E8907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3164717B-2A36-1A4F-B542-47157BF94DDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{6FE48536-7E5C-BF4C-9490-2A6392576298}"/>
   </bookViews>
@@ -16,6 +16,9 @@
     <sheet name="sum" sheetId="1" r:id="rId1"/>
     <sheet name="timeline" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sum!$A$1:$T$19</definedName>
+  </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -928,37 +931,31 @@
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="C4" t="s">
         <v>31</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="E4" t="s">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="F4" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="G4" t="s">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="H4" t="s">
         <v>25</v>
       </c>
       <c r="I4" s="1">
-        <v>45978</v>
+        <v>45931</v>
       </c>
       <c r="J4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K4" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="N4">
         <v>1</v>
@@ -967,7 +964,7 @@
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -975,34 +972,28 @@
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
         <v>31</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="E5" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="F5" t="s">
         <v>16</v>
       </c>
-      <c r="G5" t="s">
-        <v>41</v>
-      </c>
       <c r="H5" t="s">
         <v>25</v>
       </c>
       <c r="I5" s="1">
-        <v>45978</v>
+        <v>45931</v>
       </c>
       <c r="J5" t="s">
-        <v>20</v>
-      </c>
-      <c r="K5" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="N5">
         <v>1</v>
@@ -1011,7 +1002,7 @@
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1019,16 +1010,19 @@
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>50</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
       </c>
       <c r="C6" t="s">
         <v>31</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="E6" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="F6" t="s">
         <v>16</v>
@@ -1040,20 +1034,22 @@
         <v>25</v>
       </c>
       <c r="I6" s="1">
-        <v>45971</v>
+        <v>45940</v>
       </c>
       <c r="J6" t="s">
-        <v>20</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="L6" s="2"/>
+        <v>53</v>
+      </c>
+      <c r="K6" t="s">
+        <v>54</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>56</v>
+      </c>
       <c r="N6">
         <v>1</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6">
         <v>1</v>
@@ -1064,31 +1060,28 @@
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c r="C7" t="s">
         <v>31</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="E7" t="s">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="F7" t="s">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="H7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I7" s="1">
-        <v>45971</v>
-      </c>
-      <c r="K7" t="s">
-        <v>61</v>
+        <v>45940</v>
+      </c>
+      <c r="J7" t="s">
+        <v>82</v>
       </c>
       <c r="N7">
         <v>1</v>
@@ -1097,33 +1090,39 @@
         <v>0</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7">
         <v>0</v>
+      </c>
+      <c r="R7" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="S7" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="T7" s="6" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>50</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
+        <v>84</v>
       </c>
       <c r="C8" t="s">
         <v>31</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="E8" t="s">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="F8" t="s">
         <v>16</v>
       </c>
       <c r="G8" t="s">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="H8" t="s">
         <v>25</v>
@@ -1132,13 +1131,7 @@
         <v>45940</v>
       </c>
       <c r="J8" t="s">
-        <v>53</v>
-      </c>
-      <c r="K8" t="s">
-        <v>54</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="N8">
         <v>1</v>
@@ -1155,7 +1148,7 @@
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>57</v>
+        <v>101</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -1164,26 +1157,20 @@
         <v>31</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>58</v>
+        <v>102</v>
       </c>
       <c r="E9" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="F9" t="s">
         <v>16</v>
       </c>
-      <c r="H9" t="s">
-        <v>25</v>
-      </c>
       <c r="I9" s="1">
-        <v>45971</v>
+        <v>45940</v>
       </c>
       <c r="J9" t="s">
         <v>20</v>
       </c>
-      <c r="K9" t="s">
-        <v>60</v>
-      </c>
       <c r="N9">
         <v>1</v>
       </c>
@@ -1195,35 +1182,32 @@
       </c>
       <c r="Q9">
         <v>0</v>
+      </c>
+      <c r="T9" s="6" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
         <v>31</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="E10" t="s">
-        <v>64</v>
-      </c>
-      <c r="F10" t="s">
-        <v>16</v>
-      </c>
-      <c r="G10" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="H10" t="s">
-        <v>25</v>
+        <v>74</v>
       </c>
       <c r="I10" s="1">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="J10" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="N10">
         <v>1</v>
@@ -1232,7 +1216,7 @@
         <v>0</v>
       </c>
       <c r="P10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -1240,28 +1224,25 @@
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
         <v>31</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="E11" t="s">
-        <v>64</v>
-      </c>
-      <c r="F11" t="s">
-        <v>16</v>
+        <v>77</v>
       </c>
       <c r="H11" t="s">
-        <v>25</v>
+        <v>74</v>
       </c>
       <c r="I11" s="1">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="J11" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="N11">
         <v>1</v>
@@ -1270,7 +1251,7 @@
         <v>0</v>
       </c>
       <c r="P11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -1278,69 +1259,84 @@
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>70</v>
+        <v>87</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
       </c>
       <c r="C12" t="s">
         <v>31</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="E12" t="s">
-        <v>76</v>
+        <v>89</v>
+      </c>
+      <c r="F12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" t="s">
+        <v>24</v>
       </c>
       <c r="H12" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="I12" s="1">
         <v>45962</v>
       </c>
       <c r="J12" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="N12">
         <v>1</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="C13" t="s">
         <v>31</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="E13" t="s">
-        <v>77</v>
+        <v>98</v>
+      </c>
+      <c r="F13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" t="s">
+        <v>24</v>
       </c>
       <c r="H13" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="I13" s="1">
         <v>45962</v>
       </c>
       <c r="J13" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="N13">
         <v>1</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -1348,29 +1344,36 @@
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s">
         <v>31</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="E14" t="s">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="F14" t="s">
-        <v>81</v>
+        <v>16</v>
+      </c>
+      <c r="G14" t="s">
+        <v>24</v>
       </c>
       <c r="H14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I14" s="1">
-        <v>45940</v>
+        <v>45971</v>
       </c>
       <c r="J14" t="s">
-        <v>82</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="L14" s="2"/>
       <c r="N14">
         <v>1</v>
       </c>
@@ -1382,53 +1385,44 @@
       </c>
       <c r="Q14">
         <v>0</v>
-      </c>
-      <c r="R14" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="S14" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="T14" s="6" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>84</v>
+        <v>46</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
       </c>
       <c r="C15" t="s">
         <v>31</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="E15" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="F15" t="s">
-        <v>16</v>
-      </c>
-      <c r="G15" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="H15" t="s">
         <v>25</v>
       </c>
       <c r="I15" s="1">
-        <v>45940</v>
-      </c>
-      <c r="J15" t="s">
-        <v>86</v>
+        <v>45971</v>
+      </c>
+      <c r="K15" t="s">
+        <v>61</v>
       </c>
       <c r="N15">
         <v>1</v>
       </c>
       <c r="O15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -1436,7 +1430,7 @@
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>87</v>
+        <v>57</v>
       </c>
       <c r="B16">
         <v>1</v>
@@ -1445,40 +1439,40 @@
         <v>31</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>88</v>
+        <v>58</v>
       </c>
       <c r="E16" t="s">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="F16" t="s">
         <v>16</v>
       </c>
-      <c r="G16" t="s">
-        <v>24</v>
-      </c>
       <c r="H16" t="s">
         <v>25</v>
       </c>
       <c r="I16" s="1">
-        <v>45962</v>
+        <v>45971</v>
       </c>
       <c r="J16" t="s">
-        <v>90</v>
+        <v>20</v>
+      </c>
+      <c r="K16" t="s">
+        <v>60</v>
       </c>
       <c r="N16">
         <v>1</v>
       </c>
       <c r="O16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>92</v>
       </c>
@@ -1519,72 +1513,84 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>97</v>
+        <v>32</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
       </c>
       <c r="C18" t="s">
         <v>31</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>96</v>
+        <v>33</v>
       </c>
       <c r="E18" t="s">
-        <v>98</v>
+        <v>34</v>
       </c>
       <c r="F18" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="G18" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="H18" t="s">
         <v>25</v>
       </c>
       <c r="I18" s="1">
-        <v>45962</v>
+        <v>45978</v>
       </c>
       <c r="J18" t="s">
-        <v>99</v>
+        <v>20</v>
+      </c>
+      <c r="K18" t="s">
+        <v>20</v>
       </c>
       <c r="N18">
         <v>1</v>
       </c>
       <c r="O18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q18">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>101</v>
-      </c>
-      <c r="B19">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="C19" t="s">
         <v>31</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>102</v>
+        <v>39</v>
       </c>
       <c r="E19" t="s">
-        <v>103</v>
+        <v>40</v>
       </c>
       <c r="F19" t="s">
         <v>16</v>
       </c>
+      <c r="G19" t="s">
+        <v>41</v>
+      </c>
+      <c r="H19" t="s">
+        <v>25</v>
+      </c>
       <c r="I19" s="1">
-        <v>45940</v>
+        <v>45978</v>
       </c>
       <c r="J19" t="s">
         <v>20</v>
       </c>
+      <c r="K19" t="s">
+        <v>20</v>
+      </c>
       <c r="N19">
         <v>1</v>
       </c>
@@ -1597,32 +1603,34 @@
       <c r="Q19">
         <v>0</v>
       </c>
-      <c r="T19" s="6" t="s">
-        <v>83</v>
-      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:T19" xr:uid="{F7772053-9363-CA4A-A53F-040B7C700753}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T19">
+      <sortCondition ref="I1:I19"/>
+    </sortState>
+  </autoFilter>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{2FD67E99-97D4-6F4F-9C23-F094A4E233EB}"/>
     <hyperlink ref="D3" r:id="rId2" xr:uid="{C466BD2C-2D71-FD47-B267-C9470B42EAAE}"/>
-    <hyperlink ref="D4" r:id="rId3" xr:uid="{7E4575FB-8BA7-8343-9270-E933C2CF052A}"/>
-    <hyperlink ref="D5" r:id="rId4" xr:uid="{7DE2DCC0-6910-AF4A-ADA1-2F0A7CE7A46A}"/>
-    <hyperlink ref="D6" r:id="rId5" xr:uid="{9F5721B0-AA94-954A-B077-53D294EE0006}"/>
-    <hyperlink ref="K6" r:id="rId6" xr:uid="{E9AC54D1-D414-9A4A-8F10-99810DECDF26}"/>
-    <hyperlink ref="D7" r:id="rId7" xr:uid="{3DA7C680-99C0-9744-A5E3-8B70509CE1C7}"/>
-    <hyperlink ref="D8" r:id="rId8" xr:uid="{F2E0FCCF-BB13-0240-931E-487798981CC9}"/>
-    <hyperlink ref="D9" r:id="rId9" xr:uid="{DF00AD54-0273-B54C-B9CE-46119BBDF932}"/>
-    <hyperlink ref="D10" r:id="rId10" display="American Uiversity" xr:uid="{4368F24E-5E4F-B944-AB45-4045D2296D5A}"/>
-    <hyperlink ref="D11" r:id="rId11" display="American Uiversity" xr:uid="{0B28A4E3-9367-5B4E-821E-8878EF62879B}"/>
-    <hyperlink ref="L8" r:id="rId12" xr:uid="{F8BB08B3-A5E4-0244-9B87-74DC5560EA9C}"/>
-    <hyperlink ref="D12" r:id="rId13" xr:uid="{1A802253-386D-0248-869E-8A0EA127D432}"/>
-    <hyperlink ref="D13" r:id="rId14" xr:uid="{D10E5030-47DD-F84B-A85A-CB7F9EEF20B4}"/>
-    <hyperlink ref="D14" r:id="rId15" xr:uid="{AF10C3AC-DC3E-8F4B-A325-8137F8872365}"/>
-    <hyperlink ref="D15" r:id="rId16" xr:uid="{DAADFE53-28FB-BF47-B382-1AE9637B0AC9}"/>
-    <hyperlink ref="D16" r:id="rId17" xr:uid="{055B8A95-C64C-8344-8D9A-88ADC3E4C5A7}"/>
+    <hyperlink ref="D18" r:id="rId3" xr:uid="{7E4575FB-8BA7-8343-9270-E933C2CF052A}"/>
+    <hyperlink ref="D19" r:id="rId4" xr:uid="{7DE2DCC0-6910-AF4A-ADA1-2F0A7CE7A46A}"/>
+    <hyperlink ref="D14" r:id="rId5" xr:uid="{9F5721B0-AA94-954A-B077-53D294EE0006}"/>
+    <hyperlink ref="K14" r:id="rId6" xr:uid="{E9AC54D1-D414-9A4A-8F10-99810DECDF26}"/>
+    <hyperlink ref="D15" r:id="rId7" xr:uid="{3DA7C680-99C0-9744-A5E3-8B70509CE1C7}"/>
+    <hyperlink ref="D6" r:id="rId8" xr:uid="{F2E0FCCF-BB13-0240-931E-487798981CC9}"/>
+    <hyperlink ref="D16" r:id="rId9" xr:uid="{DF00AD54-0273-B54C-B9CE-46119BBDF932}"/>
+    <hyperlink ref="D4" r:id="rId10" display="American Uiversity" xr:uid="{4368F24E-5E4F-B944-AB45-4045D2296D5A}"/>
+    <hyperlink ref="D5" r:id="rId11" display="American Uiversity" xr:uid="{0B28A4E3-9367-5B4E-821E-8878EF62879B}"/>
+    <hyperlink ref="L6" r:id="rId12" xr:uid="{F8BB08B3-A5E4-0244-9B87-74DC5560EA9C}"/>
+    <hyperlink ref="D10" r:id="rId13" xr:uid="{1A802253-386D-0248-869E-8A0EA127D432}"/>
+    <hyperlink ref="D11" r:id="rId14" xr:uid="{D10E5030-47DD-F84B-A85A-CB7F9EEF20B4}"/>
+    <hyperlink ref="D7" r:id="rId15" xr:uid="{AF10C3AC-DC3E-8F4B-A325-8137F8872365}"/>
+    <hyperlink ref="D8" r:id="rId16" xr:uid="{DAADFE53-28FB-BF47-B382-1AE9637B0AC9}"/>
+    <hyperlink ref="D12" r:id="rId17" xr:uid="{055B8A95-C64C-8344-8D9A-88ADC3E4C5A7}"/>
     <hyperlink ref="D17" r:id="rId18" xr:uid="{557D8143-61B7-124A-9EC7-930988E1B3DE}"/>
-    <hyperlink ref="D18" r:id="rId19" xr:uid="{0B9459D2-C194-B546-B890-EDF488B5E508}"/>
-    <hyperlink ref="D19" r:id="rId20" xr:uid="{3E8CCC0C-C03D-0642-8D93-6D5E4E29B155}"/>
+    <hyperlink ref="D13" r:id="rId19" xr:uid="{0B9459D2-C194-B546-B890-EDF488B5E508}"/>
+    <hyperlink ref="D9" r:id="rId20" xr:uid="{3E8CCC0C-C03D-0642-8D93-6D5E4E29B155}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/EconJM_status.xlsx
+++ b/EconJM_status.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/jjgecon_dat/Dropbox/Work/Job Search/2025 EconJM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E2A8629-1269-7048-A6DF-9B9AC88A8A79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E04F9107-138F-F349-A1FB-AB9A66B90C8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{6FE48536-7E5C-BF4C-9490-2A6392576298}"/>
   </bookViews>

--- a/EconJM_status.xlsx
+++ b/EconJM_status.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/jjgecon_dat/Dropbox/Work/Job Search/2025 EconJM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E04F9107-138F-F349-A1FB-AB9A66B90C8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A67BBC1-4C1F-3742-90BA-108A88963698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{6FE48536-7E5C-BF4C-9490-2A6392576298}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" activeTab="2" xr2:uid="{6FE48536-7E5C-BF4C-9490-2A6392576298}"/>
   </bookViews>
   <sheets>
     <sheet name="sum" sheetId="1" r:id="rId1"/>
     <sheet name="timeline" sheetId="2" r:id="rId2"/>
+    <sheet name="stats" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sum!$A$1:$Y$19</definedName>
@@ -682,7 +683,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1030" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1058" uniqueCount="417">
   <si>
     <t>add_id</t>
   </si>
@@ -1940,12 +1941,39 @@
   <si>
     <t>Florian Scheuer by email (florian.scheuer@uzh.ch)</t>
   </si>
+  <si>
+    <t>Total apps</t>
+  </si>
+  <si>
+    <t>good match</t>
+  </si>
+  <si>
+    <t>top ranked</t>
+  </si>
+  <si>
+    <t>Outcomes</t>
+  </si>
+  <si>
+    <t>no news</t>
+  </si>
+  <si>
+    <t>rejected</t>
+  </si>
+  <si>
+    <t>interview</t>
+  </si>
+  <si>
+    <t>fly out</t>
+  </si>
+  <si>
+    <t>offer</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1996,6 +2024,20 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -2020,11 +2062,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
@@ -2043,19 +2086,41 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="62">
+  <dxfs count="63">
     <dxf>
       <font>
-        <color rgb="FF006100"/>
+        <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2071,25 +2136,43 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
+        <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i/>
-        <color theme="0" tint="-0.24994659260841701"/>
+        <color rgb="FF9C0006"/>
       </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
-        <color theme="5" tint="0.79998168889431442"/>
+        <color rgb="FF9C0006"/>
       </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -24262,7 +24345,7 @@
         <v>372</v>
       </c>
       <c r="D16" t="s">
-        <v>28</v>
+        <v>104</v>
       </c>
       <c r="H16" t="s">
         <v>371</v>
@@ -24850,7 +24933,7 @@
         <v>350</v>
       </c>
       <c r="D30" t="s">
-        <v>28</v>
+        <v>104</v>
       </c>
       <c r="H30" t="s">
         <v>349</v>
@@ -25355,7 +25438,7 @@
         <v>377</v>
       </c>
       <c r="D42" t="s">
-        <v>28</v>
+        <v>104</v>
       </c>
       <c r="H42" t="s">
         <v>378</v>
@@ -25393,7 +25476,7 @@
         <v>381</v>
       </c>
       <c r="D43" t="s">
-        <v>28</v>
+        <v>104</v>
       </c>
       <c r="H43" t="s">
         <v>380</v>
@@ -26234,7 +26317,7 @@
         <v>97</v>
       </c>
       <c r="D63" t="s">
-        <v>28</v>
+        <v>104</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>98</v>
@@ -26276,7 +26359,7 @@
         <v>101</v>
       </c>
       <c r="D64" t="s">
-        <v>28</v>
+        <v>104</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>102</v>
@@ -26365,7 +26448,7 @@
         <v>374</v>
       </c>
       <c r="D66" t="s">
-        <v>28</v>
+        <v>104</v>
       </c>
       <c r="H66" t="s">
         <v>375</v>
@@ -28242,7 +28325,7 @@
         <v>389</v>
       </c>
       <c r="D109" t="s">
-        <v>28</v>
+        <v>104</v>
       </c>
       <c r="H109" t="s">
         <v>388</v>
@@ -29148,32 +29231,32 @@
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="A1:B1048576">
-    <cfRule type="duplicateValues" dxfId="61" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:B22">
-    <cfRule type="duplicateValues" dxfId="60" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A61:B61">
-    <cfRule type="duplicateValues" dxfId="59" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:D1048576">
-    <cfRule type="containsText" dxfId="58" priority="1" operator="containsText" text="abandoned">
+    <cfRule type="containsText" dxfId="59" priority="1" operator="containsText" text="abandoned">
       <formula>NOT(ISERROR(SEARCH("abandoned",D1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="57" priority="3" operator="containsText" text="late app">
+    <cfRule type="containsText" dxfId="58" priority="3" operator="containsText" text="late app">
       <formula>NOT(ISERROR(SEARCH("late app",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J78:J80 J83:J89 D1:E1 J92:J112 D2:G1048576 J115:J124 J126:J128 J130:J131 L87:L131">
-    <cfRule type="containsText" dxfId="56" priority="6" operator="containsText" text="completed">
+    <cfRule type="containsText" dxfId="57" priority="6" operator="containsText" text="completed">
       <formula>NOT(ISERROR(SEARCH("completed",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J78:J80 J83:J89 J92:J112 F1:G1048576 J115:J124 J126:J128 J130:J131 L87:L131">
-    <cfRule type="containsText" dxfId="55" priority="4" operator="containsText" text="NO">
+    <cfRule type="containsText" dxfId="56" priority="4" operator="containsText" text="NO">
       <formula>NOT(ISERROR(SEARCH("NO",F1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="54" priority="5" operator="containsText" text="YES">
+    <cfRule type="containsText" dxfId="55" priority="5" operator="containsText" text="YES">
       <formula>NOT(ISERROR(SEARCH("YES",F1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29272,7 +29355,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923E81FA-B875-3C4E-A189-1A21268FA086}">
-  <dimension ref="A1:C66"/>
+  <dimension ref="A1:C77"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="32.83203125" customWidth="1"/>
@@ -29964,129 +30047,394 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A66" s="1">
-        <v>45952</v>
+        <v>45953</v>
+      </c>
+      <c r="B66" t="s">
+        <v>389</v>
       </c>
       <c r="C66" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A67" s="1">
+        <v>45953</v>
+      </c>
+      <c r="B67" t="s">
+        <v>372</v>
+      </c>
+      <c r="C67" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A68" s="1">
+        <v>45953</v>
+      </c>
+      <c r="B68" t="s">
+        <v>350</v>
+      </c>
+      <c r="C68" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A69" s="1">
+        <v>45953</v>
+      </c>
+      <c r="B69" t="s">
+        <v>377</v>
+      </c>
+      <c r="C69" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A70" s="1">
+        <v>45953</v>
+      </c>
+      <c r="B70" t="s">
+        <v>381</v>
+      </c>
+      <c r="C70" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A71" s="1">
+        <v>45953</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C71" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A72" s="1">
+        <v>45953</v>
+      </c>
+      <c r="B72" t="s">
+        <v>101</v>
+      </c>
+      <c r="C72" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A73" s="1">
+        <v>45953</v>
+      </c>
+      <c r="B73" t="s">
+        <v>374</v>
+      </c>
+      <c r="C73" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A74" s="1">
+        <v>45953</v>
+      </c>
+      <c r="C74" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A75" s="1">
+        <v>45953</v>
+      </c>
+      <c r="C75" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A76" s="1">
+        <v>45953</v>
+      </c>
+      <c r="C76" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A77" s="1">
+        <v>45953</v>
+      </c>
+      <c r="C77" t="s">
         <v>105</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5">
-    <cfRule type="duplicateValues" dxfId="53" priority="48"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="58"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B10">
-    <cfRule type="duplicateValues" dxfId="51" priority="46"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B11">
-    <cfRule type="duplicateValues" dxfId="49" priority="44"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12">
-    <cfRule type="duplicateValues" dxfId="47" priority="42"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15">
-    <cfRule type="duplicateValues" dxfId="45" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16">
-    <cfRule type="duplicateValues" dxfId="43" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17">
-    <cfRule type="duplicateValues" dxfId="42" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B18">
-    <cfRule type="duplicateValues" dxfId="40" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B19">
-    <cfRule type="duplicateValues" dxfId="38" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:B23">
-    <cfRule type="duplicateValues" dxfId="37" priority="32"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B24">
-    <cfRule type="duplicateValues" dxfId="35" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B27">
-    <cfRule type="duplicateValues" dxfId="33" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28">
-    <cfRule type="duplicateValues" dxfId="31" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29">
-    <cfRule type="duplicateValues" dxfId="30" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="28" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31">
-    <cfRule type="duplicateValues" dxfId="27" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="duplicateValues" dxfId="26" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33">
-    <cfRule type="duplicateValues" dxfId="25" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="24" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35">
-    <cfRule type="duplicateValues" dxfId="23" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37">
-    <cfRule type="duplicateValues" dxfId="22" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38">
-    <cfRule type="duplicateValues" dxfId="21" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B42">
-    <cfRule type="duplicateValues" dxfId="20" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43">
-    <cfRule type="duplicateValues" dxfId="19" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44:B45">
-    <cfRule type="duplicateValues" dxfId="18" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B46">
-    <cfRule type="duplicateValues" dxfId="17" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B48">
-    <cfRule type="duplicateValues" dxfId="16" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B49">
-    <cfRule type="duplicateValues" dxfId="15" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B51">
-    <cfRule type="duplicateValues" dxfId="14" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B52">
-    <cfRule type="duplicateValues" dxfId="13" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B58">
-    <cfRule type="duplicateValues" dxfId="12" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B59">
-    <cfRule type="duplicateValues" dxfId="11" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B63">
-    <cfRule type="duplicateValues" dxfId="10" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B64">
-    <cfRule type="duplicateValues" dxfId="9" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B66">
-    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B67">
+    <cfRule type="duplicateValues" dxfId="8" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B67">
+    <cfRule type="duplicateValues" dxfId="7" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B68">
+    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B69">
+    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B70">
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B72">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B73">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{852B2CA5-879F-3640-8AF9-56395EF3FA0F}">
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="15.83203125" style="14" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" style="18"/>
+    <col min="3" max="3" width="10.83203125" style="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="27" x14ac:dyDescent="0.35">
+      <c r="A1" s="13" t="s">
+        <v>408</v>
+      </c>
+      <c r="B1" s="17">
+        <f>COUNTA(sum!A:A) -1</f>
+        <v>130</v>
+      </c>
+      <c r="C1" s="16">
+        <f>COUNTIF(sum!D:D, "completed")/B1</f>
+        <v>0.47692307692307695</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="15" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2" s="18">
+        <f>COUNTA(sum!C:C) -1</f>
+        <v>40</v>
+      </c>
+      <c r="C2" s="12">
+        <f>COUNTIFS(sum!D:D,"completed", sum!C:C, "&lt;&gt;") / B2</f>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="15" t="s">
+        <v>410</v>
+      </c>
+      <c r="B3" s="18">
+        <f>COUNTA(sum!F:F) -1</f>
+        <v>28</v>
+      </c>
+      <c r="C3" s="12">
+        <f>COUNTIFS(sum!D:D,"completed", sum!F:F, "&lt;&gt;") / B3</f>
+        <v>0.35714285714285715</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="27" x14ac:dyDescent="0.35">
+      <c r="A5" s="13" t="s">
+        <v>411</v>
+      </c>
+      <c r="B5" s="17">
+        <f>COUNTA(sum!E:E) -1</f>
+        <v>0</v>
+      </c>
+      <c r="C5" s="16">
+        <f>B5/B1</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="15" t="s">
+        <v>412</v>
+      </c>
+      <c r="B6" s="18">
+        <f>COUNTIFS(sum!E:E,"no news")</f>
+        <v>0</v>
+      </c>
+      <c r="C6" s="12" t="e">
+        <f>B6/$B$5</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="15" t="s">
+        <v>413</v>
+      </c>
+      <c r="B7" s="18">
+        <f>COUNTIFS(sum!E:E,"rejected")</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="12" t="e">
+        <f t="shared" ref="C7:C10" si="0">B7/$B$5</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="15" t="s">
+        <v>414</v>
+      </c>
+      <c r="B8" s="18">
+        <f>COUNTIFS(sum!E:E,"interview")</f>
+        <v>0</v>
+      </c>
+      <c r="C8" s="12" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="15" t="s">
+        <v>415</v>
+      </c>
+      <c r="B9" s="18">
+        <f>COUNTIFS(sum!E:E,"fly out")</f>
+        <v>0</v>
+      </c>
+      <c r="C9" s="12" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="15" t="s">
+        <v>416</v>
+      </c>
+      <c r="B10" s="18">
+        <f>COUNTIFS(sum!E:E,"offer")</f>
+        <v>0</v>
+      </c>
+      <c r="C10" s="12" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/EconJM_status.xlsx
+++ b/EconJM_status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/jjgecon_dat/Dropbox/Work/Job Search/2025 EconJM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A67BBC1-4C1F-3742-90BA-108A88963698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F81CD67-EA7F-294E-AAE1-F7DB1362D674}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" activeTab="2" xr2:uid="{6FE48536-7E5C-BF4C-9490-2A6392576298}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" activeTab="1" xr2:uid="{6FE48536-7E5C-BF4C-9490-2A6392576298}"/>
   </bookViews>
   <sheets>
     <sheet name="sum" sheetId="1" r:id="rId1"/>
@@ -683,7 +683,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1058" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1060" uniqueCount="417">
   <si>
     <t>add_id</t>
   </si>
@@ -2113,7 +2113,37 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="63">
+  <dxfs count="66">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -26486,7 +26516,7 @@
         <v>402</v>
       </c>
       <c r="D67" t="s">
-        <v>28</v>
+        <v>104</v>
       </c>
       <c r="H67" t="s">
         <v>403</v>
@@ -26521,7 +26551,7 @@
         <v>327</v>
       </c>
       <c r="D68" t="s">
-        <v>28</v>
+        <v>104</v>
       </c>
       <c r="H68" t="s">
         <v>404</v>
@@ -26559,7 +26589,7 @@
         <v>405</v>
       </c>
       <c r="D69" t="s">
-        <v>28</v>
+        <v>104</v>
       </c>
       <c r="H69" t="s">
         <v>406</v>
@@ -29231,32 +29261,32 @@
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="A1:B1048576">
-    <cfRule type="duplicateValues" dxfId="62" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:B22">
-    <cfRule type="duplicateValues" dxfId="61" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A61:B61">
-    <cfRule type="duplicateValues" dxfId="60" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:D1048576">
-    <cfRule type="containsText" dxfId="59" priority="1" operator="containsText" text="abandoned">
+    <cfRule type="containsText" dxfId="62" priority="1" operator="containsText" text="abandoned">
       <formula>NOT(ISERROR(SEARCH("abandoned",D1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="58" priority="3" operator="containsText" text="late app">
+    <cfRule type="containsText" dxfId="61" priority="3" operator="containsText" text="late app">
       <formula>NOT(ISERROR(SEARCH("late app",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J78:J80 J83:J89 D1:E1 J92:J112 D2:G1048576 J115:J124 J126:J128 J130:J131 L87:L131">
-    <cfRule type="containsText" dxfId="57" priority="6" operator="containsText" text="completed">
+    <cfRule type="containsText" dxfId="60" priority="6" operator="containsText" text="completed">
       <formula>NOT(ISERROR(SEARCH("completed",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J78:J80 J83:J89 J92:J112 F1:G1048576 J115:J124 J126:J128 J130:J131 L87:L131">
-    <cfRule type="containsText" dxfId="56" priority="4" operator="containsText" text="NO">
+    <cfRule type="containsText" dxfId="59" priority="4" operator="containsText" text="NO">
       <formula>NOT(ISERROR(SEARCH("NO",F1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="55" priority="5" operator="containsText" text="YES">
+    <cfRule type="containsText" dxfId="58" priority="5" operator="containsText" text="YES">
       <formula>NOT(ISERROR(SEARCH("YES",F1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29355,7 +29385,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923E81FA-B875-3C4E-A189-1A21268FA086}">
-  <dimension ref="A1:C77"/>
+  <dimension ref="A1:C76"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="32.83203125" customWidth="1"/>
@@ -30137,6 +30167,9 @@
       <c r="A74" s="1">
         <v>45953</v>
       </c>
+      <c r="B74" t="s">
+        <v>402</v>
+      </c>
       <c r="C74" t="s">
         <v>105</v>
       </c>
@@ -30145,6 +30178,9 @@
       <c r="A75" s="1">
         <v>45953</v>
       </c>
+      <c r="B75" t="s">
+        <v>327</v>
+      </c>
       <c r="C75" t="s">
         <v>105</v>
       </c>
@@ -30153,154 +30189,158 @@
       <c r="A76" s="1">
         <v>45953</v>
       </c>
+      <c r="B76" t="s">
+        <v>405</v>
+      </c>
       <c r="C76" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A77" s="1">
-        <v>45953</v>
-      </c>
-      <c r="C77" t="s">
         <v>105</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5">
-    <cfRule type="duplicateValues" dxfId="54" priority="57"/>
-    <cfRule type="duplicateValues" dxfId="53" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="61"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B10">
-    <cfRule type="duplicateValues" dxfId="52" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="51" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="59"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B11">
-    <cfRule type="duplicateValues" dxfId="50" priority="53"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12">
-    <cfRule type="duplicateValues" dxfId="48" priority="51"/>
-    <cfRule type="duplicateValues" dxfId="47" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15">
+    <cfRule type="duplicateValues" dxfId="49" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="53"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B16">
+    <cfRule type="duplicateValues" dxfId="47" priority="51"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B17">
     <cfRule type="duplicateValues" dxfId="46" priority="49"/>
     <cfRule type="duplicateValues" dxfId="45" priority="50"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B16">
-    <cfRule type="duplicateValues" dxfId="44" priority="48"/>
+  <conditionalFormatting sqref="B18">
+    <cfRule type="duplicateValues" dxfId="44" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="48"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B17">
-    <cfRule type="duplicateValues" dxfId="43" priority="46"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="47"/>
+  <conditionalFormatting sqref="B19">
+    <cfRule type="duplicateValues" dxfId="42" priority="46"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B18">
+  <conditionalFormatting sqref="B22:B23">
     <cfRule type="duplicateValues" dxfId="41" priority="44"/>
     <cfRule type="duplicateValues" dxfId="40" priority="45"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B19">
-    <cfRule type="duplicateValues" dxfId="39" priority="43"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B22:B23">
-    <cfRule type="duplicateValues" dxfId="38" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="42"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B24">
-    <cfRule type="duplicateValues" dxfId="36" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B27">
+    <cfRule type="duplicateValues" dxfId="37" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="41"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B28">
+    <cfRule type="duplicateValues" dxfId="35" priority="39"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B29">
     <cfRule type="duplicateValues" dxfId="34" priority="37"/>
     <cfRule type="duplicateValues" dxfId="33" priority="38"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B28">
+  <conditionalFormatting sqref="B30">
     <cfRule type="duplicateValues" dxfId="32" priority="36"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B29">
-    <cfRule type="duplicateValues" dxfId="31" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="35"/>
+  <conditionalFormatting sqref="B31">
+    <cfRule type="duplicateValues" dxfId="31" priority="35"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B30">
+  <conditionalFormatting sqref="B32">
+    <cfRule type="duplicateValues" dxfId="30" priority="34"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B33">
     <cfRule type="duplicateValues" dxfId="29" priority="33"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B31">
+  <conditionalFormatting sqref="B34">
     <cfRule type="duplicateValues" dxfId="28" priority="32"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B32">
+  <conditionalFormatting sqref="B35">
     <cfRule type="duplicateValues" dxfId="27" priority="31"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B33">
+  <conditionalFormatting sqref="B37">
     <cfRule type="duplicateValues" dxfId="26" priority="30"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B34">
+  <conditionalFormatting sqref="B38">
     <cfRule type="duplicateValues" dxfId="25" priority="29"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B35">
+  <conditionalFormatting sqref="B42">
     <cfRule type="duplicateValues" dxfId="24" priority="28"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B37">
+  <conditionalFormatting sqref="B43">
     <cfRule type="duplicateValues" dxfId="23" priority="27"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B38">
+  <conditionalFormatting sqref="B44:B45">
     <cfRule type="duplicateValues" dxfId="22" priority="26"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B42">
+  <conditionalFormatting sqref="B46">
     <cfRule type="duplicateValues" dxfId="21" priority="25"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B43">
+  <conditionalFormatting sqref="B48">
     <cfRule type="duplicateValues" dxfId="20" priority="24"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B44:B45">
+  <conditionalFormatting sqref="B49">
     <cfRule type="duplicateValues" dxfId="19" priority="23"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B46">
+  <conditionalFormatting sqref="B51">
     <cfRule type="duplicateValues" dxfId="18" priority="22"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B48">
+  <conditionalFormatting sqref="B52">
     <cfRule type="duplicateValues" dxfId="17" priority="21"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B49">
-    <cfRule type="duplicateValues" dxfId="16" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B51">
-    <cfRule type="duplicateValues" dxfId="15" priority="19"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B52">
-    <cfRule type="duplicateValues" dxfId="14" priority="18"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B58">
-    <cfRule type="duplicateValues" dxfId="13" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B59">
-    <cfRule type="duplicateValues" dxfId="12" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B63">
-    <cfRule type="duplicateValues" dxfId="11" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B64">
-    <cfRule type="duplicateValues" dxfId="10" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B66">
+    <cfRule type="duplicateValues" dxfId="12" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B67">
+    <cfRule type="duplicateValues" dxfId="11" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B67">
+    <cfRule type="duplicateValues" dxfId="10" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B68">
     <cfRule type="duplicateValues" dxfId="9" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="8" priority="8"/>
+  <conditionalFormatting sqref="B69">
+    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="7" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B68">
+  <conditionalFormatting sqref="B70">
     <cfRule type="duplicateValues" dxfId="6" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B69">
+  <conditionalFormatting sqref="B72">
     <cfRule type="duplicateValues" dxfId="5" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B70">
+  <conditionalFormatting sqref="B73">
     <cfRule type="duplicateValues" dxfId="3" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B72">
+  <conditionalFormatting sqref="B74">
     <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B73">
+  <conditionalFormatting sqref="B75">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B76">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -30327,7 +30367,7 @@
       </c>
       <c r="C1" s="16">
         <f>COUNTIF(sum!D:D, "completed")/B1</f>
-        <v>0.47692307692307695</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">

--- a/EconJM_status.xlsx
+++ b/EconJM_status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/jjgecon_dat/Dropbox/Work/Job Search/2025 EconJM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F81CD67-EA7F-294E-AAE1-F7DB1362D674}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4185D350-D4E5-8C4C-BDC1-76E497CF2BA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" activeTab="1" xr2:uid="{6FE48536-7E5C-BF4C-9490-2A6392576298}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{6FE48536-7E5C-BF4C-9490-2A6392576298}"/>
   </bookViews>
   <sheets>
     <sheet name="sum" sheetId="1" r:id="rId1"/>
@@ -683,7 +683,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1060" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1073" uniqueCount="418">
   <si>
     <t>add_id</t>
   </si>
@@ -1967,6 +1967,9 @@
   </si>
   <si>
     <t>offer</t>
+  </si>
+  <si>
+    <t>julia cage as a potential network</t>
   </si>
 </sst>
 </file>
@@ -2113,7 +2116,17 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="66">
+  <dxfs count="67">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -23679,13 +23692,16 @@
   <dimension ref="A1:Y131"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="19.6640625" customWidth="1"/>
-    <col min="4" max="7" width="18.33203125" customWidth="1"/>
-    <col min="8" max="8" width="37.33203125" customWidth="1"/>
-    <col min="9" max="11" width="19.5" customWidth="1"/>
-    <col min="12" max="15" width="19.33203125" customWidth="1"/>
-    <col min="16" max="16" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="19.6640625" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" customWidth="1"/>
+    <col min="4" max="4" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.6640625" customWidth="1"/>
+    <col min="7" max="7" width="19.33203125" customWidth="1"/>
+    <col min="8" max="11" width="18.33203125" customWidth="1"/>
+    <col min="12" max="12" width="37.33203125" customWidth="1"/>
+    <col min="13" max="15" width="19.5" customWidth="1"/>
+    <col min="16" max="17" width="19.33203125" customWidth="1"/>
     <col min="18" max="18" width="18.1640625" customWidth="1"/>
     <col min="19" max="19" width="23.5" customWidth="1"/>
     <col min="20" max="20" width="23.5" bestFit="1" customWidth="1"/>
@@ -23704,49 +23720,49 @@
         <v>284</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="G1" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="M1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="N1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>122</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>6</v>
       </c>
       <c r="R1" s="3" t="s">
         <v>47</v>
@@ -23777,35 +23793,35 @@
       <c r="A2" t="s">
         <v>157</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="1">
+        <v>45902</v>
+      </c>
+      <c r="D2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E2" t="s">
+        <v>158</v>
+      </c>
+      <c r="F2">
         <v>1</v>
       </c>
-      <c r="D2" t="s">
+      <c r="H2" t="s">
         <v>137</v>
       </c>
-      <c r="H2" t="s">
+      <c r="L2" t="s">
         <v>156</v>
       </c>
-      <c r="I2" t="e" vm="1">
+      <c r="M2" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="J2" t="s">
+      <c r="N2" t="s">
         <v>15</v>
       </c>
-      <c r="L2" t="s">
+      <c r="P2" t="s">
         <v>23</v>
       </c>
-      <c r="M2" s="1">
+      <c r="Q2" s="1">
         <v>45902</v>
-      </c>
-      <c r="N2" s="1">
-        <v>45902</v>
-      </c>
-      <c r="P2" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>158</v>
       </c>
       <c r="T2">
         <v>1</v>
@@ -23821,36 +23837,36 @@
       <c r="A3" t="s">
         <v>11</v>
       </c>
+      <c r="C3" s="1">
+        <v>45931</v>
+      </c>
       <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="1"/>
+      <c r="H3" t="s">
         <v>104</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I3" t="e" vm="2">
+      <c r="M3" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="J3" t="s">
+      <c r="N3" t="s">
         <v>15</v>
       </c>
-      <c r="K3" t="s">
+      <c r="O3" t="s">
         <v>22</v>
       </c>
-      <c r="L3" t="s">
+      <c r="P3" t="s">
         <v>23</v>
       </c>
-      <c r="M3" s="1">
+      <c r="Q3" s="1">
         <v>45931</v>
-      </c>
-      <c r="N3" s="1">
-        <v>45931</v>
-      </c>
-      <c r="O3" s="1"/>
-      <c r="P3" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>19</v>
       </c>
       <c r="T3">
         <v>1</v>
@@ -23866,36 +23882,36 @@
       <c r="A4" t="s">
         <v>21</v>
       </c>
+      <c r="C4" s="1">
+        <v>45931</v>
+      </c>
       <c r="D4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="1"/>
+      <c r="H4" t="s">
         <v>104</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I4" t="e" vm="3">
+      <c r="M4" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
-      <c r="J4" t="s">
+      <c r="N4" t="s">
         <v>15</v>
       </c>
-      <c r="K4" t="s">
+      <c r="O4" t="s">
         <v>22</v>
       </c>
-      <c r="L4" t="s">
+      <c r="P4" t="s">
         <v>24</v>
       </c>
-      <c r="M4" s="1">
+      <c r="Q4" s="1">
         <v>45931</v>
-      </c>
-      <c r="N4" s="1">
-        <v>45931</v>
-      </c>
-      <c r="O4" s="1"/>
-      <c r="P4" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>19</v>
       </c>
       <c r="T4">
         <v>1</v>
@@ -23911,33 +23927,33 @@
       <c r="A5" t="s">
         <v>53</v>
       </c>
-      <c r="D5" t="s">
+      <c r="C5" s="1">
+        <v>45931</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G5" s="1"/>
+      <c r="H5" t="s">
         <v>104</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="L5" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="I5" t="e" vm="4">
+      <c r="M5" t="e" vm="4">
         <v>#VALUE!</v>
       </c>
-      <c r="J5" t="s">
+      <c r="N5" t="s">
         <v>15</v>
       </c>
-      <c r="K5" t="s">
+      <c r="O5" t="s">
         <v>55</v>
       </c>
-      <c r="L5" t="s">
+      <c r="P5" t="s">
         <v>23</v>
       </c>
-      <c r="M5" s="1">
+      <c r="Q5" s="1">
         <v>45931</v>
-      </c>
-      <c r="N5" s="1">
-        <v>45931</v>
-      </c>
-      <c r="O5" s="1"/>
-      <c r="P5" s="2" t="s">
-        <v>56</v>
       </c>
       <c r="T5">
         <v>1</v>
@@ -23953,30 +23969,30 @@
       <c r="A6" t="s">
         <v>58</v>
       </c>
+      <c r="C6" s="1">
+        <v>45931</v>
+      </c>
       <c r="D6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G6" s="1"/>
+      <c r="H6" t="s">
         <v>161</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="L6" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="I6" t="e" vm="4">
+      <c r="M6" t="e" vm="4">
         <v>#VALUE!</v>
       </c>
-      <c r="J6" t="s">
+      <c r="N6" t="s">
         <v>15</v>
       </c>
-      <c r="L6" t="s">
+      <c r="P6" t="s">
         <v>23</v>
       </c>
-      <c r="M6" s="1">
+      <c r="Q6" s="1">
         <v>45931</v>
-      </c>
-      <c r="N6" s="1">
-        <v>45931</v>
-      </c>
-      <c r="O6" s="1"/>
-      <c r="P6" t="s">
-        <v>59</v>
       </c>
       <c r="T6">
         <v>1</v>
@@ -23992,39 +24008,39 @@
       <c r="A7" t="s">
         <v>43</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="1">
+        <v>45940</v>
+      </c>
+      <c r="D7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7">
         <v>1</v>
       </c>
-      <c r="D7" t="s">
+      <c r="G7" s="1"/>
+      <c r="H7" t="s">
         <v>161</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="L7" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="I7" t="e" vm="5">
+      <c r="M7" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
-      <c r="J7" t="s">
+      <c r="N7" t="s">
         <v>15</v>
       </c>
-      <c r="K7" t="s">
+      <c r="O7" t="s">
         <v>22</v>
       </c>
-      <c r="L7" t="s">
+      <c r="P7" t="s">
         <v>23</v>
       </c>
-      <c r="M7" s="1">
+      <c r="Q7" s="1">
         <v>45940</v>
-      </c>
-      <c r="N7" s="1">
-        <v>45940</v>
-      </c>
-      <c r="O7" s="1"/>
-      <c r="P7" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>46</v>
       </c>
       <c r="R7" s="2" t="s">
         <v>48</v>
@@ -24043,38 +24059,38 @@
       <c r="A8" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="1">
+        <v>45940</v>
+      </c>
+      <c r="D8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8">
         <v>1</v>
       </c>
-      <c r="D8" t="s">
+      <c r="G8" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="H8" t="s">
         <v>104</v>
       </c>
-      <c r="F8" t="s">
+      <c r="J8" t="s">
         <v>318</v>
       </c>
-      <c r="G8" s="1">
+      <c r="K8" s="1">
         <v>45976</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="L8" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="I8" t="e" vm="6">
+      <c r="M8" t="e" vm="6">
         <v>#VALUE!</v>
       </c>
-      <c r="J8" t="s">
+      <c r="N8" t="s">
         <v>15</v>
       </c>
-      <c r="M8" s="1">
+      <c r="Q8" s="1">
         <v>45940</v>
-      </c>
-      <c r="N8" s="1">
-        <v>45940</v>
-      </c>
-      <c r="O8" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="P8" t="s">
-        <v>19</v>
       </c>
       <c r="T8">
         <v>1</v>
@@ -24090,30 +24106,30 @@
       <c r="A9" t="s">
         <v>66</v>
       </c>
+      <c r="C9" s="1">
+        <v>45940</v>
+      </c>
       <c r="D9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G9" s="1"/>
+      <c r="H9" t="s">
         <v>161</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="L9" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="I9" t="e" vm="7">
+      <c r="M9" t="e" vm="7">
         <v>#VALUE!</v>
       </c>
-      <c r="J9" t="s">
+      <c r="N9" t="s">
         <v>68</v>
       </c>
-      <c r="L9" t="s">
+      <c r="P9" t="s">
         <v>24</v>
       </c>
-      <c r="M9" s="1">
+      <c r="Q9" s="1">
         <v>45940</v>
-      </c>
-      <c r="N9" s="1">
-        <v>45940</v>
-      </c>
-      <c r="O9" s="1"/>
-      <c r="P9" t="s">
-        <v>69</v>
       </c>
       <c r="T9">
         <v>1</v>
@@ -24129,33 +24145,33 @@
       <c r="A10" t="s">
         <v>71</v>
       </c>
-      <c r="D10" t="s">
+      <c r="C10" s="1">
+        <v>45940</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G10" s="1"/>
+      <c r="H10" t="s">
         <v>104</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="L10" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="I10" t="e" vm="7">
+      <c r="M10" t="e" vm="7">
         <v>#VALUE!</v>
       </c>
-      <c r="J10" t="s">
+      <c r="N10" t="s">
         <v>15</v>
       </c>
-      <c r="K10" t="s">
+      <c r="O10" t="s">
         <v>72</v>
       </c>
-      <c r="L10" t="s">
+      <c r="P10" t="s">
         <v>23</v>
       </c>
-      <c r="M10" s="1">
+      <c r="Q10" s="1">
         <v>45940</v>
-      </c>
-      <c r="N10" s="1">
-        <v>45940</v>
-      </c>
-      <c r="O10" s="1"/>
-      <c r="P10" s="2" t="s">
-        <v>73</v>
       </c>
       <c r="T10">
         <v>1</v>
@@ -24171,27 +24187,27 @@
       <c r="A11" t="s">
         <v>90</v>
       </c>
-      <c r="D11" t="s">
+      <c r="C11" s="1">
+        <v>45945</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G11" s="1"/>
+      <c r="H11" t="s">
         <v>104</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="L11" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="I11" t="e" vm="4">
+      <c r="M11" t="e" vm="4">
         <v>#VALUE!</v>
       </c>
-      <c r="L11" t="s">
+      <c r="P11" t="s">
         <v>23</v>
       </c>
-      <c r="M11" s="1">
+      <c r="Q11" s="1">
         <v>45945</v>
-      </c>
-      <c r="N11" s="1">
-        <v>45945</v>
-      </c>
-      <c r="O11" s="1"/>
-      <c r="P11" s="2" t="s">
-        <v>92</v>
       </c>
       <c r="T11">
         <v>1</v>
@@ -24207,30 +24223,30 @@
       <c r="A12" t="s">
         <v>107</v>
       </c>
+      <c r="C12" s="1">
+        <v>45945</v>
+      </c>
       <c r="D12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="1"/>
+      <c r="H12" t="s">
         <v>137</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="L12" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="I12" t="e" vm="8">
+      <c r="M12" t="e" vm="8">
         <v>#VALUE!</v>
       </c>
-      <c r="J12" t="s">
+      <c r="N12" t="s">
         <v>15</v>
       </c>
-      <c r="L12" t="s">
+      <c r="P12" t="s">
         <v>23</v>
       </c>
-      <c r="M12" s="1">
+      <c r="Q12" s="1">
         <v>45945</v>
-      </c>
-      <c r="N12" s="1">
-        <v>45945</v>
-      </c>
-      <c r="O12" s="1"/>
-      <c r="P12" t="s">
-        <v>19</v>
       </c>
       <c r="T12">
         <v>1</v>
@@ -24246,30 +24262,30 @@
       <c r="A13" t="s">
         <v>108</v>
       </c>
+      <c r="C13" s="1">
+        <v>45945</v>
+      </c>
       <c r="D13" t="s">
+        <v>19</v>
+      </c>
+      <c r="G13" s="1"/>
+      <c r="H13" t="s">
         <v>137</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="L13" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="I13" t="e" vm="8">
+      <c r="M13" t="e" vm="8">
         <v>#VALUE!</v>
       </c>
-      <c r="J13" t="s">
+      <c r="N13" t="s">
         <v>15</v>
       </c>
-      <c r="L13" t="s">
+      <c r="P13" t="s">
         <v>23</v>
       </c>
-      <c r="M13" s="1">
+      <c r="Q13" s="1">
         <v>45945</v>
-      </c>
-      <c r="N13" s="1">
-        <v>45945</v>
-      </c>
-      <c r="O13" s="1"/>
-      <c r="P13" t="s">
-        <v>19</v>
       </c>
       <c r="T13">
         <v>1</v>
@@ -24285,30 +24301,30 @@
       <c r="A14" t="s">
         <v>109</v>
       </c>
+      <c r="C14" s="1">
+        <v>45945</v>
+      </c>
       <c r="D14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="G14" s="1"/>
+      <c r="H14" t="s">
         <v>104</v>
       </c>
-      <c r="H14" t="s">
+      <c r="L14" t="s">
         <v>110</v>
       </c>
-      <c r="I14" t="e" vm="9">
+      <c r="M14" t="e" vm="9">
         <v>#VALUE!</v>
       </c>
-      <c r="L14" t="s">
+      <c r="P14" t="s">
         <v>23</v>
       </c>
-      <c r="M14" s="1">
+      <c r="Q14" s="1">
         <v>45945</v>
-      </c>
-      <c r="N14" s="1">
-        <v>45945</v>
-      </c>
-      <c r="O14" s="1"/>
-      <c r="P14" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q14" s="2" t="s">
-        <v>112</v>
       </c>
       <c r="R14" s="2" t="s">
         <v>111</v>
@@ -24327,38 +24343,38 @@
       <c r="A15" t="s">
         <v>234</v>
       </c>
+      <c r="C15" s="1">
+        <v>45945</v>
+      </c>
       <c r="D15" t="s">
+        <v>45</v>
+      </c>
+      <c r="E15" t="s">
+        <v>237</v>
+      </c>
+      <c r="G15" t="s">
+        <v>239</v>
+      </c>
+      <c r="H15" t="s">
         <v>104</v>
       </c>
-      <c r="H15" s="2" t="s">
+      <c r="L15" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="I15" t="e" vm="10">
+      <c r="M15" t="e" vm="10">
         <v>#VALUE!</v>
       </c>
-      <c r="J15" t="s">
+      <c r="N15" t="s">
         <v>15</v>
       </c>
-      <c r="K15" t="s">
+      <c r="O15" t="s">
         <v>236</v>
       </c>
-      <c r="L15" t="s">
+      <c r="P15" t="s">
         <v>23</v>
       </c>
-      <c r="M15" s="1">
-        <v>45945</v>
-      </c>
-      <c r="N15" s="1">
+      <c r="Q15" s="1">
         <v>46142</v>
-      </c>
-      <c r="O15" t="s">
-        <v>239</v>
-      </c>
-      <c r="P15" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>237</v>
       </c>
       <c r="T15">
         <v>1</v>
@@ -24374,29 +24390,29 @@
       <c r="A16" t="s">
         <v>372</v>
       </c>
+      <c r="C16" s="1">
+        <v>45945</v>
+      </c>
       <c r="D16" t="s">
+        <v>373</v>
+      </c>
+      <c r="H16" t="s">
         <v>104</v>
       </c>
-      <c r="H16" t="s">
+      <c r="L16" t="s">
         <v>371</v>
       </c>
-      <c r="I16" t="e" vm="11">
+      <c r="M16" t="e" vm="11">
         <v>#VALUE!</v>
       </c>
-      <c r="J16" t="s">
+      <c r="N16" t="s">
         <v>15</v>
       </c>
-      <c r="L16" t="s">
+      <c r="P16" t="s">
         <v>23</v>
       </c>
-      <c r="M16" s="1">
+      <c r="Q16" s="1">
         <v>45945</v>
-      </c>
-      <c r="N16" s="1">
-        <v>45945</v>
-      </c>
-      <c r="P16" t="s">
-        <v>373</v>
       </c>
       <c r="T16">
         <v>1</v>
@@ -24412,38 +24428,38 @@
       <c r="A17" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="1">
+        <v>45947</v>
+      </c>
+      <c r="D17" t="s">
+        <v>45</v>
+      </c>
+      <c r="F17">
         <v>1</v>
       </c>
-      <c r="D17" t="s">
+      <c r="H17" t="s">
         <v>104</v>
       </c>
-      <c r="F17" t="s">
+      <c r="J17" t="s">
         <v>318</v>
       </c>
-      <c r="G17" s="1">
+      <c r="K17" s="1">
         <v>45976</v>
       </c>
-      <c r="H17" s="2" t="s">
+      <c r="L17" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="I17" t="e" vm="12">
+      <c r="M17" t="e" vm="12">
         <v>#VALUE!</v>
       </c>
-      <c r="J17" t="s">
+      <c r="N17" t="s">
         <v>15</v>
       </c>
-      <c r="L17" t="s">
+      <c r="P17" t="s">
         <v>23</v>
       </c>
-      <c r="M17" s="1">
-        <v>45947</v>
-      </c>
-      <c r="N17" s="1">
+      <c r="Q17" s="1">
         <v>45992</v>
-      </c>
-      <c r="P17" t="s">
-        <v>45</v>
       </c>
       <c r="T17">
         <v>1</v>
@@ -24459,35 +24475,35 @@
       <c r="A18" t="s">
         <v>180</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="1">
+        <v>45950</v>
+      </c>
+      <c r="D18" t="s">
+        <v>19</v>
+      </c>
+      <c r="F18">
         <v>1</v>
       </c>
-      <c r="D18" t="s">
+      <c r="G18" t="s">
+        <v>182</v>
+      </c>
+      <c r="H18" t="s">
         <v>104</v>
       </c>
-      <c r="H18" s="2" t="s">
+      <c r="L18" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="I18" t="e" vm="13">
+      <c r="M18" t="e" vm="13">
         <v>#VALUE!</v>
       </c>
-      <c r="J18" t="s">
+      <c r="N18" t="s">
         <v>15</v>
       </c>
-      <c r="L18" t="s">
+      <c r="P18" t="s">
         <v>23</v>
       </c>
-      <c r="M18" s="1">
-        <v>45950</v>
-      </c>
-      <c r="N18" s="1">
+      <c r="Q18" s="1">
         <v>45964</v>
-      </c>
-      <c r="O18" t="s">
-        <v>182</v>
-      </c>
-      <c r="P18" t="s">
-        <v>19</v>
       </c>
       <c r="T18">
         <v>1</v>
@@ -24503,33 +24519,33 @@
       <c r="A19" t="s">
         <v>121</v>
       </c>
+      <c r="C19" s="1">
+        <v>45950</v>
+      </c>
       <c r="D19" t="s">
+        <v>45</v>
+      </c>
+      <c r="E19" t="s">
+        <v>160</v>
+      </c>
+      <c r="G19" s="1"/>
+      <c r="H19" t="s">
         <v>104</v>
       </c>
-      <c r="H19" s="2" t="s">
+      <c r="L19" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="I19" t="e" vm="14">
+      <c r="M19" t="e" vm="14">
         <v>#VALUE!</v>
       </c>
-      <c r="J19" t="s">
+      <c r="N19" t="s">
         <v>15</v>
       </c>
-      <c r="L19" t="s">
+      <c r="P19" t="s">
         <v>23</v>
       </c>
-      <c r="M19" s="1">
-        <v>45950</v>
-      </c>
-      <c r="N19" s="1">
+      <c r="Q19" s="1">
         <v>45957</v>
-      </c>
-      <c r="O19" s="1"/>
-      <c r="P19" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>160</v>
       </c>
       <c r="T19">
         <v>1</v>
@@ -24546,29 +24562,29 @@
         <v>168</v>
       </c>
       <c r="B20" s="8"/>
+      <c r="C20" s="1">
+        <v>45950</v>
+      </c>
       <c r="D20" t="s">
+        <v>19</v>
+      </c>
+      <c r="H20" t="s">
         <v>104</v>
       </c>
-      <c r="H20" s="2" t="s">
+      <c r="L20" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="I20" t="e" vm="15">
+      <c r="M20" t="e" vm="15">
         <v>#VALUE!</v>
       </c>
-      <c r="J20" t="s">
+      <c r="N20" t="s">
         <v>15</v>
       </c>
-      <c r="L20" t="s">
+      <c r="P20" t="s">
         <v>23</v>
       </c>
-      <c r="M20" s="1">
-        <v>45950</v>
-      </c>
-      <c r="N20" s="1">
+      <c r="Q20" s="1">
         <v>45963</v>
-      </c>
-      <c r="P20" t="s">
-        <v>19</v>
       </c>
       <c r="T20">
         <v>1</v>
@@ -24584,35 +24600,35 @@
       <c r="A21" t="s">
         <v>176</v>
       </c>
+      <c r="C21" s="1">
+        <v>45950</v>
+      </c>
       <c r="D21" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="H21" t="s">
         <v>104</v>
       </c>
-      <c r="H21" s="2" t="s">
+      <c r="L21" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="I21" t="e" vm="16">
+      <c r="M21" t="e" vm="16">
         <v>#VALUE!</v>
       </c>
-      <c r="J21" t="s">
+      <c r="N21" t="s">
         <v>15</v>
       </c>
-      <c r="K21" t="s">
+      <c r="O21" t="s">
         <v>178</v>
       </c>
-      <c r="L21" t="s">
+      <c r="P21" t="s">
         <v>23</v>
       </c>
-      <c r="M21" s="1">
-        <v>45950</v>
-      </c>
-      <c r="N21" s="1">
+      <c r="Q21" s="1">
         <v>45964</v>
-      </c>
-      <c r="P21" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q21" s="2" t="s">
-        <v>179</v>
       </c>
       <c r="T21">
         <v>1</v>
@@ -24628,44 +24644,44 @@
       <c r="A22" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="1">
+        <v>45950</v>
+      </c>
+      <c r="D22" t="s">
+        <v>19</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="F22">
         <v>1</v>
       </c>
-      <c r="D22" t="s">
+      <c r="G22" t="s">
+        <v>188</v>
+      </c>
+      <c r="H22" t="s">
         <v>104</v>
       </c>
-      <c r="F22" t="s">
+      <c r="J22" t="s">
         <v>318</v>
       </c>
-      <c r="G22" s="1">
+      <c r="K22" s="1">
         <v>45976</v>
       </c>
-      <c r="H22" s="2" t="s">
+      <c r="L22" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="I22" t="e" vm="17">
+      <c r="M22" t="e" vm="17">
         <v>#VALUE!</v>
       </c>
-      <c r="J22" t="s">
+      <c r="N22" t="s">
         <v>187</v>
       </c>
-      <c r="L22" t="s">
+      <c r="P22" t="s">
         <v>24</v>
       </c>
-      <c r="M22" s="1">
-        <v>45950</v>
-      </c>
-      <c r="N22" s="1">
+      <c r="Q22" s="1">
         <v>45959</v>
-      </c>
-      <c r="O22" t="s">
-        <v>188</v>
-      </c>
-      <c r="P22" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q22" s="2" t="s">
-        <v>189</v>
       </c>
       <c r="T22">
         <v>1</v>
@@ -24681,26 +24697,26 @@
       <c r="A23" t="s">
         <v>211</v>
       </c>
+      <c r="C23" s="1">
+        <v>45950</v>
+      </c>
       <c r="D23" t="s">
+        <v>212</v>
+      </c>
+      <c r="H23" t="s">
         <v>104</v>
       </c>
-      <c r="H23" s="2" t="s">
+      <c r="L23" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="I23" t="e" vm="4">
+      <c r="M23" t="e" vm="4">
         <v>#VALUE!</v>
       </c>
-      <c r="L23" t="s">
+      <c r="P23" t="s">
         <v>23</v>
       </c>
-      <c r="M23" s="1">
-        <v>45950</v>
-      </c>
-      <c r="N23" s="1">
+      <c r="Q23" s="1">
         <v>45954</v>
-      </c>
-      <c r="P23" t="s">
-        <v>212</v>
       </c>
       <c r="T23">
         <v>1</v>
@@ -24716,35 +24732,35 @@
       <c r="A24" t="s">
         <v>221</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="1">
+        <v>45950</v>
+      </c>
+      <c r="D24" t="s">
+        <v>45</v>
+      </c>
+      <c r="E24" t="s">
+        <v>220</v>
+      </c>
+      <c r="F24">
         <v>1</v>
       </c>
-      <c r="D24" t="s">
+      <c r="H24" t="s">
         <v>104</v>
       </c>
-      <c r="H24" t="s">
+      <c r="L24" t="s">
         <v>219</v>
       </c>
-      <c r="I24" t="e" vm="5">
+      <c r="M24" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
-      <c r="J24" t="s">
+      <c r="N24" t="s">
         <v>15</v>
       </c>
-      <c r="L24" t="s">
+      <c r="P24" t="s">
         <v>23</v>
       </c>
-      <c r="M24" s="1">
-        <v>45950</v>
-      </c>
-      <c r="N24" s="1">
+      <c r="Q24" s="1">
         <v>45961</v>
-      </c>
-      <c r="P24" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>220</v>
       </c>
       <c r="T24">
         <v>1</v>
@@ -24760,29 +24776,29 @@
       <c r="A25" t="s">
         <v>228</v>
       </c>
+      <c r="C25" s="1">
+        <v>45950</v>
+      </c>
       <c r="D25" t="s">
+        <v>45</v>
+      </c>
+      <c r="H25" t="s">
         <v>104</v>
       </c>
-      <c r="H25" s="2" t="s">
+      <c r="L25" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="I25" t="e" vm="5">
+      <c r="M25" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
-      <c r="J25" t="s">
+      <c r="N25" t="s">
         <v>15</v>
       </c>
-      <c r="L25" t="s">
+      <c r="P25" t="s">
         <v>23</v>
       </c>
-      <c r="M25" s="1">
-        <v>45950</v>
-      </c>
-      <c r="N25" s="1">
+      <c r="Q25" s="1">
         <v>46022</v>
-      </c>
-      <c r="P25" t="s">
-        <v>45</v>
       </c>
       <c r="T25">
         <v>1</v>
@@ -24798,32 +24814,32 @@
       <c r="A26" t="s">
         <v>231</v>
       </c>
+      <c r="C26" s="1">
+        <v>45950</v>
+      </c>
       <c r="D26" t="s">
+        <v>45</v>
+      </c>
+      <c r="E26" t="s">
+        <v>232</v>
+      </c>
+      <c r="H26" t="s">
         <v>104</v>
       </c>
-      <c r="H26" t="s">
+      <c r="L26" t="s">
         <v>230</v>
       </c>
-      <c r="I26" t="e" vm="18">
+      <c r="M26" t="e" vm="18">
         <v>#VALUE!</v>
       </c>
-      <c r="J26" t="s">
+      <c r="N26" t="s">
         <v>15</v>
       </c>
-      <c r="L26" t="s">
+      <c r="P26" t="s">
         <v>23</v>
       </c>
-      <c r="M26" s="1">
-        <v>45950</v>
-      </c>
-      <c r="N26" s="1">
+      <c r="Q26" s="1">
         <v>46157</v>
-      </c>
-      <c r="P26" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>232</v>
       </c>
       <c r="T26">
         <v>1</v>
@@ -24839,38 +24855,38 @@
       <c r="A27" t="s">
         <v>233</v>
       </c>
+      <c r="C27" s="1">
+        <v>45950</v>
+      </c>
       <c r="D27" t="s">
+        <v>45</v>
+      </c>
+      <c r="E27" t="s">
+        <v>238</v>
+      </c>
+      <c r="G27" t="s">
+        <v>240</v>
+      </c>
+      <c r="H27" t="s">
         <v>104</v>
       </c>
-      <c r="H27" s="2" t="s">
+      <c r="L27" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="I27" t="e" vm="10">
+      <c r="M27" t="e" vm="10">
         <v>#VALUE!</v>
       </c>
-      <c r="J27" t="s">
+      <c r="N27" t="s">
         <v>15</v>
       </c>
-      <c r="K27" t="s">
+      <c r="O27" t="s">
         <v>235</v>
       </c>
-      <c r="L27" t="s">
+      <c r="P27" t="s">
         <v>23</v>
       </c>
-      <c r="M27" s="1">
-        <v>45950</v>
-      </c>
-      <c r="N27" s="1">
+      <c r="Q27" s="1">
         <v>46142</v>
-      </c>
-      <c r="O27" t="s">
-        <v>240</v>
-      </c>
-      <c r="P27" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>238</v>
       </c>
       <c r="T27">
         <v>1</v>
@@ -24886,29 +24902,29 @@
       <c r="A28" t="s">
         <v>192</v>
       </c>
+      <c r="C28" s="1">
+        <v>45950</v>
+      </c>
       <c r="D28" t="s">
+        <v>19</v>
+      </c>
+      <c r="H28" t="s">
         <v>104</v>
       </c>
-      <c r="H28" t="s">
+      <c r="L28" t="s">
         <v>261</v>
       </c>
-      <c r="I28" t="e" vm="19">
+      <c r="M28" t="e" vm="19">
         <v>#VALUE!</v>
       </c>
-      <c r="J28" t="s">
+      <c r="N28" t="s">
         <v>15</v>
       </c>
-      <c r="L28" t="s">
+      <c r="P28" t="s">
         <v>23</v>
       </c>
-      <c r="M28" s="1">
-        <v>45950</v>
-      </c>
-      <c r="N28" s="1">
+      <c r="Q28" s="1">
         <v>46022</v>
-      </c>
-      <c r="P28" t="s">
-        <v>19</v>
       </c>
       <c r="T28">
         <v>1</v>
@@ -24924,29 +24940,29 @@
       <c r="A29" t="s">
         <v>272</v>
       </c>
+      <c r="C29" s="1">
+        <v>45950</v>
+      </c>
       <c r="D29" t="s">
+        <v>19</v>
+      </c>
+      <c r="H29" t="s">
         <v>104</v>
       </c>
-      <c r="H29" t="s">
+      <c r="L29" t="s">
         <v>273</v>
       </c>
-      <c r="I29" t="e" vm="20">
+      <c r="M29" t="e" vm="20">
         <v>#VALUE!</v>
       </c>
-      <c r="J29" t="s">
+      <c r="N29" t="s">
         <v>187</v>
       </c>
-      <c r="L29" t="s">
+      <c r="P29" t="s">
         <v>24</v>
       </c>
-      <c r="M29" s="1">
-        <v>45950</v>
-      </c>
-      <c r="N29" s="1">
+      <c r="Q29" s="1">
         <v>45992</v>
-      </c>
-      <c r="P29" t="s">
-        <v>19</v>
       </c>
       <c r="T29">
         <v>1</v>
@@ -24962,26 +24978,26 @@
       <c r="A30" t="s">
         <v>350</v>
       </c>
+      <c r="C30" s="1">
+        <v>45950</v>
+      </c>
       <c r="D30" t="s">
+        <v>45</v>
+      </c>
+      <c r="H30" t="s">
         <v>104</v>
       </c>
-      <c r="H30" t="s">
+      <c r="L30" t="s">
         <v>349</v>
       </c>
-      <c r="I30" t="e" vm="4">
+      <c r="M30" t="e" vm="4">
         <v>#VALUE!</v>
       </c>
-      <c r="L30" t="s">
+      <c r="P30" t="s">
         <v>23</v>
       </c>
-      <c r="M30" s="1">
+      <c r="Q30" s="1">
         <v>45950</v>
-      </c>
-      <c r="N30" s="1">
-        <v>45950</v>
-      </c>
-      <c r="P30" t="s">
-        <v>45</v>
       </c>
       <c r="T30">
         <v>1</v>
@@ -24997,38 +25013,38 @@
       <c r="A31" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="C31">
+      <c r="C31" s="1">
+        <v>45955</v>
+      </c>
+      <c r="D31" t="s">
+        <v>19</v>
+      </c>
+      <c r="F31">
         <v>1</v>
       </c>
-      <c r="D31" t="s">
+      <c r="H31" t="s">
         <v>104</v>
       </c>
-      <c r="F31" t="s">
+      <c r="J31" t="s">
         <v>253</v>
       </c>
-      <c r="G31" s="1">
+      <c r="K31" s="1">
         <v>45965</v>
       </c>
-      <c r="H31" s="2" t="s">
+      <c r="L31" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="I31" t="e" vm="15">
+      <c r="M31" t="e" vm="15">
         <v>#VALUE!</v>
       </c>
-      <c r="J31" t="s">
+      <c r="N31" t="s">
         <v>15</v>
       </c>
-      <c r="L31" t="s">
+      <c r="P31" t="s">
         <v>23</v>
       </c>
-      <c r="M31" s="1">
-        <v>45955</v>
-      </c>
-      <c r="N31" s="1">
+      <c r="Q31" s="1">
         <v>45963</v>
-      </c>
-      <c r="P31" t="s">
-        <v>19</v>
       </c>
       <c r="T31">
         <v>1</v>
@@ -25044,36 +25060,36 @@
       <c r="A32" t="s">
         <v>74</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="1">
+        <v>45955</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F32">
         <v>1</v>
       </c>
-      <c r="D32" t="s">
+      <c r="G32" s="1"/>
+      <c r="H32" t="s">
         <v>104</v>
       </c>
-      <c r="H32" s="2" t="s">
+      <c r="L32" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="I32" t="e" vm="21">
+      <c r="M32" t="e" vm="21">
         <v>#VALUE!</v>
       </c>
-      <c r="J32" t="s">
+      <c r="N32" t="s">
         <v>15</v>
       </c>
-      <c r="K32" t="s">
+      <c r="O32" t="s">
         <v>22</v>
       </c>
-      <c r="L32" t="s">
+      <c r="P32" t="s">
         <v>23</v>
       </c>
-      <c r="M32" s="1">
-        <v>45955</v>
-      </c>
-      <c r="N32" s="1">
+      <c r="Q32" s="1">
         <v>45962</v>
-      </c>
-      <c r="O32" s="1"/>
-      <c r="P32" s="2" t="s">
-        <v>76</v>
       </c>
       <c r="T32">
         <v>1</v>
@@ -25089,42 +25105,42 @@
       <c r="A33" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="C33">
+      <c r="C33" s="1">
+        <v>45955</v>
+      </c>
+      <c r="D33" t="s">
+        <v>83</v>
+      </c>
+      <c r="F33">
         <v>1</v>
       </c>
-      <c r="D33" t="s">
+      <c r="G33" s="1"/>
+      <c r="H33" t="s">
         <v>104</v>
       </c>
-      <c r="F33" t="s">
+      <c r="J33" t="s">
         <v>253</v>
       </c>
-      <c r="G33" s="1">
+      <c r="K33" s="1">
         <v>45965</v>
       </c>
-      <c r="H33" s="2" t="s">
+      <c r="L33" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="I33" t="e" vm="22">
+      <c r="M33" t="e" vm="22">
         <v>#VALUE!</v>
       </c>
-      <c r="J33" t="s">
+      <c r="N33" t="s">
         <v>15</v>
       </c>
-      <c r="K33" t="s">
+      <c r="O33" t="s">
         <v>22</v>
       </c>
-      <c r="L33" t="s">
+      <c r="P33" t="s">
         <v>23</v>
       </c>
-      <c r="M33" s="1">
-        <v>45955</v>
-      </c>
-      <c r="N33" s="1">
+      <c r="Q33" s="1">
         <v>45962</v>
-      </c>
-      <c r="O33" s="1"/>
-      <c r="P33" t="s">
-        <v>83</v>
       </c>
       <c r="T33">
         <v>1</v>
@@ -25140,41 +25156,41 @@
       <c r="A34" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="C34">
+      <c r="C34" s="1">
+        <v>45955</v>
+      </c>
+      <c r="D34" t="s">
+        <v>19</v>
+      </c>
+      <c r="F34">
         <v>1</v>
       </c>
-      <c r="D34" t="s">
+      <c r="G34" t="s">
+        <v>133</v>
+      </c>
+      <c r="H34" t="s">
         <v>104</v>
       </c>
-      <c r="F34" t="s">
+      <c r="J34" t="s">
         <v>253</v>
       </c>
-      <c r="G34" s="1">
+      <c r="K34" s="1">
         <v>45965</v>
       </c>
-      <c r="H34" s="2" t="s">
+      <c r="L34" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="I34" t="e" vm="23">
+      <c r="M34" t="e" vm="23">
         <v>#VALUE!</v>
       </c>
-      <c r="J34" t="s">
+      <c r="N34" t="s">
         <v>15</v>
       </c>
-      <c r="L34" t="s">
+      <c r="P34" t="s">
         <v>23</v>
       </c>
-      <c r="M34" s="1">
-        <v>45955</v>
-      </c>
-      <c r="N34" s="1">
+      <c r="Q34" s="1">
         <v>45962</v>
-      </c>
-      <c r="O34" t="s">
-        <v>133</v>
-      </c>
-      <c r="P34" t="s">
-        <v>19</v>
       </c>
       <c r="T34">
         <v>1</v>
@@ -25190,41 +25206,41 @@
       <c r="A35" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="C35">
+      <c r="C35" s="1">
+        <v>45955</v>
+      </c>
+      <c r="D35" t="s">
+        <v>45</v>
+      </c>
+      <c r="F35">
         <v>1</v>
       </c>
-      <c r="D35" t="s">
+      <c r="G35" t="s">
+        <v>146</v>
+      </c>
+      <c r="H35" t="s">
         <v>104</v>
       </c>
-      <c r="F35" t="s">
+      <c r="J35" t="s">
         <v>253</v>
       </c>
-      <c r="G35" s="1">
+      <c r="K35" s="1">
         <v>45965</v>
       </c>
-      <c r="H35" s="2" t="s">
+      <c r="L35" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="I35" t="e" vm="23">
+      <c r="M35" t="e" vm="23">
         <v>#VALUE!</v>
       </c>
-      <c r="J35" t="s">
+      <c r="N35" t="s">
         <v>15</v>
       </c>
-      <c r="L35" t="s">
+      <c r="P35" t="s">
         <v>23</v>
       </c>
-      <c r="M35" s="1">
-        <v>45955</v>
-      </c>
-      <c r="N35" s="1">
+      <c r="Q35" s="1">
         <v>45969</v>
-      </c>
-      <c r="O35" t="s">
-        <v>146</v>
-      </c>
-      <c r="P35" t="s">
-        <v>45</v>
       </c>
       <c r="T35">
         <v>1</v>
@@ -25240,27 +25256,27 @@
       <c r="A36" t="s">
         <v>60</v>
       </c>
+      <c r="C36" s="1">
+        <v>45955</v>
+      </c>
       <c r="D36" t="s">
+        <v>61</v>
+      </c>
+      <c r="G36" s="1"/>
+      <c r="H36" t="s">
         <v>104</v>
       </c>
-      <c r="H36" s="2" t="s">
+      <c r="L36" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="I36" t="e" vm="24">
+      <c r="M36" t="e" vm="24">
         <v>#VALUE!</v>
       </c>
-      <c r="L36" t="s">
+      <c r="P36" t="s">
         <v>64</v>
       </c>
-      <c r="M36" s="1">
-        <v>45955</v>
-      </c>
-      <c r="N36" s="1">
+      <c r="Q36" s="1">
         <v>45962</v>
-      </c>
-      <c r="O36" s="1"/>
-      <c r="P36" t="s">
-        <v>61</v>
       </c>
       <c r="T36">
         <v>1</v>
@@ -25276,27 +25292,27 @@
       <c r="A37" t="s">
         <v>62</v>
       </c>
-      <c r="D37" t="s">
+      <c r="C37" s="1">
+        <v>45955</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G37" s="1"/>
+      <c r="H37" t="s">
         <v>104</v>
       </c>
-      <c r="H37" s="2" t="s">
+      <c r="L37" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="I37" t="e" vm="25">
+      <c r="M37" t="e" vm="25">
         <v>#VALUE!</v>
       </c>
-      <c r="L37" t="s">
+      <c r="P37" t="s">
         <v>64</v>
       </c>
-      <c r="M37" s="1">
-        <v>45955</v>
-      </c>
-      <c r="N37" s="1">
+      <c r="Q37" s="1">
         <v>45962</v>
-      </c>
-      <c r="O37" s="1"/>
-      <c r="P37" s="2" t="s">
-        <v>63</v>
       </c>
       <c r="T37">
         <v>1</v>
@@ -25312,29 +25328,29 @@
       <c r="A38" t="s">
         <v>190</v>
       </c>
+      <c r="C38" s="1">
+        <v>45955</v>
+      </c>
       <c r="D38" t="s">
+        <v>19</v>
+      </c>
+      <c r="H38" t="s">
         <v>104</v>
       </c>
-      <c r="H38" s="2" t="s">
+      <c r="L38" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="I38" t="e" vm="19">
+      <c r="M38" t="e" vm="19">
         <v>#VALUE!</v>
       </c>
-      <c r="J38" t="s">
+      <c r="N38" t="s">
         <v>15</v>
       </c>
-      <c r="L38" t="s">
+      <c r="P38" t="s">
         <v>23</v>
       </c>
-      <c r="M38" s="1">
-        <v>45955</v>
-      </c>
-      <c r="N38" s="1">
+      <c r="Q38" s="1">
         <v>45968</v>
-      </c>
-      <c r="P38" t="s">
-        <v>19</v>
       </c>
       <c r="T38">
         <v>1</v>
@@ -25350,32 +25366,32 @@
       <c r="A39" t="s">
         <v>193</v>
       </c>
+      <c r="C39" s="1">
+        <v>45955</v>
+      </c>
       <c r="D39" t="s">
+        <v>19</v>
+      </c>
+      <c r="H39" t="s">
         <v>104</v>
       </c>
-      <c r="H39" s="2" t="s">
+      <c r="L39" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="I39" t="e" vm="26">
+      <c r="M39" t="e" vm="26">
         <v>#VALUE!</v>
       </c>
-      <c r="J39" t="s">
+      <c r="N39" t="s">
         <v>15</v>
       </c>
-      <c r="K39" t="s">
+      <c r="O39" t="s">
         <v>195</v>
       </c>
-      <c r="L39" t="s">
+      <c r="P39" t="s">
         <v>23</v>
       </c>
-      <c r="M39" s="1">
-        <v>45955</v>
-      </c>
-      <c r="N39" s="1">
+      <c r="Q39" s="1">
         <v>45970</v>
-      </c>
-      <c r="P39" t="s">
-        <v>19</v>
       </c>
       <c r="T39">
         <v>1</v>
@@ -25391,29 +25407,29 @@
       <c r="A40" t="s">
         <v>196</v>
       </c>
+      <c r="C40" s="1">
+        <v>45955</v>
+      </c>
       <c r="D40" t="s">
+        <v>19</v>
+      </c>
+      <c r="H40" t="s">
         <v>104</v>
       </c>
-      <c r="H40" s="2" t="s">
+      <c r="L40" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="I40" t="e" vm="16">
+      <c r="M40" t="e" vm="16">
         <v>#VALUE!</v>
       </c>
-      <c r="J40" t="s">
+      <c r="N40" t="s">
         <v>15</v>
       </c>
-      <c r="L40" t="s">
+      <c r="P40" t="s">
         <v>23</v>
       </c>
-      <c r="M40" s="1">
-        <v>45955</v>
-      </c>
-      <c r="N40" s="1">
+      <c r="Q40" s="1">
         <v>45968</v>
-      </c>
-      <c r="P40" t="s">
-        <v>19</v>
       </c>
       <c r="T40">
         <v>1</v>
@@ -25429,29 +25445,29 @@
       <c r="A41" t="s">
         <v>216</v>
       </c>
+      <c r="C41" s="1">
+        <v>45955</v>
+      </c>
       <c r="D41" t="s">
+        <v>45</v>
+      </c>
+      <c r="H41" t="s">
         <v>104</v>
       </c>
-      <c r="H41" s="2" t="s">
+      <c r="L41" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="I41" t="e" vm="5">
+      <c r="M41" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
-      <c r="J41" t="s">
+      <c r="N41" t="s">
         <v>15</v>
       </c>
-      <c r="L41" t="s">
+      <c r="P41" t="s">
         <v>23</v>
       </c>
-      <c r="M41" s="1">
-        <v>45955</v>
-      </c>
-      <c r="N41" s="1">
+      <c r="Q41" s="1">
         <v>45968</v>
-      </c>
-      <c r="P41" t="s">
-        <v>45</v>
       </c>
       <c r="T41">
         <v>1</v>
@@ -25467,29 +25483,29 @@
       <c r="A42" t="s">
         <v>377</v>
       </c>
+      <c r="C42" s="1">
+        <v>45955</v>
+      </c>
       <c r="D42" t="s">
+        <v>379</v>
+      </c>
+      <c r="H42" t="s">
         <v>104</v>
       </c>
-      <c r="H42" t="s">
+      <c r="L42" t="s">
         <v>378</v>
       </c>
-      <c r="I42" t="e" vm="27">
+      <c r="M42" t="e" vm="27">
         <v>#VALUE!</v>
       </c>
-      <c r="J42" t="s">
+      <c r="N42" t="s">
         <v>15</v>
       </c>
-      <c r="L42" t="s">
+      <c r="P42" t="s">
         <v>23</v>
       </c>
-      <c r="M42" s="1">
-        <v>45955</v>
-      </c>
-      <c r="N42" s="1">
+      <c r="Q42" s="1">
         <v>45962</v>
-      </c>
-      <c r="P42" t="s">
-        <v>379</v>
       </c>
       <c r="T42">
         <v>1</v>
@@ -25505,29 +25521,29 @@
       <c r="A43" t="s">
         <v>381</v>
       </c>
+      <c r="C43" s="1">
+        <v>45955</v>
+      </c>
       <c r="D43" t="s">
+        <v>382</v>
+      </c>
+      <c r="H43" t="s">
         <v>104</v>
       </c>
-      <c r="H43" t="s">
+      <c r="L43" t="s">
         <v>380</v>
       </c>
-      <c r="I43" t="e" vm="28">
+      <c r="M43" t="e" vm="28">
         <v>#VALUE!</v>
       </c>
-      <c r="J43" t="s">
+      <c r="N43" t="s">
         <v>15</v>
       </c>
-      <c r="L43" t="s">
+      <c r="P43" t="s">
         <v>24</v>
       </c>
-      <c r="M43" s="1">
-        <v>45955</v>
-      </c>
-      <c r="N43" s="1">
+      <c r="Q43" s="1">
         <v>46203</v>
-      </c>
-      <c r="P43" t="s">
-        <v>382</v>
       </c>
       <c r="T43">
         <v>1</v>
@@ -25543,30 +25559,30 @@
       <c r="A44" t="s">
         <v>114</v>
       </c>
+      <c r="C44" s="1">
+        <v>45961</v>
+      </c>
       <c r="D44" t="s">
+        <v>19</v>
+      </c>
+      <c r="G44" s="1"/>
+      <c r="H44" t="s">
         <v>104</v>
       </c>
-      <c r="H44" s="2" t="s">
+      <c r="L44" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="I44" t="e" vm="9">
+      <c r="M44" t="e" vm="9">
         <v>#VALUE!</v>
       </c>
-      <c r="J44" t="s">
+      <c r="N44" t="s">
         <v>31</v>
       </c>
-      <c r="L44" t="s">
+      <c r="P44" t="s">
         <v>23</v>
       </c>
-      <c r="M44" s="1">
+      <c r="Q44" s="1">
         <v>45961</v>
-      </c>
-      <c r="N44" s="1">
-        <v>45961</v>
-      </c>
-      <c r="O44" s="1"/>
-      <c r="P44" t="s">
-        <v>19</v>
       </c>
       <c r="T44">
         <v>1</v>
@@ -25582,41 +25598,41 @@
       <c r="A45" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="C45">
+      <c r="C45" s="1">
+        <v>45962</v>
+      </c>
+      <c r="D45" t="s">
+        <v>45</v>
+      </c>
+      <c r="F45">
         <v>1</v>
       </c>
-      <c r="D45" t="s">
+      <c r="G45" t="s">
+        <v>155</v>
+      </c>
+      <c r="H45" t="s">
         <v>104</v>
       </c>
-      <c r="F45" t="s">
+      <c r="J45" t="s">
         <v>253</v>
       </c>
-      <c r="G45" s="1">
+      <c r="K45" s="1">
         <v>45976</v>
       </c>
-      <c r="H45" s="2" t="s">
+      <c r="L45" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="I45" t="e" vm="29">
+      <c r="M45" t="e" vm="29">
         <v>#VALUE!</v>
       </c>
-      <c r="J45" t="s">
+      <c r="N45" t="s">
         <v>15</v>
       </c>
-      <c r="L45" t="s">
+      <c r="P45" t="s">
         <v>23</v>
       </c>
-      <c r="M45" s="1">
-        <v>45962</v>
-      </c>
-      <c r="N45" s="1">
+      <c r="Q45" s="1">
         <v>45975</v>
-      </c>
-      <c r="O45" t="s">
-        <v>155</v>
-      </c>
-      <c r="P45" t="s">
-        <v>45</v>
       </c>
       <c r="T45">
         <v>1</v>
@@ -25632,29 +25648,29 @@
       <c r="A46" t="s">
         <v>198</v>
       </c>
+      <c r="C46" s="1">
+        <v>45962</v>
+      </c>
       <c r="D46" t="s">
+        <v>19</v>
+      </c>
+      <c r="H46" t="s">
         <v>104</v>
       </c>
-      <c r="H46" s="2" t="s">
+      <c r="L46" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="I46" t="e" vm="30">
+      <c r="M46" t="e" vm="30">
         <v>#VALUE!</v>
       </c>
-      <c r="J46" t="s">
+      <c r="N46" t="s">
         <v>15</v>
       </c>
-      <c r="L46" t="s">
+      <c r="P46" t="s">
         <v>23</v>
       </c>
-      <c r="M46" s="1">
-        <v>45962</v>
-      </c>
-      <c r="N46" s="1">
+      <c r="Q46" s="1">
         <v>45971</v>
-      </c>
-      <c r="P46" t="s">
-        <v>19</v>
       </c>
       <c r="T46">
         <v>1</v>
@@ -25670,35 +25686,35 @@
       <c r="A47" t="s">
         <v>200</v>
       </c>
+      <c r="C47" s="1">
+        <v>45962</v>
+      </c>
       <c r="D47" t="s">
+        <v>19</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="G47" t="s">
+        <v>203</v>
+      </c>
+      <c r="H47" t="s">
         <v>104</v>
       </c>
-      <c r="H47" s="2" t="s">
+      <c r="L47" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="I47" t="e" vm="11">
+      <c r="M47" t="e" vm="11">
         <v>#VALUE!</v>
       </c>
-      <c r="J47" t="s">
+      <c r="N47" t="s">
         <v>15</v>
       </c>
-      <c r="L47" t="s">
+      <c r="P47" t="s">
         <v>23</v>
       </c>
-      <c r="M47" s="1">
-        <v>45962</v>
-      </c>
-      <c r="N47" s="1">
+      <c r="Q47" s="1">
         <v>45971</v>
-      </c>
-      <c r="O47" t="s">
-        <v>203</v>
-      </c>
-      <c r="P47" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q47" s="2" t="s">
-        <v>202</v>
       </c>
       <c r="T47">
         <v>1</v>
@@ -25714,32 +25730,32 @@
       <c r="A48" t="s">
         <v>204</v>
       </c>
+      <c r="C48" s="1">
+        <v>45962</v>
+      </c>
       <c r="D48" t="s">
+        <v>19</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="H48" t="s">
         <v>104</v>
       </c>
-      <c r="H48" s="2" t="s">
+      <c r="L48" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="I48" t="e" vm="9">
+      <c r="M48" t="e" vm="9">
         <v>#VALUE!</v>
       </c>
-      <c r="J48" t="s">
+      <c r="N48" t="s">
         <v>15</v>
       </c>
-      <c r="L48" t="s">
+      <c r="P48" t="s">
         <v>23</v>
       </c>
-      <c r="M48" s="1">
-        <v>45962</v>
-      </c>
-      <c r="N48" s="1">
+      <c r="Q48" s="1">
         <v>45971</v>
-      </c>
-      <c r="P48" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q48" s="2" t="s">
-        <v>206</v>
       </c>
       <c r="T48">
         <v>1</v>
@@ -25758,29 +25774,29 @@
       <c r="B49" t="s">
         <v>289</v>
       </c>
+      <c r="C49" s="1">
+        <v>45962</v>
+      </c>
       <c r="D49" t="s">
+        <v>19</v>
+      </c>
+      <c r="H49" t="s">
         <v>104</v>
       </c>
-      <c r="H49" s="2" t="s">
+      <c r="L49" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="I49" t="e" vm="31">
+      <c r="M49" t="e" vm="31">
         <v>#VALUE!</v>
       </c>
-      <c r="J49" t="s">
+      <c r="N49" t="s">
         <v>187</v>
       </c>
-      <c r="L49" t="s">
+      <c r="P49" t="s">
         <v>24</v>
       </c>
-      <c r="M49" s="1">
-        <v>45962</v>
-      </c>
-      <c r="N49" s="1">
+      <c r="Q49" s="1">
         <v>45979</v>
-      </c>
-      <c r="P49" t="s">
-        <v>19</v>
       </c>
       <c r="T49">
         <v>1</v>
@@ -25796,32 +25812,32 @@
       <c r="A50" t="s">
         <v>223</v>
       </c>
+      <c r="C50" s="1">
+        <v>45966</v>
+      </c>
       <c r="D50" t="s">
+        <v>45</v>
+      </c>
+      <c r="E50" t="s">
+        <v>227</v>
+      </c>
+      <c r="H50" t="s">
         <v>104</v>
       </c>
-      <c r="H50" t="s">
+      <c r="L50" t="s">
         <v>222</v>
       </c>
-      <c r="I50" t="e" vm="5">
+      <c r="M50" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
-      <c r="J50" t="s">
+      <c r="N50" t="s">
         <v>15</v>
       </c>
-      <c r="L50" t="s">
+      <c r="P50" t="s">
         <v>23</v>
       </c>
-      <c r="M50" s="1">
-        <v>45966</v>
-      </c>
-      <c r="N50" s="1">
+      <c r="Q50" s="1">
         <v>45716</v>
-      </c>
-      <c r="P50" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q50" t="s">
-        <v>227</v>
       </c>
       <c r="T50">
         <v>1</v>
@@ -25837,32 +25853,32 @@
       <c r="A51" t="s">
         <v>225</v>
       </c>
+      <c r="C51" s="1">
+        <v>45966</v>
+      </c>
       <c r="D51" t="s">
+        <v>45</v>
+      </c>
+      <c r="E51" t="s">
+        <v>226</v>
+      </c>
+      <c r="H51" t="s">
         <v>104</v>
       </c>
-      <c r="H51" t="s">
+      <c r="L51" t="s">
         <v>224</v>
       </c>
-      <c r="I51" t="e" vm="5">
+      <c r="M51" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
-      <c r="J51" t="s">
+      <c r="N51" t="s">
         <v>15</v>
       </c>
-      <c r="L51" t="s">
+      <c r="P51" t="s">
         <v>23</v>
       </c>
-      <c r="M51" s="1">
-        <v>45966</v>
-      </c>
-      <c r="N51" s="1">
+      <c r="Q51" s="1">
         <v>45975</v>
-      </c>
-      <c r="P51" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q51" t="s">
-        <v>226</v>
       </c>
       <c r="T51">
         <v>1</v>
@@ -25878,35 +25894,35 @@
       <c r="A52" t="s">
         <v>243</v>
       </c>
-      <c r="C52">
+      <c r="C52" s="1">
+        <v>45966</v>
+      </c>
+      <c r="D52" t="s">
+        <v>45</v>
+      </c>
+      <c r="E52" t="s">
+        <v>244</v>
+      </c>
+      <c r="F52">
         <v>1</v>
       </c>
-      <c r="D52" t="s">
+      <c r="H52" t="s">
         <v>104</v>
       </c>
-      <c r="H52" t="s">
+      <c r="L52" t="s">
         <v>242</v>
       </c>
-      <c r="I52" t="e" vm="32">
+      <c r="M52" t="e" vm="32">
         <v>#VALUE!</v>
       </c>
-      <c r="J52" t="s">
+      <c r="N52" t="s">
         <v>15</v>
       </c>
-      <c r="L52" t="s">
+      <c r="P52" t="s">
         <v>23</v>
       </c>
-      <c r="M52" s="1">
-        <v>45966</v>
-      </c>
-      <c r="N52" s="1">
+      <c r="Q52" s="1">
         <v>45976</v>
-      </c>
-      <c r="P52" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q52" t="s">
-        <v>244</v>
       </c>
       <c r="T52">
         <v>1</v>
@@ -25922,32 +25938,32 @@
       <c r="A53" t="s">
         <v>320</v>
       </c>
+      <c r="C53" s="1">
+        <v>45966</v>
+      </c>
       <c r="D53" t="s">
+        <v>19</v>
+      </c>
+      <c r="G53" t="s">
+        <v>321</v>
+      </c>
+      <c r="H53" t="s">
         <v>104</v>
       </c>
-      <c r="H53" t="s">
+      <c r="L53" t="s">
         <v>319</v>
       </c>
-      <c r="I53" t="e" vm="17">
+      <c r="M53" t="e" vm="17">
         <v>#VALUE!</v>
       </c>
-      <c r="J53" t="s">
+      <c r="N53" t="s">
         <v>15</v>
       </c>
-      <c r="L53" t="s">
+      <c r="P53" t="s">
         <v>23</v>
       </c>
-      <c r="M53" s="1">
-        <v>45966</v>
-      </c>
-      <c r="N53" s="1">
+      <c r="Q53" s="1">
         <v>45978</v>
-      </c>
-      <c r="O53" t="s">
-        <v>321</v>
-      </c>
-      <c r="P53" t="s">
-        <v>19</v>
       </c>
       <c r="T53">
         <v>1</v>
@@ -25966,38 +25982,38 @@
       <c r="B54" t="s">
         <v>324</v>
       </c>
-      <c r="C54">
+      <c r="C54" s="1">
+        <v>45966</v>
+      </c>
+      <c r="D54" t="s">
+        <v>19</v>
+      </c>
+      <c r="F54">
         <v>1</v>
       </c>
-      <c r="D54" t="s">
+      <c r="H54" t="s">
         <v>104</v>
       </c>
-      <c r="F54" t="s">
+      <c r="J54" t="s">
         <v>253</v>
       </c>
-      <c r="G54" s="1">
+      <c r="K54" s="1">
         <v>45976</v>
       </c>
-      <c r="H54" t="s">
+      <c r="L54" t="s">
         <v>322</v>
       </c>
-      <c r="I54" t="e" vm="30">
+      <c r="M54" t="e" vm="30">
         <v>#VALUE!</v>
       </c>
-      <c r="J54" t="s">
+      <c r="N54" t="s">
         <v>15</v>
       </c>
-      <c r="L54" t="s">
+      <c r="P54" t="s">
         <v>23</v>
       </c>
-      <c r="M54" s="1">
-        <v>45966</v>
-      </c>
-      <c r="N54" s="1">
+      <c r="Q54" s="1">
         <v>45977</v>
-      </c>
-      <c r="P54" t="s">
-        <v>19</v>
       </c>
       <c r="T54">
         <v>1</v>
@@ -26013,29 +26029,29 @@
       <c r="A55" t="s">
         <v>326</v>
       </c>
+      <c r="C55" s="1">
+        <v>45966</v>
+      </c>
       <c r="D55" t="s">
+        <v>19</v>
+      </c>
+      <c r="H55" t="s">
         <v>104</v>
       </c>
-      <c r="H55" t="s">
+      <c r="L55" t="s">
         <v>325</v>
       </c>
-      <c r="I55" t="e" vm="33">
+      <c r="M55" t="e" vm="33">
         <v>#VALUE!</v>
       </c>
-      <c r="J55" t="s">
+      <c r="N55" t="s">
         <v>15</v>
       </c>
-      <c r="L55" t="s">
+      <c r="P55" t="s">
         <v>23</v>
       </c>
-      <c r="M55" s="1">
-        <v>45966</v>
-      </c>
-      <c r="N55" s="1">
+      <c r="Q55" s="1">
         <v>45977</v>
-      </c>
-      <c r="P55" t="s">
-        <v>19</v>
       </c>
       <c r="T55">
         <v>1</v>
@@ -26051,29 +26067,29 @@
       <c r="A56" t="s">
         <v>336</v>
       </c>
+      <c r="C56" s="1">
+        <v>45966</v>
+      </c>
       <c r="D56" t="s">
+        <v>19</v>
+      </c>
+      <c r="H56" t="s">
         <v>104</v>
       </c>
-      <c r="H56" t="s">
+      <c r="L56" t="s">
         <v>335</v>
       </c>
-      <c r="I56" t="e" vm="34">
+      <c r="M56" t="e" vm="34">
         <v>#VALUE!</v>
       </c>
-      <c r="J56" t="s">
+      <c r="N56" t="s">
         <v>15</v>
       </c>
-      <c r="L56" t="s">
+      <c r="P56" t="s">
         <v>23</v>
       </c>
-      <c r="M56" s="1">
-        <v>45966</v>
-      </c>
-      <c r="N56" s="1">
+      <c r="Q56" s="1">
         <v>45976</v>
-      </c>
-      <c r="P56" t="s">
-        <v>19</v>
       </c>
       <c r="T56">
         <v>1</v>
@@ -26089,29 +26105,29 @@
       <c r="A57" t="s">
         <v>338</v>
       </c>
+      <c r="C57" s="1">
+        <v>45966</v>
+      </c>
       <c r="D57" t="s">
+        <v>19</v>
+      </c>
+      <c r="H57" t="s">
         <v>104</v>
       </c>
-      <c r="H57" t="s">
+      <c r="L57" t="s">
         <v>337</v>
       </c>
-      <c r="I57" t="e" vm="30">
+      <c r="M57" t="e" vm="30">
         <v>#VALUE!</v>
       </c>
-      <c r="J57" t="s">
+      <c r="N57" t="s">
         <v>15</v>
       </c>
-      <c r="L57" t="s">
+      <c r="P57" t="s">
         <v>23</v>
       </c>
-      <c r="M57" s="1">
-        <v>45966</v>
-      </c>
-      <c r="N57" s="1">
+      <c r="Q57" s="1">
         <v>45975</v>
-      </c>
-      <c r="P57" t="s">
-        <v>19</v>
       </c>
       <c r="T57">
         <v>1</v>
@@ -26127,32 +26143,32 @@
       <c r="A58" t="s">
         <v>340</v>
       </c>
+      <c r="C58" s="1">
+        <v>45966</v>
+      </c>
       <c r="D58" t="s">
+        <v>19</v>
+      </c>
+      <c r="G58" t="s">
+        <v>341</v>
+      </c>
+      <c r="H58" t="s">
         <v>104</v>
       </c>
-      <c r="H58" t="s">
+      <c r="L58" t="s">
         <v>339</v>
       </c>
-      <c r="I58" t="e" vm="34">
+      <c r="M58" t="e" vm="34">
         <v>#VALUE!</v>
       </c>
-      <c r="J58" t="s">
+      <c r="N58" t="s">
         <v>31</v>
       </c>
-      <c r="L58" t="s">
+      <c r="P58" t="s">
         <v>23</v>
       </c>
-      <c r="M58" s="1">
-        <v>45966</v>
-      </c>
-      <c r="N58" s="1">
+      <c r="Q58" s="1">
         <v>45975</v>
-      </c>
-      <c r="O58" t="s">
-        <v>341</v>
-      </c>
-      <c r="P58" t="s">
-        <v>19</v>
       </c>
       <c r="T58">
         <v>1</v>
@@ -26168,32 +26184,32 @@
       <c r="A59" t="s">
         <v>343</v>
       </c>
+      <c r="C59" s="1">
+        <v>45966</v>
+      </c>
       <c r="D59" t="s">
+        <v>19</v>
+      </c>
+      <c r="G59" t="s">
+        <v>344</v>
+      </c>
+      <c r="H59" t="s">
         <v>104</v>
       </c>
-      <c r="H59" t="s">
+      <c r="L59" t="s">
         <v>342</v>
       </c>
-      <c r="I59" t="e" vm="34">
+      <c r="M59" t="e" vm="34">
         <v>#VALUE!</v>
       </c>
-      <c r="J59" t="s">
+      <c r="N59" t="s">
         <v>15</v>
       </c>
-      <c r="L59" t="s">
+      <c r="P59" t="s">
         <v>23</v>
       </c>
-      <c r="M59" s="1">
-        <v>45966</v>
-      </c>
-      <c r="N59" s="1">
+      <c r="Q59" s="1">
         <v>45975</v>
-      </c>
-      <c r="O59" t="s">
-        <v>344</v>
-      </c>
-      <c r="P59" t="s">
-        <v>19</v>
       </c>
       <c r="T59">
         <v>1</v>
@@ -26209,38 +26225,41 @@
       <c r="A60" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="C60">
+      <c r="B60" t="s">
+        <v>417</v>
+      </c>
+      <c r="C60" s="1">
+        <v>45966</v>
+      </c>
+      <c r="D60" t="s">
+        <v>19</v>
+      </c>
+      <c r="F60">
         <v>2</v>
       </c>
-      <c r="D60" t="s">
+      <c r="H60" t="s">
         <v>28</v>
       </c>
-      <c r="F60" t="s">
+      <c r="J60" t="s">
         <v>253</v>
       </c>
-      <c r="G60" s="1">
+      <c r="K60" s="1">
         <v>45976</v>
       </c>
-      <c r="H60" s="2" t="s">
+      <c r="L60" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="I60" t="e" vm="9">
+      <c r="M60" t="e" vm="9">
         <v>#VALUE!</v>
       </c>
-      <c r="J60" t="s">
+      <c r="N60" t="s">
         <v>15</v>
       </c>
-      <c r="L60" t="s">
+      <c r="P60" t="s">
         <v>23</v>
       </c>
-      <c r="M60" s="1">
-        <v>45966</v>
-      </c>
-      <c r="N60" s="1">
+      <c r="Q60" s="1">
         <v>45971</v>
-      </c>
-      <c r="P60" t="s">
-        <v>19</v>
       </c>
       <c r="T60">
         <v>1</v>
@@ -26256,35 +26275,35 @@
       <c r="A61" t="s">
         <v>170</v>
       </c>
+      <c r="C61" s="1">
+        <v>45966</v>
+      </c>
       <c r="D61" t="s">
+        <v>19</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H61" t="s">
         <v>104</v>
       </c>
-      <c r="H61" s="2" t="s">
+      <c r="L61" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="I61" t="e" vm="35">
+      <c r="M61" t="e" vm="35">
         <v>#VALUE!</v>
       </c>
-      <c r="J61" t="s">
+      <c r="N61" t="s">
         <v>15</v>
       </c>
-      <c r="K61" t="s">
+      <c r="O61" t="s">
         <v>100</v>
       </c>
-      <c r="L61" t="s">
+      <c r="P61" t="s">
         <v>23</v>
       </c>
-      <c r="M61" s="1">
-        <v>45966</v>
-      </c>
-      <c r="N61" s="1">
+      <c r="Q61" s="1">
         <v>45971</v>
-      </c>
-      <c r="P61" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q61" s="2" t="s">
-        <v>172</v>
       </c>
       <c r="T61">
         <v>1</v>
@@ -26300,36 +26319,36 @@
       <c r="A62" t="s">
         <v>38</v>
       </c>
+      <c r="C62" s="1">
+        <v>45966</v>
+      </c>
       <c r="D62" t="s">
+        <v>19</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G62" s="1"/>
+      <c r="H62" t="s">
         <v>104</v>
       </c>
-      <c r="H62" s="2" t="s">
+      <c r="L62" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="I62" t="e" vm="36">
+      <c r="M62" t="e" vm="36">
         <v>#VALUE!</v>
       </c>
-      <c r="J62" t="s">
+      <c r="N62" t="s">
         <v>15</v>
       </c>
-      <c r="K62" t="s">
+      <c r="O62" t="s">
         <v>22</v>
       </c>
-      <c r="L62" t="s">
+      <c r="P62" t="s">
         <v>23</v>
       </c>
-      <c r="M62" s="1">
-        <v>45966</v>
-      </c>
-      <c r="N62" s="1">
+      <c r="Q62" s="1">
         <v>45971</v>
-      </c>
-      <c r="O62" s="1"/>
-      <c r="P62" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q62" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="R62" s="2"/>
       <c r="T62">
@@ -26346,33 +26365,33 @@
       <c r="A63" t="s">
         <v>97</v>
       </c>
+      <c r="C63" s="1">
+        <v>45966</v>
+      </c>
       <c r="D63" t="s">
+        <v>99</v>
+      </c>
+      <c r="G63" s="1"/>
+      <c r="H63" t="s">
         <v>104</v>
       </c>
-      <c r="H63" s="2" t="s">
+      <c r="L63" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="I63" t="e" vm="37">
+      <c r="M63" t="e" vm="37">
         <v>#VALUE!</v>
       </c>
-      <c r="J63" t="s">
+      <c r="N63" t="s">
         <v>15</v>
       </c>
-      <c r="K63" t="s">
+      <c r="O63" t="s">
         <v>100</v>
       </c>
-      <c r="L63" t="s">
+      <c r="P63" t="s">
         <v>23</v>
       </c>
-      <c r="M63" s="1">
-        <v>45966</v>
-      </c>
-      <c r="N63" s="1">
+      <c r="Q63" s="1">
         <v>45971</v>
-      </c>
-      <c r="O63" s="1"/>
-      <c r="P63" t="s">
-        <v>99</v>
       </c>
       <c r="T63">
         <v>1</v>
@@ -26388,33 +26407,33 @@
       <c r="A64" t="s">
         <v>101</v>
       </c>
+      <c r="C64" s="1">
+        <v>45966</v>
+      </c>
       <c r="D64" t="s">
+        <v>45</v>
+      </c>
+      <c r="E64" t="s">
+        <v>103</v>
+      </c>
+      <c r="G64" s="1"/>
+      <c r="H64" t="s">
         <v>104</v>
       </c>
-      <c r="H64" s="2" t="s">
+      <c r="L64" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="I64" t="e" vm="38">
+      <c r="M64" t="e" vm="38">
         <v>#VALUE!</v>
       </c>
-      <c r="J64" t="s">
+      <c r="N64" t="s">
         <v>15</v>
       </c>
-      <c r="L64" t="s">
+      <c r="P64" t="s">
         <v>23</v>
       </c>
-      <c r="M64" s="1">
-        <v>45966</v>
-      </c>
-      <c r="N64" s="1">
+      <c r="Q64" s="1">
         <v>45971</v>
-      </c>
-      <c r="O64" s="1"/>
-      <c r="P64" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q64" t="s">
-        <v>103</v>
       </c>
       <c r="T64">
         <v>1</v>
@@ -26430,38 +26449,38 @@
       <c r="A65" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="C65">
+      <c r="C65" s="1">
+        <v>45966</v>
+      </c>
+      <c r="D65" t="s">
+        <v>19</v>
+      </c>
+      <c r="F65">
         <v>3</v>
       </c>
-      <c r="D65" t="s">
+      <c r="H65" t="s">
         <v>28</v>
       </c>
-      <c r="F65" t="s">
+      <c r="J65" t="s">
         <v>253</v>
       </c>
-      <c r="G65" s="1">
+      <c r="K65" s="1">
         <v>45976</v>
       </c>
-      <c r="H65" s="2" t="s">
+      <c r="L65" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="I65" t="e" vm="34">
+      <c r="M65" t="e" vm="34">
         <v>#VALUE!</v>
       </c>
-      <c r="J65" t="s">
+      <c r="N65" t="s">
         <v>15</v>
       </c>
-      <c r="L65" t="s">
+      <c r="P65" t="s">
         <v>23</v>
       </c>
-      <c r="M65" s="1">
-        <v>45966</v>
-      </c>
-      <c r="N65" s="1">
+      <c r="Q65" s="1">
         <v>45974</v>
-      </c>
-      <c r="P65" t="s">
-        <v>19</v>
       </c>
       <c r="T65">
         <v>1</v>
@@ -26477,29 +26496,29 @@
       <c r="A66" t="s">
         <v>374</v>
       </c>
+      <c r="C66" s="1">
+        <v>45966</v>
+      </c>
       <c r="D66" t="s">
+        <v>376</v>
+      </c>
+      <c r="H66" t="s">
         <v>104</v>
       </c>
-      <c r="H66" t="s">
+      <c r="L66" t="s">
         <v>375</v>
       </c>
-      <c r="I66" t="e" vm="39">
+      <c r="M66" t="e" vm="39">
         <v>#VALUE!</v>
       </c>
-      <c r="J66" t="s">
+      <c r="N66" t="s">
         <v>15</v>
       </c>
-      <c r="L66" t="s">
+      <c r="P66" t="s">
         <v>23</v>
       </c>
-      <c r="M66" s="1">
-        <v>45966</v>
-      </c>
-      <c r="N66" s="1">
+      <c r="Q66" s="1">
         <v>45975</v>
-      </c>
-      <c r="P66" t="s">
-        <v>376</v>
       </c>
       <c r="T66">
         <v>1</v>
@@ -26515,26 +26534,26 @@
       <c r="A67" t="s">
         <v>402</v>
       </c>
+      <c r="C67" s="1">
+        <v>45966</v>
+      </c>
       <c r="D67" t="s">
+        <v>19</v>
+      </c>
+      <c r="H67" t="s">
         <v>104</v>
       </c>
-      <c r="H67" t="s">
+      <c r="L67" t="s">
         <v>403</v>
       </c>
-      <c r="I67" t="e" vm="40">
+      <c r="M67" t="e" vm="40">
         <v>#VALUE!</v>
       </c>
-      <c r="L67" t="s">
+      <c r="P67" t="s">
         <v>23</v>
       </c>
-      <c r="M67" s="1">
-        <v>45966</v>
-      </c>
-      <c r="N67" s="1">
+      <c r="Q67" s="1">
         <v>45977</v>
-      </c>
-      <c r="P67" t="s">
-        <v>19</v>
       </c>
       <c r="T67">
         <v>1</v>
@@ -26550,29 +26569,29 @@
       <c r="A68" t="s">
         <v>327</v>
       </c>
+      <c r="C68" s="1">
+        <v>45966</v>
+      </c>
       <c r="D68" t="s">
+        <v>19</v>
+      </c>
+      <c r="H68" t="s">
         <v>104</v>
       </c>
-      <c r="H68" t="s">
+      <c r="L68" t="s">
         <v>404</v>
       </c>
-      <c r="I68" t="e" vm="41">
+      <c r="M68" t="e" vm="41">
         <v>#VALUE!</v>
       </c>
-      <c r="J68" t="s">
+      <c r="N68" t="s">
         <v>15</v>
       </c>
-      <c r="L68" t="s">
+      <c r="P68" t="s">
         <v>23</v>
       </c>
-      <c r="M68" s="1">
-        <v>45966</v>
-      </c>
-      <c r="N68" s="1">
+      <c r="Q68" s="1">
         <v>45976</v>
-      </c>
-      <c r="P68" t="s">
-        <v>19</v>
       </c>
       <c r="T68">
         <v>1</v>
@@ -26588,32 +26607,32 @@
       <c r="A69" t="s">
         <v>405</v>
       </c>
+      <c r="C69" s="1">
+        <v>45966</v>
+      </c>
       <c r="D69" t="s">
+        <v>19</v>
+      </c>
+      <c r="G69" t="s">
+        <v>407</v>
+      </c>
+      <c r="H69" t="s">
         <v>104</v>
       </c>
-      <c r="H69" t="s">
+      <c r="L69" t="s">
         <v>406</v>
       </c>
-      <c r="I69" t="e" vm="42">
+      <c r="M69" t="e" vm="42">
         <v>#VALUE!</v>
       </c>
-      <c r="J69" t="s">
+      <c r="N69" t="s">
         <v>31</v>
       </c>
-      <c r="L69" t="s">
+      <c r="P69" t="s">
         <v>23</v>
       </c>
-      <c r="M69" s="1">
-        <v>45966</v>
-      </c>
-      <c r="N69" s="1">
+      <c r="Q69" s="1">
         <v>45976</v>
-      </c>
-      <c r="O69" t="s">
-        <v>407</v>
-      </c>
-      <c r="P69" t="s">
-        <v>19</v>
       </c>
       <c r="T69">
         <v>1</v>
@@ -26629,33 +26648,33 @@
       <c r="A70" t="s">
         <v>40</v>
       </c>
-      <c r="C70">
+      <c r="C70" s="1">
+        <v>45971</v>
+      </c>
+      <c r="E70" t="s">
+        <v>52</v>
+      </c>
+      <c r="F70">
         <v>1</v>
       </c>
-      <c r="D70" t="s">
+      <c r="G70" s="1"/>
+      <c r="H70" t="s">
         <v>104</v>
       </c>
-      <c r="H70" s="2" t="s">
+      <c r="L70" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="I70" t="e" vm="43">
+      <c r="M70" t="e" vm="43">
         <v>#VALUE!</v>
       </c>
-      <c r="J70" t="s">
+      <c r="N70" t="s">
         <v>42</v>
       </c>
-      <c r="L70" t="s">
+      <c r="P70" t="s">
         <v>23</v>
       </c>
-      <c r="M70" s="1">
+      <c r="Q70" s="1">
         <v>45971</v>
-      </c>
-      <c r="N70" s="1">
-        <v>45971</v>
-      </c>
-      <c r="O70" s="1"/>
-      <c r="Q70" t="s">
-        <v>52</v>
       </c>
       <c r="T70">
         <v>1</v>
@@ -26671,36 +26690,36 @@
       <c r="A71" t="s">
         <v>49</v>
       </c>
-      <c r="C71">
+      <c r="C71" s="1">
+        <v>45971</v>
+      </c>
+      <c r="D71" t="s">
+        <v>19</v>
+      </c>
+      <c r="E71" t="s">
+        <v>51</v>
+      </c>
+      <c r="F71">
         <v>1</v>
       </c>
-      <c r="D71" t="s">
+      <c r="G71" s="1"/>
+      <c r="H71" t="s">
         <v>104</v>
       </c>
-      <c r="H71" s="2" t="s">
+      <c r="L71" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="I71" t="e" vm="44">
+      <c r="M71" t="e" vm="44">
         <v>#VALUE!</v>
       </c>
-      <c r="J71" t="s">
+      <c r="N71" t="s">
         <v>15</v>
       </c>
-      <c r="L71" t="s">
+      <c r="P71" t="s">
         <v>23</v>
       </c>
-      <c r="M71" s="1">
-        <v>45971</v>
-      </c>
-      <c r="N71" s="1">
+      <c r="Q71" s="1">
         <v>46010</v>
-      </c>
-      <c r="O71" s="1"/>
-      <c r="P71" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q71" t="s">
-        <v>51</v>
       </c>
       <c r="T71">
         <v>1</v>
@@ -26716,39 +26735,39 @@
       <c r="A72" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="C72">
+      <c r="C72" s="1">
+        <v>45971</v>
+      </c>
+      <c r="D72" t="s">
+        <v>80</v>
+      </c>
+      <c r="F72">
         <v>3</v>
       </c>
-      <c r="D72" t="s">
+      <c r="G72" s="1"/>
+      <c r="H72" t="s">
         <v>28</v>
       </c>
-      <c r="F72" t="s">
+      <c r="J72" t="s">
         <v>253</v>
       </c>
-      <c r="G72" s="1">
+      <c r="K72" s="1">
         <v>45976</v>
       </c>
-      <c r="H72" s="2" t="s">
+      <c r="L72" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="I72" t="e" vm="45">
+      <c r="M72" t="e" vm="45">
         <v>#VALUE!</v>
       </c>
-      <c r="J72" t="s">
+      <c r="N72" t="s">
         <v>15</v>
       </c>
-      <c r="L72" t="s">
+      <c r="P72" t="s">
         <v>23</v>
       </c>
-      <c r="M72" s="1">
-        <v>45971</v>
-      </c>
-      <c r="N72" s="1">
+      <c r="Q72" s="1">
         <v>45976</v>
-      </c>
-      <c r="O72" s="1"/>
-      <c r="P72" t="s">
-        <v>80</v>
       </c>
       <c r="T72">
         <v>1</v>
@@ -26764,39 +26783,39 @@
       <c r="A73" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="C73">
+      <c r="C73" s="1">
+        <v>45971</v>
+      </c>
+      <c r="D73" t="s">
+        <v>19</v>
+      </c>
+      <c r="F73">
         <v>2</v>
       </c>
-      <c r="D73" t="s">
+      <c r="G73" s="1"/>
+      <c r="H73" t="s">
         <v>28</v>
       </c>
-      <c r="F73" t="s">
+      <c r="J73" t="s">
         <v>253</v>
       </c>
-      <c r="G73" s="1">
+      <c r="K73" s="1">
         <v>45976</v>
       </c>
-      <c r="H73" s="2" t="s">
+      <c r="L73" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="I73" t="e" vm="43">
+      <c r="M73" t="e" vm="43">
         <v>#VALUE!</v>
       </c>
-      <c r="J73" t="s">
+      <c r="N73" t="s">
         <v>15</v>
       </c>
-      <c r="L73" t="s">
+      <c r="P73" t="s">
         <v>23</v>
       </c>
-      <c r="M73" s="1">
-        <v>45971</v>
-      </c>
-      <c r="N73" s="1">
+      <c r="Q73" s="1">
         <v>45976</v>
-      </c>
-      <c r="O73" s="1"/>
-      <c r="P73" t="s">
-        <v>19</v>
       </c>
       <c r="T73">
         <v>1</v>
@@ -26812,41 +26831,41 @@
       <c r="A74" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="C74">
+      <c r="C74" s="1">
+        <v>45971</v>
+      </c>
+      <c r="D74" t="s">
+        <v>19</v>
+      </c>
+      <c r="F74">
         <v>2</v>
       </c>
-      <c r="D74" t="s">
+      <c r="G74" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="H74" t="s">
         <v>104</v>
       </c>
-      <c r="F74" t="s">
+      <c r="J74" t="s">
         <v>253</v>
       </c>
-      <c r="G74" s="1">
+      <c r="K74" s="1">
         <v>45976</v>
       </c>
-      <c r="H74" s="2" t="s">
+      <c r="L74" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="I74" t="e" vm="46">
+      <c r="M74" t="e" vm="46">
         <v>#VALUE!</v>
       </c>
-      <c r="J74" t="s">
+      <c r="N74" t="s">
         <v>15</v>
       </c>
-      <c r="L74" t="s">
+      <c r="P74" t="s">
         <v>23</v>
       </c>
-      <c r="M74" s="1">
-        <v>45971</v>
-      </c>
-      <c r="N74" s="1">
+      <c r="Q74" s="1">
         <v>45976</v>
-      </c>
-      <c r="O74" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="P74" t="s">
-        <v>19</v>
       </c>
       <c r="T74">
         <v>1</v>
@@ -26862,38 +26881,38 @@
       <c r="A75" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="C75">
+      <c r="C75" s="1">
+        <v>45971</v>
+      </c>
+      <c r="D75" t="s">
+        <v>19</v>
+      </c>
+      <c r="F75">
         <v>1</v>
       </c>
-      <c r="D75" t="s">
+      <c r="H75" t="s">
         <v>28</v>
       </c>
-      <c r="F75" t="s">
+      <c r="J75" t="s">
         <v>253</v>
       </c>
-      <c r="G75" s="1">
+      <c r="K75" s="1">
         <v>45976</v>
       </c>
-      <c r="H75" s="2" t="s">
+      <c r="L75" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="I75" t="e" vm="8">
+      <c r="M75" t="e" vm="8">
         <v>#VALUE!</v>
       </c>
-      <c r="J75" t="s">
+      <c r="N75" t="s">
         <v>15</v>
       </c>
-      <c r="L75" t="s">
+      <c r="P75" t="s">
         <v>23</v>
       </c>
-      <c r="M75" s="1">
-        <v>45971</v>
-      </c>
-      <c r="N75" s="1">
+      <c r="Q75" s="1">
         <v>45976</v>
-      </c>
-      <c r="P75" t="s">
-        <v>19</v>
       </c>
       <c r="T75">
         <v>1</v>
@@ -26909,38 +26928,38 @@
       <c r="A76" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="C76">
+      <c r="C76" s="1">
+        <v>45971</v>
+      </c>
+      <c r="D76" t="s">
+        <v>19</v>
+      </c>
+      <c r="F76">
         <v>1</v>
       </c>
-      <c r="D76" t="s">
+      <c r="H76" t="s">
         <v>28</v>
       </c>
-      <c r="F76" t="s">
+      <c r="J76" t="s">
         <v>253</v>
       </c>
-      <c r="G76" s="1">
+      <c r="K76" s="1">
         <v>45976</v>
       </c>
-      <c r="H76" s="2" t="s">
+      <c r="L76" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="I76" t="e" vm="8">
+      <c r="M76" t="e" vm="8">
         <v>#VALUE!</v>
       </c>
-      <c r="J76" t="s">
+      <c r="N76" t="s">
         <v>15</v>
       </c>
-      <c r="L76" t="s">
+      <c r="P76" t="s">
         <v>23</v>
       </c>
-      <c r="M76" s="1">
-        <v>45971</v>
-      </c>
-      <c r="N76" s="1">
+      <c r="Q76" s="1">
         <v>45976</v>
-      </c>
-      <c r="P76" t="s">
-        <v>19</v>
       </c>
       <c r="T76">
         <v>1</v>
@@ -26956,41 +26975,41 @@
       <c r="A77" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="C77">
+      <c r="C77" s="1">
+        <v>45971</v>
+      </c>
+      <c r="D77" t="s">
+        <v>19</v>
+      </c>
+      <c r="E77" t="s">
+        <v>143</v>
+      </c>
+      <c r="F77">
         <v>2</v>
       </c>
-      <c r="D77" t="s">
+      <c r="H77" t="s">
         <v>28</v>
       </c>
-      <c r="F77" t="s">
+      <c r="J77" t="s">
         <v>253</v>
       </c>
-      <c r="G77" s="1">
+      <c r="K77" s="1">
         <v>45976</v>
       </c>
-      <c r="H77" s="2" t="s">
+      <c r="L77" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="I77" t="e" vm="8">
+      <c r="M77" t="e" vm="8">
         <v>#VALUE!</v>
       </c>
-      <c r="J77" t="s">
+      <c r="N77" t="s">
         <v>15</v>
       </c>
-      <c r="L77" t="s">
+      <c r="P77" t="s">
         <v>23</v>
       </c>
-      <c r="M77" s="1">
-        <v>45971</v>
-      </c>
-      <c r="N77" s="1">
+      <c r="Q77" s="1">
         <v>45974</v>
-      </c>
-      <c r="P77" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q77" t="s">
-        <v>143</v>
       </c>
       <c r="T77">
         <v>1</v>
@@ -27006,29 +27025,29 @@
       <c r="A78" t="s">
         <v>218</v>
       </c>
+      <c r="C78" s="1">
+        <v>45971</v>
+      </c>
       <c r="D78" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H78" t="s">
+        <v>104</v>
+      </c>
+      <c r="L78" t="s">
         <v>217</v>
       </c>
-      <c r="I78" t="e" vm="5">
+      <c r="M78" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
-      <c r="J78" t="s">
+      <c r="N78" t="s">
         <v>15</v>
       </c>
-      <c r="L78" t="s">
+      <c r="P78" t="s">
         <v>23</v>
       </c>
-      <c r="M78" s="1">
-        <v>45971</v>
-      </c>
-      <c r="N78" s="1">
+      <c r="Q78" s="1">
         <v>45991</v>
-      </c>
-      <c r="P78" t="s">
-        <v>45</v>
       </c>
       <c r="T78">
         <v>1</v>
@@ -27044,29 +27063,29 @@
       <c r="A79" t="s">
         <v>254</v>
       </c>
+      <c r="C79" s="1">
+        <v>45971</v>
+      </c>
       <c r="D79" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="H79" t="s">
+        <v>104</v>
+      </c>
+      <c r="L79" t="s">
         <v>255</v>
       </c>
-      <c r="I79" t="e" vm="42">
+      <c r="M79" t="e" vm="42">
         <v>#VALUE!</v>
       </c>
-      <c r="J79" t="s">
+      <c r="N79" t="s">
         <v>31</v>
       </c>
-      <c r="L79" t="s">
+      <c r="P79" t="s">
         <v>23</v>
       </c>
-      <c r="M79" s="1">
-        <v>45971</v>
-      </c>
-      <c r="N79" s="1">
+      <c r="Q79" s="1">
         <v>45977</v>
-      </c>
-      <c r="P79" t="s">
-        <v>19</v>
       </c>
       <c r="T79">
         <v>1</v>
@@ -27082,38 +27101,38 @@
       <c r="A80" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="C80">
+      <c r="C80" s="1">
+        <v>45971</v>
+      </c>
+      <c r="D80" t="s">
+        <v>19</v>
+      </c>
+      <c r="F80">
         <v>1</v>
       </c>
-      <c r="D80" t="s">
+      <c r="H80" t="s">
         <v>28</v>
       </c>
-      <c r="F80" t="s">
+      <c r="J80" t="s">
         <v>253</v>
       </c>
-      <c r="G80" s="1">
+      <c r="K80" s="1">
         <v>45976</v>
       </c>
-      <c r="H80" t="s">
+      <c r="L80" t="s">
         <v>279</v>
       </c>
-      <c r="I80" t="e" vm="46">
+      <c r="M80" t="e" vm="46">
         <v>#VALUE!</v>
       </c>
-      <c r="J80" t="s">
+      <c r="N80" t="s">
         <v>15</v>
       </c>
-      <c r="L80" t="s">
+      <c r="P80" t="s">
         <v>23</v>
       </c>
-      <c r="M80" s="1">
-        <v>45971</v>
-      </c>
-      <c r="N80" s="1">
+      <c r="Q80" s="1">
         <v>45976</v>
-      </c>
-      <c r="P80" t="s">
-        <v>19</v>
       </c>
       <c r="T80">
         <v>1</v>
@@ -27132,41 +27151,41 @@
       <c r="B81" t="s">
         <v>283</v>
       </c>
-      <c r="C81">
+      <c r="C81" s="1">
+        <v>45971</v>
+      </c>
+      <c r="D81" t="s">
+        <v>19</v>
+      </c>
+      <c r="F81">
         <v>2</v>
       </c>
-      <c r="D81" t="s">
+      <c r="G81" t="s">
+        <v>282</v>
+      </c>
+      <c r="H81" t="s">
         <v>28</v>
       </c>
-      <c r="F81" t="s">
+      <c r="J81" t="s">
         <v>253</v>
       </c>
-      <c r="G81" s="1">
+      <c r="K81" s="1">
         <v>45976</v>
       </c>
-      <c r="H81" t="s">
+      <c r="L81" t="s">
         <v>169</v>
       </c>
-      <c r="I81" t="e" vm="15">
+      <c r="M81" t="e" vm="15">
         <v>#VALUE!</v>
       </c>
-      <c r="J81" t="s">
+      <c r="N81" t="s">
         <v>15</v>
       </c>
-      <c r="L81" t="s">
+      <c r="P81" t="s">
         <v>23</v>
       </c>
-      <c r="M81" s="1">
-        <v>45971</v>
-      </c>
-      <c r="N81" s="1">
+      <c r="Q81" s="1">
         <v>45977</v>
-      </c>
-      <c r="O81" t="s">
-        <v>282</v>
-      </c>
-      <c r="P81" t="s">
-        <v>19</v>
       </c>
       <c r="T81">
         <v>1</v>
@@ -27185,29 +27204,29 @@
       <c r="B82" t="s">
         <v>383</v>
       </c>
+      <c r="C82" s="1">
+        <v>45971</v>
+      </c>
       <c r="D82" t="s">
+        <v>19</v>
+      </c>
+      <c r="H82" t="s">
         <v>28</v>
       </c>
-      <c r="H82" t="s">
+      <c r="L82" t="s">
         <v>208</v>
       </c>
-      <c r="I82" t="e" vm="31">
+      <c r="M82" t="e" vm="31">
         <v>#VALUE!</v>
       </c>
-      <c r="J82" t="s">
+      <c r="N82" t="s">
         <v>15</v>
       </c>
-      <c r="L82" t="s">
+      <c r="P82" t="s">
         <v>23</v>
       </c>
-      <c r="M82" s="1">
-        <v>45971</v>
-      </c>
-      <c r="N82" s="1">
+      <c r="Q82" s="1">
         <v>45975</v>
-      </c>
-      <c r="P82" t="s">
-        <v>19</v>
       </c>
       <c r="T82">
         <v>1</v>
@@ -27226,32 +27245,32 @@
       <c r="B83" t="s">
         <v>288</v>
       </c>
-      <c r="C83">
+      <c r="C83" s="1">
+        <v>45971</v>
+      </c>
+      <c r="D83" t="s">
+        <v>19</v>
+      </c>
+      <c r="F83">
         <v>1</v>
       </c>
-      <c r="D83" t="s">
+      <c r="H83" t="s">
         <v>28</v>
       </c>
-      <c r="H83" t="s">
+      <c r="L83" t="s">
         <v>286</v>
       </c>
-      <c r="I83" t="e" vm="31">
+      <c r="M83" t="e" vm="31">
         <v>#VALUE!</v>
       </c>
-      <c r="J83" t="s">
+      <c r="N83" t="s">
         <v>15</v>
       </c>
-      <c r="L83" t="s">
+      <c r="P83" t="s">
         <v>23</v>
       </c>
-      <c r="M83" s="1">
-        <v>45971</v>
-      </c>
-      <c r="N83" s="1">
+      <c r="Q83" s="1">
         <v>45976</v>
-      </c>
-      <c r="P83" t="s">
-        <v>19</v>
       </c>
       <c r="T83">
         <v>1</v>
@@ -27267,29 +27286,29 @@
       <c r="A84" t="s">
         <v>295</v>
       </c>
+      <c r="C84" s="1">
+        <v>45971</v>
+      </c>
       <c r="D84" t="s">
+        <v>19</v>
+      </c>
+      <c r="H84" t="s">
         <v>28</v>
       </c>
-      <c r="H84" t="s">
+      <c r="L84" t="s">
         <v>294</v>
       </c>
-      <c r="I84" t="e" vm="30">
+      <c r="M84" t="e" vm="30">
         <v>#VALUE!</v>
       </c>
-      <c r="J84" t="s">
+      <c r="N84" t="s">
         <v>31</v>
       </c>
-      <c r="L84" t="s">
+      <c r="P84" t="s">
         <v>23</v>
       </c>
-      <c r="M84" s="1">
-        <v>45971</v>
-      </c>
-      <c r="N84" s="1">
+      <c r="Q84" s="1">
         <v>45981</v>
-      </c>
-      <c r="P84" t="s">
-        <v>19</v>
       </c>
       <c r="T84">
         <v>1</v>
@@ -27305,29 +27324,29 @@
       <c r="A85" t="s">
         <v>298</v>
       </c>
+      <c r="C85" s="1">
+        <v>45971</v>
+      </c>
       <c r="D85" t="s">
+        <v>19</v>
+      </c>
+      <c r="H85" t="s">
         <v>28</v>
       </c>
-      <c r="H85" t="s">
+      <c r="L85" t="s">
         <v>299</v>
       </c>
-      <c r="I85" t="e" vm="47">
+      <c r="M85" t="e" vm="47">
         <v>#VALUE!</v>
       </c>
-      <c r="J85" t="s">
+      <c r="N85" t="s">
         <v>15</v>
       </c>
-      <c r="L85" t="s">
+      <c r="P85" t="s">
         <v>23</v>
       </c>
-      <c r="M85" s="1">
-        <v>45971</v>
-      </c>
-      <c r="N85" s="1">
+      <c r="Q85" s="1">
         <v>45989</v>
-      </c>
-      <c r="P85" t="s">
-        <v>19</v>
       </c>
       <c r="T85">
         <v>1</v>
@@ -27343,32 +27362,32 @@
       <c r="A86" t="s">
         <v>307</v>
       </c>
+      <c r="C86" s="1">
+        <v>45971</v>
+      </c>
       <c r="D86" t="s">
+        <v>19</v>
+      </c>
+      <c r="G86" t="s">
+        <v>308</v>
+      </c>
+      <c r="H86" t="s">
         <v>28</v>
       </c>
-      <c r="H86" t="s">
+      <c r="L86" t="s">
         <v>306</v>
       </c>
-      <c r="I86" t="e" vm="48">
+      <c r="M86" t="e" vm="48">
         <v>#VALUE!</v>
       </c>
-      <c r="J86" t="s">
+      <c r="N86" t="s">
         <v>15</v>
       </c>
-      <c r="L86" t="s">
+      <c r="P86" t="s">
         <v>23</v>
       </c>
-      <c r="M86" s="1">
-        <v>45971</v>
-      </c>
-      <c r="N86" s="1">
+      <c r="Q86" s="1">
         <v>45981</v>
-      </c>
-      <c r="O86" t="s">
-        <v>308</v>
-      </c>
-      <c r="P86" t="s">
-        <v>19</v>
       </c>
       <c r="T86">
         <v>1</v>
@@ -27384,29 +27403,29 @@
       <c r="A87" t="s">
         <v>310</v>
       </c>
+      <c r="C87" s="1">
+        <v>45971</v>
+      </c>
       <c r="D87" t="s">
+        <v>19</v>
+      </c>
+      <c r="H87" t="s">
         <v>28</v>
       </c>
-      <c r="H87" t="s">
+      <c r="L87" t="s">
         <v>309</v>
       </c>
-      <c r="I87" t="e" vm="49">
+      <c r="M87" t="e" vm="49">
         <v>#VALUE!</v>
       </c>
-      <c r="J87" t="s">
+      <c r="N87" t="s">
         <v>15</v>
       </c>
-      <c r="L87" t="s">
+      <c r="P87" t="s">
         <v>23</v>
       </c>
-      <c r="M87" s="1">
-        <v>45971</v>
-      </c>
-      <c r="N87" s="1">
+      <c r="Q87" s="1">
         <v>45981</v>
-      </c>
-      <c r="P87" t="s">
-        <v>19</v>
       </c>
       <c r="T87">
         <v>1</v>
@@ -27422,32 +27441,32 @@
       <c r="A88" t="s">
         <v>311</v>
       </c>
+      <c r="C88" s="1">
+        <v>45971</v>
+      </c>
       <c r="D88" t="s">
+        <v>19</v>
+      </c>
+      <c r="E88" t="s">
+        <v>313</v>
+      </c>
+      <c r="H88" t="s">
         <v>28</v>
       </c>
-      <c r="H88" t="s">
+      <c r="L88" t="s">
         <v>312</v>
       </c>
-      <c r="I88" t="e" vm="47">
+      <c r="M88" t="e" vm="47">
         <v>#VALUE!</v>
       </c>
-      <c r="J88" t="s">
+      <c r="N88" t="s">
         <v>15</v>
       </c>
-      <c r="L88" t="s">
+      <c r="P88" t="s">
         <v>23</v>
       </c>
-      <c r="M88" s="1">
-        <v>45971</v>
-      </c>
-      <c r="N88" s="1">
+      <c r="Q88" s="1">
         <v>45980</v>
-      </c>
-      <c r="P88" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q88" t="s">
-        <v>313</v>
       </c>
       <c r="T88">
         <v>1</v>
@@ -27466,35 +27485,35 @@
       <c r="B89" t="s">
         <v>401</v>
       </c>
+      <c r="C89" s="1">
+        <v>45971</v>
+      </c>
       <c r="D89" t="s">
+        <v>19</v>
+      </c>
+      <c r="E89" t="s">
+        <v>400</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="H89" t="s">
         <v>28</v>
       </c>
-      <c r="H89" t="s">
+      <c r="L89" t="s">
         <v>314</v>
       </c>
-      <c r="I89" t="e" vm="49">
+      <c r="M89" t="e" vm="49">
         <v>#VALUE!</v>
       </c>
-      <c r="J89" t="s">
+      <c r="N89" t="s">
         <v>15</v>
       </c>
-      <c r="L89" t="s">
+      <c r="P89" t="s">
         <v>23</v>
       </c>
-      <c r="M89" s="1">
-        <v>45971</v>
-      </c>
-      <c r="N89" s="1">
+      <c r="Q89" s="1">
         <v>45978</v>
-      </c>
-      <c r="O89" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="P89" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q89" t="s">
-        <v>400</v>
       </c>
       <c r="T89">
         <v>1</v>
@@ -27510,29 +27529,29 @@
       <c r="A90" t="s">
         <v>329</v>
       </c>
+      <c r="C90" s="1">
+        <v>45971</v>
+      </c>
       <c r="D90" t="s">
+        <v>19</v>
+      </c>
+      <c r="H90" t="s">
         <v>28</v>
       </c>
-      <c r="H90" t="s">
+      <c r="L90" t="s">
         <v>328</v>
       </c>
-      <c r="I90" t="e" vm="41">
+      <c r="M90" t="e" vm="41">
         <v>#VALUE!</v>
       </c>
-      <c r="J90" t="s">
+      <c r="N90" t="s">
         <v>15</v>
       </c>
-      <c r="L90" t="s">
+      <c r="P90" t="s">
         <v>23</v>
       </c>
-      <c r="M90" s="1">
-        <v>45971</v>
-      </c>
-      <c r="N90" s="1">
+      <c r="Q90" s="1">
         <v>45976</v>
-      </c>
-      <c r="P90" t="s">
-        <v>19</v>
       </c>
       <c r="T90">
         <v>1</v>
@@ -27548,32 +27567,32 @@
       <c r="A91" t="s">
         <v>331</v>
       </c>
+      <c r="C91" s="1">
+        <v>45971</v>
+      </c>
       <c r="D91" t="s">
+        <v>19</v>
+      </c>
+      <c r="G91" t="s">
+        <v>332</v>
+      </c>
+      <c r="H91" t="s">
         <v>28</v>
       </c>
-      <c r="H91" t="s">
+      <c r="L91" t="s">
         <v>330</v>
       </c>
-      <c r="I91" t="e" vm="31">
+      <c r="M91" t="e" vm="31">
         <v>#VALUE!</v>
       </c>
-      <c r="J91" t="s">
+      <c r="N91" t="s">
         <v>15</v>
       </c>
-      <c r="L91" t="s">
+      <c r="P91" t="s">
         <v>23</v>
       </c>
-      <c r="M91" s="1">
-        <v>45971</v>
-      </c>
-      <c r="N91" s="1">
+      <c r="Q91" s="1">
         <v>45976</v>
-      </c>
-      <c r="O91" t="s">
-        <v>332</v>
-      </c>
-      <c r="P91" t="s">
-        <v>19</v>
       </c>
       <c r="T91">
         <v>1</v>
@@ -27589,29 +27608,29 @@
       <c r="A92" t="s">
         <v>333</v>
       </c>
+      <c r="C92" s="1">
+        <v>45971</v>
+      </c>
       <c r="D92" t="s">
+        <v>45</v>
+      </c>
+      <c r="E92" t="s">
+        <v>334</v>
+      </c>
+      <c r="H92" t="s">
         <v>28</v>
       </c>
-      <c r="H92" t="s">
+      <c r="L92" t="s">
         <v>91</v>
       </c>
-      <c r="I92" t="e" vm="4">
+      <c r="M92" t="e" vm="4">
         <v>#VALUE!</v>
       </c>
-      <c r="L92" t="s">
+      <c r="P92" t="s">
         <v>23</v>
       </c>
-      <c r="M92" s="1">
-        <v>45971</v>
-      </c>
-      <c r="N92" s="1">
+      <c r="Q92" s="1">
         <v>45973</v>
-      </c>
-      <c r="P92" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q92" t="s">
-        <v>334</v>
       </c>
       <c r="T92">
         <v>1</v>
@@ -27627,36 +27646,36 @@
       <c r="A93" t="s">
         <v>87</v>
       </c>
+      <c r="C93" s="1">
+        <v>45971</v>
+      </c>
       <c r="D93" t="s">
+        <v>89</v>
+      </c>
+      <c r="E93" t="s">
+        <v>19</v>
+      </c>
+      <c r="G93" s="1"/>
+      <c r="H93" t="s">
         <v>28</v>
       </c>
-      <c r="H93" s="2" t="s">
+      <c r="L93" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="I93" t="e" vm="50">
+      <c r="M93" t="e" vm="50">
         <v>#VALUE!</v>
       </c>
-      <c r="J93" t="s">
+      <c r="N93" t="s">
         <v>31</v>
       </c>
-      <c r="K93" t="s">
+      <c r="O93" t="s">
         <v>22</v>
       </c>
-      <c r="L93" t="s">
+      <c r="P93" t="s">
         <v>23</v>
       </c>
-      <c r="M93" s="1">
-        <v>45971</v>
-      </c>
-      <c r="N93" s="1">
+      <c r="Q93" s="1">
         <v>45976</v>
-      </c>
-      <c r="O93" s="1"/>
-      <c r="P93" t="s">
-        <v>89</v>
-      </c>
-      <c r="Q93" t="s">
-        <v>19</v>
       </c>
       <c r="T93">
         <v>1</v>
@@ -27675,33 +27694,33 @@
       <c r="A94" t="s">
         <v>118</v>
       </c>
+      <c r="C94" s="1">
+        <v>45971</v>
+      </c>
       <c r="D94" t="s">
+        <v>45</v>
+      </c>
+      <c r="E94" t="s">
+        <v>159</v>
+      </c>
+      <c r="G94" s="1"/>
+      <c r="H94" t="s">
         <v>28</v>
       </c>
-      <c r="H94" s="2" t="s">
+      <c r="L94" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="I94" t="e" vm="1">
+      <c r="M94" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="J94" t="s">
+      <c r="N94" t="s">
         <v>15</v>
       </c>
-      <c r="L94" t="s">
+      <c r="P94" t="s">
         <v>23</v>
       </c>
-      <c r="M94" s="1">
-        <v>45971</v>
-      </c>
-      <c r="N94" s="1">
+      <c r="Q94" s="1">
         <v>45976</v>
-      </c>
-      <c r="O94" s="1"/>
-      <c r="P94" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q94" t="s">
-        <v>159</v>
       </c>
       <c r="T94">
         <v>1</v>
@@ -27717,39 +27736,39 @@
       <c r="A95" t="s">
         <v>29</v>
       </c>
-      <c r="C95">
+      <c r="C95" s="1">
+        <v>45971</v>
+      </c>
+      <c r="D95" t="s">
+        <v>19</v>
+      </c>
+      <c r="E95" t="s">
+        <v>19</v>
+      </c>
+      <c r="F95">
         <v>1</v>
       </c>
-      <c r="D95" t="s">
+      <c r="G95" s="1"/>
+      <c r="H95" t="s">
         <v>113</v>
       </c>
-      <c r="H95" s="2" t="s">
+      <c r="L95" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="I95" t="e" vm="51">
+      <c r="M95" t="e" vm="51">
         <v>#VALUE!</v>
       </c>
-      <c r="J95" t="s">
+      <c r="N95" t="s">
         <v>31</v>
       </c>
-      <c r="K95" t="s">
+      <c r="O95" t="s">
         <v>32</v>
       </c>
-      <c r="L95" t="s">
+      <c r="P95" t="s">
         <v>23</v>
       </c>
-      <c r="M95" s="1">
-        <v>45971</v>
-      </c>
-      <c r="N95" s="1">
+      <c r="Q95" s="1">
         <v>45978</v>
-      </c>
-      <c r="O95" s="1"/>
-      <c r="P95" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q95" t="s">
-        <v>19</v>
       </c>
       <c r="T95">
         <v>1</v>
@@ -27765,36 +27784,36 @@
       <c r="A96" t="s">
         <v>34</v>
       </c>
+      <c r="C96" s="1">
+        <v>45971</v>
+      </c>
       <c r="D96" t="s">
+        <v>19</v>
+      </c>
+      <c r="E96" t="s">
+        <v>19</v>
+      </c>
+      <c r="G96" s="1"/>
+      <c r="H96" t="s">
         <v>28</v>
       </c>
-      <c r="H96" s="11" t="s">
+      <c r="L96" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="I96" t="e" vm="52">
+      <c r="M96" t="e" vm="52">
         <v>#VALUE!</v>
       </c>
-      <c r="J96" t="s">
+      <c r="N96" t="s">
         <v>15</v>
       </c>
-      <c r="K96" t="s">
+      <c r="O96" t="s">
         <v>36</v>
       </c>
-      <c r="L96" t="s">
+      <c r="P96" t="s">
         <v>23</v>
       </c>
-      <c r="M96" s="1">
-        <v>45971</v>
-      </c>
-      <c r="N96" s="1">
+      <c r="Q96" s="1">
         <v>45978</v>
-      </c>
-      <c r="O96" s="1"/>
-      <c r="P96" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q96" t="s">
-        <v>19</v>
       </c>
       <c r="T96">
         <v>1</v>
@@ -27813,41 +27832,41 @@
       <c r="B97" t="s">
         <v>355</v>
       </c>
-      <c r="C97">
+      <c r="C97" s="1">
+        <v>45971</v>
+      </c>
+      <c r="D97" t="s">
+        <v>354</v>
+      </c>
+      <c r="E97" t="s">
+        <v>353</v>
+      </c>
+      <c r="F97">
         <v>1</v>
       </c>
-      <c r="D97" t="s">
+      <c r="G97" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="H97" t="s">
         <v>28</v>
       </c>
-      <c r="F97" t="s">
+      <c r="J97" t="s">
         <v>253</v>
       </c>
-      <c r="G97" s="1">
+      <c r="K97" s="1">
         <v>45986</v>
       </c>
-      <c r="H97" t="s">
+      <c r="L97" t="s">
         <v>352</v>
       </c>
-      <c r="I97" t="e" vm="50">
+      <c r="M97" t="e" vm="50">
         <v>#VALUE!</v>
       </c>
-      <c r="L97" t="s">
+      <c r="P97" t="s">
         <v>23</v>
       </c>
-      <c r="M97" s="1">
-        <v>45971</v>
-      </c>
-      <c r="N97" s="1">
+      <c r="Q97" s="1">
         <v>45981</v>
-      </c>
-      <c r="O97" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="P97" t="s">
-        <v>354</v>
-      </c>
-      <c r="Q97" t="s">
-        <v>353</v>
       </c>
       <c r="T97">
         <v>1</v>
@@ -27866,29 +27885,29 @@
       <c r="B98" t="s">
         <v>360</v>
       </c>
+      <c r="C98" s="1">
+        <v>45971</v>
+      </c>
       <c r="D98" t="s">
+        <v>359</v>
+      </c>
+      <c r="H98" t="s">
         <v>28</v>
       </c>
-      <c r="H98" t="s">
+      <c r="L98" t="s">
         <v>358</v>
       </c>
-      <c r="I98" t="e" vm="16">
+      <c r="M98" t="e" vm="16">
         <v>#VALUE!</v>
       </c>
-      <c r="J98" t="s">
+      <c r="N98" t="s">
         <v>15</v>
       </c>
-      <c r="L98" t="s">
+      <c r="P98" t="s">
         <v>23</v>
       </c>
-      <c r="M98" s="1">
-        <v>45971</v>
-      </c>
-      <c r="N98" s="1">
+      <c r="Q98" s="1">
         <v>45975</v>
-      </c>
-      <c r="P98" t="s">
-        <v>359</v>
       </c>
       <c r="T98">
         <v>1</v>
@@ -27904,29 +27923,29 @@
       <c r="A99" t="s">
         <v>365</v>
       </c>
+      <c r="C99" s="1">
+        <v>45971</v>
+      </c>
       <c r="D99" t="s">
+        <v>367</v>
+      </c>
+      <c r="H99" t="s">
         <v>28</v>
       </c>
-      <c r="H99" t="s">
+      <c r="L99" t="s">
         <v>363</v>
       </c>
-      <c r="I99" t="e" vm="14">
+      <c r="M99" t="e" vm="14">
         <v>#VALUE!</v>
       </c>
-      <c r="J99" t="s">
+      <c r="N99" t="s">
         <v>15</v>
       </c>
-      <c r="L99" t="s">
+      <c r="P99" t="s">
         <v>23</v>
       </c>
-      <c r="M99" s="1">
-        <v>45971</v>
-      </c>
-      <c r="N99" s="1">
+      <c r="Q99" s="1">
         <v>45976</v>
-      </c>
-      <c r="P99" t="s">
-        <v>367</v>
       </c>
       <c r="T99">
         <v>1</v>
@@ -27945,29 +27964,29 @@
       <c r="B100" t="s">
         <v>370</v>
       </c>
+      <c r="C100" s="1">
+        <v>45971</v>
+      </c>
       <c r="D100" t="s">
+        <v>45</v>
+      </c>
+      <c r="H100" t="s">
         <v>28</v>
       </c>
-      <c r="H100" t="s">
+      <c r="L100" t="s">
         <v>368</v>
       </c>
-      <c r="I100" t="e" vm="53">
+      <c r="M100" t="e" vm="53">
         <v>#VALUE!</v>
       </c>
-      <c r="J100" t="s">
+      <c r="N100" t="s">
         <v>15</v>
       </c>
-      <c r="L100" t="s">
+      <c r="P100" t="s">
         <v>23</v>
       </c>
-      <c r="M100" s="1">
-        <v>45971</v>
-      </c>
-      <c r="N100" s="1">
+      <c r="Q100" s="1">
         <v>45982</v>
-      </c>
-      <c r="P100" t="s">
-        <v>45</v>
       </c>
       <c r="T100">
         <v>1</v>
@@ -27986,29 +28005,29 @@
       <c r="B101" t="s">
         <v>394</v>
       </c>
+      <c r="C101" s="1">
+        <v>45971</v>
+      </c>
       <c r="D101" t="s">
+        <v>19</v>
+      </c>
+      <c r="H101" t="s">
         <v>28</v>
       </c>
-      <c r="H101" t="s">
+      <c r="L101" t="s">
         <v>174</v>
       </c>
-      <c r="I101" t="e" vm="47">
+      <c r="M101" t="e" vm="47">
         <v>#VALUE!</v>
       </c>
-      <c r="J101" t="s">
+      <c r="N101" t="s">
         <v>31</v>
       </c>
-      <c r="L101" t="s">
+      <c r="P101" t="s">
         <v>23</v>
       </c>
-      <c r="M101" s="1">
-        <v>45971</v>
-      </c>
-      <c r="N101" s="1">
+      <c r="Q101" s="1">
         <v>45982</v>
-      </c>
-      <c r="P101" t="s">
-        <v>19</v>
       </c>
       <c r="T101">
         <v>1</v>
@@ -28024,38 +28043,38 @@
       <c r="A102" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="C102">
+      <c r="C102" s="1">
+        <v>45971</v>
+      </c>
+      <c r="D102" t="s">
+        <v>19</v>
+      </c>
+      <c r="F102">
         <v>1</v>
       </c>
-      <c r="D102" t="s">
+      <c r="H102" t="s">
         <v>28</v>
       </c>
-      <c r="F102" t="s">
+      <c r="J102" t="s">
         <v>253</v>
       </c>
-      <c r="G102" s="1">
+      <c r="K102" s="1">
         <v>45986</v>
       </c>
-      <c r="H102" t="s">
+      <c r="L102" t="s">
         <v>395</v>
       </c>
-      <c r="I102" t="e" vm="54">
+      <c r="M102" t="e" vm="54">
         <v>#VALUE!</v>
       </c>
-      <c r="J102" t="s">
+      <c r="N102" t="s">
         <v>15</v>
       </c>
-      <c r="L102" t="s">
+      <c r="P102" t="s">
         <v>23</v>
       </c>
-      <c r="M102" s="1">
-        <v>45971</v>
-      </c>
-      <c r="N102" s="1">
+      <c r="Q102" s="1">
         <v>45982</v>
-      </c>
-      <c r="P102" t="s">
-        <v>19</v>
       </c>
       <c r="T102">
         <v>1</v>
@@ -28074,38 +28093,38 @@
       <c r="B103" t="s">
         <v>399</v>
       </c>
-      <c r="C103">
+      <c r="C103" s="1">
+        <v>45971</v>
+      </c>
+      <c r="D103" t="s">
+        <v>19</v>
+      </c>
+      <c r="F103">
         <v>2</v>
       </c>
-      <c r="D103" t="s">
+      <c r="H103" t="s">
         <v>28</v>
       </c>
-      <c r="F103" t="s">
+      <c r="J103" t="s">
         <v>253</v>
       </c>
-      <c r="G103" s="1">
+      <c r="K103" s="1">
         <v>45986</v>
       </c>
-      <c r="H103" t="s">
+      <c r="L103" t="s">
         <v>398</v>
       </c>
-      <c r="I103" t="e" vm="26">
+      <c r="M103" t="e" vm="26">
         <v>#VALUE!</v>
       </c>
-      <c r="J103" t="s">
+      <c r="N103" t="s">
         <v>31</v>
       </c>
-      <c r="L103" t="s">
+      <c r="P103" t="s">
         <v>23</v>
       </c>
-      <c r="M103" s="1">
-        <v>45971</v>
-      </c>
-      <c r="N103" s="1">
+      <c r="Q103" s="1">
         <v>45980</v>
-      </c>
-      <c r="P103" t="s">
-        <v>19</v>
       </c>
       <c r="T103">
         <v>1</v>
@@ -28121,41 +28140,41 @@
       <c r="A104" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="C104">
+      <c r="C104" s="1">
+        <v>45976</v>
+      </c>
+      <c r="D104" t="s">
+        <v>19</v>
+      </c>
+      <c r="E104" t="s">
+        <v>129</v>
+      </c>
+      <c r="F104">
         <v>2</v>
       </c>
-      <c r="D104" t="s">
+      <c r="H104" t="s">
         <v>28</v>
       </c>
-      <c r="F104" t="s">
+      <c r="J104" t="s">
         <v>253</v>
       </c>
-      <c r="G104" s="1">
+      <c r="K104" s="1">
         <v>45986</v>
       </c>
-      <c r="H104" s="2" t="s">
+      <c r="L104" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="I104" t="e" vm="23">
+      <c r="M104" t="e" vm="23">
         <v>#VALUE!</v>
       </c>
-      <c r="J104" t="s">
+      <c r="N104" t="s">
         <v>15</v>
       </c>
-      <c r="L104" t="s">
+      <c r="P104" t="s">
         <v>23</v>
       </c>
-      <c r="M104" s="1">
-        <v>45976</v>
-      </c>
-      <c r="N104" s="1">
+      <c r="Q104" s="1">
         <v>45988</v>
-      </c>
-      <c r="P104" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q104" t="s">
-        <v>129</v>
       </c>
       <c r="T104">
         <v>1</v>
@@ -28171,41 +28190,41 @@
       <c r="A105" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="C105">
+      <c r="C105" s="1">
+        <v>45976</v>
+      </c>
+      <c r="D105" t="s">
+        <v>19</v>
+      </c>
+      <c r="F105">
         <v>2</v>
       </c>
-      <c r="D105" t="s">
+      <c r="G105" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="H105" t="s">
         <v>28</v>
       </c>
-      <c r="F105" t="s">
+      <c r="J105" t="s">
         <v>253</v>
       </c>
-      <c r="G105" s="1">
+      <c r="K105" s="1">
         <v>45986</v>
       </c>
-      <c r="H105" s="2" t="s">
+      <c r="L105" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="I105" t="e" vm="55">
+      <c r="M105" t="e" vm="55">
         <v>#VALUE!</v>
       </c>
-      <c r="J105" t="s">
+      <c r="N105" t="s">
         <v>15</v>
       </c>
-      <c r="L105" t="s">
+      <c r="P105" t="s">
         <v>23</v>
       </c>
-      <c r="M105" s="1">
-        <v>45976</v>
-      </c>
-      <c r="N105" s="1">
+      <c r="Q105" s="1">
         <v>45982</v>
-      </c>
-      <c r="O105" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="P105" t="s">
-        <v>19</v>
       </c>
       <c r="T105">
         <v>1</v>
@@ -28221,38 +28240,38 @@
       <c r="A106" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="C106">
+      <c r="C106" s="1">
+        <v>45976</v>
+      </c>
+      <c r="D106" t="s">
+        <v>19</v>
+      </c>
+      <c r="F106">
         <v>1</v>
       </c>
-      <c r="D106" t="s">
+      <c r="H106" t="s">
         <v>28</v>
       </c>
-      <c r="F106" t="s">
+      <c r="J106" t="s">
         <v>253</v>
       </c>
-      <c r="G106" s="1">
+      <c r="K106" s="1">
         <v>45986</v>
       </c>
-      <c r="H106" s="2" t="s">
+      <c r="L106" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="I106" t="e" vm="56">
+      <c r="M106" t="e" vm="56">
         <v>#VALUE!</v>
       </c>
-      <c r="J106" t="s">
+      <c r="N106" t="s">
         <v>15</v>
       </c>
-      <c r="L106" t="s">
+      <c r="P106" t="s">
         <v>23</v>
       </c>
-      <c r="M106" s="1">
-        <v>45976</v>
-      </c>
-      <c r="N106" s="1">
+      <c r="Q106" s="1">
         <v>45986</v>
-      </c>
-      <c r="P106" t="s">
-        <v>19</v>
       </c>
       <c r="T106">
         <v>1</v>
@@ -28268,38 +28287,38 @@
       <c r="A107" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="C107">
+      <c r="C107" s="1">
+        <v>45976</v>
+      </c>
+      <c r="D107" t="s">
+        <v>19</v>
+      </c>
+      <c r="F107">
         <v>2</v>
       </c>
-      <c r="D107" t="s">
+      <c r="H107" t="s">
         <v>28</v>
       </c>
-      <c r="F107" t="s">
+      <c r="J107" t="s">
         <v>253</v>
       </c>
-      <c r="G107" s="1">
+      <c r="K107" s="1">
         <v>45986</v>
       </c>
-      <c r="H107" s="2" t="s">
+      <c r="L107" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="I107" t="e" vm="56">
+      <c r="M107" t="e" vm="56">
         <v>#VALUE!</v>
       </c>
-      <c r="J107" t="s">
+      <c r="N107" t="s">
         <v>15</v>
       </c>
-      <c r="L107" t="s">
+      <c r="P107" t="s">
         <v>23</v>
       </c>
-      <c r="M107" s="1">
-        <v>45976</v>
-      </c>
-      <c r="N107" s="1">
+      <c r="Q107" s="1">
         <v>45989</v>
-      </c>
-      <c r="P107" t="s">
-        <v>19</v>
       </c>
       <c r="T107">
         <v>1</v>
@@ -28315,30 +28334,30 @@
       <c r="A108" t="s">
         <v>116</v>
       </c>
+      <c r="C108" s="1">
+        <v>45976</v>
+      </c>
       <c r="D108" t="s">
+        <v>19</v>
+      </c>
+      <c r="G108" s="1"/>
+      <c r="H108" t="s">
         <v>28</v>
       </c>
-      <c r="H108" t="s">
+      <c r="L108" t="s">
         <v>117</v>
       </c>
-      <c r="I108" t="e" vm="12">
+      <c r="M108" t="e" vm="12">
         <v>#VALUE!</v>
       </c>
-      <c r="J108" t="s">
+      <c r="N108" t="s">
         <v>15</v>
       </c>
-      <c r="L108" t="s">
+      <c r="P108" t="s">
         <v>23</v>
       </c>
-      <c r="M108" s="1">
-        <v>45976</v>
-      </c>
-      <c r="N108" s="1">
+      <c r="Q108" s="1">
         <v>45981</v>
-      </c>
-      <c r="O108" s="1"/>
-      <c r="P108" t="s">
-        <v>19</v>
       </c>
       <c r="T108">
         <v>1</v>
@@ -28354,29 +28373,29 @@
       <c r="A109" t="s">
         <v>389</v>
       </c>
+      <c r="C109" s="1">
+        <v>45976</v>
+      </c>
       <c r="D109" t="s">
+        <v>19</v>
+      </c>
+      <c r="H109" t="s">
         <v>104</v>
       </c>
-      <c r="H109" t="s">
+      <c r="L109" t="s">
         <v>388</v>
       </c>
-      <c r="I109" t="e" vm="26">
+      <c r="M109" t="e" vm="26">
         <v>#VALUE!</v>
       </c>
-      <c r="J109" t="s">
+      <c r="N109" t="s">
         <v>15</v>
       </c>
-      <c r="L109" t="s">
+      <c r="P109" t="s">
         <v>23</v>
       </c>
-      <c r="M109" s="1">
-        <v>45976</v>
-      </c>
-      <c r="N109" s="1">
+      <c r="Q109" s="1">
         <v>45985</v>
-      </c>
-      <c r="P109" t="s">
-        <v>19</v>
       </c>
       <c r="T109">
         <v>1</v>
@@ -28392,41 +28411,41 @@
       <c r="A110" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="C110">
+      <c r="C110" s="1">
+        <v>45981</v>
+      </c>
+      <c r="D110" t="s">
+        <v>19</v>
+      </c>
+      <c r="F110">
         <v>1</v>
       </c>
-      <c r="D110" t="s">
+      <c r="G110" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="H110" t="s">
         <v>28</v>
       </c>
-      <c r="F110" t="s">
+      <c r="J110" t="s">
         <v>253</v>
       </c>
-      <c r="G110" s="1">
+      <c r="K110" s="1">
         <v>45992</v>
       </c>
-      <c r="H110" s="2" t="s">
+      <c r="L110" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="I110" t="e" vm="33">
+      <c r="M110" t="e" vm="33">
         <v>#VALUE!</v>
       </c>
-      <c r="J110" t="s">
+      <c r="N110" t="s">
         <v>31</v>
       </c>
-      <c r="L110" t="s">
+      <c r="P110" t="s">
         <v>23</v>
       </c>
-      <c r="M110" s="1">
-        <v>45981</v>
-      </c>
-      <c r="N110" s="1">
+      <c r="Q110" s="1">
         <v>45991</v>
-      </c>
-      <c r="O110" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="P110" t="s">
-        <v>19</v>
       </c>
       <c r="T110">
         <v>1</v>
@@ -28442,38 +28461,38 @@
       <c r="A111" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="C111">
+      <c r="C111" s="1">
+        <v>45981</v>
+      </c>
+      <c r="D111" t="s">
+        <v>19</v>
+      </c>
+      <c r="F111">
         <v>1</v>
       </c>
-      <c r="D111" t="s">
+      <c r="H111" t="s">
         <v>28</v>
       </c>
-      <c r="F111" t="s">
+      <c r="J111" t="s">
         <v>253</v>
       </c>
-      <c r="G111" s="1">
+      <c r="K111" s="1">
         <v>45992</v>
       </c>
-      <c r="H111" s="2" t="s">
+      <c r="L111" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="I111" t="e" vm="33">
+      <c r="M111" t="e" vm="33">
         <v>#VALUE!</v>
       </c>
-      <c r="J111" t="s">
+      <c r="N111" t="s">
         <v>31</v>
       </c>
-      <c r="L111" t="s">
+      <c r="P111" t="s">
         <v>23</v>
       </c>
-      <c r="M111" s="1">
-        <v>45981</v>
-      </c>
-      <c r="N111" s="1">
+      <c r="Q111" s="1">
         <v>45992</v>
-      </c>
-      <c r="P111" t="s">
-        <v>19</v>
       </c>
       <c r="T111">
         <v>1</v>
@@ -28489,35 +28508,35 @@
       <c r="A112" t="s">
         <v>247</v>
       </c>
+      <c r="C112" s="1">
+        <v>45981</v>
+      </c>
       <c r="D112" t="s">
+        <v>45</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="H112" t="s">
         <v>28</v>
       </c>
-      <c r="H112" t="s">
+      <c r="L112" t="s">
         <v>248</v>
       </c>
-      <c r="I112" t="e" vm="57">
+      <c r="M112" t="e" vm="57">
         <v>#VALUE!</v>
       </c>
-      <c r="J112" t="s">
+      <c r="N112" t="s">
         <v>15</v>
       </c>
-      <c r="K112" t="s">
+      <c r="O112" t="s">
         <v>72</v>
       </c>
-      <c r="L112" t="s">
+      <c r="P112" t="s">
         <v>23</v>
       </c>
-      <c r="M112" s="1">
-        <v>45981</v>
-      </c>
-      <c r="N112" s="1">
+      <c r="Q112" s="1">
         <v>45992</v>
-      </c>
-      <c r="P112" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q112" s="2" t="s">
-        <v>249</v>
       </c>
       <c r="T112">
         <v>1</v>
@@ -28533,35 +28552,35 @@
       <c r="A113" t="s">
         <v>384</v>
       </c>
-      <c r="C113">
+      <c r="C113" s="1">
+        <v>45981</v>
+      </c>
+      <c r="D113" t="s">
+        <v>19</v>
+      </c>
+      <c r="F113">
         <v>1</v>
       </c>
-      <c r="D113" t="s">
+      <c r="G113" t="s">
+        <v>257</v>
+      </c>
+      <c r="H113" t="s">
         <v>28</v>
       </c>
-      <c r="H113" t="s">
+      <c r="L113" t="s">
         <v>256</v>
       </c>
-      <c r="I113" t="e" vm="49">
+      <c r="M113" t="e" vm="49">
         <v>#VALUE!</v>
       </c>
-      <c r="J113" t="s">
+      <c r="N113" t="s">
         <v>15</v>
       </c>
-      <c r="L113" t="s">
+      <c r="P113" t="s">
         <v>23</v>
       </c>
-      <c r="M113" s="1">
-        <v>45981</v>
-      </c>
-      <c r="N113" s="1">
+      <c r="Q113" s="1">
         <v>46045</v>
-      </c>
-      <c r="O113" t="s">
-        <v>257</v>
-      </c>
-      <c r="P113" t="s">
-        <v>19</v>
       </c>
       <c r="T113">
         <v>1</v>
@@ -28577,32 +28596,32 @@
       <c r="A114" t="s">
         <v>259</v>
       </c>
+      <c r="C114" s="1">
+        <v>45981</v>
+      </c>
       <c r="D114" t="s">
+        <v>19</v>
+      </c>
+      <c r="G114" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="H114" t="s">
         <v>28</v>
       </c>
-      <c r="H114" t="s">
+      <c r="L114" t="s">
         <v>258</v>
       </c>
-      <c r="I114" t="e" vm="58">
+      <c r="M114" t="e" vm="58">
         <v>#VALUE!</v>
       </c>
-      <c r="J114" t="s">
+      <c r="N114" t="s">
         <v>31</v>
       </c>
-      <c r="L114" t="s">
+      <c r="P114" t="s">
         <v>23</v>
       </c>
-      <c r="M114" s="1">
-        <v>45981</v>
-      </c>
-      <c r="N114" s="1">
+      <c r="Q114" s="1">
         <v>46006</v>
-      </c>
-      <c r="O114" s="10" t="s">
-        <v>260</v>
-      </c>
-      <c r="P114" t="s">
-        <v>19</v>
       </c>
       <c r="T114">
         <v>1</v>
@@ -28618,29 +28637,29 @@
       <c r="A115" t="s">
         <v>263</v>
       </c>
+      <c r="C115" s="1">
+        <v>45981</v>
+      </c>
       <c r="D115" t="s">
+        <v>19</v>
+      </c>
+      <c r="H115" t="s">
         <v>28</v>
       </c>
-      <c r="H115" t="s">
+      <c r="L115" t="s">
         <v>262</v>
       </c>
-      <c r="I115" t="e" vm="59">
+      <c r="M115" t="e" vm="59">
         <v>#VALUE!</v>
       </c>
-      <c r="J115" t="s">
+      <c r="N115" t="s">
         <v>15</v>
       </c>
-      <c r="L115" t="s">
+      <c r="P115" t="s">
         <v>23</v>
       </c>
-      <c r="M115" s="1">
-        <v>45981</v>
-      </c>
-      <c r="N115" s="1">
+      <c r="Q115" s="1">
         <v>46022</v>
-      </c>
-      <c r="P115" t="s">
-        <v>19</v>
       </c>
       <c r="T115">
         <v>1</v>
@@ -28656,26 +28675,26 @@
       <c r="A116" t="s">
         <v>268</v>
       </c>
+      <c r="C116" s="1">
+        <v>45981</v>
+      </c>
       <c r="D116" t="s">
+        <v>19</v>
+      </c>
+      <c r="H116" t="s">
         <v>28</v>
       </c>
-      <c r="H116" t="s">
+      <c r="L116" t="s">
         <v>267</v>
       </c>
-      <c r="I116" t="e" vm="33">
+      <c r="M116" t="e" vm="33">
         <v>#VALUE!</v>
       </c>
-      <c r="L116" t="s">
+      <c r="P116" t="s">
         <v>23</v>
       </c>
-      <c r="M116" s="1">
-        <v>45981</v>
-      </c>
-      <c r="N116" s="1">
+      <c r="Q116" s="1">
         <v>45998</v>
-      </c>
-      <c r="P116" t="s">
-        <v>19</v>
       </c>
       <c r="T116">
         <v>1</v>
@@ -28691,29 +28710,29 @@
       <c r="A117" t="s">
         <v>269</v>
       </c>
+      <c r="C117" s="1">
+        <v>45981</v>
+      </c>
       <c r="D117" t="s">
+        <v>19</v>
+      </c>
+      <c r="G117" t="s">
+        <v>271</v>
+      </c>
+      <c r="H117" t="s">
         <v>28</v>
       </c>
-      <c r="H117" t="s">
+      <c r="L117" t="s">
         <v>270</v>
       </c>
-      <c r="I117" t="e" vm="60">
+      <c r="M117" t="e" vm="60">
         <v>#VALUE!</v>
       </c>
-      <c r="L117" t="s">
+      <c r="P117" t="s">
         <v>23</v>
       </c>
-      <c r="M117" s="1">
-        <v>45981</v>
-      </c>
-      <c r="N117" s="1">
+      <c r="Q117" s="1">
         <v>45994</v>
-      </c>
-      <c r="O117" t="s">
-        <v>271</v>
-      </c>
-      <c r="P117" t="s">
-        <v>19</v>
       </c>
       <c r="T117">
         <v>1</v>
@@ -28729,29 +28748,29 @@
       <c r="A118" t="s">
         <v>275</v>
       </c>
+      <c r="C118" s="1">
+        <v>45981</v>
+      </c>
       <c r="D118" t="s">
+        <v>19</v>
+      </c>
+      <c r="H118" t="s">
         <v>28</v>
       </c>
-      <c r="H118" t="s">
+      <c r="L118" t="s">
         <v>274</v>
       </c>
-      <c r="I118" t="e" vm="48">
+      <c r="M118" t="e" vm="48">
         <v>#VALUE!</v>
       </c>
-      <c r="J118" t="s">
+      <c r="N118" t="s">
         <v>31</v>
       </c>
-      <c r="L118" t="s">
+      <c r="P118" t="s">
         <v>23</v>
       </c>
-      <c r="M118" s="1">
-        <v>45981</v>
-      </c>
-      <c r="N118" s="1">
+      <c r="Q118" s="1">
         <v>45992</v>
-      </c>
-      <c r="P118" t="s">
-        <v>19</v>
       </c>
       <c r="T118">
         <v>1</v>
@@ -28767,32 +28786,32 @@
       <c r="A119" t="s">
         <v>276</v>
       </c>
-      <c r="C119">
+      <c r="C119" s="1">
+        <v>45981</v>
+      </c>
+      <c r="D119" t="s">
+        <v>19</v>
+      </c>
+      <c r="F119">
         <v>1</v>
       </c>
-      <c r="D119" t="s">
+      <c r="H119" t="s">
         <v>28</v>
       </c>
-      <c r="H119" t="s">
+      <c r="L119" t="s">
         <v>277</v>
       </c>
-      <c r="I119" t="e" vm="61">
+      <c r="M119" t="e" vm="61">
         <v>#VALUE!</v>
       </c>
-      <c r="J119" t="s">
+      <c r="N119" t="s">
         <v>15</v>
       </c>
-      <c r="L119" t="s">
+      <c r="P119" t="s">
         <v>23</v>
       </c>
-      <c r="M119" s="1">
-        <v>45981</v>
-      </c>
-      <c r="N119" s="1">
+      <c r="Q119" s="1">
         <v>45991</v>
-      </c>
-      <c r="P119" t="s">
-        <v>19</v>
       </c>
       <c r="T119">
         <v>1</v>
@@ -28808,26 +28827,26 @@
       <c r="A120" t="s">
         <v>290</v>
       </c>
+      <c r="C120" s="1">
+        <v>45981</v>
+      </c>
       <c r="D120" t="s">
+        <v>19</v>
+      </c>
+      <c r="H120" t="s">
         <v>28</v>
       </c>
-      <c r="H120" t="s">
+      <c r="L120" t="s">
         <v>291</v>
       </c>
-      <c r="I120" t="e" vm="53">
+      <c r="M120" t="e" vm="53">
         <v>#VALUE!</v>
       </c>
-      <c r="L120" t="s">
+      <c r="P120" t="s">
         <v>23</v>
       </c>
-      <c r="M120" s="1">
-        <v>45981</v>
-      </c>
-      <c r="N120" s="1">
+      <c r="Q120" s="1">
         <v>45991</v>
-      </c>
-      <c r="P120" t="s">
-        <v>19</v>
       </c>
       <c r="T120">
         <v>1</v>
@@ -28843,26 +28862,26 @@
       <c r="A121" t="s">
         <v>292</v>
       </c>
+      <c r="C121" s="1">
+        <v>45981</v>
+      </c>
       <c r="D121" t="s">
+        <v>19</v>
+      </c>
+      <c r="H121" t="s">
         <v>28</v>
       </c>
-      <c r="H121" t="s">
+      <c r="L121" t="s">
         <v>293</v>
       </c>
-      <c r="I121" t="e" vm="62">
+      <c r="M121" t="e" vm="62">
         <v>#VALUE!</v>
       </c>
-      <c r="L121" t="s">
+      <c r="P121" t="s">
         <v>23</v>
       </c>
-      <c r="M121" s="1">
-        <v>45981</v>
-      </c>
-      <c r="N121" s="1">
+      <c r="Q121" s="1">
         <v>45991</v>
-      </c>
-      <c r="P121" t="s">
-        <v>19</v>
       </c>
       <c r="T121">
         <v>1</v>
@@ -28878,29 +28897,29 @@
       <c r="A122" t="s">
         <v>297</v>
       </c>
+      <c r="C122" s="1">
+        <v>45981</v>
+      </c>
       <c r="D122" t="s">
+        <v>19</v>
+      </c>
+      <c r="H122" t="s">
         <v>28</v>
       </c>
-      <c r="H122" t="s">
+      <c r="L122" t="s">
         <v>296</v>
       </c>
-      <c r="I122" t="e" vm="48">
+      <c r="M122" t="e" vm="48">
         <v>#VALUE!</v>
       </c>
-      <c r="J122" t="s">
+      <c r="N122" t="s">
         <v>15</v>
       </c>
-      <c r="L122" t="s">
+      <c r="P122" t="s">
         <v>23</v>
       </c>
-      <c r="M122" s="1">
-        <v>45981</v>
-      </c>
-      <c r="N122" s="1">
+      <c r="Q122" s="1">
         <v>45991</v>
-      </c>
-      <c r="P122" t="s">
-        <v>19</v>
       </c>
       <c r="T122">
         <v>1</v>
@@ -28916,32 +28935,32 @@
       <c r="A123" t="s">
         <v>301</v>
       </c>
+      <c r="C123" s="1">
+        <v>45981</v>
+      </c>
       <c r="D123" t="s">
+        <v>19</v>
+      </c>
+      <c r="G123" t="s">
+        <v>302</v>
+      </c>
+      <c r="H123" t="s">
         <v>28</v>
       </c>
-      <c r="H123" t="s">
+      <c r="L123" t="s">
         <v>300</v>
       </c>
-      <c r="I123" t="e" vm="23">
+      <c r="M123" t="e" vm="23">
         <v>#VALUE!</v>
       </c>
-      <c r="J123" t="s">
+      <c r="N123" t="s">
         <v>15</v>
       </c>
-      <c r="L123" t="s">
+      <c r="P123" t="s">
         <v>23</v>
       </c>
-      <c r="M123" s="1">
-        <v>45981</v>
-      </c>
-      <c r="N123" s="1">
+      <c r="Q123" s="1">
         <v>45989</v>
-      </c>
-      <c r="O123" t="s">
-        <v>302</v>
-      </c>
-      <c r="P123" t="s">
-        <v>19</v>
       </c>
       <c r="T123">
         <v>1</v>
@@ -28957,35 +28976,35 @@
       <c r="A124" t="s">
         <v>304</v>
       </c>
+      <c r="C124" s="1">
+        <v>45981</v>
+      </c>
       <c r="D124" t="s">
+        <v>19</v>
+      </c>
+      <c r="G124" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="H124" t="s">
         <v>28</v>
       </c>
-      <c r="H124" t="s">
+      <c r="L124" t="s">
         <v>303</v>
       </c>
-      <c r="I124" t="e" vm="40">
+      <c r="M124" t="e" vm="40">
         <v>#VALUE!</v>
       </c>
-      <c r="J124" t="s">
+      <c r="N124" t="s">
         <v>15</v>
       </c>
-      <c r="K124" t="s">
+      <c r="O124" t="s">
         <v>72</v>
       </c>
-      <c r="L124" t="s">
+      <c r="P124" t="s">
         <v>23</v>
       </c>
-      <c r="M124" s="1">
-        <v>45981</v>
-      </c>
-      <c r="N124" s="1">
+      <c r="Q124" s="1">
         <v>45989</v>
-      </c>
-      <c r="O124" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="P124" t="s">
-        <v>19</v>
       </c>
       <c r="T124">
         <v>1</v>
@@ -29001,26 +29020,26 @@
       <c r="A125" t="s">
         <v>213</v>
       </c>
+      <c r="C125" s="1">
+        <v>45981</v>
+      </c>
       <c r="D125" t="s">
+        <v>45</v>
+      </c>
+      <c r="H125" t="s">
         <v>28</v>
       </c>
-      <c r="H125" s="2" t="s">
+      <c r="L125" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="I125" t="e" vm="5">
+      <c r="M125" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
-      <c r="L125" t="s">
+      <c r="P125" t="s">
         <v>23</v>
       </c>
-      <c r="M125" s="1">
-        <v>45981</v>
-      </c>
-      <c r="N125" s="1">
+      <c r="Q125" s="1">
         <v>46053</v>
-      </c>
-      <c r="P125" t="s">
-        <v>45</v>
       </c>
       <c r="T125">
         <v>1</v>
@@ -29036,29 +29055,29 @@
       <c r="A126" t="s">
         <v>347</v>
       </c>
+      <c r="C126" s="1">
+        <v>45981</v>
+      </c>
       <c r="D126" t="s">
+        <v>45</v>
+      </c>
+      <c r="H126" t="s">
         <v>28</v>
       </c>
-      <c r="H126" t="s">
+      <c r="L126" t="s">
         <v>348</v>
       </c>
-      <c r="I126" t="e" vm="56">
+      <c r="M126" t="e" vm="56">
         <v>#VALUE!</v>
       </c>
-      <c r="J126" t="s">
+      <c r="N126" t="s">
         <v>15</v>
       </c>
-      <c r="L126" t="s">
+      <c r="P126" t="s">
         <v>23</v>
       </c>
-      <c r="M126" s="1">
-        <v>45981</v>
-      </c>
-      <c r="N126" s="1">
+      <c r="Q126" s="1">
         <v>45661</v>
-      </c>
-      <c r="P126" t="s">
-        <v>45</v>
       </c>
       <c r="T126">
         <v>1</v>
@@ -29074,29 +29093,29 @@
       <c r="A127" t="s">
         <v>362</v>
       </c>
+      <c r="C127" s="1">
+        <v>45981</v>
+      </c>
       <c r="D127" t="s">
+        <v>45</v>
+      </c>
+      <c r="H127" t="s">
         <v>28</v>
       </c>
-      <c r="H127" t="s">
+      <c r="L127" t="s">
         <v>361</v>
       </c>
-      <c r="I127" t="e" vm="63">
+      <c r="M127" t="e" vm="63">
         <v>#VALUE!</v>
       </c>
-      <c r="J127" t="s">
+      <c r="N127" t="s">
         <v>15</v>
       </c>
-      <c r="L127" t="s">
+      <c r="P127" t="s">
         <v>23</v>
       </c>
-      <c r="M127" s="1">
-        <v>45981</v>
-      </c>
-      <c r="N127" s="1">
+      <c r="Q127" s="1">
         <v>45987</v>
-      </c>
-      <c r="P127" t="s">
-        <v>45</v>
       </c>
       <c r="T127">
         <v>1</v>
@@ -29112,29 +29131,29 @@
       <c r="A128" t="s">
         <v>386</v>
       </c>
-      <c r="D128" t="s">
+      <c r="C128" s="1">
+        <v>45981</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="H128" t="s">
         <v>28</v>
       </c>
-      <c r="H128" t="s">
+      <c r="L128" t="s">
         <v>385</v>
       </c>
-      <c r="I128" t="e" vm="26">
+      <c r="M128" t="e" vm="26">
         <v>#VALUE!</v>
       </c>
-      <c r="J128" t="s">
+      <c r="N128" t="s">
         <v>31</v>
       </c>
-      <c r="L128" t="s">
+      <c r="P128" t="s">
         <v>23</v>
       </c>
-      <c r="M128" s="1">
-        <v>45981</v>
-      </c>
-      <c r="N128" s="1">
+      <c r="Q128" s="1">
         <v>45991</v>
-      </c>
-      <c r="P128" s="2" t="s">
-        <v>387</v>
       </c>
       <c r="T128">
         <v>1</v>
@@ -29150,26 +29169,26 @@
       <c r="A129" t="s">
         <v>391</v>
       </c>
+      <c r="C129" s="1">
+        <v>45981</v>
+      </c>
       <c r="D129" t="s">
+        <v>19</v>
+      </c>
+      <c r="H129" t="s">
         <v>28</v>
       </c>
-      <c r="H129" t="s">
+      <c r="L129" t="s">
         <v>392</v>
       </c>
-      <c r="I129" t="e" vm="48">
+      <c r="M129" t="e" vm="48">
         <v>#VALUE!</v>
       </c>
-      <c r="L129" t="s">
+      <c r="P129" t="s">
         <v>23</v>
       </c>
-      <c r="M129" s="1">
-        <v>45981</v>
-      </c>
-      <c r="N129" s="1">
+      <c r="Q129" s="1">
         <v>45985</v>
-      </c>
-      <c r="P129" t="s">
-        <v>19</v>
       </c>
       <c r="T129">
         <v>1</v>
@@ -29185,29 +29204,29 @@
       <c r="A130" t="s">
         <v>364</v>
       </c>
+      <c r="C130" s="1">
+        <v>45986</v>
+      </c>
       <c r="D130" t="s">
+        <v>366</v>
+      </c>
+      <c r="H130" t="s">
         <v>28</v>
       </c>
-      <c r="H130" t="s">
+      <c r="L130" t="s">
         <v>363</v>
       </c>
-      <c r="I130" t="e" vm="14">
+      <c r="M130" t="e" vm="14">
         <v>#VALUE!</v>
       </c>
-      <c r="J130" t="s">
+      <c r="N130" t="s">
         <v>15</v>
       </c>
-      <c r="L130" t="s">
+      <c r="P130" t="s">
         <v>23</v>
       </c>
-      <c r="M130" s="1">
-        <v>45986</v>
-      </c>
-      <c r="N130" s="1">
+      <c r="Q130" s="1">
         <v>46006</v>
-      </c>
-      <c r="P130" t="s">
-        <v>366</v>
       </c>
       <c r="T130">
         <v>1</v>
@@ -29224,25 +29243,25 @@
         <v>264</v>
       </c>
       <c r="D131" t="s">
+        <v>19</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="H131" t="s">
         <v>104</v>
       </c>
-      <c r="H131" t="s">
+      <c r="L131" t="s">
         <v>265</v>
       </c>
-      <c r="I131" t="e" vm="24">
+      <c r="M131" t="e" vm="24">
         <v>#VALUE!</v>
       </c>
-      <c r="J131" t="s">
+      <c r="N131" t="s">
         <v>15</v>
       </c>
-      <c r="L131" t="s">
+      <c r="P131" t="s">
         <v>23</v>
-      </c>
-      <c r="P131" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q131" s="2" t="s">
-        <v>266</v>
       </c>
       <c r="T131">
         <v>0</v>
@@ -29255,128 +29274,124 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Y19" xr:uid="{F7772053-9363-CA4A-A53F-040B7C700753}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Y131">
-      <sortCondition ref="M1:M131"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:Y19" xr:uid="{F7772053-9363-CA4A-A53F-040B7C700753}"/>
   <conditionalFormatting sqref="A1:B1048576">
-    <cfRule type="duplicateValues" dxfId="65" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:B22">
-    <cfRule type="duplicateValues" dxfId="64" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A61:B61">
-    <cfRule type="duplicateValues" dxfId="63" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D1048576">
-    <cfRule type="containsText" dxfId="62" priority="1" operator="containsText" text="abandoned">
-      <formula>NOT(ISERROR(SEARCH("abandoned",D1)))</formula>
+  <conditionalFormatting sqref="H1:H1048576">
+    <cfRule type="containsText" dxfId="63" priority="1" operator="containsText" text="abandoned">
+      <formula>NOT(ISERROR(SEARCH("abandoned",H1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="61" priority="3" operator="containsText" text="late app">
-      <formula>NOT(ISERROR(SEARCH("late app",D1)))</formula>
+    <cfRule type="containsText" dxfId="62" priority="3" operator="containsText" text="late app">
+      <formula>NOT(ISERROR(SEARCH("late app",H1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J78:J80 J83:J89 D1:E1 J92:J112 D2:G1048576 J115:J124 J126:J128 J130:J131 L87:L131">
-    <cfRule type="containsText" dxfId="60" priority="6" operator="containsText" text="completed">
-      <formula>NOT(ISERROR(SEARCH("completed",D1)))</formula>
+  <conditionalFormatting sqref="N78:N80 N83:N89 H1:I1 N92:N112 H2:K1048576 N115:N124 N126:N128 N130:N131 P87:P131">
+    <cfRule type="containsText" dxfId="61" priority="6" operator="containsText" text="completed">
+      <formula>NOT(ISERROR(SEARCH("completed",H1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J78:J80 J83:J89 J92:J112 F1:G1048576 J115:J124 J126:J128 J130:J131 L87:L131">
-    <cfRule type="containsText" dxfId="59" priority="4" operator="containsText" text="NO">
-      <formula>NOT(ISERROR(SEARCH("NO",F1)))</formula>
+  <conditionalFormatting sqref="N78:N80 N83:N89 N92:N112 J1:K1048576 N115:N124 N126:N128 N130:N131 P87:P131">
+    <cfRule type="containsText" dxfId="60" priority="4" operator="containsText" text="NO">
+      <formula>NOT(ISERROR(SEARCH("NO",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="58" priority="5" operator="containsText" text="YES">
-      <formula>NOT(ISERROR(SEARCH("YES",F1)))</formula>
+    <cfRule type="containsText" dxfId="59" priority="5" operator="containsText" text="YES">
+      <formula>NOT(ISERROR(SEARCH("YES",J1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="H3" r:id="rId1" xr:uid="{2FD67E99-97D4-6F4F-9C23-F094A4E233EB}"/>
-    <hyperlink ref="H4" r:id="rId2" xr:uid="{C466BD2C-2D71-FD47-B267-C9470B42EAAE}"/>
-    <hyperlink ref="H95" r:id="rId3" xr:uid="{7E4575FB-8BA7-8343-9270-E933C2CF052A}"/>
-    <hyperlink ref="H96" r:id="rId4" xr:uid="{7DE2DCC0-6910-AF4A-ADA1-2F0A7CE7A46A}"/>
-    <hyperlink ref="H62" r:id="rId5" xr:uid="{9F5721B0-AA94-954A-B077-53D294EE0006}"/>
-    <hyperlink ref="Q62" r:id="rId6" xr:uid="{E9AC54D1-D414-9A4A-8F10-99810DECDF26}"/>
-    <hyperlink ref="H70" r:id="rId7" xr:uid="{3DA7C680-99C0-9744-A5E3-8B70509CE1C7}"/>
-    <hyperlink ref="H7" r:id="rId8" xr:uid="{F2E0FCCF-BB13-0240-931E-487798981CC9}"/>
-    <hyperlink ref="H71" r:id="rId9" xr:uid="{DF00AD54-0273-B54C-B9CE-46119BBDF932}"/>
-    <hyperlink ref="H5" r:id="rId10" display="American Uiversity" xr:uid="{4368F24E-5E4F-B944-AB45-4045D2296D5A}"/>
-    <hyperlink ref="H6" r:id="rId11" display="American Uiversity" xr:uid="{0B28A4E3-9367-5B4E-821E-8878EF62879B}"/>
+    <hyperlink ref="L3" r:id="rId1" xr:uid="{2FD67E99-97D4-6F4F-9C23-F094A4E233EB}"/>
+    <hyperlink ref="L4" r:id="rId2" xr:uid="{C466BD2C-2D71-FD47-B267-C9470B42EAAE}"/>
+    <hyperlink ref="L95" r:id="rId3" xr:uid="{7E4575FB-8BA7-8343-9270-E933C2CF052A}"/>
+    <hyperlink ref="L96" r:id="rId4" xr:uid="{7DE2DCC0-6910-AF4A-ADA1-2F0A7CE7A46A}"/>
+    <hyperlink ref="L62" r:id="rId5" xr:uid="{9F5721B0-AA94-954A-B077-53D294EE0006}"/>
+    <hyperlink ref="E62" r:id="rId6" xr:uid="{E9AC54D1-D414-9A4A-8F10-99810DECDF26}"/>
+    <hyperlink ref="L70" r:id="rId7" xr:uid="{3DA7C680-99C0-9744-A5E3-8B70509CE1C7}"/>
+    <hyperlink ref="L7" r:id="rId8" xr:uid="{F2E0FCCF-BB13-0240-931E-487798981CC9}"/>
+    <hyperlink ref="L71" r:id="rId9" xr:uid="{DF00AD54-0273-B54C-B9CE-46119BBDF932}"/>
+    <hyperlink ref="L5" r:id="rId10" display="American Uiversity" xr:uid="{4368F24E-5E4F-B944-AB45-4045D2296D5A}"/>
+    <hyperlink ref="L6" r:id="rId11" display="American Uiversity" xr:uid="{0B28A4E3-9367-5B4E-821E-8878EF62879B}"/>
     <hyperlink ref="R7" r:id="rId12" xr:uid="{F8BB08B3-A5E4-0244-9B87-74DC5560EA9C}"/>
-    <hyperlink ref="H36" r:id="rId13" xr:uid="{1A802253-386D-0248-869E-8A0EA127D432}"/>
-    <hyperlink ref="H37" r:id="rId14" xr:uid="{D10E5030-47DD-F84B-A85A-CB7F9EEF20B4}"/>
-    <hyperlink ref="H9" r:id="rId15" xr:uid="{AF10C3AC-DC3E-8F4B-A325-8137F8872365}"/>
-    <hyperlink ref="H10" r:id="rId16" xr:uid="{DAADFE53-28FB-BF47-B382-1AE9637B0AC9}"/>
-    <hyperlink ref="H32" r:id="rId17" xr:uid="{055B8A95-C64C-8344-8D9A-88ADC3E4C5A7}"/>
-    <hyperlink ref="H72" r:id="rId18" xr:uid="{557D8143-61B7-124A-9EC7-930988E1B3DE}"/>
-    <hyperlink ref="H33" r:id="rId19" xr:uid="{0B9459D2-C194-B546-B890-EDF488B5E508}"/>
-    <hyperlink ref="H8" r:id="rId20" xr:uid="{3E8CCC0C-C03D-0642-8D93-6D5E4E29B155}"/>
-    <hyperlink ref="H93" r:id="rId21" xr:uid="{360892F0-CC7D-924A-95AF-9E897ECEE570}"/>
-    <hyperlink ref="H11" r:id="rId22" xr:uid="{0D66B73F-990C-044A-BA9A-C5887E710F92}"/>
-    <hyperlink ref="H73" r:id="rId23" xr:uid="{79C92412-1EFA-834C-AE35-D77CA8C36A12}"/>
-    <hyperlink ref="H74" r:id="rId24" xr:uid="{DAE0AF5F-F94A-294E-86E2-555898BF42FB}"/>
-    <hyperlink ref="H63" r:id="rId25" xr:uid="{8E758C4D-96FF-B44B-AE0D-70D6A17B4A4D}"/>
-    <hyperlink ref="H64" r:id="rId26" xr:uid="{B2DCF82F-FDBE-B54E-A0A8-BB5059FDE3DE}"/>
-    <hyperlink ref="H12" r:id="rId27" xr:uid="{5CDD97D8-5C25-5D42-AA6C-3EFD455D0937}"/>
-    <hyperlink ref="H13" r:id="rId28" xr:uid="{4C952912-61F2-7F48-A61F-8171FB512E69}"/>
+    <hyperlink ref="L36" r:id="rId13" xr:uid="{1A802253-386D-0248-869E-8A0EA127D432}"/>
+    <hyperlink ref="L37" r:id="rId14" xr:uid="{D10E5030-47DD-F84B-A85A-CB7F9EEF20B4}"/>
+    <hyperlink ref="L9" r:id="rId15" xr:uid="{AF10C3AC-DC3E-8F4B-A325-8137F8872365}"/>
+    <hyperlink ref="L10" r:id="rId16" xr:uid="{DAADFE53-28FB-BF47-B382-1AE9637B0AC9}"/>
+    <hyperlink ref="L32" r:id="rId17" xr:uid="{055B8A95-C64C-8344-8D9A-88ADC3E4C5A7}"/>
+    <hyperlink ref="L72" r:id="rId18" xr:uid="{557D8143-61B7-124A-9EC7-930988E1B3DE}"/>
+    <hyperlink ref="L33" r:id="rId19" xr:uid="{0B9459D2-C194-B546-B890-EDF488B5E508}"/>
+    <hyperlink ref="L8" r:id="rId20" xr:uid="{3E8CCC0C-C03D-0642-8D93-6D5E4E29B155}"/>
+    <hyperlink ref="L93" r:id="rId21" xr:uid="{360892F0-CC7D-924A-95AF-9E897ECEE570}"/>
+    <hyperlink ref="L11" r:id="rId22" xr:uid="{0D66B73F-990C-044A-BA9A-C5887E710F92}"/>
+    <hyperlink ref="L73" r:id="rId23" xr:uid="{79C92412-1EFA-834C-AE35-D77CA8C36A12}"/>
+    <hyperlink ref="L74" r:id="rId24" xr:uid="{DAE0AF5F-F94A-294E-86E2-555898BF42FB}"/>
+    <hyperlink ref="L63" r:id="rId25" xr:uid="{8E758C4D-96FF-B44B-AE0D-70D6A17B4A4D}"/>
+    <hyperlink ref="L64" r:id="rId26" xr:uid="{B2DCF82F-FDBE-B54E-A0A8-BB5059FDE3DE}"/>
+    <hyperlink ref="L12" r:id="rId27" xr:uid="{5CDD97D8-5C25-5D42-AA6C-3EFD455D0937}"/>
+    <hyperlink ref="L13" r:id="rId28" xr:uid="{4C952912-61F2-7F48-A61F-8171FB512E69}"/>
     <hyperlink ref="R14" r:id="rId29" xr:uid="{97F45FF5-AD7B-2143-9F53-5C46956B35CE}"/>
-    <hyperlink ref="Q14" r:id="rId30" xr:uid="{3CBBC435-61F9-034D-A9A0-B71AD9A7CCE6}"/>
-    <hyperlink ref="H44" r:id="rId31" xr:uid="{115DEFD3-6759-7C49-87C4-663720AFC0F3}"/>
-    <hyperlink ref="H60" r:id="rId32" xr:uid="{B568129A-4C88-5D42-B367-90B46CA6E8A2}"/>
-    <hyperlink ref="H104" r:id="rId33" xr:uid="{F3D886C1-081B-8F41-85EF-4C299E91BBDA}"/>
-    <hyperlink ref="H34" r:id="rId34" xr:uid="{14B04134-DF47-DA43-BB43-BA8C1185A50E}"/>
-    <hyperlink ref="H31" r:id="rId35" display="https://www.upf.edu/" xr:uid="{F90D7817-7AA8-1C4B-8992-6FF849FBECCA}"/>
-    <hyperlink ref="O8" r:id="rId36" display="mailto:ferran.mane@urv.cat" xr:uid="{DFACBA33-6641-9A4D-B406-DC2FCC993612}"/>
-    <hyperlink ref="H75" r:id="rId37" xr:uid="{EFED1D5F-B3C8-6445-899D-122DB5B26298}"/>
-    <hyperlink ref="H76" r:id="rId38" xr:uid="{6E0CC17F-E103-7C43-850C-F0FC0B9A5278}"/>
-    <hyperlink ref="H77" r:id="rId39" xr:uid="{58693CCE-AFC3-AF44-BB76-62CF466ED6EA}"/>
-    <hyperlink ref="H35" r:id="rId40" xr:uid="{FC0BA615-15C1-F64A-BC32-60929732DD9E}"/>
-    <hyperlink ref="H106" r:id="rId41" xr:uid="{14CF4841-2A37-9044-AE5B-371378C8D3B9}"/>
-    <hyperlink ref="H107" r:id="rId42" xr:uid="{2E048D46-3518-2C4A-B061-479244E61709}"/>
-    <hyperlink ref="H17" r:id="rId43" xr:uid="{BA26908B-8596-4249-946E-03161834E8E5}"/>
-    <hyperlink ref="H45" r:id="rId44" xr:uid="{00B6A218-D9E8-3D4A-B0D7-CBDFA98EE6F3}"/>
-    <hyperlink ref="P10" r:id="rId45" xr:uid="{8C412634-0F9A-E946-9A3F-CA7F4E73C3AB}"/>
-    <hyperlink ref="H94" r:id="rId46" xr:uid="{1E1C35FB-7434-7842-A803-7D382F52F333}"/>
-    <hyperlink ref="H19" r:id="rId47" xr:uid="{62B1AEBF-C899-0A4B-9923-A135752FBB1C}"/>
-    <hyperlink ref="P5" r:id="rId48" xr:uid="{13514A0D-2C0E-5340-8AA2-077046FFB755}"/>
-    <hyperlink ref="P37" r:id="rId49" xr:uid="{DE8E5F09-1A02-F148-8539-188D3ED5C9F4}"/>
-    <hyperlink ref="P32" r:id="rId50" xr:uid="{84827B93-5057-1D4A-AD4E-C9D52677D58A}"/>
-    <hyperlink ref="H110" r:id="rId51" location="/admin" xr:uid="{23CE2AD2-6E21-4241-978C-EFA7C5825B0A}"/>
-    <hyperlink ref="O110" r:id="rId52" tooltip="https://www.pierrebiscaye.com/" display="https://nam10.safelinks.protection.outlook.com/?url=https%3A%2F%2Fwww.pierrebiscaye.com%2F&amp;data=05%7C02%7Cgonzalezjj%40mail.smu.edu%7Cf17b24ecae9644d5351608de0b2d3d88%7C0f450f2e334f4bada85c9adf76051d8b%7C0%7C0%7C638960486114093769%7CUnknown%7CTWFpbGZsb3d8eyJFbXB0eU1hcGkiOnRydWUsIlYiOiIwLjAuMDAwMCIsIlAiOiJXaW4zMiIsIkFOIjoiTWFpbCIsIldUIjoyfQ%3D%3D%7C0%7C%7C%7C&amp;sdata=G3tT9q0mvtmAIBnq6zF0gIXzpLRerNt4Zfffdrm2A2E%3D&amp;reserved=0" xr:uid="{B11A9620-8D5F-6A4D-A59A-6B6DCAC23722}"/>
-    <hyperlink ref="H111" r:id="rId53" xr:uid="{7C2D96E2-AEFB-4140-A2EF-40B86E5741B1}"/>
-    <hyperlink ref="H20" r:id="rId54" xr:uid="{35FAF041-CBFF-8A48-A4B3-B97381C00102}"/>
-    <hyperlink ref="H61" r:id="rId55" xr:uid="{2D03A0F6-26F5-B24A-B91A-14D38A06B992}"/>
-    <hyperlink ref="Q61" r:id="rId56" display="https://academicjobsonline.org/ajo/jobs/30626" xr:uid="{46416258-D6E3-7B41-9A73-A9A4F4E6BB34}"/>
-    <hyperlink ref="H105" r:id="rId57" xr:uid="{FEED16DA-CB82-0044-943C-358B6551EC5E}"/>
-    <hyperlink ref="O105" r:id="rId58" display="mailto:a.gorbenko@ucl.co.uk" xr:uid="{5772A23E-5235-304E-A5C1-05CB3DAB9BFC}"/>
-    <hyperlink ref="H21" r:id="rId59" xr:uid="{0F06344E-50D3-B54E-8250-7516D4B03802}"/>
-    <hyperlink ref="Q21" r:id="rId60" xr:uid="{B72DD765-9030-AC4B-9C6A-C3E6C6D825B0}"/>
-    <hyperlink ref="H18" r:id="rId61" xr:uid="{521B9389-25EE-AC42-8631-0602B790BC9F}"/>
-    <hyperlink ref="H22" r:id="rId62" xr:uid="{101CF9F0-3B9F-7741-9A08-0F724B9DFBAD}"/>
-    <hyperlink ref="Q22" r:id="rId63" xr:uid="{A1E87546-ABB3-B843-AEF8-C1E11BCA894E}"/>
-    <hyperlink ref="H38" r:id="rId64" xr:uid="{CB47483F-A82F-854C-A1D3-484A5DDC11BF}"/>
-    <hyperlink ref="H39" r:id="rId65" xr:uid="{7A6E251E-DB12-EA4C-BA94-B3B44FE73253}"/>
-    <hyperlink ref="H40" r:id="rId66" xr:uid="{7C154F49-4A52-6A48-A99D-F3C3751ADC20}"/>
-    <hyperlink ref="H46" r:id="rId67" xr:uid="{11631E55-FA21-864F-B682-18A03075BFEE}"/>
-    <hyperlink ref="H47" r:id="rId68" xr:uid="{28BB29AB-D632-9C44-9739-DFD6875CA62C}"/>
-    <hyperlink ref="Q47" r:id="rId69" xr:uid="{70571E5D-37F6-864A-9EAB-DAEF5B46CD8B}"/>
-    <hyperlink ref="H48" r:id="rId70" xr:uid="{DFCE3DEC-01C3-7D49-925B-BEFD13BC818A}"/>
-    <hyperlink ref="Q48" r:id="rId71" xr:uid="{DD5D337B-2CFC-8F41-A89C-2D8D571940BA}"/>
-    <hyperlink ref="H49" r:id="rId72" xr:uid="{EA24C43B-23D8-4E4B-9DD8-AAD27BA385E7}"/>
-    <hyperlink ref="H65" r:id="rId73" xr:uid="{8E7D4522-E2CE-7043-9079-1CE2F950B085}"/>
-    <hyperlink ref="P11" r:id="rId74" xr:uid="{4517EA95-990E-DE45-A804-67126FDDD4C3}"/>
-    <hyperlink ref="H23" r:id="rId75" xr:uid="{91C6A3A0-FE50-5B4F-8B20-8B6496F16211}"/>
-    <hyperlink ref="H125" r:id="rId76" xr:uid="{5721E0FE-84BD-D943-BC9A-5350183D9688}"/>
-    <hyperlink ref="H41" r:id="rId77" xr:uid="{FE7182CC-AEDE-E142-B842-B2FE5C063CCE}"/>
-    <hyperlink ref="H25" r:id="rId78" xr:uid="{694E8A95-02AE-9249-91C7-1102518BA774}"/>
-    <hyperlink ref="H15" r:id="rId79" xr:uid="{9A9A6BC9-B330-7842-A78C-4DCC88F5E19F}"/>
-    <hyperlink ref="H27" r:id="rId80" xr:uid="{928CABEF-4FA6-E646-8140-7B6E43F8FB96}"/>
-    <hyperlink ref="Q112" r:id="rId81" xr:uid="{82BF1574-A6C6-1641-9FFE-615861E401FD}"/>
-    <hyperlink ref="Q131" r:id="rId82" xr:uid="{3562807E-7FDA-F046-BA03-5DDD43072DB7}"/>
-    <hyperlink ref="O124" r:id="rId83" display="mailto:ivanpaya@ua.es" xr:uid="{DEFB77A5-E57F-714C-BAB9-56DE82BA0B2E}"/>
-    <hyperlink ref="O89" r:id="rId84" display="mailto:ari.hyytinen@hanken.fi" xr:uid="{7777B12A-FD99-4A43-A14B-A15661B760DC}"/>
-    <hyperlink ref="O97" r:id="rId85" display="mailto:peter.haan@fu-berlin.de" xr:uid="{3D1A69ED-8F06-1246-B586-201CB349DB62}"/>
-    <hyperlink ref="P128" r:id="rId86" xr:uid="{C3771F9C-84FC-7A41-9911-ED3B01799C9C}"/>
+    <hyperlink ref="E14" r:id="rId30" xr:uid="{3CBBC435-61F9-034D-A9A0-B71AD9A7CCE6}"/>
+    <hyperlink ref="L44" r:id="rId31" xr:uid="{115DEFD3-6759-7C49-87C4-663720AFC0F3}"/>
+    <hyperlink ref="L60" r:id="rId32" xr:uid="{B568129A-4C88-5D42-B367-90B46CA6E8A2}"/>
+    <hyperlink ref="L104" r:id="rId33" xr:uid="{F3D886C1-081B-8F41-85EF-4C299E91BBDA}"/>
+    <hyperlink ref="L34" r:id="rId34" xr:uid="{14B04134-DF47-DA43-BB43-BA8C1185A50E}"/>
+    <hyperlink ref="L31" r:id="rId35" display="https://www.upf.edu/" xr:uid="{F90D7817-7AA8-1C4B-8992-6FF849FBECCA}"/>
+    <hyperlink ref="G8" r:id="rId36" display="mailto:ferran.mane@urv.cat" xr:uid="{DFACBA33-6641-9A4D-B406-DC2FCC993612}"/>
+    <hyperlink ref="L75" r:id="rId37" xr:uid="{EFED1D5F-B3C8-6445-899D-122DB5B26298}"/>
+    <hyperlink ref="L76" r:id="rId38" xr:uid="{6E0CC17F-E103-7C43-850C-F0FC0B9A5278}"/>
+    <hyperlink ref="L77" r:id="rId39" xr:uid="{58693CCE-AFC3-AF44-BB76-62CF466ED6EA}"/>
+    <hyperlink ref="L35" r:id="rId40" xr:uid="{FC0BA615-15C1-F64A-BC32-60929732DD9E}"/>
+    <hyperlink ref="L106" r:id="rId41" xr:uid="{14CF4841-2A37-9044-AE5B-371378C8D3B9}"/>
+    <hyperlink ref="L107" r:id="rId42" xr:uid="{2E048D46-3518-2C4A-B061-479244E61709}"/>
+    <hyperlink ref="L17" r:id="rId43" xr:uid="{BA26908B-8596-4249-946E-03161834E8E5}"/>
+    <hyperlink ref="L45" r:id="rId44" xr:uid="{00B6A218-D9E8-3D4A-B0D7-CBDFA98EE6F3}"/>
+    <hyperlink ref="D10" r:id="rId45" xr:uid="{8C412634-0F9A-E946-9A3F-CA7F4E73C3AB}"/>
+    <hyperlink ref="L94" r:id="rId46" xr:uid="{1E1C35FB-7434-7842-A803-7D382F52F333}"/>
+    <hyperlink ref="L19" r:id="rId47" xr:uid="{62B1AEBF-C899-0A4B-9923-A135752FBB1C}"/>
+    <hyperlink ref="D5" r:id="rId48" xr:uid="{13514A0D-2C0E-5340-8AA2-077046FFB755}"/>
+    <hyperlink ref="D37" r:id="rId49" xr:uid="{DE8E5F09-1A02-F148-8539-188D3ED5C9F4}"/>
+    <hyperlink ref="D32" r:id="rId50" xr:uid="{84827B93-5057-1D4A-AD4E-C9D52677D58A}"/>
+    <hyperlink ref="L110" r:id="rId51" location="/admin" xr:uid="{23CE2AD2-6E21-4241-978C-EFA7C5825B0A}"/>
+    <hyperlink ref="G110" r:id="rId52" tooltip="https://www.pierrebiscaye.com/" display="https://nam10.safelinks.protection.outlook.com/?url=https%3A%2F%2Fwww.pierrebiscaye.com%2F&amp;data=05%7C02%7Cgonzalezjj%40mail.smu.edu%7Cf17b24ecae9644d5351608de0b2d3d88%7C0f450f2e334f4bada85c9adf76051d8b%7C0%7C0%7C638960486114093769%7CUnknown%7CTWFpbGZsb3d8eyJFbXB0eU1hcGkiOnRydWUsIlYiOiIwLjAuMDAwMCIsIlAiOiJXaW4zMiIsIkFOIjoiTWFpbCIsIldUIjoyfQ%3D%3D%7C0%7C%7C%7C&amp;sdata=G3tT9q0mvtmAIBnq6zF0gIXzpLRerNt4Zfffdrm2A2E%3D&amp;reserved=0" xr:uid="{B11A9620-8D5F-6A4D-A59A-6B6DCAC23722}"/>
+    <hyperlink ref="L111" r:id="rId53" xr:uid="{7C2D96E2-AEFB-4140-A2EF-40B86E5741B1}"/>
+    <hyperlink ref="L20" r:id="rId54" xr:uid="{35FAF041-CBFF-8A48-A4B3-B97381C00102}"/>
+    <hyperlink ref="L61" r:id="rId55" xr:uid="{2D03A0F6-26F5-B24A-B91A-14D38A06B992}"/>
+    <hyperlink ref="E61" r:id="rId56" display="https://academicjobsonline.org/ajo/jobs/30626" xr:uid="{46416258-D6E3-7B41-9A73-A9A4F4E6BB34}"/>
+    <hyperlink ref="L105" r:id="rId57" xr:uid="{FEED16DA-CB82-0044-943C-358B6551EC5E}"/>
+    <hyperlink ref="G105" r:id="rId58" display="mailto:a.gorbenko@ucl.co.uk" xr:uid="{5772A23E-5235-304E-A5C1-05CB3DAB9BFC}"/>
+    <hyperlink ref="L21" r:id="rId59" xr:uid="{0F06344E-50D3-B54E-8250-7516D4B03802}"/>
+    <hyperlink ref="E21" r:id="rId60" xr:uid="{B72DD765-9030-AC4B-9C6A-C3E6C6D825B0}"/>
+    <hyperlink ref="L18" r:id="rId61" xr:uid="{521B9389-25EE-AC42-8631-0602B790BC9F}"/>
+    <hyperlink ref="L22" r:id="rId62" xr:uid="{101CF9F0-3B9F-7741-9A08-0F724B9DFBAD}"/>
+    <hyperlink ref="E22" r:id="rId63" xr:uid="{A1E87546-ABB3-B843-AEF8-C1E11BCA894E}"/>
+    <hyperlink ref="L38" r:id="rId64" xr:uid="{CB47483F-A82F-854C-A1D3-484A5DDC11BF}"/>
+    <hyperlink ref="L39" r:id="rId65" xr:uid="{7A6E251E-DB12-EA4C-BA94-B3B44FE73253}"/>
+    <hyperlink ref="L40" r:id="rId66" xr:uid="{7C154F49-4A52-6A48-A99D-F3C3751ADC20}"/>
+    <hyperlink ref="L46" r:id="rId67" xr:uid="{11631E55-FA21-864F-B682-18A03075BFEE}"/>
+    <hyperlink ref="L47" r:id="rId68" xr:uid="{28BB29AB-D632-9C44-9739-DFD6875CA62C}"/>
+    <hyperlink ref="E47" r:id="rId69" xr:uid="{70571E5D-37F6-864A-9EAB-DAEF5B46CD8B}"/>
+    <hyperlink ref="L48" r:id="rId70" xr:uid="{DFCE3DEC-01C3-7D49-925B-BEFD13BC818A}"/>
+    <hyperlink ref="E48" r:id="rId71" xr:uid="{DD5D337B-2CFC-8F41-A89C-2D8D571940BA}"/>
+    <hyperlink ref="L49" r:id="rId72" xr:uid="{EA24C43B-23D8-4E4B-9DD8-AAD27BA385E7}"/>
+    <hyperlink ref="L65" r:id="rId73" xr:uid="{8E7D4522-E2CE-7043-9079-1CE2F950B085}"/>
+    <hyperlink ref="D11" r:id="rId74" xr:uid="{4517EA95-990E-DE45-A804-67126FDDD4C3}"/>
+    <hyperlink ref="L23" r:id="rId75" xr:uid="{91C6A3A0-FE50-5B4F-8B20-8B6496F16211}"/>
+    <hyperlink ref="L125" r:id="rId76" xr:uid="{5721E0FE-84BD-D943-BC9A-5350183D9688}"/>
+    <hyperlink ref="L41" r:id="rId77" xr:uid="{FE7182CC-AEDE-E142-B842-B2FE5C063CCE}"/>
+    <hyperlink ref="L25" r:id="rId78" xr:uid="{694E8A95-02AE-9249-91C7-1102518BA774}"/>
+    <hyperlink ref="L15" r:id="rId79" xr:uid="{9A9A6BC9-B330-7842-A78C-4DCC88F5E19F}"/>
+    <hyperlink ref="L27" r:id="rId80" xr:uid="{928CABEF-4FA6-E646-8140-7B6E43F8FB96}"/>
+    <hyperlink ref="E112" r:id="rId81" xr:uid="{82BF1574-A6C6-1641-9FFE-615861E401FD}"/>
+    <hyperlink ref="E131" r:id="rId82" xr:uid="{3562807E-7FDA-F046-BA03-5DDD43072DB7}"/>
+    <hyperlink ref="G124" r:id="rId83" display="mailto:ivanpaya@ua.es" xr:uid="{DEFB77A5-E57F-714C-BAB9-56DE82BA0B2E}"/>
+    <hyperlink ref="G89" r:id="rId84" display="mailto:ari.hyytinen@hanken.fi" xr:uid="{7777B12A-FD99-4A43-A14B-A15661B760DC}"/>
+    <hyperlink ref="G97" r:id="rId85" display="mailto:peter.haan@fu-berlin.de" xr:uid="{3D1A69ED-8F06-1246-B586-201CB349DB62}"/>
+    <hyperlink ref="D128" r:id="rId86" xr:uid="{C3771F9C-84FC-7A41-9911-ED3B01799C9C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29385,7 +29400,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923E81FA-B875-3C4E-A189-1A21268FA086}">
-  <dimension ref="A1:C76"/>
+  <dimension ref="A1:C86"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="32.83203125" customWidth="1"/>
@@ -30196,151 +30211,243 @@
         <v>105</v>
       </c>
     </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A77" s="1">
+        <v>45954</v>
+      </c>
+      <c r="B77" t="s">
+        <v>218</v>
+      </c>
+      <c r="C77" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A78" s="1">
+        <v>45954</v>
+      </c>
+      <c r="B78" t="s">
+        <v>254</v>
+      </c>
+      <c r="C78" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A79" s="1">
+        <v>45954</v>
+      </c>
+      <c r="C79" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A80" s="1">
+        <v>45954</v>
+      </c>
+      <c r="C80" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A81" s="1">
+        <v>45954</v>
+      </c>
+      <c r="C81" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A82" s="1">
+        <v>45954</v>
+      </c>
+      <c r="C82" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A83" s="1">
+        <v>45954</v>
+      </c>
+      <c r="C83" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A84" s="1">
+        <v>45954</v>
+      </c>
+      <c r="C84" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A85" s="1">
+        <v>45954</v>
+      </c>
+      <c r="C85" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A86" s="1">
+        <v>45954</v>
+      </c>
+      <c r="C86" t="s">
+        <v>105</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="B5">
-    <cfRule type="duplicateValues" dxfId="57" priority="60"/>
-    <cfRule type="duplicateValues" dxfId="56" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="64"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B10">
-    <cfRule type="duplicateValues" dxfId="55" priority="58"/>
-    <cfRule type="duplicateValues" dxfId="54" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="62"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B11">
-    <cfRule type="duplicateValues" dxfId="53" priority="56"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12">
-    <cfRule type="duplicateValues" dxfId="51" priority="54"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="58"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15">
-    <cfRule type="duplicateValues" dxfId="49" priority="52"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16">
-    <cfRule type="duplicateValues" dxfId="47" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17">
-    <cfRule type="duplicateValues" dxfId="46" priority="49"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B18">
-    <cfRule type="duplicateValues" dxfId="44" priority="47"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B19">
-    <cfRule type="duplicateValues" dxfId="42" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:B23">
-    <cfRule type="duplicateValues" dxfId="41" priority="44"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B24">
-    <cfRule type="duplicateValues" dxfId="39" priority="42"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B27">
-    <cfRule type="duplicateValues" dxfId="37" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28">
-    <cfRule type="duplicateValues" dxfId="35" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29">
-    <cfRule type="duplicateValues" dxfId="34" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="32" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31">
-    <cfRule type="duplicateValues" dxfId="31" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="duplicateValues" dxfId="30" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33">
-    <cfRule type="duplicateValues" dxfId="29" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="28" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35">
-    <cfRule type="duplicateValues" dxfId="27" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37">
-    <cfRule type="duplicateValues" dxfId="26" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38">
-    <cfRule type="duplicateValues" dxfId="25" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B42">
-    <cfRule type="duplicateValues" dxfId="24" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43">
-    <cfRule type="duplicateValues" dxfId="23" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44:B45">
-    <cfRule type="duplicateValues" dxfId="22" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B46">
-    <cfRule type="duplicateValues" dxfId="21" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B48">
-    <cfRule type="duplicateValues" dxfId="20" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B49">
-    <cfRule type="duplicateValues" dxfId="19" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B51">
-    <cfRule type="duplicateValues" dxfId="18" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B52">
-    <cfRule type="duplicateValues" dxfId="17" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B58">
-    <cfRule type="duplicateValues" dxfId="16" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B59">
-    <cfRule type="duplicateValues" dxfId="15" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B63">
-    <cfRule type="duplicateValues" dxfId="14" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B64">
-    <cfRule type="duplicateValues" dxfId="13" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B66">
-    <cfRule type="duplicateValues" dxfId="12" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="11" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="10" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B68">
-    <cfRule type="duplicateValues" dxfId="9" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B69">
-    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B70">
+    <cfRule type="duplicateValues" dxfId="8" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B72">
+    <cfRule type="duplicateValues" dxfId="7" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B73">
     <cfRule type="duplicateValues" dxfId="6" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B72">
+  <conditionalFormatting sqref="B74">
     <cfRule type="duplicateValues" dxfId="5" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B73">
+  <conditionalFormatting sqref="B75">
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B76">
     <cfRule type="duplicateValues" dxfId="3" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B74">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B75">
+  <conditionalFormatting sqref="B77">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B76">
+  <conditionalFormatting sqref="B78">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -30366,8 +30473,8 @@
         <v>130</v>
       </c>
       <c r="C1" s="16">
-        <f>COUNTIF(sum!D:D, "completed")/B1</f>
-        <v>0.5</v>
+        <f>COUNTIF(sum!H:H, "completed")/B1</f>
+        <v>0.51538461538461533</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -30375,11 +30482,11 @@
         <v>409</v>
       </c>
       <c r="B2" s="18">
-        <f>COUNTA(sum!C:C) -1</f>
+        <f>COUNTA(sum!F:F) -1</f>
         <v>40</v>
       </c>
       <c r="C2" s="12">
-        <f>COUNTIFS(sum!D:D,"completed", sum!C:C, "&lt;&gt;") / B2</f>
+        <f>COUNTIFS(sum!H:H,"completed", sum!F:F, "&lt;&gt;") / B2</f>
         <v>0.4</v>
       </c>
     </row>
@@ -30388,11 +30495,11 @@
         <v>410</v>
       </c>
       <c r="B3" s="18">
-        <f>COUNTA(sum!F:F) -1</f>
+        <f>COUNTA(sum!J:J) -1</f>
         <v>28</v>
       </c>
       <c r="C3" s="12">
-        <f>COUNTIFS(sum!D:D,"completed", sum!F:F, "&lt;&gt;") / B3</f>
+        <f>COUNTIFS(sum!H:H,"completed", sum!J:J, "&lt;&gt;") / B3</f>
         <v>0.35714285714285715</v>
       </c>
     </row>
@@ -30401,7 +30508,7 @@
         <v>411</v>
       </c>
       <c r="B5" s="17">
-        <f>COUNTA(sum!E:E) -1</f>
+        <f>COUNTA(sum!I:I) -1</f>
         <v>0</v>
       </c>
       <c r="C5" s="16">
@@ -30414,7 +30521,7 @@
         <v>412</v>
       </c>
       <c r="B6" s="18">
-        <f>COUNTIFS(sum!E:E,"no news")</f>
+        <f>COUNTIFS(sum!I:I,"no news")</f>
         <v>0</v>
       </c>
       <c r="C6" s="12" t="e">
@@ -30427,7 +30534,7 @@
         <v>413</v>
       </c>
       <c r="B7" s="18">
-        <f>COUNTIFS(sum!E:E,"rejected")</f>
+        <f>COUNTIFS(sum!I:I,"rejected")</f>
         <v>0</v>
       </c>
       <c r="C7" s="12" t="e">
@@ -30440,7 +30547,7 @@
         <v>414</v>
       </c>
       <c r="B8" s="18">
-        <f>COUNTIFS(sum!E:E,"interview")</f>
+        <f>COUNTIFS(sum!I:I,"interview")</f>
         <v>0</v>
       </c>
       <c r="C8" s="12" t="e">
@@ -30453,7 +30560,7 @@
         <v>415</v>
       </c>
       <c r="B9" s="18">
-        <f>COUNTIFS(sum!E:E,"fly out")</f>
+        <f>COUNTIFS(sum!I:I,"fly out")</f>
         <v>0</v>
       </c>
       <c r="C9" s="12" t="e">
@@ -30466,7 +30573,7 @@
         <v>416</v>
       </c>
       <c r="B10" s="18">
-        <f>COUNTIFS(sum!E:E,"offer")</f>
+        <f>COUNTIFS(sum!I:I,"offer")</f>
         <v>0</v>
       </c>
       <c r="C10" s="12" t="e">

--- a/EconJM_status.xlsx
+++ b/EconJM_status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/jjgecon_dat/Dropbox/Work/Job Search/2025 EconJM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4EE6198-228B-5C4D-98F2-B7C0D018765D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0B354BB-FD4A-5D47-8FB7-C4F872B51FE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{6FE48536-7E5C-BF4C-9490-2A6392576298}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" activeTab="1" xr2:uid="{6FE48536-7E5C-BF4C-9490-2A6392576298}"/>
   </bookViews>
   <sheets>
     <sheet name="sum" sheetId="1" r:id="rId1"/>
@@ -943,7 +943,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1436" uniqueCount="569">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1437" uniqueCount="570">
   <si>
     <t>add_id</t>
   </si>
@@ -2602,6 +2602,9 @@
   </si>
   <si>
     <t>University of Toledo</t>
+  </si>
+  <si>
+    <t>gatehred 10 more from JOE</t>
   </si>
   <si>
     <t>gatehred 10 more from JOE, trying to make up for 31st</t>
@@ -31645,19 +31648,19 @@
     </row>
     <row r="17" spans="1:21" ht="17" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C17" s="1">
         <v>45945</v>
       </c>
       <c r="D17" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H17" t="s">
         <v>25</v>
       </c>
       <c r="L17" s="17" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="M17" t="e" vm="12">
         <v>#VALUE!</v>
@@ -33013,13 +33016,13 @@
         <v>45955</v>
       </c>
       <c r="D50" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H50" t="s">
         <v>25</v>
       </c>
       <c r="L50" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M50" t="e" vm="34">
         <v>#VALUE!</v>
@@ -33045,19 +33048,19 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C51" s="1">
         <v>45955</v>
       </c>
       <c r="D51" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H51" t="s">
         <v>25</v>
       </c>
       <c r="L51" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="M51" t="e" vm="35">
         <v>#VALUE!</v>
@@ -33083,19 +33086,19 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C52" s="1">
         <v>45955</v>
       </c>
       <c r="D52" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H52" t="s">
         <v>25</v>
       </c>
       <c r="L52" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="M52" t="e" vm="36">
         <v>#VALUE!</v>
@@ -33623,19 +33626,19 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C65" s="1">
         <v>45962</v>
       </c>
       <c r="D65" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H65" t="s">
         <v>25</v>
       </c>
       <c r="L65" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="M65" t="e" vm="22">
         <v>#VALUE!</v>
@@ -37001,10 +37004,10 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B144" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C144" s="1">
         <v>45976</v>
@@ -37013,13 +37016,13 @@
         <v>42</v>
       </c>
       <c r="E144" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H144" t="s">
         <v>25</v>
       </c>
       <c r="L144" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="M144" t="e" vm="36">
         <v>#VALUE!</v>
@@ -37045,7 +37048,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C145" s="1">
         <v>45976</v>
@@ -37057,7 +37060,7 @@
         <v>25</v>
       </c>
       <c r="L145" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M145" t="e" vm="76">
         <v>#VALUE!</v>
@@ -37083,7 +37086,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C146" s="1">
         <v>45976</v>
@@ -37095,7 +37098,7 @@
         <v>25</v>
       </c>
       <c r="L146" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M146" t="e" vm="36">
         <v>#VALUE!</v>
@@ -38321,7 +38324,7 @@
     </row>
     <row r="177" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C177" s="1">
         <v>45986</v>
@@ -38333,7 +38336,7 @@
         <v>25</v>
       </c>
       <c r="L177" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="M177" t="e" vm="22">
         <v>#VALUE!</v>
@@ -38359,19 +38362,19 @@
     </row>
     <row r="178" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C178" s="1">
         <v>45986</v>
       </c>
       <c r="D178" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H178" t="s">
         <v>25</v>
       </c>
       <c r="L178" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M178" t="e" vm="12">
         <v>#VALUE!</v>
@@ -38643,7 +38646,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923E81FA-B875-3C4E-A189-1A21268FA086}">
-  <dimension ref="A1:C102"/>
+  <dimension ref="A1:C103"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="32.83203125" customWidth="1"/>
@@ -39725,6 +39728,14 @@
         <v>45962</v>
       </c>
       <c r="C102" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A103" s="1">
+        <v>45962</v>
+      </c>
+      <c r="C103" t="s">
         <v>541</v>
       </c>
     </row>

--- a/EconJM_status.xlsx
+++ b/EconJM_status.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\javie\Dropbox\Work\Job Search\2025 EconJM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD3E982D-2401-4F79-A5F0-4F7E0A67C3ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E0F6221-463F-40BF-8241-1560B166D507}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" xr2:uid="{6FE48536-7E5C-BF4C-9490-2A6392576298}"/>
   </bookViews>
@@ -41,11 +41,11 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="94">
+  <futureMetadata name="XLRICHVALUE" count="96">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -581,6 +581,13 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="2433"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="2121"/>
         </ext>
       </extLst>
@@ -589,13 +596,6 @@
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="836"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="2433"/>
         </ext>
       </extLst>
     </bk>
@@ -686,6 +686,20 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="2875"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="2886"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="61"/>
         </ext>
       </extLst>
@@ -693,7 +707,7 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="2875"/>
+          <xlrd:rvb i="2897"/>
         </ext>
       </extLst>
     </bk>
@@ -705,7 +719,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <valueMetadata count="94">
+  <valueMetadata count="96">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -988,12 +1002,18 @@
     <bk>
       <rc t="1" v="93"/>
     </bk>
+    <bk>
+      <rc t="1" v="94"/>
+    </bk>
+    <bk>
+      <rc t="1" v="95"/>
+    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1660" uniqueCount="641">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1756" uniqueCount="673">
   <si>
     <t>add_id</t>
   </si>
@@ -2952,6 +2972,102 @@
   </si>
   <si>
     <t>swarthmore</t>
+  </si>
+  <si>
+    <t>ppp</t>
+  </si>
+  <si>
+    <t>https://apply.interfolio.com/175034</t>
+  </si>
+  <si>
+    <t>Center for Philosophy, Politics, and Economics at Brown University (PPE Center)</t>
+  </si>
+  <si>
+    <t>CL must fit vission of the center and mix politics and econ</t>
+  </si>
+  <si>
+    <t>Singapore University of Technology and Design</t>
+  </si>
+  <si>
+    <t>add teaching dossier</t>
+  </si>
+  <si>
+    <t>sutd</t>
+  </si>
+  <si>
+    <t>https://careers.sutd.edu.sg/job/Singapore-Lecturer-in-Economics-%28Humanities%2C-Arts-and-Social-Sciences%29-138682/48335944/</t>
+  </si>
+  <si>
+    <t>rbbecon</t>
+  </si>
+  <si>
+    <t>https://cezanneondemand.intervieweb.it/rbbecon/jobs/2526-economist-phd-level-58340/en/</t>
+  </si>
+  <si>
+    <t>RBB Economics</t>
+  </si>
+  <si>
+    <t>send JMP to valentina.ruocco@rbbecon.com</t>
+  </si>
+  <si>
+    <t>cna</t>
+  </si>
+  <si>
+    <t>bank_mx</t>
+  </si>
+  <si>
+    <t>https://jobs.dayforcehcm.com/en-US/cna/CANDIDATEPORTAL/jobs/6202</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>Bank of Mexico</t>
+  </si>
+  <si>
+    <t>emphasize that you command spanish for research</t>
+  </si>
+  <si>
+    <t>Sabanci University</t>
+  </si>
+  <si>
+    <t>sabanci</t>
+  </si>
+  <si>
+    <t>Erasmus University Rotterdam</t>
+  </si>
+  <si>
+    <t>rotterdam</t>
+  </si>
+  <si>
+    <t>swiss_data</t>
+  </si>
+  <si>
+    <t>mention my proficiency is use of LLM both through API or local deployment  open source models</t>
+  </si>
+  <si>
+    <t>Prof. Elliott Ash</t>
+  </si>
+  <si>
+    <t>ETH Zurich</t>
+  </si>
+  <si>
+    <t>bologna_2</t>
+  </si>
+  <si>
+    <t>University of Bologna</t>
+  </si>
+  <si>
+    <t>Prof. Alessandro Tavoni: alessandro.tavoni@unibo.it</t>
+  </si>
+  <si>
+    <t>kiep</t>
+  </si>
+  <si>
+    <t>Korea Institute for International Economic Policy</t>
+  </si>
+  <si>
+    <t>added 10 more from EJM</t>
   </si>
 </sst>
 </file>
@@ -3106,7 +3222,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="116">
+  <dxfs count="136">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -4141,6 +4257,226 @@
       <font>
         <color rgb="FF9C0006"/>
       </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -4183,26 +4519,6 @@
         <vertical/>
         <horizontal/>
       </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -4803,11 +5119,19 @@
     <address r:id="rId185"/>
     <moreImagesAddress r:id="rId186"/>
   </webImageSrd>
+  <webImageSrd>
+    <address r:id="rId187"/>
+    <moreImagesAddress r:id="rId188"/>
+  </webImageSrd>
+  <webImageSrd>
+    <address r:id="rId189"/>
+    <moreImagesAddress r:id="rId190"/>
+  </webImageSrd>
 </webImagesSrd>
 </file>
 
 <file path=xl/richData/rdarray.xml><?xml version="1.0" encoding="utf-8"?>
-<arrayData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="175">
+<arrayData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="177">
   <a r="1">
     <v t="r">6</v>
   </a>
@@ -6077,37 +6401,21 @@
   <a r="1">
     <v t="r">2869</v>
   </a>
+  <a r="1">
+    <v t="r">2880</v>
+  </a>
+  <a r="1">
+    <v t="r">2891</v>
+  </a>
   <a r="3">
-    <v t="r">2895</v>
-    <v t="r">2896</v>
-    <v t="r">2897</v>
+    <v t="r">2917</v>
+    <v t="r">2918</v>
+    <v t="r">2919</v>
   </a>
   <a r="1">
     <v t="s">Turkish language</v>
   </a>
   <a r="81">
-    <v t="r">2911</v>
-    <v t="r">2912</v>
-    <v t="r">2913</v>
-    <v t="r">2914</v>
-    <v t="r">2915</v>
-    <v t="r">2916</v>
-    <v t="r">2917</v>
-    <v t="r">2918</v>
-    <v t="r">2919</v>
-    <v t="r">2920</v>
-    <v t="r">2921</v>
-    <v t="r">2922</v>
-    <v t="r">2923</v>
-    <v t="r">2924</v>
-    <v t="r">2925</v>
-    <v t="r">2926</v>
-    <v t="r">2927</v>
-    <v t="r">2928</v>
-    <v t="r">2929</v>
-    <v t="r">2930</v>
-    <v t="r">2931</v>
-    <v t="r">2932</v>
     <v t="r">2933</v>
     <v t="r">2934</v>
     <v t="r">2935</v>
@@ -6167,6 +6475,28 @@
     <v t="r">2989</v>
     <v t="r">2990</v>
     <v t="r">2991</v>
+    <v t="r">2992</v>
+    <v t="r">2993</v>
+    <v t="r">2994</v>
+    <v t="r">2995</v>
+    <v t="r">2996</v>
+    <v t="r">2997</v>
+    <v t="r">2998</v>
+    <v t="r">2999</v>
+    <v t="r">3000</v>
+    <v t="r">3001</v>
+    <v t="r">3002</v>
+    <v t="r">3003</v>
+    <v t="r">3004</v>
+    <v t="r">3005</v>
+    <v t="r">3006</v>
+    <v t="r">3007</v>
+    <v t="r">3008</v>
+    <v t="r">3009</v>
+    <v t="r">3010</v>
+    <v t="r">3011</v>
+    <v t="r">3012</v>
+    <v t="r">3013</v>
   </a>
   <a r="1">
     <v t="s">UTC+03:00</v>
@@ -6175,7 +6505,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="2999">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="3021">
   <rv s="0">
     <v>536870912</v>
     <v>Baltimore</v>
@@ -24728,82 +25058,243 @@
   </rv>
   <rv s="0">
     <v>536870912</v>
-    <v>Turkey</v>
-    <v>fbfb6418-e8cf-0d18-8b81-28d0fcccda7c</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="1">
-    <fb>0.49799254187076897</fb>
-    <v>29</v>
-  </rv>
-  <rv s="1">
-    <fb>783562</fb>
+    <v>Providence, Rhode Island</v>
+    <v>956379de-1782-455c-b2d8-1ba81c8965f1</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Providence County</v>
+    <v>55625e32-23f5-f927-164b-a5bce33c7bb1</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="1">
+    <fb>53.273966999999999</fb>
     <v>8</v>
-  </rv>
-  <rv s="1">
-    <fb>512000</fb>
-    <v>8</v>
-  </rv>
-  <rv s="1">
-    <fb>16.027000000000001</fb>
-    <v>30</v>
-  </rv>
-  <rv s="1">
-    <fb>90</fb>
-    <v>31</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Ankara</v>
-    <v>85c37289-d0cf-bf9c-89e0-a375b7d3c4e7</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="1">
-    <fb>372724.88099999999</fb>
-    <v>8</v>
-  </rv>
-  <rv s="1">
-    <fb>234.437126307922</fb>
-    <v>32</v>
-  </rv>
-  <rv s="1">
-    <fb>0.151768215720023</fb>
-    <v>29</v>
-  </rv>
-  <rv s="1">
-    <fb>2847.1263826231798</fb>
-    <v>8</v>
-  </rv>
-  <rv s="1">
-    <fb>2.069</fb>
-    <v>30</v>
-  </rv>
-  <rv s="1">
-    <fb>0.15354651443713199</fb>
-    <v>29</v>
-  </rv>
-  <rv s="1">
-    <fb>86.843187660707997</fb>
-    <v>33</v>
-  </rv>
-  <rv s="1">
-    <fb>754411708202.61597</fb>
-    <v>35</v>
-  </rv>
-  <rv s="1">
-    <fb>0.93154979999999998</fb>
-    <v>29</v>
-  </rv>
-  <rv s="1">
-    <fb>0.2386259</fb>
-    <v>29</v>
   </rv>
   <rv s="2">
     <v>92</v>
     <v>6</v>
+    <v>428</v>
+    <v>7</v>
+    <v>0</v>
+    <v>Image of Providence, Rhode Island</v>
+  </rv>
+  <rv s="1">
+    <fb>41.823990000000002</fb>
+    <v>9</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Brett Smiley (Mayor)</v>
+    <v>4f12ec20-fb06-ef7c-2225-f4b342e7a212</v>
+    <v>en-US</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="3">
+    <v>171</v>
+  </rv>
+  <rv s="4">
+    <v>https://www.bing.com/search?q=providence+rhode+island&amp;form=skydnc</v>
+    <v>Learn more on Bing</v>
+  </rv>
+  <rv s="1">
+    <fb>-71.41283</fb>
+    <v>9</v>
+  </rv>
+  <rv s="1">
+    <fb>190934</fb>
+    <v>8</v>
+  </rv>
+  <rv s="17">
+    <v>#VALUE!</v>
+    <v>en-US</v>
+    <v>956379de-1782-455c-b2d8-1ba81c8965f1</v>
+    <v>536870912</v>
+    <v>1</v>
     <v>429</v>
+    <v>226</v>
+    <v>Providence, Rhode Island</v>
+    <v>4</v>
+    <v>5</v>
+    <v>Map</v>
+    <v>6</v>
+    <v>46</v>
+    <v>92</v>
+    <v>2876</v>
+    <v>2877</v>
+    <v>118</v>
+    <v>Providence is the capital and most populous city of the U.S. state of Rhode Island. The county seat of Providence County, it is one of the oldest cities in New England, founded in 1636 by Roger Williams, a Reformed Baptist theologian and ...</v>
+    <v>2878</v>
+    <v>2879</v>
+    <v>2881</v>
+    <v>2882</v>
+    <v>2883</v>
+    <v>Providence, Rhode Island</v>
+    <v>2884</v>
+    <v>Providence, Rhode Island</v>
+    <v>mdp/vdpid/5488923181957775365</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Brussels</v>
+    <v>f77206fd-fe4f-6c8e-5588-1d0651b151ea</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="1">
+    <fb>161.38</fb>
+    <v>8</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Belgium</v>
+    <v>ac5bcc34-e1cd-2e76-9d31-fb1be1159a5e</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="2">
+    <v>93</v>
+    <v>6</v>
+    <v>430</v>
+    <v>7</v>
+    <v>0</v>
+    <v>Image of Brussels</v>
+  </rv>
+  <rv s="1">
+    <fb>50.8466666666667</fb>
+    <v>9</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Rachid Madrane (Speaker)</v>
+    <v>53415c53-94d6-4d5b-a2e2-e0a1340ed8ca</v>
+    <v>en-US</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="3">
+    <v>172</v>
+  </rv>
+  <rv s="4">
+    <v>https://www.bing.com/search?q=brussels&amp;form=skydnc</v>
+    <v>Learn more on Bing</v>
+  </rv>
+  <rv s="1">
+    <fb>4.3525</fb>
+    <v>9</v>
+  </rv>
+  <rv s="1">
+    <fb>1218255</fb>
+    <v>8</v>
+  </rv>
+  <rv s="26">
+    <v>#VALUE!</v>
+    <v>en-US</v>
+    <v>f77206fd-fe4f-6c8e-5588-1d0651b151ea</v>
+    <v>536870912</v>
+    <v>1</v>
+    <v>431</v>
+    <v>432</v>
+    <v>Brussels</v>
+    <v>4</v>
+    <v>5</v>
+    <v>Map</v>
+    <v>6</v>
+    <v>46</v>
+    <v>2887</v>
+    <v>2888</v>
+    <v>Brussels, officially the Brussels-Capital Region, is a region of Belgium comprising 19 municipalities, including the City of Brussels, which is the capital of Belgium. The Brussels-Capital Region is located in the central portion of the country ...</v>
+    <v>2889</v>
+    <v>2890</v>
+    <v>2892</v>
+    <v>2893</v>
+    <v>2894</v>
+    <v>Brussels</v>
+    <v>2895</v>
+    <v>2113</v>
+    <v>Brussels</v>
+    <v>mdp/vdpid/10103253</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Turkey</v>
+    <v>fbfb6418-e8cf-0d18-8b81-28d0fcccda7c</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="1">
+    <fb>0.49799254187076897</fb>
+    <v>29</v>
+  </rv>
+  <rv s="1">
+    <fb>783562</fb>
+    <v>8</v>
+  </rv>
+  <rv s="1">
+    <fb>512000</fb>
+    <v>8</v>
+  </rv>
+  <rv s="1">
+    <fb>16.027000000000001</fb>
+    <v>30</v>
+  </rv>
+  <rv s="1">
+    <fb>90</fb>
+    <v>31</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Ankara</v>
+    <v>85c37289-d0cf-bf9c-89e0-a375b7d3c4e7</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="1">
+    <fb>372724.88099999999</fb>
+    <v>8</v>
+  </rv>
+  <rv s="1">
+    <fb>234.437126307922</fb>
+    <v>32</v>
+  </rv>
+  <rv s="1">
+    <fb>0.151768215720023</fb>
+    <v>29</v>
+  </rv>
+  <rv s="1">
+    <fb>2847.1263826231798</fb>
+    <v>8</v>
+  </rv>
+  <rv s="1">
+    <fb>2.069</fb>
+    <v>30</v>
+  </rv>
+  <rv s="1">
+    <fb>0.15354651443713199</fb>
+    <v>29</v>
+  </rv>
+  <rv s="1">
+    <fb>86.843187660707997</fb>
+    <v>33</v>
+  </rv>
+  <rv s="1">
+    <fb>754411708202.61597</fb>
+    <v>35</v>
+  </rv>
+  <rv s="1">
+    <fb>0.93154979999999998</fb>
+    <v>29</v>
+  </rv>
+  <rv s="1">
+    <fb>0.2386259</fb>
+    <v>29</v>
+  </rv>
+  <rv s="2">
+    <v>94</v>
+    <v>6</v>
+    <v>434</v>
     <v>7</v>
     <v>0</v>
     <v>Image of Turkey</v>
@@ -24841,7 +25332,7 @@
     <v>Generic</v>
   </rv>
   <rv s="3">
-    <v>171</v>
+    <v>173</v>
   </rv>
   <rv s="4">
     <v>https://www.bing.com/search?q=turkey&amp;form=skydnc</v>
@@ -24860,7 +25351,7 @@
     <v>34</v>
   </rv>
   <rv s="3">
-    <v>172</v>
+    <v>174</v>
   </rv>
   <rv s="1">
     <fb>0.16948329139999999</fb>
@@ -25458,14 +25949,14 @@
     <v>Map</v>
   </rv>
   <rv s="3">
-    <v>173</v>
+    <v>175</v>
   </rv>
   <rv s="1">
     <fb>0.178640331232954</fb>
     <v>29</v>
   </rv>
   <rv s="3">
-    <v>174</v>
+    <v>176</v>
   </rv>
   <rv s="1">
     <fb>0.42299999999999999</fb>
@@ -25485,72 +25976,72 @@
     <v>fbfb6418-e8cf-0d18-8b81-28d0fcccda7c</v>
     <v>536870912</v>
     <v>1</v>
-    <v>432</v>
+    <v>437</v>
     <v>27</v>
     <v>Turkey</v>
     <v>4</v>
     <v>5</v>
     <v>Map</v>
     <v>6</v>
-    <v>433</v>
+    <v>438</v>
     <v>TR</v>
-    <v>2876</v>
-    <v>2877</v>
-    <v>2878</v>
-    <v>2879</v>
-    <v>2880</v>
-    <v>2881</v>
-    <v>2882</v>
-    <v>2883</v>
-    <v>2884</v>
-    <v>TRL</v>
-    <v>Turkey, officially the Republic of Türkiye, is a country mainly located in Anatolia in West Asia, with a relatively small part called East Thrace in Southeast Europe. It borders the Black Sea to the north; Georgia, Armenia, Azerbaijan, and Iran ...</v>
-    <v>2885</v>
-    <v>2886</v>
-    <v>2887</v>
-    <v>2888</v>
-    <v>1794</v>
-    <v>2889</v>
-    <v>2890</v>
-    <v>2891</v>
-    <v>2892</v>
-    <v>2893</v>
-    <v>2894</v>
     <v>2898</v>
     <v>2899</v>
     <v>2900</v>
     <v>2901</v>
-    <v>2057</v>
     <v>2902</v>
-    <v>Turkey</v>
-    <v>İstiklal Marşı</v>
     <v>2903</v>
-    <v>Türkiye Cumhuriyeti</v>
     <v>2904</v>
     <v>2905</v>
     <v>2906</v>
-    <v>177</v>
+    <v>TRL</v>
+    <v>Turkey, officially the Republic of Türkiye, is a country mainly located in Anatolia in West Asia, with a relatively small part called East Thrace in Southeast Europe. It borders the Black Sea to the north; Georgia, Armenia, Azerbaijan, and Iran ...</v>
     <v>2907</v>
     <v>2908</v>
+    <v>2909</v>
+    <v>2910</v>
+    <v>1794</v>
+    <v>2911</v>
+    <v>2912</v>
+    <v>2913</v>
+    <v>2914</v>
+    <v>2915</v>
+    <v>2916</v>
+    <v>2920</v>
+    <v>2921</v>
+    <v>2922</v>
+    <v>2923</v>
+    <v>2057</v>
+    <v>2924</v>
+    <v>Turkey</v>
+    <v>İstiklal Marşı</v>
+    <v>2925</v>
+    <v>Türkiye Cumhuriyeti</v>
+    <v>2926</v>
+    <v>2927</v>
+    <v>2928</v>
+    <v>177</v>
+    <v>2929</v>
+    <v>2930</v>
     <v>288</v>
     <v>490</v>
     <v>671</v>
-    <v>2909</v>
-    <v>2910</v>
-    <v>2992</v>
-    <v>2993</v>
-    <v>2994</v>
-    <v>2995</v>
-    <v>2996</v>
+    <v>2931</v>
+    <v>2932</v>
+    <v>3014</v>
+    <v>3015</v>
+    <v>3016</v>
+    <v>3017</v>
+    <v>3018</v>
     <v>Turkey</v>
-    <v>2997</v>
+    <v>3019</v>
     <v>mdp/vdpid/235</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="26">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="27">
   <s t="_linkedentity2">
     <k n="%EntityServiceId" t="i"/>
     <k n="_DisplayString" t="s"/>
@@ -26394,12 +26885,40 @@
     <k n="UniqueName" t="s"/>
     <k n="VDPID/VSID" t="s"/>
   </s>
+  <s t="_linkedentity2core">
+    <k n="_CRID" t="e"/>
+    <k n="%EntityCulture" t="s"/>
+    <k n="%EntityId" t="s"/>
+    <k n="%EntityServiceId" t="i"/>
+    <k n="%IsRefreshable" t="b"/>
+    <k n="_Attribution" t="spb"/>
+    <k n="_Display" t="spb"/>
+    <k n="_DisplayString" t="s"/>
+    <k n="_Flags" t="spb"/>
+    <k n="_Format" t="spb"/>
+    <k n="_Icon" t="s"/>
+    <k n="_Provider" t="spb"/>
+    <k n="_SubLabel" t="spb"/>
+    <k n="Area" t="r"/>
+    <k n="Country/region" t="r"/>
+    <k n="Description" t="s"/>
+    <k n="Image" t="r"/>
+    <k n="Latitude" t="r"/>
+    <k n="Leader(s)" t="r"/>
+    <k n="LearnMoreOnLink" t="r"/>
+    <k n="Longitude" t="r"/>
+    <k n="Name" t="s"/>
+    <k n="Population" t="r"/>
+    <k n="Time zone(s)" t="r"/>
+    <k n="UniqueName" t="s"/>
+    <k n="VDPID/VSID" t="s"/>
+  </s>
 </rvStructures>
 </file>
 
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
-  <spbArrays count="21">
+  <spbArrays count="22">
     <a count="26">
       <v t="s">%EntityServiceId</v>
       <v t="s">%IsRefreshable</v>
@@ -27197,8 +27716,35 @@
       <v t="s">Image</v>
       <v t="s">Description</v>
     </a>
+    <a count="25">
+      <v t="s">%EntityServiceId</v>
+      <v t="s">%IsRefreshable</v>
+      <v t="s">%EntityCulture</v>
+      <v t="s">%EntityId</v>
+      <v t="s">_Icon</v>
+      <v t="s">_Provider</v>
+      <v t="s">_Attribution</v>
+      <v t="s">_Display</v>
+      <v t="s">Name</v>
+      <v t="s">_Format</v>
+      <v t="s">Country/region</v>
+      <v t="s">Leader(s)</v>
+      <v t="s">_SubLabel</v>
+      <v t="s">Population</v>
+      <v t="s">Area</v>
+      <v t="s">Latitude</v>
+      <v t="s">Longitude</v>
+      <v t="s">Time zone(s)</v>
+      <v t="s">_Flags</v>
+      <v t="s">VDPID/VSID</v>
+      <v t="s">UniqueName</v>
+      <v t="s">_DisplayString</v>
+      <v t="s">LearnMoreOnLink</v>
+      <v t="s">Image</v>
+      <v t="s">Description</v>
+    </a>
   </spbArrays>
-  <spbData count="434">
+  <spbData count="439">
     <spb s="0">
       <v xml:space="preserve">Wikipedia	</v>
       <v xml:space="preserve">CC BY-SA 3.0	</v>
@@ -32523,6 +33069,45 @@
       <v>426</v>
     </spb>
     <spb s="0">
+      <v xml:space="preserve">Wikipedia	</v>
+      <v xml:space="preserve">CC BY-SA 3.0	</v>
+      <v xml:space="preserve">https://en.wikipedia.org/wiki/Providence,_Rhode_Island	</v>
+      <v xml:space="preserve">https://creativecommons.org/licenses/by-sa/3.0	</v>
+    </spb>
+    <spb s="16">
+      <v>428</v>
+      <v>428</v>
+      <v>428</v>
+      <v>428</v>
+      <v>428</v>
+      <v>428</v>
+      <v>428</v>
+      <v>428</v>
+      <v>428</v>
+      <v>428</v>
+    </spb>
+    <spb s="0">
+      <v xml:space="preserve">Wikipedia	</v>
+      <v xml:space="preserve">CC BY-SA 3.0	</v>
+      <v xml:space="preserve">https://en.wikipedia.org/wiki/Brussels	</v>
+      <v xml:space="preserve">https://creativecommons.org/licenses/by-sa/3.0	</v>
+    </spb>
+    <spb s="34">
+      <v>430</v>
+      <v>430</v>
+      <v>430</v>
+      <v>430</v>
+      <v>430</v>
+      <v>430</v>
+      <v>430</v>
+      <v>430</v>
+    </spb>
+    <spb s="2">
+      <v>21</v>
+      <v>Name</v>
+      <v>LearnMoreOnLink</v>
+    </spb>
+    <spb s="0">
       <v xml:space="preserve">Wikipedia	Cia	travel.state.gov	</v>
       <v xml:space="preserve">CC-BY-SA			</v>
       <v xml:space="preserve">http://en.wikipedia.org/wiki/Turkey	https://www.cia.gov/library/publications/the-world-factbook/geos/tu.html?Transportation	https://travel.state.gov/content/travel/en/international-travel/International-Travel-Country-Information-Pages/Turkey.html	</v>
@@ -32548,49 +33133,49 @@
     </spb>
     <spb s="17">
       <v>10</v>
-      <v>428</v>
-      <v>429</v>
-      <v>429</v>
+      <v>433</v>
+      <v>434</v>
+      <v>434</v>
       <v>13</v>
-      <v>429</v>
-      <v>429</v>
-      <v>429</v>
-      <v>430</v>
-      <v>429</v>
-      <v>429</v>
-      <v>430</v>
-      <v>429</v>
-      <v>429</v>
-      <v>431</v>
+      <v>434</v>
+      <v>434</v>
+      <v>434</v>
+      <v>435</v>
+      <v>434</v>
+      <v>434</v>
+      <v>435</v>
+      <v>434</v>
+      <v>434</v>
+      <v>436</v>
       <v>15</v>
-      <v>428</v>
-      <v>431</v>
+      <v>433</v>
+      <v>436</v>
       <v>17</v>
-      <v>429</v>
-      <v>431</v>
+      <v>434</v>
+      <v>436</v>
       <v>18</v>
       <v>19</v>
       <v>20</v>
-      <v>431</v>
-      <v>431</v>
-      <v>429</v>
-      <v>431</v>
+      <v>436</v>
+      <v>436</v>
+      <v>434</v>
+      <v>436</v>
       <v>21</v>
       <v>22</v>
       <v>23</v>
       <v>24</v>
-      <v>431</v>
-      <v>428</v>
-      <v>431</v>
-      <v>431</v>
-      <v>431</v>
-      <v>431</v>
-      <v>431</v>
-      <v>431</v>
-      <v>431</v>
-      <v>431</v>
-      <v>431</v>
-      <v>431</v>
+      <v>436</v>
+      <v>433</v>
+      <v>436</v>
+      <v>436</v>
+      <v>436</v>
+      <v>436</v>
+      <v>436</v>
+      <v>436</v>
+      <v>436</v>
+      <v>436</v>
+      <v>436</v>
+      <v>436</v>
       <v>25</v>
     </spb>
     <spb s="10">
@@ -32634,7 +33219,7 @@
 </file>
 
 <file path=xl/richData/rdsupportingpropertybagstructure.xml><?xml version="1.0" encoding="utf-8"?>
-<spbStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="34">
+<spbStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="35">
   <s>
     <k n="SourceText" t="s"/>
     <k n="LicenseText" t="s"/>
@@ -33192,6 +33777,16 @@
     <k n="Abbreviation" t="spb"/>
     <k n="Country/region" t="spb"/>
   </s>
+  <s>
+    <k n="Area" t="spb"/>
+    <k n="Name" t="spb"/>
+    <k n="Latitude" t="spb"/>
+    <k n="Longitude" t="spb"/>
+    <k n="Population" t="spb"/>
+    <k n="UniqueName" t="spb"/>
+    <k n="Description" t="spb"/>
+    <k n="Country/region" t="spb"/>
+  </s>
 </spbStructures>
 </file>
 
@@ -33589,7 +34184,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7772053-9363-CA4A-A53F-040B7C700753}">
-  <dimension ref="A1:U202"/>
+  <dimension ref="A1:U212"/>
   <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -35836,7 +36431,7 @@
         <v>626</v>
       </c>
       <c r="H54" t="s">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="L54" t="s">
         <v>624</v>
@@ -36417,7 +37012,7 @@
         <v>602</v>
       </c>
       <c r="H68" t="s">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="L68" t="s">
         <v>601</v>
@@ -36458,7 +37053,7 @@
         <v>614</v>
       </c>
       <c r="H69" t="s">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="L69" t="s">
         <v>613</v>
@@ -36502,7 +37097,7 @@
         <v>628</v>
       </c>
       <c r="H70" t="s">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="L70" t="s">
         <v>630</v>
@@ -36543,7 +37138,7 @@
         <v>632</v>
       </c>
       <c r="H71" t="s">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="L71" t="s">
         <v>633</v>
@@ -39465,7 +40060,7 @@
         <v>1</v>
       </c>
       <c r="H139" t="s">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="L139" t="s">
         <v>517</v>
@@ -39509,7 +40104,7 @@
         <v>578</v>
       </c>
       <c r="H140" t="s">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="L140" t="s">
         <v>579</v>
@@ -39597,7 +40192,7 @@
         <v>620</v>
       </c>
       <c r="H142" t="s">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="L142" t="s">
         <v>619</v>
@@ -39688,7 +40283,7 @@
         <v>636</v>
       </c>
       <c r="H144" t="s">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="L144" t="s">
         <v>635</v>
@@ -39717,32 +40312,31 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A145" t="s">
-        <v>110</v>
+        <v>654</v>
+      </c>
+      <c r="B145" t="s">
+        <v>658</v>
       </c>
       <c r="C145" s="1">
-        <v>45976</v>
+        <v>45971</v>
       </c>
       <c r="D145" t="s">
         <v>16</v>
       </c>
-      <c r="G145" s="1"/>
       <c r="H145" t="s">
         <v>25</v>
       </c>
       <c r="L145" t="s">
-        <v>111</v>
-      </c>
-      <c r="M145" t="e" vm="14">
+        <v>657</v>
+      </c>
+      <c r="M145" t="e" vm="77">
         <v>#VALUE!</v>
-      </c>
-      <c r="N145" t="s">
-        <v>12</v>
       </c>
       <c r="P145" t="s">
         <v>20</v>
       </c>
       <c r="Q145" s="1">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="S145">
         <v>1</v>
@@ -39755,34 +40349,22 @@
       </c>
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.4">
-      <c r="A146" s="4" t="s">
-        <v>167</v>
+      <c r="A146" t="s">
+        <v>662</v>
       </c>
       <c r="C146" s="1">
-        <v>45976</v>
+        <v>45971</v>
       </c>
       <c r="D146" t="s">
         <v>16</v>
       </c>
-      <c r="F146">
-        <v>2</v>
-      </c>
-      <c r="G146" s="7" t="s">
-        <v>169</v>
-      </c>
       <c r="H146" t="s">
         <v>25</v>
       </c>
-      <c r="J146" t="s">
-        <v>247</v>
-      </c>
-      <c r="K146" s="1">
-        <v>45986</v>
-      </c>
-      <c r="L146" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="M146" t="e" vm="77">
+      <c r="L146" t="s">
+        <v>661</v>
+      </c>
+      <c r="M146" t="e" vm="16">
         <v>#VALUE!</v>
       </c>
       <c r="N146" t="s">
@@ -39806,7 +40388,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A147" t="s">
-        <v>383</v>
+        <v>110</v>
       </c>
       <c r="C147" s="1">
         <v>45976</v>
@@ -39814,13 +40396,14 @@
       <c r="D147" t="s">
         <v>16</v>
       </c>
+      <c r="G147" s="1"/>
       <c r="H147" t="s">
         <v>99</v>
       </c>
       <c r="L147" t="s">
-        <v>382</v>
-      </c>
-      <c r="M147" t="e" vm="31">
+        <v>111</v>
+      </c>
+      <c r="M147" t="e" vm="14">
         <v>#VALUE!</v>
       </c>
       <c r="N147" t="s">
@@ -39830,7 +40413,7 @@
         <v>20</v>
       </c>
       <c r="Q147" s="1">
-        <v>45985</v>
+        <v>45981</v>
       </c>
       <c r="S147">
         <v>1</v>
@@ -39843,23 +40426,32 @@
       </c>
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.4">
-      <c r="A148" t="s">
-        <v>462</v>
+      <c r="A148" s="4" t="s">
+        <v>167</v>
       </c>
       <c r="C148" s="1">
         <v>45976</v>
       </c>
       <c r="D148" t="s">
-        <v>42</v>
-      </c>
-      <c r="E148" t="s">
-        <v>463</v>
+        <v>16</v>
+      </c>
+      <c r="F148">
+        <v>2</v>
+      </c>
+      <c r="G148" s="7" t="s">
+        <v>169</v>
       </c>
       <c r="H148" t="s">
         <v>25</v>
       </c>
-      <c r="L148" t="s">
-        <v>464</v>
+      <c r="J148" t="s">
+        <v>247</v>
+      </c>
+      <c r="K148" s="1">
+        <v>45986</v>
+      </c>
+      <c r="L148" s="2" t="s">
+        <v>168</v>
       </c>
       <c r="M148" t="e" vm="78">
         <v>#VALUE!</v>
@@ -39871,21 +40463,21 @@
         <v>20</v>
       </c>
       <c r="Q148" s="1">
-        <v>45985</v>
+        <v>45982</v>
       </c>
       <c r="S148">
         <v>1</v>
       </c>
       <c r="T148">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U148">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.4">
-      <c r="A149" s="4" t="s">
-        <v>141</v>
+      <c r="A149" t="s">
+        <v>383</v>
       </c>
       <c r="C149" s="1">
         <v>45976</v>
@@ -39893,22 +40485,13 @@
       <c r="D149" t="s">
         <v>16</v>
       </c>
-      <c r="F149">
-        <v>1</v>
-      </c>
       <c r="H149" t="s">
-        <v>25</v>
-      </c>
-      <c r="J149" t="s">
-        <v>247</v>
-      </c>
-      <c r="K149" s="1">
-        <v>45986</v>
-      </c>
-      <c r="L149" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="M149" t="e" vm="79">
+        <v>99</v>
+      </c>
+      <c r="L149" t="s">
+        <v>382</v>
+      </c>
+      <c r="M149" t="e" vm="31">
         <v>#VALUE!</v>
       </c>
       <c r="N149" t="s">
@@ -39918,47 +40501,38 @@
         <v>20</v>
       </c>
       <c r="Q149" s="1">
-        <v>45986</v>
+        <v>45985</v>
       </c>
       <c r="S149">
         <v>1</v>
       </c>
       <c r="T149">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U149">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.4">
-      <c r="A150" s="4" t="s">
-        <v>122</v>
+      <c r="A150" t="s">
+        <v>462</v>
       </c>
       <c r="C150" s="1">
         <v>45976</v>
       </c>
       <c r="D150" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="E150" t="s">
-        <v>123</v>
-      </c>
-      <c r="F150">
-        <v>2</v>
+        <v>463</v>
       </c>
       <c r="H150" t="s">
-        <v>25</v>
-      </c>
-      <c r="J150" t="s">
-        <v>247</v>
-      </c>
-      <c r="K150" s="1">
-        <v>45986</v>
-      </c>
-      <c r="L150" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="M150" t="e" vm="27">
+        <v>99</v>
+      </c>
+      <c r="L150" t="s">
+        <v>464</v>
+      </c>
+      <c r="M150" t="e" vm="79">
         <v>#VALUE!</v>
       </c>
       <c r="N150" t="s">
@@ -39968,24 +40542,21 @@
         <v>20</v>
       </c>
       <c r="Q150" s="1">
-        <v>45988</v>
+        <v>45985</v>
       </c>
       <c r="S150">
         <v>1</v>
       </c>
       <c r="T150">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U150">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A151" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="B151" t="s">
-        <v>638</v>
+        <v>141</v>
       </c>
       <c r="C151" s="1">
         <v>45976</v>
@@ -39994,7 +40565,7 @@
         <v>16</v>
       </c>
       <c r="F151">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H151" t="s">
         <v>25</v>
@@ -40006,9 +40577,9 @@
         <v>45986</v>
       </c>
       <c r="L151" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="M151" t="e" vm="79">
+        <v>142</v>
+      </c>
+      <c r="M151" t="e" vm="77">
         <v>#VALUE!</v>
       </c>
       <c r="N151" t="s">
@@ -40018,35 +40589,47 @@
         <v>20</v>
       </c>
       <c r="Q151" s="1">
-        <v>45989</v>
+        <v>45986</v>
       </c>
       <c r="S151">
         <v>1</v>
       </c>
       <c r="T151">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U151">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.4">
-      <c r="A152" t="s">
-        <v>529</v>
+      <c r="A152" s="4" t="s">
+        <v>122</v>
       </c>
       <c r="C152" s="1">
         <v>45976</v>
       </c>
       <c r="D152" t="s">
-        <v>530</v>
+        <v>16</v>
+      </c>
+      <c r="E152" t="s">
+        <v>123</v>
+      </c>
+      <c r="F152">
+        <v>2</v>
       </c>
       <c r="H152" t="s">
         <v>25</v>
       </c>
-      <c r="L152" t="s">
-        <v>531</v>
-      </c>
-      <c r="M152" t="e" vm="43">
+      <c r="J152" t="s">
+        <v>247</v>
+      </c>
+      <c r="K152" s="1">
+        <v>45986</v>
+      </c>
+      <c r="L152" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="M152" t="e" vm="27">
         <v>#VALUE!</v>
       </c>
       <c r="N152" t="s">
@@ -40056,7 +40639,7 @@
         <v>20</v>
       </c>
       <c r="Q152" s="1">
-        <v>46081</v>
+        <v>45988</v>
       </c>
       <c r="S152">
         <v>1</v>
@@ -40069,25 +40652,34 @@
       </c>
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.4">
-      <c r="A153" t="s">
-        <v>535</v>
+      <c r="A153" s="4" t="s">
+        <v>143</v>
       </c>
       <c r="B153" t="s">
-        <v>536</v>
+        <v>638</v>
       </c>
       <c r="C153" s="1">
         <v>45976</v>
       </c>
       <c r="D153" t="s">
-        <v>537</v>
+        <v>16</v>
+      </c>
+      <c r="F153">
+        <v>2</v>
       </c>
       <c r="H153" t="s">
         <v>25</v>
       </c>
-      <c r="L153" t="s">
-        <v>538</v>
-      </c>
-      <c r="M153" t="e" vm="37">
+      <c r="J153" t="s">
+        <v>247</v>
+      </c>
+      <c r="K153" s="1">
+        <v>45986</v>
+      </c>
+      <c r="L153" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="M153" t="e" vm="77">
         <v>#VALUE!</v>
       </c>
       <c r="N153" t="s">
@@ -40097,7 +40689,7 @@
         <v>20</v>
       </c>
       <c r="Q153" s="1">
-        <v>46082</v>
+        <v>45989</v>
       </c>
       <c r="S153">
         <v>1</v>
@@ -40106,32 +40698,26 @@
         <v>0</v>
       </c>
       <c r="U153">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A154" t="s">
-        <v>555</v>
-      </c>
-      <c r="B154" t="s">
-        <v>556</v>
+        <v>529</v>
       </c>
       <c r="C154" s="1">
         <v>45976</v>
       </c>
       <c r="D154" t="s">
-        <v>42</v>
-      </c>
-      <c r="E154" t="s">
-        <v>557</v>
+        <v>530</v>
       </c>
       <c r="H154" t="s">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="L154" t="s">
-        <v>554</v>
-      </c>
-      <c r="M154" t="e" vm="37">
+        <v>531</v>
+      </c>
+      <c r="M154" t="e" vm="43">
         <v>#VALUE!</v>
       </c>
       <c r="N154" t="s">
@@ -40141,7 +40727,7 @@
         <v>20</v>
       </c>
       <c r="Q154" s="1">
-        <v>45688</v>
+        <v>46081</v>
       </c>
       <c r="S154">
         <v>1</v>
@@ -40150,26 +40736,29 @@
         <v>0</v>
       </c>
       <c r="U154">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A155" t="s">
-        <v>561</v>
+        <v>535</v>
+      </c>
+      <c r="B155" t="s">
+        <v>536</v>
       </c>
       <c r="C155" s="1">
         <v>45976</v>
       </c>
       <c r="D155" t="s">
-        <v>42</v>
+        <v>537</v>
       </c>
       <c r="H155" t="s">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="L155" t="s">
-        <v>562</v>
-      </c>
-      <c r="M155" t="e" vm="80">
+        <v>538</v>
+      </c>
+      <c r="M155" t="e" vm="37">
         <v>#VALUE!</v>
       </c>
       <c r="N155" t="s">
@@ -40179,7 +40768,7 @@
         <v>20</v>
       </c>
       <c r="Q155" s="1">
-        <v>46022</v>
+        <v>46082</v>
       </c>
       <c r="S155">
         <v>1</v>
@@ -40188,12 +40777,15 @@
         <v>0</v>
       </c>
       <c r="U155">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A156" t="s">
-        <v>564</v>
+        <v>555</v>
+      </c>
+      <c r="B156" t="s">
+        <v>556</v>
       </c>
       <c r="C156" s="1">
         <v>45976</v>
@@ -40201,11 +40793,14 @@
       <c r="D156" t="s">
         <v>42</v>
       </c>
+      <c r="E156" t="s">
+        <v>557</v>
+      </c>
       <c r="H156" t="s">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="L156" t="s">
-        <v>563</v>
+        <v>554</v>
       </c>
       <c r="M156" t="e" vm="37">
         <v>#VALUE!</v>
@@ -40217,13 +40812,13 @@
         <v>20</v>
       </c>
       <c r="Q156" s="1">
-        <v>46053</v>
+        <v>45688</v>
       </c>
       <c r="S156">
         <v>1</v>
       </c>
       <c r="T156">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U156">
         <v>1</v>
@@ -40231,7 +40826,7 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A157" t="s">
-        <v>640</v>
+        <v>561</v>
       </c>
       <c r="C157" s="1">
         <v>45976</v>
@@ -40239,16 +40834,13 @@
       <c r="D157" t="s">
         <v>42</v>
       </c>
-      <c r="E157" t="s">
-        <v>584</v>
-      </c>
       <c r="H157" t="s">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="L157" t="s">
-        <v>585</v>
-      </c>
-      <c r="M157" t="e" vm="15">
+        <v>562</v>
+      </c>
+      <c r="M157" t="e" vm="80">
         <v>#VALUE!</v>
       </c>
       <c r="N157" t="s">
@@ -40258,7 +40850,7 @@
         <v>20</v>
       </c>
       <c r="Q157" s="1">
-        <v>45976</v>
+        <v>46022</v>
       </c>
       <c r="S157">
         <v>1</v>
@@ -40267,12 +40859,12 @@
         <v>0</v>
       </c>
       <c r="U157">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A158" t="s">
-        <v>598</v>
+        <v>564</v>
       </c>
       <c r="C158" s="1">
         <v>45976</v>
@@ -40280,16 +40872,13 @@
       <c r="D158" t="s">
         <v>42</v>
       </c>
-      <c r="E158" t="s">
-        <v>599</v>
-      </c>
       <c r="H158" t="s">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="L158" t="s">
-        <v>597</v>
-      </c>
-      <c r="M158" t="e" vm="81">
+        <v>563</v>
+      </c>
+      <c r="M158" t="e" vm="37">
         <v>#VALUE!</v>
       </c>
       <c r="N158" t="s">
@@ -40299,7 +40888,7 @@
         <v>20</v>
       </c>
       <c r="Q158" s="1">
-        <v>45991</v>
+        <v>46053</v>
       </c>
       <c r="S158">
         <v>1</v>
@@ -40313,21 +40902,24 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A159" t="s">
-        <v>341</v>
+        <v>640</v>
       </c>
       <c r="C159" s="1">
-        <v>45981</v>
+        <v>45976</v>
       </c>
       <c r="D159" t="s">
         <v>42</v>
       </c>
+      <c r="E159" t="s">
+        <v>584</v>
+      </c>
       <c r="H159" t="s">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="L159" t="s">
-        <v>342</v>
-      </c>
-      <c r="M159" t="e" vm="79">
+        <v>585</v>
+      </c>
+      <c r="M159" t="e" vm="15">
         <v>#VALUE!</v>
       </c>
       <c r="N159" t="s">
@@ -40337,7 +40929,7 @@
         <v>20</v>
       </c>
       <c r="Q159" s="1">
-        <v>45661</v>
+        <v>45976</v>
       </c>
       <c r="S159">
         <v>1</v>
@@ -40346,26 +40938,29 @@
         <v>0</v>
       </c>
       <c r="U159">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A160" t="s">
-        <v>416</v>
+        <v>598</v>
       </c>
       <c r="C160" s="1">
-        <v>45981</v>
+        <v>45976</v>
       </c>
       <c r="D160" t="s">
-        <v>417</v>
+        <v>42</v>
+      </c>
+      <c r="E160" t="s">
+        <v>599</v>
       </c>
       <c r="H160" t="s">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="L160" t="s">
-        <v>105</v>
-      </c>
-      <c r="M160" t="e" vm="58">
+        <v>597</v>
+      </c>
+      <c r="M160" t="e" vm="81">
         <v>#VALUE!</v>
       </c>
       <c r="N160" t="s">
@@ -40375,42 +40970,45 @@
         <v>20</v>
       </c>
       <c r="Q160" s="1">
-        <v>45984</v>
+        <v>45991</v>
       </c>
       <c r="S160">
         <v>1</v>
       </c>
       <c r="T160">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U160">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A161" t="s">
-        <v>385</v>
+        <v>341</v>
       </c>
       <c r="C161" s="1">
         <v>45981</v>
       </c>
       <c r="D161" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="H161" t="s">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="L161" t="s">
-        <v>386</v>
-      </c>
-      <c r="M161" t="e" vm="70">
+        <v>342</v>
+      </c>
+      <c r="M161" t="e" vm="77">
         <v>#VALUE!</v>
+      </c>
+      <c r="N161" t="s">
+        <v>12</v>
       </c>
       <c r="P161" t="s">
         <v>20</v>
       </c>
       <c r="Q161" s="1">
-        <v>45985</v>
+        <v>45661</v>
       </c>
       <c r="S161">
         <v>1</v>
@@ -40424,21 +41022,21 @@
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A162" t="s">
-        <v>356</v>
+        <v>416</v>
       </c>
       <c r="C162" s="1">
         <v>45981</v>
       </c>
       <c r="D162" t="s">
-        <v>42</v>
+        <v>417</v>
       </c>
       <c r="H162" t="s">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="L162" t="s">
-        <v>355</v>
-      </c>
-      <c r="M162" t="e" vm="82">
+        <v>105</v>
+      </c>
+      <c r="M162" t="e" vm="58">
         <v>#VALUE!</v>
       </c>
       <c r="N162" t="s">
@@ -40448,7 +41046,7 @@
         <v>20</v>
       </c>
       <c r="Q162" s="1">
-        <v>45987</v>
+        <v>45984</v>
       </c>
       <c r="S162">
         <v>1</v>
@@ -40457,12 +41055,12 @@
         <v>0</v>
       </c>
       <c r="U162">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A163" t="s">
-        <v>295</v>
+        <v>385</v>
       </c>
       <c r="C163" s="1">
         <v>45981</v>
@@ -40470,26 +41068,20 @@
       <c r="D163" t="s">
         <v>16</v>
       </c>
-      <c r="G163" t="s">
-        <v>296</v>
-      </c>
       <c r="H163" t="s">
         <v>25</v>
       </c>
       <c r="L163" t="s">
-        <v>294</v>
-      </c>
-      <c r="M163" t="e" vm="27">
+        <v>386</v>
+      </c>
+      <c r="M163" t="e" vm="70">
         <v>#VALUE!</v>
-      </c>
-      <c r="N163" t="s">
-        <v>12</v>
       </c>
       <c r="P163" t="s">
         <v>20</v>
       </c>
       <c r="Q163" s="1">
-        <v>45989</v>
+        <v>45985</v>
       </c>
       <c r="S163">
         <v>1</v>
@@ -40503,37 +41095,31 @@
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A164" t="s">
-        <v>298</v>
+        <v>356</v>
       </c>
       <c r="C164" s="1">
         <v>45981</v>
       </c>
       <c r="D164" t="s">
-        <v>16</v>
-      </c>
-      <c r="G164" s="2" t="s">
-        <v>299</v>
+        <v>42</v>
       </c>
       <c r="H164" t="s">
         <v>25</v>
       </c>
       <c r="L164" t="s">
-        <v>297</v>
-      </c>
-      <c r="M164" t="e" vm="59">
+        <v>355</v>
+      </c>
+      <c r="M164" t="e" vm="82">
         <v>#VALUE!</v>
       </c>
       <c r="N164" t="s">
         <v>12</v>
       </c>
-      <c r="O164" t="s">
-        <v>67</v>
-      </c>
       <c r="P164" t="s">
         <v>20</v>
       </c>
       <c r="Q164" s="1">
-        <v>45989</v>
+        <v>45987</v>
       </c>
       <c r="S164">
         <v>1</v>
@@ -40542,12 +41128,12 @@
         <v>0</v>
       </c>
       <c r="U164">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.4">
-      <c r="A165" s="4" t="s">
-        <v>156</v>
+      <c r="A165" t="s">
+        <v>295</v>
       </c>
       <c r="C165" s="1">
         <v>45981</v>
@@ -40555,41 +41141,32 @@
       <c r="D165" t="s">
         <v>16</v>
       </c>
-      <c r="F165">
-        <v>1</v>
-      </c>
-      <c r="G165" s="7" t="s">
-        <v>158</v>
+      <c r="G165" t="s">
+        <v>296</v>
       </c>
       <c r="H165" t="s">
         <v>25</v>
       </c>
-      <c r="J165" t="s">
-        <v>247</v>
-      </c>
-      <c r="K165" s="1">
-        <v>45992</v>
-      </c>
-      <c r="L165" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="M165" t="e" vm="58">
+      <c r="L165" t="s">
+        <v>294</v>
+      </c>
+      <c r="M165" t="e" vm="27">
         <v>#VALUE!</v>
       </c>
       <c r="N165" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="P165" t="s">
         <v>20</v>
       </c>
       <c r="Q165" s="1">
-        <v>45991</v>
+        <v>45989</v>
       </c>
       <c r="S165">
         <v>1</v>
       </c>
       <c r="T165">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U165">
         <v>0</v>
@@ -40597,7 +41174,7 @@
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A166" t="s">
-        <v>270</v>
+        <v>298</v>
       </c>
       <c r="C166" s="1">
         <v>45981</v>
@@ -40605,26 +41182,29 @@
       <c r="D166" t="s">
         <v>16</v>
       </c>
-      <c r="F166">
-        <v>1</v>
+      <c r="G166" s="2" t="s">
+        <v>299</v>
       </c>
       <c r="H166" t="s">
         <v>25</v>
       </c>
       <c r="L166" t="s">
-        <v>271</v>
-      </c>
-      <c r="M166" t="e" vm="83">
+        <v>297</v>
+      </c>
+      <c r="M166" t="e" vm="59">
         <v>#VALUE!</v>
       </c>
       <c r="N166" t="s">
         <v>12</v>
       </c>
+      <c r="O166" t="s">
+        <v>67</v>
+      </c>
       <c r="P166" t="s">
         <v>20</v>
       </c>
       <c r="Q166" s="1">
-        <v>45991</v>
+        <v>45989</v>
       </c>
       <c r="S166">
         <v>1</v>
@@ -40637,8 +41217,8 @@
       </c>
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.4">
-      <c r="A167" t="s">
-        <v>284</v>
+      <c r="A167" s="4" t="s">
+        <v>156</v>
       </c>
       <c r="C167" s="1">
         <v>45981</v>
@@ -40646,14 +41226,29 @@
       <c r="D167" t="s">
         <v>16</v>
       </c>
+      <c r="F167">
+        <v>1</v>
+      </c>
+      <c r="G167" s="7" t="s">
+        <v>158</v>
+      </c>
       <c r="H167" t="s">
         <v>25</v>
       </c>
-      <c r="L167" t="s">
-        <v>285</v>
-      </c>
-      <c r="M167" t="e" vm="71">
+      <c r="J167" t="s">
+        <v>247</v>
+      </c>
+      <c r="K167" s="1">
+        <v>45992</v>
+      </c>
+      <c r="L167" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="M167" t="e" vm="58">
         <v>#VALUE!</v>
+      </c>
+      <c r="N167" t="s">
+        <v>28</v>
       </c>
       <c r="P167" t="s">
         <v>20</v>
@@ -40665,7 +41260,7 @@
         <v>1</v>
       </c>
       <c r="T167">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U167">
         <v>0</v>
@@ -40673,7 +41268,7 @@
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A168" t="s">
-        <v>286</v>
+        <v>270</v>
       </c>
       <c r="C168" s="1">
         <v>45981</v>
@@ -40681,14 +41276,20 @@
       <c r="D168" t="s">
         <v>16</v>
       </c>
+      <c r="F168">
+        <v>1</v>
+      </c>
       <c r="H168" t="s">
         <v>25</v>
       </c>
       <c r="L168" t="s">
-        <v>287</v>
-      </c>
-      <c r="M168" t="e" vm="84">
+        <v>271</v>
+      </c>
+      <c r="M168" t="e" vm="83">
         <v>#VALUE!</v>
+      </c>
+      <c r="N168" t="s">
+        <v>12</v>
       </c>
       <c r="P168" t="s">
         <v>20</v>
@@ -40708,7 +41309,7 @@
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A169" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="C169" s="1">
         <v>45981</v>
@@ -40720,13 +41321,10 @@
         <v>25</v>
       </c>
       <c r="L169" t="s">
-        <v>290</v>
-      </c>
-      <c r="M169" t="e" vm="70">
+        <v>285</v>
+      </c>
+      <c r="M169" t="e" vm="71">
         <v>#VALUE!</v>
-      </c>
-      <c r="N169" t="s">
-        <v>12</v>
       </c>
       <c r="P169" t="s">
         <v>20</v>
@@ -40738,33 +41336,30 @@
         <v>1</v>
       </c>
       <c r="T169">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U169">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A170" t="s">
-        <v>380</v>
+        <v>286</v>
       </c>
       <c r="C170" s="1">
         <v>45981</v>
       </c>
-      <c r="D170" s="2" t="s">
-        <v>381</v>
+      <c r="D170" t="s">
+        <v>16</v>
       </c>
       <c r="H170" t="s">
         <v>25</v>
       </c>
       <c r="L170" t="s">
-        <v>379</v>
-      </c>
-      <c r="M170" t="e" vm="31">
+        <v>287</v>
+      </c>
+      <c r="M170" t="e" vm="84">
         <v>#VALUE!</v>
-      </c>
-      <c r="N170" t="s">
-        <v>28</v>
       </c>
       <c r="P170" t="s">
         <v>20</v>
@@ -40784,27 +41379,21 @@
     </row>
     <row r="171" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A171" t="s">
-        <v>412</v>
+        <v>291</v>
       </c>
       <c r="C171" s="1">
         <v>45981</v>
       </c>
-      <c r="D171" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="E171" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="G171" t="s">
-        <v>415</v>
+      <c r="D171" t="s">
+        <v>16</v>
       </c>
       <c r="H171" t="s">
         <v>25</v>
       </c>
       <c r="L171" t="s">
-        <v>111</v>
-      </c>
-      <c r="M171" t="e" vm="85">
+        <v>290</v>
+      </c>
+      <c r="M171" t="e" vm="70">
         <v>#VALUE!</v>
       </c>
       <c r="N171" t="s">
@@ -40823,35 +41412,26 @@
         <v>1</v>
       </c>
       <c r="U171">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="172" spans="1:21" x14ac:dyDescent="0.4">
-      <c r="A172" s="4" t="s">
-        <v>160</v>
+      <c r="A172" t="s">
+        <v>380</v>
       </c>
       <c r="C172" s="1">
         <v>45981</v>
       </c>
-      <c r="D172" t="s">
-        <v>16</v>
-      </c>
-      <c r="F172">
-        <v>1</v>
+      <c r="D172" s="2" t="s">
+        <v>381</v>
       </c>
       <c r="H172" t="s">
         <v>25</v>
       </c>
-      <c r="J172" t="s">
-        <v>247</v>
-      </c>
-      <c r="K172" s="1">
-        <v>45992</v>
-      </c>
-      <c r="L172" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="M172" t="e" vm="58">
+      <c r="L172" t="s">
+        <v>379</v>
+      </c>
+      <c r="M172" t="e" vm="31">
         <v>#VALUE!</v>
       </c>
       <c r="N172" t="s">
@@ -40861,13 +41441,13 @@
         <v>20</v>
       </c>
       <c r="Q172" s="1">
-        <v>45992</v>
+        <v>45991</v>
       </c>
       <c r="S172">
         <v>1</v>
       </c>
       <c r="T172">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U172">
         <v>0</v>
@@ -40875,22 +41455,25 @@
     </row>
     <row r="173" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A173" t="s">
-        <v>241</v>
+        <v>412</v>
       </c>
       <c r="C173" s="1">
         <v>45981</v>
       </c>
-      <c r="D173" t="s">
-        <v>42</v>
+      <c r="D173" s="2" t="s">
+        <v>413</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>243</v>
+        <v>414</v>
+      </c>
+      <c r="G173" t="s">
+        <v>415</v>
       </c>
       <c r="H173" t="s">
         <v>25</v>
       </c>
       <c r="L173" t="s">
-        <v>242</v>
+        <v>111</v>
       </c>
       <c r="M173" t="e" vm="85">
         <v>#VALUE!</v>
@@ -40898,28 +41481,25 @@
       <c r="N173" t="s">
         <v>12</v>
       </c>
-      <c r="O173" t="s">
-        <v>67</v>
-      </c>
       <c r="P173" t="s">
         <v>20</v>
       </c>
       <c r="Q173" s="1">
-        <v>45992</v>
+        <v>45991</v>
       </c>
       <c r="S173">
         <v>1</v>
       </c>
       <c r="T173">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U173">
         <v>0</v>
       </c>
     </row>
     <row r="174" spans="1:21" x14ac:dyDescent="0.4">
-      <c r="A174" t="s">
-        <v>269</v>
+      <c r="A174" s="4" t="s">
+        <v>160</v>
       </c>
       <c r="C174" s="1">
         <v>45981</v>
@@ -40927,13 +41507,22 @@
       <c r="D174" t="s">
         <v>16</v>
       </c>
+      <c r="F174">
+        <v>1</v>
+      </c>
       <c r="H174" t="s">
         <v>25</v>
       </c>
-      <c r="L174" t="s">
-        <v>268</v>
-      </c>
-      <c r="M174" t="e" vm="70">
+      <c r="J174" t="s">
+        <v>247</v>
+      </c>
+      <c r="K174" s="1">
+        <v>45992</v>
+      </c>
+      <c r="L174" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="M174" t="e" vm="58">
         <v>#VALUE!</v>
       </c>
       <c r="N174" t="s">
@@ -40957,29 +41546,32 @@
     </row>
     <row r="175" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A175" t="s">
-        <v>427</v>
+        <v>241</v>
       </c>
       <c r="C175" s="1">
         <v>45981</v>
       </c>
       <c r="D175" t="s">
-        <v>429</v>
-      </c>
-      <c r="E175" t="s">
-        <v>428</v>
+        <v>42</v>
+      </c>
+      <c r="E175" s="2" t="s">
+        <v>243</v>
       </c>
       <c r="H175" t="s">
         <v>25</v>
       </c>
       <c r="L175" t="s">
-        <v>430</v>
-      </c>
-      <c r="M175" t="e" vm="41">
+        <v>242</v>
+      </c>
+      <c r="M175" t="e" vm="85">
         <v>#VALUE!</v>
       </c>
       <c r="N175" t="s">
         <v>12</v>
       </c>
+      <c r="O175" t="s">
+        <v>67</v>
+      </c>
       <c r="P175" t="s">
         <v>20</v>
       </c>
@@ -40990,15 +41582,15 @@
         <v>1</v>
       </c>
       <c r="T175">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U175">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A176" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="C176" s="1">
         <v>45981</v>
@@ -41006,29 +41598,29 @@
       <c r="D176" t="s">
         <v>16</v>
       </c>
-      <c r="G176" t="s">
-        <v>265</v>
-      </c>
       <c r="H176" t="s">
         <v>25</v>
       </c>
       <c r="L176" t="s">
-        <v>264</v>
-      </c>
-      <c r="M176" t="e" vm="86">
+        <v>268</v>
+      </c>
+      <c r="M176" t="e" vm="70">
         <v>#VALUE!</v>
+      </c>
+      <c r="N176" t="s">
+        <v>28</v>
       </c>
       <c r="P176" t="s">
         <v>20</v>
       </c>
       <c r="Q176" s="1">
-        <v>45994</v>
+        <v>45992</v>
       </c>
       <c r="S176">
         <v>1</v>
       </c>
       <c r="T176">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U176">
         <v>0</v>
@@ -41036,72 +41628,72 @@
     </row>
     <row r="177" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A177" t="s">
-        <v>262</v>
+        <v>427</v>
       </c>
       <c r="C177" s="1">
         <v>45981</v>
       </c>
       <c r="D177" t="s">
-        <v>16</v>
+        <v>429</v>
+      </c>
+      <c r="E177" t="s">
+        <v>428</v>
       </c>
       <c r="H177" t="s">
         <v>25</v>
       </c>
       <c r="L177" t="s">
-        <v>261</v>
-      </c>
-      <c r="M177" t="e" vm="58">
+        <v>430</v>
+      </c>
+      <c r="M177" t="e" vm="41">
         <v>#VALUE!</v>
+      </c>
+      <c r="N177" t="s">
+        <v>12</v>
       </c>
       <c r="P177" t="s">
         <v>20</v>
       </c>
       <c r="Q177" s="1">
-        <v>45998</v>
+        <v>45992</v>
       </c>
       <c r="S177">
         <v>1</v>
       </c>
       <c r="T177">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U177">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="178" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A178" t="s">
-        <v>452</v>
-      </c>
-      <c r="B178" t="s">
-        <v>454</v>
+        <v>263</v>
       </c>
       <c r="C178" s="1">
         <v>45981</v>
       </c>
       <c r="D178" t="s">
-        <v>42</v>
-      </c>
-      <c r="E178" t="s">
-        <v>453</v>
+        <v>16</v>
+      </c>
+      <c r="G178" t="s">
+        <v>265</v>
       </c>
       <c r="H178" t="s">
         <v>25</v>
       </c>
       <c r="L178" t="s">
-        <v>455</v>
-      </c>
-      <c r="M178" t="e" vm="45">
+        <v>264</v>
+      </c>
+      <c r="M178" t="e" vm="86">
         <v>#VALUE!</v>
-      </c>
-      <c r="N178" t="s">
-        <v>12</v>
       </c>
       <c r="P178" t="s">
         <v>20</v>
       </c>
       <c r="Q178" s="1">
-        <v>46003</v>
+        <v>45994</v>
       </c>
       <c r="S178">
         <v>1</v>
@@ -41110,12 +41702,12 @@
         <v>0</v>
       </c>
       <c r="U178">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A179" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="C179" s="1">
         <v>45981</v>
@@ -41123,26 +41715,20 @@
       <c r="D179" t="s">
         <v>16</v>
       </c>
-      <c r="G179" s="8" t="s">
-        <v>254</v>
-      </c>
       <c r="H179" t="s">
         <v>25</v>
       </c>
       <c r="L179" t="s">
-        <v>252</v>
-      </c>
-      <c r="M179" t="e" vm="87">
+        <v>261</v>
+      </c>
+      <c r="M179" t="e" vm="58">
         <v>#VALUE!</v>
-      </c>
-      <c r="N179" t="s">
-        <v>28</v>
       </c>
       <c r="P179" t="s">
         <v>20</v>
       </c>
       <c r="Q179" s="1">
-        <v>46006</v>
+        <v>45998</v>
       </c>
       <c r="S179">
         <v>1</v>
@@ -41156,21 +41742,27 @@
     </row>
     <row r="180" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A180" t="s">
-        <v>257</v>
+        <v>452</v>
+      </c>
+      <c r="B180" t="s">
+        <v>454</v>
       </c>
       <c r="C180" s="1">
         <v>45981</v>
       </c>
       <c r="D180" t="s">
-        <v>16</v>
+        <v>42</v>
+      </c>
+      <c r="E180" t="s">
+        <v>453</v>
       </c>
       <c r="H180" t="s">
         <v>25</v>
       </c>
       <c r="L180" t="s">
-        <v>256</v>
-      </c>
-      <c r="M180" t="e" vm="88">
+        <v>455</v>
+      </c>
+      <c r="M180" t="e" vm="45">
         <v>#VALUE!</v>
       </c>
       <c r="N180" t="s">
@@ -41180,7 +41772,7 @@
         <v>20</v>
       </c>
       <c r="Q180" s="1">
-        <v>46022</v>
+        <v>46003</v>
       </c>
       <c r="S180">
         <v>1</v>
@@ -41189,12 +41781,12 @@
         <v>0</v>
       </c>
       <c r="U180">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="181" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A181" t="s">
-        <v>378</v>
+        <v>253</v>
       </c>
       <c r="C181" s="1">
         <v>45981</v>
@@ -41202,29 +41794,26 @@
       <c r="D181" t="s">
         <v>16</v>
       </c>
-      <c r="F181">
-        <v>1</v>
-      </c>
-      <c r="G181" t="s">
-        <v>251</v>
+      <c r="G181" s="8" t="s">
+        <v>254</v>
       </c>
       <c r="H181" t="s">
         <v>25</v>
       </c>
       <c r="L181" t="s">
-        <v>250</v>
-      </c>
-      <c r="M181" t="e" vm="67">
+        <v>252</v>
+      </c>
+      <c r="M181" t="e" vm="87">
         <v>#VALUE!</v>
       </c>
       <c r="N181" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="P181" t="s">
         <v>20</v>
       </c>
       <c r="Q181" s="1">
-        <v>46045</v>
+        <v>46006</v>
       </c>
       <c r="S181">
         <v>1</v>
@@ -41238,28 +41827,31 @@
     </row>
     <row r="182" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A182" t="s">
-        <v>207</v>
+        <v>257</v>
       </c>
       <c r="C182" s="1">
         <v>45981</v>
       </c>
       <c r="D182" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="H182" t="s">
         <v>25</v>
       </c>
-      <c r="L182" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="M182" t="e" vm="6">
+      <c r="L182" t="s">
+        <v>256</v>
+      </c>
+      <c r="M182" t="e" vm="88">
         <v>#VALUE!</v>
+      </c>
+      <c r="N182" t="s">
+        <v>12</v>
       </c>
       <c r="P182" t="s">
         <v>20</v>
       </c>
       <c r="Q182" s="1">
-        <v>46053</v>
+        <v>46022</v>
       </c>
       <c r="S182">
         <v>1</v>
@@ -41273,24 +41865,27 @@
     </row>
     <row r="183" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A183" t="s">
-        <v>479</v>
+        <v>378</v>
       </c>
       <c r="C183" s="1">
         <v>45981</v>
       </c>
       <c r="D183" t="s">
-        <v>42</v>
-      </c>
-      <c r="E183" t="s">
-        <v>480</v>
+        <v>16</v>
+      </c>
+      <c r="F183">
+        <v>1</v>
+      </c>
+      <c r="G183" t="s">
+        <v>251</v>
       </c>
       <c r="H183" t="s">
         <v>25</v>
       </c>
       <c r="L183" t="s">
-        <v>481</v>
-      </c>
-      <c r="M183" t="e" vm="89">
+        <v>250</v>
+      </c>
+      <c r="M183" t="e" vm="67">
         <v>#VALUE!</v>
       </c>
       <c r="N183" t="s">
@@ -41300,21 +41895,21 @@
         <v>20</v>
       </c>
       <c r="Q183" s="1">
-        <v>45996</v>
+        <v>46045</v>
       </c>
       <c r="S183">
         <v>1</v>
       </c>
       <c r="T183">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U183">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A184" t="s">
-        <v>485</v>
+        <v>207</v>
       </c>
       <c r="C184" s="1">
         <v>45981</v>
@@ -41322,40 +41917,34 @@
       <c r="D184" t="s">
         <v>42</v>
       </c>
-      <c r="E184" t="s">
-        <v>486</v>
-      </c>
       <c r="H184" t="s">
         <v>25</v>
       </c>
-      <c r="L184" t="s">
-        <v>487</v>
-      </c>
-      <c r="M184" t="e" vm="90">
+      <c r="L184" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="M184" t="e" vm="6">
         <v>#VALUE!</v>
-      </c>
-      <c r="N184" t="s">
-        <v>490</v>
       </c>
       <c r="P184" t="s">
         <v>20</v>
       </c>
       <c r="Q184" s="1">
-        <v>45688</v>
+        <v>46053</v>
       </c>
       <c r="S184">
         <v>1</v>
       </c>
       <c r="T184">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U184">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A185" t="s">
-        <v>501</v>
+        <v>479</v>
       </c>
       <c r="C185" s="1">
         <v>45981</v>
@@ -41364,15 +41953,15 @@
         <v>42</v>
       </c>
       <c r="E185" t="s">
-        <v>502</v>
+        <v>480</v>
       </c>
       <c r="H185" t="s">
         <v>25</v>
       </c>
       <c r="L185" t="s">
-        <v>503</v>
-      </c>
-      <c r="M185" t="e" vm="91">
+        <v>481</v>
+      </c>
+      <c r="M185" t="e" vm="89">
         <v>#VALUE!</v>
       </c>
       <c r="N185" t="s">
@@ -41382,7 +41971,7 @@
         <v>20</v>
       </c>
       <c r="Q185" s="1">
-        <v>46022</v>
+        <v>45996</v>
       </c>
       <c r="S185">
         <v>1</v>
@@ -41395,8 +41984,8 @@
       </c>
     </row>
     <row r="186" spans="1:21" x14ac:dyDescent="0.4">
-      <c r="A186" s="4" t="s">
-        <v>504</v>
+      <c r="A186" t="s">
+        <v>485</v>
       </c>
       <c r="C186" s="1">
         <v>45981</v>
@@ -41404,40 +41993,40 @@
       <c r="D186" t="s">
         <v>42</v>
       </c>
-      <c r="F186">
-        <v>1</v>
+      <c r="E186" t="s">
+        <v>486</v>
       </c>
       <c r="H186" t="s">
         <v>25</v>
       </c>
       <c r="L186" t="s">
-        <v>505</v>
-      </c>
-      <c r="M186" t="e" vm="85">
+        <v>487</v>
+      </c>
+      <c r="M186" t="e" vm="90">
         <v>#VALUE!</v>
       </c>
       <c r="N186" t="s">
-        <v>12</v>
+        <v>490</v>
       </c>
       <c r="P186" t="s">
         <v>20</v>
       </c>
       <c r="Q186" s="1">
-        <v>45997</v>
+        <v>45688</v>
       </c>
       <c r="S186">
         <v>1</v>
       </c>
       <c r="T186">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U186">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="187" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A187" t="s">
-        <v>576</v>
+        <v>501</v>
       </c>
       <c r="C187" s="1">
         <v>45981</v>
@@ -41445,13 +42034,16 @@
       <c r="D187" t="s">
         <v>42</v>
       </c>
+      <c r="E187" t="s">
+        <v>502</v>
+      </c>
       <c r="H187" t="s">
         <v>25</v>
       </c>
       <c r="L187" t="s">
-        <v>575</v>
-      </c>
-      <c r="M187" t="e" vm="89">
+        <v>503</v>
+      </c>
+      <c r="M187" t="e" vm="91">
         <v>#VALUE!</v>
       </c>
       <c r="N187" t="s">
@@ -41461,7 +42053,7 @@
         <v>20</v>
       </c>
       <c r="Q187" s="1">
-        <v>45992</v>
+        <v>46022</v>
       </c>
       <c r="S187">
         <v>1</v>
@@ -41474,8 +42066,8 @@
       </c>
     </row>
     <row r="188" spans="1:21" x14ac:dyDescent="0.4">
-      <c r="A188" t="s">
-        <v>582</v>
+      <c r="A188" s="4" t="s">
+        <v>504</v>
       </c>
       <c r="C188" s="1">
         <v>45981</v>
@@ -41483,16 +42075,16 @@
       <c r="D188" t="s">
         <v>42</v>
       </c>
-      <c r="E188" t="s">
-        <v>583</v>
+      <c r="F188">
+        <v>1</v>
       </c>
       <c r="H188" t="s">
         <v>25</v>
       </c>
       <c r="L188" t="s">
-        <v>581</v>
-      </c>
-      <c r="M188" t="e" vm="72">
+        <v>505</v>
+      </c>
+      <c r="M188" t="e" vm="85">
         <v>#VALUE!</v>
       </c>
       <c r="N188" t="s">
@@ -41502,24 +42094,21 @@
         <v>20</v>
       </c>
       <c r="Q188" s="1">
-        <v>45992</v>
+        <v>45997</v>
       </c>
       <c r="S188">
         <v>1</v>
       </c>
       <c r="T188">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U188">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A189" t="s">
-        <v>586</v>
-      </c>
-      <c r="B189" t="s">
-        <v>589</v>
+        <v>576</v>
       </c>
       <c r="C189" s="1">
         <v>45981</v>
@@ -41527,16 +42116,13 @@
       <c r="D189" t="s">
         <v>42</v>
       </c>
-      <c r="E189" t="s">
-        <v>587</v>
-      </c>
       <c r="H189" t="s">
         <v>25</v>
       </c>
       <c r="L189" t="s">
-        <v>588</v>
-      </c>
-      <c r="M189" t="e" vm="81">
+        <v>575</v>
+      </c>
+      <c r="M189" t="e" vm="89">
         <v>#VALUE!</v>
       </c>
       <c r="N189" t="s">
@@ -41546,7 +42132,7 @@
         <v>20</v>
       </c>
       <c r="Q189" s="1">
-        <v>45991</v>
+        <v>45992</v>
       </c>
       <c r="S189">
         <v>1</v>
@@ -41560,7 +42146,7 @@
     </row>
     <row r="190" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A190" t="s">
-        <v>591</v>
+        <v>582</v>
       </c>
       <c r="C190" s="1">
         <v>45981</v>
@@ -41569,15 +42155,15 @@
         <v>42</v>
       </c>
       <c r="E190" t="s">
-        <v>592</v>
+        <v>583</v>
       </c>
       <c r="H190" t="s">
         <v>25</v>
       </c>
       <c r="L190" t="s">
-        <v>590</v>
-      </c>
-      <c r="M190" t="e" vm="81">
+        <v>581</v>
+      </c>
+      <c r="M190" t="e" vm="72">
         <v>#VALUE!</v>
       </c>
       <c r="N190" t="s">
@@ -41587,13 +42173,13 @@
         <v>20</v>
       </c>
       <c r="Q190" s="1">
-        <v>46006</v>
+        <v>45992</v>
       </c>
       <c r="S190">
         <v>1</v>
       </c>
       <c r="T190">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U190">
         <v>1</v>
@@ -41601,10 +42187,10 @@
     </row>
     <row r="191" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A191" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="B191" t="s">
-        <v>596</v>
+        <v>589</v>
       </c>
       <c r="C191" s="1">
         <v>45981</v>
@@ -41613,13 +42199,13 @@
         <v>42</v>
       </c>
       <c r="E191" t="s">
-        <v>594</v>
+        <v>587</v>
       </c>
       <c r="H191" t="s">
         <v>25</v>
       </c>
       <c r="L191" t="s">
-        <v>595</v>
+        <v>588</v>
       </c>
       <c r="M191" t="e" vm="81">
         <v>#VALUE!</v>
@@ -41631,13 +42217,13 @@
         <v>20</v>
       </c>
       <c r="Q191" s="1">
-        <v>45992</v>
+        <v>45991</v>
       </c>
       <c r="S191">
         <v>1</v>
       </c>
       <c r="T191">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U191">
         <v>1</v>
@@ -41645,10 +42231,7 @@
     </row>
     <row r="192" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A192" t="s">
-        <v>604</v>
-      </c>
-      <c r="B192" t="s">
-        <v>606</v>
+        <v>591</v>
       </c>
       <c r="C192" s="1">
         <v>45981</v>
@@ -41657,24 +42240,42 @@
         <v>42</v>
       </c>
       <c r="E192" t="s">
-        <v>607</v>
+        <v>592</v>
       </c>
       <c r="H192" t="s">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="L192" t="s">
-        <v>605</v>
-      </c>
-      <c r="M192" t="e" vm="2">
+        <v>590</v>
+      </c>
+      <c r="M192" t="e" vm="81">
         <v>#VALUE!</v>
       </c>
+      <c r="N192" t="s">
+        <v>12</v>
+      </c>
+      <c r="P192" t="s">
+        <v>20</v>
+      </c>
       <c r="Q192" s="1">
-        <v>45992</v>
+        <v>46006</v>
+      </c>
+      <c r="S192">
+        <v>1</v>
+      </c>
+      <c r="T192">
+        <v>0</v>
+      </c>
+      <c r="U192">
+        <v>1</v>
       </c>
     </row>
     <row r="193" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A193" t="s">
-        <v>610</v>
+        <v>593</v>
+      </c>
+      <c r="B193" t="s">
+        <v>596</v>
       </c>
       <c r="C193" s="1">
         <v>45981</v>
@@ -41683,15 +42284,15 @@
         <v>42</v>
       </c>
       <c r="E193" t="s">
-        <v>611</v>
+        <v>594</v>
       </c>
       <c r="H193" t="s">
         <v>25</v>
       </c>
       <c r="L193" t="s">
-        <v>609</v>
-      </c>
-      <c r="M193" t="e" vm="20">
+        <v>595</v>
+      </c>
+      <c r="M193" t="e" vm="81">
         <v>#VALUE!</v>
       </c>
       <c r="N193" t="s">
@@ -41701,13 +42302,13 @@
         <v>20</v>
       </c>
       <c r="Q193" s="1">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="S193">
         <v>1</v>
       </c>
       <c r="T193">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U193">
         <v>1</v>
@@ -41715,69 +42316,63 @@
     </row>
     <row r="194" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A194" t="s">
-        <v>358</v>
+        <v>604</v>
+      </c>
+      <c r="B194" t="s">
+        <v>606</v>
       </c>
       <c r="C194" s="1">
-        <v>45986</v>
+        <v>45981</v>
       </c>
       <c r="D194" t="s">
-        <v>360</v>
+        <v>42</v>
+      </c>
+      <c r="E194" t="s">
+        <v>607</v>
       </c>
       <c r="H194" t="s">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="L194" t="s">
-        <v>357</v>
-      </c>
-      <c r="M194" t="e" vm="15">
+        <v>605</v>
+      </c>
+      <c r="M194" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="N194" t="s">
-        <v>12</v>
-      </c>
-      <c r="P194" t="s">
-        <v>20</v>
-      </c>
       <c r="Q194" s="1">
-        <v>46006</v>
-      </c>
-      <c r="S194">
-        <v>1</v>
-      </c>
-      <c r="T194">
-        <v>1</v>
-      </c>
-      <c r="U194">
-        <v>1</v>
+        <v>45992</v>
       </c>
     </row>
     <row r="195" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A195" t="s">
-        <v>525</v>
+        <v>610</v>
       </c>
       <c r="C195" s="1">
-        <v>45986</v>
+        <v>45981</v>
       </c>
       <c r="D195" t="s">
         <v>42</v>
       </c>
+      <c r="E195" t="s">
+        <v>611</v>
+      </c>
       <c r="H195" t="s">
         <v>25</v>
       </c>
       <c r="L195" t="s">
-        <v>524</v>
-      </c>
-      <c r="M195" t="e" vm="36">
+        <v>609</v>
+      </c>
+      <c r="M195" t="e" vm="20">
         <v>#VALUE!</v>
       </c>
       <c r="N195" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="P195" t="s">
         <v>20</v>
       </c>
       <c r="Q195" s="1">
-        <v>45991</v>
+        <v>45989</v>
       </c>
       <c r="S195">
         <v>1</v>
@@ -41786,42 +42381,51 @@
         <v>1</v>
       </c>
       <c r="U195">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="196" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A196" t="s">
-        <v>541</v>
+        <v>641</v>
+      </c>
+      <c r="B196" t="s">
+        <v>644</v>
       </c>
       <c r="C196" s="1">
-        <v>45986</v>
+        <v>45981</v>
       </c>
       <c r="D196" t="s">
-        <v>42</v>
+        <v>642</v>
       </c>
       <c r="H196" t="s">
         <v>25</v>
       </c>
+      <c r="J196" t="s">
+        <v>247</v>
+      </c>
+      <c r="K196" s="1">
+        <v>45992</v>
+      </c>
       <c r="L196" t="s">
-        <v>542</v>
-      </c>
-      <c r="M196" t="e" vm="23">
+        <v>643</v>
+      </c>
+      <c r="M196" t="e" vm="92">
         <v>#VALUE!</v>
       </c>
       <c r="N196" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="P196" t="s">
         <v>20</v>
       </c>
       <c r="Q196" s="1">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="S196">
         <v>1</v>
       </c>
       <c r="T196">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U196">
         <v>1</v>
@@ -41829,21 +42433,24 @@
     </row>
     <row r="197" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A197" t="s">
-        <v>548</v>
+        <v>647</v>
+      </c>
+      <c r="B197" t="s">
+        <v>646</v>
       </c>
       <c r="C197" s="1">
-        <v>45986</v>
+        <v>45981</v>
       </c>
       <c r="D197" t="s">
-        <v>547</v>
+        <v>648</v>
       </c>
       <c r="H197" t="s">
         <v>25</v>
       </c>
       <c r="L197" t="s">
-        <v>546</v>
-      </c>
-      <c r="M197" t="e" vm="13">
+        <v>645</v>
+      </c>
+      <c r="M197" t="e" vm="75">
         <v>#VALUE!</v>
       </c>
       <c r="N197" t="s">
@@ -41853,7 +42460,7 @@
         <v>20</v>
       </c>
       <c r="Q197" s="1">
-        <v>45992</v>
+        <v>46022</v>
       </c>
       <c r="S197">
         <v>1</v>
@@ -41867,37 +42474,40 @@
     </row>
     <row r="198" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A198" t="s">
-        <v>418</v>
+        <v>649</v>
+      </c>
+      <c r="B198" t="s">
+        <v>652</v>
       </c>
       <c r="C198" s="1">
-        <v>45992</v>
+        <v>45981</v>
       </c>
       <c r="D198" t="s">
-        <v>42</v>
+        <v>650</v>
       </c>
       <c r="H198" t="s">
         <v>25</v>
       </c>
       <c r="L198" t="s">
-        <v>419</v>
-      </c>
-      <c r="M198" t="e" vm="92">
+        <v>651</v>
+      </c>
+      <c r="M198" t="e" vm="93">
         <v>#VALUE!</v>
       </c>
       <c r="N198" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="P198" t="s">
         <v>20</v>
       </c>
       <c r="Q198" s="1">
-        <v>45688</v>
+        <v>45992</v>
       </c>
       <c r="S198">
         <v>1</v>
       </c>
       <c r="T198">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U198">
         <v>0</v>
@@ -41905,28 +42515,28 @@
     </row>
     <row r="199" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A199" t="s">
-        <v>572</v>
+        <v>653</v>
       </c>
       <c r="C199" s="1">
-        <v>45992</v>
-      </c>
-      <c r="D199" t="s">
-        <v>573</v>
+        <v>45981</v>
+      </c>
+      <c r="D199" s="2" t="s">
+        <v>655</v>
       </c>
       <c r="H199" t="s">
         <v>25</v>
       </c>
       <c r="L199" t="s">
-        <v>574</v>
-      </c>
-      <c r="M199" t="e" vm="2">
+        <v>656</v>
+      </c>
+      <c r="M199" t="e" vm="11">
         <v>#VALUE!</v>
       </c>
       <c r="Q199" s="1">
-        <v>46053</v>
+        <v>45991</v>
       </c>
       <c r="S199">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T199">
         <v>0</v>
@@ -41936,70 +42546,82 @@
       </c>
     </row>
     <row r="200" spans="1:21" x14ac:dyDescent="0.4">
-      <c r="A200" t="s">
-        <v>618</v>
+      <c r="A200" s="4" t="s">
+        <v>663</v>
+      </c>
+      <c r="B200" t="s">
+        <v>664</v>
       </c>
       <c r="C200" s="1">
-        <v>45992</v>
+        <v>45981</v>
       </c>
       <c r="D200" t="s">
-        <v>617</v>
+        <v>16</v>
+      </c>
+      <c r="F200">
+        <v>3</v>
+      </c>
+      <c r="G200" s="2" t="s">
+        <v>665</v>
       </c>
       <c r="H200" t="s">
         <v>25</v>
       </c>
+      <c r="J200" t="s">
+        <v>247</v>
+      </c>
+      <c r="K200" s="1">
+        <v>45992</v>
+      </c>
       <c r="L200" t="s">
-        <v>616</v>
-      </c>
-      <c r="M200" t="e" vm="93">
+        <v>666</v>
+      </c>
+      <c r="M200" t="e" vm="56">
         <v>#VALUE!</v>
       </c>
       <c r="N200" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="P200" t="s">
         <v>20</v>
       </c>
       <c r="Q200" s="1">
-        <v>46006</v>
+        <v>45992</v>
       </c>
       <c r="S200">
         <v>1</v>
       </c>
       <c r="T200">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U200">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="201" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A201" t="s">
-        <v>532</v>
-      </c>
-      <c r="B201" t="s">
-        <v>181</v>
+        <v>670</v>
       </c>
       <c r="C201" s="1">
-        <v>46023</v>
+        <v>45981</v>
       </c>
       <c r="D201" t="s">
-        <v>533</v>
+        <v>16</v>
       </c>
       <c r="H201" t="s">
         <v>25</v>
       </c>
       <c r="L201" t="s">
-        <v>534</v>
-      </c>
-      <c r="M201" t="e" vm="94">
+        <v>671</v>
+      </c>
+      <c r="M201" t="e" vm="86">
         <v>#VALUE!</v>
       </c>
-      <c r="N201" t="s">
-        <v>21</v>
+      <c r="P201" t="s">
+        <v>20</v>
       </c>
       <c r="Q201" s="1">
-        <v>46041</v>
+        <v>45992</v>
       </c>
       <c r="S201">
         <v>1</v>
@@ -42008,26 +42630,26 @@
         <v>0</v>
       </c>
       <c r="U201">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="202" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A202" t="s">
-        <v>258</v>
+        <v>358</v>
+      </c>
+      <c r="C202" s="1">
+        <v>45986</v>
       </c>
       <c r="D202" t="s">
-        <v>16</v>
-      </c>
-      <c r="E202" s="2" t="s">
-        <v>260</v>
+        <v>360</v>
       </c>
       <c r="H202" t="s">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="L202" t="s">
-        <v>259</v>
-      </c>
-      <c r="M202" t="e" vm="28">
+        <v>357</v>
+      </c>
+      <c r="M202" t="e" vm="15">
         <v>#VALUE!</v>
       </c>
       <c r="N202" t="s">
@@ -42036,67 +42658,444 @@
       <c r="P202" t="s">
         <v>20</v>
       </c>
+      <c r="Q202" s="1">
+        <v>46006</v>
+      </c>
       <c r="S202">
+        <v>1</v>
+      </c>
+      <c r="T202">
+        <v>1</v>
+      </c>
+      <c r="U202">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A203" t="s">
+        <v>525</v>
+      </c>
+      <c r="C203" s="1">
+        <v>45986</v>
+      </c>
+      <c r="D203" t="s">
+        <v>42</v>
+      </c>
+      <c r="H203" t="s">
+        <v>25</v>
+      </c>
+      <c r="L203" t="s">
+        <v>524</v>
+      </c>
+      <c r="M203" t="e" vm="36">
+        <v>#VALUE!</v>
+      </c>
+      <c r="N203" t="s">
+        <v>28</v>
+      </c>
+      <c r="P203" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q203" s="1">
+        <v>45991</v>
+      </c>
+      <c r="S203">
+        <v>1</v>
+      </c>
+      <c r="T203">
+        <v>1</v>
+      </c>
+      <c r="U203">
         <v>0</v>
       </c>
-      <c r="T202">
+    </row>
+    <row r="204" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A204" t="s">
+        <v>541</v>
+      </c>
+      <c r="C204" s="1">
+        <v>45986</v>
+      </c>
+      <c r="D204" t="s">
+        <v>42</v>
+      </c>
+      <c r="H204" t="s">
+        <v>25</v>
+      </c>
+      <c r="L204" t="s">
+        <v>542</v>
+      </c>
+      <c r="M204" t="e" vm="23">
+        <v>#VALUE!</v>
+      </c>
+      <c r="N204" t="s">
+        <v>12</v>
+      </c>
+      <c r="P204" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q204" s="1">
+        <v>46022</v>
+      </c>
+      <c r="S204">
+        <v>1</v>
+      </c>
+      <c r="T204">
+        <v>1</v>
+      </c>
+      <c r="U204">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A205" t="s">
+        <v>548</v>
+      </c>
+      <c r="C205" s="1">
+        <v>45986</v>
+      </c>
+      <c r="D205" t="s">
+        <v>547</v>
+      </c>
+      <c r="H205" t="s">
+        <v>25</v>
+      </c>
+      <c r="L205" t="s">
+        <v>546</v>
+      </c>
+      <c r="M205" t="e" vm="13">
+        <v>#VALUE!</v>
+      </c>
+      <c r="N205" t="s">
+        <v>12</v>
+      </c>
+      <c r="P205" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q205" s="1">
+        <v>45992</v>
+      </c>
+      <c r="S205">
+        <v>1</v>
+      </c>
+      <c r="T205">
         <v>0</v>
       </c>
-      <c r="U202">
+      <c r="U205">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A206" t="s">
+        <v>418</v>
+      </c>
+      <c r="C206" s="1">
+        <v>45992</v>
+      </c>
+      <c r="D206" t="s">
+        <v>42</v>
+      </c>
+      <c r="H206" t="s">
+        <v>25</v>
+      </c>
+      <c r="L206" t="s">
+        <v>419</v>
+      </c>
+      <c r="M206" t="e" vm="94">
+        <v>#VALUE!</v>
+      </c>
+      <c r="N206" t="s">
+        <v>28</v>
+      </c>
+      <c r="P206" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q206" s="1">
+        <v>45688</v>
+      </c>
+      <c r="S206">
+        <v>1</v>
+      </c>
+      <c r="T206">
+        <v>1</v>
+      </c>
+      <c r="U206">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A207" t="s">
+        <v>572</v>
+      </c>
+      <c r="C207" s="1">
+        <v>45992</v>
+      </c>
+      <c r="D207" t="s">
+        <v>573</v>
+      </c>
+      <c r="H207" t="s">
+        <v>25</v>
+      </c>
+      <c r="L207" t="s">
+        <v>574</v>
+      </c>
+      <c r="M207" t="e" vm="2">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q207" s="1">
+        <v>46053</v>
+      </c>
+      <c r="S207">
+        <v>0</v>
+      </c>
+      <c r="T207">
+        <v>0</v>
+      </c>
+      <c r="U207">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A208" t="s">
+        <v>618</v>
+      </c>
+      <c r="C208" s="1">
+        <v>45992</v>
+      </c>
+      <c r="D208" t="s">
+        <v>617</v>
+      </c>
+      <c r="H208" t="s">
+        <v>25</v>
+      </c>
+      <c r="L208" t="s">
+        <v>616</v>
+      </c>
+      <c r="M208" t="e" vm="95">
+        <v>#VALUE!</v>
+      </c>
+      <c r="N208" t="s">
+        <v>12</v>
+      </c>
+      <c r="P208" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q208" s="1">
+        <v>46006</v>
+      </c>
+      <c r="S208">
+        <v>1</v>
+      </c>
+      <c r="T208">
+        <v>1</v>
+      </c>
+      <c r="U208">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A209" t="s">
+        <v>660</v>
+      </c>
+      <c r="C209" s="1">
+        <v>45992</v>
+      </c>
+      <c r="D209" t="s">
+        <v>16</v>
+      </c>
+      <c r="H209" t="s">
+        <v>25</v>
+      </c>
+      <c r="L209" t="s">
+        <v>659</v>
+      </c>
+      <c r="M209" t="e" vm="95">
+        <v>#VALUE!</v>
+      </c>
+      <c r="N209" t="s">
+        <v>12</v>
+      </c>
+      <c r="P209" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q209" s="1">
+        <v>46006</v>
+      </c>
+      <c r="S209">
+        <v>1</v>
+      </c>
+      <c r="T209">
+        <v>0</v>
+      </c>
+      <c r="U209">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A210" t="s">
+        <v>667</v>
+      </c>
+      <c r="C210" s="1">
+        <v>46011</v>
+      </c>
+      <c r="D210" t="s">
+        <v>16</v>
+      </c>
+      <c r="G210" t="s">
+        <v>669</v>
+      </c>
+      <c r="H210" t="s">
+        <v>25</v>
+      </c>
+      <c r="L210" t="s">
+        <v>668</v>
+      </c>
+      <c r="M210" t="e" vm="38">
+        <v>#VALUE!</v>
+      </c>
+      <c r="N210" t="s">
+        <v>28</v>
+      </c>
+      <c r="P210" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q210" s="1">
+        <v>46037</v>
+      </c>
+      <c r="S210">
+        <v>1</v>
+      </c>
+      <c r="T210">
+        <v>0</v>
+      </c>
+      <c r="U210">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A211" t="s">
+        <v>532</v>
+      </c>
+      <c r="B211" t="s">
+        <v>181</v>
+      </c>
+      <c r="C211" s="1">
+        <v>46023</v>
+      </c>
+      <c r="D211" t="s">
+        <v>533</v>
+      </c>
+      <c r="H211" t="s">
+        <v>25</v>
+      </c>
+      <c r="L211" t="s">
+        <v>534</v>
+      </c>
+      <c r="M211" t="e" vm="96">
+        <v>#VALUE!</v>
+      </c>
+      <c r="N211" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q211" s="1">
+        <v>46041</v>
+      </c>
+      <c r="S211">
+        <v>1</v>
+      </c>
+      <c r="T211">
+        <v>0</v>
+      </c>
+      <c r="U211">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A212" t="s">
+        <v>258</v>
+      </c>
+      <c r="D212" t="s">
+        <v>16</v>
+      </c>
+      <c r="E212" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="H212" t="s">
+        <v>99</v>
+      </c>
+      <c r="L212" t="s">
+        <v>259</v>
+      </c>
+      <c r="M212" t="e" vm="28">
+        <v>#VALUE!</v>
+      </c>
+      <c r="N212" t="s">
+        <v>12</v>
+      </c>
+      <c r="P212" t="s">
+        <v>20</v>
+      </c>
+      <c r="S212">
+        <v>0</v>
+      </c>
+      <c r="T212">
+        <v>0</v>
+      </c>
+      <c r="U212">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:U19" xr:uid="{F7772053-9363-CA4A-A53F-040B7C700753}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U202">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U212">
       <sortCondition ref="C1:C19"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="115" priority="13"/>
+  <conditionalFormatting sqref="A1:A208 A210:A1048576">
+    <cfRule type="duplicateValues" dxfId="135" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:A22">
-    <cfRule type="duplicateValues" dxfId="114" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="134" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A61">
-    <cfRule type="duplicateValues" dxfId="113" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="133" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:H1048576">
-    <cfRule type="containsText" dxfId="112" priority="5" operator="containsText" text="closed">
+    <cfRule type="containsText" dxfId="132" priority="5" operator="containsText" text="closed">
       <formula>NOT(ISERROR(SEARCH("closed",H1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="111" priority="6" operator="containsText" text="abandoned">
+    <cfRule type="containsText" dxfId="131" priority="6" operator="containsText" text="abandoned">
       <formula>NOT(ISERROR(SEARCH("abandoned",H1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="110" priority="8" operator="containsText" text="late app">
+    <cfRule type="containsText" dxfId="130" priority="8" operator="containsText" text="late app">
       <formula>NOT(ISERROR(SEARCH("late app",H1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N78:N80 N83:N89 N92:N112 N115:N124 N126:N181 Q136 Q153 Q159 Q166 P168 P170:P181 Q173 Q178 H1:I1 P87:P166 H2:K1048576 P183:P191 N183:N202 P193:P202">
-    <cfRule type="containsText" dxfId="109" priority="11" operator="containsText" text="completed">
+  <conditionalFormatting sqref="H2:K1048576 N78:N80 N83:N89 P87:P166 N92:N112 N115:N124 N126:N181 Q136 Q153 Q159 Q166 P168 P170:P181 Q173 Q178 P183:P191 N183:N205 P193:P205 P207:P212 N208:N211 H1:I1">
+    <cfRule type="containsText" dxfId="129" priority="11" operator="containsText" text="completed">
       <formula>NOT(ISERROR(SEARCH("completed",H1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N78:N80 N83:N89 N92:N112 N115:N124 N126:N181 Q136 Q153 Q159 Q166 P168 P170:P181 Q173 Q178 P87:P166 J1:K1048576 P183:P191 N183:N202 P193:P202">
-    <cfRule type="containsText" dxfId="108" priority="9" operator="containsText" text="NO">
+  <conditionalFormatting sqref="I1:I1048576">
+    <cfRule type="containsText" dxfId="128" priority="1" operator="containsText" text="offer">
+      <formula>NOT(ISERROR(SEARCH("offer",I1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="127" priority="2" operator="containsText" text="fly out">
+      <formula>NOT(ISERROR(SEARCH("fly out",I1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="126" priority="3" operator="containsText" text="interview">
+      <formula>NOT(ISERROR(SEARCH("interview",I1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="125" priority="4" operator="containsText" text="rejected">
+      <formula>NOT(ISERROR(SEARCH("rejected",I1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J1:K1048576 N78:N80 N83:N89 P87:P166 N92:N112 N115:N124 N126:N181 Q136 Q153 Q159 Q166 P168 P170:P181 Q173 Q178 P183:P191 N183:N205 P193:P205 P207:P212 N208:N211">
+    <cfRule type="containsText" dxfId="124" priority="9" operator="containsText" text="NO">
       <formula>NOT(ISERROR(SEARCH("NO",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="107" priority="10" operator="containsText" text="YES">
+    <cfRule type="containsText" dxfId="123" priority="10" operator="containsText" text="YES">
       <formula>NOT(ISERROR(SEARCH("YES",J1)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="containsText" dxfId="106" priority="1" operator="containsText" text="offer">
-      <formula>NOT(ISERROR(SEARCH("offer",I1)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="105" priority="2" operator="containsText" text="fly out">
-      <formula>NOT(ISERROR(SEARCH("fly out",I1)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="104" priority="3" operator="containsText" text="interview">
-      <formula>NOT(ISERROR(SEARCH("interview",I1)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="103" priority="4" operator="containsText" text="rejected">
-      <formula>NOT(ISERROR(SEARCH("rejected",I1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
@@ -42132,7 +43131,7 @@
     <hyperlink ref="E15" r:id="rId30" xr:uid="{3CBBC435-61F9-034D-A9A0-B71AD9A7CCE6}"/>
     <hyperlink ref="L56" r:id="rId31" xr:uid="{115DEFD3-6759-7C49-87C4-663720AFC0F3}"/>
     <hyperlink ref="L73" r:id="rId32" xr:uid="{B568129A-4C88-5D42-B367-90B46CA6E8A2}"/>
-    <hyperlink ref="L150" r:id="rId33" xr:uid="{F3D886C1-081B-8F41-85EF-4C299E91BBDA}"/>
+    <hyperlink ref="L152" r:id="rId33" xr:uid="{F3D886C1-081B-8F41-85EF-4C299E91BBDA}"/>
     <hyperlink ref="L38" r:id="rId34" xr:uid="{14B04134-DF47-DA43-BB43-BA8C1185A50E}"/>
     <hyperlink ref="L42" r:id="rId35" display="https://www.upf.edu/" xr:uid="{F90D7817-7AA8-1C4B-8992-6FF849FBECCA}"/>
     <hyperlink ref="G9" r:id="rId36" display="mailto:ferran.mane@urv.cat" xr:uid="{DFACBA33-6641-9A4D-B406-DC2FCC993612}"/>
@@ -42140,8 +43139,8 @@
     <hyperlink ref="L110" r:id="rId38" xr:uid="{6E0CC17F-E103-7C43-850C-F0FC0B9A5278}"/>
     <hyperlink ref="L102" r:id="rId39" xr:uid="{58693CCE-AFC3-AF44-BB76-62CF466ED6EA}"/>
     <hyperlink ref="L46" r:id="rId40" xr:uid="{FC0BA615-15C1-F64A-BC32-60929732DD9E}"/>
-    <hyperlink ref="L149" r:id="rId41" xr:uid="{14CF4841-2A37-9044-AE5B-371378C8D3B9}"/>
-    <hyperlink ref="L151" r:id="rId42" xr:uid="{2E048D46-3518-2C4A-B061-479244E61709}"/>
+    <hyperlink ref="L151" r:id="rId41" xr:uid="{14CF4841-2A37-9044-AE5B-371378C8D3B9}"/>
+    <hyperlink ref="L153" r:id="rId42" xr:uid="{2E048D46-3518-2C4A-B061-479244E61709}"/>
     <hyperlink ref="L19" r:id="rId43" xr:uid="{BA26908B-8596-4249-946E-03161834E8E5}"/>
     <hyperlink ref="L60" r:id="rId44" xr:uid="{00B6A218-D9E8-3D4A-B0D7-CBDFA98EE6F3}"/>
     <hyperlink ref="D11" r:id="rId45" xr:uid="{8C412634-0F9A-E946-9A3F-CA7F4E73C3AB}"/>
@@ -42150,14 +43149,14 @@
     <hyperlink ref="D6" r:id="rId48" xr:uid="{13514A0D-2C0E-5340-8AA2-077046FFB755}"/>
     <hyperlink ref="D40" r:id="rId49" xr:uid="{DE8E5F09-1A02-F148-8539-188D3ED5C9F4}"/>
     <hyperlink ref="D36" r:id="rId50" xr:uid="{84827B93-5057-1D4A-AD4E-C9D52677D58A}"/>
-    <hyperlink ref="L165" r:id="rId51" location="/admin" xr:uid="{23CE2AD2-6E21-4241-978C-EFA7C5825B0A}"/>
-    <hyperlink ref="G165" r:id="rId52" tooltip="https://www.pierrebiscaye.com/" display="https://nam10.safelinks.protection.outlook.com/?url=https%3A%2F%2Fwww.pierrebiscaye.com%2F&amp;data=05%7C02%7Cgonzalezjj%40mail.smu.edu%7Cf17b24ecae9644d5351608de0b2d3d88%7C0f450f2e334f4bada85c9adf76051d8b%7C0%7C0%7C638960486114093769%7CUnknown%7CTWFpbGZsb3d8eyJFbXB0eU1hcGkiOnRydWUsIlYiOiIwLjAuMDAwMCIsIlAiOiJXaW4zMiIsIkFOIjoiTWFpbCIsIldUIjoyfQ%3D%3D%7C0%7C%7C%7C&amp;sdata=G3tT9q0mvtmAIBnq6zF0gIXzpLRerNt4Zfffdrm2A2E%3D&amp;reserved=0" xr:uid="{B11A9620-8D5F-6A4D-A59A-6B6DCAC23722}"/>
-    <hyperlink ref="L172" r:id="rId53" xr:uid="{7C2D96E2-AEFB-4140-A2EF-40B86E5741B1}"/>
+    <hyperlink ref="L167" r:id="rId51" location="/admin" xr:uid="{23CE2AD2-6E21-4241-978C-EFA7C5825B0A}"/>
+    <hyperlink ref="G167" r:id="rId52" tooltip="https://www.pierrebiscaye.com/" display="https://nam10.safelinks.protection.outlook.com/?url=https%3A%2F%2Fwww.pierrebiscaye.com%2F&amp;data=05%7C02%7Cgonzalezjj%40mail.smu.edu%7Cf17b24ecae9644d5351608de0b2d3d88%7C0f450f2e334f4bada85c9adf76051d8b%7C0%7C0%7C638960486114093769%7CUnknown%7CTWFpbGZsb3d8eyJFbXB0eU1hcGkiOnRydWUsIlYiOiIwLjAuMDAwMCIsIlAiOiJXaW4zMiIsIkFOIjoiTWFpbCIsIldUIjoyfQ%3D%3D%7C0%7C%7C%7C&amp;sdata=G3tT9q0mvtmAIBnq6zF0gIXzpLRerNt4Zfffdrm2A2E%3D&amp;reserved=0" xr:uid="{B11A9620-8D5F-6A4D-A59A-6B6DCAC23722}"/>
+    <hyperlink ref="L174" r:id="rId53" xr:uid="{7C2D96E2-AEFB-4140-A2EF-40B86E5741B1}"/>
     <hyperlink ref="L26" r:id="rId54" xr:uid="{35FAF041-CBFF-8A48-A4B3-B97381C00102}"/>
     <hyperlink ref="L74" r:id="rId55" xr:uid="{2D03A0F6-26F5-B24A-B91A-14D38A06B992}"/>
     <hyperlink ref="E74" r:id="rId56" display="https://academicjobsonline.org/ajo/jobs/30626" xr:uid="{46416258-D6E3-7B41-9A73-A9A4F4E6BB34}"/>
-    <hyperlink ref="L146" r:id="rId57" xr:uid="{FEED16DA-CB82-0044-943C-358B6551EC5E}"/>
-    <hyperlink ref="G146" r:id="rId58" display="mailto:a.gorbenko@ucl.co.uk" xr:uid="{5772A23E-5235-304E-A5C1-05CB3DAB9BFC}"/>
+    <hyperlink ref="L148" r:id="rId57" xr:uid="{FEED16DA-CB82-0044-943C-358B6551EC5E}"/>
+    <hyperlink ref="G148" r:id="rId58" display="mailto:a.gorbenko@ucl.co.uk" xr:uid="{5772A23E-5235-304E-A5C1-05CB3DAB9BFC}"/>
     <hyperlink ref="L28" r:id="rId59" xr:uid="{0F06344E-50D3-B54E-8250-7516D4B03802}"/>
     <hyperlink ref="E28" r:id="rId60" xr:uid="{B72DD765-9030-AC4B-9C6A-C3E6C6D825B0}"/>
     <hyperlink ref="L27" r:id="rId61" xr:uid="{521B9389-25EE-AC42-8631-0602B790BC9F}"/>
@@ -42175,32 +43174,34 @@
     <hyperlink ref="L79" r:id="rId73" xr:uid="{8E7D4522-E2CE-7043-9079-1CE2F950B085}"/>
     <hyperlink ref="D12" r:id="rId74" xr:uid="{4517EA95-990E-DE45-A804-67126FDDD4C3}"/>
     <hyperlink ref="L21" r:id="rId75" xr:uid="{91C6A3A0-FE50-5B4F-8B20-8B6496F16211}"/>
-    <hyperlink ref="L182" r:id="rId76" xr:uid="{5721E0FE-84BD-D943-BC9A-5350183D9688}"/>
+    <hyperlink ref="L184" r:id="rId76" xr:uid="{5721E0FE-84BD-D943-BC9A-5350183D9688}"/>
     <hyperlink ref="L45" r:id="rId77" xr:uid="{FE7182CC-AEDE-E142-B842-B2FE5C063CCE}"/>
     <hyperlink ref="L30" r:id="rId78" xr:uid="{694E8A95-02AE-9249-91C7-1102518BA774}"/>
     <hyperlink ref="L17" r:id="rId79" xr:uid="{9A9A6BC9-B330-7842-A78C-4DCC88F5E19F}"/>
     <hyperlink ref="L32" r:id="rId80" xr:uid="{928CABEF-4FA6-E646-8140-7B6E43F8FB96}"/>
-    <hyperlink ref="E173" r:id="rId81" xr:uid="{82BF1574-A6C6-1641-9FFE-615861E401FD}"/>
-    <hyperlink ref="E202" r:id="rId82" xr:uid="{3562807E-7FDA-F046-BA03-5DDD43072DB7}"/>
-    <hyperlink ref="G164" r:id="rId83" display="mailto:ivanpaya@ua.es" xr:uid="{DEFB77A5-E57F-714C-BAB9-56DE82BA0B2E}"/>
+    <hyperlink ref="E175" r:id="rId81" xr:uid="{82BF1574-A6C6-1641-9FFE-615861E401FD}"/>
+    <hyperlink ref="E212" r:id="rId82" xr:uid="{3562807E-7FDA-F046-BA03-5DDD43072DB7}"/>
+    <hyperlink ref="G166" r:id="rId83" display="mailto:ivanpaya@ua.es" xr:uid="{DEFB77A5-E57F-714C-BAB9-56DE82BA0B2E}"/>
     <hyperlink ref="G121" r:id="rId84" display="mailto:ari.hyytinen@hanken.fi" xr:uid="{7777B12A-FD99-4A43-A14B-A15661B760DC}"/>
     <hyperlink ref="G129" r:id="rId85" display="mailto:peter.haan@fu-berlin.de" xr:uid="{3D1A69ED-8F06-1246-B586-201CB349DB62}"/>
-    <hyperlink ref="D170" r:id="rId86" xr:uid="{C3771F9C-84FC-7A41-9911-ED3B01799C9C}"/>
-    <hyperlink ref="D171" r:id="rId87" xr:uid="{A2B41E48-AA17-FE45-B67C-A5398A81BF2D}"/>
-    <hyperlink ref="E171" r:id="rId88" xr:uid="{D2EC3FFA-793B-E54C-B216-5D503F8901AE}"/>
+    <hyperlink ref="D172" r:id="rId86" xr:uid="{C3771F9C-84FC-7A41-9911-ED3B01799C9C}"/>
+    <hyperlink ref="D173" r:id="rId87" xr:uid="{A2B41E48-AA17-FE45-B67C-A5398A81BF2D}"/>
+    <hyperlink ref="E173" r:id="rId88" xr:uid="{D2EC3FFA-793B-E54C-B216-5D503F8901AE}"/>
     <hyperlink ref="D62" r:id="rId89" xr:uid="{A30F6415-AE46-5540-B683-ED472CE378B6}"/>
     <hyperlink ref="E64" r:id="rId90" xr:uid="{F44B5BBE-5828-6740-B73D-EFF8E8646AE0}"/>
     <hyperlink ref="D24" r:id="rId91" xr:uid="{8166B827-50E4-644E-A453-5F1CFFE18AAB}"/>
     <hyperlink ref="E34" r:id="rId92" xr:uid="{CE88CF57-77B5-1E49-888D-C53C88BC7BE5}"/>
+    <hyperlink ref="D199" r:id="rId93" xr:uid="{1038528D-03E5-437B-A0C6-EA3911052C09}"/>
+    <hyperlink ref="G200" r:id="rId94" display="https://elliottash.com/" xr:uid="{00E7B1FA-3490-4C02-A813-67E9093D5D0E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId93"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId95"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923E81FA-B875-3C4E-A189-1A21268FA086}">
-  <dimension ref="A1:C145"/>
+  <dimension ref="A1:C156"/>
   <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="32.83203125" customWidth="1"/>
@@ -43643,6 +44644,9 @@
       <c r="A136" s="1">
         <v>45964</v>
       </c>
+      <c r="B136" t="s">
+        <v>625</v>
+      </c>
       <c r="C136" t="s">
         <v>100</v>
       </c>
@@ -43651,6 +44655,9 @@
       <c r="A137" s="1">
         <v>45964</v>
       </c>
+      <c r="B137" t="s">
+        <v>603</v>
+      </c>
       <c r="C137" t="s">
         <v>100</v>
       </c>
@@ -43659,6 +44666,9 @@
       <c r="A138" s="1">
         <v>45964</v>
       </c>
+      <c r="B138" t="s">
+        <v>615</v>
+      </c>
       <c r="C138" t="s">
         <v>100</v>
       </c>
@@ -43667,6 +44677,9 @@
       <c r="A139" s="1">
         <v>45964</v>
       </c>
+      <c r="B139" t="s">
+        <v>627</v>
+      </c>
       <c r="C139" t="s">
         <v>100</v>
       </c>
@@ -43675,6 +44688,9 @@
       <c r="A140" s="1">
         <v>45964</v>
       </c>
+      <c r="B140" t="s">
+        <v>631</v>
+      </c>
       <c r="C140" t="s">
         <v>100</v>
       </c>
@@ -43683,6 +44699,9 @@
       <c r="A141" s="1">
         <v>45964</v>
       </c>
+      <c r="B141" t="s">
+        <v>514</v>
+      </c>
       <c r="C141" t="s">
         <v>100</v>
       </c>
@@ -43691,6 +44710,9 @@
       <c r="A142" s="1">
         <v>45964</v>
       </c>
+      <c r="B142" t="s">
+        <v>577</v>
+      </c>
       <c r="C142" t="s">
         <v>100</v>
       </c>
@@ -43699,6 +44721,9 @@
       <c r="A143" s="1">
         <v>45964</v>
       </c>
+      <c r="B143" t="s">
+        <v>621</v>
+      </c>
       <c r="C143" t="s">
         <v>100</v>
       </c>
@@ -43707,6 +44732,9 @@
       <c r="A144" s="1">
         <v>45964</v>
       </c>
+      <c r="B144" t="s">
+        <v>634</v>
+      </c>
       <c r="C144" t="s">
         <v>100</v>
       </c>
@@ -43715,292 +44743,473 @@
       <c r="A145" s="1">
         <v>45964</v>
       </c>
+      <c r="B145" t="s">
+        <v>110</v>
+      </c>
       <c r="C145" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A146" s="1">
+        <v>45965</v>
+      </c>
+      <c r="C146" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A147" s="1">
+        <v>45965</v>
+      </c>
+      <c r="B147" t="s">
+        <v>462</v>
+      </c>
+      <c r="C147" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A148" s="1">
+        <v>45965</v>
+      </c>
+      <c r="B148" t="s">
+        <v>529</v>
+      </c>
+      <c r="C148" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A149" s="1">
+        <v>45965</v>
+      </c>
+      <c r="B149" t="s">
+        <v>535</v>
+      </c>
+      <c r="C149" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A150" s="1">
+        <v>45965</v>
+      </c>
+      <c r="B150" t="s">
+        <v>555</v>
+      </c>
+      <c r="C150" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A151" s="1">
+        <v>45965</v>
+      </c>
+      <c r="B151" t="s">
+        <v>561</v>
+      </c>
+      <c r="C151" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A152" s="1">
+        <v>45965</v>
+      </c>
+      <c r="B152" t="s">
+        <v>564</v>
+      </c>
+      <c r="C152" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A153" s="1">
+        <v>45965</v>
+      </c>
+      <c r="B153" t="s">
+        <v>640</v>
+      </c>
+      <c r="C153" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A154" s="1">
+        <v>45965</v>
+      </c>
+      <c r="B154" t="s">
+        <v>598</v>
+      </c>
+      <c r="C154" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A155" s="1">
+        <v>45965</v>
+      </c>
+      <c r="B155" t="s">
+        <v>341</v>
+      </c>
+      <c r="C155" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A156" s="1">
+        <v>45965</v>
+      </c>
+      <c r="B156" t="s">
+        <v>416</v>
+      </c>
+      <c r="C156" t="s">
         <v>100</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5">
-    <cfRule type="duplicateValues" dxfId="102" priority="108"/>
-    <cfRule type="duplicateValues" dxfId="101" priority="109"/>
+    <cfRule type="duplicateValues" dxfId="122" priority="128"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="129"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B10">
-    <cfRule type="duplicateValues" dxfId="100" priority="106"/>
-    <cfRule type="duplicateValues" dxfId="99" priority="107"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="127"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="126"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B11">
-    <cfRule type="duplicateValues" dxfId="98" priority="104"/>
-    <cfRule type="duplicateValues" dxfId="97" priority="105"/>
+    <cfRule type="duplicateValues" dxfId="118" priority="125"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="124"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12">
-    <cfRule type="duplicateValues" dxfId="96" priority="102"/>
-    <cfRule type="duplicateValues" dxfId="95" priority="103"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="122"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="123"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15">
-    <cfRule type="duplicateValues" dxfId="94" priority="100"/>
-    <cfRule type="duplicateValues" dxfId="93" priority="101"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="121"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="120"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16">
+    <cfRule type="duplicateValues" dxfId="112" priority="119"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B17">
+    <cfRule type="duplicateValues" dxfId="111" priority="118"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="117"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B18">
+    <cfRule type="duplicateValues" dxfId="109" priority="115"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="116"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B19">
+    <cfRule type="duplicateValues" dxfId="107" priority="114"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B22:B23">
+    <cfRule type="duplicateValues" dxfId="106" priority="113"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="112"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B24">
+    <cfRule type="duplicateValues" dxfId="104" priority="111"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="110"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B27">
+    <cfRule type="duplicateValues" dxfId="102" priority="109"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="108"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B28">
+    <cfRule type="duplicateValues" dxfId="100" priority="107"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B29">
+    <cfRule type="duplicateValues" dxfId="99" priority="106"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="105"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B30">
+    <cfRule type="duplicateValues" dxfId="97" priority="104"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31">
+    <cfRule type="duplicateValues" dxfId="96" priority="103"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B32">
+    <cfRule type="duplicateValues" dxfId="95" priority="102"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B33">
+    <cfRule type="duplicateValues" dxfId="94" priority="101"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B34">
+    <cfRule type="duplicateValues" dxfId="93" priority="100"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B35">
     <cfRule type="duplicateValues" dxfId="92" priority="99"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B17">
-    <cfRule type="duplicateValues" dxfId="91" priority="97"/>
-    <cfRule type="duplicateValues" dxfId="90" priority="98"/>
+  <conditionalFormatting sqref="B37">
+    <cfRule type="duplicateValues" dxfId="91" priority="98"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B18">
-    <cfRule type="duplicateValues" dxfId="89" priority="95"/>
-    <cfRule type="duplicateValues" dxfId="88" priority="96"/>
+  <conditionalFormatting sqref="B38">
+    <cfRule type="duplicateValues" dxfId="90" priority="97"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B19">
+  <conditionalFormatting sqref="B42">
+    <cfRule type="duplicateValues" dxfId="89" priority="96"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B43">
+    <cfRule type="duplicateValues" dxfId="88" priority="95"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B44:B45">
     <cfRule type="duplicateValues" dxfId="87" priority="94"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B22:B23">
-    <cfRule type="duplicateValues" dxfId="86" priority="92"/>
-    <cfRule type="duplicateValues" dxfId="85" priority="93"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B24">
-    <cfRule type="duplicateValues" dxfId="84" priority="90"/>
-    <cfRule type="duplicateValues" dxfId="83" priority="91"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B27">
-    <cfRule type="duplicateValues" dxfId="82" priority="88"/>
-    <cfRule type="duplicateValues" dxfId="81" priority="89"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B28">
-    <cfRule type="duplicateValues" dxfId="80" priority="87"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B29">
-    <cfRule type="duplicateValues" dxfId="79" priority="85"/>
-    <cfRule type="duplicateValues" dxfId="78" priority="86"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="77" priority="84"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B31">
-    <cfRule type="duplicateValues" dxfId="76" priority="83"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B32">
-    <cfRule type="duplicateValues" dxfId="75" priority="82"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B33">
-    <cfRule type="duplicateValues" dxfId="74" priority="81"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="73" priority="80"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B35">
-    <cfRule type="duplicateValues" dxfId="72" priority="79"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B37">
-    <cfRule type="duplicateValues" dxfId="71" priority="78"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B38">
-    <cfRule type="duplicateValues" dxfId="70" priority="77"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B42">
-    <cfRule type="duplicateValues" dxfId="69" priority="76"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B43">
-    <cfRule type="duplicateValues" dxfId="68" priority="75"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B44:B45">
-    <cfRule type="duplicateValues" dxfId="67" priority="74"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B46">
-    <cfRule type="duplicateValues" dxfId="66" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="93"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B48">
-    <cfRule type="duplicateValues" dxfId="65" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="92"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B49">
-    <cfRule type="duplicateValues" dxfId="64" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="91"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B51">
-    <cfRule type="duplicateValues" dxfId="63" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="90"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B52">
-    <cfRule type="duplicateValues" dxfId="62" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="89"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B58">
-    <cfRule type="duplicateValues" dxfId="61" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="87"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B59">
-    <cfRule type="duplicateValues" dxfId="60" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="85"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B63">
-    <cfRule type="duplicateValues" dxfId="59" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="84"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B64">
-    <cfRule type="duplicateValues" dxfId="58" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="82"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B66">
-    <cfRule type="duplicateValues" dxfId="57" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="81"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="56" priority="59"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="79"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B68">
-    <cfRule type="duplicateValues" dxfId="54" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="78"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B69">
-    <cfRule type="duplicateValues" dxfId="53" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="77"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B70">
-    <cfRule type="duplicateValues" dxfId="52" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="75"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B72">
-    <cfRule type="duplicateValues" dxfId="51" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="74"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B73">
-    <cfRule type="duplicateValues" dxfId="50" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="72"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B74">
-    <cfRule type="duplicateValues" dxfId="49" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B75">
-    <cfRule type="duplicateValues" dxfId="48" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B76">
-    <cfRule type="duplicateValues" dxfId="47" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="69"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B77">
-    <cfRule type="duplicateValues" dxfId="46" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B78">
+    <cfRule type="duplicateValues" dxfId="65" priority="66"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B83">
+    <cfRule type="duplicateValues" dxfId="64" priority="65"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B84">
+    <cfRule type="duplicateValues" dxfId="63" priority="64"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B85">
+    <cfRule type="duplicateValues" dxfId="62" priority="63"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B87">
+    <cfRule type="duplicateValues" dxfId="61" priority="62"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B88">
+    <cfRule type="duplicateValues" dxfId="60" priority="61"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B89">
+    <cfRule type="duplicateValues" dxfId="59" priority="60"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B90">
+    <cfRule type="duplicateValues" dxfId="58" priority="59"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B91">
+    <cfRule type="duplicateValues" dxfId="57" priority="58"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B92">
+    <cfRule type="duplicateValues" dxfId="56" priority="57"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B93">
+    <cfRule type="duplicateValues" dxfId="55" priority="56"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B94">
+    <cfRule type="duplicateValues" dxfId="54" priority="55"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B95">
+    <cfRule type="duplicateValues" dxfId="53" priority="54"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B96">
+    <cfRule type="duplicateValues" dxfId="52" priority="53"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B97">
+    <cfRule type="duplicateValues" dxfId="51" priority="52"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B98">
+    <cfRule type="duplicateValues" dxfId="50" priority="51"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B99">
+    <cfRule type="duplicateValues" dxfId="49" priority="50"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B100">
+    <cfRule type="duplicateValues" dxfId="48" priority="49"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B101">
+    <cfRule type="duplicateValues" dxfId="47" priority="48"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B104">
+    <cfRule type="duplicateValues" dxfId="46" priority="47"/>
     <cfRule type="duplicateValues" dxfId="45" priority="46"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B83">
+  <conditionalFormatting sqref="B105:B106">
     <cfRule type="duplicateValues" dxfId="44" priority="45"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B84">
+  <conditionalFormatting sqref="B107">
     <cfRule type="duplicateValues" dxfId="43" priority="44"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B85">
+  <conditionalFormatting sqref="B108">
     <cfRule type="duplicateValues" dxfId="42" priority="43"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B87">
+  <conditionalFormatting sqref="B109">
     <cfRule type="duplicateValues" dxfId="41" priority="42"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B88">
+  <conditionalFormatting sqref="B110">
     <cfRule type="duplicateValues" dxfId="40" priority="41"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B89">
+  <conditionalFormatting sqref="B111">
     <cfRule type="duplicateValues" dxfId="39" priority="40"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B90">
+  <conditionalFormatting sqref="B112">
     <cfRule type="duplicateValues" dxfId="38" priority="39"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B91">
+  <conditionalFormatting sqref="B113">
     <cfRule type="duplicateValues" dxfId="37" priority="38"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B92">
+  <conditionalFormatting sqref="B114">
     <cfRule type="duplicateValues" dxfId="36" priority="37"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B93">
+  <conditionalFormatting sqref="B115">
     <cfRule type="duplicateValues" dxfId="35" priority="36"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B94">
+  <conditionalFormatting sqref="B116">
     <cfRule type="duplicateValues" dxfId="34" priority="35"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B95">
+  <conditionalFormatting sqref="B117">
     <cfRule type="duplicateValues" dxfId="33" priority="34"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B96">
+  <conditionalFormatting sqref="B118">
     <cfRule type="duplicateValues" dxfId="32" priority="33"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B97">
+  <conditionalFormatting sqref="B119">
     <cfRule type="duplicateValues" dxfId="31" priority="32"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B98">
+  <conditionalFormatting sqref="B120">
     <cfRule type="duplicateValues" dxfId="30" priority="31"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B99">
+  <conditionalFormatting sqref="B121">
     <cfRule type="duplicateValues" dxfId="29" priority="30"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B100">
+  <conditionalFormatting sqref="B122">
     <cfRule type="duplicateValues" dxfId="28" priority="29"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B101">
+  <conditionalFormatting sqref="B126">
     <cfRule type="duplicateValues" dxfId="27" priority="28"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B104">
-    <cfRule type="duplicateValues" dxfId="26" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="27"/>
+  <conditionalFormatting sqref="B127">
+    <cfRule type="duplicateValues" dxfId="26" priority="27"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B105:B106">
+  <conditionalFormatting sqref="B128">
+    <cfRule type="duplicateValues" dxfId="25" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B129">
     <cfRule type="duplicateValues" dxfId="24" priority="25"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B107">
+  <conditionalFormatting sqref="B130">
     <cfRule type="duplicateValues" dxfId="23" priority="24"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B108">
+  <conditionalFormatting sqref="B131">
     <cfRule type="duplicateValues" dxfId="22" priority="23"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B109">
+  <conditionalFormatting sqref="B132">
     <cfRule type="duplicateValues" dxfId="21" priority="22"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B110">
+  <conditionalFormatting sqref="B133">
     <cfRule type="duplicateValues" dxfId="20" priority="21"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B111">
+  <conditionalFormatting sqref="B136">
     <cfRule type="duplicateValues" dxfId="19" priority="20"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B112">
+  <conditionalFormatting sqref="B137">
     <cfRule type="duplicateValues" dxfId="18" priority="19"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B113">
+  <conditionalFormatting sqref="B138">
     <cfRule type="duplicateValues" dxfId="17" priority="18"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B114">
+  <conditionalFormatting sqref="B139">
     <cfRule type="duplicateValues" dxfId="16" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B115">
+  <conditionalFormatting sqref="B140">
     <cfRule type="duplicateValues" dxfId="15" priority="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B116">
+  <conditionalFormatting sqref="B141">
     <cfRule type="duplicateValues" dxfId="14" priority="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B117">
+  <conditionalFormatting sqref="B142">
     <cfRule type="duplicateValues" dxfId="13" priority="14"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B118">
+  <conditionalFormatting sqref="B143">
     <cfRule type="duplicateValues" dxfId="12" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B119">
+  <conditionalFormatting sqref="B144">
     <cfRule type="duplicateValues" dxfId="11" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B120">
+  <conditionalFormatting sqref="B145">
     <cfRule type="duplicateValues" dxfId="10" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B121">
+  <conditionalFormatting sqref="B147">
     <cfRule type="duplicateValues" dxfId="9" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B122">
+  <conditionalFormatting sqref="B148">
     <cfRule type="duplicateValues" dxfId="8" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B126">
+  <conditionalFormatting sqref="B149">
     <cfRule type="duplicateValues" dxfId="7" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B127">
+  <conditionalFormatting sqref="B150">
     <cfRule type="duplicateValues" dxfId="6" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B128">
+  <conditionalFormatting sqref="B151">
     <cfRule type="duplicateValues" dxfId="5" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B129">
+  <conditionalFormatting sqref="B152">
     <cfRule type="duplicateValues" dxfId="4" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B130">
+  <conditionalFormatting sqref="B153">
     <cfRule type="duplicateValues" dxfId="3" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B131">
+  <conditionalFormatting sqref="B154">
     <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B132">
+  <conditionalFormatting sqref="B155">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B133">
+  <conditionalFormatting sqref="B156">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -44023,11 +45232,11 @@
       </c>
       <c r="B1" s="15">
         <f>COUNTA(sum!A:A) -1</f>
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="C1" s="14">
         <f>COUNTIF(sum!H:H, "completed")/B1</f>
-        <v>0.58706467661691542</v>
+        <v>0.65402843601895733</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.4">
@@ -44036,11 +45245,11 @@
       </c>
       <c r="B2" s="16">
         <f>COUNTA(sum!F:F) -1</f>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C2" s="10">
         <f>COUNTIFS(sum!H:H,"completed", sum!F:F, "&lt;&gt;") / B2</f>
-        <v>0.48888888888888887</v>
+        <v>0.47826086956521741</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.4">
@@ -44049,11 +45258,11 @@
       </c>
       <c r="B3" s="16">
         <f>COUNTA(sum!J:J) -1</f>
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C3" s="10">
         <f>COUNTIFS(sum!H:H,"completed", sum!J:J, "&lt;&gt;") / B3</f>
-        <v>0.42424242424242425</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="26" x14ac:dyDescent="0.6">
@@ -44066,7 +45275,7 @@
       </c>
       <c r="C5" s="14">
         <f>B5/B1</f>
-        <v>4.9751243781094526E-3</v>
+        <v>4.7393364928909956E-3</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.4">

--- a/EconJM_status.xlsx
+++ b/EconJM_status.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\javie\Dropbox\Work\Job Search\2025 EconJM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E0F6221-463F-40BF-8241-1560B166D507}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCD51917-4EE7-4ED0-A560-DC42A0FFD553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" xr2:uid="{6FE48536-7E5C-BF4C-9490-2A6392576298}"/>
   </bookViews>
@@ -45,7 +45,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="96">
+  <futureMetadata name="XLRICHVALUE" count="98">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -588,6 +588,13 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="2508"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="2121"/>
         </ext>
       </extLst>
@@ -602,7 +609,7 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="2508"/>
+          <xlrd:rvb i="2520"/>
         </ext>
       </extLst>
     </bk>
@@ -616,6 +623,13 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="2645"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="76"/>
         </ext>
       </extLst>
@@ -623,14 +637,14 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="2633"/>
+          <xlrd:rvb i="2691"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="2642"/>
+          <xlrd:rvb i="2700"/>
         </ext>
       </extLst>
     </bk>
@@ -644,21 +658,21 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="2689"/>
+          <xlrd:rvb i="2747"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="2748"/>
+          <xlrd:rvb i="2806"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="2800"/>
+          <xlrd:rvb i="2858"/>
         </ext>
       </extLst>
     </bk>
@@ -672,7 +686,7 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="2864"/>
+          <xlrd:rvb i="2922"/>
         </ext>
       </extLst>
     </bk>
@@ -686,14 +700,14 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="2875"/>
+          <xlrd:rvb i="2933"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="2886"/>
+          <xlrd:rvb i="2944"/>
         </ext>
       </extLst>
     </bk>
@@ -707,7 +721,7 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="2897"/>
+          <xlrd:rvb i="2955"/>
         </ext>
       </extLst>
     </bk>
@@ -719,7 +733,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <valueMetadata count="96">
+  <valueMetadata count="98">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -1008,12 +1022,18 @@
     <bk>
       <rc t="1" v="95"/>
     </bk>
+    <bk>
+      <rc t="1" v="96"/>
+    </bk>
+    <bk>
+      <rc t="1" v="97"/>
+    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1756" uniqueCount="673">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1836" uniqueCount="703">
   <si>
     <t>add_id</t>
   </si>
@@ -3068,6 +3088,96 @@
   </si>
   <si>
     <t>added 10 more from EJM</t>
+  </si>
+  <si>
+    <t>University College Dublin</t>
+  </si>
+  <si>
+    <t>https://my.corehr.com/pls/ucdrecruit/erq_search_package.search_form?p_company=1&amp;p_internal_external=E#</t>
+  </si>
+  <si>
+    <t>ucd_1</t>
+  </si>
+  <si>
+    <t>ucd_2</t>
+  </si>
+  <si>
+    <t>jib ref (019094) and china application</t>
+  </si>
+  <si>
+    <t>job ref (019090)</t>
+  </si>
+  <si>
+    <t>Professor Benjamin Elsner</t>
+  </si>
+  <si>
+    <t>aix</t>
+  </si>
+  <si>
+    <t>Aix-Marseille Université</t>
+  </si>
+  <si>
+    <t>oslo_post</t>
+  </si>
+  <si>
+    <t>cl must match a project</t>
+  </si>
+  <si>
+    <t>laval</t>
+  </si>
+  <si>
+    <t>Université Laval</t>
+  </si>
+  <si>
+    <t>Stephen Gordon, Chair</t>
+  </si>
+  <si>
+    <t>sacro</t>
+  </si>
+  <si>
+    <t>Università Cattolica del Sacro Cuore</t>
+  </si>
+  <si>
+    <t>bank_alemania</t>
+  </si>
+  <si>
+    <t>Deutsche Bundesbank</t>
+  </si>
+  <si>
+    <t>specify the preference of topics (AI effect on finance and macrofinance)</t>
+  </si>
+  <si>
+    <t>luis_guido</t>
+  </si>
+  <si>
+    <t>LUISS Guido Carli</t>
+  </si>
+  <si>
+    <t>Paris School of Economics (PSE)</t>
+  </si>
+  <si>
+    <t>pse</t>
+  </si>
+  <si>
+    <t>https://www.parisschoolofeconomics.eu/en/job-opportunities/assistant-professor/</t>
+  </si>
+  <si>
+    <t>finished adding EJM</t>
+  </si>
+  <si>
+    <t>vienna</t>
+  </si>
+  <si>
+    <t>University of Vienna</t>
+  </si>
+  <si>
+    <t>specify that I want to do applied micro, but have good synergy with behavioral group</t>
+  </si>
+  <si>
+    <t>obrero</t>
+  </si>
+  <si>
+    <t>Örebro University</t>
   </si>
 </sst>
 </file>
@@ -3222,7 +3332,27 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="136">
+  <dxfs count="138">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -5127,11 +5257,19 @@
     <address r:id="rId189"/>
     <moreImagesAddress r:id="rId190"/>
   </webImageSrd>
+  <webImageSrd>
+    <address r:id="rId191"/>
+    <moreImagesAddress r:id="rId192"/>
+  </webImageSrd>
+  <webImageSrd>
+    <address r:id="rId193"/>
+    <moreImagesAddress r:id="rId194"/>
+  </webImageSrd>
 </webImagesSrd>
 </file>
 
 <file path=xl/richData/rdarray.xml><?xml version="1.0" encoding="utf-8"?>
-<arrayData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="177">
+<arrayData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="182">
   <a r="1">
     <v t="r">6</v>
   </a>
@@ -6172,26 +6310,20 @@
     <v t="s">Pacific Time Zone</v>
     <v t="s">Eastern Time Zone</v>
   </a>
+  <a r="1">
+    <v t="r">2513</v>
+  </a>
+  <a r="1">
+    <v t="s">UTC+00:00</v>
+  </a>
   <a r="2">
-    <v t="r">2528</v>
-    <v t="r">2529</v>
+    <v t="r">2540</v>
+    <v t="r">2541</v>
   </a>
   <a r="1">
     <v t="s">Russian language</v>
   </a>
   <a r="83">
-    <v t="r">2544</v>
-    <v t="r">2545</v>
-    <v t="r">2546</v>
-    <v t="r">2547</v>
-    <v t="r">2548</v>
-    <v t="r">2549</v>
-    <v t="r">2550</v>
-    <v t="r">2551</v>
-    <v t="r">2552</v>
-    <v t="r">2553</v>
-    <v t="r">2554</v>
-    <v t="r">2555</v>
     <v t="r">2556</v>
     <v t="r">2557</v>
     <v t="r">2558</v>
@@ -6255,7 +6387,6 @@
     <v t="r">2616</v>
     <v t="r">2617</v>
     <v t="r">2618</v>
-    <v t="r">2514</v>
     <v t="r">2619</v>
     <v t="r">2620</v>
     <v t="r">2621</v>
@@ -6263,6 +6394,19 @@
     <v t="r">2623</v>
     <v t="r">2624</v>
     <v t="r">2625</v>
+    <v t="r">2626</v>
+    <v t="r">2627</v>
+    <v t="r">2628</v>
+    <v t="r">2629</v>
+    <v t="r">2630</v>
+    <v t="r">2526</v>
+    <v t="r">2631</v>
+    <v t="r">2632</v>
+    <v t="r">2633</v>
+    <v t="r">2634</v>
+    <v t="r">2635</v>
+    <v t="r">2636</v>
+    <v t="r">2637</v>
   </a>
   <a r="13">
     <v t="s">Moscow Time</v>
@@ -6279,46 +6423,38 @@
     <v t="s">Magadan Time</v>
     <v t="s">Kaliningrad Time</v>
   </a>
-  <a r="1">
-    <v t="r">2637</v>
+  <a r="2">
+    <v t="r">2663</v>
+    <v t="r">2664</v>
   </a>
-  <a r="2">
-    <v t="r">2660</v>
-    <v t="r">2661</v>
+  <a r="4">
+    <v t="s">Burgenland Croatian</v>
+    <v t="s">Hungarian language</v>
+    <v t="s">Slovene language</v>
+    <v t="s">German language</v>
   </a>
-  <a r="1">
-    <v t="s">Slovak language</v>
-  </a>
-  <a r="8">
-    <v t="r">2675</v>
-    <v t="r">2676</v>
+  <a r="9">
     <v t="r">2677</v>
     <v t="r">2678</v>
     <v t="r">2679</v>
     <v t="r">2680</v>
     <v t="r">2681</v>
     <v t="r">2682</v>
+    <v t="r">2683</v>
+    <v t="r">2684</v>
+    <v t="r">2649</v>
   </a>
-  <a r="4">
-    <v t="r">2709</v>
-    <v t="r">2710</v>
-    <v t="r">2711</v>
-    <v t="r">2712</v>
+  <a r="1">
+    <v t="r">2695</v>
   </a>
   <a r="2">
-    <v t="s">Korean Sign Language</v>
-    <v t="s">Korean language</v>
+    <v t="r">2718</v>
+    <v t="r">2719</v>
   </a>
-  <a r="17">
-    <v t="r">2695</v>
-    <v t="r">2725</v>
-    <v t="r">2726</v>
-    <v t="r">2727</v>
-    <v t="r">2728</v>
-    <v t="r">2729</v>
-    <v t="r">2730</v>
-    <v t="r">2731</v>
-    <v t="r">2732</v>
+  <a r="1">
+    <v t="s">Slovak language</v>
+  </a>
+  <a r="8">
     <v t="r">2733</v>
     <v t="r">2734</v>
     <v t="r">2735</v>
@@ -6328,12 +6464,41 @@
     <v t="r">2739</v>
     <v t="r">2740</v>
   </a>
+  <a r="4">
+    <v t="r">2767</v>
+    <v t="r">2768</v>
+    <v t="r">2769</v>
+    <v t="r">2770</v>
+  </a>
+  <a r="2">
+    <v t="s">Korean Sign Language</v>
+    <v t="s">Korean language</v>
+  </a>
+  <a r="17">
+    <v t="r">2753</v>
+    <v t="r">2783</v>
+    <v t="r">2784</v>
+    <v t="r">2785</v>
+    <v t="r">2786</v>
+    <v t="r">2787</v>
+    <v t="r">2788</v>
+    <v t="r">2789</v>
+    <v t="r">2790</v>
+    <v t="r">2791</v>
+    <v t="r">2792</v>
+    <v t="r">2793</v>
+    <v t="r">2794</v>
+    <v t="r">2795</v>
+    <v t="r">2796</v>
+    <v t="r">2797</v>
+    <v t="r">2798</v>
+  </a>
   <a r="1">
     <v t="s">Time in South Korea</v>
   </a>
   <a r="2">
-    <v t="r">2769</v>
-    <v t="r">2770</v>
+    <v t="r">2827</v>
+    <v t="r">2828</v>
   </a>
   <a r="12">
     <v t="s">South African English</v>
@@ -6350,35 +6515,6 @@
     <v t="s">Northern Sotho</v>
   </a>
   <a r="9">
-    <v t="r">2784</v>
-    <v t="r">2785</v>
-    <v t="r">2786</v>
-    <v t="r">2787</v>
-    <v t="r">2788</v>
-    <v t="r">2789</v>
-    <v t="r">2790</v>
-    <v t="r">2791</v>
-    <v t="r">2792</v>
-  </a>
-  <a r="1">
-    <v t="s">Africa/Johannesburg</v>
-  </a>
-  <a r="2">
-    <v t="r">2820</v>
-    <v t="r">2821</v>
-  </a>
-  <a r="1">
-    <v t="s">Rioplatense Spanish</v>
-  </a>
-  <a r="23">
-    <v t="r">2834</v>
-    <v t="r">2835</v>
-    <v t="r">2836</v>
-    <v t="r">2837</v>
-    <v t="r">2838</v>
-    <v t="r">2839</v>
-    <v t="r">2840</v>
-    <v t="r">2841</v>
     <v t="r">2842</v>
     <v t="r">2843</v>
     <v t="r">2844</v>
@@ -6388,92 +6524,63 @@
     <v t="r">2848</v>
     <v t="r">2849</v>
     <v t="r">2850</v>
-    <v t="r">2851</v>
-    <v t="r">2852</v>
-    <v t="r">2853</v>
-    <v t="r">2854</v>
-    <v t="r">2855</v>
-    <v t="r">2856</v>
+  </a>
+  <a r="1">
+    <v t="s">Africa/Johannesburg</v>
+  </a>
+  <a r="2">
+    <v t="r">2878</v>
+    <v t="r">2879</v>
+  </a>
+  <a r="1">
+    <v t="s">Rioplatense Spanish</v>
+  </a>
+  <a r="23">
+    <v t="r">2892</v>
+    <v t="r">2893</v>
+    <v t="r">2894</v>
+    <v t="r">2895</v>
+    <v t="r">2896</v>
+    <v t="r">2897</v>
+    <v t="r">2898</v>
+    <v t="r">2899</v>
+    <v t="r">2900</v>
+    <v t="r">2901</v>
+    <v t="r">2902</v>
+    <v t="r">2903</v>
+    <v t="r">2904</v>
+    <v t="r">2905</v>
+    <v t="r">2906</v>
+    <v t="r">2907</v>
+    <v t="r">2908</v>
+    <v t="r">2909</v>
+    <v t="r">2910</v>
+    <v t="r">2911</v>
+    <v t="r">2912</v>
+    <v t="r">2913</v>
+    <v t="r">2914</v>
   </a>
   <a r="1">
     <v t="s">Time in Argentina</v>
   </a>
   <a r="1">
-    <v t="r">2869</v>
+    <v t="r">2927</v>
   </a>
   <a r="1">
-    <v t="r">2880</v>
+    <v t="r">2938</v>
   </a>
   <a r="1">
-    <v t="r">2891</v>
+    <v t="r">2949</v>
   </a>
   <a r="3">
-    <v t="r">2917</v>
-    <v t="r">2918</v>
-    <v t="r">2919</v>
+    <v t="r">2975</v>
+    <v t="r">2976</v>
+    <v t="r">2977</v>
   </a>
   <a r="1">
     <v t="s">Turkish language</v>
   </a>
   <a r="81">
-    <v t="r">2933</v>
-    <v t="r">2934</v>
-    <v t="r">2935</v>
-    <v t="r">2936</v>
-    <v t="r">2937</v>
-    <v t="r">2938</v>
-    <v t="r">2939</v>
-    <v t="r">2940</v>
-    <v t="r">2941</v>
-    <v t="r">2942</v>
-    <v t="r">2943</v>
-    <v t="r">2944</v>
-    <v t="r">2945</v>
-    <v t="r">2946</v>
-    <v t="r">2947</v>
-    <v t="r">2948</v>
-    <v t="r">2949</v>
-    <v t="r">2950</v>
-    <v t="r">2951</v>
-    <v t="r">2952</v>
-    <v t="r">2953</v>
-    <v t="r">2954</v>
-    <v t="r">2955</v>
-    <v t="r">2956</v>
-    <v t="r">2957</v>
-    <v t="r">2958</v>
-    <v t="r">2959</v>
-    <v t="r">2960</v>
-    <v t="r">2961</v>
-    <v t="r">2962</v>
-    <v t="r">2963</v>
-    <v t="r">2964</v>
-    <v t="r">2965</v>
-    <v t="r">2966</v>
-    <v t="r">2967</v>
-    <v t="r">2968</v>
-    <v t="r">2969</v>
-    <v t="r">2970</v>
-    <v t="r">2971</v>
-    <v t="r">2972</v>
-    <v t="r">2973</v>
-    <v t="r">2974</v>
-    <v t="r">2975</v>
-    <v t="r">2976</v>
-    <v t="r">2977</v>
-    <v t="r">2978</v>
-    <v t="r">2979</v>
-    <v t="r">2980</v>
-    <v t="r">2981</v>
-    <v t="r">2982</v>
-    <v t="r">2983</v>
-    <v t="r">2984</v>
-    <v t="r">2985</v>
-    <v t="r">2986</v>
-    <v t="r">2987</v>
-    <v t="r">2988</v>
-    <v t="r">2989</v>
-    <v t="r">2990</v>
     <v t="r">2991</v>
     <v t="r">2992</v>
     <v t="r">2993</v>
@@ -6497,6 +6604,64 @@
     <v t="r">3011</v>
     <v t="r">3012</v>
     <v t="r">3013</v>
+    <v t="r">3014</v>
+    <v t="r">3015</v>
+    <v t="r">3016</v>
+    <v t="r">3017</v>
+    <v t="r">3018</v>
+    <v t="r">3019</v>
+    <v t="r">3020</v>
+    <v t="r">3021</v>
+    <v t="r">3022</v>
+    <v t="r">3023</v>
+    <v t="r">3024</v>
+    <v t="r">3025</v>
+    <v t="r">3026</v>
+    <v t="r">3027</v>
+    <v t="r">3028</v>
+    <v t="r">3029</v>
+    <v t="r">3030</v>
+    <v t="r">3031</v>
+    <v t="r">3032</v>
+    <v t="r">3033</v>
+    <v t="r">3034</v>
+    <v t="r">3035</v>
+    <v t="r">3036</v>
+    <v t="r">3037</v>
+    <v t="r">3038</v>
+    <v t="r">3039</v>
+    <v t="r">3040</v>
+    <v t="r">3041</v>
+    <v t="r">3042</v>
+    <v t="r">3043</v>
+    <v t="r">3044</v>
+    <v t="r">3045</v>
+    <v t="r">3046</v>
+    <v t="r">3047</v>
+    <v t="r">3048</v>
+    <v t="r">3049</v>
+    <v t="r">3050</v>
+    <v t="r">3051</v>
+    <v t="r">3052</v>
+    <v t="r">3053</v>
+    <v t="r">3054</v>
+    <v t="r">3055</v>
+    <v t="r">3056</v>
+    <v t="r">3057</v>
+    <v t="r">3058</v>
+    <v t="r">3059</v>
+    <v t="r">3060</v>
+    <v t="r">3061</v>
+    <v t="r">3062</v>
+    <v t="r">3063</v>
+    <v t="r">3064</v>
+    <v t="r">3065</v>
+    <v t="r">3066</v>
+    <v t="r">3067</v>
+    <v t="r">3068</v>
+    <v t="r">3069</v>
+    <v t="r">3070</v>
+    <v t="r">3071</v>
   </a>
   <a r="1">
     <v t="s">UTC+03:00</v>
@@ -6505,7 +6670,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="3021">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="3079">
   <rv s="0">
     <v>536870912</v>
     <v>Baltimore</v>
@@ -22719,81 +22884,21 @@
   </rv>
   <rv s="0">
     <v>536870912</v>
-    <v>Russia</v>
-    <v>ed4fce79-8ad4-352b-205b-e4db36c49bbe</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="1">
-    <fb>0.13294470341402198</fb>
-    <v>29</v>
-  </rv>
-  <rv s="1">
-    <fb>17075400</fb>
+    <v>Dublin</v>
+    <v>7e7d2832-97c8-afa4-d282-865c20a549c9</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="1">
+    <fb>114.99</fb>
     <v>8</v>
   </rv>
-  <rv s="1">
-    <fb>1454000</fb>
-    <v>8</v>
-  </rv>
-  <rv s="1">
-    <fb>11.5</fb>
-    <v>30</v>
-  </rv>
-  <rv s="1">
-    <fb>7</fb>
-    <v>31</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Moscow</v>
-    <v>6bb559e5-6af9-adf8-d8bc-7f999aba8a3a</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="1">
-    <fb>1732026.7760000001</fb>
-    <v>8</v>
-  </rv>
-  <rv s="1">
-    <fb>180.74643865422601</fb>
-    <v>32</v>
-  </rv>
-  <rv s="1">
-    <fb>4.4703597689969995E-2</fb>
-    <v>29</v>
-  </rv>
-  <rv s="1">
-    <fb>6602.6575252928196</fb>
-    <v>8</v>
-  </rv>
-  <rv s="1">
-    <fb>1.57</fb>
-    <v>30</v>
-  </rv>
-  <rv s="1">
-    <fb>0.49758561923004796</fb>
-    <v>29</v>
-  </rv>
-  <rv s="1">
-    <fb>92.142875817828696</fb>
-    <v>33</v>
-  </rv>
-  <rv s="1">
-    <fb>0.59</fb>
-    <v>34</v>
-  </rv>
-  <rv s="1">
-    <fb>1699876578871.3501</fb>
-    <v>35</v>
-  </rv>
-  <rv s="1">
-    <fb>1.0258246</fb>
-    <v>29</v>
-  </rv>
-  <rv s="1">
-    <fb>0.81909310000000002</fb>
-    <v>29</v>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Republic of Ireland</v>
+    <v>77f28672-5669-4775-a58a-b62b17779010</v>
+    <v>en-US</v>
+    <v>Map</v>
   </rv>
   <rv s="2">
     <v>85</v>
@@ -22801,6 +22906,149 @@
     <v>392</v>
     <v>7</v>
     <v>0</v>
+    <v>Image of Dublin</v>
+  </rv>
+  <rv s="1">
+    <fb>53.349722222222198</fb>
+    <v>9</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Emma Blain (Mayor)</v>
+    <v>b5d63317-690f-39b5-8ae9-56eaac5c2452</v>
+    <v>en-US</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="3">
+    <v>150</v>
+  </rv>
+  <rv s="4">
+    <v>https://www.bing.com/search?q=dublin+ireland&amp;form=skydnc</v>
+    <v>Learn more on Bing</v>
+  </rv>
+  <rv s="1">
+    <fb>-6.2602777777777803</fb>
+    <v>9</v>
+  </rv>
+  <rv s="1">
+    <fb>592713</fb>
+    <v>8</v>
+  </rv>
+  <rv s="3">
+    <v>151</v>
+  </rv>
+  <rv s="25">
+    <v>#VALUE!</v>
+    <v>en-US</v>
+    <v>7e7d2832-97c8-afa4-d282-865c20a549c9</v>
+    <v>536870912</v>
+    <v>1</v>
+    <v>393</v>
+    <v>394</v>
+    <v>Dublin</v>
+    <v>4</v>
+    <v>5</v>
+    <v>Map</v>
+    <v>6</v>
+    <v>246</v>
+    <v>2509</v>
+    <v>2510</v>
+    <v>Dublin is the capital city of Ireland. On a bay at the mouth of the River Liffey, it is in the province of Leinster, bordered on the south by the Dublin Mountains, a part of the Wicklow Mountains range. At the 2022 census, the city council area ...</v>
+    <v>2511</v>
+    <v>2512</v>
+    <v>2514</v>
+    <v>2515</v>
+    <v>2516</v>
+    <v>Dublin</v>
+    <v>2517</v>
+    <v>2518</v>
+    <v>Dublin</v>
+    <v>mdp/vdpid/5469235680884293633</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Russia</v>
+    <v>ed4fce79-8ad4-352b-205b-e4db36c49bbe</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="1">
+    <fb>0.13294470341402198</fb>
+    <v>29</v>
+  </rv>
+  <rv s="1">
+    <fb>17075400</fb>
+    <v>8</v>
+  </rv>
+  <rv s="1">
+    <fb>1454000</fb>
+    <v>8</v>
+  </rv>
+  <rv s="1">
+    <fb>11.5</fb>
+    <v>30</v>
+  </rv>
+  <rv s="1">
+    <fb>7</fb>
+    <v>31</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Moscow</v>
+    <v>6bb559e5-6af9-adf8-d8bc-7f999aba8a3a</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="1">
+    <fb>1732026.7760000001</fb>
+    <v>8</v>
+  </rv>
+  <rv s="1">
+    <fb>180.74643865422601</fb>
+    <v>32</v>
+  </rv>
+  <rv s="1">
+    <fb>4.4703597689969995E-2</fb>
+    <v>29</v>
+  </rv>
+  <rv s="1">
+    <fb>6602.6575252928196</fb>
+    <v>8</v>
+  </rv>
+  <rv s="1">
+    <fb>1.57</fb>
+    <v>30</v>
+  </rv>
+  <rv s="1">
+    <fb>0.49758561923004796</fb>
+    <v>29</v>
+  </rv>
+  <rv s="1">
+    <fb>92.142875817828696</fb>
+    <v>33</v>
+  </rv>
+  <rv s="1">
+    <fb>0.59</fb>
+    <v>34</v>
+  </rv>
+  <rv s="1">
+    <fb>1699876578871.3501</fb>
+    <v>35</v>
+  </rv>
+  <rv s="1">
+    <fb>1.0258246</fb>
+    <v>29</v>
+  </rv>
+  <rv s="1">
+    <fb>0.81909310000000002</fb>
+    <v>29</v>
+  </rv>
+  <rv s="2">
+    <v>86</v>
+    <v>6</v>
+    <v>396</v>
+    <v>7</v>
+    <v>0</v>
     <v>Image of Russia</v>
   </rv>
   <rv s="1">
@@ -22822,7 +23070,7 @@
     <v>Generic</v>
   </rv>
   <rv s="3">
-    <v>150</v>
+    <v>152</v>
   </rv>
   <rv s="4">
     <v>https://www.bing.com/search?q=russia&amp;form=skydnc</v>
@@ -22841,7 +23089,7 @@
     <v>34</v>
   </rv>
   <rv s="3">
-    <v>151</v>
+    <v>153</v>
   </rv>
   <rv s="1">
     <fb>0.36436404289999996</fb>
@@ -23450,14 +23698,14 @@
     <v>Map</v>
   </rv>
   <rv s="3">
-    <v>152</v>
+    <v>154</v>
   </rv>
   <rv s="1">
     <fb>0.11384595754929799</fb>
     <v>29</v>
   </rv>
   <rv s="3">
-    <v>153</v>
+    <v>155</v>
   </rv>
   <rv s="1">
     <fb>0.46200000000000002</fb>
@@ -23477,29 +23725,15 @@
     <v>ed4fce79-8ad4-352b-205b-e4db36c49bbe</v>
     <v>536870912</v>
     <v>1</v>
-    <v>395</v>
+    <v>399</v>
     <v>27</v>
     <v>Russia</v>
     <v>4</v>
     <v>5</v>
     <v>Map</v>
     <v>6</v>
-    <v>396</v>
+    <v>400</v>
     <v>RU</v>
-    <v>2509</v>
-    <v>2510</v>
-    <v>2511</v>
-    <v>2512</v>
-    <v>2513</v>
-    <v>2514</v>
-    <v>2515</v>
-    <v>2516</v>
-    <v>2517</v>
-    <v>RUB</v>
-    <v>Russia, or the Russian Federation, is a country spanning Eastern Europe and North Asia. It is the largest country in the world by land area, and extends across eleven time zones; sharing land borders with fourteen countries. Russia is the most ...</v>
-    <v>2518</v>
-    <v>2519</v>
-    <v>2520</v>
     <v>2521</v>
     <v>2522</v>
     <v>2523</v>
@@ -23507,176 +23741,119 @@
     <v>2525</v>
     <v>2526</v>
     <v>2527</v>
-    <v>2514</v>
+    <v>2528</v>
+    <v>2529</v>
+    <v>RUB</v>
+    <v>Russia, or the Russian Federation, is a country spanning Eastern Europe and North Asia. It is the largest country in the world by land area, and extends across eleven time zones; sharing land borders with fourteen countries. Russia is the most ...</v>
     <v>2530</v>
     <v>2531</v>
     <v>2532</v>
     <v>2533</v>
-    <v>2057</v>
     <v>2534</v>
-    <v>Russia</v>
-    <v>National anthem of Russia</v>
     <v>2535</v>
-    <v>Российская Федерация</v>
     <v>2536</v>
     <v>2537</v>
     <v>2538</v>
     <v>2539</v>
-    <v>2540</v>
-    <v>2541</v>
+    <v>2526</v>
+    <v>2542</v>
+    <v>2543</v>
+    <v>2544</v>
+    <v>2545</v>
+    <v>2057</v>
+    <v>2546</v>
+    <v>Russia</v>
+    <v>National anthem of Russia</v>
+    <v>2547</v>
+    <v>Российская Федерация</v>
+    <v>2548</v>
+    <v>2549</v>
+    <v>2550</v>
+    <v>2551</v>
+    <v>2552</v>
+    <v>2553</v>
     <v>253</v>
     <v>287</v>
     <v>458</v>
-    <v>2542</v>
-    <v>2543</v>
-    <v>2626</v>
-    <v>2627</v>
-    <v>2628</v>
-    <v>2629</v>
-    <v>2630</v>
-    <v>Russia</v>
-    <v>2631</v>
-    <v>mdp/vdpid/203</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Prague</v>
-    <v>a3446df9-1e81-03b1-d08c-0593eead811a</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="1">
-    <fb>496.21</fb>
-    <v>8</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Austria-Hungary</v>
-    <v>09b8630d-3ac1-93e8-a27e-b8a55de26a17</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="2">
-    <v>86</v>
-    <v>6</v>
-    <v>397</v>
-    <v>7</v>
-    <v>0</v>
-    <v>Image of Prague</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Bohuslav Svoboda (Mayor)</v>
-    <v>d22dc65d-617c-120b-8290-4e1215938b85</v>
-    <v>en-US</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="3">
-    <v>154</v>
-  </rv>
-  <rv s="4">
-    <v>https://www.bing.com/search?q=prague+czech+republic&amp;form=skydnc</v>
-    <v>Learn more on Bing</v>
-  </rv>
-  <rv s="1">
-    <fb>1357326</fb>
-    <v>8</v>
-  </rv>
-  <rv s="25">
-    <v>#VALUE!</v>
-    <v>en-US</v>
-    <v>a3446df9-1e81-03b1-d08c-0593eead811a</v>
-    <v>536870912</v>
-    <v>1</v>
-    <v>399</v>
-    <v>400</v>
-    <v>Prague</v>
-    <v>4</v>
-    <v>5</v>
-    <v>Map</v>
-    <v>6</v>
-    <v>160</v>
-    <v>CZ-10</v>
-    <v>2634</v>
-    <v>2635</v>
-    <v>Prague is the capital and largest city of the Czech Republic and the historical capital of Bohemia. Situated on the Vltava river, Prague is home to about 1.4 million people. Prague is a political, cultural, and economic hub of Central Europe, ...</v>
-    <v>2636</v>
+    <v>2554</v>
+    <v>2555</v>
     <v>2638</v>
     <v>2639</v>
-    <v>Prague</v>
     <v>2640</v>
-    <v>1136</v>
-    <v>Prague</v>
-    <v>mdp/vdpid/9446826</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Slovakia</v>
-    <v>edb4720a-f85f-2ef3-4669-e9de895513b0</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="1">
-    <fb>0.39226289517470903</fb>
-    <v>29</v>
-  </rv>
-  <rv s="1">
-    <fb>49035</fb>
+    <v>2641</v>
+    <v>2642</v>
+    <v>Russia</v>
+    <v>2643</v>
+    <v>mdp/vdpid/203</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Austria</v>
+    <v>c3f78b59-5e8d-133a-d0e2-ff2e71c4a5d5</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="1">
+    <fb>0.32356676139641499</fb>
+    <v>29</v>
+  </rv>
+  <rv s="1">
+    <fb>83878.990000000005</fb>
     <v>8</v>
   </rv>
   <rv s="1">
-    <fb>16000</fb>
+    <fb>43</fb>
+    <v>31</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Vienna</v>
+    <v>a844b6d2-ff6e-902b-d359-8f7db08f7bb9</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="1">
+    <fb>61447.919000000002</fb>
     <v>8</v>
   </rv>
   <rv s="1">
-    <fb>421</fb>
-    <v>31</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Bratislava</v>
-    <v>58b70fde-dfcf-1beb-05ed-c5baeec68486</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="1">
-    <fb>32423.614000000001</fb>
+    <fb>118.057979804947</fb>
+    <v>32</v>
+  </rv>
+  <rv s="1">
+    <fb>1.5308955342270201E-2</fb>
+    <v>29</v>
+  </rv>
+  <rv s="1">
+    <fb>8355.8419518213395</fb>
     <v>8</v>
   </rv>
   <rv s="1">
-    <fb>115.338987748767</fb>
-    <v>32</v>
-  </rv>
-  <rv s="1">
-    <fb>2.6645613342544297E-2</fb>
-    <v>29</v>
-  </rv>
-  <rv s="1">
-    <fb>5137.0738351939799</fb>
-    <v>8</v>
-  </rv>
-  <rv s="1">
-    <fb>0.40353576355488302</fb>
-    <v>29</v>
-  </rv>
-  <rv s="1">
-    <fb>64.091495098880202</fb>
+    <fb>1.47</fb>
+    <v>30</v>
+  </rv>
+  <rv s="1">
+    <fb>0.46905712836916402</fb>
+    <v>29</v>
+  </rv>
+  <rv s="1">
+    <fb>65.661821989472699</fb>
     <v>33</v>
   </rv>
   <rv s="1">
-    <fb>1.32</fb>
+    <fb>1.2</fb>
     <v>34</v>
   </rv>
   <rv s="1">
-    <fb>105422304975.576</fb>
+    <fb>446314739528.46997</fb>
     <v>35</v>
   </rv>
   <rv s="1">
-    <fb>0.98732050000000005</fb>
-    <v>29</v>
-  </rv>
-  <rv s="1">
-    <fb>0.46634390000000003</fb>
+    <fb>1.0311315000000001</fb>
+    <v>29</v>
+  </rv>
+  <rv s="1">
+    <fb>0.85057140000000009</fb>
     <v>29</v>
   </rv>
   <rv s="2">
@@ -23685,180 +23862,173 @@
     <v>402</v>
     <v>7</v>
     <v>0</v>
-    <v>Image of Slovakia</v>
-  </rv>
-  <rv s="1">
-    <fb>4.5999999999999996</fb>
+    <v>Image of Austria</v>
+  </rv>
+  <rv s="1">
+    <fb>2.9</fb>
     <v>33</v>
   </rv>
   <rv s="0">
     <v>805306368</v>
-    <v>Peter Pellegrini (President)</v>
-    <v>f629decd-819c-5335-3056-a303e967b3ef</v>
+    <v>Alexander Van der Bellen (President)</v>
+    <v>09a88c4e-ba78-3b88-7539-fedb6d48b4a2</v>
     <v>en-US</v>
     <v>Generic</v>
   </rv>
   <rv s="0">
     <v>805306368</v>
-    <v>Robert Fico (Prime minister)</v>
-    <v>8e083165-c1e0-fe2d-8b3f-c60ab5f7ccbc</v>
+    <v>Alexander Schallenberg (Chancellor)</v>
+    <v>6a2cc2d0-2c8f-3759-887b-96e073689083</v>
     <v>en-US</v>
     <v>Generic</v>
-  </rv>
-  <rv s="3">
-    <v>155</v>
-  </rv>
-  <rv s="4">
-    <v>https://www.bing.com/search?q=slovakia&amp;form=skydnc</v>
-    <v>Learn more on Bing</v>
-  </rv>
-  <rv s="1">
-    <fb>77.165853658536605</fb>
-    <v>33</v>
-  </rv>
-  <rv s="1">
-    <fb>4801320000</fb>
-    <v>35</v>
-  </rv>
-  <rv s="1">
-    <fb>3.11</fb>
-    <v>34</v>
   </rv>
   <rv s="3">
     <v>156</v>
   </rv>
-  <rv s="1">
-    <fb>0.18443573520000001</fb>
-    <v>29</v>
-  </rv>
-  <rv s="1">
-    <fb>3.4156</fb>
-    <v>30</v>
-  </rv>
-  <rv s="1">
-    <fb>5431752</fb>
-    <v>8</v>
-  </rv>
-  <rv s="1">
-    <fb>0.23199999999999998</fb>
-    <v>29</v>
-  </rv>
-  <rv s="1">
-    <fb>8.6999999999999994E-2</fb>
-    <v>29</v>
-  </rv>
-  <rv s="1">
-    <fb>0.19</fb>
-    <v>29</v>
-  </rv>
-  <rv s="1">
-    <fb>0.59541000366210906</fb>
-    <v>29</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Bratislava Region</v>
-    <v>e637bf19-eeaa-4459-9caf-f56123dbf175</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Trnava Region</v>
-    <v>4f2bb7cb-6583-4c39-9bf0-d4e3bb63dc18</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Nitra Region</v>
-    <v>d1ead58e-466d-468e-a927-7b14d511bee9</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Trenčín Region</v>
-    <v>20297534-639a-464f-90d3-81da4026bd2b</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Žilina Region</v>
-    <v>712f0aa7-5c71-4ca0-b231-743ce5252eb2</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Banská Bystrica Region</v>
-    <v>2e442f08-059f-48a2-8f6e-cbe382c50935</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Košice Region</v>
-    <v>d93306fe-d07e-40fc-876e-e0ebf15d5b24</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Prešov Region</v>
-    <v>9ed1d64f-c597-423c-8a57-6c255167c0ef</v>
-    <v>en-US</v>
-    <v>Map</v>
+  <rv s="4">
+    <v>https://www.bing.com/search?q=austria&amp;form=skydnc</v>
+    <v>Learn more on Bing</v>
+  </rv>
+  <rv s="1">
+    <fb>81.643902439024401</fb>
+    <v>33</v>
+  </rv>
+  <rv s="1">
+    <fb>133098220000</fb>
+    <v>35</v>
   </rv>
   <rv s="3">
     <v>157</v>
   </rv>
   <rv s="1">
-    <fb>0.18701973520562698</fb>
-    <v>29</v>
-  </rv>
-  <rv s="1">
-    <fb>0.49700000000000005</fb>
-    <v>29</v>
-  </rv>
-  <rv s="1">
-    <fb>5.56099987030029E-2</fb>
+    <fb>0.179240277</fb>
+    <v>29</v>
+  </rv>
+  <rv s="1">
+    <fb>5.1696999999999997</fb>
+    <v>30</v>
+  </rv>
+  <rv s="1">
+    <fb>9042528</fb>
+    <v>8</v>
+  </rv>
+  <rv s="1">
+    <fb>0.37799999999999995</fb>
+    <v>29</v>
+  </rv>
+  <rv s="1">
+    <fb>0.08</fb>
+    <v>29</v>
+  </rv>
+  <rv s="1">
+    <fb>0.17800000000000002</fb>
+    <v>29</v>
+  </rv>
+  <rv s="1">
+    <fb>0.60683998107910198</fb>
+    <v>29</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Burgenland</v>
+    <v>20b1c17e-6204-a0df-6047-2725dec16761</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Carinthia</v>
+    <v>5e37573b-7455-bff5-b6e2-1efd0b0d6059</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Lower Austria</v>
+    <v>4dcd6132-5fe3-19ce-a37c-ff75732178e2</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Upper Austria</v>
+    <v>5eda3d8d-2623-8c5c-71b9-98e76b245f37</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Salzburg</v>
+    <v>f1e6feb1-ca38-e293-2657-06a535e7d8ed</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Styria</v>
+    <v>27e5c768-8121-a58a-3641-f4576289d790</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Tyrol</v>
+    <v>bbfb1e8f-7c58-8f12-9249-9ff4d210f1d6</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Vorarlberg</v>
+    <v>515e6b8f-2ef0-2ac9-184c-2834f6770193</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="3">
+    <v>158</v>
+  </rv>
+  <rv s="1">
+    <fb>0.25405547466329398</fb>
+    <v>29</v>
+  </rv>
+  <rv s="1">
+    <fb>0.51400000000000001</fb>
+    <v>29</v>
+  </rv>
+  <rv s="1">
+    <fb>4.6739997863769499E-2</fb>
     <v>36</v>
   </rv>
   <rv s="1">
-    <fb>2930419</fb>
+    <fb>5194416</fb>
     <v>8</v>
   </rv>
-  <rv s="6">
+  <rv s="20">
     <v>#VALUE!</v>
     <v>en-US</v>
-    <v>edb4720a-f85f-2ef3-4669-e9de895513b0</v>
+    <v>c3f78b59-5e8d-133a-d0e2-ff2e71c4a5d5</v>
     <v>536870912</v>
     <v>1</v>
     <v>405</v>
-    <v>27</v>
-    <v>Slovakia</v>
+    <v>279</v>
+    <v>Austria</v>
     <v>4</v>
     <v>5</v>
     <v>Map</v>
     <v>6</v>
-    <v>406</v>
-    <v>SK</v>
-    <v>2643</v>
-    <v>2644</v>
-    <v>2645</v>
-    <v>2352</v>
+    <v>208</v>
+    <v>AT</v>
     <v>2646</v>
     <v>2647</v>
+    <v>1954</v>
+    <v>1362</v>
     <v>2648</v>
     <v>2649</v>
     <v>2650</v>
+    <v>2651</v>
+    <v>2652</v>
     <v>EUR</v>
-    <v>Slovakia, officially the Slovak Republic, is a landlocked country in Central Europe. It is bordered by Poland to the north, Ukraine to the east, Hungary to the south, Austria to the west, and the Czech Republic to the northwest. Slovakia's ...</v>
-    <v>2651</v>
-    <v>1962</v>
-    <v>2652</v>
+    <v>Austria, formally the Republic of Austria, is a landlocked country in Central Europe, lying in the Eastern Alps. It is a federation of nine states, of which the capital Vienna is the most populous city and state. Austria is bordered by Germany ...</v>
     <v>2653</v>
     <v>2654</v>
     <v>2655</v>
@@ -23866,663 +24036,712 @@
     <v>2657</v>
     <v>2658</v>
     <v>2659</v>
-    <v>2647</v>
+    <v>2660</v>
+    <v>2661</v>
     <v>2662</v>
-    <v>2663</v>
-    <v>2664</v>
+    <v>2649</v>
     <v>2665</v>
+    <v>2666</v>
+    <v>2667</v>
+    <v>2668</v>
     <v>1053</v>
-    <v>2666</v>
-    <v>Slovakia</v>
-    <v>Nad Tatrou sa blýska</v>
-    <v>2667</v>
-    <v>Slovenská republika</v>
-    <v>2668</v>
+    <v>Austria</v>
+    <v>National anthem of Austria</v>
     <v>2669</v>
+    <v>Österreich</v>
     <v>2670</v>
     <v>2671</v>
-    <v>1696</v>
-    <v>1354</v>
-    <v>253</v>
     <v>2672</v>
-    <v>616</v>
+    <v>1810</v>
+    <v>254</v>
     <v>2673</v>
+    <v>484</v>
     <v>2674</v>
-    <v>2683</v>
-    <v>2684</v>
-    <v>1288</v>
+    <v>210</v>
+    <v>2675</v>
+    <v>2676</v>
     <v>2685</v>
     <v>2686</v>
-    <v>Slovakia</v>
+    <v>1288</v>
     <v>2687</v>
-    <v>mdp/vdpid/143</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>South Korea</v>
-    <v>c0e15be0-5113-402c-c03f-516a6265e9cb</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="1">
-    <fb>0.17446070640579101</fb>
-    <v>29</v>
-  </rv>
-  <rv s="1">
-    <fb>100295</fb>
+    <v>2688</v>
+    <v>Austria</v>
+    <v>2689</v>
+    <v>mdp/vdpid/14</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Prague</v>
+    <v>a3446df9-1e81-03b1-d08c-0593eead811a</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="1">
+    <fb>496.21</fb>
     <v>8</v>
   </rv>
-  <rv s="1">
-    <fb>634000</fb>
-    <v>8</v>
-  </rv>
-  <rv s="1">
-    <fb>6.4</fb>
-    <v>30</v>
-  </rv>
-  <rv s="1">
-    <fb>82</fb>
-    <v>31</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Seoul</v>
-    <v>669b47ba-40b4-0147-3657-a7dd0861132c</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="1">
-    <fb>620302.38600000006</fb>
-    <v>8</v>
-  </rv>
-  <rv s="1">
-    <fb>115.15858742558</fb>
-    <v>32</v>
-  </rv>
-  <rv s="1">
-    <fb>3.8294613224406E-3</fb>
-    <v>29</v>
-  </rv>
-  <rv s="1">
-    <fb>10496.5136719641</fb>
-    <v>8</v>
-  </rv>
-  <rv s="1">
-    <fb>0.97699999999999998</fb>
-    <v>30</v>
-  </rv>
-  <rv s="1">
-    <fb>0.63354836492977906</fb>
-    <v>29</v>
-  </rv>
-  <rv s="1">
-    <fb>81.028475807144503</fb>
-    <v>33</v>
-  </rv>
-  <rv s="1">
-    <fb>1.22</fb>
-    <v>34</v>
-  </rv>
-  <rv s="1">
-    <fb>2029000000000</fb>
-    <v>35</v>
-  </rv>
-  <rv s="1">
-    <fb>0.98088600000000004</fb>
-    <v>29</v>
-  </rv>
-  <rv s="1">
-    <fb>0.94349689999999997</fb>
-    <v>29</v>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Austria-Hungary</v>
+    <v>09b8630d-3ac1-93e8-a27e-b8a55de26a17</v>
+    <v>en-US</v>
+    <v>Map</v>
   </rv>
   <rv s="2">
     <v>88</v>
     <v>6</v>
-    <v>408</v>
+    <v>406</v>
     <v>7</v>
     <v>0</v>
-    <v>Image of South Korea</v>
-  </rv>
-  <rv s="1">
-    <fb>2.7</fb>
-    <v>33</v>
+    <v>Image of Prague</v>
   </rv>
   <rv s="0">
     <v>805306368</v>
-    <v>Yoon Suk Yeol (President)</v>
-    <v>af8383ab-575b-52df-438a-1678504626cd</v>
+    <v>Bohuslav Svoboda (Mayor)</v>
+    <v>d22dc65d-617c-120b-8290-4e1215938b85</v>
     <v>en-US</v>
     <v>Generic</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Choi Sang-mok (President)</v>
-    <v>6d3217c1-26df-bcef-6a5b-413608e6ec60</v>
-    <v>en-US</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Han Duck-soo (Prime minister)</v>
-    <v>058dfd81-df36-7fb6-eadf-9736baef167f</v>
-    <v>en-US</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Choi Sang-mok (Prime minister)</v>
-    <v>6d3217c1-26df-bcef-6a5b-413608e6ec60</v>
-    <v>en-US</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="3">
-    <v>158</v>
-  </rv>
-  <rv s="4">
-    <v>https://www.bing.com/search?q=south+korea&amp;form=skydnc</v>
-    <v>Learn more on Bing</v>
-  </rv>
-  <rv s="1">
-    <fb>82.626829268292695</fb>
-    <v>33</v>
-  </rv>
-  <rv s="1">
-    <fb>1413716510000</fb>
-    <v>35</v>
-  </rv>
-  <rv s="1">
-    <fb>6.49</fb>
-    <v>34</v>
   </rv>
   <rv s="3">
     <v>159</v>
   </rv>
-  <rv s="1">
-    <fb>0.36792971710000005</fb>
-    <v>29</v>
-  </rv>
-  <rv s="1">
-    <fb>2.3607999999999998</fb>
-    <v>30</v>
-  </rv>
-  <rv s="1">
-    <fb>51628117</fb>
+  <rv s="4">
+    <v>https://www.bing.com/search?q=prague+czech+republic&amp;form=skydnc</v>
+    <v>Learn more on Bing</v>
+  </rv>
+  <rv s="1">
+    <fb>1357326</fb>
     <v>8</v>
   </rv>
-  <rv s="1">
-    <fb>0.39</fb>
-    <v>29</v>
-  </rv>
-  <rv s="1">
-    <fb>2.6000000000000002E-2</fb>
-    <v>29</v>
-  </rv>
-  <rv s="1">
-    <fb>0.62970001220703098</fb>
-    <v>29</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Busan</v>
-    <v>ab78ce75-913b-16f3-a3d1-72a46c7e4c42</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Daegu</v>
-    <v>ed9efeb7-692d-e93b-eeff-c93b6f906f73</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Incheon</v>
-    <v>251c93a5-c29d-4e48-dd3f-1d5ac7861fa3</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Gwangju</v>
-    <v>1ceff0b5-a865-dd51-d697-9fee8740447e</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Daejeon</v>
-    <v>6f5216bc-1581-3eaa-8a74-f4122af47cdd</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Ulsan</v>
-    <v>91c0546f-5834-7fd6-735f-542bc70be1cf</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Sejong City</v>
-    <v>4b3538fb-9c24-d852-b122-f107916a0663</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Gyeonggi Province</v>
-    <v>6b578621-8b2d-13ef-1af0-281a90a0fd92</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Gangwon Province, South Korea</v>
-    <v>969f749a-ed96-7379-b76c-a7fc63af8e94</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>North Chungcheong Province</v>
-    <v>ea7cdefc-04fe-45be-8ac1-07b9a4d6dc32</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>South Chungcheong Province</v>
-    <v>302fa333-ce2a-affc-c170-5f8d18500d9b</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>North Jeolla Province</v>
-    <v>d8cda014-25af-90ec-91e8-3b7ffccc6380</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>South Jeolla Province</v>
-    <v>9a4dcd3b-649f-605b-aee3-3f6dcf5c3680</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>North Gyeongsang Province</v>
-    <v>44899bdf-131d-a103-5b55-bb862b8d3bf3</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>South Gyeongsang Province</v>
-    <v>86e32791-8efc-1d3b-3a8f-1b9d6fd990a1</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Jeju Province</v>
-    <v>30be7545-0861-845d-8d83-ec99d53fc5d9</v>
-    <v>en-US</v>
-    <v>Map</v>
+  <rv s="26">
+    <v>#VALUE!</v>
+    <v>en-US</v>
+    <v>a3446df9-1e81-03b1-d08c-0593eead811a</v>
+    <v>536870912</v>
+    <v>1</v>
+    <v>408</v>
+    <v>409</v>
+    <v>Prague</v>
+    <v>4</v>
+    <v>5</v>
+    <v>Map</v>
+    <v>6</v>
+    <v>160</v>
+    <v>CZ-10</v>
+    <v>2692</v>
+    <v>2693</v>
+    <v>Prague is the capital and largest city of the Czech Republic and the historical capital of Bohemia. Situated on the Vltava river, Prague is home to about 1.4 million people. Prague is a political, cultural, and economic hub of Central Europe, ...</v>
+    <v>2694</v>
+    <v>2696</v>
+    <v>2697</v>
+    <v>Prague</v>
+    <v>2698</v>
+    <v>1136</v>
+    <v>Prague</v>
+    <v>mdp/vdpid/9446826</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Slovakia</v>
+    <v>edb4720a-f85f-2ef3-4669-e9de895513b0</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="1">
+    <fb>0.39226289517470903</fb>
+    <v>29</v>
+  </rv>
+  <rv s="1">
+    <fb>49035</fb>
+    <v>8</v>
+  </rv>
+  <rv s="1">
+    <fb>16000</fb>
+    <v>8</v>
+  </rv>
+  <rv s="1">
+    <fb>421</fb>
+    <v>31</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Bratislava</v>
+    <v>58b70fde-dfcf-1beb-05ed-c5baeec68486</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="1">
+    <fb>32423.614000000001</fb>
+    <v>8</v>
+  </rv>
+  <rv s="1">
+    <fb>115.338987748767</fb>
+    <v>32</v>
+  </rv>
+  <rv s="1">
+    <fb>2.6645613342544297E-2</fb>
+    <v>29</v>
+  </rv>
+  <rv s="1">
+    <fb>5137.0738351939799</fb>
+    <v>8</v>
+  </rv>
+  <rv s="1">
+    <fb>0.40353576355488302</fb>
+    <v>29</v>
+  </rv>
+  <rv s="1">
+    <fb>64.091495098880202</fb>
+    <v>33</v>
+  </rv>
+  <rv s="1">
+    <fb>1.32</fb>
+    <v>34</v>
+  </rv>
+  <rv s="1">
+    <fb>105422304975.576</fb>
+    <v>35</v>
+  </rv>
+  <rv s="1">
+    <fb>0.98732050000000005</fb>
+    <v>29</v>
+  </rv>
+  <rv s="1">
+    <fb>0.46634390000000003</fb>
+    <v>29</v>
+  </rv>
+  <rv s="2">
+    <v>89</v>
+    <v>6</v>
+    <v>411</v>
+    <v>7</v>
+    <v>0</v>
+    <v>Image of Slovakia</v>
+  </rv>
+  <rv s="1">
+    <fb>4.5999999999999996</fb>
+    <v>33</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Peter Pellegrini (President)</v>
+    <v>f629decd-819c-5335-3056-a303e967b3ef</v>
+    <v>en-US</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Robert Fico (Prime minister)</v>
+    <v>8e083165-c1e0-fe2d-8b3f-c60ab5f7ccbc</v>
+    <v>en-US</v>
+    <v>Generic</v>
   </rv>
   <rv s="3">
     <v>160</v>
   </rv>
-  <rv s="1">
-    <fb>0.15574911728035101</fb>
-    <v>29</v>
+  <rv s="4">
+    <v>https://www.bing.com/search?q=slovakia&amp;form=skydnc</v>
+    <v>Learn more on Bing</v>
+  </rv>
+  <rv s="1">
+    <fb>77.165853658536605</fb>
+    <v>33</v>
+  </rv>
+  <rv s="1">
+    <fb>4801320000</fb>
+    <v>35</v>
+  </rv>
+  <rv s="1">
+    <fb>3.11</fb>
+    <v>34</v>
   </rv>
   <rv s="3">
     <v>161</v>
   </rv>
   <rv s="1">
-    <fb>0.33200000000000002</fb>
-    <v>29</v>
-  </rv>
-  <rv s="1">
-    <fb>4.1479997634887703E-2</fb>
+    <fb>0.18443573520000001</fb>
+    <v>29</v>
+  </rv>
+  <rv s="1">
+    <fb>3.4156</fb>
+    <v>30</v>
+  </rv>
+  <rv s="1">
+    <fb>5431752</fb>
+    <v>8</v>
+  </rv>
+  <rv s="1">
+    <fb>0.23199999999999998</fb>
+    <v>29</v>
+  </rv>
+  <rv s="1">
+    <fb>8.6999999999999994E-2</fb>
+    <v>29</v>
+  </rv>
+  <rv s="1">
+    <fb>0.19</fb>
+    <v>29</v>
+  </rv>
+  <rv s="1">
+    <fb>0.59541000366210906</fb>
+    <v>29</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Bratislava Region</v>
+    <v>e637bf19-eeaa-4459-9caf-f56123dbf175</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Trnava Region</v>
+    <v>4f2bb7cb-6583-4c39-9bf0-d4e3bb63dc18</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Nitra Region</v>
+    <v>d1ead58e-466d-468e-a927-7b14d511bee9</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Trenčín Region</v>
+    <v>20297534-639a-464f-90d3-81da4026bd2b</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Žilina Region</v>
+    <v>712f0aa7-5c71-4ca0-b231-743ce5252eb2</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Banská Bystrica Region</v>
+    <v>2e442f08-059f-48a2-8f6e-cbe382c50935</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Košice Region</v>
+    <v>d93306fe-d07e-40fc-876e-e0ebf15d5b24</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Prešov Region</v>
+    <v>9ed1d64f-c597-423c-8a57-6c255167c0ef</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="3">
+    <v>162</v>
+  </rv>
+  <rv s="1">
+    <fb>0.18701973520562698</fb>
+    <v>29</v>
+  </rv>
+  <rv s="1">
+    <fb>0.49700000000000005</fb>
+    <v>29</v>
+  </rv>
+  <rv s="1">
+    <fb>5.56099987030029E-2</fb>
     <v>36</v>
   </rv>
   <rv s="1">
-    <fb>42106719</fb>
+    <fb>2930419</fb>
     <v>8</v>
   </rv>
   <rv s="6">
     <v>#VALUE!</v>
     <v>en-US</v>
-    <v>c0e15be0-5113-402c-c03f-516a6265e9cb</v>
+    <v>edb4720a-f85f-2ef3-4669-e9de895513b0</v>
     <v>536870912</v>
     <v>1</v>
-    <v>412</v>
+    <v>414</v>
     <v>27</v>
-    <v>South Korea</v>
+    <v>Slovakia</v>
     <v>4</v>
     <v>5</v>
     <v>Map</v>
     <v>6</v>
-    <v>413</v>
-    <v>KR</v>
-    <v>2690</v>
-    <v>2691</v>
-    <v>2692</v>
-    <v>2693</v>
-    <v>2694</v>
-    <v>2695</v>
-    <v>2696</v>
-    <v>2697</v>
-    <v>2698</v>
-    <v>KRW</v>
-    <v>South Korea, officially the Republic of Korea, is a country in East Asia. It constitutes the southern half of the Korean Peninsula and borders North Korea along the Korean Demilitarized Zone, with the Yellow Sea to the west and the Sea of Japan ...</v>
-    <v>2699</v>
-    <v>2700</v>
+    <v>415</v>
+    <v>SK</v>
     <v>2701</v>
     <v>2702</v>
     <v>2703</v>
+    <v>2352</v>
     <v>2704</v>
     <v>2705</v>
     <v>2706</v>
     <v>2707</v>
     <v>2708</v>
-    <v>2695</v>
+    <v>EUR</v>
+    <v>Slovakia, officially the Slovak Republic, is a landlocked country in Central Europe. It is bordered by Poland to the north, Ukraine to the east, Hungary to the south, Austria to the west, and the Czech Republic to the northwest. Slovakia's ...</v>
+    <v>2709</v>
+    <v>1962</v>
+    <v>2710</v>
+    <v>2711</v>
+    <v>2712</v>
     <v>2713</v>
     <v>2714</v>
     <v>2715</v>
     <v>2716</v>
-    <v>2452</v>
     <v>2717</v>
-    <v>South Korea</v>
-    <v>Aegukga</v>
-    <v>2718</v>
-    <v>대한민국</v>
-    <v>2719</v>
+    <v>2705</v>
     <v>2720</v>
     <v>2721</v>
-    <v>2671</v>
-    <v>2386</v>
     <v>2722</v>
     <v>2723</v>
-    <v>568</v>
-    <v>244</v>
-    <v>1390</v>
+    <v>1053</v>
     <v>2724</v>
+    <v>Slovakia</v>
+    <v>Nad Tatrou sa blýska</v>
+    <v>2725</v>
+    <v>Slovenská republika</v>
+    <v>2726</v>
+    <v>2727</v>
+    <v>2728</v>
+    <v>2729</v>
+    <v>1696</v>
+    <v>1354</v>
+    <v>253</v>
+    <v>2730</v>
+    <v>616</v>
+    <v>2731</v>
+    <v>2732</v>
     <v>2741</v>
     <v>2742</v>
+    <v>1288</v>
     <v>2743</v>
     <v>2744</v>
+    <v>Slovakia</v>
     <v>2745</v>
+    <v>mdp/vdpid/143</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
     <v>South Korea</v>
-    <v>2746</v>
-    <v>mdp/vdpid/134</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>South Africa</v>
-    <v>38a9fd4a-4f7c-6d91-d6dd-4eed3131672d</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="1">
-    <fb>0.79830020855830996</fb>
-    <v>29</v>
-  </rv>
-  <rv s="1">
-    <fb>1221037</fb>
+    <v>c0e15be0-5113-402c-c03f-516a6265e9cb</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="1">
+    <fb>0.17446070640579101</fb>
+    <v>29</v>
+  </rv>
+  <rv s="1">
+    <fb>100295</fb>
     <v>8</v>
   </rv>
   <rv s="1">
-    <fb>80000</fb>
+    <fb>634000</fb>
     <v>8</v>
   </rv>
   <rv s="1">
-    <fb>20.51</fb>
+    <fb>6.4</fb>
     <v>30</v>
   </rv>
   <rv s="1">
-    <fb>27</fb>
+    <fb>82</fb>
     <v>31</v>
   </rv>
   <rv s="0">
     <v>536870912</v>
-    <v>Pretoria</v>
-    <v>3fa43cca-3409-4d81-f4f9-2df74e37e177</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="1">
-    <fb>476643.99400000001</fb>
+    <v>Seoul</v>
+    <v>669b47ba-40b4-0147-3657-a7dd0861132c</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="1">
+    <fb>620302.38600000006</fb>
     <v>8</v>
   </rv>
   <rv s="1">
-    <fb>158.92793752218699</fb>
+    <fb>115.15858742558</fb>
     <v>32</v>
   </rv>
   <rv s="1">
-    <fb>4.1243507248623905E-2</fb>
-    <v>29</v>
-  </rv>
-  <rv s="1">
-    <fb>4197.9070469175304</fb>
+    <fb>3.8294613224406E-3</fb>
+    <v>29</v>
+  </rv>
+  <rv s="1">
+    <fb>10496.5136719641</fb>
     <v>8</v>
   </rv>
   <rv s="1">
-    <fb>2.4049999999999998</fb>
+    <fb>0.97699999999999998</fb>
     <v>30</v>
   </rv>
   <rv s="1">
-    <fb>7.6177365240831296E-2</fb>
-    <v>29</v>
-  </rv>
-  <rv s="1">
-    <fb>86.791431691401598</fb>
+    <fb>0.63354836492977906</fb>
+    <v>29</v>
+  </rv>
+  <rv s="1">
+    <fb>81.028475807144503</fb>
     <v>33</v>
   </rv>
   <rv s="1">
-    <fb>0.92</fb>
+    <fb>1.22</fb>
     <v>34</v>
   </rv>
   <rv s="1">
-    <fb>351431649241.43903</fb>
+    <fb>2029000000000</fb>
     <v>35</v>
   </rv>
   <rv s="1">
-    <fb>1.0086473</fb>
-    <v>29</v>
-  </rv>
-  <rv s="1">
-    <fb>0.22366029999999998</fb>
+    <fb>0.98088600000000004</fb>
+    <v>29</v>
+  </rv>
+  <rv s="1">
+    <fb>0.94349689999999997</fb>
     <v>29</v>
   </rv>
   <rv s="2">
-    <v>89</v>
+    <v>90</v>
     <v>6</v>
-    <v>415</v>
+    <v>417</v>
     <v>7</v>
     <v>0</v>
-    <v>Image of South Africa</v>
-  </rv>
-  <rv s="1">
-    <fb>28.5</fb>
+    <v>Image of South Korea</v>
+  </rv>
+  <rv s="1">
+    <fb>2.7</fb>
     <v>33</v>
   </rv>
   <rv s="0">
-    <v>536870912</v>
-    <v>Johannesburg</v>
-    <v>fdf01f15-cb04-8b6c-43e6-a8b2138c0312</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
     <v>805306368</v>
-    <v>Cyril Ramaphosa (President)</v>
-    <v>c3bf14fa-ef5e-696f-af28-746c7d0b22a9</v>
+    <v>Yoon Suk Yeol (President)</v>
+    <v>af8383ab-575b-52df-438a-1678504626cd</v>
     <v>en-US</v>
     <v>Generic</v>
   </rv>
   <rv s="0">
     <v>805306368</v>
-    <v>Mandisa Maya (Chief justice)</v>
-    <v>d7f4df4e-1431-de9c-d625-ad5005dd70e1</v>
+    <v>Choi Sang-mok (President)</v>
+    <v>6d3217c1-26df-bcef-6a5b-413608e6ec60</v>
     <v>en-US</v>
     <v>Generic</v>
   </rv>
-  <rv s="3">
-    <v>162</v>
-  </rv>
-  <rv s="4">
-    <v>https://www.bing.com/search?q=south+africa&amp;form=skydnc</v>
-    <v>Learn more on Bing</v>
-  </rv>
-  <rv s="1">
-    <fb>63.856999999999999</fb>
-    <v>33</v>
-  </rv>
-  <rv s="1">
-    <fb>1056341440000</fb>
-    <v>35</v>
-  </rv>
-  <rv s="1">
-    <fb>119</fb>
-    <v>33</v>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Han Duck-soo (Prime minister)</v>
+    <v>058dfd81-df36-7fb6-eadf-9736baef167f</v>
+    <v>en-US</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Choi Sang-mok (Prime minister)</v>
+    <v>6d3217c1-26df-bcef-6a5b-413608e6ec60</v>
+    <v>en-US</v>
+    <v>Generic</v>
   </rv>
   <rv s="3">
     <v>163</v>
   </rv>
-  <rv s="1">
-    <fb>7.6985469299999998E-2</fb>
-    <v>29</v>
-  </rv>
-  <rv s="1">
-    <fb>0.90539999999999998</fb>
-    <v>30</v>
-  </rv>
-  <rv s="1">
-    <fb>59893885</fb>
-    <v>8</v>
-  </rv>
-  <rv s="1">
-    <fb>0.505</fb>
-    <v>29</v>
-  </rv>
-  <rv s="1">
-    <fb>0.68200000000000005</fb>
-    <v>29</v>
-  </rv>
-  <rv s="1">
-    <fb>9.0000000000000011E-3</fb>
-    <v>29</v>
-  </rv>
-  <rv s="1">
-    <fb>0.56016998291015596</fb>
-    <v>29</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Eastern Cape</v>
-    <v>52d32047-22e4-2498-c546-1854275462d0</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Free State</v>
-    <v>a80d303a-f84e-1047-ecc5-821b167d82e2</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Gauteng</v>
-    <v>adc304a6-9c62-702f-7ed7-29afec5c41a8</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>KwaZulu-Natal</v>
-    <v>b18f871a-4296-ec9f-bd43-fc7b0e94f309</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Limpopo</v>
-    <v>1145af3c-da05-7eb5-c05e-8dbdf794ccd4</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Mpumalanga</v>
-    <v>fe8e43ff-3125-ea79-5306-db1bee5c12d8</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>North West</v>
-    <v>a9ca554b-55e2-f0d1-dbe6-796b1fc29dff</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Northern Cape</v>
-    <v>c7811f0b-afea-afb9-4c2d-695826b9ca98</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Western Cape</v>
-    <v>c7b124b8-e75d-0b9b-5245-dda6bbb13800</v>
-    <v>en-US</v>
-    <v>Map</v>
+  <rv s="4">
+    <v>https://www.bing.com/search?q=south+korea&amp;form=skydnc</v>
+    <v>Learn more on Bing</v>
+  </rv>
+  <rv s="1">
+    <fb>82.626829268292695</fb>
+    <v>33</v>
+  </rv>
+  <rv s="1">
+    <fb>1413716510000</fb>
+    <v>35</v>
+  </rv>
+  <rv s="1">
+    <fb>6.49</fb>
+    <v>34</v>
   </rv>
   <rv s="3">
     <v>164</v>
   </rv>
   <rv s="1">
-    <fb>0.27465217966612804</fb>
-    <v>29</v>
+    <fb>0.36792971710000005</fb>
+    <v>29</v>
+  </rv>
+  <rv s="1">
+    <fb>2.3607999999999998</fb>
+    <v>30</v>
+  </rv>
+  <rv s="1">
+    <fb>51628117</fb>
+    <v>8</v>
+  </rv>
+  <rv s="1">
+    <fb>0.39</fb>
+    <v>29</v>
+  </rv>
+  <rv s="1">
+    <fb>2.6000000000000002E-2</fb>
+    <v>29</v>
+  </rv>
+  <rv s="1">
+    <fb>0.62970001220703098</fb>
+    <v>29</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Busan</v>
+    <v>ab78ce75-913b-16f3-a3d1-72a46c7e4c42</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Daegu</v>
+    <v>ed9efeb7-692d-e93b-eeff-c93b6f906f73</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Incheon</v>
+    <v>251c93a5-c29d-4e48-dd3f-1d5ac7861fa3</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Gwangju</v>
+    <v>1ceff0b5-a865-dd51-d697-9fee8740447e</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Daejeon</v>
+    <v>6f5216bc-1581-3eaa-8a74-f4122af47cdd</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Ulsan</v>
+    <v>91c0546f-5834-7fd6-735f-542bc70be1cf</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Sejong City</v>
+    <v>4b3538fb-9c24-d852-b122-f107916a0663</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Gyeonggi Province</v>
+    <v>6b578621-8b2d-13ef-1af0-281a90a0fd92</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Gangwon Province, South Korea</v>
+    <v>969f749a-ed96-7379-b76c-a7fc63af8e94</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>North Chungcheong Province</v>
+    <v>ea7cdefc-04fe-45be-8ac1-07b9a4d6dc32</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>South Chungcheong Province</v>
+    <v>302fa333-ce2a-affc-c170-5f8d18500d9b</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>North Jeolla Province</v>
+    <v>d8cda014-25af-90ec-91e8-3b7ffccc6380</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>South Jeolla Province</v>
+    <v>9a4dcd3b-649f-605b-aee3-3f6dcf5c3680</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>North Gyeongsang Province</v>
+    <v>44899bdf-131d-a103-5b55-bb862b8d3bf3</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>South Gyeongsang Province</v>
+    <v>86e32791-8efc-1d3b-3a8f-1b9d6fd990a1</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Jeju Province</v>
+    <v>30be7545-0861-845d-8d83-ec99d53fc5d9</v>
+    <v>en-US</v>
+    <v>Map</v>
   </rv>
   <rv s="3">
     <v>165</v>
   </rv>
   <rv s="1">
-    <fb>0.29199999999999998</fb>
-    <v>29</v>
-  </rv>
-  <rv s="1">
-    <fb>0.28180999755859398</fb>
+    <fb>0.15574911728035101</fb>
+    <v>29</v>
+  </rv>
+  <rv s="3">
+    <v>166</v>
+  </rv>
+  <rv s="1">
+    <fb>0.33200000000000002</fb>
+    <v>29</v>
+  </rv>
+  <rv s="1">
+    <fb>4.1479997634887703E-2</fb>
     <v>36</v>
   </rv>
   <rv s="1">
-    <fb>39149717</fb>
+    <fb>42106719</fb>
     <v>8</v>
   </rv>
-  <rv s="20">
+  <rv s="6">
     <v>#VALUE!</v>
     <v>en-US</v>
-    <v>38a9fd4a-4f7c-6d91-d6dd-4eed3131672d</v>
+    <v>c0e15be0-5113-402c-c03f-516a6265e9cb</v>
     <v>536870912</v>
     <v>1</v>
-    <v>418</v>
-    <v>279</v>
-    <v>South Africa</v>
+    <v>421</v>
+    <v>27</v>
+    <v>South Korea</v>
     <v>4</v>
     <v>5</v>
     <v>Map</v>
     <v>6</v>
-    <v>419</v>
-    <v>ZA</v>
+    <v>422</v>
+    <v>KR</v>
+    <v>2748</v>
     <v>2749</v>
     <v>2750</v>
     <v>2751</v>
@@ -24531,9 +24750,9 @@
     <v>2754</v>
     <v>2755</v>
     <v>2756</v>
+    <v>KRW</v>
+    <v>South Korea, officially the Republic of Korea, is a country in East Asia. It constitutes the southern half of the Korean Peninsula and borders North Korea along the Korean Demilitarized Zone, with the Yellow Sea to the west and the Sea of Japan ...</v>
     <v>2757</v>
-    <v>ZAR</v>
-    <v>South Africa, officially the Republic of South Africa, is the southernmost country in Africa. Its nine provinces are bounded to the south by 2,798 kilometres of coastline that stretches along the South Atlantic and Indian Ocean; to the north by ...</v>
     <v>2758</v>
     <v>2759</v>
     <v>2760</v>
@@ -24543,435 +24762,747 @@
     <v>2764</v>
     <v>2765</v>
     <v>2766</v>
-    <v>2767</v>
-    <v>2768</v>
+    <v>2753</v>
     <v>2771</v>
     <v>2772</v>
     <v>2773</v>
     <v>2774</v>
+    <v>2452</v>
     <v>2775</v>
-    <v>South Africa</v>
-    <v>National anthem of South Africa</v>
+    <v>South Korea</v>
+    <v>Aegukga</v>
     <v>2776</v>
-    <v>Republic of South Africa</v>
+    <v>대한민국</v>
     <v>2777</v>
     <v>2778</v>
     <v>2779</v>
-    <v>2266</v>
+    <v>2729</v>
+    <v>2386</v>
     <v>2780</v>
     <v>2781</v>
+    <v>568</v>
+    <v>244</v>
+    <v>1390</v>
     <v>2782</v>
-    <v>396</v>
-    <v>728</v>
-    <v>881</v>
-    <v>2783</v>
-    <v>2793</v>
-    <v>2794</v>
-    <v>2795</v>
-    <v>2796</v>
-    <v>2797</v>
-    <v>South Africa</v>
-    <v>2798</v>
-    <v>mdp/vdpid/209</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Argentina</v>
-    <v>87153d87-9bb0-166a-3d56-613bdc274e1b</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="1">
-    <fb>0.54335712119385104</fb>
-    <v>29</v>
-  </rv>
-  <rv s="1">
-    <fb>2780400</fb>
-    <v>8</v>
-  </rv>
-  <rv s="1">
-    <fb>105000</fb>
-    <v>8</v>
-  </rv>
-  <rv s="1">
-    <fb>17.021000000000001</fb>
-    <v>30</v>
-  </rv>
-  <rv s="1">
-    <fb>54</fb>
-    <v>31</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Buenos Aires</v>
-    <v>857a6814-3fe8-c414-84da-24018be87fce</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="1">
-    <fb>201347.636</fb>
-    <v>8</v>
-  </rv>
-  <rv s="1">
-    <fb>232.75109166666701</fb>
-    <v>32</v>
-  </rv>
-  <rv s="1">
-    <fb>0.53548304349234199</fb>
-    <v>29</v>
-  </rv>
-  <rv s="1">
-    <fb>3074.70207056563</fb>
-    <v>8</v>
-  </rv>
-  <rv s="1">
-    <fb>2.2610000000000001</fb>
-    <v>30</v>
-  </rv>
-  <rv s="1">
-    <fb>9.7984058182512504E-2</fb>
-    <v>29</v>
-  </rv>
-  <rv s="1">
-    <fb>87.722407479689195</fb>
-    <v>33</v>
-  </rv>
-  <rv s="1">
-    <fb>1.1000000000000001</fb>
-    <v>34</v>
-  </rv>
-  <rv s="1">
-    <fb>449663446954.073</fb>
-    <v>35</v>
-  </rv>
-  <rv s="1">
-    <fb>1.0974146</fb>
-    <v>29</v>
-  </rv>
-  <rv s="1">
-    <fb>0.89958519999999997</fb>
-    <v>29</v>
-  </rv>
-  <rv s="2">
-    <v>90</v>
-    <v>6</v>
-    <v>421</v>
-    <v>7</v>
-    <v>0</v>
-    <v>Image of Argentina</v>
-  </rv>
-  <rv s="1">
-    <fb>8.8000000000000007</fb>
-    <v>33</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Javier Milei (President)</v>
-    <v>9e292152-d659-8459-891a-e2e34df73a4f</v>
-    <v>en-US</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Victoria Villarruel (Vice president)</v>
-    <v>c9d496be-e912-ca9e-b72e-cd37e371c69a</v>
-    <v>en-US</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="3">
-    <v>166</v>
-  </rv>
-  <rv s="4">
-    <v>https://www.bing.com/search?q=argentina&amp;form=skydnc</v>
-    <v>Learn more on Bing</v>
-  </rv>
-  <rv s="1">
-    <fb>76.52</fb>
-    <v>33</v>
-  </rv>
-  <rv s="1">
-    <fb>39393540000</fb>
-    <v>35</v>
-  </rv>
-  <rv s="1">
-    <fb>39</fb>
-    <v>33</v>
-  </rv>
-  <rv s="1">
-    <fb>3.35</fb>
-    <v>34</v>
-  </rv>
-  <rv s="3">
-    <v>167</v>
-  </rv>
-  <rv s="1">
-    <fb>0.17628076140000001</fb>
-    <v>29</v>
-  </rv>
-  <rv s="1">
-    <fb>3.96</fb>
-    <v>30</v>
-  </rv>
-  <rv s="1">
-    <fb>46234830</fb>
-    <v>8</v>
-  </rv>
-  <rv s="1">
-    <fb>0.46500000000000002</fb>
-    <v>29</v>
-  </rv>
-  <rv s="1">
-    <fb>0.61301998138427694</fb>
-    <v>29</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Buenos Aires Province</v>
-    <v>83e02b50-6d03-7c2c-eadf-7346066b2dea</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Catamarca Province</v>
-    <v>3c1c44fb-1be4-0807-a41a-389b53882281</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Chaco Province</v>
-    <v>7ba7eceb-7d6e-ca38-3de8-8edff91abe6c</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Córdoba Province, Argentina</v>
-    <v>ee360e95-eb6e-6500-1854-d0ba2979c8c5</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Corrientes Province</v>
-    <v>370306e6-e553-7210-5bdd-cba530b5bb5e</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Entre Ríos Province</v>
-    <v>8f271891-a2e7-4452-b33a-32b209204098</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Formosa Province</v>
-    <v>2c10e13d-832d-d54f-08b1-364c9870d186</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Jujuy Province</v>
-    <v>4336eba8-fc73-200e-9d91-4273dd01d498</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>La Pampa Province</v>
-    <v>44de277d-e840-a824-59d9-b6a9740aba03</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>La Rioja Province, Argentina</v>
-    <v>dac821c4-934d-98a0-3515-ecf294d05f34</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Mendoza Province</v>
-    <v>67d55d79-bbf5-f1ea-b2b6-9eaf7f8cbf5c</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Misiones Province</v>
-    <v>b5dd089e-a58d-3344-220d-67d53fbe2b62</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Neuquén Province</v>
-    <v>bf5efd04-a076-eedb-ad38-b133bbf30276</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Río Negro Province</v>
-    <v>d2c8f222-11b8-dd86-e0ab-8d14cb406edc</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Salta Province</v>
-    <v>f6ae2fbd-0520-148c-3526-8bf23d36cb82</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>San Juan Province, Argentina</v>
-    <v>17fa2e93-239c-11e6-f03e-d1c2f5cce2fe</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>San Luis Province</v>
-    <v>5bdf188c-b213-ac45-dd24-12759c1ef35f</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Santa Cruz Province, Argentina</v>
-    <v>33b38460-8bb6-75dd-5a16-ccfffb6378dc</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Santa Fe Province</v>
-    <v>7e0bc671-7ee3-bfe7-3fbf-0780b251b2f6</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Santiago del Estero Province</v>
-    <v>ec88ec56-2be0-4304-ab71-391ce9c013de</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Tierra del Fuego Province, Argentina</v>
-    <v>3bb8cbb1-ced9-fc53-1bf4-d1685a3435ea</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Tucumán Province</v>
-    <v>4f81112c-c69e-b6cc-2acc-73c36fc9a0aa</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Chubut Province</v>
-    <v>893cfb2e-6128-06e8-d927-6cdee06773f8</v>
-    <v>en-US</v>
-    <v>Map</v>
-  </rv>
-  <rv s="3">
-    <v>168</v>
-  </rv>
-  <rv s="1">
-    <fb>0.10087499305375699</fb>
-    <v>29</v>
-  </rv>
-  <rv s="3">
-    <v>169</v>
-  </rv>
-  <rv s="1">
-    <fb>1.0629999999999999</fb>
-    <v>29</v>
-  </rv>
-  <rv s="1">
-    <fb>9.7889995574951205E-2</fb>
-    <v>36</v>
-  </rv>
-  <rv s="1">
-    <fb>41339571</fb>
-    <v>8</v>
-  </rv>
-  <rv s="6">
-    <v>#VALUE!</v>
-    <v>en-US</v>
-    <v>87153d87-9bb0-166a-3d56-613bdc274e1b</v>
-    <v>536870912</v>
-    <v>1</v>
-    <v>424</v>
-    <v>27</v>
-    <v>Argentina</v>
-    <v>4</v>
-    <v>5</v>
-    <v>Map</v>
-    <v>6</v>
-    <v>425</v>
-    <v>AR</v>
+    <v>2799</v>
+    <v>2800</v>
     <v>2801</v>
     <v>2802</v>
     <v>2803</v>
+    <v>South Korea</v>
     <v>2804</v>
-    <v>2805</v>
-    <v>2806</v>
+    <v>mdp/vdpid/134</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>South Africa</v>
+    <v>38a9fd4a-4f7c-6d91-d6dd-4eed3131672d</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="1">
+    <fb>0.79830020855830996</fb>
+    <v>29</v>
+  </rv>
+  <rv s="1">
+    <fb>1221037</fb>
+    <v>8</v>
+  </rv>
+  <rv s="1">
+    <fb>80000</fb>
+    <v>8</v>
+  </rv>
+  <rv s="1">
+    <fb>20.51</fb>
+    <v>30</v>
+  </rv>
+  <rv s="1">
+    <fb>27</fb>
+    <v>31</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Pretoria</v>
+    <v>3fa43cca-3409-4d81-f4f9-2df74e37e177</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="1">
+    <fb>476643.99400000001</fb>
+    <v>8</v>
+  </rv>
+  <rv s="1">
+    <fb>158.92793752218699</fb>
+    <v>32</v>
+  </rv>
+  <rv s="1">
+    <fb>4.1243507248623905E-2</fb>
+    <v>29</v>
+  </rv>
+  <rv s="1">
+    <fb>4197.9070469175304</fb>
+    <v>8</v>
+  </rv>
+  <rv s="1">
+    <fb>2.4049999999999998</fb>
+    <v>30</v>
+  </rv>
+  <rv s="1">
+    <fb>7.6177365240831296E-2</fb>
+    <v>29</v>
+  </rv>
+  <rv s="1">
+    <fb>86.791431691401598</fb>
+    <v>33</v>
+  </rv>
+  <rv s="1">
+    <fb>0.92</fb>
+    <v>34</v>
+  </rv>
+  <rv s="1">
+    <fb>351431649241.43903</fb>
+    <v>35</v>
+  </rv>
+  <rv s="1">
+    <fb>1.0086473</fb>
+    <v>29</v>
+  </rv>
+  <rv s="1">
+    <fb>0.22366029999999998</fb>
+    <v>29</v>
+  </rv>
+  <rv s="2">
+    <v>91</v>
+    <v>6</v>
+    <v>424</v>
+    <v>7</v>
+    <v>0</v>
+    <v>Image of South Africa</v>
+  </rv>
+  <rv s="1">
+    <fb>28.5</fb>
+    <v>33</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Johannesburg</v>
+    <v>fdf01f15-cb04-8b6c-43e6-a8b2138c0312</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Cyril Ramaphosa (President)</v>
+    <v>c3bf14fa-ef5e-696f-af28-746c7d0b22a9</v>
+    <v>en-US</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Mandisa Maya (Chief justice)</v>
+    <v>d7f4df4e-1431-de9c-d625-ad5005dd70e1</v>
+    <v>en-US</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="3">
+    <v>167</v>
+  </rv>
+  <rv s="4">
+    <v>https://www.bing.com/search?q=south+africa&amp;form=skydnc</v>
+    <v>Learn more on Bing</v>
+  </rv>
+  <rv s="1">
+    <fb>63.856999999999999</fb>
+    <v>33</v>
+  </rv>
+  <rv s="1">
+    <fb>1056341440000</fb>
+    <v>35</v>
+  </rv>
+  <rv s="1">
+    <fb>119</fb>
+    <v>33</v>
+  </rv>
+  <rv s="3">
+    <v>168</v>
+  </rv>
+  <rv s="1">
+    <fb>7.6985469299999998E-2</fb>
+    <v>29</v>
+  </rv>
+  <rv s="1">
+    <fb>0.90539999999999998</fb>
+    <v>30</v>
+  </rv>
+  <rv s="1">
+    <fb>59893885</fb>
+    <v>8</v>
+  </rv>
+  <rv s="1">
+    <fb>0.505</fb>
+    <v>29</v>
+  </rv>
+  <rv s="1">
+    <fb>0.68200000000000005</fb>
+    <v>29</v>
+  </rv>
+  <rv s="1">
+    <fb>9.0000000000000011E-3</fb>
+    <v>29</v>
+  </rv>
+  <rv s="1">
+    <fb>0.56016998291015596</fb>
+    <v>29</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Eastern Cape</v>
+    <v>52d32047-22e4-2498-c546-1854275462d0</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Free State</v>
+    <v>a80d303a-f84e-1047-ecc5-821b167d82e2</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Gauteng</v>
+    <v>adc304a6-9c62-702f-7ed7-29afec5c41a8</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>KwaZulu-Natal</v>
+    <v>b18f871a-4296-ec9f-bd43-fc7b0e94f309</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Limpopo</v>
+    <v>1145af3c-da05-7eb5-c05e-8dbdf794ccd4</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Mpumalanga</v>
+    <v>fe8e43ff-3125-ea79-5306-db1bee5c12d8</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>North West</v>
+    <v>a9ca554b-55e2-f0d1-dbe6-796b1fc29dff</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Northern Cape</v>
+    <v>c7811f0b-afea-afb9-4c2d-695826b9ca98</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Western Cape</v>
+    <v>c7b124b8-e75d-0b9b-5245-dda6bbb13800</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="3">
+    <v>169</v>
+  </rv>
+  <rv s="1">
+    <fb>0.27465217966612804</fb>
+    <v>29</v>
+  </rv>
+  <rv s="3">
+    <v>170</v>
+  </rv>
+  <rv s="1">
+    <fb>0.29199999999999998</fb>
+    <v>29</v>
+  </rv>
+  <rv s="1">
+    <fb>0.28180999755859398</fb>
+    <v>36</v>
+  </rv>
+  <rv s="1">
+    <fb>39149717</fb>
+    <v>8</v>
+  </rv>
+  <rv s="20">
+    <v>#VALUE!</v>
+    <v>en-US</v>
+    <v>38a9fd4a-4f7c-6d91-d6dd-4eed3131672d</v>
+    <v>536870912</v>
+    <v>1</v>
+    <v>427</v>
+    <v>279</v>
+    <v>South Africa</v>
+    <v>4</v>
+    <v>5</v>
+    <v>Map</v>
+    <v>6</v>
+    <v>428</v>
+    <v>ZA</v>
     <v>2807</v>
     <v>2808</v>
     <v>2809</v>
-    <v>ARS</v>
-    <v>Argentina, officially the Argentine Republic, is a country in the southern half of South America. It covers an area of 2,780,085 km², making it the second-largest country in South America after Brazil, the fourth-largest country in the Americas, ...</v>
     <v>2810</v>
     <v>2811</v>
     <v>2812</v>
     <v>2813</v>
     <v>2814</v>
     <v>2815</v>
+    <v>ZAR</v>
+    <v>South Africa, officially the Republic of South Africa, is the southernmost country in Africa. Its nine provinces are bounded to the south by 2,798 kilometres of coastline that stretches along the South Atlantic and Indian Ocean; to the north by ...</v>
     <v>2816</v>
     <v>2817</v>
     <v>2818</v>
     <v>2819</v>
-    <v>2806</v>
+    <v>2820</v>
+    <v>2821</v>
     <v>2822</v>
     <v>2823</v>
     <v>2824</v>
     <v>2825</v>
     <v>2826</v>
-    <v>2827</v>
-    <v>Argentina</v>
-    <v>Argentine National Anthem</v>
-    <v>2828</v>
-    <v>República Argentina</v>
     <v>2829</v>
     <v>2830</v>
     <v>2831</v>
-    <v>2671</v>
-    <v>2540</v>
     <v>2832</v>
+    <v>2833</v>
+    <v>South Africa</v>
+    <v>National anthem of South Africa</v>
+    <v>2834</v>
+    <v>Republic of South Africa</v>
+    <v>2835</v>
+    <v>2836</v>
+    <v>2837</v>
+    <v>2266</v>
+    <v>2838</v>
+    <v>2839</v>
+    <v>2840</v>
+    <v>396</v>
+    <v>728</v>
+    <v>881</v>
+    <v>2841</v>
+    <v>2851</v>
+    <v>2852</v>
+    <v>2853</v>
+    <v>2854</v>
+    <v>2855</v>
+    <v>South Africa</v>
+    <v>2856</v>
+    <v>mdp/vdpid/209</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Argentina</v>
+    <v>87153d87-9bb0-166a-3d56-613bdc274e1b</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="1">
+    <fb>0.54335712119385104</fb>
+    <v>29</v>
+  </rv>
+  <rv s="1">
+    <fb>2780400</fb>
+    <v>8</v>
+  </rv>
+  <rv s="1">
+    <fb>105000</fb>
+    <v>8</v>
+  </rv>
+  <rv s="1">
+    <fb>17.021000000000001</fb>
+    <v>30</v>
+  </rv>
+  <rv s="1">
+    <fb>54</fb>
+    <v>31</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Buenos Aires</v>
+    <v>857a6814-3fe8-c414-84da-24018be87fce</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="1">
+    <fb>201347.636</fb>
+    <v>8</v>
+  </rv>
+  <rv s="1">
+    <fb>232.75109166666701</fb>
+    <v>32</v>
+  </rv>
+  <rv s="1">
+    <fb>0.53548304349234199</fb>
+    <v>29</v>
+  </rv>
+  <rv s="1">
+    <fb>3074.70207056563</fb>
+    <v>8</v>
+  </rv>
+  <rv s="1">
+    <fb>2.2610000000000001</fb>
+    <v>30</v>
+  </rv>
+  <rv s="1">
+    <fb>9.7984058182512504E-2</fb>
+    <v>29</v>
+  </rv>
+  <rv s="1">
+    <fb>87.722407479689195</fb>
+    <v>33</v>
+  </rv>
+  <rv s="1">
+    <fb>1.1000000000000001</fb>
+    <v>34</v>
+  </rv>
+  <rv s="1">
+    <fb>449663446954.073</fb>
+    <v>35</v>
+  </rv>
+  <rv s="1">
+    <fb>1.0974146</fb>
+    <v>29</v>
+  </rv>
+  <rv s="1">
+    <fb>0.89958519999999997</fb>
+    <v>29</v>
+  </rv>
+  <rv s="2">
+    <v>92</v>
+    <v>6</v>
+    <v>430</v>
+    <v>7</v>
+    <v>0</v>
+    <v>Image of Argentina</v>
+  </rv>
+  <rv s="1">
+    <fb>8.8000000000000007</fb>
+    <v>33</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Javier Milei (President)</v>
+    <v>9e292152-d659-8459-891a-e2e34df73a4f</v>
+    <v>en-US</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Victoria Villarruel (Vice president)</v>
+    <v>c9d496be-e912-ca9e-b72e-cd37e371c69a</v>
+    <v>en-US</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="3">
+    <v>171</v>
+  </rv>
+  <rv s="4">
+    <v>https://www.bing.com/search?q=argentina&amp;form=skydnc</v>
+    <v>Learn more on Bing</v>
+  </rv>
+  <rv s="1">
+    <fb>76.52</fb>
+    <v>33</v>
+  </rv>
+  <rv s="1">
+    <fb>39393540000</fb>
+    <v>35</v>
+  </rv>
+  <rv s="1">
+    <fb>39</fb>
+    <v>33</v>
+  </rv>
+  <rv s="1">
+    <fb>3.35</fb>
+    <v>34</v>
+  </rv>
+  <rv s="3">
+    <v>172</v>
+  </rv>
+  <rv s="1">
+    <fb>0.17628076140000001</fb>
+    <v>29</v>
+  </rv>
+  <rv s="1">
+    <fb>3.96</fb>
+    <v>30</v>
+  </rv>
+  <rv s="1">
+    <fb>46234830</fb>
+    <v>8</v>
+  </rv>
+  <rv s="1">
+    <fb>0.46500000000000002</fb>
+    <v>29</v>
+  </rv>
+  <rv s="1">
+    <fb>0.61301998138427694</fb>
+    <v>29</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Buenos Aires Province</v>
+    <v>83e02b50-6d03-7c2c-eadf-7346066b2dea</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Catamarca Province</v>
+    <v>3c1c44fb-1be4-0807-a41a-389b53882281</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Chaco Province</v>
+    <v>7ba7eceb-7d6e-ca38-3de8-8edff91abe6c</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Córdoba Province, Argentina</v>
+    <v>ee360e95-eb6e-6500-1854-d0ba2979c8c5</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Corrientes Province</v>
+    <v>370306e6-e553-7210-5bdd-cba530b5bb5e</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Entre Ríos Province</v>
+    <v>8f271891-a2e7-4452-b33a-32b209204098</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Formosa Province</v>
+    <v>2c10e13d-832d-d54f-08b1-364c9870d186</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Jujuy Province</v>
+    <v>4336eba8-fc73-200e-9d91-4273dd01d498</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>La Pampa Province</v>
+    <v>44de277d-e840-a824-59d9-b6a9740aba03</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>La Rioja Province, Argentina</v>
+    <v>dac821c4-934d-98a0-3515-ecf294d05f34</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Mendoza Province</v>
+    <v>67d55d79-bbf5-f1ea-b2b6-9eaf7f8cbf5c</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Misiones Province</v>
+    <v>b5dd089e-a58d-3344-220d-67d53fbe2b62</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Neuquén Province</v>
+    <v>bf5efd04-a076-eedb-ad38-b133bbf30276</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Río Negro Province</v>
+    <v>d2c8f222-11b8-dd86-e0ab-8d14cb406edc</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Salta Province</v>
+    <v>f6ae2fbd-0520-148c-3526-8bf23d36cb82</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>San Juan Province, Argentina</v>
+    <v>17fa2e93-239c-11e6-f03e-d1c2f5cce2fe</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>San Luis Province</v>
+    <v>5bdf188c-b213-ac45-dd24-12759c1ef35f</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Santa Cruz Province, Argentina</v>
+    <v>33b38460-8bb6-75dd-5a16-ccfffb6378dc</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Santa Fe Province</v>
+    <v>7e0bc671-7ee3-bfe7-3fbf-0780b251b2f6</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Santiago del Estero Province</v>
+    <v>ec88ec56-2be0-4304-ab71-391ce9c013de</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Tierra del Fuego Province, Argentina</v>
+    <v>3bb8cbb1-ced9-fc53-1bf4-d1685a3435ea</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Tucumán Province</v>
+    <v>4f81112c-c69e-b6cc-2acc-73c36fc9a0aa</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Chubut Province</v>
+    <v>893cfb2e-6128-06e8-d927-6cdee06773f8</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="3">
+    <v>173</v>
+  </rv>
+  <rv s="1">
+    <fb>0.10087499305375699</fb>
+    <v>29</v>
+  </rv>
+  <rv s="3">
+    <v>174</v>
+  </rv>
+  <rv s="1">
+    <fb>1.0629999999999999</fb>
+    <v>29</v>
+  </rv>
+  <rv s="1">
+    <fb>9.7889995574951205E-2</fb>
+    <v>36</v>
+  </rv>
+  <rv s="1">
+    <fb>41339571</fb>
+    <v>8</v>
+  </rv>
+  <rv s="6">
+    <v>#VALUE!</v>
+    <v>en-US</v>
+    <v>87153d87-9bb0-166a-3d56-613bdc274e1b</v>
+    <v>536870912</v>
+    <v>1</v>
+    <v>433</v>
+    <v>27</v>
+    <v>Argentina</v>
+    <v>4</v>
+    <v>5</v>
+    <v>Map</v>
+    <v>6</v>
+    <v>434</v>
+    <v>AR</v>
+    <v>2859</v>
+    <v>2860</v>
+    <v>2861</v>
+    <v>2862</v>
+    <v>2863</v>
+    <v>2864</v>
+    <v>2865</v>
+    <v>2866</v>
+    <v>2867</v>
+    <v>ARS</v>
+    <v>Argentina, officially the Argentine Republic, is a country in the southern half of South America. It covers an area of 2,780,085 km², making it the second-largest country in South America after Brazil, the fourth-largest country in the Americas, ...</v>
+    <v>2868</v>
+    <v>2869</v>
+    <v>2870</v>
+    <v>2871</v>
+    <v>2872</v>
+    <v>2873</v>
+    <v>2874</v>
+    <v>2875</v>
+    <v>2876</v>
+    <v>2877</v>
+    <v>2864</v>
+    <v>2880</v>
+    <v>2881</v>
+    <v>2882</v>
+    <v>2883</v>
+    <v>2884</v>
+    <v>2885</v>
+    <v>Argentina</v>
+    <v>Argentine National Anthem</v>
+    <v>2886</v>
+    <v>República Argentina</v>
+    <v>2887</v>
+    <v>2888</v>
+    <v>2889</v>
+    <v>2729</v>
+    <v>2552</v>
+    <v>2890</v>
     <v>402</v>
     <v>430</v>
     <v>649</v>
     <v>285</v>
-    <v>2833</v>
-    <v>2857</v>
-    <v>2858</v>
-    <v>2859</v>
-    <v>2860</v>
-    <v>2861</v>
+    <v>2891</v>
+    <v>2915</v>
+    <v>2916</v>
+    <v>2917</v>
+    <v>2918</v>
+    <v>2919</v>
     <v>Argentina</v>
-    <v>2862</v>
+    <v>2920</v>
     <v>mdp/vdpid/11</v>
   </rv>
   <rv s="0">
@@ -24993,9 +25524,9 @@
     <v>8</v>
   </rv>
   <rv s="2">
-    <v>91</v>
+    <v>93</v>
     <v>6</v>
-    <v>426</v>
+    <v>435</v>
     <v>7</v>
     <v>0</v>
     <v>Image of Miami</v>
@@ -25012,7 +25543,7 @@
     <v>Generic</v>
   </rv>
   <rv s="3">
-    <v>170</v>
+    <v>175</v>
   </rv>
   <rv s="4">
     <v>https://www.bing.com/search?q=miami+florida&amp;form=skydnc</v>
@@ -25032,7 +25563,7 @@
     <v>0f9ee715-4425-4f86-a2e6-2fe7befe1ac6</v>
     <v>536870912</v>
     <v>1</v>
-    <v>427</v>
+    <v>436</v>
     <v>159</v>
     <v>Miami</v>
     <v>4</v>
@@ -25041,17 +25572,17 @@
     <v>6</v>
     <v>160</v>
     <v>63</v>
-    <v>2865</v>
-    <v>2866</v>
+    <v>2923</v>
+    <v>2924</v>
     <v>3</v>
     <v>Miami is a coastal city in the U.S. state of Florida and the county seat of Miami-Dade County in South Florida. It is the core of the Miami metropolitan area, which, with a population of 6.14 million, is the second-largest metropolitan area in ...</v>
-    <v>2867</v>
-    <v>2868</v>
-    <v>2870</v>
-    <v>2871</v>
-    <v>2872</v>
+    <v>2925</v>
+    <v>2926</v>
+    <v>2928</v>
+    <v>2929</v>
+    <v>2930</v>
     <v>Miami</v>
-    <v>2873</v>
+    <v>2931</v>
     <v>11</v>
     <v>Miami</v>
     <v>mdp/vdpid/5502110112036159489</v>
@@ -25075,9 +25606,9 @@
     <v>8</v>
   </rv>
   <rv s="2">
-    <v>92</v>
+    <v>94</v>
     <v>6</v>
-    <v>428</v>
+    <v>437</v>
     <v>7</v>
     <v>0</v>
     <v>Image of Providence, Rhode Island</v>
@@ -25094,7 +25625,7 @@
     <v>Generic</v>
   </rv>
   <rv s="3">
-    <v>171</v>
+    <v>176</v>
   </rv>
   <rv s="4">
     <v>https://www.bing.com/search?q=providence+rhode+island&amp;form=skydnc</v>
@@ -25114,7 +25645,7 @@
     <v>956379de-1782-455c-b2d8-1ba81c8965f1</v>
     <v>536870912</v>
     <v>1</v>
-    <v>429</v>
+    <v>438</v>
     <v>226</v>
     <v>Providence, Rhode Island</v>
     <v>4</v>
@@ -25123,17 +25654,17 @@
     <v>6</v>
     <v>46</v>
     <v>92</v>
-    <v>2876</v>
-    <v>2877</v>
+    <v>2934</v>
+    <v>2935</v>
     <v>118</v>
     <v>Providence is the capital and most populous city of the U.S. state of Rhode Island. The county seat of Providence County, it is one of the oldest cities in New England, founded in 1636 by Roger Williams, a Reformed Baptist theologian and ...</v>
-    <v>2878</v>
-    <v>2879</v>
-    <v>2881</v>
-    <v>2882</v>
-    <v>2883</v>
+    <v>2936</v>
+    <v>2937</v>
+    <v>2939</v>
+    <v>2940</v>
+    <v>2941</v>
     <v>Providence, Rhode Island</v>
-    <v>2884</v>
+    <v>2942</v>
     <v>Providence, Rhode Island</v>
     <v>mdp/vdpid/5488923181957775365</v>
   </rv>
@@ -25156,9 +25687,9 @@
     <v>Map</v>
   </rv>
   <rv s="2">
-    <v>93</v>
+    <v>95</v>
     <v>6</v>
-    <v>430</v>
+    <v>439</v>
     <v>7</v>
     <v>0</v>
     <v>Image of Brussels</v>
@@ -25175,7 +25706,7 @@
     <v>Generic</v>
   </rv>
   <rv s="3">
-    <v>172</v>
+    <v>177</v>
   </rv>
   <rv s="4">
     <v>https://www.bing.com/search?q=brussels&amp;form=skydnc</v>
@@ -25189,30 +25720,30 @@
     <fb>1218255</fb>
     <v>8</v>
   </rv>
-  <rv s="26">
+  <rv s="25">
     <v>#VALUE!</v>
     <v>en-US</v>
     <v>f77206fd-fe4f-6c8e-5588-1d0651b151ea</v>
     <v>536870912</v>
     <v>1</v>
-    <v>431</v>
-    <v>432</v>
+    <v>440</v>
+    <v>394</v>
     <v>Brussels</v>
     <v>4</v>
     <v>5</v>
     <v>Map</v>
     <v>6</v>
     <v>46</v>
-    <v>2887</v>
-    <v>2888</v>
+    <v>2945</v>
+    <v>2946</v>
     <v>Brussels, officially the Brussels-Capital Region, is a region of Belgium comprising 19 municipalities, including the City of Brussels, which is the capital of Belgium. The Brussels-Capital Region is located in the central portion of the country ...</v>
-    <v>2889</v>
-    <v>2890</v>
-    <v>2892</v>
-    <v>2893</v>
-    <v>2894</v>
+    <v>2947</v>
+    <v>2948</v>
+    <v>2950</v>
+    <v>2951</v>
+    <v>2952</v>
     <v>Brussels</v>
-    <v>2895</v>
+    <v>2953</v>
     <v>2113</v>
     <v>Brussels</v>
     <v>mdp/vdpid/10103253</v>
@@ -25292,9 +25823,9 @@
     <v>29</v>
   </rv>
   <rv s="2">
-    <v>94</v>
+    <v>96</v>
     <v>6</v>
-    <v>434</v>
+    <v>442</v>
     <v>7</v>
     <v>0</v>
     <v>Image of Turkey</v>
@@ -25332,7 +25863,7 @@
     <v>Generic</v>
   </rv>
   <rv s="3">
-    <v>173</v>
+    <v>178</v>
   </rv>
   <rv s="4">
     <v>https://www.bing.com/search?q=turkey&amp;form=skydnc</v>
@@ -25351,7 +25882,7 @@
     <v>34</v>
   </rv>
   <rv s="3">
-    <v>174</v>
+    <v>179</v>
   </rv>
   <rv s="1">
     <fb>0.16948329139999999</fb>
@@ -25949,14 +26480,14 @@
     <v>Map</v>
   </rv>
   <rv s="3">
-    <v>175</v>
+    <v>180</v>
   </rv>
   <rv s="1">
     <fb>0.178640331232954</fb>
     <v>29</v>
   </rv>
   <rv s="3">
-    <v>176</v>
+    <v>181</v>
   </rv>
   <rv s="1">
     <fb>0.42299999999999999</fb>
@@ -25976,65 +26507,65 @@
     <v>fbfb6418-e8cf-0d18-8b81-28d0fcccda7c</v>
     <v>536870912</v>
     <v>1</v>
-    <v>437</v>
+    <v>445</v>
     <v>27</v>
     <v>Turkey</v>
     <v>4</v>
     <v>5</v>
     <v>Map</v>
     <v>6</v>
-    <v>438</v>
+    <v>446</v>
     <v>TR</v>
-    <v>2898</v>
-    <v>2899</v>
-    <v>2900</v>
-    <v>2901</v>
-    <v>2902</v>
-    <v>2903</v>
-    <v>2904</v>
-    <v>2905</v>
-    <v>2906</v>
+    <v>2956</v>
+    <v>2957</v>
+    <v>2958</v>
+    <v>2959</v>
+    <v>2960</v>
+    <v>2961</v>
+    <v>2962</v>
+    <v>2963</v>
+    <v>2964</v>
     <v>TRL</v>
     <v>Turkey, officially the Republic of Türkiye, is a country mainly located in Anatolia in West Asia, with a relatively small part called East Thrace in Southeast Europe. It borders the Black Sea to the north; Georgia, Armenia, Azerbaijan, and Iran ...</v>
-    <v>2907</v>
-    <v>2908</v>
-    <v>2909</v>
-    <v>2910</v>
+    <v>2965</v>
+    <v>2966</v>
+    <v>2967</v>
+    <v>2968</v>
     <v>1794</v>
-    <v>2911</v>
-    <v>2912</v>
-    <v>2913</v>
-    <v>2914</v>
-    <v>2915</v>
-    <v>2916</v>
-    <v>2920</v>
-    <v>2921</v>
-    <v>2922</v>
-    <v>2923</v>
+    <v>2969</v>
+    <v>2970</v>
+    <v>2971</v>
+    <v>2972</v>
+    <v>2973</v>
+    <v>2974</v>
+    <v>2978</v>
+    <v>2979</v>
+    <v>2980</v>
+    <v>2981</v>
     <v>2057</v>
-    <v>2924</v>
+    <v>2982</v>
     <v>Turkey</v>
     <v>İstiklal Marşı</v>
-    <v>2925</v>
+    <v>2983</v>
     <v>Türkiye Cumhuriyeti</v>
-    <v>2926</v>
-    <v>2927</v>
-    <v>2928</v>
+    <v>2984</v>
+    <v>2985</v>
+    <v>2986</v>
     <v>177</v>
-    <v>2929</v>
-    <v>2930</v>
+    <v>2987</v>
+    <v>2988</v>
     <v>288</v>
     <v>490</v>
     <v>671</v>
-    <v>2931</v>
-    <v>2932</v>
-    <v>3014</v>
-    <v>3015</v>
-    <v>3016</v>
-    <v>3017</v>
-    <v>3018</v>
+    <v>2989</v>
+    <v>2990</v>
+    <v>3072</v>
+    <v>3073</v>
+    <v>3074</v>
+    <v>3075</v>
+    <v>3076</v>
     <v>Turkey</v>
-    <v>3019</v>
+    <v>3077</v>
     <v>mdp/vdpid/235</v>
   </rv>
 </rvData>
@@ -26872,13 +27403,14 @@
     <k n="_Icon" t="s"/>
     <k n="_Provider" t="spb"/>
     <k n="_SubLabel" t="spb"/>
-    <k n="Abbreviation" t="s"/>
     <k n="Area" t="r"/>
     <k n="Country/region" t="r"/>
     <k n="Description" t="s"/>
     <k n="Image" t="r"/>
+    <k n="Latitude" t="r"/>
     <k n="Leader(s)" t="r"/>
     <k n="LearnMoreOnLink" t="r"/>
+    <k n="Longitude" t="r"/>
     <k n="Name" t="s"/>
     <k n="Population" t="r"/>
     <k n="Time zone(s)" t="r"/>
@@ -26899,14 +27431,13 @@
     <k n="_Icon" t="s"/>
     <k n="_Provider" t="spb"/>
     <k n="_SubLabel" t="spb"/>
+    <k n="Abbreviation" t="s"/>
     <k n="Area" t="r"/>
     <k n="Country/region" t="r"/>
     <k n="Description" t="s"/>
     <k n="Image" t="r"/>
-    <k n="Latitude" t="r"/>
     <k n="Leader(s)" t="r"/>
     <k n="LearnMoreOnLink" t="r"/>
-    <k n="Longitude" t="r"/>
     <k n="Name" t="s"/>
     <k n="Population" t="r"/>
     <k n="Time zone(s)" t="r"/>
@@ -27690,32 +28221,6 @@
       <v t="s">Image</v>
       <v t="s">Description</v>
     </a>
-    <a count="24">
-      <v t="s">%EntityServiceId</v>
-      <v t="s">%IsRefreshable</v>
-      <v t="s">%EntityCulture</v>
-      <v t="s">%EntityId</v>
-      <v t="s">_Icon</v>
-      <v t="s">_Provider</v>
-      <v t="s">_Attribution</v>
-      <v t="s">_Display</v>
-      <v t="s">Name</v>
-      <v t="s">_Format</v>
-      <v t="s">Leader(s)</v>
-      <v t="s">Country/region</v>
-      <v t="s">_SubLabel</v>
-      <v t="s">Population</v>
-      <v t="s">Area</v>
-      <v t="s">Abbreviation</v>
-      <v t="s">Time zone(s)</v>
-      <v t="s">_Flags</v>
-      <v t="s">VDPID/VSID</v>
-      <v t="s">UniqueName</v>
-      <v t="s">_DisplayString</v>
-      <v t="s">LearnMoreOnLink</v>
-      <v t="s">Image</v>
-      <v t="s">Description</v>
-    </a>
     <a count="25">
       <v t="s">%EntityServiceId</v>
       <v t="s">%IsRefreshable</v>
@@ -27743,8 +28248,34 @@
       <v t="s">Image</v>
       <v t="s">Description</v>
     </a>
+    <a count="24">
+      <v t="s">%EntityServiceId</v>
+      <v t="s">%IsRefreshable</v>
+      <v t="s">%EntityCulture</v>
+      <v t="s">%EntityId</v>
+      <v t="s">_Icon</v>
+      <v t="s">_Provider</v>
+      <v t="s">_Attribution</v>
+      <v t="s">_Display</v>
+      <v t="s">Name</v>
+      <v t="s">_Format</v>
+      <v t="s">Leader(s)</v>
+      <v t="s">Country/region</v>
+      <v t="s">_SubLabel</v>
+      <v t="s">Population</v>
+      <v t="s">Area</v>
+      <v t="s">Abbreviation</v>
+      <v t="s">Time zone(s)</v>
+      <v t="s">_Flags</v>
+      <v t="s">VDPID/VSID</v>
+      <v t="s">UniqueName</v>
+      <v t="s">_DisplayString</v>
+      <v t="s">LearnMoreOnLink</v>
+      <v t="s">Image</v>
+      <v t="s">Description</v>
+    </a>
   </spbArrays>
-  <spbData count="439">
+  <spbData count="447">
     <spb s="0">
       <v xml:space="preserve">Wikipedia	</v>
       <v xml:space="preserve">CC BY-SA 3.0	</v>
@@ -32485,6 +33016,33 @@
       <v>2019</v>
     </spb>
     <spb s="0">
+      <v xml:space="preserve">Wikipedia	</v>
+      <v xml:space="preserve">CC-BY-SA	</v>
+      <v xml:space="preserve">http://en.wikipedia.org/wiki/Dublin	</v>
+      <v xml:space="preserve">http://creativecommons.org/licenses/by-sa/3.0/	</v>
+    </spb>
+    <spb s="0">
+      <v xml:space="preserve">Wikipedia	</v>
+      <v xml:space="preserve">CC BY-SA 3.0	</v>
+      <v xml:space="preserve">https://en.wikipedia.org/wiki/Dublin	</v>
+      <v xml:space="preserve">https://creativecommons.org/licenses/by-sa/3.0	</v>
+    </spb>
+    <spb s="33">
+      <v>391</v>
+      <v>392</v>
+      <v>392</v>
+      <v>392</v>
+      <v>392</v>
+      <v>392</v>
+      <v>392</v>
+      <v>392</v>
+    </spb>
+    <spb s="2">
+      <v>20</v>
+      <v>Name</v>
+      <v>LearnMoreOnLink</v>
+    </spb>
+    <spb s="0">
       <v xml:space="preserve">Wikipedia	Cia	travel.state.gov	</v>
       <v xml:space="preserve">CC-BY-SA			</v>
       <v xml:space="preserve">http://en.wikipedia.org/wiki/Russia	https://www.cia.gov/library/publications/the-world-factbook/geos/rs.html?Transportation	https://travel.state.gov/content/travel/en/international-travel/International-Travel-Country-Information-Pages/RussianFederation.html	</v>
@@ -32510,49 +33068,49 @@
     </spb>
     <spb s="17">
       <v>10</v>
-      <v>391</v>
-      <v>392</v>
-      <v>392</v>
+      <v>395</v>
+      <v>396</v>
+      <v>396</v>
       <v>13</v>
-      <v>392</v>
-      <v>392</v>
-      <v>392</v>
-      <v>393</v>
-      <v>392</v>
-      <v>392</v>
-      <v>393</v>
-      <v>392</v>
-      <v>392</v>
-      <v>394</v>
+      <v>396</v>
+      <v>396</v>
+      <v>396</v>
+      <v>397</v>
+      <v>396</v>
+      <v>396</v>
+      <v>397</v>
+      <v>396</v>
+      <v>396</v>
+      <v>398</v>
       <v>15</v>
-      <v>391</v>
-      <v>394</v>
+      <v>395</v>
+      <v>398</v>
       <v>17</v>
-      <v>392</v>
-      <v>394</v>
+      <v>396</v>
+      <v>398</v>
       <v>18</v>
       <v>19</v>
       <v>20</v>
-      <v>394</v>
-      <v>394</v>
-      <v>392</v>
-      <v>394</v>
+      <v>398</v>
+      <v>398</v>
+      <v>396</v>
+      <v>398</v>
       <v>21</v>
       <v>22</v>
       <v>23</v>
       <v>24</v>
-      <v>394</v>
-      <v>391</v>
-      <v>394</v>
-      <v>394</v>
-      <v>394</v>
-      <v>394</v>
-      <v>394</v>
-      <v>394</v>
-      <v>394</v>
-      <v>394</v>
-      <v>394</v>
-      <v>394</v>
+      <v>398</v>
+      <v>395</v>
+      <v>398</v>
+      <v>398</v>
+      <v>398</v>
+      <v>398</v>
+      <v>398</v>
+      <v>398</v>
+      <v>398</v>
+      <v>398</v>
+      <v>398</v>
+      <v>398</v>
       <v>25</v>
     </spb>
     <spb s="10">
@@ -32592,56 +33150,30 @@
       <v>2019</v>
     </spb>
     <spb s="0">
+      <v xml:space="preserve">Wikipedia	Cia	travel.state.gov	</v>
+      <v xml:space="preserve">CC-BY-SA			</v>
+      <v xml:space="preserve">http://en.wikipedia.org/wiki/Austria	https://www.cia.gov/library/publications/the-world-factbook/geos/au.html?Transportation	https://travel.state.gov/content/travel/en/international-travel/International-Travel-Country-Information-Pages/Austria.html	</v>
+      <v xml:space="preserve">http://creativecommons.org/licenses/by-sa/3.0/			</v>
+    </spb>
+    <spb s="0">
       <v xml:space="preserve">Wikipedia	</v>
       <v xml:space="preserve">CC BY-SA 3.0	</v>
-      <v xml:space="preserve">https://en.wikipedia.org/wiki/Prague	</v>
+      <v xml:space="preserve">https://en.wikipedia.org/wiki/Austria	</v>
       <v xml:space="preserve">https://creativecommons.org/licenses/by-sa/3.0	</v>
     </spb>
     <spb s="0">
       <v xml:space="preserve">Wikipedia	</v>
       <v xml:space="preserve">CC-BY-SA	</v>
-      <v xml:space="preserve">http://en.wikipedia.org/wiki/Prague	</v>
-      <v xml:space="preserve">http://creativecommons.org/licenses/by-sa/3.0/	</v>
-    </spb>
-    <spb s="33">
-      <v>397</v>
-      <v>397</v>
-      <v>397</v>
-      <v>397</v>
-      <v>397</v>
-      <v>398</v>
-      <v>397</v>
-    </spb>
-    <spb s="2">
-      <v>20</v>
-      <v>Name</v>
-      <v>LearnMoreOnLink</v>
-    </spb>
-    <spb s="0">
-      <v xml:space="preserve">Wikipedia	Cia	travel.state.gov	</v>
-      <v xml:space="preserve">CC-BY-SA			</v>
-      <v xml:space="preserve">http://en.wikipedia.org/wiki/Slovakia	https://www.cia.gov/library/publications/the-world-factbook/geos/lo.html?Transportation	https://travel.state.gov/content/travel/en/international-travel/International-Travel-Country-Information-Pages/Slovakia.html	</v>
-      <v xml:space="preserve">http://creativecommons.org/licenses/by-sa/3.0/			</v>
-    </spb>
-    <spb s="0">
-      <v xml:space="preserve">Wikipedia	</v>
-      <v xml:space="preserve">CC BY-SA 3.0	</v>
-      <v xml:space="preserve">https://en.wikipedia.org/wiki/Slovakia	</v>
-      <v xml:space="preserve">https://creativecommons.org/licenses/by-sa/3.0	</v>
-    </spb>
-    <spb s="0">
-      <v xml:space="preserve">Wikipedia	</v>
-      <v xml:space="preserve">CC-BY-SA	</v>
-      <v xml:space="preserve">http://en.wikipedia.org/wiki/Slovakia	</v>
+      <v xml:space="preserve">http://en.wikipedia.org/wiki/Austria	</v>
       <v xml:space="preserve">http://creativecommons.org/licenses/by-sa/3.0/	</v>
     </spb>
     <spb s="0">
       <v xml:space="preserve">Cia	</v>
       <v xml:space="preserve">	</v>
-      <v xml:space="preserve">https://www.cia.gov/library/publications/the-world-factbook/geos/lo.html?Transportation	</v>
+      <v xml:space="preserve">https://www.cia.gov/library/publications/the-world-factbook/geos/au.html?Transportation	</v>
       <v xml:space="preserve">	</v>
     </spb>
-    <spb s="17">
+    <spb s="23">
       <v>10</v>
       <v>401</v>
       <v>402</v>
@@ -32653,7 +33185,6 @@
       <v>403</v>
       <v>402</v>
       <v>402</v>
-      <v>403</v>
       <v>402</v>
       <v>402</v>
       <v>404</v>
@@ -32686,6 +33217,103 @@
       <v>404</v>
       <v>404</v>
       <v>404</v>
+      <v>25</v>
+    </spb>
+    <spb s="0">
+      <v xml:space="preserve">Wikipedia	</v>
+      <v xml:space="preserve">CC BY-SA 3.0	</v>
+      <v xml:space="preserve">https://en.wikipedia.org/wiki/Prague	</v>
+      <v xml:space="preserve">https://creativecommons.org/licenses/by-sa/3.0	</v>
+    </spb>
+    <spb s="0">
+      <v xml:space="preserve">Wikipedia	</v>
+      <v xml:space="preserve">CC-BY-SA	</v>
+      <v xml:space="preserve">http://en.wikipedia.org/wiki/Prague	</v>
+      <v xml:space="preserve">http://creativecommons.org/licenses/by-sa/3.0/	</v>
+    </spb>
+    <spb s="34">
+      <v>406</v>
+      <v>406</v>
+      <v>406</v>
+      <v>406</v>
+      <v>406</v>
+      <v>407</v>
+      <v>406</v>
+    </spb>
+    <spb s="2">
+      <v>21</v>
+      <v>Name</v>
+      <v>LearnMoreOnLink</v>
+    </spb>
+    <spb s="0">
+      <v xml:space="preserve">Wikipedia	Cia	travel.state.gov	</v>
+      <v xml:space="preserve">CC-BY-SA			</v>
+      <v xml:space="preserve">http://en.wikipedia.org/wiki/Slovakia	https://www.cia.gov/library/publications/the-world-factbook/geos/lo.html?Transportation	https://travel.state.gov/content/travel/en/international-travel/International-Travel-Country-Information-Pages/Slovakia.html	</v>
+      <v xml:space="preserve">http://creativecommons.org/licenses/by-sa/3.0/			</v>
+    </spb>
+    <spb s="0">
+      <v xml:space="preserve">Wikipedia	</v>
+      <v xml:space="preserve">CC BY-SA 3.0	</v>
+      <v xml:space="preserve">https://en.wikipedia.org/wiki/Slovakia	</v>
+      <v xml:space="preserve">https://creativecommons.org/licenses/by-sa/3.0	</v>
+    </spb>
+    <spb s="0">
+      <v xml:space="preserve">Wikipedia	</v>
+      <v xml:space="preserve">CC-BY-SA	</v>
+      <v xml:space="preserve">http://en.wikipedia.org/wiki/Slovakia	</v>
+      <v xml:space="preserve">http://creativecommons.org/licenses/by-sa/3.0/	</v>
+    </spb>
+    <spb s="0">
+      <v xml:space="preserve">Cia	</v>
+      <v xml:space="preserve">	</v>
+      <v xml:space="preserve">https://www.cia.gov/library/publications/the-world-factbook/geos/lo.html?Transportation	</v>
+      <v xml:space="preserve">	</v>
+    </spb>
+    <spb s="17">
+      <v>10</v>
+      <v>410</v>
+      <v>411</v>
+      <v>411</v>
+      <v>13</v>
+      <v>411</v>
+      <v>411</v>
+      <v>411</v>
+      <v>412</v>
+      <v>411</v>
+      <v>411</v>
+      <v>412</v>
+      <v>411</v>
+      <v>411</v>
+      <v>413</v>
+      <v>15</v>
+      <v>410</v>
+      <v>413</v>
+      <v>17</v>
+      <v>411</v>
+      <v>413</v>
+      <v>18</v>
+      <v>19</v>
+      <v>20</v>
+      <v>413</v>
+      <v>413</v>
+      <v>411</v>
+      <v>413</v>
+      <v>21</v>
+      <v>22</v>
+      <v>23</v>
+      <v>24</v>
+      <v>413</v>
+      <v>410</v>
+      <v>413</v>
+      <v>413</v>
+      <v>413</v>
+      <v>413</v>
+      <v>413</v>
+      <v>413</v>
+      <v>413</v>
+      <v>413</v>
+      <v>413</v>
+      <v>413</v>
       <v>25</v>
     </spb>
     <spb s="10">
@@ -32756,49 +33384,49 @@
     </spb>
     <spb s="17">
       <v>10</v>
-      <v>407</v>
-      <v>408</v>
-      <v>408</v>
+      <v>416</v>
+      <v>417</v>
+      <v>417</v>
       <v>13</v>
-      <v>408</v>
-      <v>408</v>
-      <v>408</v>
-      <v>409</v>
-      <v>408</v>
-      <v>408</v>
-      <v>409</v>
-      <v>408</v>
-      <v>408</v>
-      <v>410</v>
+      <v>417</v>
+      <v>417</v>
+      <v>417</v>
+      <v>418</v>
+      <v>417</v>
+      <v>417</v>
+      <v>418</v>
+      <v>417</v>
+      <v>417</v>
+      <v>419</v>
       <v>15</v>
-      <v>411</v>
-      <v>410</v>
+      <v>420</v>
+      <v>419</v>
       <v>17</v>
-      <v>408</v>
-      <v>410</v>
+      <v>417</v>
+      <v>419</v>
       <v>18</v>
       <v>19</v>
       <v>20</v>
-      <v>410</v>
-      <v>410</v>
-      <v>408</v>
-      <v>410</v>
+      <v>419</v>
+      <v>419</v>
+      <v>417</v>
+      <v>419</v>
       <v>21</v>
       <v>22</v>
       <v>23</v>
       <v>24</v>
-      <v>410</v>
-      <v>411</v>
-      <v>410</v>
-      <v>410</v>
-      <v>410</v>
-      <v>410</v>
-      <v>410</v>
-      <v>410</v>
-      <v>410</v>
-      <v>410</v>
-      <v>410</v>
-      <v>410</v>
+      <v>419</v>
+      <v>420</v>
+      <v>419</v>
+      <v>419</v>
+      <v>419</v>
+      <v>419</v>
+      <v>419</v>
+      <v>419</v>
+      <v>419</v>
+      <v>419</v>
+      <v>419</v>
+      <v>419</v>
       <v>25</v>
     </spb>
     <spb s="10">
@@ -32863,48 +33491,48 @@
     </spb>
     <spb s="23">
       <v>10</v>
-      <v>414</v>
-      <v>415</v>
-      <v>415</v>
+      <v>423</v>
+      <v>424</v>
+      <v>424</v>
       <v>13</v>
-      <v>415</v>
-      <v>415</v>
-      <v>415</v>
-      <v>416</v>
-      <v>415</v>
-      <v>415</v>
-      <v>415</v>
-      <v>415</v>
-      <v>417</v>
+      <v>424</v>
+      <v>424</v>
+      <v>424</v>
+      <v>425</v>
+      <v>424</v>
+      <v>424</v>
+      <v>424</v>
+      <v>424</v>
+      <v>426</v>
       <v>15</v>
-      <v>414</v>
-      <v>417</v>
+      <v>423</v>
+      <v>426</v>
       <v>17</v>
-      <v>415</v>
-      <v>417</v>
+      <v>424</v>
+      <v>426</v>
       <v>18</v>
       <v>19</v>
       <v>20</v>
-      <v>417</v>
-      <v>417</v>
-      <v>415</v>
-      <v>417</v>
+      <v>426</v>
+      <v>426</v>
+      <v>424</v>
+      <v>426</v>
       <v>21</v>
       <v>22</v>
       <v>23</v>
       <v>24</v>
-      <v>417</v>
-      <v>414</v>
-      <v>417</v>
-      <v>417</v>
-      <v>417</v>
-      <v>417</v>
-      <v>417</v>
-      <v>417</v>
-      <v>417</v>
-      <v>417</v>
-      <v>417</v>
-      <v>417</v>
+      <v>426</v>
+      <v>423</v>
+      <v>426</v>
+      <v>426</v>
+      <v>426</v>
+      <v>426</v>
+      <v>426</v>
+      <v>426</v>
+      <v>426</v>
+      <v>426</v>
+      <v>426</v>
+      <v>426</v>
       <v>25</v>
     </spb>
     <spb s="10">
@@ -32969,49 +33597,49 @@
     </spb>
     <spb s="17">
       <v>10</v>
-      <v>420</v>
-      <v>421</v>
-      <v>421</v>
+      <v>429</v>
+      <v>430</v>
+      <v>430</v>
       <v>13</v>
-      <v>421</v>
-      <v>421</v>
-      <v>421</v>
-      <v>422</v>
-      <v>421</v>
-      <v>421</v>
-      <v>422</v>
-      <v>421</v>
-      <v>421</v>
-      <v>423</v>
+      <v>430</v>
+      <v>430</v>
+      <v>430</v>
+      <v>431</v>
+      <v>430</v>
+      <v>430</v>
+      <v>431</v>
+      <v>430</v>
+      <v>430</v>
+      <v>432</v>
       <v>15</v>
-      <v>420</v>
-      <v>423</v>
+      <v>429</v>
+      <v>432</v>
       <v>17</v>
-      <v>421</v>
-      <v>423</v>
+      <v>430</v>
+      <v>432</v>
       <v>18</v>
       <v>19</v>
       <v>20</v>
-      <v>423</v>
-      <v>423</v>
-      <v>421</v>
-      <v>423</v>
+      <v>432</v>
+      <v>432</v>
+      <v>430</v>
+      <v>432</v>
       <v>21</v>
       <v>22</v>
       <v>23</v>
       <v>24</v>
-      <v>423</v>
-      <v>420</v>
-      <v>423</v>
-      <v>423</v>
-      <v>423</v>
-      <v>423</v>
-      <v>423</v>
-      <v>423</v>
-      <v>423</v>
-      <v>423</v>
-      <v>423</v>
-      <v>423</v>
+      <v>432</v>
+      <v>429</v>
+      <v>432</v>
+      <v>432</v>
+      <v>432</v>
+      <v>432</v>
+      <v>432</v>
+      <v>432</v>
+      <v>432</v>
+      <v>432</v>
+      <v>432</v>
+      <v>432</v>
       <v>25</v>
     </spb>
     <spb s="10">
@@ -33057,16 +33685,16 @@
       <v xml:space="preserve">https://creativecommons.org/licenses/by-sa/3.0	</v>
     </spb>
     <spb s="16">
-      <v>426</v>
-      <v>426</v>
-      <v>426</v>
-      <v>426</v>
-      <v>426</v>
-      <v>426</v>
-      <v>426</v>
-      <v>426</v>
-      <v>426</v>
-      <v>426</v>
+      <v>435</v>
+      <v>435</v>
+      <v>435</v>
+      <v>435</v>
+      <v>435</v>
+      <v>435</v>
+      <v>435</v>
+      <v>435</v>
+      <v>435</v>
+      <v>435</v>
     </spb>
     <spb s="0">
       <v xml:space="preserve">Wikipedia	</v>
@@ -33075,16 +33703,16 @@
       <v xml:space="preserve">https://creativecommons.org/licenses/by-sa/3.0	</v>
     </spb>
     <spb s="16">
-      <v>428</v>
-      <v>428</v>
-      <v>428</v>
-      <v>428</v>
-      <v>428</v>
-      <v>428</v>
-      <v>428</v>
-      <v>428</v>
-      <v>428</v>
-      <v>428</v>
+      <v>437</v>
+      <v>437</v>
+      <v>437</v>
+      <v>437</v>
+      <v>437</v>
+      <v>437</v>
+      <v>437</v>
+      <v>437</v>
+      <v>437</v>
+      <v>437</v>
     </spb>
     <spb s="0">
       <v xml:space="preserve">Wikipedia	</v>
@@ -33092,20 +33720,15 @@
       <v xml:space="preserve">https://en.wikipedia.org/wiki/Brussels	</v>
       <v xml:space="preserve">https://creativecommons.org/licenses/by-sa/3.0	</v>
     </spb>
-    <spb s="34">
-      <v>430</v>
-      <v>430</v>
-      <v>430</v>
-      <v>430</v>
-      <v>430</v>
-      <v>430</v>
-      <v>430</v>
-      <v>430</v>
-    </spb>
-    <spb s="2">
-      <v>21</v>
-      <v>Name</v>
-      <v>LearnMoreOnLink</v>
+    <spb s="33">
+      <v>439</v>
+      <v>439</v>
+      <v>439</v>
+      <v>439</v>
+      <v>439</v>
+      <v>439</v>
+      <v>439</v>
+      <v>439</v>
     </spb>
     <spb s="0">
       <v xml:space="preserve">Wikipedia	Cia	travel.state.gov	</v>
@@ -33133,49 +33756,49 @@
     </spb>
     <spb s="17">
       <v>10</v>
-      <v>433</v>
-      <v>434</v>
-      <v>434</v>
+      <v>441</v>
+      <v>442</v>
+      <v>442</v>
       <v>13</v>
-      <v>434</v>
-      <v>434</v>
-      <v>434</v>
-      <v>435</v>
-      <v>434</v>
-      <v>434</v>
-      <v>435</v>
-      <v>434</v>
-      <v>434</v>
-      <v>436</v>
+      <v>442</v>
+      <v>442</v>
+      <v>442</v>
+      <v>443</v>
+      <v>442</v>
+      <v>442</v>
+      <v>443</v>
+      <v>442</v>
+      <v>442</v>
+      <v>444</v>
       <v>15</v>
-      <v>433</v>
-      <v>436</v>
+      <v>441</v>
+      <v>444</v>
       <v>17</v>
-      <v>434</v>
-      <v>436</v>
+      <v>442</v>
+      <v>444</v>
       <v>18</v>
       <v>19</v>
       <v>20</v>
-      <v>436</v>
-      <v>436</v>
-      <v>434</v>
-      <v>436</v>
+      <v>444</v>
+      <v>444</v>
+      <v>442</v>
+      <v>444</v>
       <v>21</v>
       <v>22</v>
       <v>23</v>
       <v>24</v>
-      <v>436</v>
-      <v>433</v>
-      <v>436</v>
-      <v>436</v>
-      <v>436</v>
-      <v>436</v>
-      <v>436</v>
-      <v>436</v>
-      <v>436</v>
-      <v>436</v>
-      <v>436</v>
-      <v>436</v>
+      <v>444</v>
+      <v>441</v>
+      <v>444</v>
+      <v>444</v>
+      <v>444</v>
+      <v>444</v>
+      <v>444</v>
+      <v>444</v>
+      <v>444</v>
+      <v>444</v>
+      <v>444</v>
+      <v>444</v>
       <v>25</v>
     </spb>
     <spb s="10">
@@ -33771,20 +34394,20 @@
   <s>
     <k n="Area" t="spb"/>
     <k n="Name" t="spb"/>
+    <k n="Latitude" t="spb"/>
+    <k n="Longitude" t="spb"/>
     <k n="Population" t="spb"/>
     <k n="UniqueName" t="spb"/>
     <k n="Description" t="spb"/>
-    <k n="Abbreviation" t="spb"/>
     <k n="Country/region" t="spb"/>
   </s>
   <s>
     <k n="Area" t="spb"/>
     <k n="Name" t="spb"/>
-    <k n="Latitude" t="spb"/>
-    <k n="Longitude" t="spb"/>
     <k n="Population" t="spb"/>
     <k n="UniqueName" t="spb"/>
     <k n="Description" t="spb"/>
+    <k n="Abbreviation" t="spb"/>
     <k n="Country/region" t="spb"/>
   </s>
 </spbStructures>
@@ -34184,7 +34807,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7772053-9363-CA4A-A53F-040B7C700753}">
-  <dimension ref="A1:U212"/>
+  <dimension ref="A1:U223"/>
   <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -35160,6 +35783,9 @@
       <c r="H23" t="s">
         <v>99</v>
       </c>
+      <c r="I23" t="s">
+        <v>407</v>
+      </c>
       <c r="J23" t="s">
         <v>312</v>
       </c>
@@ -40388,22 +41014,27 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A147" t="s">
-        <v>110</v>
+        <v>675</v>
+      </c>
+      <c r="B147" t="s">
+        <v>677</v>
       </c>
       <c r="C147" s="1">
-        <v>45976</v>
+        <v>45971</v>
       </c>
       <c r="D147" t="s">
-        <v>16</v>
-      </c>
-      <c r="G147" s="1"/>
+        <v>674</v>
+      </c>
+      <c r="G147" t="s">
+        <v>679</v>
+      </c>
       <c r="H147" t="s">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="L147" t="s">
-        <v>111</v>
-      </c>
-      <c r="M147" t="e" vm="14">
+        <v>673</v>
+      </c>
+      <c r="M147" t="e" vm="78">
         <v>#VALUE!</v>
       </c>
       <c r="N147" t="s">
@@ -40413,33 +41044,33 @@
         <v>20</v>
       </c>
       <c r="Q147" s="1">
-        <v>45981</v>
+        <v>45986</v>
       </c>
       <c r="S147">
         <v>1</v>
       </c>
       <c r="T147">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U147">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A148" s="4" t="s">
-        <v>167</v>
+        <v>676</v>
+      </c>
+      <c r="B148" t="s">
+        <v>678</v>
       </c>
       <c r="C148" s="1">
-        <v>45976</v>
+        <v>45971</v>
       </c>
       <c r="D148" t="s">
-        <v>16</v>
-      </c>
-      <c r="F148">
-        <v>2</v>
-      </c>
-      <c r="G148" s="7" t="s">
-        <v>169</v>
+        <v>674</v>
+      </c>
+      <c r="G148" t="s">
+        <v>679</v>
       </c>
       <c r="H148" t="s">
         <v>25</v>
@@ -40450,8 +41081,8 @@
       <c r="K148" s="1">
         <v>45986</v>
       </c>
-      <c r="L148" s="2" t="s">
-        <v>168</v>
+      <c r="L148" t="s">
+        <v>673</v>
       </c>
       <c r="M148" t="e" vm="78">
         <v>#VALUE!</v>
@@ -40463,35 +41094,38 @@
         <v>20</v>
       </c>
       <c r="Q148" s="1">
-        <v>45982</v>
+        <v>45986</v>
       </c>
       <c r="S148">
         <v>1</v>
       </c>
       <c r="T148">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U148">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A149" t="s">
-        <v>383</v>
+        <v>695</v>
       </c>
       <c r="C149" s="1">
-        <v>45976</v>
+        <v>45971</v>
       </c>
       <c r="D149" t="s">
         <v>16</v>
       </c>
+      <c r="E149" t="s">
+        <v>696</v>
+      </c>
       <c r="H149" t="s">
         <v>99</v>
       </c>
       <c r="L149" t="s">
-        <v>382</v>
-      </c>
-      <c r="M149" t="e" vm="31">
+        <v>694</v>
+      </c>
+      <c r="M149" t="e" vm="58">
         <v>#VALUE!</v>
       </c>
       <c r="N149" t="s">
@@ -40501,10 +41135,10 @@
         <v>20</v>
       </c>
       <c r="Q149" s="1">
-        <v>45985</v>
+        <v>45984</v>
       </c>
       <c r="S149">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T149">
         <v>0</v>
@@ -40515,34 +41149,31 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A150" t="s">
-        <v>462</v>
+        <v>701</v>
       </c>
       <c r="C150" s="1">
-        <v>45976</v>
+        <v>45971</v>
       </c>
       <c r="D150" t="s">
-        <v>42</v>
-      </c>
-      <c r="E150" t="s">
-        <v>463</v>
+        <v>16</v>
       </c>
       <c r="H150" t="s">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="L150" t="s">
-        <v>464</v>
-      </c>
-      <c r="M150" t="e" vm="79">
+        <v>702</v>
+      </c>
+      <c r="M150" t="e" vm="51">
         <v>#VALUE!</v>
       </c>
       <c r="N150" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="P150" t="s">
         <v>20</v>
       </c>
       <c r="Q150" s="1">
-        <v>45985</v>
+        <v>45978</v>
       </c>
       <c r="S150">
         <v>1</v>
@@ -40551,12 +41182,12 @@
         <v>1</v>
       </c>
       <c r="U150">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.4">
-      <c r="A151" s="4" t="s">
-        <v>141</v>
+      <c r="A151" t="s">
+        <v>110</v>
       </c>
       <c r="C151" s="1">
         <v>45976</v>
@@ -40564,22 +41195,14 @@
       <c r="D151" t="s">
         <v>16</v>
       </c>
-      <c r="F151">
-        <v>1</v>
-      </c>
+      <c r="G151" s="1"/>
       <c r="H151" t="s">
-        <v>25</v>
-      </c>
-      <c r="J151" t="s">
-        <v>247</v>
-      </c>
-      <c r="K151" s="1">
-        <v>45986</v>
-      </c>
-      <c r="L151" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="M151" t="e" vm="77">
+        <v>99</v>
+      </c>
+      <c r="L151" t="s">
+        <v>111</v>
+      </c>
+      <c r="M151" t="e" vm="14">
         <v>#VALUE!</v>
       </c>
       <c r="N151" t="s">
@@ -40589,21 +41212,21 @@
         <v>20</v>
       </c>
       <c r="Q151" s="1">
-        <v>45986</v>
+        <v>45981</v>
       </c>
       <c r="S151">
         <v>1</v>
       </c>
       <c r="T151">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U151">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A152" s="4" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="C152" s="1">
         <v>45976</v>
@@ -40611,12 +41234,12 @@
       <c r="D152" t="s">
         <v>16</v>
       </c>
-      <c r="E152" t="s">
-        <v>123</v>
-      </c>
       <c r="F152">
         <v>2</v>
       </c>
+      <c r="G152" s="7" t="s">
+        <v>169</v>
+      </c>
       <c r="H152" t="s">
         <v>25</v>
       </c>
@@ -40627,9 +41250,9 @@
         <v>45986</v>
       </c>
       <c r="L152" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="M152" t="e" vm="27">
+        <v>168</v>
+      </c>
+      <c r="M152" t="e" vm="79">
         <v>#VALUE!</v>
       </c>
       <c r="N152" t="s">
@@ -40639,7 +41262,7 @@
         <v>20</v>
       </c>
       <c r="Q152" s="1">
-        <v>45988</v>
+        <v>45982</v>
       </c>
       <c r="S152">
         <v>1</v>
@@ -40652,11 +41275,8 @@
       </c>
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.4">
-      <c r="A153" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="B153" t="s">
-        <v>638</v>
+      <c r="A153" t="s">
+        <v>383</v>
       </c>
       <c r="C153" s="1">
         <v>45976</v>
@@ -40664,22 +41284,13 @@
       <c r="D153" t="s">
         <v>16</v>
       </c>
-      <c r="F153">
-        <v>2</v>
-      </c>
       <c r="H153" t="s">
-        <v>25</v>
-      </c>
-      <c r="J153" t="s">
-        <v>247</v>
-      </c>
-      <c r="K153" s="1">
-        <v>45986</v>
-      </c>
-      <c r="L153" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="M153" t="e" vm="77">
+        <v>99</v>
+      </c>
+      <c r="L153" t="s">
+        <v>382</v>
+      </c>
+      <c r="M153" t="e" vm="31">
         <v>#VALUE!</v>
       </c>
       <c r="N153" t="s">
@@ -40689,7 +41300,7 @@
         <v>20</v>
       </c>
       <c r="Q153" s="1">
-        <v>45989</v>
+        <v>45985</v>
       </c>
       <c r="S153">
         <v>1</v>
@@ -40703,21 +41314,24 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A154" t="s">
-        <v>529</v>
+        <v>462</v>
       </c>
       <c r="C154" s="1">
         <v>45976</v>
       </c>
       <c r="D154" t="s">
-        <v>530</v>
+        <v>42</v>
+      </c>
+      <c r="E154" t="s">
+        <v>463</v>
       </c>
       <c r="H154" t="s">
         <v>99</v>
       </c>
       <c r="L154" t="s">
-        <v>531</v>
-      </c>
-      <c r="M154" t="e" vm="43">
+        <v>464</v>
+      </c>
+      <c r="M154" t="e" vm="80">
         <v>#VALUE!</v>
       </c>
       <c r="N154" t="s">
@@ -40727,38 +41341,44 @@
         <v>20</v>
       </c>
       <c r="Q154" s="1">
-        <v>46081</v>
+        <v>45985</v>
       </c>
       <c r="S154">
         <v>1</v>
       </c>
       <c r="T154">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U154">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.4">
-      <c r="A155" t="s">
-        <v>535</v>
-      </c>
-      <c r="B155" t="s">
-        <v>536</v>
+      <c r="A155" s="4" t="s">
+        <v>141</v>
       </c>
       <c r="C155" s="1">
         <v>45976</v>
       </c>
       <c r="D155" t="s">
-        <v>537</v>
+        <v>16</v>
+      </c>
+      <c r="F155">
+        <v>1</v>
       </c>
       <c r="H155" t="s">
-        <v>99</v>
-      </c>
-      <c r="L155" t="s">
-        <v>538</v>
-      </c>
-      <c r="M155" t="e" vm="37">
+        <v>25</v>
+      </c>
+      <c r="J155" t="s">
+        <v>247</v>
+      </c>
+      <c r="K155" s="1">
+        <v>45986</v>
+      </c>
+      <c r="L155" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="M155" t="e" vm="77">
         <v>#VALUE!</v>
       </c>
       <c r="N155" t="s">
@@ -40768,41 +41388,47 @@
         <v>20</v>
       </c>
       <c r="Q155" s="1">
-        <v>46082</v>
+        <v>45986</v>
       </c>
       <c r="S155">
         <v>1</v>
       </c>
       <c r="T155">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U155">
         <v>1</v>
       </c>
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.4">
-      <c r="A156" t="s">
-        <v>555</v>
-      </c>
-      <c r="B156" t="s">
-        <v>556</v>
+      <c r="A156" s="4" t="s">
+        <v>122</v>
       </c>
       <c r="C156" s="1">
         <v>45976</v>
       </c>
       <c r="D156" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="E156" t="s">
-        <v>557</v>
+        <v>123</v>
+      </c>
+      <c r="F156">
+        <v>2</v>
       </c>
       <c r="H156" t="s">
-        <v>99</v>
-      </c>
-      <c r="L156" t="s">
-        <v>554</v>
-      </c>
-      <c r="M156" t="e" vm="37">
+        <v>25</v>
+      </c>
+      <c r="J156" t="s">
+        <v>247</v>
+      </c>
+      <c r="K156" s="1">
+        <v>45986</v>
+      </c>
+      <c r="L156" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="M156" t="e" vm="27">
         <v>#VALUE!</v>
       </c>
       <c r="N156" t="s">
@@ -40812,7 +41438,7 @@
         <v>20</v>
       </c>
       <c r="Q156" s="1">
-        <v>45688</v>
+        <v>45988</v>
       </c>
       <c r="S156">
         <v>1</v>
@@ -40821,26 +41447,38 @@
         <v>0</v>
       </c>
       <c r="U156">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.4">
-      <c r="A157" t="s">
-        <v>561</v>
+      <c r="A157" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B157" t="s">
+        <v>638</v>
       </c>
       <c r="C157" s="1">
         <v>45976</v>
       </c>
       <c r="D157" t="s">
-        <v>42</v>
+        <v>16</v>
+      </c>
+      <c r="F157">
+        <v>2</v>
       </c>
       <c r="H157" t="s">
-        <v>99</v>
-      </c>
-      <c r="L157" t="s">
-        <v>562</v>
-      </c>
-      <c r="M157" t="e" vm="80">
+        <v>25</v>
+      </c>
+      <c r="J157" t="s">
+        <v>247</v>
+      </c>
+      <c r="K157" s="1">
+        <v>45986</v>
+      </c>
+      <c r="L157" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="M157" t="e" vm="77">
         <v>#VALUE!</v>
       </c>
       <c r="N157" t="s">
@@ -40850,7 +41488,7 @@
         <v>20</v>
       </c>
       <c r="Q157" s="1">
-        <v>46022</v>
+        <v>45989</v>
       </c>
       <c r="S157">
         <v>1</v>
@@ -40864,21 +41502,21 @@
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A158" t="s">
-        <v>564</v>
+        <v>529</v>
       </c>
       <c r="C158" s="1">
         <v>45976</v>
       </c>
       <c r="D158" t="s">
-        <v>42</v>
+        <v>530</v>
       </c>
       <c r="H158" t="s">
         <v>99</v>
       </c>
       <c r="L158" t="s">
-        <v>563</v>
-      </c>
-      <c r="M158" t="e" vm="37">
+        <v>531</v>
+      </c>
+      <c r="M158" t="e" vm="43">
         <v>#VALUE!</v>
       </c>
       <c r="N158" t="s">
@@ -40888,38 +41526,38 @@
         <v>20</v>
       </c>
       <c r="Q158" s="1">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="S158">
         <v>1</v>
       </c>
       <c r="T158">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U158">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A159" t="s">
-        <v>640</v>
+        <v>535</v>
+      </c>
+      <c r="B159" t="s">
+        <v>536</v>
       </c>
       <c r="C159" s="1">
         <v>45976</v>
       </c>
       <c r="D159" t="s">
-        <v>42</v>
-      </c>
-      <c r="E159" t="s">
-        <v>584</v>
+        <v>537</v>
       </c>
       <c r="H159" t="s">
         <v>99</v>
       </c>
       <c r="L159" t="s">
-        <v>585</v>
-      </c>
-      <c r="M159" t="e" vm="15">
+        <v>538</v>
+      </c>
+      <c r="M159" t="e" vm="37">
         <v>#VALUE!</v>
       </c>
       <c r="N159" t="s">
@@ -40929,7 +41567,7 @@
         <v>20</v>
       </c>
       <c r="Q159" s="1">
-        <v>45976</v>
+        <v>46082</v>
       </c>
       <c r="S159">
         <v>1</v>
@@ -40943,7 +41581,10 @@
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A160" t="s">
-        <v>598</v>
+        <v>555</v>
+      </c>
+      <c r="B160" t="s">
+        <v>556</v>
       </c>
       <c r="C160" s="1">
         <v>45976</v>
@@ -40952,15 +41593,15 @@
         <v>42</v>
       </c>
       <c r="E160" t="s">
-        <v>599</v>
+        <v>557</v>
       </c>
       <c r="H160" t="s">
         <v>99</v>
       </c>
       <c r="L160" t="s">
-        <v>597</v>
-      </c>
-      <c r="M160" t="e" vm="81">
+        <v>554</v>
+      </c>
+      <c r="M160" t="e" vm="37">
         <v>#VALUE!</v>
       </c>
       <c r="N160" t="s">
@@ -40970,13 +41611,13 @@
         <v>20</v>
       </c>
       <c r="Q160" s="1">
-        <v>45991</v>
+        <v>45688</v>
       </c>
       <c r="S160">
         <v>1</v>
       </c>
       <c r="T160">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U160">
         <v>1</v>
@@ -40984,10 +41625,10 @@
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A161" t="s">
-        <v>341</v>
+        <v>561</v>
       </c>
       <c r="C161" s="1">
-        <v>45981</v>
+        <v>45976</v>
       </c>
       <c r="D161" t="s">
         <v>42</v>
@@ -40996,9 +41637,9 @@
         <v>99</v>
       </c>
       <c r="L161" t="s">
-        <v>342</v>
-      </c>
-      <c r="M161" t="e" vm="77">
+        <v>562</v>
+      </c>
+      <c r="M161" t="e" vm="81">
         <v>#VALUE!</v>
       </c>
       <c r="N161" t="s">
@@ -41008,7 +41649,7 @@
         <v>20</v>
       </c>
       <c r="Q161" s="1">
-        <v>45661</v>
+        <v>46022</v>
       </c>
       <c r="S161">
         <v>1</v>
@@ -41022,21 +41663,21 @@
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A162" t="s">
-        <v>416</v>
+        <v>564</v>
       </c>
       <c r="C162" s="1">
-        <v>45981</v>
+        <v>45976</v>
       </c>
       <c r="D162" t="s">
-        <v>417</v>
+        <v>42</v>
       </c>
       <c r="H162" t="s">
         <v>99</v>
       </c>
       <c r="L162" t="s">
-        <v>105</v>
-      </c>
-      <c r="M162" t="e" vm="58">
+        <v>563</v>
+      </c>
+      <c r="M162" t="e" vm="37">
         <v>#VALUE!</v>
       </c>
       <c r="N162" t="s">
@@ -41046,42 +41687,48 @@
         <v>20</v>
       </c>
       <c r="Q162" s="1">
-        <v>45984</v>
+        <v>46053</v>
       </c>
       <c r="S162">
         <v>1</v>
       </c>
       <c r="T162">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U162">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A163" t="s">
-        <v>385</v>
+        <v>640</v>
       </c>
       <c r="C163" s="1">
-        <v>45981</v>
+        <v>45976</v>
       </c>
       <c r="D163" t="s">
-        <v>16</v>
+        <v>42</v>
+      </c>
+      <c r="E163" t="s">
+        <v>584</v>
       </c>
       <c r="H163" t="s">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="L163" t="s">
-        <v>386</v>
-      </c>
-      <c r="M163" t="e" vm="70">
+        <v>585</v>
+      </c>
+      <c r="M163" t="e" vm="15">
         <v>#VALUE!</v>
+      </c>
+      <c r="N163" t="s">
+        <v>12</v>
       </c>
       <c r="P163" t="s">
         <v>20</v>
       </c>
       <c r="Q163" s="1">
-        <v>45985</v>
+        <v>45976</v>
       </c>
       <c r="S163">
         <v>1</v>
@@ -41090,24 +41737,27 @@
         <v>0</v>
       </c>
       <c r="U163">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A164" t="s">
-        <v>356</v>
+        <v>598</v>
       </c>
       <c r="C164" s="1">
-        <v>45981</v>
+        <v>45976</v>
       </c>
       <c r="D164" t="s">
         <v>42</v>
       </c>
+      <c r="E164" t="s">
+        <v>599</v>
+      </c>
       <c r="H164" t="s">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="L164" t="s">
-        <v>355</v>
+        <v>597</v>
       </c>
       <c r="M164" t="e" vm="82">
         <v>#VALUE!</v>
@@ -41119,13 +41769,13 @@
         <v>20</v>
       </c>
       <c r="Q164" s="1">
-        <v>45987</v>
+        <v>45991</v>
       </c>
       <c r="S164">
         <v>1</v>
       </c>
       <c r="T164">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U164">
         <v>1</v>
@@ -41133,24 +41783,21 @@
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A165" t="s">
-        <v>295</v>
+        <v>692</v>
       </c>
       <c r="C165" s="1">
-        <v>45981</v>
+        <v>45976</v>
       </c>
       <c r="D165" t="s">
         <v>16</v>
       </c>
-      <c r="G165" t="s">
-        <v>296</v>
-      </c>
       <c r="H165" t="s">
         <v>25</v>
       </c>
       <c r="L165" t="s">
-        <v>294</v>
-      </c>
-      <c r="M165" t="e" vm="27">
+        <v>693</v>
+      </c>
+      <c r="M165" t="e" vm="38">
         <v>#VALUE!</v>
       </c>
       <c r="N165" t="s">
@@ -41160,7 +41807,7 @@
         <v>20</v>
       </c>
       <c r="Q165" s="1">
-        <v>45989</v>
+        <v>45984</v>
       </c>
       <c r="S165">
         <v>1</v>
@@ -41174,37 +41821,34 @@
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A166" t="s">
-        <v>298</v>
+        <v>698</v>
+      </c>
+      <c r="B166" t="s">
+        <v>700</v>
       </c>
       <c r="C166" s="1">
-        <v>45981</v>
+        <v>45976</v>
       </c>
       <c r="D166" t="s">
         <v>16</v>
       </c>
-      <c r="G166" s="2" t="s">
-        <v>299</v>
-      </c>
       <c r="H166" t="s">
         <v>25</v>
       </c>
       <c r="L166" t="s">
-        <v>297</v>
-      </c>
-      <c r="M166" t="e" vm="59">
+        <v>699</v>
+      </c>
+      <c r="M166" t="e" vm="83">
         <v>#VALUE!</v>
       </c>
       <c r="N166" t="s">
         <v>12</v>
       </c>
-      <c r="O166" t="s">
-        <v>67</v>
-      </c>
       <c r="P166" t="s">
         <v>20</v>
       </c>
       <c r="Q166" s="1">
-        <v>45989</v>
+        <v>45984</v>
       </c>
       <c r="S166">
         <v>1</v>
@@ -41217,50 +41861,38 @@
       </c>
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.4">
-      <c r="A167" s="4" t="s">
-        <v>156</v>
+      <c r="A167" t="s">
+        <v>341</v>
       </c>
       <c r="C167" s="1">
         <v>45981</v>
       </c>
       <c r="D167" t="s">
-        <v>16</v>
-      </c>
-      <c r="F167">
-        <v>1</v>
-      </c>
-      <c r="G167" s="7" t="s">
-        <v>158</v>
+        <v>42</v>
       </c>
       <c r="H167" t="s">
-        <v>25</v>
-      </c>
-      <c r="J167" t="s">
-        <v>247</v>
-      </c>
-      <c r="K167" s="1">
-        <v>45992</v>
-      </c>
-      <c r="L167" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="M167" t="e" vm="58">
+        <v>99</v>
+      </c>
+      <c r="L167" t="s">
+        <v>342</v>
+      </c>
+      <c r="M167" t="e" vm="77">
         <v>#VALUE!</v>
       </c>
       <c r="N167" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="P167" t="s">
         <v>20</v>
       </c>
       <c r="Q167" s="1">
-        <v>45991</v>
+        <v>45661</v>
       </c>
       <c r="S167">
         <v>1</v>
       </c>
       <c r="T167">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U167">
         <v>0</v>
@@ -41268,24 +41900,21 @@
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A168" t="s">
-        <v>270</v>
+        <v>416</v>
       </c>
       <c r="C168" s="1">
         <v>45981</v>
       </c>
       <c r="D168" t="s">
-        <v>16</v>
-      </c>
-      <c r="F168">
-        <v>1</v>
+        <v>417</v>
       </c>
       <c r="H168" t="s">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="L168" t="s">
-        <v>271</v>
-      </c>
-      <c r="M168" t="e" vm="83">
+        <v>105</v>
+      </c>
+      <c r="M168" t="e" vm="58">
         <v>#VALUE!</v>
       </c>
       <c r="N168" t="s">
@@ -41295,7 +41924,7 @@
         <v>20</v>
       </c>
       <c r="Q168" s="1">
-        <v>45991</v>
+        <v>45984</v>
       </c>
       <c r="S168">
         <v>1</v>
@@ -41309,7 +41938,7 @@
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A169" t="s">
-        <v>284</v>
+        <v>385</v>
       </c>
       <c r="C169" s="1">
         <v>45981</v>
@@ -41321,16 +41950,16 @@
         <v>25</v>
       </c>
       <c r="L169" t="s">
-        <v>285</v>
-      </c>
-      <c r="M169" t="e" vm="71">
+        <v>386</v>
+      </c>
+      <c r="M169" t="e" vm="70">
         <v>#VALUE!</v>
       </c>
       <c r="P169" t="s">
         <v>20</v>
       </c>
       <c r="Q169" s="1">
-        <v>45991</v>
+        <v>45985</v>
       </c>
       <c r="S169">
         <v>1</v>
@@ -41344,28 +41973,31 @@
     </row>
     <row r="170" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A170" t="s">
-        <v>286</v>
+        <v>356</v>
       </c>
       <c r="C170" s="1">
         <v>45981</v>
       </c>
       <c r="D170" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="H170" t="s">
         <v>25</v>
       </c>
       <c r="L170" t="s">
-        <v>287</v>
+        <v>355</v>
       </c>
       <c r="M170" t="e" vm="84">
         <v>#VALUE!</v>
       </c>
+      <c r="N170" t="s">
+        <v>12</v>
+      </c>
       <c r="P170" t="s">
         <v>20</v>
       </c>
       <c r="Q170" s="1">
-        <v>45991</v>
+        <v>45987</v>
       </c>
       <c r="S170">
         <v>1</v>
@@ -41374,12 +42006,12 @@
         <v>0</v>
       </c>
       <c r="U170">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="171" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A171" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="C171" s="1">
         <v>45981</v>
@@ -41387,13 +42019,16 @@
       <c r="D171" t="s">
         <v>16</v>
       </c>
+      <c r="G171" t="s">
+        <v>296</v>
+      </c>
       <c r="H171" t="s">
         <v>25</v>
       </c>
       <c r="L171" t="s">
-        <v>290</v>
-      </c>
-      <c r="M171" t="e" vm="70">
+        <v>294</v>
+      </c>
+      <c r="M171" t="e" vm="27">
         <v>#VALUE!</v>
       </c>
       <c r="N171" t="s">
@@ -41403,45 +42038,51 @@
         <v>20</v>
       </c>
       <c r="Q171" s="1">
-        <v>45991</v>
+        <v>45989</v>
       </c>
       <c r="S171">
         <v>1</v>
       </c>
       <c r="T171">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U171">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A172" t="s">
-        <v>380</v>
+        <v>298</v>
       </c>
       <c r="C172" s="1">
         <v>45981</v>
       </c>
-      <c r="D172" s="2" t="s">
-        <v>381</v>
+      <c r="D172" t="s">
+        <v>16</v>
+      </c>
+      <c r="G172" s="2" t="s">
+        <v>299</v>
       </c>
       <c r="H172" t="s">
         <v>25</v>
       </c>
       <c r="L172" t="s">
-        <v>379</v>
-      </c>
-      <c r="M172" t="e" vm="31">
+        <v>297</v>
+      </c>
+      <c r="M172" t="e" vm="59">
         <v>#VALUE!</v>
       </c>
       <c r="N172" t="s">
-        <v>28</v>
+        <v>12</v>
+      </c>
+      <c r="O172" t="s">
+        <v>67</v>
       </c>
       <c r="P172" t="s">
         <v>20</v>
       </c>
       <c r="Q172" s="1">
-        <v>45991</v>
+        <v>45989</v>
       </c>
       <c r="S172">
         <v>1</v>
@@ -41454,32 +42095,38 @@
       </c>
     </row>
     <row r="173" spans="1:21" x14ac:dyDescent="0.4">
-      <c r="A173" t="s">
-        <v>412</v>
+      <c r="A173" s="4" t="s">
+        <v>156</v>
       </c>
       <c r="C173" s="1">
         <v>45981</v>
       </c>
-      <c r="D173" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="E173" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="G173" t="s">
-        <v>415</v>
+      <c r="D173" t="s">
+        <v>16</v>
+      </c>
+      <c r="F173">
+        <v>1</v>
+      </c>
+      <c r="G173" s="7" t="s">
+        <v>158</v>
       </c>
       <c r="H173" t="s">
         <v>25</v>
       </c>
-      <c r="L173" t="s">
-        <v>111</v>
-      </c>
-      <c r="M173" t="e" vm="85">
+      <c r="J173" t="s">
+        <v>247</v>
+      </c>
+      <c r="K173" s="1">
+        <v>45992</v>
+      </c>
+      <c r="L173" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="M173" t="e" vm="58">
         <v>#VALUE!</v>
       </c>
       <c r="N173" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="P173" t="s">
         <v>20</v>
@@ -41498,8 +42145,8 @@
       </c>
     </row>
     <row r="174" spans="1:21" x14ac:dyDescent="0.4">
-      <c r="A174" s="4" t="s">
-        <v>160</v>
+      <c r="A174" t="s">
+        <v>270</v>
       </c>
       <c r="C174" s="1">
         <v>45981</v>
@@ -41513,32 +42160,26 @@
       <c r="H174" t="s">
         <v>25</v>
       </c>
-      <c r="J174" t="s">
-        <v>247</v>
-      </c>
-      <c r="K174" s="1">
-        <v>45992</v>
-      </c>
-      <c r="L174" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="M174" t="e" vm="58">
+      <c r="L174" t="s">
+        <v>271</v>
+      </c>
+      <c r="M174" t="e" vm="85">
         <v>#VALUE!</v>
       </c>
       <c r="N174" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="P174" t="s">
         <v>20</v>
       </c>
       <c r="Q174" s="1">
-        <v>45992</v>
+        <v>45991</v>
       </c>
       <c r="S174">
         <v>1</v>
       </c>
       <c r="T174">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U174">
         <v>0</v>
@@ -41546,37 +42187,28 @@
     </row>
     <row r="175" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A175" t="s">
-        <v>241</v>
+        <v>284</v>
       </c>
       <c r="C175" s="1">
         <v>45981</v>
       </c>
       <c r="D175" t="s">
-        <v>42</v>
-      </c>
-      <c r="E175" s="2" t="s">
-        <v>243</v>
+        <v>16</v>
       </c>
       <c r="H175" t="s">
         <v>25</v>
       </c>
       <c r="L175" t="s">
-        <v>242</v>
-      </c>
-      <c r="M175" t="e" vm="85">
+        <v>285</v>
+      </c>
+      <c r="M175" t="e" vm="71">
         <v>#VALUE!</v>
-      </c>
-      <c r="N175" t="s">
-        <v>12</v>
-      </c>
-      <c r="O175" t="s">
-        <v>67</v>
       </c>
       <c r="P175" t="s">
         <v>20</v>
       </c>
       <c r="Q175" s="1">
-        <v>45992</v>
+        <v>45991</v>
       </c>
       <c r="S175">
         <v>1</v>
@@ -41590,7 +42222,7 @@
     </row>
     <row r="176" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A176" t="s">
-        <v>269</v>
+        <v>286</v>
       </c>
       <c r="C176" s="1">
         <v>45981</v>
@@ -41602,25 +42234,22 @@
         <v>25</v>
       </c>
       <c r="L176" t="s">
-        <v>268</v>
-      </c>
-      <c r="M176" t="e" vm="70">
+        <v>287</v>
+      </c>
+      <c r="M176" t="e" vm="86">
         <v>#VALUE!</v>
-      </c>
-      <c r="N176" t="s">
-        <v>28</v>
       </c>
       <c r="P176" t="s">
         <v>20</v>
       </c>
       <c r="Q176" s="1">
-        <v>45992</v>
+        <v>45991</v>
       </c>
       <c r="S176">
         <v>1</v>
       </c>
       <c r="T176">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U176">
         <v>0</v>
@@ -41628,24 +42257,21 @@
     </row>
     <row r="177" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A177" t="s">
-        <v>427</v>
+        <v>291</v>
       </c>
       <c r="C177" s="1">
         <v>45981</v>
       </c>
       <c r="D177" t="s">
-        <v>429</v>
-      </c>
-      <c r="E177" t="s">
-        <v>428</v>
+        <v>16</v>
       </c>
       <c r="H177" t="s">
         <v>25</v>
       </c>
       <c r="L177" t="s">
-        <v>430</v>
-      </c>
-      <c r="M177" t="e" vm="41">
+        <v>290</v>
+      </c>
+      <c r="M177" t="e" vm="70">
         <v>#VALUE!</v>
       </c>
       <c r="N177" t="s">
@@ -41655,7 +42281,7 @@
         <v>20</v>
       </c>
       <c r="Q177" s="1">
-        <v>45992</v>
+        <v>45991</v>
       </c>
       <c r="S177">
         <v>1</v>
@@ -41669,31 +42295,31 @@
     </row>
     <row r="178" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A178" t="s">
-        <v>263</v>
+        <v>380</v>
       </c>
       <c r="C178" s="1">
         <v>45981</v>
       </c>
-      <c r="D178" t="s">
-        <v>16</v>
-      </c>
-      <c r="G178" t="s">
-        <v>265</v>
+      <c r="D178" s="2" t="s">
+        <v>381</v>
       </c>
       <c r="H178" t="s">
         <v>25</v>
       </c>
       <c r="L178" t="s">
-        <v>264</v>
-      </c>
-      <c r="M178" t="e" vm="86">
+        <v>379</v>
+      </c>
+      <c r="M178" t="e" vm="31">
         <v>#VALUE!</v>
+      </c>
+      <c r="N178" t="s">
+        <v>28</v>
       </c>
       <c r="P178" t="s">
         <v>20</v>
       </c>
       <c r="Q178" s="1">
-        <v>45994</v>
+        <v>45991</v>
       </c>
       <c r="S178">
         <v>1</v>
@@ -41707,113 +42333,128 @@
     </row>
     <row r="179" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A179" t="s">
-        <v>262</v>
+        <v>412</v>
       </c>
       <c r="C179" s="1">
         <v>45981</v>
       </c>
-      <c r="D179" t="s">
-        <v>16</v>
+      <c r="D179" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="E179" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="G179" t="s">
+        <v>415</v>
       </c>
       <c r="H179" t="s">
         <v>25</v>
       </c>
       <c r="L179" t="s">
-        <v>261</v>
-      </c>
-      <c r="M179" t="e" vm="58">
+        <v>111</v>
+      </c>
+      <c r="M179" t="e" vm="87">
         <v>#VALUE!</v>
+      </c>
+      <c r="N179" t="s">
+        <v>12</v>
       </c>
       <c r="P179" t="s">
         <v>20</v>
       </c>
       <c r="Q179" s="1">
-        <v>45998</v>
+        <v>45991</v>
       </c>
       <c r="S179">
         <v>1</v>
       </c>
       <c r="T179">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U179">
         <v>0</v>
       </c>
     </row>
     <row r="180" spans="1:21" x14ac:dyDescent="0.4">
-      <c r="A180" t="s">
-        <v>452</v>
-      </c>
-      <c r="B180" t="s">
-        <v>454</v>
+      <c r="A180" s="4" t="s">
+        <v>160</v>
       </c>
       <c r="C180" s="1">
         <v>45981</v>
       </c>
       <c r="D180" t="s">
-        <v>42</v>
-      </c>
-      <c r="E180" t="s">
-        <v>453</v>
+        <v>16</v>
+      </c>
+      <c r="F180">
+        <v>1</v>
       </c>
       <c r="H180" t="s">
         <v>25</v>
       </c>
-      <c r="L180" t="s">
-        <v>455</v>
-      </c>
-      <c r="M180" t="e" vm="45">
+      <c r="J180" t="s">
+        <v>247</v>
+      </c>
+      <c r="K180" s="1">
+        <v>45992</v>
+      </c>
+      <c r="L180" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="M180" t="e" vm="58">
         <v>#VALUE!</v>
       </c>
       <c r="N180" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="P180" t="s">
         <v>20</v>
       </c>
       <c r="Q180" s="1">
-        <v>46003</v>
+        <v>45992</v>
       </c>
       <c r="S180">
         <v>1</v>
       </c>
       <c r="T180">
+        <v>1</v>
+      </c>
+      <c r="U180">
         <v>0</v>
-      </c>
-      <c r="U180">
-        <v>1</v>
       </c>
     </row>
     <row r="181" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A181" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="C181" s="1">
         <v>45981</v>
       </c>
       <c r="D181" t="s">
-        <v>16</v>
-      </c>
-      <c r="G181" s="8" t="s">
-        <v>254</v>
+        <v>42</v>
+      </c>
+      <c r="E181" s="2" t="s">
+        <v>243</v>
       </c>
       <c r="H181" t="s">
         <v>25</v>
       </c>
       <c r="L181" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="M181" t="e" vm="87">
         <v>#VALUE!</v>
       </c>
       <c r="N181" t="s">
-        <v>28</v>
+        <v>12</v>
+      </c>
+      <c r="O181" t="s">
+        <v>67</v>
       </c>
       <c r="P181" t="s">
         <v>20</v>
       </c>
       <c r="Q181" s="1">
-        <v>46006</v>
+        <v>45992</v>
       </c>
       <c r="S181">
         <v>1</v>
@@ -41827,7 +42468,7 @@
     </row>
     <row r="182" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A182" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="C182" s="1">
         <v>45981</v>
@@ -41839,25 +42480,25 @@
         <v>25</v>
       </c>
       <c r="L182" t="s">
-        <v>256</v>
-      </c>
-      <c r="M182" t="e" vm="88">
+        <v>268</v>
+      </c>
+      <c r="M182" t="e" vm="70">
         <v>#VALUE!</v>
       </c>
       <c r="N182" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="P182" t="s">
         <v>20</v>
       </c>
       <c r="Q182" s="1">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="S182">
         <v>1</v>
       </c>
       <c r="T182">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U182">
         <v>0</v>
@@ -41865,27 +42506,24 @@
     </row>
     <row r="183" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A183" t="s">
-        <v>378</v>
+        <v>427</v>
       </c>
       <c r="C183" s="1">
         <v>45981</v>
       </c>
       <c r="D183" t="s">
-        <v>16</v>
-      </c>
-      <c r="F183">
-        <v>1</v>
-      </c>
-      <c r="G183" t="s">
-        <v>251</v>
+        <v>429</v>
+      </c>
+      <c r="E183" t="s">
+        <v>428</v>
       </c>
       <c r="H183" t="s">
         <v>25</v>
       </c>
       <c r="L183" t="s">
-        <v>250</v>
-      </c>
-      <c r="M183" t="e" vm="67">
+        <v>430</v>
+      </c>
+      <c r="M183" t="e" vm="41">
         <v>#VALUE!</v>
       </c>
       <c r="N183" t="s">
@@ -41895,42 +42533,45 @@
         <v>20</v>
       </c>
       <c r="Q183" s="1">
-        <v>46045</v>
+        <v>45992</v>
       </c>
       <c r="S183">
         <v>1</v>
       </c>
       <c r="T183">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U183">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="184" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A184" t="s">
-        <v>207</v>
+        <v>263</v>
       </c>
       <c r="C184" s="1">
         <v>45981</v>
       </c>
       <c r="D184" t="s">
-        <v>42</v>
+        <v>16</v>
+      </c>
+      <c r="G184" t="s">
+        <v>265</v>
       </c>
       <c r="H184" t="s">
         <v>25</v>
       </c>
-      <c r="L184" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="M184" t="e" vm="6">
+      <c r="L184" t="s">
+        <v>264</v>
+      </c>
+      <c r="M184" t="e" vm="88">
         <v>#VALUE!</v>
       </c>
       <c r="P184" t="s">
         <v>20</v>
       </c>
       <c r="Q184" s="1">
-        <v>46053</v>
+        <v>45994</v>
       </c>
       <c r="S184">
         <v>1</v>
@@ -41944,48 +42585,45 @@
     </row>
     <row r="185" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A185" t="s">
-        <v>479</v>
+        <v>262</v>
       </c>
       <c r="C185" s="1">
         <v>45981</v>
       </c>
       <c r="D185" t="s">
-        <v>42</v>
-      </c>
-      <c r="E185" t="s">
-        <v>480</v>
+        <v>16</v>
       </c>
       <c r="H185" t="s">
         <v>25</v>
       </c>
       <c r="L185" t="s">
-        <v>481</v>
-      </c>
-      <c r="M185" t="e" vm="89">
+        <v>261</v>
+      </c>
+      <c r="M185" t="e" vm="58">
         <v>#VALUE!</v>
-      </c>
-      <c r="N185" t="s">
-        <v>12</v>
       </c>
       <c r="P185" t="s">
         <v>20</v>
       </c>
       <c r="Q185" s="1">
-        <v>45996</v>
+        <v>45998</v>
       </c>
       <c r="S185">
         <v>1</v>
       </c>
       <c r="T185">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U185">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A186" t="s">
-        <v>485</v>
+        <v>452</v>
+      </c>
+      <c r="B186" t="s">
+        <v>454</v>
       </c>
       <c r="C186" s="1">
         <v>45981</v>
@@ -41994,31 +42632,31 @@
         <v>42</v>
       </c>
       <c r="E186" t="s">
-        <v>486</v>
+        <v>453</v>
       </c>
       <c r="H186" t="s">
         <v>25</v>
       </c>
       <c r="L186" t="s">
-        <v>487</v>
-      </c>
-      <c r="M186" t="e" vm="90">
+        <v>455</v>
+      </c>
+      <c r="M186" t="e" vm="45">
         <v>#VALUE!</v>
       </c>
       <c r="N186" t="s">
-        <v>490</v>
+        <v>12</v>
       </c>
       <c r="P186" t="s">
         <v>20</v>
       </c>
       <c r="Q186" s="1">
-        <v>45688</v>
+        <v>46003</v>
       </c>
       <c r="S186">
         <v>1</v>
       </c>
       <c r="T186">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U186">
         <v>1</v>
@@ -42026,65 +42664,62 @@
     </row>
     <row r="187" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A187" t="s">
-        <v>501</v>
+        <v>253</v>
       </c>
       <c r="C187" s="1">
         <v>45981</v>
       </c>
       <c r="D187" t="s">
-        <v>42</v>
-      </c>
-      <c r="E187" t="s">
-        <v>502</v>
+        <v>16</v>
+      </c>
+      <c r="G187" s="8" t="s">
+        <v>254</v>
       </c>
       <c r="H187" t="s">
         <v>25</v>
       </c>
       <c r="L187" t="s">
-        <v>503</v>
-      </c>
-      <c r="M187" t="e" vm="91">
+        <v>252</v>
+      </c>
+      <c r="M187" t="e" vm="89">
         <v>#VALUE!</v>
       </c>
       <c r="N187" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="P187" t="s">
         <v>20</v>
       </c>
       <c r="Q187" s="1">
-        <v>46022</v>
+        <v>46006</v>
       </c>
       <c r="S187">
         <v>1</v>
       </c>
       <c r="T187">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U187">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188" spans="1:21" x14ac:dyDescent="0.4">
-      <c r="A188" s="4" t="s">
-        <v>504</v>
+      <c r="A188" t="s">
+        <v>257</v>
       </c>
       <c r="C188" s="1">
         <v>45981</v>
       </c>
       <c r="D188" t="s">
-        <v>42</v>
-      </c>
-      <c r="F188">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="H188" t="s">
         <v>25</v>
       </c>
       <c r="L188" t="s">
-        <v>505</v>
-      </c>
-      <c r="M188" t="e" vm="85">
+        <v>256</v>
+      </c>
+      <c r="M188" t="e" vm="90">
         <v>#VALUE!</v>
       </c>
       <c r="N188" t="s">
@@ -42094,7 +42729,7 @@
         <v>20</v>
       </c>
       <c r="Q188" s="1">
-        <v>45997</v>
+        <v>46022</v>
       </c>
       <c r="S188">
         <v>1</v>
@@ -42108,21 +42743,27 @@
     </row>
     <row r="189" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A189" t="s">
-        <v>576</v>
+        <v>378</v>
       </c>
       <c r="C189" s="1">
         <v>45981</v>
       </c>
       <c r="D189" t="s">
-        <v>42</v>
+        <v>16</v>
+      </c>
+      <c r="F189">
+        <v>1</v>
+      </c>
+      <c r="G189" t="s">
+        <v>251</v>
       </c>
       <c r="H189" t="s">
         <v>25</v>
       </c>
       <c r="L189" t="s">
-        <v>575</v>
-      </c>
-      <c r="M189" t="e" vm="89">
+        <v>250</v>
+      </c>
+      <c r="M189" t="e" vm="67">
         <v>#VALUE!</v>
       </c>
       <c r="N189" t="s">
@@ -42132,21 +42773,21 @@
         <v>20</v>
       </c>
       <c r="Q189" s="1">
-        <v>45992</v>
+        <v>46045</v>
       </c>
       <c r="S189">
         <v>1</v>
       </c>
       <c r="T189">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U189">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A190" t="s">
-        <v>582</v>
+        <v>207</v>
       </c>
       <c r="C190" s="1">
         <v>45981</v>
@@ -42154,43 +42795,34 @@
       <c r="D190" t="s">
         <v>42</v>
       </c>
-      <c r="E190" t="s">
-        <v>583</v>
-      </c>
       <c r="H190" t="s">
         <v>25</v>
       </c>
-      <c r="L190" t="s">
-        <v>581</v>
-      </c>
-      <c r="M190" t="e" vm="72">
+      <c r="L190" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="M190" t="e" vm="6">
         <v>#VALUE!</v>
-      </c>
-      <c r="N190" t="s">
-        <v>12</v>
       </c>
       <c r="P190" t="s">
         <v>20</v>
       </c>
       <c r="Q190" s="1">
-        <v>45992</v>
+        <v>46053</v>
       </c>
       <c r="S190">
         <v>1</v>
       </c>
       <c r="T190">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U190">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A191" t="s">
-        <v>586</v>
-      </c>
-      <c r="B191" t="s">
-        <v>589</v>
+        <v>479</v>
       </c>
       <c r="C191" s="1">
         <v>45981</v>
@@ -42199,15 +42831,15 @@
         <v>42</v>
       </c>
       <c r="E191" t="s">
-        <v>587</v>
+        <v>480</v>
       </c>
       <c r="H191" t="s">
         <v>25</v>
       </c>
       <c r="L191" t="s">
-        <v>588</v>
-      </c>
-      <c r="M191" t="e" vm="81">
+        <v>481</v>
+      </c>
+      <c r="M191" t="e" vm="91">
         <v>#VALUE!</v>
       </c>
       <c r="N191" t="s">
@@ -42217,7 +42849,7 @@
         <v>20</v>
       </c>
       <c r="Q191" s="1">
-        <v>45991</v>
+        <v>45996</v>
       </c>
       <c r="S191">
         <v>1</v>
@@ -42231,7 +42863,7 @@
     </row>
     <row r="192" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A192" t="s">
-        <v>591</v>
+        <v>485</v>
       </c>
       <c r="C192" s="1">
         <v>45981</v>
@@ -42240,31 +42872,31 @@
         <v>42</v>
       </c>
       <c r="E192" t="s">
-        <v>592</v>
+        <v>486</v>
       </c>
       <c r="H192" t="s">
         <v>25</v>
       </c>
       <c r="L192" t="s">
-        <v>590</v>
-      </c>
-      <c r="M192" t="e" vm="81">
+        <v>487</v>
+      </c>
+      <c r="M192" t="e" vm="92">
         <v>#VALUE!</v>
       </c>
       <c r="N192" t="s">
-        <v>12</v>
+        <v>490</v>
       </c>
       <c r="P192" t="s">
         <v>20</v>
       </c>
       <c r="Q192" s="1">
-        <v>46006</v>
+        <v>45688</v>
       </c>
       <c r="S192">
         <v>1</v>
       </c>
       <c r="T192">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U192">
         <v>1</v>
@@ -42272,10 +42904,7 @@
     </row>
     <row r="193" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A193" t="s">
-        <v>593</v>
-      </c>
-      <c r="B193" t="s">
-        <v>596</v>
+        <v>501</v>
       </c>
       <c r="C193" s="1">
         <v>45981</v>
@@ -42284,15 +42913,15 @@
         <v>42</v>
       </c>
       <c r="E193" t="s">
-        <v>594</v>
+        <v>502</v>
       </c>
       <c r="H193" t="s">
         <v>25</v>
       </c>
       <c r="L193" t="s">
-        <v>595</v>
-      </c>
-      <c r="M193" t="e" vm="81">
+        <v>503</v>
+      </c>
+      <c r="M193" t="e" vm="93">
         <v>#VALUE!</v>
       </c>
       <c r="N193" t="s">
@@ -42302,24 +42931,21 @@
         <v>20</v>
       </c>
       <c r="Q193" s="1">
-        <v>45992</v>
+        <v>46022</v>
       </c>
       <c r="S193">
         <v>1</v>
       </c>
       <c r="T193">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U193">
         <v>1</v>
       </c>
     </row>
     <row r="194" spans="1:21" x14ac:dyDescent="0.4">
-      <c r="A194" t="s">
-        <v>604</v>
-      </c>
-      <c r="B194" t="s">
-        <v>606</v>
+      <c r="A194" s="4" t="s">
+        <v>504</v>
       </c>
       <c r="C194" s="1">
         <v>45981</v>
@@ -42327,25 +42953,40 @@
       <c r="D194" t="s">
         <v>42</v>
       </c>
-      <c r="E194" t="s">
-        <v>607</v>
+      <c r="F194">
+        <v>1</v>
       </c>
       <c r="H194" t="s">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="L194" t="s">
-        <v>605</v>
-      </c>
-      <c r="M194" t="e" vm="2">
+        <v>505</v>
+      </c>
+      <c r="M194" t="e" vm="87">
         <v>#VALUE!</v>
       </c>
+      <c r="N194" t="s">
+        <v>12</v>
+      </c>
+      <c r="P194" t="s">
+        <v>20</v>
+      </c>
       <c r="Q194" s="1">
-        <v>45992</v>
+        <v>45997</v>
+      </c>
+      <c r="S194">
+        <v>1</v>
+      </c>
+      <c r="T194">
+        <v>0</v>
+      </c>
+      <c r="U194">
+        <v>0</v>
       </c>
     </row>
     <row r="195" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A195" t="s">
-        <v>610</v>
+        <v>576</v>
       </c>
       <c r="C195" s="1">
         <v>45981</v>
@@ -42353,16 +42994,13 @@
       <c r="D195" t="s">
         <v>42</v>
       </c>
-      <c r="E195" t="s">
-        <v>611</v>
-      </c>
       <c r="H195" t="s">
         <v>25</v>
       </c>
       <c r="L195" t="s">
-        <v>609</v>
-      </c>
-      <c r="M195" t="e" vm="20">
+        <v>575</v>
+      </c>
+      <c r="M195" t="e" vm="91">
         <v>#VALUE!</v>
       </c>
       <c r="N195" t="s">
@@ -42372,7 +43010,7 @@
         <v>20</v>
       </c>
       <c r="Q195" s="1">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="S195">
         <v>1</v>
@@ -42386,34 +43024,28 @@
     </row>
     <row r="196" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A196" t="s">
-        <v>641</v>
-      </c>
-      <c r="B196" t="s">
-        <v>644</v>
+        <v>582</v>
       </c>
       <c r="C196" s="1">
         <v>45981</v>
       </c>
       <c r="D196" t="s">
-        <v>642</v>
+        <v>42</v>
+      </c>
+      <c r="E196" t="s">
+        <v>583</v>
       </c>
       <c r="H196" t="s">
         <v>25</v>
       </c>
-      <c r="J196" t="s">
-        <v>247</v>
-      </c>
-      <c r="K196" s="1">
-        <v>45992</v>
-      </c>
       <c r="L196" t="s">
-        <v>643</v>
-      </c>
-      <c r="M196" t="e" vm="92">
+        <v>581</v>
+      </c>
+      <c r="M196" t="e" vm="72">
         <v>#VALUE!</v>
       </c>
       <c r="N196" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="P196" t="s">
         <v>20</v>
@@ -42425,7 +43057,7 @@
         <v>1</v>
       </c>
       <c r="T196">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U196">
         <v>1</v>
@@ -42433,24 +43065,27 @@
     </row>
     <row r="197" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A197" t="s">
-        <v>647</v>
+        <v>586</v>
       </c>
       <c r="B197" t="s">
-        <v>646</v>
+        <v>589</v>
       </c>
       <c r="C197" s="1">
         <v>45981</v>
       </c>
       <c r="D197" t="s">
-        <v>648</v>
+        <v>42</v>
+      </c>
+      <c r="E197" t="s">
+        <v>587</v>
       </c>
       <c r="H197" t="s">
         <v>25</v>
       </c>
       <c r="L197" t="s">
-        <v>645</v>
-      </c>
-      <c r="M197" t="e" vm="75">
+        <v>588</v>
+      </c>
+      <c r="M197" t="e" vm="82">
         <v>#VALUE!</v>
       </c>
       <c r="N197" t="s">
@@ -42460,38 +43095,38 @@
         <v>20</v>
       </c>
       <c r="Q197" s="1">
-        <v>46022</v>
+        <v>45991</v>
       </c>
       <c r="S197">
         <v>1</v>
       </c>
       <c r="T197">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U197">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="198" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A198" t="s">
-        <v>649</v>
-      </c>
-      <c r="B198" t="s">
-        <v>652</v>
+        <v>591</v>
       </c>
       <c r="C198" s="1">
         <v>45981</v>
       </c>
       <c r="D198" t="s">
-        <v>650</v>
+        <v>42</v>
+      </c>
+      <c r="E198" t="s">
+        <v>592</v>
       </c>
       <c r="H198" t="s">
         <v>25</v>
       </c>
       <c r="L198" t="s">
-        <v>651</v>
-      </c>
-      <c r="M198" t="e" vm="93">
+        <v>590</v>
+      </c>
+      <c r="M198" t="e" vm="82">
         <v>#VALUE!</v>
       </c>
       <c r="N198" t="s">
@@ -42501,7 +43136,7 @@
         <v>20</v>
       </c>
       <c r="Q198" s="1">
-        <v>45992</v>
+        <v>46006</v>
       </c>
       <c r="S198">
         <v>1</v>
@@ -42510,30 +43145,42 @@
         <v>0</v>
       </c>
       <c r="U198">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="199" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A199" t="s">
-        <v>653</v>
+        <v>593</v>
+      </c>
+      <c r="B199" t="s">
+        <v>596</v>
       </c>
       <c r="C199" s="1">
         <v>45981</v>
       </c>
-      <c r="D199" s="2" t="s">
-        <v>655</v>
+      <c r="D199" t="s">
+        <v>42</v>
+      </c>
+      <c r="E199" t="s">
+        <v>594</v>
       </c>
       <c r="H199" t="s">
         <v>25</v>
       </c>
       <c r="L199" t="s">
-        <v>656</v>
-      </c>
-      <c r="M199" t="e" vm="11">
+        <v>595</v>
+      </c>
+      <c r="M199" t="e" vm="82">
         <v>#VALUE!</v>
       </c>
+      <c r="N199" t="s">
+        <v>12</v>
+      </c>
+      <c r="P199" t="s">
+        <v>20</v>
+      </c>
       <c r="Q199" s="1">
-        <v>45991</v>
+        <v>45992</v>
       </c>
       <c r="S199">
         <v>1</v>
@@ -42542,130 +43189,121 @@
         <v>0</v>
       </c>
       <c r="U199">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="200" spans="1:21" x14ac:dyDescent="0.4">
-      <c r="A200" s="4" t="s">
-        <v>663</v>
+      <c r="A200" t="s">
+        <v>604</v>
       </c>
       <c r="B200" t="s">
-        <v>664</v>
+        <v>606</v>
       </c>
       <c r="C200" s="1">
         <v>45981</v>
       </c>
       <c r="D200" t="s">
-        <v>16</v>
-      </c>
-      <c r="F200">
-        <v>3</v>
-      </c>
-      <c r="G200" s="2" t="s">
-        <v>665</v>
+        <v>42</v>
+      </c>
+      <c r="E200" t="s">
+        <v>607</v>
       </c>
       <c r="H200" t="s">
-        <v>25</v>
-      </c>
-      <c r="J200" t="s">
-        <v>247</v>
-      </c>
-      <c r="K200" s="1">
-        <v>45992</v>
+        <v>99</v>
       </c>
       <c r="L200" t="s">
-        <v>666</v>
-      </c>
-      <c r="M200" t="e" vm="56">
+        <v>605</v>
+      </c>
+      <c r="M200" t="e" vm="2">
         <v>#VALUE!</v>
-      </c>
-      <c r="N200" t="s">
-        <v>28</v>
-      </c>
-      <c r="P200" t="s">
-        <v>20</v>
       </c>
       <c r="Q200" s="1">
         <v>45992</v>
-      </c>
-      <c r="S200">
-        <v>1</v>
-      </c>
-      <c r="T200">
-        <v>0</v>
-      </c>
-      <c r="U200">
-        <v>0</v>
       </c>
     </row>
     <row r="201" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A201" t="s">
-        <v>670</v>
+        <v>610</v>
       </c>
       <c r="C201" s="1">
         <v>45981</v>
       </c>
       <c r="D201" t="s">
-        <v>16</v>
+        <v>42</v>
+      </c>
+      <c r="E201" t="s">
+        <v>611</v>
       </c>
       <c r="H201" t="s">
         <v>25</v>
       </c>
       <c r="L201" t="s">
-        <v>671</v>
-      </c>
-      <c r="M201" t="e" vm="86">
+        <v>609</v>
+      </c>
+      <c r="M201" t="e" vm="20">
         <v>#VALUE!</v>
+      </c>
+      <c r="N201" t="s">
+        <v>12</v>
       </c>
       <c r="P201" t="s">
         <v>20</v>
       </c>
       <c r="Q201" s="1">
-        <v>45992</v>
+        <v>45989</v>
       </c>
       <c r="S201">
         <v>1</v>
       </c>
       <c r="T201">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U201">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="202" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A202" t="s">
-        <v>358</v>
+        <v>641</v>
+      </c>
+      <c r="B202" t="s">
+        <v>644</v>
       </c>
       <c r="C202" s="1">
-        <v>45986</v>
+        <v>45981</v>
       </c>
       <c r="D202" t="s">
-        <v>360</v>
+        <v>642</v>
       </c>
       <c r="H202" t="s">
         <v>25</v>
       </c>
+      <c r="J202" t="s">
+        <v>247</v>
+      </c>
+      <c r="K202" s="1">
+        <v>45992</v>
+      </c>
       <c r="L202" t="s">
-        <v>357</v>
-      </c>
-      <c r="M202" t="e" vm="15">
+        <v>643</v>
+      </c>
+      <c r="M202" t="e" vm="94">
         <v>#VALUE!</v>
       </c>
       <c r="N202" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="P202" t="s">
         <v>20</v>
       </c>
       <c r="Q202" s="1">
-        <v>46006</v>
+        <v>45992</v>
       </c>
       <c r="S202">
         <v>1</v>
       </c>
       <c r="T202">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U202">
         <v>1</v>
@@ -42673,37 +43311,40 @@
     </row>
     <row r="203" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A203" t="s">
-        <v>525</v>
+        <v>647</v>
+      </c>
+      <c r="B203" t="s">
+        <v>646</v>
       </c>
       <c r="C203" s="1">
-        <v>45986</v>
+        <v>45981</v>
       </c>
       <c r="D203" t="s">
-        <v>42</v>
+        <v>648</v>
       </c>
       <c r="H203" t="s">
         <v>25</v>
       </c>
       <c r="L203" t="s">
-        <v>524</v>
-      </c>
-      <c r="M203" t="e" vm="36">
+        <v>645</v>
+      </c>
+      <c r="M203" t="e" vm="75">
         <v>#VALUE!</v>
       </c>
       <c r="N203" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="P203" t="s">
         <v>20</v>
       </c>
       <c r="Q203" s="1">
-        <v>45991</v>
+        <v>46022</v>
       </c>
       <c r="S203">
         <v>1</v>
       </c>
       <c r="T203">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U203">
         <v>0</v>
@@ -42711,21 +43352,24 @@
     </row>
     <row r="204" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A204" t="s">
-        <v>541</v>
+        <v>649</v>
+      </c>
+      <c r="B204" t="s">
+        <v>652</v>
       </c>
       <c r="C204" s="1">
-        <v>45986</v>
+        <v>45981</v>
       </c>
       <c r="D204" t="s">
-        <v>42</v>
+        <v>650</v>
       </c>
       <c r="H204" t="s">
         <v>25</v>
       </c>
       <c r="L204" t="s">
-        <v>542</v>
-      </c>
-      <c r="M204" t="e" vm="23">
+        <v>651</v>
+      </c>
+      <c r="M204" t="e" vm="95">
         <v>#VALUE!</v>
       </c>
       <c r="N204" t="s">
@@ -42735,45 +43379,39 @@
         <v>20</v>
       </c>
       <c r="Q204" s="1">
-        <v>46022</v>
+        <v>45992</v>
       </c>
       <c r="S204">
         <v>1</v>
       </c>
       <c r="T204">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U204">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="205" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A205" t="s">
-        <v>548</v>
+        <v>653</v>
       </c>
       <c r="C205" s="1">
-        <v>45986</v>
-      </c>
-      <c r="D205" t="s">
-        <v>547</v>
+        <v>45981</v>
+      </c>
+      <c r="D205" s="2" t="s">
+        <v>655</v>
       </c>
       <c r="H205" t="s">
         <v>25</v>
       </c>
       <c r="L205" t="s">
-        <v>546</v>
-      </c>
-      <c r="M205" t="e" vm="13">
+        <v>656</v>
+      </c>
+      <c r="M205" t="e" vm="11">
         <v>#VALUE!</v>
       </c>
-      <c r="N205" t="s">
-        <v>12</v>
-      </c>
-      <c r="P205" t="s">
-        <v>20</v>
-      </c>
       <c r="Q205" s="1">
-        <v>45992</v>
+        <v>45991</v>
       </c>
       <c r="S205">
         <v>1</v>
@@ -42786,22 +43424,37 @@
       </c>
     </row>
     <row r="206" spans="1:21" x14ac:dyDescent="0.4">
-      <c r="A206" t="s">
-        <v>418</v>
+      <c r="A206" s="4" t="s">
+        <v>663</v>
+      </c>
+      <c r="B206" t="s">
+        <v>664</v>
       </c>
       <c r="C206" s="1">
-        <v>45992</v>
+        <v>45981</v>
       </c>
       <c r="D206" t="s">
-        <v>42</v>
+        <v>16</v>
+      </c>
+      <c r="F206">
+        <v>3</v>
+      </c>
+      <c r="G206" s="2" t="s">
+        <v>665</v>
       </c>
       <c r="H206" t="s">
         <v>25</v>
       </c>
+      <c r="J206" t="s">
+        <v>247</v>
+      </c>
+      <c r="K206" s="1">
+        <v>45992</v>
+      </c>
       <c r="L206" t="s">
-        <v>419</v>
-      </c>
-      <c r="M206" t="e" vm="94">
+        <v>666</v>
+      </c>
+      <c r="M206" t="e" vm="56">
         <v>#VALUE!</v>
       </c>
       <c r="N206" t="s">
@@ -42811,13 +43464,13 @@
         <v>20</v>
       </c>
       <c r="Q206" s="1">
-        <v>45688</v>
+        <v>45992</v>
       </c>
       <c r="S206">
         <v>1</v>
       </c>
       <c r="T206">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U206">
         <v>0</v>
@@ -42825,28 +43478,31 @@
     </row>
     <row r="207" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A207" t="s">
-        <v>572</v>
+        <v>670</v>
       </c>
       <c r="C207" s="1">
-        <v>45992</v>
+        <v>45981</v>
       </c>
       <c r="D207" t="s">
-        <v>573</v>
+        <v>16</v>
       </c>
       <c r="H207" t="s">
         <v>25</v>
       </c>
       <c r="L207" t="s">
-        <v>574</v>
-      </c>
-      <c r="M207" t="e" vm="2">
+        <v>671</v>
+      </c>
+      <c r="M207" t="e" vm="88">
         <v>#VALUE!</v>
       </c>
+      <c r="P207" t="s">
+        <v>20</v>
+      </c>
       <c r="Q207" s="1">
-        <v>46053</v>
+        <v>45992</v>
       </c>
       <c r="S207">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T207">
         <v>0</v>
@@ -42856,22 +43512,28 @@
       </c>
     </row>
     <row r="208" spans="1:21" x14ac:dyDescent="0.4">
-      <c r="A208" t="s">
-        <v>618</v>
+      <c r="A208" s="4" t="s">
+        <v>680</v>
       </c>
       <c r="C208" s="1">
-        <v>45992</v>
+        <v>45981</v>
       </c>
       <c r="D208" t="s">
-        <v>617</v>
+        <v>16</v>
       </c>
       <c r="H208" t="s">
         <v>25</v>
       </c>
+      <c r="J208" t="s">
+        <v>247</v>
+      </c>
+      <c r="K208" s="1">
+        <v>45992</v>
+      </c>
       <c r="L208" t="s">
-        <v>616</v>
-      </c>
-      <c r="M208" t="e" vm="95">
+        <v>681</v>
+      </c>
+      <c r="M208" t="e" vm="58">
         <v>#VALUE!</v>
       </c>
       <c r="N208" t="s">
@@ -42881,24 +43543,27 @@
         <v>20</v>
       </c>
       <c r="Q208" s="1">
-        <v>46006</v>
+        <v>45991</v>
       </c>
       <c r="S208">
         <v>1</v>
       </c>
       <c r="T208">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U208">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="209" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A209" t="s">
-        <v>660</v>
+        <v>682</v>
+      </c>
+      <c r="B209" t="s">
+        <v>683</v>
       </c>
       <c r="C209" s="1">
-        <v>45992</v>
+        <v>45981</v>
       </c>
       <c r="D209" t="s">
         <v>16</v>
@@ -42907,60 +43572,60 @@
         <v>25</v>
       </c>
       <c r="L209" t="s">
-        <v>659</v>
-      </c>
-      <c r="M209" t="e" vm="95">
+        <v>290</v>
+      </c>
+      <c r="M209" t="e" vm="70">
         <v>#VALUE!</v>
       </c>
       <c r="N209" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="P209" t="s">
         <v>20</v>
       </c>
       <c r="Q209" s="1">
-        <v>46006</v>
+        <v>45991</v>
       </c>
       <c r="S209">
         <v>1</v>
       </c>
       <c r="T209">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U209">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="210" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A210" t="s">
-        <v>667</v>
+        <v>684</v>
       </c>
       <c r="C210" s="1">
-        <v>46011</v>
+        <v>45981</v>
       </c>
       <c r="D210" t="s">
         <v>16</v>
       </c>
       <c r="G210" t="s">
-        <v>669</v>
+        <v>686</v>
       </c>
       <c r="H210" t="s">
         <v>25</v>
       </c>
       <c r="L210" t="s">
-        <v>668</v>
-      </c>
-      <c r="M210" t="e" vm="38">
+        <v>685</v>
+      </c>
+      <c r="M210" t="e" vm="40">
         <v>#VALUE!</v>
       </c>
       <c r="N210" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="P210" t="s">
         <v>20</v>
       </c>
       <c r="Q210" s="1">
-        <v>46037</v>
+        <v>45991</v>
       </c>
       <c r="S210">
         <v>1</v>
@@ -42974,127 +43639,542 @@
     </row>
     <row r="211" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A211" t="s">
-        <v>532</v>
-      </c>
-      <c r="B211" t="s">
-        <v>181</v>
+        <v>687</v>
       </c>
       <c r="C211" s="1">
-        <v>46023</v>
+        <v>45981</v>
       </c>
       <c r="D211" t="s">
-        <v>533</v>
+        <v>16</v>
       </c>
       <c r="H211" t="s">
         <v>25</v>
       </c>
       <c r="L211" t="s">
-        <v>534</v>
-      </c>
-      <c r="M211" t="e" vm="96">
+        <v>688</v>
+      </c>
+      <c r="M211" t="e" vm="38">
         <v>#VALUE!</v>
       </c>
       <c r="N211" t="s">
-        <v>21</v>
+        <v>28</v>
+      </c>
+      <c r="P211" t="s">
+        <v>20</v>
       </c>
       <c r="Q211" s="1">
-        <v>46041</v>
+        <v>45991</v>
       </c>
       <c r="S211">
         <v>1</v>
       </c>
       <c r="T211">
+        <v>1</v>
+      </c>
+      <c r="U211">
         <v>0</v>
-      </c>
-      <c r="U211">
-        <v>1</v>
       </c>
     </row>
     <row r="212" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A212" t="s">
-        <v>258</v>
+        <v>689</v>
+      </c>
+      <c r="B212" t="s">
+        <v>691</v>
+      </c>
+      <c r="C212" s="1">
+        <v>45981</v>
       </c>
       <c r="D212" t="s">
         <v>16</v>
       </c>
-      <c r="E212" s="2" t="s">
-        <v>260</v>
-      </c>
       <c r="H212" t="s">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="L212" t="s">
-        <v>259</v>
-      </c>
-      <c r="M212" t="e" vm="28">
+        <v>690</v>
+      </c>
+      <c r="M212" t="e" vm="31">
         <v>#VALUE!</v>
-      </c>
-      <c r="N212" t="s">
-        <v>12</v>
       </c>
       <c r="P212" t="s">
         <v>20</v>
       </c>
+      <c r="Q212" s="1">
+        <v>45985</v>
+      </c>
       <c r="S212">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T212">
         <v>0</v>
       </c>
       <c r="U212">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A213" t="s">
+        <v>358</v>
+      </c>
+      <c r="C213" s="1">
+        <v>45986</v>
+      </c>
+      <c r="D213" t="s">
+        <v>360</v>
+      </c>
+      <c r="H213" t="s">
+        <v>25</v>
+      </c>
+      <c r="L213" t="s">
+        <v>357</v>
+      </c>
+      <c r="M213" t="e" vm="15">
+        <v>#VALUE!</v>
+      </c>
+      <c r="N213" t="s">
+        <v>12</v>
+      </c>
+      <c r="P213" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q213" s="1">
+        <v>46006</v>
+      </c>
+      <c r="S213">
+        <v>1</v>
+      </c>
+      <c r="T213">
+        <v>1</v>
+      </c>
+      <c r="U213">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A214" t="s">
+        <v>525</v>
+      </c>
+      <c r="C214" s="1">
+        <v>45986</v>
+      </c>
+      <c r="D214" t="s">
+        <v>42</v>
+      </c>
+      <c r="H214" t="s">
+        <v>25</v>
+      </c>
+      <c r="L214" t="s">
+        <v>524</v>
+      </c>
+      <c r="M214" t="e" vm="36">
+        <v>#VALUE!</v>
+      </c>
+      <c r="N214" t="s">
+        <v>28</v>
+      </c>
+      <c r="P214" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q214" s="1">
+        <v>45991</v>
+      </c>
+      <c r="S214">
+        <v>1</v>
+      </c>
+      <c r="T214">
+        <v>1</v>
+      </c>
+      <c r="U214">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A215" t="s">
+        <v>541</v>
+      </c>
+      <c r="C215" s="1">
+        <v>45986</v>
+      </c>
+      <c r="D215" t="s">
+        <v>42</v>
+      </c>
+      <c r="H215" t="s">
+        <v>25</v>
+      </c>
+      <c r="L215" t="s">
+        <v>542</v>
+      </c>
+      <c r="M215" t="e" vm="23">
+        <v>#VALUE!</v>
+      </c>
+      <c r="N215" t="s">
+        <v>12</v>
+      </c>
+      <c r="P215" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q215" s="1">
+        <v>46022</v>
+      </c>
+      <c r="S215">
+        <v>1</v>
+      </c>
+      <c r="T215">
+        <v>1</v>
+      </c>
+      <c r="U215">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="216" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A216" t="s">
+        <v>548</v>
+      </c>
+      <c r="C216" s="1">
+        <v>45986</v>
+      </c>
+      <c r="D216" t="s">
+        <v>547</v>
+      </c>
+      <c r="H216" t="s">
+        <v>25</v>
+      </c>
+      <c r="L216" t="s">
+        <v>546</v>
+      </c>
+      <c r="M216" t="e" vm="13">
+        <v>#VALUE!</v>
+      </c>
+      <c r="N216" t="s">
+        <v>12</v>
+      </c>
+      <c r="P216" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q216" s="1">
+        <v>45992</v>
+      </c>
+      <c r="S216">
+        <v>1</v>
+      </c>
+      <c r="T216">
+        <v>0</v>
+      </c>
+      <c r="U216">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A217" t="s">
+        <v>418</v>
+      </c>
+      <c r="C217" s="1">
+        <v>45992</v>
+      </c>
+      <c r="D217" t="s">
+        <v>42</v>
+      </c>
+      <c r="H217" t="s">
+        <v>25</v>
+      </c>
+      <c r="L217" t="s">
+        <v>419</v>
+      </c>
+      <c r="M217" t="e" vm="96">
+        <v>#VALUE!</v>
+      </c>
+      <c r="N217" t="s">
+        <v>28</v>
+      </c>
+      <c r="P217" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q217" s="1">
+        <v>45688</v>
+      </c>
+      <c r="S217">
+        <v>1</v>
+      </c>
+      <c r="T217">
+        <v>1</v>
+      </c>
+      <c r="U217">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A218" t="s">
+        <v>572</v>
+      </c>
+      <c r="C218" s="1">
+        <v>45992</v>
+      </c>
+      <c r="D218" t="s">
+        <v>573</v>
+      </c>
+      <c r="H218" t="s">
+        <v>25</v>
+      </c>
+      <c r="L218" t="s">
+        <v>574</v>
+      </c>
+      <c r="M218" t="e" vm="2">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q218" s="1">
+        <v>46053</v>
+      </c>
+      <c r="S218">
+        <v>0</v>
+      </c>
+      <c r="T218">
+        <v>0</v>
+      </c>
+      <c r="U218">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A219" t="s">
+        <v>618</v>
+      </c>
+      <c r="C219" s="1">
+        <v>45992</v>
+      </c>
+      <c r="D219" t="s">
+        <v>617</v>
+      </c>
+      <c r="H219" t="s">
+        <v>25</v>
+      </c>
+      <c r="L219" t="s">
+        <v>616</v>
+      </c>
+      <c r="M219" t="e" vm="97">
+        <v>#VALUE!</v>
+      </c>
+      <c r="N219" t="s">
+        <v>12</v>
+      </c>
+      <c r="P219" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q219" s="1">
+        <v>46006</v>
+      </c>
+      <c r="S219">
+        <v>1</v>
+      </c>
+      <c r="T219">
+        <v>1</v>
+      </c>
+      <c r="U219">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="220" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A220" t="s">
+        <v>660</v>
+      </c>
+      <c r="C220" s="1">
+        <v>45992</v>
+      </c>
+      <c r="D220" t="s">
+        <v>16</v>
+      </c>
+      <c r="H220" t="s">
+        <v>25</v>
+      </c>
+      <c r="L220" t="s">
+        <v>659</v>
+      </c>
+      <c r="M220" t="e" vm="97">
+        <v>#VALUE!</v>
+      </c>
+      <c r="N220" t="s">
+        <v>12</v>
+      </c>
+      <c r="P220" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q220" s="1">
+        <v>46006</v>
+      </c>
+      <c r="S220">
+        <v>1</v>
+      </c>
+      <c r="T220">
+        <v>0</v>
+      </c>
+      <c r="U220">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A221" t="s">
+        <v>667</v>
+      </c>
+      <c r="C221" s="1">
+        <v>46011</v>
+      </c>
+      <c r="D221" t="s">
+        <v>16</v>
+      </c>
+      <c r="G221" t="s">
+        <v>669</v>
+      </c>
+      <c r="H221" t="s">
+        <v>25</v>
+      </c>
+      <c r="L221" t="s">
+        <v>668</v>
+      </c>
+      <c r="M221" t="e" vm="38">
+        <v>#VALUE!</v>
+      </c>
+      <c r="N221" t="s">
+        <v>28</v>
+      </c>
+      <c r="P221" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q221" s="1">
+        <v>46037</v>
+      </c>
+      <c r="S221">
+        <v>1</v>
+      </c>
+      <c r="T221">
+        <v>0</v>
+      </c>
+      <c r="U221">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A222" t="s">
+        <v>532</v>
+      </c>
+      <c r="B222" t="s">
+        <v>181</v>
+      </c>
+      <c r="C222" s="1">
+        <v>46023</v>
+      </c>
+      <c r="D222" t="s">
+        <v>533</v>
+      </c>
+      <c r="H222" t="s">
+        <v>25</v>
+      </c>
+      <c r="L222" t="s">
+        <v>534</v>
+      </c>
+      <c r="M222" t="e" vm="98">
+        <v>#VALUE!</v>
+      </c>
+      <c r="N222" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q222" s="1">
+        <v>46041</v>
+      </c>
+      <c r="S222">
+        <v>1</v>
+      </c>
+      <c r="T222">
+        <v>0</v>
+      </c>
+      <c r="U222">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="223" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A223" t="s">
+        <v>258</v>
+      </c>
+      <c r="D223" t="s">
+        <v>16</v>
+      </c>
+      <c r="E223" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="H223" t="s">
+        <v>99</v>
+      </c>
+      <c r="L223" t="s">
+        <v>259</v>
+      </c>
+      <c r="M223" t="e" vm="28">
+        <v>#VALUE!</v>
+      </c>
+      <c r="N223" t="s">
+        <v>12</v>
+      </c>
+      <c r="P223" t="s">
+        <v>20</v>
+      </c>
+      <c r="S223">
+        <v>0</v>
+      </c>
+      <c r="T223">
+        <v>0</v>
+      </c>
+      <c r="U223">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:U19" xr:uid="{F7772053-9363-CA4A-A53F-040B7C700753}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U212">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U223">
       <sortCondition ref="C1:C19"/>
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="A1:A208 A210:A1048576">
-    <cfRule type="duplicateValues" dxfId="135" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="137" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:A22">
-    <cfRule type="duplicateValues" dxfId="134" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="136" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A61">
-    <cfRule type="duplicateValues" dxfId="133" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="135" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:H1048576">
-    <cfRule type="containsText" dxfId="132" priority="5" operator="containsText" text="closed">
+    <cfRule type="containsText" dxfId="134" priority="5" operator="containsText" text="closed">
       <formula>NOT(ISERROR(SEARCH("closed",H1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="131" priority="6" operator="containsText" text="abandoned">
+    <cfRule type="containsText" dxfId="133" priority="6" operator="containsText" text="abandoned">
       <formula>NOT(ISERROR(SEARCH("abandoned",H1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="130" priority="8" operator="containsText" text="late app">
+    <cfRule type="containsText" dxfId="132" priority="8" operator="containsText" text="late app">
       <formula>NOT(ISERROR(SEARCH("late app",H1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:K1048576 N78:N80 N83:N89 P87:P166 N92:N112 N115:N124 N126:N181 Q136 Q153 Q159 Q166 P168 P170:P181 Q173 Q178 P183:P191 N183:N205 P193:P205 P207:P212 N208:N211 H1:I1">
-    <cfRule type="containsText" dxfId="129" priority="11" operator="containsText" text="completed">
+  <conditionalFormatting sqref="N78:N80 N83:N89 P87:P166 N92:N112 N115:N124 N126:N181 Q136 Q153 Q159 Q166 P168 P170:P181 Q173 Q178 P183:P191 N183:N205 P193:P205 N208:N211 H1:I1 H2:K1048576 N213:N218 N220:N223 P207:P223">
+    <cfRule type="containsText" dxfId="131" priority="11" operator="containsText" text="completed">
       <formula>NOT(ISERROR(SEARCH("completed",H1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="containsText" dxfId="128" priority="1" operator="containsText" text="offer">
+    <cfRule type="containsText" dxfId="130" priority="1" operator="containsText" text="offer">
       <formula>NOT(ISERROR(SEARCH("offer",I1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="127" priority="2" operator="containsText" text="fly out">
+    <cfRule type="containsText" dxfId="129" priority="2" operator="containsText" text="fly out">
       <formula>NOT(ISERROR(SEARCH("fly out",I1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="126" priority="3" operator="containsText" text="interview">
+    <cfRule type="containsText" dxfId="128" priority="3" operator="containsText" text="interview">
       <formula>NOT(ISERROR(SEARCH("interview",I1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="125" priority="4" operator="containsText" text="rejected">
+    <cfRule type="containsText" dxfId="127" priority="4" operator="containsText" text="rejected">
       <formula>NOT(ISERROR(SEARCH("rejected",I1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J1:K1048576 N78:N80 N83:N89 P87:P166 N92:N112 N115:N124 N126:N181 Q136 Q153 Q159 Q166 P168 P170:P181 Q173 Q178 P183:P191 N183:N205 P193:P205 P207:P212 N208:N211">
-    <cfRule type="containsText" dxfId="124" priority="9" operator="containsText" text="NO">
+  <conditionalFormatting sqref="N78:N80 N83:N89 P87:P166 N92:N112 N115:N124 N126:N181 Q136 Q153 Q159 Q166 P168 P170:P181 Q173 Q178 P183:P191 N183:N205 P193:P205 N208:N211 J1:K1048576 N213:N218 N220:N223 P207:P223">
+    <cfRule type="containsText" dxfId="126" priority="9" operator="containsText" text="NO">
       <formula>NOT(ISERROR(SEARCH("NO",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="123" priority="10" operator="containsText" text="YES">
+    <cfRule type="containsText" dxfId="125" priority="10" operator="containsText" text="YES">
       <formula>NOT(ISERROR(SEARCH("YES",J1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -43131,7 +44211,7 @@
     <hyperlink ref="E15" r:id="rId30" xr:uid="{3CBBC435-61F9-034D-A9A0-B71AD9A7CCE6}"/>
     <hyperlink ref="L56" r:id="rId31" xr:uid="{115DEFD3-6759-7C49-87C4-663720AFC0F3}"/>
     <hyperlink ref="L73" r:id="rId32" xr:uid="{B568129A-4C88-5D42-B367-90B46CA6E8A2}"/>
-    <hyperlink ref="L152" r:id="rId33" xr:uid="{F3D886C1-081B-8F41-85EF-4C299E91BBDA}"/>
+    <hyperlink ref="L156" r:id="rId33" xr:uid="{F3D886C1-081B-8F41-85EF-4C299E91BBDA}"/>
     <hyperlink ref="L38" r:id="rId34" xr:uid="{14B04134-DF47-DA43-BB43-BA8C1185A50E}"/>
     <hyperlink ref="L42" r:id="rId35" display="https://www.upf.edu/" xr:uid="{F90D7817-7AA8-1C4B-8992-6FF849FBECCA}"/>
     <hyperlink ref="G9" r:id="rId36" display="mailto:ferran.mane@urv.cat" xr:uid="{DFACBA33-6641-9A4D-B406-DC2FCC993612}"/>
@@ -43139,8 +44219,8 @@
     <hyperlink ref="L110" r:id="rId38" xr:uid="{6E0CC17F-E103-7C43-850C-F0FC0B9A5278}"/>
     <hyperlink ref="L102" r:id="rId39" xr:uid="{58693CCE-AFC3-AF44-BB76-62CF466ED6EA}"/>
     <hyperlink ref="L46" r:id="rId40" xr:uid="{FC0BA615-15C1-F64A-BC32-60929732DD9E}"/>
-    <hyperlink ref="L151" r:id="rId41" xr:uid="{14CF4841-2A37-9044-AE5B-371378C8D3B9}"/>
-    <hyperlink ref="L153" r:id="rId42" xr:uid="{2E048D46-3518-2C4A-B061-479244E61709}"/>
+    <hyperlink ref="L155" r:id="rId41" xr:uid="{14CF4841-2A37-9044-AE5B-371378C8D3B9}"/>
+    <hyperlink ref="L157" r:id="rId42" xr:uid="{2E048D46-3518-2C4A-B061-479244E61709}"/>
     <hyperlink ref="L19" r:id="rId43" xr:uid="{BA26908B-8596-4249-946E-03161834E8E5}"/>
     <hyperlink ref="L60" r:id="rId44" xr:uid="{00B6A218-D9E8-3D4A-B0D7-CBDFA98EE6F3}"/>
     <hyperlink ref="D11" r:id="rId45" xr:uid="{8C412634-0F9A-E946-9A3F-CA7F4E73C3AB}"/>
@@ -43149,14 +44229,14 @@
     <hyperlink ref="D6" r:id="rId48" xr:uid="{13514A0D-2C0E-5340-8AA2-077046FFB755}"/>
     <hyperlink ref="D40" r:id="rId49" xr:uid="{DE8E5F09-1A02-F148-8539-188D3ED5C9F4}"/>
     <hyperlink ref="D36" r:id="rId50" xr:uid="{84827B93-5057-1D4A-AD4E-C9D52677D58A}"/>
-    <hyperlink ref="L167" r:id="rId51" location="/admin" xr:uid="{23CE2AD2-6E21-4241-978C-EFA7C5825B0A}"/>
-    <hyperlink ref="G167" r:id="rId52" tooltip="https://www.pierrebiscaye.com/" display="https://nam10.safelinks.protection.outlook.com/?url=https%3A%2F%2Fwww.pierrebiscaye.com%2F&amp;data=05%7C02%7Cgonzalezjj%40mail.smu.edu%7Cf17b24ecae9644d5351608de0b2d3d88%7C0f450f2e334f4bada85c9adf76051d8b%7C0%7C0%7C638960486114093769%7CUnknown%7CTWFpbGZsb3d8eyJFbXB0eU1hcGkiOnRydWUsIlYiOiIwLjAuMDAwMCIsIlAiOiJXaW4zMiIsIkFOIjoiTWFpbCIsIldUIjoyfQ%3D%3D%7C0%7C%7C%7C&amp;sdata=G3tT9q0mvtmAIBnq6zF0gIXzpLRerNt4Zfffdrm2A2E%3D&amp;reserved=0" xr:uid="{B11A9620-8D5F-6A4D-A59A-6B6DCAC23722}"/>
-    <hyperlink ref="L174" r:id="rId53" xr:uid="{7C2D96E2-AEFB-4140-A2EF-40B86E5741B1}"/>
+    <hyperlink ref="L173" r:id="rId51" location="/admin" xr:uid="{23CE2AD2-6E21-4241-978C-EFA7C5825B0A}"/>
+    <hyperlink ref="G173" r:id="rId52" tooltip="https://www.pierrebiscaye.com/" display="https://nam10.safelinks.protection.outlook.com/?url=https%3A%2F%2Fwww.pierrebiscaye.com%2F&amp;data=05%7C02%7Cgonzalezjj%40mail.smu.edu%7Cf17b24ecae9644d5351608de0b2d3d88%7C0f450f2e334f4bada85c9adf76051d8b%7C0%7C0%7C638960486114093769%7CUnknown%7CTWFpbGZsb3d8eyJFbXB0eU1hcGkiOnRydWUsIlYiOiIwLjAuMDAwMCIsIlAiOiJXaW4zMiIsIkFOIjoiTWFpbCIsIldUIjoyfQ%3D%3D%7C0%7C%7C%7C&amp;sdata=G3tT9q0mvtmAIBnq6zF0gIXzpLRerNt4Zfffdrm2A2E%3D&amp;reserved=0" xr:uid="{B11A9620-8D5F-6A4D-A59A-6B6DCAC23722}"/>
+    <hyperlink ref="L180" r:id="rId53" xr:uid="{7C2D96E2-AEFB-4140-A2EF-40B86E5741B1}"/>
     <hyperlink ref="L26" r:id="rId54" xr:uid="{35FAF041-CBFF-8A48-A4B3-B97381C00102}"/>
     <hyperlink ref="L74" r:id="rId55" xr:uid="{2D03A0F6-26F5-B24A-B91A-14D38A06B992}"/>
     <hyperlink ref="E74" r:id="rId56" display="https://academicjobsonline.org/ajo/jobs/30626" xr:uid="{46416258-D6E3-7B41-9A73-A9A4F4E6BB34}"/>
-    <hyperlink ref="L148" r:id="rId57" xr:uid="{FEED16DA-CB82-0044-943C-358B6551EC5E}"/>
-    <hyperlink ref="G148" r:id="rId58" display="mailto:a.gorbenko@ucl.co.uk" xr:uid="{5772A23E-5235-304E-A5C1-05CB3DAB9BFC}"/>
+    <hyperlink ref="L152" r:id="rId57" xr:uid="{FEED16DA-CB82-0044-943C-358B6551EC5E}"/>
+    <hyperlink ref="G152" r:id="rId58" display="mailto:a.gorbenko@ucl.co.uk" xr:uid="{5772A23E-5235-304E-A5C1-05CB3DAB9BFC}"/>
     <hyperlink ref="L28" r:id="rId59" xr:uid="{0F06344E-50D3-B54E-8250-7516D4B03802}"/>
     <hyperlink ref="E28" r:id="rId60" xr:uid="{B72DD765-9030-AC4B-9C6A-C3E6C6D825B0}"/>
     <hyperlink ref="L27" r:id="rId61" xr:uid="{521B9389-25EE-AC42-8631-0602B790BC9F}"/>
@@ -43174,25 +44254,25 @@
     <hyperlink ref="L79" r:id="rId73" xr:uid="{8E7D4522-E2CE-7043-9079-1CE2F950B085}"/>
     <hyperlink ref="D12" r:id="rId74" xr:uid="{4517EA95-990E-DE45-A804-67126FDDD4C3}"/>
     <hyperlink ref="L21" r:id="rId75" xr:uid="{91C6A3A0-FE50-5B4F-8B20-8B6496F16211}"/>
-    <hyperlink ref="L184" r:id="rId76" xr:uid="{5721E0FE-84BD-D943-BC9A-5350183D9688}"/>
+    <hyperlink ref="L190" r:id="rId76" xr:uid="{5721E0FE-84BD-D943-BC9A-5350183D9688}"/>
     <hyperlink ref="L45" r:id="rId77" xr:uid="{FE7182CC-AEDE-E142-B842-B2FE5C063CCE}"/>
     <hyperlink ref="L30" r:id="rId78" xr:uid="{694E8A95-02AE-9249-91C7-1102518BA774}"/>
     <hyperlink ref="L17" r:id="rId79" xr:uid="{9A9A6BC9-B330-7842-A78C-4DCC88F5E19F}"/>
     <hyperlink ref="L32" r:id="rId80" xr:uid="{928CABEF-4FA6-E646-8140-7B6E43F8FB96}"/>
-    <hyperlink ref="E175" r:id="rId81" xr:uid="{82BF1574-A6C6-1641-9FFE-615861E401FD}"/>
-    <hyperlink ref="E212" r:id="rId82" xr:uid="{3562807E-7FDA-F046-BA03-5DDD43072DB7}"/>
-    <hyperlink ref="G166" r:id="rId83" display="mailto:ivanpaya@ua.es" xr:uid="{DEFB77A5-E57F-714C-BAB9-56DE82BA0B2E}"/>
+    <hyperlink ref="E181" r:id="rId81" xr:uid="{82BF1574-A6C6-1641-9FFE-615861E401FD}"/>
+    <hyperlink ref="E223" r:id="rId82" xr:uid="{3562807E-7FDA-F046-BA03-5DDD43072DB7}"/>
+    <hyperlink ref="G172" r:id="rId83" display="mailto:ivanpaya@ua.es" xr:uid="{DEFB77A5-E57F-714C-BAB9-56DE82BA0B2E}"/>
     <hyperlink ref="G121" r:id="rId84" display="mailto:ari.hyytinen@hanken.fi" xr:uid="{7777B12A-FD99-4A43-A14B-A15661B760DC}"/>
     <hyperlink ref="G129" r:id="rId85" display="mailto:peter.haan@fu-berlin.de" xr:uid="{3D1A69ED-8F06-1246-B586-201CB349DB62}"/>
-    <hyperlink ref="D172" r:id="rId86" xr:uid="{C3771F9C-84FC-7A41-9911-ED3B01799C9C}"/>
-    <hyperlink ref="D173" r:id="rId87" xr:uid="{A2B41E48-AA17-FE45-B67C-A5398A81BF2D}"/>
-    <hyperlink ref="E173" r:id="rId88" xr:uid="{D2EC3FFA-793B-E54C-B216-5D503F8901AE}"/>
+    <hyperlink ref="D178" r:id="rId86" xr:uid="{C3771F9C-84FC-7A41-9911-ED3B01799C9C}"/>
+    <hyperlink ref="D179" r:id="rId87" xr:uid="{A2B41E48-AA17-FE45-B67C-A5398A81BF2D}"/>
+    <hyperlink ref="E179" r:id="rId88" xr:uid="{D2EC3FFA-793B-E54C-B216-5D503F8901AE}"/>
     <hyperlink ref="D62" r:id="rId89" xr:uid="{A30F6415-AE46-5540-B683-ED472CE378B6}"/>
     <hyperlink ref="E64" r:id="rId90" xr:uid="{F44B5BBE-5828-6740-B73D-EFF8E8646AE0}"/>
     <hyperlink ref="D24" r:id="rId91" xr:uid="{8166B827-50E4-644E-A453-5F1CFFE18AAB}"/>
     <hyperlink ref="E34" r:id="rId92" xr:uid="{CE88CF57-77B5-1E49-888D-C53C88BC7BE5}"/>
-    <hyperlink ref="D199" r:id="rId93" xr:uid="{1038528D-03E5-437B-A0C6-EA3911052C09}"/>
-    <hyperlink ref="G200" r:id="rId94" display="https://elliottash.com/" xr:uid="{00E7B1FA-3490-4C02-A813-67E9093D5D0E}"/>
+    <hyperlink ref="D205" r:id="rId93" xr:uid="{1038528D-03E5-437B-A0C6-EA3911052C09}"/>
+    <hyperlink ref="G206" r:id="rId94" display="https://elliottash.com/" xr:uid="{00E7B1FA-3490-4C02-A813-67E9093D5D0E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId95"/>
@@ -43201,7 +44281,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923E81FA-B875-3C4E-A189-1A21268FA086}">
-  <dimension ref="A1:C156"/>
+  <dimension ref="A1:C158"/>
   <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="32.83203125" customWidth="1"/>
@@ -44868,348 +45948,370 @@
         <v>100</v>
       </c>
     </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A157" s="1">
+        <v>45967</v>
+      </c>
+      <c r="B157" t="s">
+        <v>695</v>
+      </c>
+      <c r="C157" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A158" s="1">
+        <v>45967</v>
+      </c>
+      <c r="C158" t="s">
+        <v>697</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="B5">
-    <cfRule type="duplicateValues" dxfId="122" priority="128"/>
-    <cfRule type="duplicateValues" dxfId="121" priority="129"/>
+    <cfRule type="duplicateValues" dxfId="124" priority="129"/>
+    <cfRule type="duplicateValues" dxfId="123" priority="130"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B10">
-    <cfRule type="duplicateValues" dxfId="120" priority="127"/>
-    <cfRule type="duplicateValues" dxfId="119" priority="126"/>
+    <cfRule type="duplicateValues" dxfId="122" priority="128"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="127"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B11">
-    <cfRule type="duplicateValues" dxfId="118" priority="125"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="126"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="125"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B12">
+    <cfRule type="duplicateValues" dxfId="118" priority="123"/>
     <cfRule type="duplicateValues" dxfId="117" priority="124"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B12">
+  <conditionalFormatting sqref="B15">
     <cfRule type="duplicateValues" dxfId="116" priority="122"/>
-    <cfRule type="duplicateValues" dxfId="115" priority="123"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B15">
-    <cfRule type="duplicateValues" dxfId="114" priority="121"/>
-    <cfRule type="duplicateValues" dxfId="113" priority="120"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="121"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16">
-    <cfRule type="duplicateValues" dxfId="112" priority="119"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="120"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17">
-    <cfRule type="duplicateValues" dxfId="111" priority="118"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="119"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="118"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B18">
+    <cfRule type="duplicateValues" dxfId="111" priority="116"/>
     <cfRule type="duplicateValues" dxfId="110" priority="117"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B18">
+  <conditionalFormatting sqref="B19">
     <cfRule type="duplicateValues" dxfId="109" priority="115"/>
-    <cfRule type="duplicateValues" dxfId="108" priority="116"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B19">
-    <cfRule type="duplicateValues" dxfId="107" priority="114"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:B23">
-    <cfRule type="duplicateValues" dxfId="106" priority="113"/>
-    <cfRule type="duplicateValues" dxfId="105" priority="112"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="114"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="113"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B24">
-    <cfRule type="duplicateValues" dxfId="104" priority="111"/>
-    <cfRule type="duplicateValues" dxfId="103" priority="110"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="112"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="111"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B27">
-    <cfRule type="duplicateValues" dxfId="102" priority="109"/>
-    <cfRule type="duplicateValues" dxfId="101" priority="108"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="110"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="109"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28">
-    <cfRule type="duplicateValues" dxfId="100" priority="107"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="108"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29">
-    <cfRule type="duplicateValues" dxfId="99" priority="106"/>
-    <cfRule type="duplicateValues" dxfId="98" priority="105"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="107"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="106"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="97" priority="104"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="105"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31">
-    <cfRule type="duplicateValues" dxfId="96" priority="103"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="104"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="duplicateValues" dxfId="95" priority="102"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="103"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33">
-    <cfRule type="duplicateValues" dxfId="94" priority="101"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="102"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="93" priority="100"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="101"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35">
-    <cfRule type="duplicateValues" dxfId="92" priority="99"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="100"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37">
-    <cfRule type="duplicateValues" dxfId="91" priority="98"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="99"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38">
-    <cfRule type="duplicateValues" dxfId="90" priority="97"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="98"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B42">
-    <cfRule type="duplicateValues" dxfId="89" priority="96"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="97"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43">
-    <cfRule type="duplicateValues" dxfId="88" priority="95"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="96"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44:B45">
-    <cfRule type="duplicateValues" dxfId="87" priority="94"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="95"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B46">
-    <cfRule type="duplicateValues" dxfId="86" priority="93"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="94"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B48">
-    <cfRule type="duplicateValues" dxfId="85" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="93"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B49">
-    <cfRule type="duplicateValues" dxfId="84" priority="91"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="92"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B51">
-    <cfRule type="duplicateValues" dxfId="83" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="91"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B52">
-    <cfRule type="duplicateValues" dxfId="82" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="90"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B58">
-    <cfRule type="duplicateValues" dxfId="81" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="88"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B59">
-    <cfRule type="duplicateValues" dxfId="80" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="86"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B63">
-    <cfRule type="duplicateValues" dxfId="79" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="85"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B64">
-    <cfRule type="duplicateValues" dxfId="78" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="83"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B66">
-    <cfRule type="duplicateValues" dxfId="77" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="82"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="76" priority="80"/>
-    <cfRule type="duplicateValues" dxfId="75" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="80"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B68">
-    <cfRule type="duplicateValues" dxfId="74" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="79"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B69">
-    <cfRule type="duplicateValues" dxfId="73" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="78"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B70">
-    <cfRule type="duplicateValues" dxfId="72" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="76"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B72">
-    <cfRule type="duplicateValues" dxfId="71" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="75"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B73">
-    <cfRule type="duplicateValues" dxfId="70" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="73"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B74">
-    <cfRule type="duplicateValues" dxfId="69" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="72"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B75">
-    <cfRule type="duplicateValues" dxfId="68" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B76">
-    <cfRule type="duplicateValues" dxfId="67" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B77">
-    <cfRule type="duplicateValues" dxfId="66" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="68"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B78">
-    <cfRule type="duplicateValues" dxfId="65" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B83">
-    <cfRule type="duplicateValues" dxfId="64" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="66"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B84">
-    <cfRule type="duplicateValues" dxfId="63" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B85">
-    <cfRule type="duplicateValues" dxfId="62" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="64"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B87">
-    <cfRule type="duplicateValues" dxfId="61" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="63"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B88">
-    <cfRule type="duplicateValues" dxfId="60" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="62"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B89">
-    <cfRule type="duplicateValues" dxfId="59" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="61"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B90">
-    <cfRule type="duplicateValues" dxfId="58" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B91">
-    <cfRule type="duplicateValues" dxfId="57" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="59"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B92">
-    <cfRule type="duplicateValues" dxfId="56" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="58"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B93">
-    <cfRule type="duplicateValues" dxfId="55" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B94">
-    <cfRule type="duplicateValues" dxfId="54" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B95">
-    <cfRule type="duplicateValues" dxfId="53" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B96">
-    <cfRule type="duplicateValues" dxfId="52" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B97">
-    <cfRule type="duplicateValues" dxfId="51" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B98">
-    <cfRule type="duplicateValues" dxfId="50" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B99">
-    <cfRule type="duplicateValues" dxfId="49" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B100">
-    <cfRule type="duplicateValues" dxfId="48" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B101">
-    <cfRule type="duplicateValues" dxfId="47" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B104">
-    <cfRule type="duplicateValues" dxfId="46" priority="47"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B105:B106">
-    <cfRule type="duplicateValues" dxfId="44" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B107">
-    <cfRule type="duplicateValues" dxfId="43" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B108">
-    <cfRule type="duplicateValues" dxfId="42" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B109">
-    <cfRule type="duplicateValues" dxfId="41" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B110">
-    <cfRule type="duplicateValues" dxfId="40" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B111">
-    <cfRule type="duplicateValues" dxfId="39" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B112">
-    <cfRule type="duplicateValues" dxfId="38" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B113">
-    <cfRule type="duplicateValues" dxfId="37" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B114">
-    <cfRule type="duplicateValues" dxfId="36" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B115">
-    <cfRule type="duplicateValues" dxfId="35" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B116">
-    <cfRule type="duplicateValues" dxfId="34" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B117">
-    <cfRule type="duplicateValues" dxfId="33" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B118">
-    <cfRule type="duplicateValues" dxfId="32" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B119">
-    <cfRule type="duplicateValues" dxfId="31" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B120">
-    <cfRule type="duplicateValues" dxfId="30" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B121">
-    <cfRule type="duplicateValues" dxfId="29" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B122">
-    <cfRule type="duplicateValues" dxfId="28" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B126">
-    <cfRule type="duplicateValues" dxfId="27" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B127">
-    <cfRule type="duplicateValues" dxfId="26" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B128">
-    <cfRule type="duplicateValues" dxfId="25" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B129">
-    <cfRule type="duplicateValues" dxfId="24" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B130">
-    <cfRule type="duplicateValues" dxfId="23" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B131">
-    <cfRule type="duplicateValues" dxfId="22" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B132">
-    <cfRule type="duplicateValues" dxfId="21" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B133">
-    <cfRule type="duplicateValues" dxfId="20" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B136">
-    <cfRule type="duplicateValues" dxfId="19" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B137">
-    <cfRule type="duplicateValues" dxfId="18" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B138">
-    <cfRule type="duplicateValues" dxfId="17" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B139">
-    <cfRule type="duplicateValues" dxfId="16" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B140">
-    <cfRule type="duplicateValues" dxfId="15" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B141">
-    <cfRule type="duplicateValues" dxfId="14" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B142">
-    <cfRule type="duplicateValues" dxfId="13" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B143">
-    <cfRule type="duplicateValues" dxfId="12" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B144">
-    <cfRule type="duplicateValues" dxfId="11" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B145">
-    <cfRule type="duplicateValues" dxfId="10" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B147">
-    <cfRule type="duplicateValues" dxfId="9" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B148">
-    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B149">
-    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B150">
-    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B151">
-    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B152">
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B153">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B154">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B155">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B156">
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B157">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -45232,11 +46334,11 @@
       </c>
       <c r="B1" s="15">
         <f>COUNTA(sum!A:A) -1</f>
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="C1" s="14">
         <f>COUNTIF(sum!H:H, "completed")/B1</f>
-        <v>0.65402843601895733</v>
+        <v>0.62612612612612617</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.4">
@@ -45258,11 +46360,11 @@
       </c>
       <c r="B3" s="16">
         <f>COUNTA(sum!J:J) -1</f>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C3" s="10">
         <f>COUNTIFS(sum!H:H,"completed", sum!J:J, "&lt;&gt;") / B3</f>
-        <v>0.4</v>
+        <v>0.3783783783783784</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="26" x14ac:dyDescent="0.6">
@@ -45271,11 +46373,11 @@
       </c>
       <c r="B5" s="15">
         <f>COUNTA(sum!I:I) -1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" s="14">
         <f>B5/B1</f>
-        <v>4.7393364928909956E-3</v>
+        <v>9.0090090090090089E-3</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.4">
@@ -45297,7 +46399,7 @@
       </c>
       <c r="B7" s="16">
         <f>COUNTIFS(sum!I:I,"rejected")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" s="10">
         <f t="shared" ref="C7:C10" si="0">B7/$B$5</f>

--- a/EconJM_status.xlsx
+++ b/EconJM_status.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\javie\Dropbox\Work\Job Search\2025 EconJM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5E492A9-30AE-401B-9934-DDC120683073}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6BECE46-260F-430F-9FA4-C278874CD683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" xr2:uid="{6FE48536-7E5C-BF4C-9490-2A6392576298}"/>
   </bookViews>
@@ -1083,7 +1083,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2380" uniqueCount="777">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2463" uniqueCount="784">
   <si>
     <t>add_id</t>
   </si>
@@ -3451,12 +3451,33 @@
   <si>
     <t>research</t>
   </si>
+  <si>
+    <t>need people with AI</t>
+  </si>
+  <si>
+    <t>something about the ML with Python</t>
+  </si>
+  <si>
+    <t>Add that you work on AI and can teach labor</t>
+  </si>
+  <si>
+    <t>confirmation number is 7Bujxrta</t>
+  </si>
+  <si>
+    <t>AI for the finance department</t>
+  </si>
+  <si>
+    <t>Dr. Inmyung Choi, Search Committee Chair at inmyung.choi@ttu.edu</t>
+  </si>
+  <si>
+    <t>great fit with the department? (a bunch of new PhD have graduated with media + AI)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -3529,6 +3550,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -3570,7 +3598,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
@@ -3612,13 +3640,67 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="168">
+  <dxfs count="191">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -5161,11 +5243,201 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
+        <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5233,16 +5505,6 @@
       <fill>
         <patternFill patternType="none">
           <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -37278,7 +37540,7 @@
         <v>96</v>
       </c>
       <c r="J13" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M13" s="2" t="s">
         <v>83</v>
@@ -43539,7 +43801,7 @@
         <v>740</v>
       </c>
       <c r="I151" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J151" t="s">
         <v>402</v>
@@ -43570,8 +43832,11 @@
       </c>
     </row>
     <row r="152" spans="1:22" x14ac:dyDescent="0.4">
-      <c r="A152" t="s">
+      <c r="A152" s="4" t="s">
         <v>747</v>
+      </c>
+      <c r="C152" t="s">
+        <v>777</v>
       </c>
       <c r="D152" s="1">
         <v>45971</v>
@@ -43579,11 +43844,20 @@
       <c r="E152" s="2" t="s">
         <v>749</v>
       </c>
+      <c r="G152">
+        <v>1</v>
+      </c>
       <c r="I152" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J152" t="s">
         <v>402</v>
+      </c>
+      <c r="K152" t="s">
+        <v>244</v>
+      </c>
+      <c r="L152" s="1">
+        <v>45986</v>
       </c>
       <c r="M152" t="s">
         <v>748</v>
@@ -45037,7 +45311,7 @@
         <v>590</v>
       </c>
       <c r="I183" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J183" t="s">
         <v>402</v>
@@ -45068,8 +45342,11 @@
       </c>
     </row>
     <row r="184" spans="1:22" x14ac:dyDescent="0.4">
-      <c r="A184" t="s">
+      <c r="A184" s="4" t="s">
         <v>587</v>
+      </c>
+      <c r="C184" t="s">
+        <v>778</v>
       </c>
       <c r="D184" s="1">
         <v>45981</v>
@@ -45080,8 +45357,11 @@
       <c r="F184" t="s">
         <v>588</v>
       </c>
+      <c r="G184">
+        <v>1</v>
+      </c>
       <c r="I184" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J184" t="s">
         <v>402</v>
@@ -45213,7 +45493,7 @@
         <v>15</v>
       </c>
       <c r="I187" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J187" t="s">
         <v>402</v>
@@ -45292,7 +45572,7 @@
         <v>645</v>
       </c>
       <c r="I189" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J189" t="s">
         <v>402</v>
@@ -45390,7 +45670,7 @@
         <v>607</v>
       </c>
       <c r="I191" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J191" t="s">
         <v>402</v>
@@ -45472,7 +45752,7 @@
         <v>15</v>
       </c>
       <c r="I193" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J193" t="s">
         <v>402</v>
@@ -45721,7 +46001,7 @@
         <v>681</v>
       </c>
       <c r="I199" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J199" t="s">
         <v>402</v>
@@ -45762,7 +46042,7 @@
         <v>15</v>
       </c>
       <c r="I200" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J200" t="s">
         <v>402</v>
@@ -45875,8 +46155,11 @@
       </c>
     </row>
     <row r="203" spans="1:22" x14ac:dyDescent="0.4">
-      <c r="A203" t="s">
+      <c r="A203" s="4" t="s">
         <v>572</v>
+      </c>
+      <c r="C203" t="s">
+        <v>779</v>
       </c>
       <c r="D203" s="1">
         <v>45981</v>
@@ -45885,10 +46168,16 @@
         <v>40</v>
       </c>
       <c r="I203" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J203" t="s">
         <v>402</v>
+      </c>
+      <c r="K203" t="s">
+        <v>244</v>
+      </c>
+      <c r="L203" s="1">
+        <v>45992</v>
       </c>
       <c r="M203" t="s">
         <v>571</v>
@@ -45932,7 +46221,7 @@
         <v>708</v>
       </c>
       <c r="I204" t="s">
-        <v>23</v>
+        <v>152</v>
       </c>
       <c r="J204" t="s">
         <v>402</v>
@@ -46092,6 +46381,9 @@
       <c r="A208" t="s">
         <v>648</v>
       </c>
+      <c r="C208" t="s">
+        <v>780</v>
+      </c>
       <c r="D208" s="1">
         <v>45981</v>
       </c>
@@ -46099,7 +46391,7 @@
         <v>650</v>
       </c>
       <c r="I208" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J208" t="s">
         <v>402</v>
@@ -46345,7 +46637,7 @@
         <v>15</v>
       </c>
       <c r="I214" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J214" t="s">
         <v>402</v>
@@ -46467,8 +46759,11 @@
       </c>
     </row>
     <row r="217" spans="1:22" x14ac:dyDescent="0.4">
-      <c r="A217" t="s">
+      <c r="A217" s="4" t="s">
         <v>728</v>
+      </c>
+      <c r="C217" t="s">
+        <v>781</v>
       </c>
       <c r="D217" s="1">
         <v>45981</v>
@@ -46476,11 +46771,23 @@
       <c r="E217" t="s">
         <v>729</v>
       </c>
+      <c r="G217">
+        <v>1</v>
+      </c>
+      <c r="H217" t="s">
+        <v>782</v>
+      </c>
       <c r="I217" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J217" t="s">
         <v>402</v>
+      </c>
+      <c r="K217" t="s">
+        <v>244</v>
+      </c>
+      <c r="L217" s="1">
+        <v>45992</v>
       </c>
       <c r="M217" t="s">
         <v>730</v>
@@ -46524,7 +46831,7 @@
         <v>733</v>
       </c>
       <c r="I218" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J218" t="s">
         <v>402</v>
@@ -46568,7 +46875,7 @@
         <v>736</v>
       </c>
       <c r="I219" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J219" t="s">
         <v>402</v>
@@ -46606,7 +46913,7 @@
         <v>40</v>
       </c>
       <c r="I220" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J220" t="s">
         <v>402</v>
@@ -46647,10 +46954,16 @@
         <v>15</v>
       </c>
       <c r="I221" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J221" t="s">
         <v>402</v>
+      </c>
+      <c r="K221" t="s">
+        <v>244</v>
+      </c>
+      <c r="L221" s="1">
+        <v>45992</v>
       </c>
       <c r="M221" t="s">
         <v>716</v>
@@ -46688,7 +47001,7 @@
         <v>543</v>
       </c>
       <c r="I222" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J222" t="s">
         <v>402</v>
@@ -46729,7 +47042,7 @@
         <v>40</v>
       </c>
       <c r="I223" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J223" t="s">
         <v>402</v>
@@ -46773,7 +47086,7 @@
         <v>15</v>
       </c>
       <c r="I224" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J224" t="s">
         <v>402</v>
@@ -46814,7 +47127,7 @@
         <v>357</v>
       </c>
       <c r="I225" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J225" t="s">
         <v>402</v>
@@ -46858,7 +47171,7 @@
         <v>743</v>
       </c>
       <c r="I226" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J226" t="s">
         <v>402</v>
@@ -46899,7 +47212,7 @@
         <v>15</v>
       </c>
       <c r="I227" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J227" t="s">
         <v>402</v>
@@ -46937,7 +47250,7 @@
         <v>15</v>
       </c>
       <c r="I228" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J228" t="s">
         <v>402</v>
@@ -46981,10 +47294,10 @@
         <v>15</v>
       </c>
       <c r="G229">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I229" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J229" t="s">
         <v>402</v>
@@ -47031,7 +47344,7 @@
         <v>15</v>
       </c>
       <c r="I230" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J230" t="s">
         <v>402</v>
@@ -47072,7 +47385,7 @@
         <v>15</v>
       </c>
       <c r="I231" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J231" t="s">
         <v>402</v>
@@ -47109,7 +47422,7 @@
       </c>
     </row>
     <row r="232" spans="1:22" x14ac:dyDescent="0.4">
-      <c r="A232" s="4" t="s">
+      <c r="A232" s="22" t="s">
         <v>760</v>
       </c>
       <c r="D232" s="1">
@@ -47119,7 +47432,7 @@
         <v>15</v>
       </c>
       <c r="I232" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J232" t="s">
         <v>402</v>
@@ -47160,10 +47473,16 @@
         <v>15</v>
       </c>
       <c r="I233" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J233" t="s">
         <v>402</v>
+      </c>
+      <c r="K233" t="s">
+        <v>244</v>
+      </c>
+      <c r="L233" s="1">
+        <v>45992</v>
       </c>
       <c r="M233" t="s">
         <v>762</v>
@@ -47204,7 +47523,7 @@
         <v>1</v>
       </c>
       <c r="I234" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J234" t="s">
         <v>402</v>
@@ -47260,7 +47579,7 @@
         <v>768</v>
       </c>
       <c r="I235" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J235" t="s">
         <v>402</v>
@@ -47310,7 +47629,7 @@
         <v>15</v>
       </c>
       <c r="I236" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J236" t="s">
         <v>402</v>
@@ -47398,7 +47717,7 @@
         <v>15</v>
       </c>
       <c r="I238" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J238" t="s">
         <v>402</v>
@@ -47439,7 +47758,7 @@
         <v>15</v>
       </c>
       <c r="I239" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J239" t="s">
         <v>402</v>
@@ -47568,7 +47887,7 @@
         <v>664</v>
       </c>
       <c r="I242" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J242" t="s">
         <v>402</v>
@@ -47646,8 +47965,11 @@
       </c>
     </row>
     <row r="244" spans="1:22" x14ac:dyDescent="0.4">
-      <c r="A244" t="s">
+      <c r="A244" s="4" t="s">
         <v>719</v>
+      </c>
+      <c r="C244" t="s">
+        <v>783</v>
       </c>
       <c r="D244" s="1">
         <v>46016</v>
@@ -47655,13 +47977,22 @@
       <c r="E244" t="s">
         <v>15</v>
       </c>
+      <c r="G244">
+        <v>3</v>
+      </c>
       <c r="I244" t="s">
         <v>23</v>
       </c>
       <c r="J244" t="s">
         <v>402</v>
       </c>
-      <c r="M244" t="s">
+      <c r="K244" t="s">
+        <v>244</v>
+      </c>
+      <c r="L244" s="1">
+        <v>45992</v>
+      </c>
+      <c r="M244" s="2" t="s">
         <v>718</v>
       </c>
       <c r="N244" t="e" vm="45">
@@ -47816,52 +48147,52 @@
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="A1:B208 A210:B1048576">
-    <cfRule type="duplicateValues" dxfId="167" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="190" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:B22">
-    <cfRule type="duplicateValues" dxfId="166" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="189" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A61:B61">
-    <cfRule type="duplicateValues" dxfId="165" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="188" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="containsText" dxfId="164" priority="6" operator="containsText" text="closed">
+    <cfRule type="containsText" dxfId="187" priority="6" operator="containsText" text="closed">
       <formula>NOT(ISERROR(SEARCH("closed",I1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="163" priority="7" operator="containsText" text="abandoned">
+    <cfRule type="containsText" dxfId="186" priority="7" operator="containsText" text="abandoned">
       <formula>NOT(ISERROR(SEARCH("abandoned",I1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="162" priority="9" operator="containsText" text="late app">
+    <cfRule type="containsText" dxfId="185" priority="9" operator="containsText" text="late app">
       <formula>NOT(ISERROR(SEARCH("late app",I1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:L223 O78:O80 O83:O89 O92:O112 O115:O124 O126:O181 R136 R153 R159 R166 R173 R178 O183:O205 O208:O211 O213:O218 O220:O233 I224:K224 R225 I225:L1048576 O235:O237 O239:O247 I1:J1">
-    <cfRule type="containsText" dxfId="161" priority="12" operator="containsText" text="completed">
+  <conditionalFormatting sqref="I2:L223 O78:O80 O83:O89 O92:O112 O115:O124 O126:O181 R136 R153 R159 R166 R173 R178 O183:O205 O208:O211 O213:O218 O220:O233 I224:K224 R225 O235:O237 O239:O247 I1:J1 I225:L1048576">
+    <cfRule type="containsText" dxfId="4" priority="12" operator="containsText" text="completed">
       <formula>NOT(ISERROR(SEARCH("completed",I1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:J1048576">
-    <cfRule type="containsText" dxfId="160" priority="1" operator="containsText" text="no news">
+    <cfRule type="containsText" dxfId="184" priority="1" operator="containsText" text="no news">
       <formula>NOT(ISERROR(SEARCH("no news",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="159" priority="2" operator="containsText" text="offer">
+    <cfRule type="containsText" dxfId="183" priority="2" operator="containsText" text="offer">
       <formula>NOT(ISERROR(SEARCH("offer",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="158" priority="3" operator="containsText" text="fly out">
+    <cfRule type="containsText" dxfId="182" priority="3" operator="containsText" text="fly out">
       <formula>NOT(ISERROR(SEARCH("fly out",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="157" priority="4" operator="containsText" text="interview">
+    <cfRule type="containsText" dxfId="181" priority="4" operator="containsText" text="interview">
       <formula>NOT(ISERROR(SEARCH("interview",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="156" priority="5" operator="containsText" text="rejected">
+    <cfRule type="containsText" dxfId="180" priority="5" operator="containsText" text="rejected">
       <formula>NOT(ISERROR(SEARCH("rejected",J1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K1:L223 O78:O80 O83:O89 O92:O112 O115:O124 O126:O181 R136 R153 R159 R166 R173 R178 O183:O205 O208:O211 O213:O218 O220:O233 K224 R225 K225:L1048576 O235:O237 O239:O247">
-    <cfRule type="containsText" dxfId="155" priority="10" operator="containsText" text="NO">
+  <conditionalFormatting sqref="K1:L223 O78:O80 O83:O89 O92:O112 O115:O124 O126:O181 R136 R153 R159 R166 R173 R178 O183:O205 O208:O211 O213:O218 O220:O233 K224 R225 O235:O237 O239:O247 K225:L1048576">
+    <cfRule type="containsText" dxfId="3" priority="10" operator="containsText" text="NO">
       <formula>NOT(ISERROR(SEARCH("NO",K1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="154" priority="11" operator="containsText" text="YES">
+    <cfRule type="containsText" dxfId="2" priority="11" operator="containsText" text="YES">
       <formula>NOT(ISERROR(SEARCH("YES",K1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -47965,15 +48296,16 @@
     <hyperlink ref="H240" r:id="rId97" display="mailto:ondrej.krcal@econ.muni.cz" xr:uid="{EDDEB1E6-5767-4FFB-A0AE-57A909D04E81}"/>
     <hyperlink ref="M218" r:id="rId98" display="https://www.ovgu.de/unimagdeburg/en/" xr:uid="{BCB3935D-2B6D-4090-86F5-762D762ED0E3}"/>
     <hyperlink ref="E152" r:id="rId99" xr:uid="{550520C0-1E25-41CD-9AEE-9A3C4D7D328C}"/>
+    <hyperlink ref="M244" r:id="rId100" xr:uid="{F0DD6D71-3FFD-4EAB-A251-AAF2DA8EF53C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId100"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId101"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923E81FA-B875-3C4E-A189-1A21268FA086}">
-  <dimension ref="A1:C220"/>
+  <dimension ref="A1:C252"/>
   <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="32.83203125" customWidth="1"/>
@@ -50306,449 +50638,891 @@
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A218" s="1"/>
+      <c r="A218" s="1">
+        <v>45979</v>
+      </c>
+      <c r="B218" t="s">
+        <v>739</v>
+      </c>
+      <c r="C218" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A219" s="1"/>
+      <c r="A219" s="1">
+        <v>45979</v>
+      </c>
+      <c r="B219" t="s">
+        <v>747</v>
+      </c>
+      <c r="C219" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A220" s="1"/>
+      <c r="A220" s="1">
+        <v>45979</v>
+      </c>
+      <c r="B220" t="s">
+        <v>589</v>
+      </c>
+      <c r="C220" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A221" s="1">
+        <v>45979</v>
+      </c>
+      <c r="B221" t="s">
+        <v>587</v>
+      </c>
+      <c r="C221" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A222" s="1">
+        <v>45979</v>
+      </c>
+      <c r="B222" t="s">
+        <v>682</v>
+      </c>
+      <c r="C222" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A223" s="1">
+        <v>45979</v>
+      </c>
+      <c r="B223" t="s">
+        <v>644</v>
+      </c>
+      <c r="C223" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A224" s="1">
+        <v>45979</v>
+      </c>
+      <c r="B224" t="s">
+        <v>606</v>
+      </c>
+      <c r="C224" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A225" s="1">
+        <v>45979</v>
+      </c>
+      <c r="B225" t="s">
+        <v>677</v>
+      </c>
+      <c r="C225" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A226" s="1">
+        <v>45979</v>
+      </c>
+      <c r="B226" t="s">
+        <v>679</v>
+      </c>
+      <c r="C226" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A227" s="1">
+        <v>45979</v>
+      </c>
+      <c r="B227" t="s">
+        <v>665</v>
+      </c>
+      <c r="C227" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A228" s="1">
+        <v>45980</v>
+      </c>
+      <c r="B228" t="s">
+        <v>572</v>
+      </c>
+      <c r="C228" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A229" s="1">
+        <v>45980</v>
+      </c>
+      <c r="B229" t="s">
+        <v>648</v>
+      </c>
+      <c r="C229" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A230" s="1">
+        <v>45980</v>
+      </c>
+      <c r="B230" t="s">
+        <v>684</v>
+      </c>
+      <c r="C230" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A231" s="1">
+        <v>45980</v>
+      </c>
+      <c r="B231" t="s">
+        <v>728</v>
+      </c>
+      <c r="C231" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A232" s="1">
+        <v>45980</v>
+      </c>
+      <c r="B232" t="s">
+        <v>731</v>
+      </c>
+      <c r="C232" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A233" s="1">
+        <v>45980</v>
+      </c>
+      <c r="B233" t="s">
+        <v>735</v>
+      </c>
+      <c r="C233" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A234" s="1">
+        <v>45980</v>
+      </c>
+      <c r="B234" t="s">
+        <v>537</v>
+      </c>
+      <c r="C234" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A235" s="1">
+        <v>45980</v>
+      </c>
+      <c r="B235" t="s">
+        <v>717</v>
+      </c>
+      <c r="C235" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A236" s="1">
+        <v>45980</v>
+      </c>
+      <c r="B236" t="s">
+        <v>544</v>
+      </c>
+      <c r="C236" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A237" s="1">
+        <v>45980</v>
+      </c>
+      <c r="B237" t="s">
+        <v>521</v>
+      </c>
+      <c r="C237" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A238" s="1">
+        <v>45981</v>
+      </c>
+      <c r="B238" t="s">
+        <v>710</v>
+      </c>
+      <c r="C238" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A239" s="1">
+        <v>45981</v>
+      </c>
+      <c r="B239" t="s">
+        <v>355</v>
+      </c>
+      <c r="C239" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A240" s="1">
+        <v>45981</v>
+      </c>
+      <c r="B240" t="s">
+        <v>744</v>
+      </c>
+      <c r="C240" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A241" s="1">
+        <v>45981</v>
+      </c>
+      <c r="B241" t="s">
+        <v>751</v>
+      </c>
+      <c r="C241" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A242" s="1">
+        <v>45981</v>
+      </c>
+      <c r="B242" t="s">
+        <v>752</v>
+      </c>
+      <c r="C242" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A243" s="1">
+        <v>45981</v>
+      </c>
+      <c r="B243" t="s">
+        <v>756</v>
+      </c>
+      <c r="C243" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A244" s="1">
+        <v>45981</v>
+      </c>
+      <c r="B244" t="s">
+        <v>758</v>
+      </c>
+      <c r="C244" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A245" s="1">
+        <v>45981</v>
+      </c>
+      <c r="B245" t="s">
+        <v>760</v>
+      </c>
+      <c r="C245" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A246" s="1">
+        <v>45981</v>
+      </c>
+      <c r="B246" t="s">
+        <v>763</v>
+      </c>
+      <c r="C246" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A247" s="1">
+        <v>45981</v>
+      </c>
+      <c r="B247" t="s">
+        <v>765</v>
+      </c>
+      <c r="C247" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A248" s="1">
+        <v>45981</v>
+      </c>
+      <c r="B248" t="s">
+        <v>767</v>
+      </c>
+      <c r="C248" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A249" s="1">
+        <v>45981</v>
+      </c>
+      <c r="B249" t="s">
+        <v>771</v>
+      </c>
+      <c r="C249" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A250" s="1">
+        <v>45981</v>
+      </c>
+      <c r="B250" t="s">
+        <v>655</v>
+      </c>
+      <c r="C250" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A251" s="1">
+        <v>45981</v>
+      </c>
+      <c r="B251" t="s">
+        <v>613</v>
+      </c>
+      <c r="C251" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A252" s="1">
+        <v>45981</v>
+      </c>
+      <c r="B252" t="s">
+        <v>662</v>
+      </c>
+      <c r="C252" t="s">
+        <v>97</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5">
-    <cfRule type="duplicateValues" dxfId="153" priority="159"/>
-    <cfRule type="duplicateValues" dxfId="152" priority="160"/>
+    <cfRule type="duplicateValues" dxfId="179" priority="182"/>
+    <cfRule type="duplicateValues" dxfId="178" priority="183"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B10">
-    <cfRule type="duplicateValues" dxfId="151" priority="157"/>
-    <cfRule type="duplicateValues" dxfId="150" priority="158"/>
+    <cfRule type="duplicateValues" dxfId="177" priority="181"/>
+    <cfRule type="duplicateValues" dxfId="176" priority="180"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B11">
-    <cfRule type="duplicateValues" dxfId="149" priority="155"/>
-    <cfRule type="duplicateValues" dxfId="148" priority="156"/>
+    <cfRule type="duplicateValues" dxfId="175" priority="179"/>
+    <cfRule type="duplicateValues" dxfId="174" priority="178"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12">
-    <cfRule type="duplicateValues" dxfId="147" priority="153"/>
-    <cfRule type="duplicateValues" dxfId="146" priority="154"/>
+    <cfRule type="duplicateValues" dxfId="173" priority="177"/>
+    <cfRule type="duplicateValues" dxfId="172" priority="176"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15">
-    <cfRule type="duplicateValues" dxfId="145" priority="151"/>
-    <cfRule type="duplicateValues" dxfId="144" priority="152"/>
+    <cfRule type="duplicateValues" dxfId="171" priority="175"/>
+    <cfRule type="duplicateValues" dxfId="170" priority="174"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16">
-    <cfRule type="duplicateValues" dxfId="143" priority="150"/>
+    <cfRule type="duplicateValues" dxfId="169" priority="173"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17">
-    <cfRule type="duplicateValues" dxfId="142" priority="148"/>
-    <cfRule type="duplicateValues" dxfId="141" priority="149"/>
+    <cfRule type="duplicateValues" dxfId="168" priority="172"/>
+    <cfRule type="duplicateValues" dxfId="167" priority="171"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B18">
-    <cfRule type="duplicateValues" dxfId="140" priority="146"/>
-    <cfRule type="duplicateValues" dxfId="139" priority="147"/>
+    <cfRule type="duplicateValues" dxfId="166" priority="170"/>
+    <cfRule type="duplicateValues" dxfId="165" priority="169"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B19">
-    <cfRule type="duplicateValues" dxfId="138" priority="145"/>
+    <cfRule type="duplicateValues" dxfId="164" priority="168"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:B23">
-    <cfRule type="duplicateValues" dxfId="137" priority="143"/>
-    <cfRule type="duplicateValues" dxfId="136" priority="144"/>
+    <cfRule type="duplicateValues" dxfId="163" priority="167"/>
+    <cfRule type="duplicateValues" dxfId="162" priority="166"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B24">
-    <cfRule type="duplicateValues" dxfId="135" priority="141"/>
-    <cfRule type="duplicateValues" dxfId="134" priority="142"/>
+    <cfRule type="duplicateValues" dxfId="161" priority="165"/>
+    <cfRule type="duplicateValues" dxfId="160" priority="164"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B27">
-    <cfRule type="duplicateValues" dxfId="133" priority="139"/>
-    <cfRule type="duplicateValues" dxfId="132" priority="140"/>
+    <cfRule type="duplicateValues" dxfId="159" priority="163"/>
+    <cfRule type="duplicateValues" dxfId="158" priority="162"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28">
-    <cfRule type="duplicateValues" dxfId="131" priority="138"/>
+    <cfRule type="duplicateValues" dxfId="157" priority="161"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29">
-    <cfRule type="duplicateValues" dxfId="130" priority="136"/>
-    <cfRule type="duplicateValues" dxfId="129" priority="137"/>
+    <cfRule type="duplicateValues" dxfId="156" priority="160"/>
+    <cfRule type="duplicateValues" dxfId="155" priority="159"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="128" priority="135"/>
+    <cfRule type="duplicateValues" dxfId="154" priority="158"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31">
-    <cfRule type="duplicateValues" dxfId="127" priority="134"/>
+    <cfRule type="duplicateValues" dxfId="153" priority="157"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="duplicateValues" dxfId="126" priority="133"/>
+    <cfRule type="duplicateValues" dxfId="152" priority="156"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33">
-    <cfRule type="duplicateValues" dxfId="125" priority="132"/>
+    <cfRule type="duplicateValues" dxfId="151" priority="155"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="124" priority="131"/>
+    <cfRule type="duplicateValues" dxfId="150" priority="154"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35">
-    <cfRule type="duplicateValues" dxfId="123" priority="130"/>
+    <cfRule type="duplicateValues" dxfId="149" priority="153"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37">
-    <cfRule type="duplicateValues" dxfId="122" priority="129"/>
+    <cfRule type="duplicateValues" dxfId="148" priority="152"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38">
-    <cfRule type="duplicateValues" dxfId="121" priority="128"/>
+    <cfRule type="duplicateValues" dxfId="147" priority="151"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B42">
-    <cfRule type="duplicateValues" dxfId="120" priority="127"/>
+    <cfRule type="duplicateValues" dxfId="146" priority="150"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43">
-    <cfRule type="duplicateValues" dxfId="119" priority="126"/>
+    <cfRule type="duplicateValues" dxfId="145" priority="149"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44:B45">
-    <cfRule type="duplicateValues" dxfId="118" priority="125"/>
+    <cfRule type="duplicateValues" dxfId="144" priority="148"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B46">
-    <cfRule type="duplicateValues" dxfId="117" priority="124"/>
+    <cfRule type="duplicateValues" dxfId="143" priority="147"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B48">
-    <cfRule type="duplicateValues" dxfId="116" priority="123"/>
+    <cfRule type="duplicateValues" dxfId="142" priority="146"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B49">
-    <cfRule type="duplicateValues" dxfId="115" priority="122"/>
+    <cfRule type="duplicateValues" dxfId="141" priority="145"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B51">
-    <cfRule type="duplicateValues" dxfId="114" priority="121"/>
+    <cfRule type="duplicateValues" dxfId="140" priority="144"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B52">
-    <cfRule type="duplicateValues" dxfId="113" priority="120"/>
+    <cfRule type="duplicateValues" dxfId="139" priority="143"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B58">
-    <cfRule type="duplicateValues" dxfId="112" priority="118"/>
+    <cfRule type="duplicateValues" dxfId="138" priority="141"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B59">
-    <cfRule type="duplicateValues" dxfId="111" priority="116"/>
+    <cfRule type="duplicateValues" dxfId="137" priority="139"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B63">
-    <cfRule type="duplicateValues" dxfId="110" priority="115"/>
+    <cfRule type="duplicateValues" dxfId="136" priority="138"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B64">
-    <cfRule type="duplicateValues" dxfId="109" priority="113"/>
+    <cfRule type="duplicateValues" dxfId="135" priority="136"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B66">
-    <cfRule type="duplicateValues" dxfId="108" priority="112"/>
+    <cfRule type="duplicateValues" dxfId="134" priority="135"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="107" priority="110"/>
-    <cfRule type="duplicateValues" dxfId="106" priority="111"/>
+    <cfRule type="duplicateValues" dxfId="133" priority="134"/>
+    <cfRule type="duplicateValues" dxfId="132" priority="133"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B68">
-    <cfRule type="duplicateValues" dxfId="105" priority="109"/>
+    <cfRule type="duplicateValues" dxfId="131" priority="132"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B69">
-    <cfRule type="duplicateValues" dxfId="104" priority="108"/>
+    <cfRule type="duplicateValues" dxfId="130" priority="131"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B70">
-    <cfRule type="duplicateValues" dxfId="103" priority="106"/>
+    <cfRule type="duplicateValues" dxfId="129" priority="129"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B72">
-    <cfRule type="duplicateValues" dxfId="102" priority="105"/>
+    <cfRule type="duplicateValues" dxfId="128" priority="128"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B73">
-    <cfRule type="duplicateValues" dxfId="101" priority="103"/>
+    <cfRule type="duplicateValues" dxfId="127" priority="126"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B74">
-    <cfRule type="duplicateValues" dxfId="100" priority="102"/>
+    <cfRule type="duplicateValues" dxfId="126" priority="125"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B75">
-    <cfRule type="duplicateValues" dxfId="99" priority="101"/>
+    <cfRule type="duplicateValues" dxfId="125" priority="124"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B76">
-    <cfRule type="duplicateValues" dxfId="98" priority="100"/>
+    <cfRule type="duplicateValues" dxfId="124" priority="123"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B77">
-    <cfRule type="duplicateValues" dxfId="97" priority="98"/>
+    <cfRule type="duplicateValues" dxfId="123" priority="121"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B78">
-    <cfRule type="duplicateValues" dxfId="96" priority="97"/>
+    <cfRule type="duplicateValues" dxfId="122" priority="120"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B83">
-    <cfRule type="duplicateValues" dxfId="95" priority="96"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="119"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B84">
-    <cfRule type="duplicateValues" dxfId="94" priority="95"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="118"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B85">
-    <cfRule type="duplicateValues" dxfId="93" priority="94"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="117"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B87">
-    <cfRule type="duplicateValues" dxfId="92" priority="93"/>
+    <cfRule type="duplicateValues" dxfId="118" priority="116"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B88">
-    <cfRule type="duplicateValues" dxfId="91" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="115"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B89">
-    <cfRule type="duplicateValues" dxfId="90" priority="91"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="114"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B90">
-    <cfRule type="duplicateValues" dxfId="89" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="113"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B91">
-    <cfRule type="duplicateValues" dxfId="88" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="112"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B92">
-    <cfRule type="duplicateValues" dxfId="87" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="111"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B93">
-    <cfRule type="duplicateValues" dxfId="86" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="110"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B94">
-    <cfRule type="duplicateValues" dxfId="85" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="111" priority="109"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B95">
-    <cfRule type="duplicateValues" dxfId="84" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="108"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B96">
-    <cfRule type="duplicateValues" dxfId="83" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="107"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B97">
-    <cfRule type="duplicateValues" dxfId="82" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="106"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B98">
-    <cfRule type="duplicateValues" dxfId="81" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="105"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B99">
-    <cfRule type="duplicateValues" dxfId="80" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="104"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B100">
-    <cfRule type="duplicateValues" dxfId="79" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="103"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B101">
-    <cfRule type="duplicateValues" dxfId="78" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="102"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B104">
-    <cfRule type="duplicateValues" dxfId="77" priority="77"/>
-    <cfRule type="duplicateValues" dxfId="76" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="101"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="100"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B105:B106">
-    <cfRule type="duplicateValues" dxfId="75" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="99"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B107">
-    <cfRule type="duplicateValues" dxfId="74" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="98"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B108">
-    <cfRule type="duplicateValues" dxfId="73" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="97"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B109">
-    <cfRule type="duplicateValues" dxfId="72" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="96"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B110">
-    <cfRule type="duplicateValues" dxfId="71" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="95"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B111">
-    <cfRule type="duplicateValues" dxfId="70" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="94"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B112">
-    <cfRule type="duplicateValues" dxfId="69" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="93"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B113">
-    <cfRule type="duplicateValues" dxfId="68" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="92"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B114">
-    <cfRule type="duplicateValues" dxfId="67" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="91"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B115">
-    <cfRule type="duplicateValues" dxfId="66" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="90"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B116">
-    <cfRule type="duplicateValues" dxfId="65" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="89"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B117">
-    <cfRule type="duplicateValues" dxfId="64" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="88"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B118">
-    <cfRule type="duplicateValues" dxfId="63" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="87"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B119">
-    <cfRule type="duplicateValues" dxfId="62" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="86"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B120">
-    <cfRule type="duplicateValues" dxfId="61" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="85"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B121">
-    <cfRule type="duplicateValues" dxfId="60" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="84"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B122">
-    <cfRule type="duplicateValues" dxfId="59" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="83"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B126">
-    <cfRule type="duplicateValues" dxfId="58" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="82"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B127">
-    <cfRule type="duplicateValues" dxfId="57" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="81"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B128">
-    <cfRule type="duplicateValues" dxfId="56" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="80"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B129">
-    <cfRule type="duplicateValues" dxfId="55" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="79"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B130">
-    <cfRule type="duplicateValues" dxfId="54" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="78"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B131">
-    <cfRule type="duplicateValues" dxfId="53" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="77"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B132">
-    <cfRule type="duplicateValues" dxfId="52" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="76"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B133">
-    <cfRule type="duplicateValues" dxfId="51" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="75"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B136">
-    <cfRule type="duplicateValues" dxfId="50" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="74"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B137">
-    <cfRule type="duplicateValues" dxfId="49" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="73"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B138">
-    <cfRule type="duplicateValues" dxfId="48" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="72"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B139">
-    <cfRule type="duplicateValues" dxfId="47" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B140">
-    <cfRule type="duplicateValues" dxfId="46" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B141">
-    <cfRule type="duplicateValues" dxfId="45" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="69"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B142">
-    <cfRule type="duplicateValues" dxfId="44" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="68"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B143">
-    <cfRule type="duplicateValues" dxfId="43" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B144">
-    <cfRule type="duplicateValues" dxfId="42" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="66"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B145">
-    <cfRule type="duplicateValues" dxfId="41" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B147">
-    <cfRule type="duplicateValues" dxfId="40" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="64"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B148">
-    <cfRule type="duplicateValues" dxfId="39" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="63"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B149">
-    <cfRule type="duplicateValues" dxfId="38" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="62"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B150">
-    <cfRule type="duplicateValues" dxfId="37" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="61"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B151">
-    <cfRule type="duplicateValues" dxfId="36" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B152">
-    <cfRule type="duplicateValues" dxfId="35" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="59"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B153">
-    <cfRule type="duplicateValues" dxfId="34" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="58"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B154">
-    <cfRule type="duplicateValues" dxfId="33" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B155">
-    <cfRule type="duplicateValues" dxfId="32" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B156">
-    <cfRule type="duplicateValues" dxfId="31" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B157">
-    <cfRule type="duplicateValues" dxfId="30" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B171">
-    <cfRule type="duplicateValues" dxfId="29" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B172">
-    <cfRule type="duplicateValues" dxfId="28" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B174">
-    <cfRule type="duplicateValues" dxfId="27" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B177:B178">
-    <cfRule type="duplicateValues" dxfId="26" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B181">
-    <cfRule type="duplicateValues" dxfId="25" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B182">
-    <cfRule type="duplicateValues" dxfId="24" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B183">
-    <cfRule type="duplicateValues" dxfId="23" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B184">
-    <cfRule type="duplicateValues" dxfId="22" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B185">
-    <cfRule type="duplicateValues" dxfId="21" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B186">
-    <cfRule type="duplicateValues" dxfId="20" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B188">
-    <cfRule type="duplicateValues" dxfId="19" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B189">
-    <cfRule type="duplicateValues" dxfId="18" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B190">
-    <cfRule type="duplicateValues" dxfId="17" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B191">
-    <cfRule type="duplicateValues" dxfId="16" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B192">
-    <cfRule type="duplicateValues" dxfId="15" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B193">
-    <cfRule type="duplicateValues" dxfId="14" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B195">
-    <cfRule type="duplicateValues" dxfId="13" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B196">
-    <cfRule type="duplicateValues" dxfId="12" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B197">
-    <cfRule type="duplicateValues" dxfId="11" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B198">
-    <cfRule type="duplicateValues" dxfId="10" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B199">
-    <cfRule type="duplicateValues" dxfId="9" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B200">
-    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B201">
-    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B202">
-    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B203">
-    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B204">
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B205">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B206">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B207">
+    <cfRule type="duplicateValues" dxfId="27" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B215">
+    <cfRule type="duplicateValues" dxfId="26" priority="24"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B218">
+    <cfRule type="duplicateValues" dxfId="25" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B220">
+    <cfRule type="duplicateValues" dxfId="24" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B222">
+    <cfRule type="duplicateValues" dxfId="23" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B223">
+    <cfRule type="duplicateValues" dxfId="22" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B224">
+    <cfRule type="duplicateValues" dxfId="21" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B225">
+    <cfRule type="duplicateValues" dxfId="20" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B227">
+    <cfRule type="duplicateValues" dxfId="19" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B229">
+    <cfRule type="duplicateValues" dxfId="18" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B230">
+    <cfRule type="duplicateValues" dxfId="17" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B232">
+    <cfRule type="duplicateValues" dxfId="16" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B233">
+    <cfRule type="duplicateValues" dxfId="15" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B234">
+    <cfRule type="duplicateValues" dxfId="14" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B235">
+    <cfRule type="duplicateValues" dxfId="13" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B236">
+    <cfRule type="duplicateValues" dxfId="12" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B237">
+    <cfRule type="duplicateValues" dxfId="11" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B239">
+    <cfRule type="duplicateValues" dxfId="9" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B240">
+    <cfRule type="duplicateValues" dxfId="8" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B241">
+    <cfRule type="duplicateValues" dxfId="7" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B242">
+    <cfRule type="duplicateValues" dxfId="6" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B243">
+    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B250">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B215">
+  <conditionalFormatting sqref="B251">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -50757,7 +51531,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{852B2CA5-879F-3640-8AF9-56395EF3FA0F}">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="15.83203125" style="12" customWidth="1"/>
@@ -50765,7 +51539,7 @@
     <col min="3" max="3" width="10.83203125" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="26" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:4" ht="26" x14ac:dyDescent="0.6">
       <c r="A1" s="11" t="s">
         <v>399</v>
       </c>
@@ -50775,36 +51549,40 @@
       </c>
       <c r="C1" s="14">
         <f>COUNTIF(sum!I:I, "completed")/B1</f>
-        <v>0.80081300813008127</v>
+        <v>0.94715447154471544</v>
+      </c>
+      <c r="D1" s="21">
+        <f>COUNTIF(sum!I:I, "completed")</f>
+        <v>233</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="13" t="s">
         <v>400</v>
       </c>
       <c r="B2" s="16">
         <f>COUNTA(sum!G:G) -1</f>
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C2" s="10">
         <f>COUNTIFS(sum!I:I,"completed", sum!G:G, "&lt;&gt;") / B2</f>
-        <v>0.89795918367346939</v>
+        <v>0.94339622641509435</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="13" t="s">
         <v>774</v>
       </c>
       <c r="B3" s="16">
         <f>COUNTA(sum!K:K) -1</f>
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C3" s="10">
         <f>COUNTIFS(sum!I:I,"completed", sum!K:K, "&lt;&gt;") / B3</f>
-        <v>0.9</v>
+        <v>0.9821428571428571</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="26" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:4" ht="26" x14ac:dyDescent="0.6">
       <c r="A5" s="11" t="s">
         <v>401</v>
       </c>
@@ -50817,33 +51595,33 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" s="13" t="s">
         <v>402</v>
       </c>
       <c r="B6" s="16">
         <f>COUNTIFS(sum!J:J,"no news")</f>
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C6" s="10">
         <f>B6/$B$5</f>
-        <v>0.98373983739837401</v>
+        <v>0.97967479674796742</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" s="13" t="s">
         <v>403</v>
       </c>
       <c r="B7" s="16">
         <f>COUNTIFS(sum!J:J,"rejected")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C7" s="10">
         <f t="shared" ref="C7:C10" si="0">B7/$B$5</f>
-        <v>1.6260162601626018E-2</v>
+        <v>2.032520325203252E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8" s="13" t="s">
         <v>404</v>
       </c>
@@ -50856,7 +51634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9" s="18" t="s">
         <v>405</v>
       </c>
@@ -50869,7 +51647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A10" s="13" t="s">
         <v>406</v>
       </c>

--- a/EconJM_status.xlsx
+++ b/EconJM_status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\javie\Dropbox\Work\Job Search\2025 EconJM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6BECE46-260F-430F-9FA4-C278874CD683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{818DAC6E-E42D-4253-9031-FD3B496FCE97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" xr2:uid="{6FE48536-7E5C-BF4C-9490-2A6392576298}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" activeTab="2" xr2:uid="{6FE48536-7E5C-BF4C-9490-2A6392576298}"/>
   </bookViews>
   <sheets>
     <sheet name="sum" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="stats" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sum!$A$1:$V$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sum!$A$1:$V$248</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1083,7 +1083,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2463" uniqueCount="784">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2496" uniqueCount="789">
   <si>
     <t>add_id</t>
   </si>
@@ -3471,6 +3471,21 @@
   </si>
   <si>
     <t>great fit with the department? (a bunch of new PhD have graduated with media + AI)</t>
+  </si>
+  <si>
+    <t>dartmouth_post</t>
+  </si>
+  <si>
+    <t>https://apply.interfolio.com/176743</t>
+  </si>
+  <si>
+    <t>Dartmouth</t>
+  </si>
+  <si>
+    <t>eca</t>
+  </si>
+  <si>
+    <t>E.CA Economics</t>
   </si>
 </sst>
 </file>
@@ -3598,7 +3613,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
@@ -3644,13 +3659,16 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="191">
+  <dxfs count="194">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3658,46 +3676,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5455,6 +5433,66 @@
       <font>
         <color rgb="FF9C0006"/>
       </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -5505,6 +5543,16 @@
       <fill>
         <patternFill patternType="none">
           <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -36926,7 +36974,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7772053-9363-CA4A-A53F-040B7C700753}">
-  <dimension ref="A1:V247"/>
+  <dimension ref="A1:V249"/>
   <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="19.6640625" customWidth="1"/>
@@ -38659,7 +38707,7 @@
       <c r="A38" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B38" s="19"/>
+      <c r="B38" s="22"/>
       <c r="D38" s="1">
         <v>45955</v>
       </c>
@@ -40095,6 +40143,7 @@
       <c r="A71" s="4" t="s">
         <v>314</v>
       </c>
+      <c r="B71" s="19"/>
       <c r="C71" t="s">
         <v>315</v>
       </c>
@@ -40199,7 +40248,7 @@
       <c r="A73" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="B73" s="19"/>
+      <c r="B73" s="22"/>
       <c r="C73" t="s">
         <v>407</v>
       </c>
@@ -40911,9 +40960,10 @@
       </c>
     </row>
     <row r="89" spans="1:22" x14ac:dyDescent="0.4">
-      <c r="A89" t="s">
+      <c r="A89" s="4" t="s">
         <v>327</v>
       </c>
+      <c r="B89" s="19"/>
       <c r="D89" s="1">
         <v>45966</v>
       </c>
@@ -42087,7 +42137,7 @@
       <c r="A113" s="4" t="s">
         <v>388</v>
       </c>
-      <c r="B113" s="19"/>
+      <c r="B113" s="22"/>
       <c r="C113" t="s">
         <v>390</v>
       </c>
@@ -42192,7 +42242,7 @@
       <c r="A115" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="B115" s="19"/>
+      <c r="B115" s="22"/>
       <c r="C115" t="s">
         <v>346</v>
       </c>
@@ -43991,6 +44041,7 @@
       <c r="A155" s="4" t="s">
         <v>140</v>
       </c>
+      <c r="B155" s="19"/>
       <c r="C155" t="s">
         <v>633</v>
       </c>
@@ -45960,7 +46011,7 @@
         <v>96</v>
       </c>
       <c r="J198" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M198" t="s">
         <v>376</v>
@@ -46394,7 +46445,7 @@
         <v>96</v>
       </c>
       <c r="J208" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M208" t="s">
         <v>651</v>
@@ -47422,7 +47473,7 @@
       </c>
     </row>
     <row r="232" spans="1:22" x14ac:dyDescent="0.4">
-      <c r="A232" s="22" t="s">
+      <c r="A232" t="s">
         <v>760</v>
       </c>
       <c r="D232" s="1">
@@ -47676,7 +47727,7 @@
         <v>40</v>
       </c>
       <c r="I237" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J237" t="s">
         <v>402</v>
@@ -47805,7 +47856,7 @@
         <v>715</v>
       </c>
       <c r="I240" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J240" t="s">
         <v>402</v>
@@ -47846,7 +47897,7 @@
         <v>569</v>
       </c>
       <c r="I241" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J241" t="s">
         <v>402</v>
@@ -47934,7 +47985,7 @@
         <v>721</v>
       </c>
       <c r="I243" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J243" t="s">
         <v>402</v>
@@ -47968,6 +48019,7 @@
       <c r="A244" s="4" t="s">
         <v>719</v>
       </c>
+      <c r="B244" s="19"/>
       <c r="C244" t="s">
         <v>783</v>
       </c>
@@ -47981,7 +48033,7 @@
         <v>3</v>
       </c>
       <c r="I244" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J244" t="s">
         <v>402</v>
@@ -48031,7 +48083,7 @@
         <v>529</v>
       </c>
       <c r="I245" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J245" t="s">
         <v>402</v>
@@ -48140,59 +48192,147 @@
         <v>0</v>
       </c>
     </row>
+    <row r="248" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A248" t="s">
+        <v>784</v>
+      </c>
+      <c r="D248" s="1">
+        <v>45992</v>
+      </c>
+      <c r="E248" t="s">
+        <v>40</v>
+      </c>
+      <c r="F248" t="s">
+        <v>785</v>
+      </c>
+      <c r="I248" t="s">
+        <v>23</v>
+      </c>
+      <c r="J248" t="s">
+        <v>402</v>
+      </c>
+      <c r="K248" t="s">
+        <v>244</v>
+      </c>
+      <c r="L248" s="1">
+        <v>46027</v>
+      </c>
+      <c r="M248" t="s">
+        <v>786</v>
+      </c>
+      <c r="N248" t="e" vm="35">
+        <v>#VALUE!</v>
+      </c>
+      <c r="O248" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q248" t="s">
+        <v>776</v>
+      </c>
+      <c r="R248" s="1">
+        <v>46026</v>
+      </c>
+      <c r="T248">
+        <v>1</v>
+      </c>
+      <c r="U248">
+        <v>0</v>
+      </c>
+      <c r="V248">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A249" t="s">
+        <v>787</v>
+      </c>
+      <c r="D249" s="1">
+        <v>46016</v>
+      </c>
+      <c r="E249" t="s">
+        <v>15</v>
+      </c>
+      <c r="I249" t="s">
+        <v>96</v>
+      </c>
+      <c r="J249" t="s">
+        <v>402</v>
+      </c>
+      <c r="M249" t="s">
+        <v>788</v>
+      </c>
+      <c r="N249" t="e" vm="29">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q249" t="s">
+        <v>776</v>
+      </c>
+      <c r="R249" s="1">
+        <v>45992</v>
+      </c>
+      <c r="T249">
+        <v>0</v>
+      </c>
+      <c r="U249">
+        <v>0</v>
+      </c>
+      <c r="V249">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V19" xr:uid="{F7772053-9363-CA4A-A53F-040B7C700753}">
+  <autoFilter ref="A1:V248" xr:uid="{F7772053-9363-CA4A-A53F-040B7C700753}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V247">
       <sortCondition ref="D1:D19"/>
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="A1:B208 A210:B1048576">
-    <cfRule type="duplicateValues" dxfId="190" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="193" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:B22">
-    <cfRule type="duplicateValues" dxfId="189" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="192" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A61:B61">
-    <cfRule type="duplicateValues" dxfId="188" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="191" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="containsText" dxfId="187" priority="6" operator="containsText" text="closed">
+    <cfRule type="containsText" dxfId="190" priority="6" operator="containsText" text="closed">
       <formula>NOT(ISERROR(SEARCH("closed",I1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="186" priority="7" operator="containsText" text="abandoned">
+    <cfRule type="containsText" dxfId="189" priority="7" operator="containsText" text="abandoned">
       <formula>NOT(ISERROR(SEARCH("abandoned",I1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="185" priority="9" operator="containsText" text="late app">
+    <cfRule type="containsText" dxfId="188" priority="9" operator="containsText" text="late app">
       <formula>NOT(ISERROR(SEARCH("late app",I1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:L223 O78:O80 O83:O89 O92:O112 O115:O124 O126:O181 R136 R153 R159 R166 R173 R178 O183:O205 O208:O211 O213:O218 O220:O233 I224:K224 R225 O235:O237 O239:O247 I1:J1 I225:L1048576">
-    <cfRule type="containsText" dxfId="4" priority="12" operator="containsText" text="completed">
+  <conditionalFormatting sqref="I2:L223 O78:O80 O83:O89 O92:O112 O115:O124 O126:O181 R136 R153 R159 R166 R173 R178 O183:O205 O208:O211 O213:O218 O220:O233 I224:K224 R225 I225:L1048576 O235:O237 I1:J1 M248 O239:O248">
+    <cfRule type="containsText" dxfId="187" priority="12" operator="containsText" text="completed">
       <formula>NOT(ISERROR(SEARCH("completed",I1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:J1048576">
-    <cfRule type="containsText" dxfId="184" priority="1" operator="containsText" text="no news">
+    <cfRule type="containsText" dxfId="186" priority="1" operator="containsText" text="no news">
       <formula>NOT(ISERROR(SEARCH("no news",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="183" priority="2" operator="containsText" text="offer">
+    <cfRule type="containsText" dxfId="185" priority="2" operator="containsText" text="offer">
       <formula>NOT(ISERROR(SEARCH("offer",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="182" priority="3" operator="containsText" text="fly out">
+    <cfRule type="containsText" dxfId="184" priority="3" operator="containsText" text="fly out">
       <formula>NOT(ISERROR(SEARCH("fly out",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="181" priority="4" operator="containsText" text="interview">
+    <cfRule type="containsText" dxfId="183" priority="4" operator="containsText" text="interview">
       <formula>NOT(ISERROR(SEARCH("interview",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="180" priority="5" operator="containsText" text="rejected">
+    <cfRule type="containsText" dxfId="182" priority="5" operator="containsText" text="rejected">
       <formula>NOT(ISERROR(SEARCH("rejected",J1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K1:L223 O78:O80 O83:O89 O92:O112 O115:O124 O126:O181 R136 R153 R159 R166 R173 R178 O183:O205 O208:O211 O213:O218 O220:O233 K224 R225 O235:O237 O239:O247 K225:L1048576">
-    <cfRule type="containsText" dxfId="3" priority="10" operator="containsText" text="NO">
+  <conditionalFormatting sqref="K1:L223 O78:O80 O83:O89 O92:O112 O115:O124 O126:O181 R136 R153 R159 R166 R173 R178 O183:O205 O208:O211 O213:O218 O220:O233 K224 R225 K225:L1048576 O235:O237 M248 O239:O248">
+    <cfRule type="containsText" dxfId="181" priority="10" operator="containsText" text="NO">
       <formula>NOT(ISERROR(SEARCH("NO",K1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="11" operator="containsText" text="YES">
+    <cfRule type="containsText" dxfId="180" priority="11" operator="containsText" text="YES">
       <formula>NOT(ISERROR(SEARCH("YES",K1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -48305,7 +48445,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923E81FA-B875-3C4E-A189-1A21268FA086}">
-  <dimension ref="A1:C252"/>
+  <dimension ref="A1:C261"/>
   <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="32.83203125" customWidth="1"/>
@@ -51022,507 +51162,618 @@
         <v>97</v>
       </c>
     </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A253" s="1">
+        <v>45983</v>
+      </c>
+      <c r="B253" t="s">
+        <v>648</v>
+      </c>
+      <c r="C253" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A254" s="1">
+        <v>45983</v>
+      </c>
+      <c r="B254" t="s">
+        <v>719</v>
+      </c>
+      <c r="C254" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A255" s="1">
+        <v>45985</v>
+      </c>
+      <c r="B255" t="s">
+        <v>414</v>
+      </c>
+      <c r="C255" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A256" s="1">
+        <v>45985</v>
+      </c>
+      <c r="B256" t="s">
+        <v>377</v>
+      </c>
+      <c r="C256" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A257" s="1">
+        <v>45985</v>
+      </c>
+      <c r="B257" t="s">
+        <v>714</v>
+      </c>
+      <c r="C257" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A258" s="1">
+        <v>45985</v>
+      </c>
+      <c r="B258" t="s">
+        <v>568</v>
+      </c>
+      <c r="C258" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A259" s="1">
+        <v>45985</v>
+      </c>
+      <c r="B259" t="s">
+        <v>787</v>
+      </c>
+      <c r="C259" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A260" s="1">
+        <v>45985</v>
+      </c>
+      <c r="B260" t="s">
+        <v>722</v>
+      </c>
+      <c r="C260" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A261" s="1">
+        <v>45985</v>
+      </c>
+      <c r="B261" t="s">
+        <v>528</v>
+      </c>
+      <c r="C261" t="s">
+        <v>97</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="B5">
-    <cfRule type="duplicateValues" dxfId="179" priority="182"/>
-    <cfRule type="duplicateValues" dxfId="178" priority="183"/>
+    <cfRule type="duplicateValues" dxfId="179" priority="186"/>
+    <cfRule type="duplicateValues" dxfId="178" priority="187"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B10">
-    <cfRule type="duplicateValues" dxfId="177" priority="181"/>
-    <cfRule type="duplicateValues" dxfId="176" priority="180"/>
+    <cfRule type="duplicateValues" dxfId="177" priority="185"/>
+    <cfRule type="duplicateValues" dxfId="176" priority="184"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B11">
-    <cfRule type="duplicateValues" dxfId="175" priority="179"/>
-    <cfRule type="duplicateValues" dxfId="174" priority="178"/>
+    <cfRule type="duplicateValues" dxfId="175" priority="183"/>
+    <cfRule type="duplicateValues" dxfId="174" priority="182"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12">
-    <cfRule type="duplicateValues" dxfId="173" priority="177"/>
-    <cfRule type="duplicateValues" dxfId="172" priority="176"/>
+    <cfRule type="duplicateValues" dxfId="173" priority="181"/>
+    <cfRule type="duplicateValues" dxfId="172" priority="180"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15">
-    <cfRule type="duplicateValues" dxfId="171" priority="175"/>
-    <cfRule type="duplicateValues" dxfId="170" priority="174"/>
+    <cfRule type="duplicateValues" dxfId="171" priority="179"/>
+    <cfRule type="duplicateValues" dxfId="170" priority="178"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16">
-    <cfRule type="duplicateValues" dxfId="169" priority="173"/>
+    <cfRule type="duplicateValues" dxfId="169" priority="177"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17">
-    <cfRule type="duplicateValues" dxfId="168" priority="172"/>
-    <cfRule type="duplicateValues" dxfId="167" priority="171"/>
+    <cfRule type="duplicateValues" dxfId="168" priority="176"/>
+    <cfRule type="duplicateValues" dxfId="167" priority="175"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B18">
-    <cfRule type="duplicateValues" dxfId="166" priority="170"/>
-    <cfRule type="duplicateValues" dxfId="165" priority="169"/>
+    <cfRule type="duplicateValues" dxfId="166" priority="174"/>
+    <cfRule type="duplicateValues" dxfId="165" priority="173"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B19">
-    <cfRule type="duplicateValues" dxfId="164" priority="168"/>
+    <cfRule type="duplicateValues" dxfId="164" priority="172"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:B23">
-    <cfRule type="duplicateValues" dxfId="163" priority="167"/>
-    <cfRule type="duplicateValues" dxfId="162" priority="166"/>
+    <cfRule type="duplicateValues" dxfId="163" priority="171"/>
+    <cfRule type="duplicateValues" dxfId="162" priority="170"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B24">
-    <cfRule type="duplicateValues" dxfId="161" priority="165"/>
-    <cfRule type="duplicateValues" dxfId="160" priority="164"/>
+    <cfRule type="duplicateValues" dxfId="161" priority="169"/>
+    <cfRule type="duplicateValues" dxfId="160" priority="168"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B27">
-    <cfRule type="duplicateValues" dxfId="159" priority="163"/>
-    <cfRule type="duplicateValues" dxfId="158" priority="162"/>
+    <cfRule type="duplicateValues" dxfId="159" priority="167"/>
+    <cfRule type="duplicateValues" dxfId="158" priority="166"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28">
-    <cfRule type="duplicateValues" dxfId="157" priority="161"/>
+    <cfRule type="duplicateValues" dxfId="157" priority="165"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29">
-    <cfRule type="duplicateValues" dxfId="156" priority="160"/>
-    <cfRule type="duplicateValues" dxfId="155" priority="159"/>
+    <cfRule type="duplicateValues" dxfId="156" priority="164"/>
+    <cfRule type="duplicateValues" dxfId="155" priority="163"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="154" priority="158"/>
+    <cfRule type="duplicateValues" dxfId="154" priority="162"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31">
-    <cfRule type="duplicateValues" dxfId="153" priority="157"/>
+    <cfRule type="duplicateValues" dxfId="153" priority="161"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="duplicateValues" dxfId="152" priority="156"/>
+    <cfRule type="duplicateValues" dxfId="152" priority="160"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33">
-    <cfRule type="duplicateValues" dxfId="151" priority="155"/>
+    <cfRule type="duplicateValues" dxfId="151" priority="159"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="150" priority="154"/>
+    <cfRule type="duplicateValues" dxfId="150" priority="158"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35">
-    <cfRule type="duplicateValues" dxfId="149" priority="153"/>
+    <cfRule type="duplicateValues" dxfId="149" priority="157"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37">
-    <cfRule type="duplicateValues" dxfId="148" priority="152"/>
+    <cfRule type="duplicateValues" dxfId="148" priority="156"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38">
-    <cfRule type="duplicateValues" dxfId="147" priority="151"/>
+    <cfRule type="duplicateValues" dxfId="147" priority="155"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B42">
-    <cfRule type="duplicateValues" dxfId="146" priority="150"/>
+    <cfRule type="duplicateValues" dxfId="146" priority="154"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43">
-    <cfRule type="duplicateValues" dxfId="145" priority="149"/>
+    <cfRule type="duplicateValues" dxfId="145" priority="153"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44:B45">
-    <cfRule type="duplicateValues" dxfId="144" priority="148"/>
+    <cfRule type="duplicateValues" dxfId="144" priority="152"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B46">
-    <cfRule type="duplicateValues" dxfId="143" priority="147"/>
+    <cfRule type="duplicateValues" dxfId="143" priority="151"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B48">
-    <cfRule type="duplicateValues" dxfId="142" priority="146"/>
+    <cfRule type="duplicateValues" dxfId="142" priority="150"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B49">
-    <cfRule type="duplicateValues" dxfId="141" priority="145"/>
+    <cfRule type="duplicateValues" dxfId="141" priority="149"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B51">
-    <cfRule type="duplicateValues" dxfId="140" priority="144"/>
+    <cfRule type="duplicateValues" dxfId="140" priority="148"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B52">
-    <cfRule type="duplicateValues" dxfId="139" priority="143"/>
+    <cfRule type="duplicateValues" dxfId="139" priority="147"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B58">
-    <cfRule type="duplicateValues" dxfId="138" priority="141"/>
+    <cfRule type="duplicateValues" dxfId="138" priority="145"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B59">
-    <cfRule type="duplicateValues" dxfId="137" priority="139"/>
+    <cfRule type="duplicateValues" dxfId="137" priority="143"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B63">
-    <cfRule type="duplicateValues" dxfId="136" priority="138"/>
+    <cfRule type="duplicateValues" dxfId="136" priority="142"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B64">
-    <cfRule type="duplicateValues" dxfId="135" priority="136"/>
+    <cfRule type="duplicateValues" dxfId="135" priority="140"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B66">
-    <cfRule type="duplicateValues" dxfId="134" priority="135"/>
+    <cfRule type="duplicateValues" dxfId="134" priority="139"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="133" priority="134"/>
-    <cfRule type="duplicateValues" dxfId="132" priority="133"/>
+    <cfRule type="duplicateValues" dxfId="133" priority="138"/>
+    <cfRule type="duplicateValues" dxfId="132" priority="137"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B68">
-    <cfRule type="duplicateValues" dxfId="131" priority="132"/>
+    <cfRule type="duplicateValues" dxfId="131" priority="136"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B69">
-    <cfRule type="duplicateValues" dxfId="130" priority="131"/>
+    <cfRule type="duplicateValues" dxfId="130" priority="135"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B70">
-    <cfRule type="duplicateValues" dxfId="129" priority="129"/>
+    <cfRule type="duplicateValues" dxfId="129" priority="133"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B72">
-    <cfRule type="duplicateValues" dxfId="128" priority="128"/>
+    <cfRule type="duplicateValues" dxfId="128" priority="132"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B73">
-    <cfRule type="duplicateValues" dxfId="127" priority="126"/>
+    <cfRule type="duplicateValues" dxfId="127" priority="130"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B74">
-    <cfRule type="duplicateValues" dxfId="126" priority="125"/>
+    <cfRule type="duplicateValues" dxfId="126" priority="129"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B75">
-    <cfRule type="duplicateValues" dxfId="125" priority="124"/>
+    <cfRule type="duplicateValues" dxfId="125" priority="128"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B76">
-    <cfRule type="duplicateValues" dxfId="124" priority="123"/>
+    <cfRule type="duplicateValues" dxfId="124" priority="127"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B77">
-    <cfRule type="duplicateValues" dxfId="123" priority="121"/>
+    <cfRule type="duplicateValues" dxfId="123" priority="125"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B78">
-    <cfRule type="duplicateValues" dxfId="122" priority="120"/>
+    <cfRule type="duplicateValues" dxfId="122" priority="124"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B83">
-    <cfRule type="duplicateValues" dxfId="121" priority="119"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="123"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B84">
-    <cfRule type="duplicateValues" dxfId="120" priority="118"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="122"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B85">
-    <cfRule type="duplicateValues" dxfId="119" priority="117"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="121"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B87">
-    <cfRule type="duplicateValues" dxfId="118" priority="116"/>
+    <cfRule type="duplicateValues" dxfId="118" priority="120"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B88">
-    <cfRule type="duplicateValues" dxfId="117" priority="115"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="119"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B89">
-    <cfRule type="duplicateValues" dxfId="116" priority="114"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="118"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B90">
-    <cfRule type="duplicateValues" dxfId="115" priority="113"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="117"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B91">
-    <cfRule type="duplicateValues" dxfId="114" priority="112"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="116"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B92">
-    <cfRule type="duplicateValues" dxfId="113" priority="111"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="115"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B93">
-    <cfRule type="duplicateValues" dxfId="112" priority="110"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="114"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B94">
-    <cfRule type="duplicateValues" dxfId="111" priority="109"/>
+    <cfRule type="duplicateValues" dxfId="111" priority="113"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B95">
-    <cfRule type="duplicateValues" dxfId="110" priority="108"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="112"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B96">
-    <cfRule type="duplicateValues" dxfId="109" priority="107"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="111"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B97">
-    <cfRule type="duplicateValues" dxfId="108" priority="106"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="110"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B98">
-    <cfRule type="duplicateValues" dxfId="107" priority="105"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="109"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B99">
-    <cfRule type="duplicateValues" dxfId="106" priority="104"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="108"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B100">
-    <cfRule type="duplicateValues" dxfId="105" priority="103"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="107"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B101">
-    <cfRule type="duplicateValues" dxfId="104" priority="102"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="106"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B104">
-    <cfRule type="duplicateValues" dxfId="103" priority="101"/>
-    <cfRule type="duplicateValues" dxfId="102" priority="100"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="105"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="104"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B105:B106">
-    <cfRule type="duplicateValues" dxfId="101" priority="99"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="103"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B107">
-    <cfRule type="duplicateValues" dxfId="100" priority="98"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="102"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B108">
-    <cfRule type="duplicateValues" dxfId="99" priority="97"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="101"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B109">
-    <cfRule type="duplicateValues" dxfId="98" priority="96"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="100"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B110">
-    <cfRule type="duplicateValues" dxfId="97" priority="95"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="99"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B111">
-    <cfRule type="duplicateValues" dxfId="96" priority="94"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="98"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B112">
-    <cfRule type="duplicateValues" dxfId="95" priority="93"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="97"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B113">
-    <cfRule type="duplicateValues" dxfId="94" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="96"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B114">
-    <cfRule type="duplicateValues" dxfId="93" priority="91"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="95"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B115">
-    <cfRule type="duplicateValues" dxfId="92" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="94"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B116">
-    <cfRule type="duplicateValues" dxfId="91" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="93"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B117">
-    <cfRule type="duplicateValues" dxfId="90" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="92"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B118">
-    <cfRule type="duplicateValues" dxfId="89" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="91"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B119">
-    <cfRule type="duplicateValues" dxfId="88" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="90"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B120">
-    <cfRule type="duplicateValues" dxfId="87" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="89"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B121">
-    <cfRule type="duplicateValues" dxfId="86" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="88"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B122">
-    <cfRule type="duplicateValues" dxfId="85" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="87"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B126">
-    <cfRule type="duplicateValues" dxfId="84" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="86"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B127">
-    <cfRule type="duplicateValues" dxfId="83" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="85"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B128">
-    <cfRule type="duplicateValues" dxfId="82" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="84"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B129">
-    <cfRule type="duplicateValues" dxfId="81" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="83"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B130">
-    <cfRule type="duplicateValues" dxfId="80" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="82"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B131">
-    <cfRule type="duplicateValues" dxfId="79" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="81"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B132">
-    <cfRule type="duplicateValues" dxfId="78" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="80"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B133">
-    <cfRule type="duplicateValues" dxfId="77" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="79"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B136">
-    <cfRule type="duplicateValues" dxfId="76" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="78"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B137">
-    <cfRule type="duplicateValues" dxfId="75" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="77"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B138">
-    <cfRule type="duplicateValues" dxfId="74" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="76"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B139">
-    <cfRule type="duplicateValues" dxfId="73" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="75"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B140">
-    <cfRule type="duplicateValues" dxfId="72" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="74"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B141">
-    <cfRule type="duplicateValues" dxfId="71" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="73"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B142">
-    <cfRule type="duplicateValues" dxfId="70" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="72"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B143">
-    <cfRule type="duplicateValues" dxfId="69" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B144">
-    <cfRule type="duplicateValues" dxfId="68" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B145">
-    <cfRule type="duplicateValues" dxfId="67" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="69"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B147">
-    <cfRule type="duplicateValues" dxfId="66" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="68"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B148">
-    <cfRule type="duplicateValues" dxfId="65" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B149">
-    <cfRule type="duplicateValues" dxfId="64" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="66"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B150">
-    <cfRule type="duplicateValues" dxfId="63" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B151">
-    <cfRule type="duplicateValues" dxfId="62" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="64"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B152">
-    <cfRule type="duplicateValues" dxfId="61" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="63"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B153">
-    <cfRule type="duplicateValues" dxfId="60" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="62"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B154">
-    <cfRule type="duplicateValues" dxfId="59" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="61"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B155">
-    <cfRule type="duplicateValues" dxfId="58" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B156">
-    <cfRule type="duplicateValues" dxfId="57" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="59"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B157">
-    <cfRule type="duplicateValues" dxfId="56" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="58"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B171">
-    <cfRule type="duplicateValues" dxfId="55" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B172">
-    <cfRule type="duplicateValues" dxfId="54" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B174">
-    <cfRule type="duplicateValues" dxfId="53" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B177:B178">
-    <cfRule type="duplicateValues" dxfId="52" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B181">
-    <cfRule type="duplicateValues" dxfId="51" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B182">
-    <cfRule type="duplicateValues" dxfId="50" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B183">
-    <cfRule type="duplicateValues" dxfId="49" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B184">
-    <cfRule type="duplicateValues" dxfId="48" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B185">
-    <cfRule type="duplicateValues" dxfId="47" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B186">
-    <cfRule type="duplicateValues" dxfId="46" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B188">
-    <cfRule type="duplicateValues" dxfId="45" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B189">
-    <cfRule type="duplicateValues" dxfId="44" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B190">
-    <cfRule type="duplicateValues" dxfId="43" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B191">
-    <cfRule type="duplicateValues" dxfId="42" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B192">
-    <cfRule type="duplicateValues" dxfId="41" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B193">
-    <cfRule type="duplicateValues" dxfId="40" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B195">
-    <cfRule type="duplicateValues" dxfId="39" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B196">
-    <cfRule type="duplicateValues" dxfId="38" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B197">
-    <cfRule type="duplicateValues" dxfId="37" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B198">
-    <cfRule type="duplicateValues" dxfId="36" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B199">
-    <cfRule type="duplicateValues" dxfId="35" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B200">
-    <cfRule type="duplicateValues" dxfId="34" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B201">
-    <cfRule type="duplicateValues" dxfId="33" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B202">
-    <cfRule type="duplicateValues" dxfId="32" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B203">
-    <cfRule type="duplicateValues" dxfId="31" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B204">
-    <cfRule type="duplicateValues" dxfId="30" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B205">
-    <cfRule type="duplicateValues" dxfId="29" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B206">
-    <cfRule type="duplicateValues" dxfId="28" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B207">
-    <cfRule type="duplicateValues" dxfId="27" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B215">
-    <cfRule type="duplicateValues" dxfId="26" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B218">
-    <cfRule type="duplicateValues" dxfId="25" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B220">
-    <cfRule type="duplicateValues" dxfId="24" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B222">
-    <cfRule type="duplicateValues" dxfId="23" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B223">
-    <cfRule type="duplicateValues" dxfId="22" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B224">
-    <cfRule type="duplicateValues" dxfId="21" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B225">
-    <cfRule type="duplicateValues" dxfId="20" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B227">
-    <cfRule type="duplicateValues" dxfId="19" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B229">
-    <cfRule type="duplicateValues" dxfId="18" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B230">
-    <cfRule type="duplicateValues" dxfId="17" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B232">
-    <cfRule type="duplicateValues" dxfId="16" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B233">
-    <cfRule type="duplicateValues" dxfId="15" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B234">
-    <cfRule type="duplicateValues" dxfId="14" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B235">
-    <cfRule type="duplicateValues" dxfId="13" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B236">
-    <cfRule type="duplicateValues" dxfId="12" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B237">
-    <cfRule type="duplicateValues" dxfId="11" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B239">
-    <cfRule type="duplicateValues" dxfId="9" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B240">
-    <cfRule type="duplicateValues" dxfId="8" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B241">
-    <cfRule type="duplicateValues" dxfId="7" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B242">
-    <cfRule type="duplicateValues" dxfId="6" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B243">
-    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B250">
+    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B251">
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B253">
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B255">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B258:B259">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B251">
+  <conditionalFormatting sqref="B260">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -51536,7 +51787,7 @@
   <cols>
     <col min="1" max="1" width="15.83203125" style="12" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" style="16"/>
-    <col min="3" max="3" width="10.83203125" style="10"/>
+    <col min="3" max="3" width="15.33203125" style="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="26" x14ac:dyDescent="0.6">
@@ -51545,15 +51796,15 @@
       </c>
       <c r="B1" s="15">
         <f>COUNTA(sum!A:A) -1</f>
-        <v>246</v>
-      </c>
-      <c r="C1" s="14">
-        <f>COUNTIF(sum!I:I, "completed")/B1</f>
-        <v>0.94715447154471544</v>
+        <v>248</v>
+      </c>
+      <c r="C1" s="23">
+        <f>COUNTIF(sum!I:I, "completed")/(B1-COUNTIF(sum!I:I, "abandoned")-COUNTIF(sum!I:I, "late app"))</f>
+        <v>0.99585062240663902</v>
       </c>
       <c r="D1" s="21">
         <f>COUNTIF(sum!I:I, "completed")</f>
-        <v>233</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.4">
@@ -51566,7 +51817,7 @@
       </c>
       <c r="C2" s="10">
         <f>COUNTIFS(sum!I:I,"completed", sum!G:G, "&lt;&gt;") / B2</f>
-        <v>0.94339622641509435</v>
+        <v>0.96226415094339623</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.4">
@@ -51575,11 +51826,11 @@
       </c>
       <c r="B3" s="16">
         <f>COUNTA(sum!K:K) -1</f>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C3" s="10">
         <f>COUNTIFS(sum!I:I,"completed", sum!K:K, "&lt;&gt;") / B3</f>
-        <v>0.9821428571428571</v>
+        <v>0.98245614035087714</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="26" x14ac:dyDescent="0.6">
@@ -51588,7 +51839,7 @@
       </c>
       <c r="B5" s="15">
         <f>COUNTA(sum!J:J) -1</f>
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C5" s="14">
         <f>B5/B1</f>
@@ -51605,7 +51856,7 @@
       </c>
       <c r="C6" s="10">
         <f>B6/$B$5</f>
-        <v>0.97967479674796742</v>
+        <v>0.97177419354838712</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
@@ -51614,11 +51865,11 @@
       </c>
       <c r="B7" s="16">
         <f>COUNTIFS(sum!J:J,"rejected")</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C7" s="10">
         <f t="shared" ref="C7:C10" si="0">B7/$B$5</f>
-        <v>2.032520325203252E-2</v>
+        <v>2.8225806451612902E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">

--- a/EconJM_status.xlsx
+++ b/EconJM_status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\javie\Dropbox\Work\Job Search\2025 EconJM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{818DAC6E-E42D-4253-9031-FD3B496FCE97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33AB038B-FA27-40F4-A9D7-3716430E3770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" activeTab="2" xr2:uid="{6FE48536-7E5C-BF4C-9490-2A6392576298}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" activeTab="1" xr2:uid="{6FE48536-7E5C-BF4C-9490-2A6392576298}"/>
   </bookViews>
   <sheets>
     <sheet name="sum" sheetId="1" r:id="rId1"/>
@@ -1083,7 +1083,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2496" uniqueCount="789">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2538" uniqueCount="802">
   <si>
     <t>add_id</t>
   </si>
@@ -3486,6 +3486,45 @@
   </si>
   <si>
     <t>E.CA Economics</t>
+  </si>
+  <si>
+    <t>Lisbon School of Economics and Management</t>
+  </si>
+  <si>
+    <t>iseg</t>
+  </si>
+  <si>
+    <t>manhaeim</t>
+  </si>
+  <si>
+    <t>escp</t>
+  </si>
+  <si>
+    <t>ESCP Business School</t>
+  </si>
+  <si>
+    <t>submit CV to https://tinyurl.com/BerlinESCPEcon</t>
+  </si>
+  <si>
+    <t>https://tinyurl.com/BerlinESCPEcon</t>
+  </si>
+  <si>
+    <t>unidistance_post</t>
+  </si>
+  <si>
+    <t>Michael Kurschilgen: michael.kurschilgen@unidistance.ch</t>
+  </si>
+  <si>
+    <t>kings</t>
+  </si>
+  <si>
+    <t>Kings College</t>
+  </si>
+  <si>
+    <t>historical econ</t>
+  </si>
+  <si>
+    <t>added some info of stragelers in EJM and JOE</t>
   </si>
 </sst>
 </file>
@@ -3613,7 +3652,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
@@ -3658,7 +3697,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -36974,7 +37012,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7772053-9363-CA4A-A53F-040B7C700753}">
-  <dimension ref="A1:V249"/>
+  <dimension ref="A1:V254"/>
   <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="19.6640625" customWidth="1"/>
@@ -38707,7 +38745,6 @@
       <c r="A38" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B38" s="22"/>
       <c r="D38" s="1">
         <v>45955</v>
       </c>
@@ -40143,7 +40180,6 @@
       <c r="A71" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="B71" s="19"/>
       <c r="C71" t="s">
         <v>315</v>
       </c>
@@ -40248,7 +40284,6 @@
       <c r="A73" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="B73" s="22"/>
       <c r="C73" t="s">
         <v>407</v>
       </c>
@@ -41396,7 +41431,6 @@
       <c r="A99" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="B99" s="19"/>
       <c r="C99" t="s">
         <v>279</v>
       </c>
@@ -42137,7 +42171,6 @@
       <c r="A113" s="4" t="s">
         <v>388</v>
       </c>
-      <c r="B113" s="22"/>
       <c r="C113" t="s">
         <v>390</v>
       </c>
@@ -42242,7 +42275,7 @@
       <c r="A115" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="B115" s="22"/>
+      <c r="B115" s="19"/>
       <c r="C115" t="s">
         <v>346</v>
       </c>
@@ -42629,7 +42662,7 @@
         <v>96</v>
       </c>
       <c r="J123" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M123" t="s">
         <v>575</v>
@@ -44041,7 +44074,6 @@
       <c r="A155" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="B155" s="19"/>
       <c r="C155" t="s">
         <v>633</v>
       </c>
@@ -44525,6 +44557,7 @@
       <c r="A166" s="4" t="s">
         <v>687</v>
       </c>
+      <c r="B166" s="19"/>
       <c r="D166" s="1">
         <v>45976</v>
       </c>
@@ -44714,6 +44747,7 @@
       <c r="A170" s="4" t="s">
         <v>658</v>
       </c>
+      <c r="B170" s="19"/>
       <c r="C170" t="s">
         <v>659</v>
       </c>
@@ -47926,27 +47960,33 @@
     </row>
     <row r="242" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A242" t="s">
-        <v>662</v>
+        <v>784</v>
       </c>
       <c r="D242" s="1">
-        <v>46011</v>
+        <v>45992</v>
       </c>
       <c r="E242" t="s">
-        <v>15</v>
-      </c>
-      <c r="H242" t="s">
-        <v>664</v>
+        <v>40</v>
+      </c>
+      <c r="F242" t="s">
+        <v>785</v>
       </c>
       <c r="I242" t="s">
-        <v>96</v>
+        <v>23</v>
       </c>
       <c r="J242" t="s">
         <v>402</v>
       </c>
+      <c r="K242" t="s">
+        <v>244</v>
+      </c>
+      <c r="L242" s="1">
+        <v>46027</v>
+      </c>
       <c r="M242" t="s">
-        <v>663</v>
-      </c>
-      <c r="N242" t="e" vm="45">
+        <v>786</v>
+      </c>
+      <c r="N242" t="e" vm="35">
         <v>#VALUE!</v>
       </c>
       <c r="O242" t="s">
@@ -47956,7 +47996,7 @@
         <v>776</v>
       </c>
       <c r="R242" s="1">
-        <v>46037</v>
+        <v>46026</v>
       </c>
       <c r="T242">
         <v>1</v>
@@ -47970,30 +48010,24 @@
     </row>
     <row r="243" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A243" t="s">
-        <v>722</v>
-      </c>
-      <c r="C243" t="s">
-        <v>723</v>
+        <v>791</v>
       </c>
       <c r="D243" s="1">
-        <v>46016</v>
+        <v>45992</v>
       </c>
       <c r="E243" t="s">
         <v>15</v>
       </c>
-      <c r="F243" t="s">
-        <v>721</v>
-      </c>
       <c r="I243" t="s">
-        <v>96</v>
+        <v>23</v>
       </c>
       <c r="J243" t="s">
         <v>402</v>
       </c>
       <c r="M243" t="s">
-        <v>720</v>
-      </c>
-      <c r="N243" t="e" vm="68">
+        <v>185</v>
+      </c>
+      <c r="N243" t="e" vm="29">
         <v>#VALUE!</v>
       </c>
       <c r="O243" t="s">
@@ -48003,7 +48037,7 @@
         <v>776</v>
       </c>
       <c r="R243" s="1">
-        <v>45992</v>
+        <v>46022</v>
       </c>
       <c r="T243">
         <v>1</v>
@@ -48016,48 +48050,41 @@
       </c>
     </row>
     <row r="244" spans="1:22" x14ac:dyDescent="0.4">
-      <c r="A244" s="4" t="s">
-        <v>719</v>
-      </c>
-      <c r="B244" s="19"/>
+      <c r="A244" t="s">
+        <v>792</v>
+      </c>
       <c r="C244" t="s">
-        <v>783</v>
+        <v>794</v>
       </c>
       <c r="D244" s="1">
-        <v>46016</v>
+        <v>45992</v>
       </c>
       <c r="E244" t="s">
         <v>15</v>
       </c>
-      <c r="G244">
-        <v>3</v>
+      <c r="F244" s="2" t="s">
+        <v>795</v>
       </c>
       <c r="I244" t="s">
-        <v>96</v>
+        <v>23</v>
       </c>
       <c r="J244" t="s">
         <v>402</v>
       </c>
-      <c r="K244" t="s">
-        <v>244</v>
-      </c>
-      <c r="L244" s="1">
-        <v>45992</v>
-      </c>
-      <c r="M244" s="2" t="s">
-        <v>718</v>
-      </c>
-      <c r="N244" t="e" vm="45">
+      <c r="M244" t="s">
+        <v>793</v>
+      </c>
+      <c r="N244" t="e" vm="29">
         <v>#VALUE!</v>
       </c>
       <c r="O244" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="Q244" t="s">
         <v>776</v>
       </c>
       <c r="R244" s="1">
-        <v>45996</v>
+        <v>46053</v>
       </c>
       <c r="T244">
         <v>1</v>
@@ -48071,37 +48098,37 @@
     </row>
     <row r="245" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A245" t="s">
-        <v>528</v>
-      </c>
-      <c r="C245" t="s">
-        <v>178</v>
+        <v>796</v>
       </c>
       <c r="D245" s="1">
-        <v>46023</v>
+        <v>45992</v>
       </c>
       <c r="E245" t="s">
-        <v>529</v>
+        <v>15</v>
+      </c>
+      <c r="H245" t="s">
+        <v>797</v>
       </c>
       <c r="I245" t="s">
-        <v>96</v>
+        <v>23</v>
       </c>
       <c r="J245" t="s">
         <v>402</v>
       </c>
       <c r="M245" t="s">
-        <v>530</v>
-      </c>
-      <c r="N245" t="e" vm="102">
+        <v>750</v>
+      </c>
+      <c r="N245" t="e" vm="47">
         <v>#VALUE!</v>
       </c>
       <c r="O245" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="Q245" t="s">
         <v>776</v>
       </c>
       <c r="R245" s="1">
-        <v>46041</v>
+        <v>46054</v>
       </c>
       <c r="T245">
         <v>1</v>
@@ -48110,18 +48137,21 @@
         <v>0</v>
       </c>
       <c r="V245">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="246" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A246" t="s">
-        <v>564</v>
+        <v>662</v>
       </c>
       <c r="D246" s="1">
-        <v>46023</v>
+        <v>46011</v>
       </c>
       <c r="E246" t="s">
-        <v>565</v>
+        <v>15</v>
+      </c>
+      <c r="H246" t="s">
+        <v>664</v>
       </c>
       <c r="I246" t="s">
         <v>96</v>
@@ -48130,9 +48160,9 @@
         <v>402</v>
       </c>
       <c r="M246" t="s">
-        <v>566</v>
-      </c>
-      <c r="N246" t="e" vm="103">
+        <v>663</v>
+      </c>
+      <c r="N246" t="e" vm="45">
         <v>#VALUE!</v>
       </c>
       <c r="O246" t="s">
@@ -48142,7 +48172,7 @@
         <v>776</v>
       </c>
       <c r="R246" s="1">
-        <v>45664</v>
+        <v>46037</v>
       </c>
       <c r="T246">
         <v>1</v>
@@ -48156,13 +48186,19 @@
     </row>
     <row r="247" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A247" t="s">
-        <v>255</v>
+        <v>722</v>
+      </c>
+      <c r="C247" t="s">
+        <v>723</v>
+      </c>
+      <c r="D247" s="1">
+        <v>46016</v>
       </c>
       <c r="E247" t="s">
         <v>15</v>
       </c>
-      <c r="F247" s="2" t="s">
-        <v>257</v>
+      <c r="F247" t="s">
+        <v>721</v>
       </c>
       <c r="I247" t="s">
         <v>96</v>
@@ -48171,19 +48207,22 @@
         <v>402</v>
       </c>
       <c r="M247" t="s">
-        <v>256</v>
-      </c>
-      <c r="N247" t="e" vm="35">
+        <v>720</v>
+      </c>
+      <c r="N247" t="e" vm="68">
         <v>#VALUE!</v>
       </c>
       <c r="O247" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="Q247" t="s">
         <v>776</v>
       </c>
+      <c r="R247" s="1">
+        <v>45992</v>
+      </c>
       <c r="T247">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U247">
         <v>0</v>
@@ -48193,20 +48232,24 @@
       </c>
     </row>
     <row r="248" spans="1:22" x14ac:dyDescent="0.4">
-      <c r="A248" t="s">
-        <v>784</v>
+      <c r="A248" s="4" t="s">
+        <v>719</v>
+      </c>
+      <c r="B248" s="19"/>
+      <c r="C248" t="s">
+        <v>783</v>
       </c>
       <c r="D248" s="1">
-        <v>45992</v>
+        <v>46016</v>
       </c>
       <c r="E248" t="s">
-        <v>40</v>
-      </c>
-      <c r="F248" t="s">
-        <v>785</v>
+        <v>15</v>
+      </c>
+      <c r="G248">
+        <v>3</v>
       </c>
       <c r="I248" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J248" t="s">
         <v>402</v>
@@ -48215,22 +48258,22 @@
         <v>244</v>
       </c>
       <c r="L248" s="1">
-        <v>46027</v>
-      </c>
-      <c r="M248" t="s">
-        <v>786</v>
-      </c>
-      <c r="N248" t="e" vm="35">
+        <v>45992</v>
+      </c>
+      <c r="M248" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="N248" t="e" vm="45">
         <v>#VALUE!</v>
       </c>
       <c r="O248" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="Q248" t="s">
         <v>776</v>
       </c>
       <c r="R248" s="1">
-        <v>46026</v>
+        <v>45996</v>
       </c>
       <c r="T248">
         <v>1</v>
@@ -48280,10 +48323,218 @@
         <v>0</v>
       </c>
     </row>
+    <row r="250" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A250" t="s">
+        <v>790</v>
+      </c>
+      <c r="D250" s="1">
+        <v>46016</v>
+      </c>
+      <c r="E250" t="s">
+        <v>15</v>
+      </c>
+      <c r="I250" t="s">
+        <v>23</v>
+      </c>
+      <c r="J250" t="s">
+        <v>402</v>
+      </c>
+      <c r="M250" t="s">
+        <v>789</v>
+      </c>
+      <c r="N250" t="e" vm="75">
+        <v>#VALUE!</v>
+      </c>
+      <c r="O250" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q250" t="s">
+        <v>776</v>
+      </c>
+      <c r="R250" s="1">
+        <v>45992</v>
+      </c>
+      <c r="T250">
+        <v>1</v>
+      </c>
+      <c r="U250">
+        <v>0</v>
+      </c>
+      <c r="V250">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A251" t="s">
+        <v>528</v>
+      </c>
+      <c r="C251" t="s">
+        <v>178</v>
+      </c>
+      <c r="D251" s="1">
+        <v>46023</v>
+      </c>
+      <c r="E251" t="s">
+        <v>529</v>
+      </c>
+      <c r="I251" t="s">
+        <v>96</v>
+      </c>
+      <c r="J251" t="s">
+        <v>402</v>
+      </c>
+      <c r="M251" t="s">
+        <v>530</v>
+      </c>
+      <c r="N251" t="e" vm="102">
+        <v>#VALUE!</v>
+      </c>
+      <c r="O251" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q251" t="s">
+        <v>776</v>
+      </c>
+      <c r="R251" s="1">
+        <v>46041</v>
+      </c>
+      <c r="T251">
+        <v>1</v>
+      </c>
+      <c r="U251">
+        <v>0</v>
+      </c>
+      <c r="V251">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="252" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A252" t="s">
+        <v>564</v>
+      </c>
+      <c r="D252" s="1">
+        <v>46023</v>
+      </c>
+      <c r="E252" t="s">
+        <v>565</v>
+      </c>
+      <c r="I252" t="s">
+        <v>96</v>
+      </c>
+      <c r="J252" t="s">
+        <v>402</v>
+      </c>
+      <c r="M252" t="s">
+        <v>566</v>
+      </c>
+      <c r="N252" t="e" vm="103">
+        <v>#VALUE!</v>
+      </c>
+      <c r="O252" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q252" t="s">
+        <v>776</v>
+      </c>
+      <c r="R252" s="1">
+        <v>45664</v>
+      </c>
+      <c r="T252">
+        <v>1</v>
+      </c>
+      <c r="U252">
+        <v>0</v>
+      </c>
+      <c r="V252">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A253" t="s">
+        <v>255</v>
+      </c>
+      <c r="E253" t="s">
+        <v>15</v>
+      </c>
+      <c r="F253" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="I253" t="s">
+        <v>96</v>
+      </c>
+      <c r="J253" t="s">
+        <v>402</v>
+      </c>
+      <c r="M253" t="s">
+        <v>256</v>
+      </c>
+      <c r="N253" t="e" vm="35">
+        <v>#VALUE!</v>
+      </c>
+      <c r="O253" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q253" t="s">
+        <v>776</v>
+      </c>
+      <c r="T253">
+        <v>0</v>
+      </c>
+      <c r="U253">
+        <v>0</v>
+      </c>
+      <c r="V253">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A254" t="s">
+        <v>798</v>
+      </c>
+      <c r="C254" t="s">
+        <v>800</v>
+      </c>
+      <c r="D254" s="1">
+        <v>45992</v>
+      </c>
+      <c r="E254" t="s">
+        <v>40</v>
+      </c>
+      <c r="I254" t="s">
+        <v>23</v>
+      </c>
+      <c r="J254" t="s">
+        <v>402</v>
+      </c>
+      <c r="M254" t="s">
+        <v>799</v>
+      </c>
+      <c r="N254" t="e" vm="70">
+        <v>#VALUE!</v>
+      </c>
+      <c r="O254" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q254" t="s">
+        <v>776</v>
+      </c>
+      <c r="R254" s="1">
+        <v>46026</v>
+      </c>
+      <c r="T254">
+        <v>1</v>
+      </c>
+      <c r="U254">
+        <v>0</v>
+      </c>
+      <c r="V254">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:V248" xr:uid="{F7772053-9363-CA4A-A53F-040B7C700753}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V247">
-      <sortCondition ref="D1:D19"/>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V253">
+      <sortCondition ref="D1:D248"/>
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="A1:B208 A210:B1048576">
@@ -48306,7 +48557,7 @@
       <formula>NOT(ISERROR(SEARCH("late app",I1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:L223 O78:O80 O83:O89 O92:O112 O115:O124 O126:O181 R136 R153 R159 R166 R173 R178 O183:O205 O208:O211 O213:O218 O220:O233 I224:K224 R225 I225:L1048576 O235:O237 I1:J1 M248 O239:O248">
+  <conditionalFormatting sqref="I2:L223 O78:O80 O83:O89 O92:O112 O115:O124 O126:O181 R136 R153 R159 R166 R173 R178 O183:O205 O208:O211 O213:O218 O220:O233 I224:K224 R225 I225:L1048576 O235:O237 O239:O248 M248 O250:O254 I1:J1">
     <cfRule type="containsText" dxfId="187" priority="12" operator="containsText" text="completed">
       <formula>NOT(ISERROR(SEARCH("completed",I1)))</formula>
     </cfRule>
@@ -48328,7 +48579,7 @@
       <formula>NOT(ISERROR(SEARCH("rejected",J1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K1:L223 O78:O80 O83:O89 O92:O112 O115:O124 O126:O181 R136 R153 R159 R166 R173 R178 O183:O205 O208:O211 O213:O218 O220:O233 K224 R225 K225:L1048576 O235:O237 M248 O239:O248">
+  <conditionalFormatting sqref="K1:L223 O78:O80 O83:O89 O92:O112 O115:O124 O126:O181 R136 R153 R159 R166 R173 R178 O183:O205 O208:O211 O213:O218 O220:O233 K224 R225 K225:L1048576 O235:O237 O239:O248 M248 O250:O254">
     <cfRule type="containsText" dxfId="181" priority="10" operator="containsText" text="NO">
       <formula>NOT(ISERROR(SEARCH("NO",K1)))</formula>
     </cfRule>
@@ -48418,7 +48669,7 @@
     <hyperlink ref="M17" r:id="rId79" xr:uid="{9A9A6BC9-B330-7842-A78C-4DCC88F5E19F}"/>
     <hyperlink ref="M32" r:id="rId80" xr:uid="{928CABEF-4FA6-E646-8140-7B6E43F8FB96}"/>
     <hyperlink ref="F177" r:id="rId81" xr:uid="{82BF1574-A6C6-1641-9FFE-615861E401FD}"/>
-    <hyperlink ref="F247" r:id="rId82" xr:uid="{3562807E-7FDA-F046-BA03-5DDD43072DB7}"/>
+    <hyperlink ref="F253" r:id="rId82" xr:uid="{3562807E-7FDA-F046-BA03-5DDD43072DB7}"/>
     <hyperlink ref="H215" r:id="rId83" display="mailto:ivanpaya@ua.es" xr:uid="{DEFB77A5-E57F-714C-BAB9-56DE82BA0B2E}"/>
     <hyperlink ref="H138" r:id="rId84" display="mailto:ari.hyytinen@hanken.fi" xr:uid="{7777B12A-FD99-4A43-A14B-A15661B760DC}"/>
     <hyperlink ref="H115" r:id="rId85" display="mailto:peter.haan@fu-berlin.de" xr:uid="{3D1A69ED-8F06-1246-B586-201CB349DB62}"/>
@@ -48436,16 +48687,17 @@
     <hyperlink ref="H240" r:id="rId97" display="mailto:ondrej.krcal@econ.muni.cz" xr:uid="{EDDEB1E6-5767-4FFB-A0AE-57A909D04E81}"/>
     <hyperlink ref="M218" r:id="rId98" display="https://www.ovgu.de/unimagdeburg/en/" xr:uid="{BCB3935D-2B6D-4090-86F5-762D762ED0E3}"/>
     <hyperlink ref="E152" r:id="rId99" xr:uid="{550520C0-1E25-41CD-9AEE-9A3C4D7D328C}"/>
-    <hyperlink ref="M244" r:id="rId100" xr:uid="{F0DD6D71-3FFD-4EAB-A251-AAF2DA8EF53C}"/>
+    <hyperlink ref="M248" r:id="rId100" xr:uid="{F0DD6D71-3FFD-4EAB-A251-AAF2DA8EF53C}"/>
+    <hyperlink ref="F244" r:id="rId101" xr:uid="{BDBBC2E2-C3C5-4526-A621-853D22D99CCF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId101"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId102"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923E81FA-B875-3C4E-A189-1A21268FA086}">
-  <dimension ref="A1:C261"/>
+  <dimension ref="A1:C263"/>
   <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="32.83203125" customWidth="1"/>
@@ -51259,6 +51511,25 @@
       </c>
       <c r="C261" t="s">
         <v>97</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A262" s="1">
+        <v>45990</v>
+      </c>
+      <c r="C262" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A263" s="1">
+        <v>45990</v>
+      </c>
+      <c r="B263" t="s">
+        <v>573</v>
+      </c>
+      <c r="C263" t="s">
+        <v>403</v>
       </c>
     </row>
   </sheetData>
@@ -51279,8 +51550,8 @@
     <cfRule type="duplicateValues" dxfId="172" priority="180"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15">
-    <cfRule type="duplicateValues" dxfId="171" priority="179"/>
-    <cfRule type="duplicateValues" dxfId="170" priority="178"/>
+    <cfRule type="duplicateValues" dxfId="171" priority="178"/>
+    <cfRule type="duplicateValues" dxfId="170" priority="179"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16">
     <cfRule type="duplicateValues" dxfId="169" priority="177"/>
@@ -51301,12 +51572,12 @@
     <cfRule type="duplicateValues" dxfId="162" priority="170"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B24">
-    <cfRule type="duplicateValues" dxfId="161" priority="169"/>
-    <cfRule type="duplicateValues" dxfId="160" priority="168"/>
+    <cfRule type="duplicateValues" dxfId="161" priority="168"/>
+    <cfRule type="duplicateValues" dxfId="160" priority="169"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B27">
-    <cfRule type="duplicateValues" dxfId="159" priority="167"/>
-    <cfRule type="duplicateValues" dxfId="158" priority="166"/>
+    <cfRule type="duplicateValues" dxfId="159" priority="166"/>
+    <cfRule type="duplicateValues" dxfId="158" priority="167"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28">
     <cfRule type="duplicateValues" dxfId="157" priority="165"/>
@@ -51796,11 +52067,11 @@
       </c>
       <c r="B1" s="15">
         <f>COUNTA(sum!A:A) -1</f>
-        <v>248</v>
-      </c>
-      <c r="C1" s="23">
+        <v>253</v>
+      </c>
+      <c r="C1" s="22">
         <f>COUNTIF(sum!I:I, "completed")/(B1-COUNTIF(sum!I:I, "abandoned")-COUNTIF(sum!I:I, "late app"))</f>
-        <v>0.99585062240663902</v>
+        <v>0.97560975609756095</v>
       </c>
       <c r="D1" s="21">
         <f>COUNTIF(sum!I:I, "completed")</f>
@@ -51839,7 +52110,7 @@
       </c>
       <c r="B5" s="15">
         <f>COUNTA(sum!J:J) -1</f>
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="C5" s="14">
         <f>B5/B1</f>
@@ -51852,11 +52123,11 @@
       </c>
       <c r="B6" s="16">
         <f>COUNTIFS(sum!J:J,"no news")</f>
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C6" s="10">
         <f>B6/$B$5</f>
-        <v>0.97177419354838712</v>
+        <v>0.96837944664031617</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
@@ -51865,11 +52136,11 @@
       </c>
       <c r="B7" s="16">
         <f>COUNTIFS(sum!J:J,"rejected")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C7" s="10">
         <f t="shared" ref="C7:C10" si="0">B7/$B$5</f>
-        <v>2.8225806451612902E-2</v>
+        <v>3.1620553359683792E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">

--- a/EconJM_status.xlsx
+++ b/EconJM_status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\javie\Dropbox\Work\Job Search\2025 EconJM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33AB038B-FA27-40F4-A9D7-3716430E3770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{820AC922-C742-4C7E-AD3C-B3FC9CEE83F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" activeTab="1" xr2:uid="{6FE48536-7E5C-BF4C-9490-2A6392576298}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" xr2:uid="{6FE48536-7E5C-BF4C-9490-2A6392576298}"/>
   </bookViews>
   <sheets>
     <sheet name="sum" sheetId="1" r:id="rId1"/>
@@ -1083,7 +1083,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2538" uniqueCount="802">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2551" uniqueCount="803">
   <si>
     <t>add_id</t>
   </si>
@@ -3525,6 +3525,9 @@
   </si>
   <si>
     <t>added some info of stragelers in EJM and JOE</t>
+  </si>
+  <si>
+    <t>Prof. Philipp Ager philipp.ager@uni-mannheim.de</t>
   </si>
 </sst>
 </file>
@@ -3706,7 +3709,27 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="194">
+  <dxfs count="196">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -39524,7 +39547,7 @@
         <v>96</v>
       </c>
       <c r="J56" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="K56" t="s">
         <v>309</v>
@@ -48018,8 +48041,11 @@
       <c r="E243" t="s">
         <v>15</v>
       </c>
+      <c r="H243" t="s">
+        <v>802</v>
+      </c>
       <c r="I243" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J243" t="s">
         <v>402</v>
@@ -48066,7 +48092,7 @@
         <v>795</v>
       </c>
       <c r="I244" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J244" t="s">
         <v>402</v>
@@ -48110,7 +48136,7 @@
         <v>797</v>
       </c>
       <c r="I245" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J245" t="s">
         <v>402</v>
@@ -48334,7 +48360,7 @@
         <v>15</v>
       </c>
       <c r="I250" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J250" t="s">
         <v>402</v>
@@ -48501,7 +48527,7 @@
         <v>40</v>
       </c>
       <c r="I254" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J254" t="s">
         <v>402</v>
@@ -48538,52 +48564,52 @@
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="A1:B208 A210:B1048576">
-    <cfRule type="duplicateValues" dxfId="193" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="195" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:B22">
-    <cfRule type="duplicateValues" dxfId="192" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="194" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A61:B61">
-    <cfRule type="duplicateValues" dxfId="191" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="193" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="containsText" dxfId="190" priority="6" operator="containsText" text="closed">
+    <cfRule type="containsText" dxfId="192" priority="6" operator="containsText" text="closed">
       <formula>NOT(ISERROR(SEARCH("closed",I1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="189" priority="7" operator="containsText" text="abandoned">
+    <cfRule type="containsText" dxfId="191" priority="7" operator="containsText" text="abandoned">
       <formula>NOT(ISERROR(SEARCH("abandoned",I1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="188" priority="9" operator="containsText" text="late app">
+    <cfRule type="containsText" dxfId="190" priority="9" operator="containsText" text="late app">
       <formula>NOT(ISERROR(SEARCH("late app",I1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:L223 O78:O80 O83:O89 O92:O112 O115:O124 O126:O181 R136 R153 R159 R166 R173 R178 O183:O205 O208:O211 O213:O218 O220:O233 I224:K224 R225 I225:L1048576 O235:O237 O239:O248 M248 O250:O254 I1:J1">
-    <cfRule type="containsText" dxfId="187" priority="12" operator="containsText" text="completed">
+    <cfRule type="containsText" dxfId="189" priority="12" operator="containsText" text="completed">
       <formula>NOT(ISERROR(SEARCH("completed",I1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:J1048576">
-    <cfRule type="containsText" dxfId="186" priority="1" operator="containsText" text="no news">
+    <cfRule type="containsText" dxfId="188" priority="1" operator="containsText" text="no news">
       <formula>NOT(ISERROR(SEARCH("no news",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="185" priority="2" operator="containsText" text="offer">
+    <cfRule type="containsText" dxfId="187" priority="2" operator="containsText" text="offer">
       <formula>NOT(ISERROR(SEARCH("offer",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="184" priority="3" operator="containsText" text="fly out">
+    <cfRule type="containsText" dxfId="186" priority="3" operator="containsText" text="fly out">
       <formula>NOT(ISERROR(SEARCH("fly out",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="183" priority="4" operator="containsText" text="interview">
+    <cfRule type="containsText" dxfId="185" priority="4" operator="containsText" text="interview">
       <formula>NOT(ISERROR(SEARCH("interview",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="182" priority="5" operator="containsText" text="rejected">
+    <cfRule type="containsText" dxfId="184" priority="5" operator="containsText" text="rejected">
       <formula>NOT(ISERROR(SEARCH("rejected",J1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1:L223 O78:O80 O83:O89 O92:O112 O115:O124 O126:O181 R136 R153 R159 R166 R173 R178 O183:O205 O208:O211 O213:O218 O220:O233 K224 R225 K225:L1048576 O235:O237 O239:O248 M248 O250:O254">
-    <cfRule type="containsText" dxfId="181" priority="10" operator="containsText" text="NO">
+    <cfRule type="containsText" dxfId="183" priority="10" operator="containsText" text="NO">
       <formula>NOT(ISERROR(SEARCH("NO",K1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="180" priority="11" operator="containsText" text="YES">
+    <cfRule type="containsText" dxfId="182" priority="11" operator="containsText" text="YES">
       <formula>NOT(ISERROR(SEARCH("YES",K1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -48697,7 +48723,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923E81FA-B875-3C4E-A189-1A21268FA086}">
-  <dimension ref="A1:C263"/>
+  <dimension ref="A1:C269"/>
   <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="32.83203125" customWidth="1"/>
@@ -51532,519 +51558,591 @@
         <v>403</v>
       </c>
     </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A264" s="1">
+        <v>45989</v>
+      </c>
+      <c r="B264" t="s">
+        <v>144</v>
+      </c>
+      <c r="C264" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A265" s="1">
+        <v>45991</v>
+      </c>
+      <c r="B265" t="s">
+        <v>791</v>
+      </c>
+      <c r="C265" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A266" s="1">
+        <v>45991</v>
+      </c>
+      <c r="B266" t="s">
+        <v>792</v>
+      </c>
+      <c r="C266" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A267" s="1">
+        <v>45991</v>
+      </c>
+      <c r="B267" t="s">
+        <v>796</v>
+      </c>
+      <c r="C267" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A268" s="1">
+        <v>45991</v>
+      </c>
+      <c r="B268" t="s">
+        <v>790</v>
+      </c>
+      <c r="C268" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A269" s="1">
+        <v>45991</v>
+      </c>
+      <c r="B269" t="s">
+        <v>798</v>
+      </c>
+      <c r="C269" t="s">
+        <v>97</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="B5">
-    <cfRule type="duplicateValues" dxfId="179" priority="186"/>
-    <cfRule type="duplicateValues" dxfId="178" priority="187"/>
+    <cfRule type="duplicateValues" dxfId="181" priority="188"/>
+    <cfRule type="duplicateValues" dxfId="180" priority="189"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B10">
+    <cfRule type="duplicateValues" dxfId="179" priority="187"/>
+    <cfRule type="duplicateValues" dxfId="178" priority="186"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B11">
     <cfRule type="duplicateValues" dxfId="177" priority="185"/>
     <cfRule type="duplicateValues" dxfId="176" priority="184"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B11">
+  <conditionalFormatting sqref="B12">
     <cfRule type="duplicateValues" dxfId="175" priority="183"/>
     <cfRule type="duplicateValues" dxfId="174" priority="182"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B12">
-    <cfRule type="duplicateValues" dxfId="173" priority="181"/>
-    <cfRule type="duplicateValues" dxfId="172" priority="180"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B15">
-    <cfRule type="duplicateValues" dxfId="171" priority="178"/>
-    <cfRule type="duplicateValues" dxfId="170" priority="179"/>
+    <cfRule type="duplicateValues" dxfId="173" priority="180"/>
+    <cfRule type="duplicateValues" dxfId="172" priority="181"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16">
+    <cfRule type="duplicateValues" dxfId="171" priority="179"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B17">
+    <cfRule type="duplicateValues" dxfId="170" priority="178"/>
     <cfRule type="duplicateValues" dxfId="169" priority="177"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B17">
+  <conditionalFormatting sqref="B18">
     <cfRule type="duplicateValues" dxfId="168" priority="176"/>
     <cfRule type="duplicateValues" dxfId="167" priority="175"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B18">
+  <conditionalFormatting sqref="B19">
     <cfRule type="duplicateValues" dxfId="166" priority="174"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B22:B23">
     <cfRule type="duplicateValues" dxfId="165" priority="173"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B19">
     <cfRule type="duplicateValues" dxfId="164" priority="172"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B22:B23">
-    <cfRule type="duplicateValues" dxfId="163" priority="171"/>
-    <cfRule type="duplicateValues" dxfId="162" priority="170"/>
+  <conditionalFormatting sqref="B24">
+    <cfRule type="duplicateValues" dxfId="163" priority="170"/>
+    <cfRule type="duplicateValues" dxfId="162" priority="171"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B24">
+  <conditionalFormatting sqref="B27">
     <cfRule type="duplicateValues" dxfId="161" priority="168"/>
     <cfRule type="duplicateValues" dxfId="160" priority="169"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B27">
-    <cfRule type="duplicateValues" dxfId="159" priority="166"/>
-    <cfRule type="duplicateValues" dxfId="158" priority="167"/>
+  <conditionalFormatting sqref="B28">
+    <cfRule type="duplicateValues" dxfId="159" priority="167"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B28">
+  <conditionalFormatting sqref="B29">
+    <cfRule type="duplicateValues" dxfId="158" priority="166"/>
     <cfRule type="duplicateValues" dxfId="157" priority="165"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B29">
+  <conditionalFormatting sqref="B30">
     <cfRule type="duplicateValues" dxfId="156" priority="164"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31">
     <cfRule type="duplicateValues" dxfId="155" priority="163"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B30">
+  <conditionalFormatting sqref="B32">
     <cfRule type="duplicateValues" dxfId="154" priority="162"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B31">
+  <conditionalFormatting sqref="B33">
     <cfRule type="duplicateValues" dxfId="153" priority="161"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B32">
+  <conditionalFormatting sqref="B34">
     <cfRule type="duplicateValues" dxfId="152" priority="160"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B33">
+  <conditionalFormatting sqref="B35">
     <cfRule type="duplicateValues" dxfId="151" priority="159"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B34">
+  <conditionalFormatting sqref="B37">
     <cfRule type="duplicateValues" dxfId="150" priority="158"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B35">
+  <conditionalFormatting sqref="B38">
     <cfRule type="duplicateValues" dxfId="149" priority="157"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B37">
+  <conditionalFormatting sqref="B42">
     <cfRule type="duplicateValues" dxfId="148" priority="156"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B38">
+  <conditionalFormatting sqref="B43">
     <cfRule type="duplicateValues" dxfId="147" priority="155"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B42">
+  <conditionalFormatting sqref="B44:B45">
     <cfRule type="duplicateValues" dxfId="146" priority="154"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B43">
+  <conditionalFormatting sqref="B46">
     <cfRule type="duplicateValues" dxfId="145" priority="153"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B44:B45">
+  <conditionalFormatting sqref="B48">
     <cfRule type="duplicateValues" dxfId="144" priority="152"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B46">
+  <conditionalFormatting sqref="B49">
     <cfRule type="duplicateValues" dxfId="143" priority="151"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B48">
+  <conditionalFormatting sqref="B51">
     <cfRule type="duplicateValues" dxfId="142" priority="150"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B49">
+  <conditionalFormatting sqref="B52">
     <cfRule type="duplicateValues" dxfId="141" priority="149"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B51">
-    <cfRule type="duplicateValues" dxfId="140" priority="148"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B52">
-    <cfRule type="duplicateValues" dxfId="139" priority="147"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B58">
-    <cfRule type="duplicateValues" dxfId="138" priority="145"/>
+    <cfRule type="duplicateValues" dxfId="140" priority="147"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B59">
-    <cfRule type="duplicateValues" dxfId="137" priority="143"/>
+    <cfRule type="duplicateValues" dxfId="139" priority="145"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B63">
-    <cfRule type="duplicateValues" dxfId="136" priority="142"/>
+    <cfRule type="duplicateValues" dxfId="138" priority="144"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B64">
-    <cfRule type="duplicateValues" dxfId="135" priority="140"/>
+    <cfRule type="duplicateValues" dxfId="137" priority="142"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B66">
+    <cfRule type="duplicateValues" dxfId="136" priority="141"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B67">
+    <cfRule type="duplicateValues" dxfId="135" priority="140"/>
     <cfRule type="duplicateValues" dxfId="134" priority="139"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B67">
+  <conditionalFormatting sqref="B68">
     <cfRule type="duplicateValues" dxfId="133" priority="138"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B69">
     <cfRule type="duplicateValues" dxfId="132" priority="137"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B68">
-    <cfRule type="duplicateValues" dxfId="131" priority="136"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B69">
-    <cfRule type="duplicateValues" dxfId="130" priority="135"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B70">
-    <cfRule type="duplicateValues" dxfId="129" priority="133"/>
+    <cfRule type="duplicateValues" dxfId="131" priority="135"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B72">
-    <cfRule type="duplicateValues" dxfId="128" priority="132"/>
+    <cfRule type="duplicateValues" dxfId="130" priority="134"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B73">
+    <cfRule type="duplicateValues" dxfId="129" priority="132"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B74">
+    <cfRule type="duplicateValues" dxfId="128" priority="131"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B75">
     <cfRule type="duplicateValues" dxfId="127" priority="130"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B74">
+  <conditionalFormatting sqref="B76">
     <cfRule type="duplicateValues" dxfId="126" priority="129"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B75">
-    <cfRule type="duplicateValues" dxfId="125" priority="128"/>
+  <conditionalFormatting sqref="B77">
+    <cfRule type="duplicateValues" dxfId="125" priority="127"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B76">
-    <cfRule type="duplicateValues" dxfId="124" priority="127"/>
+  <conditionalFormatting sqref="B78">
+    <cfRule type="duplicateValues" dxfId="124" priority="126"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B77">
+  <conditionalFormatting sqref="B83">
     <cfRule type="duplicateValues" dxfId="123" priority="125"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B78">
+  <conditionalFormatting sqref="B84">
     <cfRule type="duplicateValues" dxfId="122" priority="124"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B83">
+  <conditionalFormatting sqref="B85">
     <cfRule type="duplicateValues" dxfId="121" priority="123"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B84">
+  <conditionalFormatting sqref="B87">
     <cfRule type="duplicateValues" dxfId="120" priority="122"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B85">
+  <conditionalFormatting sqref="B88">
     <cfRule type="duplicateValues" dxfId="119" priority="121"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B87">
+  <conditionalFormatting sqref="B89">
     <cfRule type="duplicateValues" dxfId="118" priority="120"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B88">
+  <conditionalFormatting sqref="B90">
     <cfRule type="duplicateValues" dxfId="117" priority="119"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B89">
+  <conditionalFormatting sqref="B91">
     <cfRule type="duplicateValues" dxfId="116" priority="118"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B90">
+  <conditionalFormatting sqref="B92">
     <cfRule type="duplicateValues" dxfId="115" priority="117"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B91">
+  <conditionalFormatting sqref="B93">
     <cfRule type="duplicateValues" dxfId="114" priority="116"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B92">
+  <conditionalFormatting sqref="B94">
     <cfRule type="duplicateValues" dxfId="113" priority="115"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B93">
+  <conditionalFormatting sqref="B95">
     <cfRule type="duplicateValues" dxfId="112" priority="114"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B94">
+  <conditionalFormatting sqref="B96">
     <cfRule type="duplicateValues" dxfId="111" priority="113"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B95">
+  <conditionalFormatting sqref="B97">
     <cfRule type="duplicateValues" dxfId="110" priority="112"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B96">
+  <conditionalFormatting sqref="B98">
     <cfRule type="duplicateValues" dxfId="109" priority="111"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B97">
+  <conditionalFormatting sqref="B99">
     <cfRule type="duplicateValues" dxfId="108" priority="110"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B98">
+  <conditionalFormatting sqref="B100">
     <cfRule type="duplicateValues" dxfId="107" priority="109"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B99">
+  <conditionalFormatting sqref="B101">
     <cfRule type="duplicateValues" dxfId="106" priority="108"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B100">
+  <conditionalFormatting sqref="B104">
     <cfRule type="duplicateValues" dxfId="105" priority="107"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B101">
     <cfRule type="duplicateValues" dxfId="104" priority="106"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B104">
+  <conditionalFormatting sqref="B105:B106">
     <cfRule type="duplicateValues" dxfId="103" priority="105"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B107">
     <cfRule type="duplicateValues" dxfId="102" priority="104"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B105:B106">
+  <conditionalFormatting sqref="B108">
     <cfRule type="duplicateValues" dxfId="101" priority="103"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B107">
+  <conditionalFormatting sqref="B109">
     <cfRule type="duplicateValues" dxfId="100" priority="102"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B108">
+  <conditionalFormatting sqref="B110">
     <cfRule type="duplicateValues" dxfId="99" priority="101"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B109">
+  <conditionalFormatting sqref="B111">
     <cfRule type="duplicateValues" dxfId="98" priority="100"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B110">
+  <conditionalFormatting sqref="B112">
     <cfRule type="duplicateValues" dxfId="97" priority="99"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B111">
+  <conditionalFormatting sqref="B113">
     <cfRule type="duplicateValues" dxfId="96" priority="98"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B112">
+  <conditionalFormatting sqref="B114">
     <cfRule type="duplicateValues" dxfId="95" priority="97"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B113">
+  <conditionalFormatting sqref="B115">
     <cfRule type="duplicateValues" dxfId="94" priority="96"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B114">
+  <conditionalFormatting sqref="B116">
     <cfRule type="duplicateValues" dxfId="93" priority="95"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B115">
+  <conditionalFormatting sqref="B117">
     <cfRule type="duplicateValues" dxfId="92" priority="94"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B116">
+  <conditionalFormatting sqref="B118">
     <cfRule type="duplicateValues" dxfId="91" priority="93"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B117">
+  <conditionalFormatting sqref="B119">
     <cfRule type="duplicateValues" dxfId="90" priority="92"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B118">
+  <conditionalFormatting sqref="B120">
     <cfRule type="duplicateValues" dxfId="89" priority="91"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B119">
+  <conditionalFormatting sqref="B121">
     <cfRule type="duplicateValues" dxfId="88" priority="90"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B120">
+  <conditionalFormatting sqref="B122">
     <cfRule type="duplicateValues" dxfId="87" priority="89"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B121">
+  <conditionalFormatting sqref="B126">
     <cfRule type="duplicateValues" dxfId="86" priority="88"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B122">
+  <conditionalFormatting sqref="B127">
     <cfRule type="duplicateValues" dxfId="85" priority="87"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B126">
+  <conditionalFormatting sqref="B128">
     <cfRule type="duplicateValues" dxfId="84" priority="86"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B127">
+  <conditionalFormatting sqref="B129">
     <cfRule type="duplicateValues" dxfId="83" priority="85"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B128">
+  <conditionalFormatting sqref="B130">
     <cfRule type="duplicateValues" dxfId="82" priority="84"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B129">
+  <conditionalFormatting sqref="B131">
     <cfRule type="duplicateValues" dxfId="81" priority="83"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B130">
+  <conditionalFormatting sqref="B132">
     <cfRule type="duplicateValues" dxfId="80" priority="82"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B131">
+  <conditionalFormatting sqref="B133">
     <cfRule type="duplicateValues" dxfId="79" priority="81"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B132">
+  <conditionalFormatting sqref="B136">
     <cfRule type="duplicateValues" dxfId="78" priority="80"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B133">
+  <conditionalFormatting sqref="B137">
     <cfRule type="duplicateValues" dxfId="77" priority="79"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B136">
+  <conditionalFormatting sqref="B138">
     <cfRule type="duplicateValues" dxfId="76" priority="78"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B137">
+  <conditionalFormatting sqref="B139">
     <cfRule type="duplicateValues" dxfId="75" priority="77"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B138">
+  <conditionalFormatting sqref="B140">
     <cfRule type="duplicateValues" dxfId="74" priority="76"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B139">
+  <conditionalFormatting sqref="B141">
     <cfRule type="duplicateValues" dxfId="73" priority="75"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B140">
+  <conditionalFormatting sqref="B142">
     <cfRule type="duplicateValues" dxfId="72" priority="74"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B141">
+  <conditionalFormatting sqref="B143">
     <cfRule type="duplicateValues" dxfId="71" priority="73"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B142">
+  <conditionalFormatting sqref="B144">
     <cfRule type="duplicateValues" dxfId="70" priority="72"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B143">
+  <conditionalFormatting sqref="B145">
     <cfRule type="duplicateValues" dxfId="69" priority="71"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B144">
+  <conditionalFormatting sqref="B147">
     <cfRule type="duplicateValues" dxfId="68" priority="70"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B145">
+  <conditionalFormatting sqref="B148">
     <cfRule type="duplicateValues" dxfId="67" priority="69"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B147">
+  <conditionalFormatting sqref="B149">
     <cfRule type="duplicateValues" dxfId="66" priority="68"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B148">
+  <conditionalFormatting sqref="B150">
     <cfRule type="duplicateValues" dxfId="65" priority="67"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B149">
+  <conditionalFormatting sqref="B151">
     <cfRule type="duplicateValues" dxfId="64" priority="66"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B150">
+  <conditionalFormatting sqref="B152">
     <cfRule type="duplicateValues" dxfId="63" priority="65"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B151">
+  <conditionalFormatting sqref="B153">
     <cfRule type="duplicateValues" dxfId="62" priority="64"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B152">
+  <conditionalFormatting sqref="B154">
     <cfRule type="duplicateValues" dxfId="61" priority="63"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B153">
+  <conditionalFormatting sqref="B155">
     <cfRule type="duplicateValues" dxfId="60" priority="62"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B154">
+  <conditionalFormatting sqref="B156">
     <cfRule type="duplicateValues" dxfId="59" priority="61"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B155">
+  <conditionalFormatting sqref="B157">
     <cfRule type="duplicateValues" dxfId="58" priority="60"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B156">
+  <conditionalFormatting sqref="B171">
     <cfRule type="duplicateValues" dxfId="57" priority="59"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B157">
+  <conditionalFormatting sqref="B172">
     <cfRule type="duplicateValues" dxfId="56" priority="58"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B171">
+  <conditionalFormatting sqref="B174">
     <cfRule type="duplicateValues" dxfId="55" priority="57"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B172">
+  <conditionalFormatting sqref="B177:B178">
     <cfRule type="duplicateValues" dxfId="54" priority="56"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B174">
+  <conditionalFormatting sqref="B181">
     <cfRule type="duplicateValues" dxfId="53" priority="55"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B177:B178">
+  <conditionalFormatting sqref="B182">
     <cfRule type="duplicateValues" dxfId="52" priority="54"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B181">
+  <conditionalFormatting sqref="B183">
     <cfRule type="duplicateValues" dxfId="51" priority="53"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B182">
+  <conditionalFormatting sqref="B184">
     <cfRule type="duplicateValues" dxfId="50" priority="52"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B183">
+  <conditionalFormatting sqref="B185">
     <cfRule type="duplicateValues" dxfId="49" priority="51"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B184">
+  <conditionalFormatting sqref="B186">
     <cfRule type="duplicateValues" dxfId="48" priority="50"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B185">
+  <conditionalFormatting sqref="B188">
     <cfRule type="duplicateValues" dxfId="47" priority="49"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B186">
+  <conditionalFormatting sqref="B189">
     <cfRule type="duplicateValues" dxfId="46" priority="48"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B188">
+  <conditionalFormatting sqref="B190">
     <cfRule type="duplicateValues" dxfId="45" priority="47"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B189">
+  <conditionalFormatting sqref="B191">
     <cfRule type="duplicateValues" dxfId="44" priority="46"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B190">
+  <conditionalFormatting sqref="B192">
     <cfRule type="duplicateValues" dxfId="43" priority="45"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B191">
+  <conditionalFormatting sqref="B193">
     <cfRule type="duplicateValues" dxfId="42" priority="44"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B192">
+  <conditionalFormatting sqref="B195">
     <cfRule type="duplicateValues" dxfId="41" priority="43"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B193">
+  <conditionalFormatting sqref="B196">
     <cfRule type="duplicateValues" dxfId="40" priority="42"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B195">
+  <conditionalFormatting sqref="B197">
     <cfRule type="duplicateValues" dxfId="39" priority="41"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B196">
+  <conditionalFormatting sqref="B198">
     <cfRule type="duplicateValues" dxfId="38" priority="40"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B197">
+  <conditionalFormatting sqref="B199">
     <cfRule type="duplicateValues" dxfId="37" priority="39"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B198">
+  <conditionalFormatting sqref="B200">
     <cfRule type="duplicateValues" dxfId="36" priority="38"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B199">
+  <conditionalFormatting sqref="B201">
     <cfRule type="duplicateValues" dxfId="35" priority="37"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B200">
+  <conditionalFormatting sqref="B202">
     <cfRule type="duplicateValues" dxfId="34" priority="36"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B201">
+  <conditionalFormatting sqref="B203">
     <cfRule type="duplicateValues" dxfId="33" priority="35"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B202">
+  <conditionalFormatting sqref="B204">
     <cfRule type="duplicateValues" dxfId="32" priority="34"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B203">
+  <conditionalFormatting sqref="B205">
     <cfRule type="duplicateValues" dxfId="31" priority="33"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B204">
+  <conditionalFormatting sqref="B206">
     <cfRule type="duplicateValues" dxfId="30" priority="32"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B205">
+  <conditionalFormatting sqref="B207">
     <cfRule type="duplicateValues" dxfId="29" priority="31"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B206">
+  <conditionalFormatting sqref="B215">
     <cfRule type="duplicateValues" dxfId="28" priority="30"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B207">
+  <conditionalFormatting sqref="B218">
     <cfRule type="duplicateValues" dxfId="27" priority="29"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B215">
+  <conditionalFormatting sqref="B220">
     <cfRule type="duplicateValues" dxfId="26" priority="28"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B218">
+  <conditionalFormatting sqref="B222">
     <cfRule type="duplicateValues" dxfId="25" priority="27"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B220">
+  <conditionalFormatting sqref="B223">
     <cfRule type="duplicateValues" dxfId="24" priority="26"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B222">
+  <conditionalFormatting sqref="B224">
     <cfRule type="duplicateValues" dxfId="23" priority="25"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B223">
+  <conditionalFormatting sqref="B225">
     <cfRule type="duplicateValues" dxfId="22" priority="24"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B224">
+  <conditionalFormatting sqref="B227">
     <cfRule type="duplicateValues" dxfId="21" priority="23"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B225">
+  <conditionalFormatting sqref="B229">
     <cfRule type="duplicateValues" dxfId="20" priority="22"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B227">
+  <conditionalFormatting sqref="B230">
     <cfRule type="duplicateValues" dxfId="19" priority="21"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B229">
+  <conditionalFormatting sqref="B232">
     <cfRule type="duplicateValues" dxfId="18" priority="20"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B230">
+  <conditionalFormatting sqref="B233">
     <cfRule type="duplicateValues" dxfId="17" priority="19"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B232">
+  <conditionalFormatting sqref="B234">
     <cfRule type="duplicateValues" dxfId="16" priority="18"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B233">
+  <conditionalFormatting sqref="B235">
     <cfRule type="duplicateValues" dxfId="15" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B234">
+  <conditionalFormatting sqref="B236">
     <cfRule type="duplicateValues" dxfId="14" priority="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B235">
+  <conditionalFormatting sqref="B237">
     <cfRule type="duplicateValues" dxfId="13" priority="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B236">
-    <cfRule type="duplicateValues" dxfId="12" priority="14"/>
+  <conditionalFormatting sqref="B239">
+    <cfRule type="duplicateValues" dxfId="12" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B237">
-    <cfRule type="duplicateValues" dxfId="11" priority="13"/>
+  <conditionalFormatting sqref="B240">
+    <cfRule type="duplicateValues" dxfId="11" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B239">
+  <conditionalFormatting sqref="B241">
     <cfRule type="duplicateValues" dxfId="10" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B240">
+  <conditionalFormatting sqref="B242">
     <cfRule type="duplicateValues" dxfId="9" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B241">
+  <conditionalFormatting sqref="B243">
     <cfRule type="duplicateValues" dxfId="8" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B242">
+  <conditionalFormatting sqref="B250">
     <cfRule type="duplicateValues" dxfId="7" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B243">
+  <conditionalFormatting sqref="B251">
     <cfRule type="duplicateValues" dxfId="6" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B250">
+  <conditionalFormatting sqref="B253">
     <cfRule type="duplicateValues" dxfId="5" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B251">
+  <conditionalFormatting sqref="B255">
     <cfRule type="duplicateValues" dxfId="4" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B253">
+  <conditionalFormatting sqref="B258:B259">
     <cfRule type="duplicateValues" dxfId="3" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B255">
+  <conditionalFormatting sqref="B260">
     <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B258:B259">
+  <conditionalFormatting sqref="B265:B267 B269">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B260">
+  <conditionalFormatting sqref="B268">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -52071,11 +52169,11 @@
       </c>
       <c r="C1" s="22">
         <f>COUNTIF(sum!I:I, "completed")/(B1-COUNTIF(sum!I:I, "abandoned")-COUNTIF(sum!I:I, "late app"))</f>
-        <v>0.97560975609756095</v>
+        <v>0.99593495934959353</v>
       </c>
       <c r="D1" s="21">
         <f>COUNTIF(sum!I:I, "completed")</f>
-        <v>240</v>
+        <v>245</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.4">
@@ -52123,11 +52221,11 @@
       </c>
       <c r="B6" s="16">
         <f>COUNTIFS(sum!J:J,"no news")</f>
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C6" s="10">
         <f>B6/$B$5</f>
-        <v>0.96837944664031617</v>
+        <v>0.96442687747035571</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
@@ -52149,11 +52247,11 @@
       </c>
       <c r="B8" s="16">
         <f>COUNTIFS(sum!J:J,"interview")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3.952569169960474E-3</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">

--- a/EconJM_status.xlsx
+++ b/EconJM_status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\javie\Dropbox\Work\Job Search\2025 EconJM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{820AC922-C742-4C7E-AD3C-B3FC9CEE83F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE209D34-6373-4EA0-B5DA-E4851DEED772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" xr2:uid="{6FE48536-7E5C-BF4C-9490-2A6392576298}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" activeTab="1" xr2:uid="{6FE48536-7E5C-BF4C-9490-2A6392576298}"/>
   </bookViews>
   <sheets>
     <sheet name="sum" sheetId="1" r:id="rId1"/>
@@ -1083,7 +1083,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2551" uniqueCount="803">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2675" uniqueCount="853">
   <si>
     <t>add_id</t>
   </si>
@@ -3528,6 +3528,156 @@
   </si>
   <si>
     <t>Prof. Philipp Ager philipp.ager@uni-mannheim.de</t>
+  </si>
+  <si>
+    <t>https://postdocs.northwestern.edu/announcements/positions-at-northwestern/2025/postdoctoral-research-opportunity-global-llm-values-benchmarking-working-group.html</t>
+  </si>
+  <si>
+    <t>llm_nwest</t>
+  </si>
+  <si>
+    <t>Northwestern University</t>
+  </si>
+  <si>
+    <t>Yingdan Lu. </t>
+  </si>
+  <si>
+    <t>hec_paris</t>
+  </si>
+  <si>
+    <t>HEC Paris</t>
+  </si>
+  <si>
+    <t>monash_post_2</t>
+  </si>
+  <si>
+    <t>Ricardo Dahis, the Primary Investigator (PI)</t>
+  </si>
+  <si>
+    <t>virginia_common</t>
+  </si>
+  <si>
+    <t>Virginia Commonwealth University</t>
+  </si>
+  <si>
+    <t>https://vcujobs.com/jobs/assistant-professor-economics-vcu-main-campus-virginia-united-states</t>
+  </si>
+  <si>
+    <t>apply in JOE + internal wb</t>
+  </si>
+  <si>
+    <t>Christopher Herrington   herringtoncm@vcu.edu</t>
+  </si>
+  <si>
+    <t>bowling_state</t>
+  </si>
+  <si>
+    <t>https://www.schooljobs.com/careers/bgsu/faculty/jobs/5151499/assistant-teaching-professor-of-economics?pagetype=jobOpportunitiesJobs</t>
+  </si>
+  <si>
+    <t>Bowling Green State University</t>
+  </si>
+  <si>
+    <t>osaka_micro</t>
+  </si>
+  <si>
+    <t>https://www.econ.osaka-u.ac.jp/en/en-news/3377/</t>
+  </si>
+  <si>
+    <t>Osaka University</t>
+  </si>
+  <si>
+    <t>Duquesne University</t>
+  </si>
+  <si>
+    <t>duquesne</t>
+  </si>
+  <si>
+    <t>https://apply.interfolio.com/178305</t>
+  </si>
+  <si>
+    <t>rochester</t>
+  </si>
+  <si>
+    <t>c.massaro@rochester.edu</t>
+  </si>
+  <si>
+    <t>University of Rochester</t>
+  </si>
+  <si>
+    <t>uncarolina</t>
+  </si>
+  <si>
+    <t>The University of North Carolina, Charlotte</t>
+  </si>
+  <si>
+    <t>email rec letters to econsearch@charlotte.edu</t>
+  </si>
+  <si>
+    <t>send to email + letter of rec</t>
+  </si>
+  <si>
+    <t>https://jobs.charlotte.edu/postings/65111</t>
+  </si>
+  <si>
+    <t>fiu</t>
+  </si>
+  <si>
+    <t>Florida International University</t>
+  </si>
+  <si>
+    <t>https://pslinks.fiu.edu/psc/jobs/CUSTOMER/HRMS/c/HRS_HRAM_FL.HRS_CG_SEARCH_FL.GBL?Page=HRS_APP_SCHJOB_FL&amp;Action=U</t>
+  </si>
+  <si>
+    <t>Job Opening ID 536413</t>
+  </si>
+  <si>
+    <t>added some stragelers from JOE and EJM</t>
+  </si>
+  <si>
+    <t>rio_grande</t>
+  </si>
+  <si>
+    <t>https://careers.utrgv.edu/postings/49492</t>
+  </si>
+  <si>
+    <t>U Texas Rio Grande Valey</t>
+  </si>
+  <si>
+    <t>lund_post</t>
+  </si>
+  <si>
+    <t>Professor Jutta Bolt</t>
+  </si>
+  <si>
+    <t>University of Lund</t>
+  </si>
+  <si>
+    <t>https://lu.varbi.com/en/what:job/jobID:875828/type:job/where:4/apply:1</t>
+  </si>
+  <si>
+    <t>hse</t>
+  </si>
+  <si>
+    <t>https://iri.hse.ru/announcements/876324879.html</t>
+  </si>
+  <si>
+    <t>National Research University Higher School of Economics</t>
+  </si>
+  <si>
+    <t>warthon_media</t>
+  </si>
+  <si>
+    <t>University of Pennsylvania</t>
+  </si>
+  <si>
+    <t>https://infodem.upenn.edu/wharton-postdoc/</t>
+  </si>
+  <si>
+    <t>about media effects and LLMs</t>
+  </si>
+  <si>
+    <t>added a few more stragelers</t>
   </si>
 </sst>
 </file>
@@ -3709,7 +3859,57 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="196">
+  <dxfs count="208">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -5517,6 +5717,76 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -37035,7 +37305,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7772053-9363-CA4A-A53F-040B7C700753}">
-  <dimension ref="A1:V254"/>
+  <dimension ref="A1:V268"/>
   <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="19.6640625" customWidth="1"/>
@@ -39955,7 +40225,7 @@
         <v>96</v>
       </c>
       <c r="J65" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M65" t="s">
         <v>609</v>
@@ -40172,7 +40442,7 @@
         <v>96</v>
       </c>
       <c r="J70" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M70" s="2" t="s">
         <v>196</v>
@@ -42213,7 +42483,7 @@
         <v>402</v>
       </c>
       <c r="K113" t="s">
-        <v>244</v>
+        <v>309</v>
       </c>
       <c r="L113" s="1">
         <v>45986</v>
@@ -42264,7 +42534,7 @@
         <v>402</v>
       </c>
       <c r="K114" t="s">
-        <v>244</v>
+        <v>309</v>
       </c>
       <c r="L114" s="1">
         <v>45986</v>
@@ -42324,7 +42594,7 @@
         <v>402</v>
       </c>
       <c r="K115" t="s">
-        <v>244</v>
+        <v>309</v>
       </c>
       <c r="L115" s="1">
         <v>45986</v>
@@ -43960,7 +44230,7 @@
         <v>402</v>
       </c>
       <c r="K152" t="s">
-        <v>244</v>
+        <v>309</v>
       </c>
       <c r="L152" s="1">
         <v>45986</v>
@@ -44013,7 +44283,7 @@
         <v>402</v>
       </c>
       <c r="K153" t="s">
-        <v>244</v>
+        <v>309</v>
       </c>
       <c r="L153" s="1">
         <v>45986</v>
@@ -44063,7 +44333,7 @@
         <v>402</v>
       </c>
       <c r="K154" t="s">
-        <v>244</v>
+        <v>309</v>
       </c>
       <c r="L154" s="1">
         <v>45986</v>
@@ -44116,7 +44386,7 @@
         <v>402</v>
       </c>
       <c r="K155" t="s">
-        <v>244</v>
+        <v>309</v>
       </c>
       <c r="L155" s="1">
         <v>45986</v>
@@ -44594,7 +44864,7 @@
         <v>402</v>
       </c>
       <c r="K166" t="s">
-        <v>244</v>
+        <v>309</v>
       </c>
       <c r="L166" s="1">
         <v>45986</v>
@@ -44736,7 +45006,7 @@
         <v>402</v>
       </c>
       <c r="K169" t="s">
-        <v>244</v>
+        <v>309</v>
       </c>
       <c r="L169" s="1">
         <v>45986</v>
@@ -44793,7 +45063,7 @@
         <v>402</v>
       </c>
       <c r="K170" t="s">
-        <v>244</v>
+        <v>309</v>
       </c>
       <c r="L170" s="1">
         <v>45992</v>
@@ -44843,7 +45113,7 @@
         <v>402</v>
       </c>
       <c r="K171" t="s">
-        <v>244</v>
+        <v>309</v>
       </c>
       <c r="L171" s="1">
         <v>45992</v>
@@ -44893,7 +45163,7 @@
         <v>402</v>
       </c>
       <c r="K172" t="s">
-        <v>244</v>
+        <v>309</v>
       </c>
       <c r="L172" s="1">
         <v>45992</v>
@@ -44946,7 +45216,7 @@
         <v>402</v>
       </c>
       <c r="K173" t="s">
-        <v>244</v>
+        <v>309</v>
       </c>
       <c r="L173" s="1">
         <v>45992</v>
@@ -44993,7 +45263,7 @@
         <v>402</v>
       </c>
       <c r="K174" t="s">
-        <v>244</v>
+        <v>309</v>
       </c>
       <c r="L174" s="1">
         <v>45992</v>
@@ -45087,7 +45357,7 @@
         <v>402</v>
       </c>
       <c r="K176" t="s">
-        <v>244</v>
+        <v>309</v>
       </c>
       <c r="L176" s="1">
         <v>45992</v>
@@ -45137,7 +45407,7 @@
         <v>402</v>
       </c>
       <c r="K177" t="s">
-        <v>244</v>
+        <v>309</v>
       </c>
       <c r="L177" s="1">
         <v>45992</v>
@@ -45234,7 +45504,7 @@
         <v>402</v>
       </c>
       <c r="K179" t="s">
-        <v>244</v>
+        <v>309</v>
       </c>
       <c r="L179" s="1">
         <v>45992</v>
@@ -45331,7 +45601,7 @@
         <v>402</v>
       </c>
       <c r="K181" t="s">
-        <v>244</v>
+        <v>309</v>
       </c>
       <c r="L181" s="1">
         <v>45992</v>
@@ -45734,7 +46004,7 @@
         <v>402</v>
       </c>
       <c r="K190" t="s">
-        <v>244</v>
+        <v>309</v>
       </c>
       <c r="L190" s="1">
         <v>45992</v>
@@ -46114,6 +46384,12 @@
       <c r="J199" t="s">
         <v>402</v>
       </c>
+      <c r="K199" t="s">
+        <v>309</v>
+      </c>
+      <c r="L199" s="1">
+        <v>45992</v>
+      </c>
       <c r="M199" t="s">
         <v>680</v>
       </c>
@@ -46282,7 +46558,7 @@
         <v>402</v>
       </c>
       <c r="K203" t="s">
-        <v>244</v>
+        <v>309</v>
       </c>
       <c r="L203" s="1">
         <v>45992</v>
@@ -46455,7 +46731,7 @@
         <v>402</v>
       </c>
       <c r="K207" t="s">
-        <v>244</v>
+        <v>309</v>
       </c>
       <c r="L207" s="1">
         <v>45992</v>
@@ -46892,7 +47168,7 @@
         <v>402</v>
       </c>
       <c r="K217" t="s">
-        <v>244</v>
+        <v>309</v>
       </c>
       <c r="L217" s="1">
         <v>45992</v>
@@ -47068,7 +47344,7 @@
         <v>402</v>
       </c>
       <c r="K221" t="s">
-        <v>244</v>
+        <v>309</v>
       </c>
       <c r="L221" s="1">
         <v>45992</v>
@@ -47199,6 +47475,12 @@
       <c r="J224" t="s">
         <v>402</v>
       </c>
+      <c r="K224" t="s">
+        <v>309</v>
+      </c>
+      <c r="L224" s="1">
+        <v>45992</v>
+      </c>
       <c r="M224" t="s">
         <v>709</v>
       </c>
@@ -47411,7 +47693,7 @@
         <v>402</v>
       </c>
       <c r="K229" t="s">
-        <v>244</v>
+        <v>309</v>
       </c>
       <c r="L229" s="1">
         <v>45992</v>
@@ -47499,7 +47781,7 @@
         <v>402</v>
       </c>
       <c r="K231" t="s">
-        <v>244</v>
+        <v>309</v>
       </c>
       <c r="L231" s="1">
         <v>45992</v>
@@ -47587,7 +47869,7 @@
         <v>402</v>
       </c>
       <c r="K233" t="s">
-        <v>244</v>
+        <v>309</v>
       </c>
       <c r="L233" s="1">
         <v>45992</v>
@@ -47637,7 +47919,7 @@
         <v>402</v>
       </c>
       <c r="K234" t="s">
-        <v>244</v>
+        <v>309</v>
       </c>
       <c r="L234" s="1">
         <v>45992</v>
@@ -47693,7 +47975,7 @@
         <v>402</v>
       </c>
       <c r="K235" t="s">
-        <v>244</v>
+        <v>309</v>
       </c>
       <c r="L235" s="1">
         <v>45992</v>
@@ -47743,7 +48025,7 @@
         <v>402</v>
       </c>
       <c r="K236" t="s">
-        <v>244</v>
+        <v>309</v>
       </c>
       <c r="L236" s="1">
         <v>45992</v>
@@ -47957,7 +48239,7 @@
         <v>96</v>
       </c>
       <c r="J241" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M241" t="s">
         <v>570</v>
@@ -47983,33 +48265,27 @@
     </row>
     <row r="242" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A242" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="D242" s="1">
         <v>45992</v>
       </c>
       <c r="E242" t="s">
-        <v>40</v>
-      </c>
-      <c r="F242" t="s">
-        <v>785</v>
+        <v>15</v>
+      </c>
+      <c r="H242" t="s">
+        <v>802</v>
       </c>
       <c r="I242" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J242" t="s">
         <v>402</v>
       </c>
-      <c r="K242" t="s">
-        <v>244</v>
-      </c>
-      <c r="L242" s="1">
-        <v>46027</v>
-      </c>
       <c r="M242" t="s">
-        <v>786</v>
-      </c>
-      <c r="N242" t="e" vm="35">
+        <v>185</v>
+      </c>
+      <c r="N242" t="e" vm="29">
         <v>#VALUE!</v>
       </c>
       <c r="O242" t="s">
@@ -48019,7 +48295,7 @@
         <v>776</v>
       </c>
       <c r="R242" s="1">
-        <v>46026</v>
+        <v>46022</v>
       </c>
       <c r="T242">
         <v>1</v>
@@ -48033,7 +48309,10 @@
     </row>
     <row r="243" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A243" t="s">
-        <v>791</v>
+        <v>792</v>
+      </c>
+      <c r="C243" t="s">
+        <v>794</v>
       </c>
       <c r="D243" s="1">
         <v>45992</v>
@@ -48041,8 +48320,8 @@
       <c r="E243" t="s">
         <v>15</v>
       </c>
-      <c r="H243" t="s">
-        <v>802</v>
+      <c r="F243" s="2" t="s">
+        <v>795</v>
       </c>
       <c r="I243" t="s">
         <v>96</v>
@@ -48051,7 +48330,7 @@
         <v>402</v>
       </c>
       <c r="M243" t="s">
-        <v>185</v>
+        <v>793</v>
       </c>
       <c r="N243" t="e" vm="29">
         <v>#VALUE!</v>
@@ -48063,7 +48342,7 @@
         <v>776</v>
       </c>
       <c r="R243" s="1">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="T243">
         <v>1</v>
@@ -48077,10 +48356,7 @@
     </row>
     <row r="244" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A244" t="s">
-        <v>792</v>
-      </c>
-      <c r="C244" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="D244" s="1">
         <v>45992</v>
@@ -48088,8 +48364,8 @@
       <c r="E244" t="s">
         <v>15</v>
       </c>
-      <c r="F244" s="2" t="s">
-        <v>795</v>
+      <c r="H244" t="s">
+        <v>797</v>
       </c>
       <c r="I244" t="s">
         <v>96</v>
@@ -48098,9 +48374,9 @@
         <v>402</v>
       </c>
       <c r="M244" t="s">
-        <v>793</v>
-      </c>
-      <c r="N244" t="e" vm="29">
+        <v>750</v>
+      </c>
+      <c r="N244" t="e" vm="47">
         <v>#VALUE!</v>
       </c>
       <c r="O244" t="s">
@@ -48110,7 +48386,7 @@
         <v>776</v>
       </c>
       <c r="R244" s="1">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="T244">
         <v>1</v>
@@ -48124,16 +48400,16 @@
     </row>
     <row r="245" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A245" t="s">
-        <v>796</v>
+        <v>798</v>
+      </c>
+      <c r="C245" t="s">
+        <v>800</v>
       </c>
       <c r="D245" s="1">
         <v>45992</v>
       </c>
       <c r="E245" t="s">
-        <v>15</v>
-      </c>
-      <c r="H245" t="s">
-        <v>797</v>
+        <v>40</v>
       </c>
       <c r="I245" t="s">
         <v>96</v>
@@ -48142,19 +48418,19 @@
         <v>402</v>
       </c>
       <c r="M245" t="s">
-        <v>750</v>
-      </c>
-      <c r="N245" t="e" vm="47">
+        <v>799</v>
+      </c>
+      <c r="N245" t="e" vm="70">
         <v>#VALUE!</v>
       </c>
       <c r="O245" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="Q245" t="s">
         <v>776</v>
       </c>
       <c r="R245" s="1">
-        <v>46054</v>
+        <v>46026</v>
       </c>
       <c r="T245">
         <v>1</v>
@@ -48168,27 +48444,33 @@
     </row>
     <row r="246" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A246" t="s">
-        <v>662</v>
+        <v>784</v>
       </c>
       <c r="D246" s="1">
-        <v>46011</v>
+        <v>46006</v>
       </c>
       <c r="E246" t="s">
-        <v>15</v>
-      </c>
-      <c r="H246" t="s">
-        <v>664</v>
+        <v>40</v>
+      </c>
+      <c r="F246" t="s">
+        <v>785</v>
       </c>
       <c r="I246" t="s">
-        <v>96</v>
+        <v>23</v>
       </c>
       <c r="J246" t="s">
         <v>402</v>
       </c>
+      <c r="K246" t="s">
+        <v>244</v>
+      </c>
+      <c r="L246" s="1">
+        <v>46027</v>
+      </c>
       <c r="M246" t="s">
-        <v>663</v>
-      </c>
-      <c r="N246" t="e" vm="45">
+        <v>786</v>
+      </c>
+      <c r="N246" t="e" vm="35">
         <v>#VALUE!</v>
       </c>
       <c r="O246" t="s">
@@ -48198,7 +48480,7 @@
         <v>776</v>
       </c>
       <c r="R246" s="1">
-        <v>46037</v>
+        <v>46026</v>
       </c>
       <c r="T246">
         <v>1</v>
@@ -48212,30 +48494,27 @@
     </row>
     <row r="247" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A247" t="s">
-        <v>722</v>
-      </c>
-      <c r="C247" t="s">
-        <v>723</v>
+        <v>841</v>
       </c>
       <c r="D247" s="1">
-        <v>46016</v>
+        <v>46006</v>
       </c>
       <c r="E247" t="s">
-        <v>15</v>
-      </c>
-      <c r="F247" t="s">
-        <v>721</v>
+        <v>844</v>
+      </c>
+      <c r="H247" t="s">
+        <v>842</v>
       </c>
       <c r="I247" t="s">
-        <v>96</v>
+        <v>23</v>
       </c>
       <c r="J247" t="s">
         <v>402</v>
       </c>
       <c r="M247" t="s">
-        <v>720</v>
-      </c>
-      <c r="N247" t="e" vm="68">
+        <v>843</v>
+      </c>
+      <c r="N247" t="e" vm="46">
         <v>#VALUE!</v>
       </c>
       <c r="O247" t="s">
@@ -48245,7 +48524,7 @@
         <v>776</v>
       </c>
       <c r="R247" s="1">
-        <v>45992</v>
+        <v>46022</v>
       </c>
       <c r="T247">
         <v>1</v>
@@ -48258,21 +48537,17 @@
       </c>
     </row>
     <row r="248" spans="1:22" x14ac:dyDescent="0.4">
-      <c r="A248" s="4" t="s">
-        <v>719</v>
-      </c>
-      <c r="B248" s="19"/>
-      <c r="C248" t="s">
-        <v>783</v>
+      <c r="A248" t="s">
+        <v>662</v>
       </c>
       <c r="D248" s="1">
-        <v>46016</v>
+        <v>46011</v>
       </c>
       <c r="E248" t="s">
         <v>15</v>
       </c>
-      <c r="G248">
-        <v>3</v>
+      <c r="H248" t="s">
+        <v>664</v>
       </c>
       <c r="I248" t="s">
         <v>96</v>
@@ -48280,26 +48555,20 @@
       <c r="J248" t="s">
         <v>402</v>
       </c>
-      <c r="K248" t="s">
-        <v>244</v>
-      </c>
-      <c r="L248" s="1">
-        <v>45992</v>
-      </c>
-      <c r="M248" s="2" t="s">
-        <v>718</v>
+      <c r="M248" t="s">
+        <v>663</v>
       </c>
       <c r="N248" t="e" vm="45">
         <v>#VALUE!</v>
       </c>
       <c r="O248" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="Q248" t="s">
         <v>776</v>
       </c>
       <c r="R248" s="1">
-        <v>45996</v>
+        <v>46037</v>
       </c>
       <c r="T248">
         <v>1</v>
@@ -48313,7 +48582,10 @@
     </row>
     <row r="249" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A249" t="s">
-        <v>787</v>
+        <v>722</v>
+      </c>
+      <c r="C249" t="s">
+        <v>723</v>
       </c>
       <c r="D249" s="1">
         <v>46016</v>
@@ -48321,6 +48593,9 @@
       <c r="E249" t="s">
         <v>15</v>
       </c>
+      <c r="F249" t="s">
+        <v>721</v>
+      </c>
       <c r="I249" t="s">
         <v>96</v>
       </c>
@@ -48328,10 +48603,13 @@
         <v>402</v>
       </c>
       <c r="M249" t="s">
-        <v>788</v>
-      </c>
-      <c r="N249" t="e" vm="29">
+        <v>720</v>
+      </c>
+      <c r="N249" t="e" vm="68">
         <v>#VALUE!</v>
+      </c>
+      <c r="O249" t="s">
+        <v>26</v>
       </c>
       <c r="Q249" t="s">
         <v>776</v>
@@ -48340,7 +48618,7 @@
         <v>45992</v>
       </c>
       <c r="T249">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U249">
         <v>0</v>
@@ -48350,8 +48628,12 @@
       </c>
     </row>
     <row r="250" spans="1:22" x14ac:dyDescent="0.4">
-      <c r="A250" t="s">
-        <v>790</v>
+      <c r="A250" s="4" t="s">
+        <v>719</v>
+      </c>
+      <c r="B250" s="19"/>
+      <c r="C250" t="s">
+        <v>783</v>
       </c>
       <c r="D250" s="1">
         <v>46016</v>
@@ -48359,16 +48641,25 @@
       <c r="E250" t="s">
         <v>15</v>
       </c>
+      <c r="G250">
+        <v>3</v>
+      </c>
       <c r="I250" t="s">
         <v>96</v>
       </c>
       <c r="J250" t="s">
         <v>402</v>
       </c>
-      <c r="M250" t="s">
-        <v>789</v>
-      </c>
-      <c r="N250" t="e" vm="75">
+      <c r="K250" t="s">
+        <v>309</v>
+      </c>
+      <c r="L250" s="1">
+        <v>45992</v>
+      </c>
+      <c r="M250" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="N250" t="e" vm="45">
         <v>#VALUE!</v>
       </c>
       <c r="O250" t="s">
@@ -48378,7 +48669,7 @@
         <v>776</v>
       </c>
       <c r="R250" s="1">
-        <v>45992</v>
+        <v>45996</v>
       </c>
       <c r="T250">
         <v>1</v>
@@ -48392,16 +48683,13 @@
     </row>
     <row r="251" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A251" t="s">
-        <v>528</v>
-      </c>
-      <c r="C251" t="s">
-        <v>178</v>
+        <v>787</v>
       </c>
       <c r="D251" s="1">
-        <v>46023</v>
+        <v>46016</v>
       </c>
       <c r="E251" t="s">
-        <v>529</v>
+        <v>15</v>
       </c>
       <c r="I251" t="s">
         <v>96</v>
@@ -48410,39 +48698,36 @@
         <v>402</v>
       </c>
       <c r="M251" t="s">
-        <v>530</v>
-      </c>
-      <c r="N251" t="e" vm="102">
+        <v>788</v>
+      </c>
+      <c r="N251" t="e" vm="29">
         <v>#VALUE!</v>
-      </c>
-      <c r="O251" t="s">
-        <v>19</v>
       </c>
       <c r="Q251" t="s">
         <v>776</v>
       </c>
       <c r="R251" s="1">
-        <v>46041</v>
+        <v>45992</v>
       </c>
       <c r="T251">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U251">
         <v>0</v>
       </c>
       <c r="V251">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="252" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A252" t="s">
-        <v>564</v>
+        <v>790</v>
       </c>
       <c r="D252" s="1">
-        <v>46023</v>
+        <v>46016</v>
       </c>
       <c r="E252" t="s">
-        <v>565</v>
+        <v>15</v>
       </c>
       <c r="I252" t="s">
         <v>96</v>
@@ -48451,19 +48736,19 @@
         <v>402</v>
       </c>
       <c r="M252" t="s">
-        <v>566</v>
-      </c>
-      <c r="N252" t="e" vm="103">
+        <v>789</v>
+      </c>
+      <c r="N252" t="e" vm="75">
         <v>#VALUE!</v>
       </c>
       <c r="O252" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="Q252" t="s">
         <v>776</v>
       </c>
       <c r="R252" s="1">
-        <v>45664</v>
+        <v>45992</v>
       </c>
       <c r="T252">
         <v>1</v>
@@ -48477,13 +48762,16 @@
     </row>
     <row r="253" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A253" t="s">
-        <v>255</v>
+        <v>528</v>
+      </c>
+      <c r="C253" t="s">
+        <v>178</v>
+      </c>
+      <c r="D253" s="1">
+        <v>46023</v>
       </c>
       <c r="E253" t="s">
-        <v>15</v>
-      </c>
-      <c r="F253" s="2" t="s">
-        <v>257</v>
+        <v>529</v>
       </c>
       <c r="I253" t="s">
         <v>96</v>
@@ -48492,39 +48780,39 @@
         <v>402</v>
       </c>
       <c r="M253" t="s">
-        <v>256</v>
-      </c>
-      <c r="N253" t="e" vm="35">
+        <v>530</v>
+      </c>
+      <c r="N253" t="e" vm="102">
         <v>#VALUE!</v>
       </c>
       <c r="O253" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="Q253" t="s">
         <v>776</v>
       </c>
+      <c r="R253" s="1">
+        <v>46041</v>
+      </c>
       <c r="T253">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U253">
         <v>0</v>
       </c>
       <c r="V253">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="254" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A254" t="s">
-        <v>798</v>
-      </c>
-      <c r="C254" t="s">
-        <v>800</v>
+        <v>564</v>
       </c>
       <c r="D254" s="1">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="E254" t="s">
-        <v>40</v>
+        <v>565</v>
       </c>
       <c r="I254" t="s">
         <v>96</v>
@@ -48533,19 +48821,19 @@
         <v>402</v>
       </c>
       <c r="M254" t="s">
-        <v>799</v>
-      </c>
-      <c r="N254" t="e" vm="70">
+        <v>566</v>
+      </c>
+      <c r="N254" t="e" vm="103">
         <v>#VALUE!</v>
       </c>
       <c r="O254" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="Q254" t="s">
         <v>776</v>
       </c>
       <c r="R254" s="1">
-        <v>46026</v>
+        <v>45664</v>
       </c>
       <c r="T254">
         <v>1</v>
@@ -48557,60 +48845,706 @@
         <v>0</v>
       </c>
     </row>
+    <row r="255" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A255" t="s">
+        <v>804</v>
+      </c>
+      <c r="D255" s="1">
+        <v>46023</v>
+      </c>
+      <c r="E255" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="F255" s="2" t="s">
+        <v>806</v>
+      </c>
+      <c r="I255" t="s">
+        <v>23</v>
+      </c>
+      <c r="J255" t="s">
+        <v>402</v>
+      </c>
+      <c r="M255" t="s">
+        <v>805</v>
+      </c>
+      <c r="N255" t="e" vm="35">
+        <v>#VALUE!</v>
+      </c>
+      <c r="O255" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q255" t="s">
+        <v>776</v>
+      </c>
+      <c r="R255" s="1">
+        <v>46038</v>
+      </c>
+      <c r="T255">
+        <v>1</v>
+      </c>
+      <c r="U255">
+        <v>0</v>
+      </c>
+      <c r="V255">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A256" t="s">
+        <v>807</v>
+      </c>
+      <c r="D256" s="1">
+        <v>46023</v>
+      </c>
+      <c r="E256" t="s">
+        <v>15</v>
+      </c>
+      <c r="I256" t="s">
+        <v>23</v>
+      </c>
+      <c r="J256" t="s">
+        <v>402</v>
+      </c>
+      <c r="M256" t="s">
+        <v>808</v>
+      </c>
+      <c r="N256" t="e" vm="54">
+        <v>#VALUE!</v>
+      </c>
+      <c r="O256" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q256" t="s">
+        <v>776</v>
+      </c>
+      <c r="R256" s="1">
+        <v>46052</v>
+      </c>
+      <c r="T256">
+        <v>1</v>
+      </c>
+      <c r="U256">
+        <v>0</v>
+      </c>
+      <c r="V256">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A257" t="s">
+        <v>809</v>
+      </c>
+      <c r="D257" s="1">
+        <v>46023</v>
+      </c>
+      <c r="E257" t="s">
+        <v>15</v>
+      </c>
+      <c r="H257" t="s">
+        <v>810</v>
+      </c>
+      <c r="I257" t="s">
+        <v>23</v>
+      </c>
+      <c r="J257" t="s">
+        <v>402</v>
+      </c>
+      <c r="M257" t="s">
+        <v>123</v>
+      </c>
+      <c r="N257" t="e" vm="25">
+        <v>#VALUE!</v>
+      </c>
+      <c r="O257" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q257" t="s">
+        <v>776</v>
+      </c>
+      <c r="R257" s="1">
+        <v>46052</v>
+      </c>
+      <c r="T257">
+        <v>1</v>
+      </c>
+      <c r="U257">
+        <v>0</v>
+      </c>
+      <c r="V257">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A258" t="s">
+        <v>811</v>
+      </c>
+      <c r="C258" t="s">
+        <v>814</v>
+      </c>
+      <c r="D258" s="1">
+        <v>46023</v>
+      </c>
+      <c r="E258" t="s">
+        <v>40</v>
+      </c>
+      <c r="F258" t="s">
+        <v>813</v>
+      </c>
+      <c r="H258" t="s">
+        <v>815</v>
+      </c>
+      <c r="I258" t="s">
+        <v>23</v>
+      </c>
+      <c r="J258" t="s">
+        <v>402</v>
+      </c>
+      <c r="M258" t="s">
+        <v>812</v>
+      </c>
+      <c r="N258" t="e" vm="35">
+        <v>#VALUE!</v>
+      </c>
+      <c r="O258" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q258" t="s">
+        <v>776</v>
+      </c>
+      <c r="R258" s="1">
+        <v>46037</v>
+      </c>
+      <c r="T258">
+        <v>1</v>
+      </c>
+      <c r="U258">
+        <v>0</v>
+      </c>
+      <c r="V258">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A259" t="s">
+        <v>816</v>
+      </c>
+      <c r="D259" s="1">
+        <v>46023</v>
+      </c>
+      <c r="E259" t="s">
+        <v>40</v>
+      </c>
+      <c r="F259" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="I259" t="s">
+        <v>23</v>
+      </c>
+      <c r="J259" t="s">
+        <v>402</v>
+      </c>
+      <c r="M259" t="s">
+        <v>818</v>
+      </c>
+      <c r="N259" t="e" vm="35">
+        <v>#VALUE!</v>
+      </c>
+      <c r="O259" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q259" t="s">
+        <v>776</v>
+      </c>
+      <c r="R259" s="1">
+        <v>46066</v>
+      </c>
+      <c r="T259">
+        <v>1</v>
+      </c>
+      <c r="U259">
+        <v>0</v>
+      </c>
+      <c r="V259">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A260" t="s">
+        <v>819</v>
+      </c>
+      <c r="D260" s="1">
+        <v>46023</v>
+      </c>
+      <c r="E260" t="s">
+        <v>40</v>
+      </c>
+      <c r="F260" t="s">
+        <v>820</v>
+      </c>
+      <c r="I260" t="s">
+        <v>23</v>
+      </c>
+      <c r="J260" t="s">
+        <v>402</v>
+      </c>
+      <c r="M260" t="s">
+        <v>821</v>
+      </c>
+      <c r="N260" t="e" vm="6">
+        <v>#VALUE!</v>
+      </c>
+      <c r="O260" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q260" t="s">
+        <v>776</v>
+      </c>
+      <c r="R260" s="1">
+        <v>46052</v>
+      </c>
+      <c r="T260">
+        <v>1</v>
+      </c>
+      <c r="U260">
+        <v>0</v>
+      </c>
+      <c r="V260">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A261" t="s">
+        <v>823</v>
+      </c>
+      <c r="D261" s="1">
+        <v>46023</v>
+      </c>
+      <c r="E261" t="s">
+        <v>40</v>
+      </c>
+      <c r="F261" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="I261" t="s">
+        <v>23</v>
+      </c>
+      <c r="J261" t="s">
+        <v>402</v>
+      </c>
+      <c r="M261" t="s">
+        <v>822</v>
+      </c>
+      <c r="N261" t="e" vm="35">
+        <v>#VALUE!</v>
+      </c>
+      <c r="O261" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q261" t="s">
+        <v>776</v>
+      </c>
+      <c r="R261" s="1">
+        <v>46113</v>
+      </c>
+      <c r="T261">
+        <v>1</v>
+      </c>
+      <c r="U261">
+        <v>0</v>
+      </c>
+      <c r="V261">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A262" t="s">
+        <v>825</v>
+      </c>
+      <c r="C262" t="s">
+        <v>831</v>
+      </c>
+      <c r="D262" s="1">
+        <v>46023</v>
+      </c>
+      <c r="E262" t="s">
+        <v>40</v>
+      </c>
+      <c r="F262" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="I262" t="s">
+        <v>23</v>
+      </c>
+      <c r="J262" t="s">
+        <v>402</v>
+      </c>
+      <c r="M262" t="s">
+        <v>827</v>
+      </c>
+      <c r="N262" t="e" vm="35">
+        <v>#VALUE!</v>
+      </c>
+      <c r="O262" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q262" t="s">
+        <v>776</v>
+      </c>
+      <c r="R262" s="1">
+        <v>46038</v>
+      </c>
+      <c r="T262">
+        <v>1</v>
+      </c>
+      <c r="U262">
+        <v>0</v>
+      </c>
+      <c r="V262">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A263" t="s">
+        <v>828</v>
+      </c>
+      <c r="C263" t="s">
+        <v>830</v>
+      </c>
+      <c r="D263" s="1">
+        <v>46023</v>
+      </c>
+      <c r="E263" t="s">
+        <v>40</v>
+      </c>
+      <c r="F263" t="s">
+        <v>832</v>
+      </c>
+      <c r="I263" t="s">
+        <v>23</v>
+      </c>
+      <c r="J263" t="s">
+        <v>402</v>
+      </c>
+      <c r="M263" t="s">
+        <v>829</v>
+      </c>
+      <c r="N263" t="e" vm="35">
+        <v>#VALUE!</v>
+      </c>
+      <c r="O263" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q263" t="s">
+        <v>776</v>
+      </c>
+      <c r="R263" s="1">
+        <v>46143</v>
+      </c>
+      <c r="T263">
+        <v>1</v>
+      </c>
+      <c r="U263">
+        <v>0</v>
+      </c>
+      <c r="V263">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A264" t="s">
+        <v>833</v>
+      </c>
+      <c r="C264" t="s">
+        <v>836</v>
+      </c>
+      <c r="D264" s="1">
+        <v>46023</v>
+      </c>
+      <c r="E264" t="s">
+        <v>40</v>
+      </c>
+      <c r="F264" s="2" t="s">
+        <v>835</v>
+      </c>
+      <c r="I264" t="s">
+        <v>23</v>
+      </c>
+      <c r="J264" t="s">
+        <v>402</v>
+      </c>
+      <c r="M264" t="s">
+        <v>834</v>
+      </c>
+      <c r="N264" t="e" vm="35">
+        <v>#VALUE!</v>
+      </c>
+      <c r="O264" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q264" t="s">
+        <v>776</v>
+      </c>
+      <c r="R264" s="1">
+        <v>46027</v>
+      </c>
+      <c r="T264">
+        <v>1</v>
+      </c>
+      <c r="U264">
+        <v>0</v>
+      </c>
+      <c r="V264">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A265" t="s">
+        <v>838</v>
+      </c>
+      <c r="D265" s="1">
+        <v>46023</v>
+      </c>
+      <c r="E265" t="s">
+        <v>839</v>
+      </c>
+      <c r="I265" t="s">
+        <v>23</v>
+      </c>
+      <c r="J265" t="s">
+        <v>402</v>
+      </c>
+      <c r="M265" t="s">
+        <v>840</v>
+      </c>
+      <c r="N265" t="e" vm="35">
+        <v>#VALUE!</v>
+      </c>
+      <c r="O265" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q265" t="s">
+        <v>776</v>
+      </c>
+      <c r="T265">
+        <v>1</v>
+      </c>
+      <c r="U265">
+        <v>0</v>
+      </c>
+      <c r="V265">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A266" t="s">
+        <v>845</v>
+      </c>
+      <c r="D266" s="1">
+        <v>46023</v>
+      </c>
+      <c r="E266" t="s">
+        <v>846</v>
+      </c>
+      <c r="I266" t="s">
+        <v>23</v>
+      </c>
+      <c r="J266" t="s">
+        <v>402</v>
+      </c>
+      <c r="M266" t="s">
+        <v>847</v>
+      </c>
+      <c r="N266" t="e" vm="84">
+        <v>#VALUE!</v>
+      </c>
+      <c r="O266" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q266" t="s">
+        <v>776</v>
+      </c>
+      <c r="R266" s="1">
+        <v>46037</v>
+      </c>
+      <c r="T266">
+        <v>1</v>
+      </c>
+      <c r="U266">
+        <v>0</v>
+      </c>
+      <c r="V266">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A267" t="s">
+        <v>848</v>
+      </c>
+      <c r="C267" t="s">
+        <v>851</v>
+      </c>
+      <c r="D267" s="1">
+        <v>46023</v>
+      </c>
+      <c r="E267" t="s">
+        <v>850</v>
+      </c>
+      <c r="I267" t="s">
+        <v>23</v>
+      </c>
+      <c r="J267" t="s">
+        <v>402</v>
+      </c>
+      <c r="M267" t="s">
+        <v>849</v>
+      </c>
+      <c r="N267" t="e" vm="35">
+        <v>#VALUE!</v>
+      </c>
+      <c r="O267" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q267" t="s">
+        <v>776</v>
+      </c>
+      <c r="R267" s="1">
+        <v>46033</v>
+      </c>
+      <c r="T267">
+        <v>1</v>
+      </c>
+      <c r="U267">
+        <v>0</v>
+      </c>
+      <c r="V267">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A268" t="s">
+        <v>255</v>
+      </c>
+      <c r="E268" t="s">
+        <v>15</v>
+      </c>
+      <c r="F268" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="I268" t="s">
+        <v>96</v>
+      </c>
+      <c r="J268" t="s">
+        <v>402</v>
+      </c>
+      <c r="M268" t="s">
+        <v>256</v>
+      </c>
+      <c r="N268" t="e" vm="35">
+        <v>#VALUE!</v>
+      </c>
+      <c r="O268" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q268" t="s">
+        <v>776</v>
+      </c>
+      <c r="T268">
+        <v>0</v>
+      </c>
+      <c r="U268">
+        <v>0</v>
+      </c>
+      <c r="V268">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:V248" xr:uid="{F7772053-9363-CA4A-A53F-040B7C700753}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V253">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V268">
       <sortCondition ref="D1:D248"/>
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="A1:B208 A210:B1048576">
-    <cfRule type="duplicateValues" dxfId="195" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="207" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:B22">
-    <cfRule type="duplicateValues" dxfId="194" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="206" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A61:B61">
-    <cfRule type="duplicateValues" dxfId="193" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="205" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="containsText" dxfId="192" priority="6" operator="containsText" text="closed">
+    <cfRule type="containsText" dxfId="204" priority="15" operator="containsText" text="closed">
       <formula>NOT(ISERROR(SEARCH("closed",I1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="191" priority="7" operator="containsText" text="abandoned">
+    <cfRule type="containsText" dxfId="203" priority="16" operator="containsText" text="abandoned">
       <formula>NOT(ISERROR(SEARCH("abandoned",I1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="190" priority="9" operator="containsText" text="late app">
+    <cfRule type="containsText" dxfId="202" priority="18" operator="containsText" text="late app">
       <formula>NOT(ISERROR(SEARCH("late app",I1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:L223 O78:O80 O83:O89 O92:O112 O115:O124 O126:O181 R136 R153 R159 R166 R173 R178 O183:O205 O208:O211 O213:O218 O220:O233 I224:K224 R225 I225:L1048576 O235:O237 O239:O248 M248 O250:O254 I1:J1">
-    <cfRule type="containsText" dxfId="189" priority="12" operator="containsText" text="completed">
+  <conditionalFormatting sqref="I2:L1048576 O78:O80 O83:O89 O92:O112 O115:O124 O126:O181 R136 R153 R159 R166 R173 R178 O183:O205 O208:O211 O213:O218 O220:O233 R225 O235:O237 O239:O248 M248 O250:O255 I1:J1 M266 N267">
+    <cfRule type="containsText" dxfId="201" priority="21" operator="containsText" text="completed">
       <formula>NOT(ISERROR(SEARCH("completed",I1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:J1048576">
-    <cfRule type="containsText" dxfId="188" priority="1" operator="containsText" text="no news">
+    <cfRule type="containsText" dxfId="200" priority="10" operator="containsText" text="no news">
       <formula>NOT(ISERROR(SEARCH("no news",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="187" priority="2" operator="containsText" text="offer">
+    <cfRule type="containsText" dxfId="199" priority="11" operator="containsText" text="offer">
       <formula>NOT(ISERROR(SEARCH("offer",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="186" priority="3" operator="containsText" text="fly out">
+    <cfRule type="containsText" dxfId="198" priority="12" operator="containsText" text="fly out">
       <formula>NOT(ISERROR(SEARCH("fly out",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="185" priority="4" operator="containsText" text="interview">
+    <cfRule type="containsText" dxfId="197" priority="13" operator="containsText" text="interview">
       <formula>NOT(ISERROR(SEARCH("interview",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="184" priority="5" operator="containsText" text="rejected">
+    <cfRule type="containsText" dxfId="196" priority="14" operator="containsText" text="rejected">
       <formula>NOT(ISERROR(SEARCH("rejected",J1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K1:L223 O78:O80 O83:O89 O92:O112 O115:O124 O126:O181 R136 R153 R159 R166 R173 R178 O183:O205 O208:O211 O213:O218 O220:O233 K224 R225 K225:L1048576 O235:O237 O239:O248 M248 O250:O254">
-    <cfRule type="containsText" dxfId="183" priority="10" operator="containsText" text="NO">
+  <conditionalFormatting sqref="K1:L1048576 O78:O80 O83:O89 O92:O112 O115:O124 O126:O181 R136 R153 R159 R166 R173 R178 O183:O205 O208:O211 O213:O218 O220:O233 R225 O235:O237 O239:O248 M248 O250:O255 M266 N267">
+    <cfRule type="containsText" dxfId="195" priority="19" operator="containsText" text="NO">
       <formula>NOT(ISERROR(SEARCH("NO",K1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="182" priority="11" operator="containsText" text="YES">
+    <cfRule type="containsText" dxfId="194" priority="20" operator="containsText" text="YES">
       <formula>NOT(ISERROR(SEARCH("YES",K1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N256:O264 O265 N266:O266 O267:O268">
+    <cfRule type="containsText" dxfId="193" priority="7" operator="containsText" text="NO">
+      <formula>NOT(ISERROR(SEARCH("NO",N256)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="192" priority="8" operator="containsText" text="YES">
+      <formula>NOT(ISERROR(SEARCH("YES",N256)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="191" priority="9" operator="containsText" text="completed">
+      <formula>NOT(ISERROR(SEARCH("completed",N256)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N265">
+    <cfRule type="containsText" dxfId="5" priority="4" operator="containsText" text="NO">
+      <formula>NOT(ISERROR(SEARCH("NO",N265)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="YES">
+      <formula>NOT(ISERROR(SEARCH("YES",N265)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="6" operator="containsText" text="completed">
+      <formula>NOT(ISERROR(SEARCH("completed",N265)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N268">
+    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="NO">
+      <formula>NOT(ISERROR(SEARCH("NO",N268)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="YES">
+      <formula>NOT(ISERROR(SEARCH("YES",N268)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="completed">
+      <formula>NOT(ISERROR(SEARCH("completed",N268)))</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
@@ -48695,7 +49629,7 @@
     <hyperlink ref="M17" r:id="rId79" xr:uid="{9A9A6BC9-B330-7842-A78C-4DCC88F5E19F}"/>
     <hyperlink ref="M32" r:id="rId80" xr:uid="{928CABEF-4FA6-E646-8140-7B6E43F8FB96}"/>
     <hyperlink ref="F177" r:id="rId81" xr:uid="{82BF1574-A6C6-1641-9FFE-615861E401FD}"/>
-    <hyperlink ref="F253" r:id="rId82" xr:uid="{3562807E-7FDA-F046-BA03-5DDD43072DB7}"/>
+    <hyperlink ref="F268" r:id="rId82" xr:uid="{3562807E-7FDA-F046-BA03-5DDD43072DB7}"/>
     <hyperlink ref="H215" r:id="rId83" display="mailto:ivanpaya@ua.es" xr:uid="{DEFB77A5-E57F-714C-BAB9-56DE82BA0B2E}"/>
     <hyperlink ref="H138" r:id="rId84" display="mailto:ari.hyytinen@hanken.fi" xr:uid="{7777B12A-FD99-4A43-A14B-A15661B760DC}"/>
     <hyperlink ref="H115" r:id="rId85" display="mailto:peter.haan@fu-berlin.de" xr:uid="{3D1A69ED-8F06-1246-B586-201CB349DB62}"/>
@@ -48713,17 +49647,23 @@
     <hyperlink ref="H240" r:id="rId97" display="mailto:ondrej.krcal@econ.muni.cz" xr:uid="{EDDEB1E6-5767-4FFB-A0AE-57A909D04E81}"/>
     <hyperlink ref="M218" r:id="rId98" display="https://www.ovgu.de/unimagdeburg/en/" xr:uid="{BCB3935D-2B6D-4090-86F5-762D762ED0E3}"/>
     <hyperlink ref="E152" r:id="rId99" xr:uid="{550520C0-1E25-41CD-9AEE-9A3C4D7D328C}"/>
-    <hyperlink ref="M248" r:id="rId100" xr:uid="{F0DD6D71-3FFD-4EAB-A251-AAF2DA8EF53C}"/>
-    <hyperlink ref="F244" r:id="rId101" xr:uid="{BDBBC2E2-C3C5-4526-A621-853D22D99CCF}"/>
+    <hyperlink ref="M250" r:id="rId100" xr:uid="{F0DD6D71-3FFD-4EAB-A251-AAF2DA8EF53C}"/>
+    <hyperlink ref="F243" r:id="rId101" xr:uid="{BDBBC2E2-C3C5-4526-A621-853D22D99CCF}"/>
+    <hyperlink ref="F255" r:id="rId102" display="mailto:comap@northwestern.edu" xr:uid="{4DD04925-4C98-401C-B09E-A61B83C23B4E}"/>
+    <hyperlink ref="E255" r:id="rId103" xr:uid="{491ECAF5-1DC5-4C3F-B1BE-621395157776}"/>
+    <hyperlink ref="F259" r:id="rId104" xr:uid="{B084E08B-44BE-4FA5-A345-8036292B3E22}"/>
+    <hyperlink ref="F261" r:id="rId105" xr:uid="{F59B1D31-814A-4100-8601-8879ABB1E739}"/>
+    <hyperlink ref="F262" r:id="rId106" xr:uid="{C4BD89A9-F3F0-4E10-BAC5-751787E6C1A9}"/>
+    <hyperlink ref="F264" r:id="rId107" xr:uid="{64E2681C-F146-4414-BBE6-9DC59E57C615}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId102"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId108"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923E81FA-B875-3C4E-A189-1A21268FA086}">
-  <dimension ref="A1:C269"/>
+  <dimension ref="A1:C274"/>
   <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="32.83203125" customWidth="1"/>
@@ -51624,526 +52564,584 @@
         <v>97</v>
       </c>
     </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A270" s="1">
+        <v>45992</v>
+      </c>
+      <c r="B270" t="s">
+        <v>195</v>
+      </c>
+      <c r="C270" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A271" s="1">
+        <v>45993</v>
+      </c>
+      <c r="B271" t="s">
+        <v>611</v>
+      </c>
+      <c r="C271" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A272" s="1">
+        <v>45993</v>
+      </c>
+      <c r="C272" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A273" s="1">
+        <v>45993</v>
+      </c>
+      <c r="B273" t="s">
+        <v>568</v>
+      </c>
+      <c r="C273" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A274" s="1">
+        <v>45994</v>
+      </c>
+      <c r="C274" t="s">
+        <v>852</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="B5">
-    <cfRule type="duplicateValues" dxfId="181" priority="188"/>
-    <cfRule type="duplicateValues" dxfId="180" priority="189"/>
+    <cfRule type="duplicateValues" dxfId="190" priority="191"/>
+    <cfRule type="duplicateValues" dxfId="189" priority="192"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B10">
-    <cfRule type="duplicateValues" dxfId="179" priority="187"/>
-    <cfRule type="duplicateValues" dxfId="178" priority="186"/>
+    <cfRule type="duplicateValues" dxfId="188" priority="190"/>
+    <cfRule type="duplicateValues" dxfId="187" priority="189"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B11">
-    <cfRule type="duplicateValues" dxfId="177" priority="185"/>
-    <cfRule type="duplicateValues" dxfId="176" priority="184"/>
+    <cfRule type="duplicateValues" dxfId="186" priority="188"/>
+    <cfRule type="duplicateValues" dxfId="185" priority="187"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12">
-    <cfRule type="duplicateValues" dxfId="175" priority="183"/>
-    <cfRule type="duplicateValues" dxfId="174" priority="182"/>
+    <cfRule type="duplicateValues" dxfId="184" priority="186"/>
+    <cfRule type="duplicateValues" dxfId="183" priority="185"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15">
-    <cfRule type="duplicateValues" dxfId="173" priority="180"/>
-    <cfRule type="duplicateValues" dxfId="172" priority="181"/>
+    <cfRule type="duplicateValues" dxfId="182" priority="184"/>
+    <cfRule type="duplicateValues" dxfId="181" priority="183"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16">
-    <cfRule type="duplicateValues" dxfId="171" priority="179"/>
+    <cfRule type="duplicateValues" dxfId="180" priority="182"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17">
-    <cfRule type="duplicateValues" dxfId="170" priority="178"/>
-    <cfRule type="duplicateValues" dxfId="169" priority="177"/>
+    <cfRule type="duplicateValues" dxfId="179" priority="181"/>
+    <cfRule type="duplicateValues" dxfId="178" priority="180"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B18">
-    <cfRule type="duplicateValues" dxfId="168" priority="176"/>
-    <cfRule type="duplicateValues" dxfId="167" priority="175"/>
+    <cfRule type="duplicateValues" dxfId="177" priority="179"/>
+    <cfRule type="duplicateValues" dxfId="176" priority="178"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B19">
-    <cfRule type="duplicateValues" dxfId="166" priority="174"/>
+    <cfRule type="duplicateValues" dxfId="175" priority="177"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:B23">
-    <cfRule type="duplicateValues" dxfId="165" priority="173"/>
-    <cfRule type="duplicateValues" dxfId="164" priority="172"/>
+    <cfRule type="duplicateValues" dxfId="174" priority="176"/>
+    <cfRule type="duplicateValues" dxfId="173" priority="175"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B24">
-    <cfRule type="duplicateValues" dxfId="163" priority="170"/>
-    <cfRule type="duplicateValues" dxfId="162" priority="171"/>
+    <cfRule type="duplicateValues" dxfId="172" priority="174"/>
+    <cfRule type="duplicateValues" dxfId="171" priority="173"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B27">
-    <cfRule type="duplicateValues" dxfId="161" priority="168"/>
-    <cfRule type="duplicateValues" dxfId="160" priority="169"/>
+    <cfRule type="duplicateValues" dxfId="170" priority="172"/>
+    <cfRule type="duplicateValues" dxfId="169" priority="171"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28">
-    <cfRule type="duplicateValues" dxfId="159" priority="167"/>
+    <cfRule type="duplicateValues" dxfId="168" priority="170"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29">
-    <cfRule type="duplicateValues" dxfId="158" priority="166"/>
-    <cfRule type="duplicateValues" dxfId="157" priority="165"/>
+    <cfRule type="duplicateValues" dxfId="167" priority="169"/>
+    <cfRule type="duplicateValues" dxfId="166" priority="168"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="156" priority="164"/>
+    <cfRule type="duplicateValues" dxfId="165" priority="167"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31">
-    <cfRule type="duplicateValues" dxfId="155" priority="163"/>
+    <cfRule type="duplicateValues" dxfId="164" priority="166"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="duplicateValues" dxfId="154" priority="162"/>
+    <cfRule type="duplicateValues" dxfId="163" priority="165"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33">
-    <cfRule type="duplicateValues" dxfId="153" priority="161"/>
+    <cfRule type="duplicateValues" dxfId="162" priority="164"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="152" priority="160"/>
+    <cfRule type="duplicateValues" dxfId="161" priority="163"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35">
-    <cfRule type="duplicateValues" dxfId="151" priority="159"/>
+    <cfRule type="duplicateValues" dxfId="160" priority="162"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37">
-    <cfRule type="duplicateValues" dxfId="150" priority="158"/>
+    <cfRule type="duplicateValues" dxfId="159" priority="161"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38">
-    <cfRule type="duplicateValues" dxfId="149" priority="157"/>
+    <cfRule type="duplicateValues" dxfId="158" priority="160"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B42">
-    <cfRule type="duplicateValues" dxfId="148" priority="156"/>
+    <cfRule type="duplicateValues" dxfId="157" priority="159"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43">
-    <cfRule type="duplicateValues" dxfId="147" priority="155"/>
+    <cfRule type="duplicateValues" dxfId="156" priority="158"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44:B45">
-    <cfRule type="duplicateValues" dxfId="146" priority="154"/>
+    <cfRule type="duplicateValues" dxfId="155" priority="157"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B46">
-    <cfRule type="duplicateValues" dxfId="145" priority="153"/>
+    <cfRule type="duplicateValues" dxfId="154" priority="156"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B48">
-    <cfRule type="duplicateValues" dxfId="144" priority="152"/>
+    <cfRule type="duplicateValues" dxfId="153" priority="155"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B49">
-    <cfRule type="duplicateValues" dxfId="143" priority="151"/>
+    <cfRule type="duplicateValues" dxfId="152" priority="154"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B51">
-    <cfRule type="duplicateValues" dxfId="142" priority="150"/>
+    <cfRule type="duplicateValues" dxfId="151" priority="153"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B52">
-    <cfRule type="duplicateValues" dxfId="141" priority="149"/>
+    <cfRule type="duplicateValues" dxfId="150" priority="152"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B58">
-    <cfRule type="duplicateValues" dxfId="140" priority="147"/>
+    <cfRule type="duplicateValues" dxfId="149" priority="150"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B59">
-    <cfRule type="duplicateValues" dxfId="139" priority="145"/>
+    <cfRule type="duplicateValues" dxfId="148" priority="148"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B63">
-    <cfRule type="duplicateValues" dxfId="138" priority="144"/>
+    <cfRule type="duplicateValues" dxfId="147" priority="147"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B64">
-    <cfRule type="duplicateValues" dxfId="137" priority="142"/>
+    <cfRule type="duplicateValues" dxfId="146" priority="145"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B66">
-    <cfRule type="duplicateValues" dxfId="136" priority="141"/>
+    <cfRule type="duplicateValues" dxfId="145" priority="144"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="135" priority="140"/>
-    <cfRule type="duplicateValues" dxfId="134" priority="139"/>
+    <cfRule type="duplicateValues" dxfId="144" priority="143"/>
+    <cfRule type="duplicateValues" dxfId="143" priority="142"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B68">
-    <cfRule type="duplicateValues" dxfId="133" priority="138"/>
+    <cfRule type="duplicateValues" dxfId="142" priority="141"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B69">
-    <cfRule type="duplicateValues" dxfId="132" priority="137"/>
+    <cfRule type="duplicateValues" dxfId="141" priority="140"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B70">
-    <cfRule type="duplicateValues" dxfId="131" priority="135"/>
+    <cfRule type="duplicateValues" dxfId="140" priority="138"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B72">
-    <cfRule type="duplicateValues" dxfId="130" priority="134"/>
+    <cfRule type="duplicateValues" dxfId="139" priority="137"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B73">
-    <cfRule type="duplicateValues" dxfId="129" priority="132"/>
+    <cfRule type="duplicateValues" dxfId="138" priority="135"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B74">
-    <cfRule type="duplicateValues" dxfId="128" priority="131"/>
+    <cfRule type="duplicateValues" dxfId="137" priority="134"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B75">
-    <cfRule type="duplicateValues" dxfId="127" priority="130"/>
+    <cfRule type="duplicateValues" dxfId="136" priority="133"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B76">
-    <cfRule type="duplicateValues" dxfId="126" priority="129"/>
+    <cfRule type="duplicateValues" dxfId="135" priority="132"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B77">
-    <cfRule type="duplicateValues" dxfId="125" priority="127"/>
+    <cfRule type="duplicateValues" dxfId="134" priority="130"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B78">
-    <cfRule type="duplicateValues" dxfId="124" priority="126"/>
+    <cfRule type="duplicateValues" dxfId="133" priority="129"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B83">
-    <cfRule type="duplicateValues" dxfId="123" priority="125"/>
+    <cfRule type="duplicateValues" dxfId="132" priority="128"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B84">
-    <cfRule type="duplicateValues" dxfId="122" priority="124"/>
+    <cfRule type="duplicateValues" dxfId="131" priority="127"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B85">
-    <cfRule type="duplicateValues" dxfId="121" priority="123"/>
+    <cfRule type="duplicateValues" dxfId="130" priority="126"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B87">
-    <cfRule type="duplicateValues" dxfId="120" priority="122"/>
+    <cfRule type="duplicateValues" dxfId="129" priority="125"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B88">
-    <cfRule type="duplicateValues" dxfId="119" priority="121"/>
+    <cfRule type="duplicateValues" dxfId="128" priority="124"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B89">
-    <cfRule type="duplicateValues" dxfId="118" priority="120"/>
+    <cfRule type="duplicateValues" dxfId="127" priority="123"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B90">
-    <cfRule type="duplicateValues" dxfId="117" priority="119"/>
+    <cfRule type="duplicateValues" dxfId="126" priority="122"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B91">
-    <cfRule type="duplicateValues" dxfId="116" priority="118"/>
+    <cfRule type="duplicateValues" dxfId="125" priority="121"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B92">
-    <cfRule type="duplicateValues" dxfId="115" priority="117"/>
+    <cfRule type="duplicateValues" dxfId="124" priority="120"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B93">
-    <cfRule type="duplicateValues" dxfId="114" priority="116"/>
+    <cfRule type="duplicateValues" dxfId="123" priority="119"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B94">
-    <cfRule type="duplicateValues" dxfId="113" priority="115"/>
+    <cfRule type="duplicateValues" dxfId="122" priority="118"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B95">
-    <cfRule type="duplicateValues" dxfId="112" priority="114"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="117"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B96">
-    <cfRule type="duplicateValues" dxfId="111" priority="113"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="116"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B97">
-    <cfRule type="duplicateValues" dxfId="110" priority="112"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="115"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B98">
-    <cfRule type="duplicateValues" dxfId="109" priority="111"/>
+    <cfRule type="duplicateValues" dxfId="118" priority="114"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B99">
-    <cfRule type="duplicateValues" dxfId="108" priority="110"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="113"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B100">
-    <cfRule type="duplicateValues" dxfId="107" priority="109"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="112"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B101">
-    <cfRule type="duplicateValues" dxfId="106" priority="108"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="111"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B104">
-    <cfRule type="duplicateValues" dxfId="105" priority="107"/>
-    <cfRule type="duplicateValues" dxfId="104" priority="106"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="110"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="109"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B105:B106">
-    <cfRule type="duplicateValues" dxfId="103" priority="105"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="108"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B107">
-    <cfRule type="duplicateValues" dxfId="102" priority="104"/>
+    <cfRule type="duplicateValues" dxfId="111" priority="107"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B108">
-    <cfRule type="duplicateValues" dxfId="101" priority="103"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="106"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B109">
-    <cfRule type="duplicateValues" dxfId="100" priority="102"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="105"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B110">
-    <cfRule type="duplicateValues" dxfId="99" priority="101"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="104"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B111">
-    <cfRule type="duplicateValues" dxfId="98" priority="100"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="103"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B112">
-    <cfRule type="duplicateValues" dxfId="97" priority="99"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="102"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B113">
-    <cfRule type="duplicateValues" dxfId="96" priority="98"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="101"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B114">
-    <cfRule type="duplicateValues" dxfId="95" priority="97"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="100"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B115">
-    <cfRule type="duplicateValues" dxfId="94" priority="96"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="99"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B116">
-    <cfRule type="duplicateValues" dxfId="93" priority="95"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="98"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B117">
-    <cfRule type="duplicateValues" dxfId="92" priority="94"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="97"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B118">
-    <cfRule type="duplicateValues" dxfId="91" priority="93"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="96"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B119">
-    <cfRule type="duplicateValues" dxfId="90" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="95"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B120">
-    <cfRule type="duplicateValues" dxfId="89" priority="91"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="94"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B121">
-    <cfRule type="duplicateValues" dxfId="88" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="93"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B122">
-    <cfRule type="duplicateValues" dxfId="87" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="92"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B126">
-    <cfRule type="duplicateValues" dxfId="86" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="91"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B127">
-    <cfRule type="duplicateValues" dxfId="85" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="90"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B128">
-    <cfRule type="duplicateValues" dxfId="84" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="89"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B129">
-    <cfRule type="duplicateValues" dxfId="83" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="88"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B130">
-    <cfRule type="duplicateValues" dxfId="82" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="87"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B131">
-    <cfRule type="duplicateValues" dxfId="81" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="86"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B132">
-    <cfRule type="duplicateValues" dxfId="80" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="85"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B133">
-    <cfRule type="duplicateValues" dxfId="79" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="84"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B136">
-    <cfRule type="duplicateValues" dxfId="78" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="83"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B137">
-    <cfRule type="duplicateValues" dxfId="77" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="82"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B138">
-    <cfRule type="duplicateValues" dxfId="76" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="81"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B139">
-    <cfRule type="duplicateValues" dxfId="75" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="80"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B140">
-    <cfRule type="duplicateValues" dxfId="74" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="79"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B141">
-    <cfRule type="duplicateValues" dxfId="73" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="78"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B142">
-    <cfRule type="duplicateValues" dxfId="72" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="77"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B143">
-    <cfRule type="duplicateValues" dxfId="71" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="76"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B144">
-    <cfRule type="duplicateValues" dxfId="70" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="75"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B145">
-    <cfRule type="duplicateValues" dxfId="69" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="74"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B147">
-    <cfRule type="duplicateValues" dxfId="68" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="73"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B148">
-    <cfRule type="duplicateValues" dxfId="67" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="72"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B149">
-    <cfRule type="duplicateValues" dxfId="66" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B150">
-    <cfRule type="duplicateValues" dxfId="65" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B151">
-    <cfRule type="duplicateValues" dxfId="64" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="69"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B152">
-    <cfRule type="duplicateValues" dxfId="63" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="68"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B153">
-    <cfRule type="duplicateValues" dxfId="62" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B154">
-    <cfRule type="duplicateValues" dxfId="61" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="66"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B155">
-    <cfRule type="duplicateValues" dxfId="60" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B156">
-    <cfRule type="duplicateValues" dxfId="59" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="64"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B157">
-    <cfRule type="duplicateValues" dxfId="58" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="63"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B171">
-    <cfRule type="duplicateValues" dxfId="57" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="62"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B172">
-    <cfRule type="duplicateValues" dxfId="56" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="61"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B174">
-    <cfRule type="duplicateValues" dxfId="55" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B177:B178">
-    <cfRule type="duplicateValues" dxfId="54" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="59"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B181">
-    <cfRule type="duplicateValues" dxfId="53" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="58"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B182">
-    <cfRule type="duplicateValues" dxfId="52" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B183">
-    <cfRule type="duplicateValues" dxfId="51" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B184">
-    <cfRule type="duplicateValues" dxfId="50" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B185">
-    <cfRule type="duplicateValues" dxfId="49" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B186">
-    <cfRule type="duplicateValues" dxfId="48" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B188">
-    <cfRule type="duplicateValues" dxfId="47" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B189">
-    <cfRule type="duplicateValues" dxfId="46" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B190">
-    <cfRule type="duplicateValues" dxfId="45" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B191">
-    <cfRule type="duplicateValues" dxfId="44" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B192">
-    <cfRule type="duplicateValues" dxfId="43" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B193">
-    <cfRule type="duplicateValues" dxfId="42" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B195">
-    <cfRule type="duplicateValues" dxfId="41" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B196">
-    <cfRule type="duplicateValues" dxfId="40" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B197">
-    <cfRule type="duplicateValues" dxfId="39" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B198">
-    <cfRule type="duplicateValues" dxfId="38" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B199">
-    <cfRule type="duplicateValues" dxfId="37" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B200">
-    <cfRule type="duplicateValues" dxfId="36" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B201">
-    <cfRule type="duplicateValues" dxfId="35" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B202">
-    <cfRule type="duplicateValues" dxfId="34" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B203">
-    <cfRule type="duplicateValues" dxfId="33" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B204">
-    <cfRule type="duplicateValues" dxfId="32" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B205">
-    <cfRule type="duplicateValues" dxfId="31" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B206">
-    <cfRule type="duplicateValues" dxfId="30" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B207">
-    <cfRule type="duplicateValues" dxfId="29" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B215">
-    <cfRule type="duplicateValues" dxfId="28" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B218">
-    <cfRule type="duplicateValues" dxfId="27" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B220">
-    <cfRule type="duplicateValues" dxfId="26" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B222">
-    <cfRule type="duplicateValues" dxfId="25" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B223">
-    <cfRule type="duplicateValues" dxfId="24" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B224">
-    <cfRule type="duplicateValues" dxfId="23" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B225">
-    <cfRule type="duplicateValues" dxfId="22" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B227">
-    <cfRule type="duplicateValues" dxfId="21" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B229">
-    <cfRule type="duplicateValues" dxfId="20" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B230">
-    <cfRule type="duplicateValues" dxfId="19" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B232">
-    <cfRule type="duplicateValues" dxfId="18" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B233">
-    <cfRule type="duplicateValues" dxfId="17" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B234">
-    <cfRule type="duplicateValues" dxfId="16" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B235">
-    <cfRule type="duplicateValues" dxfId="15" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B236">
-    <cfRule type="duplicateValues" dxfId="14" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B237">
-    <cfRule type="duplicateValues" dxfId="13" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B239">
-    <cfRule type="duplicateValues" dxfId="12" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B240">
-    <cfRule type="duplicateValues" dxfId="11" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B241">
-    <cfRule type="duplicateValues" dxfId="10" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B242">
-    <cfRule type="duplicateValues" dxfId="9" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B243">
-    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B250">
-    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B251">
-    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B253">
-    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B255">
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B258:B259">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B260">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B265:B267 B269">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B268">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B270">
+    <cfRule type="duplicateValues" dxfId="8" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B271">
+    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B273">
+    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -52165,11 +53163,11 @@
       </c>
       <c r="B1" s="15">
         <f>COUNTA(sum!A:A) -1</f>
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="C1" s="22">
         <f>COUNTIF(sum!I:I, "completed")/(B1-COUNTIF(sum!I:I, "abandoned")-COUNTIF(sum!I:I, "late app"))</f>
-        <v>0.99593495934959353</v>
+        <v>0.94230769230769229</v>
       </c>
       <c r="D1" s="21">
         <f>COUNTIF(sum!I:I, "completed")</f>
@@ -52195,11 +53193,11 @@
       </c>
       <c r="B3" s="16">
         <f>COUNTA(sum!K:K) -1</f>
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C3" s="10">
         <f>COUNTIFS(sum!I:I,"completed", sum!K:K, "&lt;&gt;") / B3</f>
-        <v>0.98245614035087714</v>
+        <v>0.98305084745762716</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="26" x14ac:dyDescent="0.6">
@@ -52208,7 +53206,7 @@
       </c>
       <c r="B5" s="15">
         <f>COUNTA(sum!J:J) -1</f>
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="C5" s="14">
         <f>B5/B1</f>
@@ -52221,11 +53219,11 @@
       </c>
       <c r="B6" s="16">
         <f>COUNTIFS(sum!J:J,"no news")</f>
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="C6" s="10">
         <f>B6/$B$5</f>
-        <v>0.96442687747035571</v>
+        <v>0.9550561797752809</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
@@ -52234,11 +53232,11 @@
       </c>
       <c r="B7" s="16">
         <f>COUNTIFS(sum!J:J,"rejected")</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C7" s="10">
         <f t="shared" ref="C7:C10" si="0">B7/$B$5</f>
-        <v>3.1620553359683792E-2</v>
+        <v>4.1198501872659173E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">
@@ -52251,7 +53249,7 @@
       </c>
       <c r="C8" s="10">
         <f t="shared" si="0"/>
-        <v>3.952569169960474E-3</v>
+        <v>3.7453183520599251E-3</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">

--- a/EconJM_status.xlsx
+++ b/EconJM_status.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\javie\Dropbox\Work\Job Search\2025 EconJM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE209D34-6373-4EA0-B5DA-E4851DEED772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2472ACC8-6AF5-40ED-BCEE-1A327BB2778B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" activeTab="1" xr2:uid="{6FE48536-7E5C-BF4C-9490-2A6392576298}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" xr2:uid="{6FE48536-7E5C-BF4C-9490-2A6392576298}"/>
   </bookViews>
   <sheets>
     <sheet name="sum" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="stats" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sum!$A$1:$V$248</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sum!$A$1:$V$267</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +45,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="103">
+  <futureMetadata name="XLRICHVALUE" count="104">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -767,8 +767,15 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="3219"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="103">
+  <valueMetadata count="104">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -1078,12 +1085,15 @@
     <bk>
       <rc t="1" v="102"/>
     </bk>
+    <bk>
+      <rc t="1" v="103"/>
+    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2675" uniqueCount="853">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2767" uniqueCount="872">
   <si>
     <t>add_id</t>
   </si>
@@ -3548,12 +3558,6 @@
     <t>HEC Paris</t>
   </si>
   <si>
-    <t>monash_post_2</t>
-  </si>
-  <si>
-    <t>Ricardo Dahis, the Primary Investigator (PI)</t>
-  </si>
-  <si>
     <t>virginia_common</t>
   </si>
   <si>
@@ -3626,9 +3630,6 @@
     <t>Florida International University</t>
   </si>
   <si>
-    <t>https://pslinks.fiu.edu/psc/jobs/CUSTOMER/HRMS/c/HRS_HRAM_FL.HRS_CG_SEARCH_FL.GBL?Page=HRS_APP_SCHJOB_FL&amp;Action=U</t>
-  </si>
-  <si>
     <t>Job Opening ID 536413</t>
   </si>
   <si>
@@ -3678,6 +3679,72 @@
   </si>
   <si>
     <t>added a few more stragelers</t>
+  </si>
+  <si>
+    <t>sloan</t>
+  </si>
+  <si>
+    <t>https://sloan.org/about/careers</t>
+  </si>
+  <si>
+    <t>Alfred P. Sloan Foundation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cover letter and resume/CV via email to HR@sloan.org with “LAST NAME – Program Associate, Economics” </t>
+  </si>
+  <si>
+    <t>urbana_champ_post</t>
+  </si>
+  <si>
+    <t>https://illinois.csod.com/ux/ats/careersite/1/home/requisition/15669?c=illinois</t>
+  </si>
+  <si>
+    <t>st_andrews</t>
+  </si>
+  <si>
+    <t>https://www.vacancies.st-andrews.ac.uk/Vacancies/W/4445/0/461020/889/senior-lecturer-or-reader-in-economics-microeconomics-ac2400</t>
+  </si>
+  <si>
+    <t>University of St Andrews</t>
+  </si>
+  <si>
+    <t>Professor Conny Wollbrant, Head of Department (conny.wollbrant@st-andrews.ac.uk) or Professor Mark Brewer, Dean of the Business School (BSchoolDean@st-andrews.ac.uk).</t>
+  </si>
+  <si>
+    <t>namur</t>
+  </si>
+  <si>
+    <t>University of Namur</t>
+  </si>
+  <si>
+    <t>app form (https://www.unamur.be/en/university/work/forms)</t>
+  </si>
+  <si>
+    <t>https://jobs.unamur.be/emploi.2025-12-02.1636013715</t>
+  </si>
+  <si>
+    <t>coppen_post2</t>
+  </si>
+  <si>
+    <t>https://candidate.hr-manager.net/ApplicationForm/SinglePageApplicationForm.aspx?cid=3010&amp;departmentId=19853&amp;ProjectId=152721&amp;MediaId=5105</t>
+  </si>
+  <si>
+    <t>zurich_dev</t>
+  </si>
+  <si>
+    <t>kyev</t>
+  </si>
+  <si>
+    <t>Kyiv School of Economics</t>
+  </si>
+  <si>
+    <t>san_andres</t>
+  </si>
+  <si>
+    <t>Universidad de San Andrés</t>
+  </si>
+  <si>
+    <t>https://careers.fiu.edu/</t>
   </si>
 </sst>
 </file>
@@ -3859,24 +3926,14 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="208">
+  <dxfs count="214">
     <dxf>
       <font>
-        <color rgb="FF006100"/>
+        <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3892,21 +3949,91 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
+        <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
+        <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6512,11 +6639,15 @@
     <address r:id="rId203"/>
     <moreImagesAddress r:id="rId204"/>
   </webImageSrd>
+  <webImageSrd>
+    <address r:id="rId205"/>
+    <moreImagesAddress r:id="rId206"/>
+  </webImageSrd>
 </webImagesSrd>
 </file>
 
 <file path=xl/richData/rdarray.xml><?xml version="1.0" encoding="utf-8"?>
-<arrayData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="192">
+<arrayData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="196">
   <a r="1">
     <v t="r">6</v>
   </a>
@@ -7964,11 +8095,51 @@
   <a r="1">
     <v t="r">3213</v>
   </a>
+  <a r="3">
+    <v t="r">3239</v>
+    <v t="r">3240</v>
+    <v t="r">3241</v>
+  </a>
+  <a r="1">
+    <v t="s">Ukrainian language</v>
+  </a>
+  <a r="27">
+    <v t="r">3225</v>
+    <v t="r">3253</v>
+    <v t="r">3254</v>
+    <v t="r">3255</v>
+    <v t="r">3256</v>
+    <v t="r">3257</v>
+    <v t="r">3258</v>
+    <v t="r">3259</v>
+    <v t="r">3260</v>
+    <v t="r">3261</v>
+    <v t="r">3262</v>
+    <v t="r">3263</v>
+    <v t="r">3264</v>
+    <v t="r">3265</v>
+    <v t="r">3266</v>
+    <v t="r">3267</v>
+    <v t="r">3268</v>
+    <v t="r">3269</v>
+    <v t="r">3270</v>
+    <v t="r">3271</v>
+    <v t="r">3272</v>
+    <v t="r">3273</v>
+    <v t="r">3274</v>
+    <v t="r">3275</v>
+    <v t="r">3276</v>
+    <v t="r">3277</v>
+    <v t="r">2725</v>
+  </a>
+  <a r="1">
+    <v t="s">Eastern European Time</v>
+  </a>
 </arrayData>
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="3219">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="3285">
   <rv s="0">
     <v>536870912</v>
     <v>New York City</v>
@@ -28762,6 +28933,423 @@
     <v>11</v>
     <v>Baltimore</v>
     <v>mdp/vdpid/5490064267963006978</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Ukraine</v>
+    <v>ad599477-9e6d-4a0e-bab5-0edf9db7115a</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="1">
+    <fb>0.71665314436637995</fb>
+    <v>19</v>
+  </rv>
+  <rv s="1">
+    <fb>603550</fb>
+    <v>8</v>
+  </rv>
+  <rv s="1">
+    <fb>297000</fb>
+    <v>8</v>
+  </rv>
+  <rv s="1">
+    <fb>8.6999999999999993</fb>
+    <v>18</v>
+  </rv>
+  <rv s="1">
+    <fb>380</fb>
+    <v>39</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Kyiv</v>
+    <v>79c78723-042d-4572-bc87-599fa1203134</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="1">
+    <fb>202249.71799999999</fb>
+    <v>8</v>
+  </rv>
+  <rv s="1">
+    <fb>281.658595641646</fb>
+    <v>40</v>
+  </rv>
+  <rv s="1">
+    <fb>7.8867174561113002E-2</fb>
+    <v>19</v>
+  </rv>
+  <rv s="1">
+    <fb>3418.56924154441</fb>
+    <v>8</v>
+  </rv>
+  <rv s="1">
+    <fb>1.3009999999999999</fb>
+    <v>18</v>
+  </rv>
+  <rv s="1">
+    <fb>0.167080388142165</fb>
+    <v>19</v>
+  </rv>
+  <rv s="1">
+    <fb>75.3495057807649</fb>
+    <v>41</v>
+  </rv>
+  <rv s="1">
+    <fb>0.83</fb>
+    <v>42</v>
+  </rv>
+  <rv s="1">
+    <fb>153781069118.14801</fb>
+    <v>17</v>
+  </rv>
+  <rv s="1">
+    <fb>0.99040940000000011</fb>
+    <v>19</v>
+  </rv>
+  <rv s="1">
+    <fb>0.82671180000000011</fb>
+    <v>19</v>
+  </rv>
+  <rv s="2">
+    <v>102</v>
+    <v>6</v>
+    <v>470</v>
+    <v>7</v>
+    <v>0</v>
+    <v>Image of Ukraine</v>
+  </rv>
+  <rv s="1">
+    <fb>7.5</fb>
+    <v>41</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Volodymyr Zelenskyy (President)</v>
+    <v>9bae3411-f7b7-35a0-00a8-57f94c361da9</v>
+    <v>en-US</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Denys Shmyhal (Prime minister)</v>
+    <v>be5cbc70-24e7-afe9-a0b1-49d91b73bd1a</v>
+    <v>en-US</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Ruslan Stefanchuk (Chairman)</v>
+    <v>f285b81d-480f-2679-16cf-096a649d7b5e</v>
+    <v>en-US</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="3">
+    <v>192</v>
+  </rv>
+  <rv s="4">
+    <v>https://www.bing.com/search?q=ukraine&amp;form=skydnc</v>
+    <v>Learn more on Bing</v>
+  </rv>
+  <rv s="1">
+    <fb>71.582682926829307</fb>
+    <v>41</v>
+  </rv>
+  <rv s="1">
+    <fb>4415440000</fb>
+    <v>17</v>
+  </rv>
+  <rv s="1">
+    <fb>0.84</fb>
+    <v>42</v>
+  </rv>
+  <rv s="3">
+    <v>193</v>
+  </rv>
+  <rv s="1">
+    <fb>0.47811215909999999</fb>
+    <v>19</v>
+  </rv>
+  <rv s="1">
+    <fb>2.9923000000000002</fb>
+    <v>18</v>
+  </rv>
+  <rv s="1">
+    <fb>38000000</fb>
+    <v>8</v>
+  </rv>
+  <rv s="1">
+    <fb>0.36099999999999999</fb>
+    <v>19</v>
+  </rv>
+  <rv s="1">
+    <fb>0.54151000976562502</fb>
+    <v>19</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Cherkasy Oblast</v>
+    <v>c9976b82-1310-ef4d-b0c9-a9afe6a1007f</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Chernihiv Oblast</v>
+    <v>4d3c108d-9f83-97bb-6c45-e5206908c9ba</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Chernivtsi Oblast</v>
+    <v>2b816ee4-0e8d-8ada-257c-6b9b23a72ad0</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Dnipropetrovsk Oblast</v>
+    <v>83b98499-16b8-bb03-d593-dd4bdf6eca84</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Donetsk Oblast</v>
+    <v>66af6664-7bd4-318e-e6c4-a5eba1b797fa</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Ivano-Frankivsk Oblast</v>
+    <v>5ab8bbed-4d8c-3a6e-ce49-db79ef72183f</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Kharkiv Oblast</v>
+    <v>80a0fd15-8a6f-05e0-ef8e-3ac5b137b76c</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Kherson Oblast</v>
+    <v>3d03caa9-910c-b257-2449-cb94ef57e497</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Khmelnytskyi Oblast</v>
+    <v>d8d2d1e1-25b5-cc8e-95a9-dd2af8f5b7a7</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Kyiv Oblast</v>
+    <v>4c971681-9dca-2885-9bc5-18f1d3b975b1</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Kirovohrad Oblast</v>
+    <v>ef8d4608-76c2-a832-264e-4cf51a0c5dbd</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Luhansk Oblast</v>
+    <v>cccfd56b-f7a9-dd2a-d268-68084adf28b4</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Lviv Oblast</v>
+    <v>aa5637b1-7fe1-a3c0-42df-6616eb84675a</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Mykolaiv Oblast</v>
+    <v>11f87280-610e-7272-da94-5f8890fcf23d</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Odesa Oblast</v>
+    <v>ab1bf172-10d2-6650-704b-07f524561e0c</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Poltava Oblast</v>
+    <v>e5ca22a5-cbe2-e9f8-df2a-c271030dccc7</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Rivne Oblast</v>
+    <v>d6cdb68d-5af6-afd9-b456-affff06b0df7</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Sumy Oblast</v>
+    <v>f7532844-70f6-fa1d-38eb-23fd0dbcb818</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Ternopil Oblast</v>
+    <v>8546d368-622f-6499-3510-030c076e5f17</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Vinnytsia Oblast</v>
+    <v>f740bcec-499b-0dee-db2b-31a5e212bb43</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Volyn Oblast</v>
+    <v>0e1b7fc3-81cf-e44d-b558-4f6a739d4ab5</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Zakarpattia Oblast</v>
+    <v>2b40bf9f-f59e-2eda-4e2c-ab42a853d304</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Zaporizhzhia Oblast</v>
+    <v>cfdae36e-e003-7dea-83b3-d9f416b99469</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Zhytomyr Oblast</v>
+    <v>8a86953e-fa05-4b29-ba68-763eb4012703</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Autonomous Republic of Crimea</v>
+    <v>79c3dba3-7806-419d-9763-6a5bc8e8e810</v>
+    <v>en-US</v>
+    <v>Map</v>
+  </rv>
+  <rv s="3">
+    <v>194</v>
+  </rv>
+  <rv s="1">
+    <fb>0.201408893342575</fb>
+    <v>19</v>
+  </rv>
+  <rv s="3">
+    <v>195</v>
+  </rv>
+  <rv s="1">
+    <fb>0.45200000000000001</fb>
+    <v>19</v>
+  </rv>
+  <rv s="1">
+    <fb>8.8819999694824195E-2</fb>
+    <v>43</v>
+  </rv>
+  <rv s="1">
+    <fb>30835699</fb>
+    <v>8</v>
+  </rv>
+  <rv s="7">
+    <v>#VALUE!</v>
+    <v>en-US</v>
+    <v>ad599477-9e6d-4a0e-bab5-0edf9db7115a</v>
+    <v>536870912</v>
+    <v>1</v>
+    <v>473</v>
+    <v>37</v>
+    <v>Ukraine</v>
+    <v>4</v>
+    <v>5</v>
+    <v>Map</v>
+    <v>6</v>
+    <v>474</v>
+    <v>UA</v>
+    <v>3220</v>
+    <v>3221</v>
+    <v>3222</v>
+    <v>3223</v>
+    <v>3224</v>
+    <v>3225</v>
+    <v>3226</v>
+    <v>3227</v>
+    <v>3228</v>
+    <v>UAH</v>
+    <v>Ukraine is a country in Eastern Europe. It is the second-largest country in Europe after Russia, which borders it to the east and northeast. Ukraine also borders Belarus to the north; Poland and Slovakia to the west; Hungary, Romania and Moldova ...</v>
+    <v>3229</v>
+    <v>3230</v>
+    <v>3231</v>
+    <v>3232</v>
+    <v>3233</v>
+    <v>3234</v>
+    <v>3235</v>
+    <v>3236</v>
+    <v>3237</v>
+    <v>3238</v>
+    <v>3225</v>
+    <v>3242</v>
+    <v>3243</v>
+    <v>3244</v>
+    <v>3245</v>
+    <v>74</v>
+    <v>3246</v>
+    <v>Ukraine</v>
+    <v>National anthem of Ukraine</v>
+    <v>3247</v>
+    <v>Україна</v>
+    <v>3248</v>
+    <v>3249</v>
+    <v>3250</v>
+    <v>786</v>
+    <v>3192</v>
+    <v>3251</v>
+    <v>175</v>
+    <v>708</v>
+    <v>178</v>
+    <v>2589</v>
+    <v>3252</v>
+    <v>3278</v>
+    <v>3279</v>
+    <v>3280</v>
+    <v>3281</v>
+    <v>3282</v>
+    <v>Ukraine</v>
+    <v>3283</v>
+    <v>mdp/vdpid/241</v>
   </rv>
 </rvData>
 </file>
@@ -30470,7 +31058,7 @@
       <v t="s">Description</v>
     </a>
   </spbArrays>
-  <spbData count="469">
+  <spbData count="475">
     <spb s="0">
       <v xml:space="preserve">Wikipedia	</v>
       <v xml:space="preserve">CC BY-SA 3.0	</v>
@@ -36335,6 +36923,113 @@
       <v>467</v>
       <v>467</v>
     </spb>
+    <spb s="0">
+      <v xml:space="preserve">Wikipedia	Cia	Youtube	</v>
+      <v xml:space="preserve">CC-BY-SA			</v>
+      <v xml:space="preserve">http://en.wikipedia.org/wiki/Ukraine	https://www.cia.gov/library/publications/the-world-factbook/geos/up.html?Transportation	https://www.youtube.com/channel/UC3ZSveaqIraw9BASEyDLYXg	</v>
+      <v xml:space="preserve">http://creativecommons.org/licenses/by-sa/3.0/			</v>
+    </spb>
+    <spb s="0">
+      <v xml:space="preserve">Wikipedia	</v>
+      <v xml:space="preserve">CC BY-SA 3.0	</v>
+      <v xml:space="preserve">https://en.wikipedia.org/wiki/Ukraine	</v>
+      <v xml:space="preserve">https://creativecommons.org/licenses/by-sa/3.0	</v>
+    </spb>
+    <spb s="0">
+      <v xml:space="preserve">Wikipedia	</v>
+      <v xml:space="preserve">CC-BY-SA	</v>
+      <v xml:space="preserve">http://en.wikipedia.org/wiki/Ukraine	</v>
+      <v xml:space="preserve">http://creativecommons.org/licenses/by-sa/3.0/	</v>
+    </spb>
+    <spb s="0">
+      <v xml:space="preserve">Cia	</v>
+      <v xml:space="preserve">	</v>
+      <v xml:space="preserve">https://www.cia.gov/library/publications/the-world-factbook/geos/up.html?Transportation	</v>
+      <v xml:space="preserve">	</v>
+    </spb>
+    <spb s="17">
+      <v>21</v>
+      <v>469</v>
+      <v>470</v>
+      <v>470</v>
+      <v>24</v>
+      <v>470</v>
+      <v>470</v>
+      <v>470</v>
+      <v>471</v>
+      <v>470</v>
+      <v>470</v>
+      <v>471</v>
+      <v>470</v>
+      <v>470</v>
+      <v>472</v>
+      <v>26</v>
+      <v>469</v>
+      <v>472</v>
+      <v>27</v>
+      <v>470</v>
+      <v>472</v>
+      <v>28</v>
+      <v>29</v>
+      <v>30</v>
+      <v>472</v>
+      <v>472</v>
+      <v>470</v>
+      <v>472</v>
+      <v>31</v>
+      <v>32</v>
+      <v>33</v>
+      <v>34</v>
+      <v>472</v>
+      <v>469</v>
+      <v>472</v>
+      <v>472</v>
+      <v>472</v>
+      <v>472</v>
+      <v>472</v>
+      <v>472</v>
+      <v>472</v>
+      <v>472</v>
+      <v>472</v>
+      <v>472</v>
+      <v>35</v>
+    </spb>
+    <spb s="12">
+      <v>2019</v>
+      <v>2019</v>
+      <v>square km</v>
+      <v>per thousand (2018)</v>
+      <v>2022</v>
+      <v>2019</v>
+      <v>2018</v>
+      <v>per liter (2016)</v>
+      <v>2019</v>
+      <v>years (2018)</v>
+      <v>2018</v>
+      <v>per thousand (2018)</v>
+      <v>2019</v>
+      <v>2017</v>
+      <v>2016</v>
+      <v>2019</v>
+      <v>2016</v>
+      <v>2014</v>
+      <v>kilotons per year (2016)</v>
+      <v>deaths per 100,000 (2017)</v>
+      <v>kWh (2014)</v>
+      <v>2014</v>
+      <v>2018</v>
+      <v>2018</v>
+      <v>2018</v>
+      <v>2018</v>
+      <v>2018</v>
+      <v>2018</v>
+      <v>2015</v>
+      <v>2018</v>
+      <v>2018</v>
+      <v>2014</v>
+      <v>2014</v>
+      <v>2019</v>
+    </spb>
   </spbData>
 </supportingPropertyBags>
 </file>
@@ -37305,7 +38000,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7772053-9363-CA4A-A53F-040B7C700753}">
-  <dimension ref="A1:V268"/>
+  <dimension ref="A1:V275"/>
   <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="19.6640625" customWidth="1"/>
@@ -39646,7 +40341,7 @@
         <v>96</v>
       </c>
       <c r="J52" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="M52" s="2" t="s">
         <v>58</v>
@@ -39817,7 +40512,7 @@
         <v>96</v>
       </c>
       <c r="J56" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K56" t="s">
         <v>309</v>
@@ -40489,7 +41184,7 @@
         <v>96</v>
       </c>
       <c r="J71" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="K71" t="s">
         <v>309</v>
@@ -44774,7 +45469,7 @@
         <v>96</v>
       </c>
       <c r="J164" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="M164" t="s">
         <v>558</v>
@@ -45833,7 +46528,7 @@
         <v>96</v>
       </c>
       <c r="J186" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="M186" t="s">
         <v>249</v>
@@ -47262,7 +47957,7 @@
         <v>96</v>
       </c>
       <c r="J219" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M219" t="s">
         <v>737</v>
@@ -47972,7 +48667,7 @@
         <v>96</v>
       </c>
       <c r="J235" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="K235" t="s">
         <v>309</v>
@@ -48444,33 +49139,27 @@
     </row>
     <row r="246" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A246" t="s">
-        <v>784</v>
+        <v>864</v>
       </c>
       <c r="D246" s="1">
-        <v>46006</v>
+        <v>45996</v>
       </c>
       <c r="E246" t="s">
-        <v>40</v>
-      </c>
-      <c r="F246" t="s">
-        <v>785</v>
+        <v>15</v>
+      </c>
+      <c r="F246" s="2" t="s">
+        <v>865</v>
       </c>
       <c r="I246" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J246" t="s">
         <v>402</v>
       </c>
-      <c r="K246" t="s">
-        <v>244</v>
-      </c>
-      <c r="L246" s="1">
-        <v>46027</v>
-      </c>
       <c r="M246" t="s">
-        <v>786</v>
-      </c>
-      <c r="N246" t="e" vm="35">
+        <v>720</v>
+      </c>
+      <c r="N246" t="e" vm="68">
         <v>#VALUE!</v>
       </c>
       <c r="O246" t="s">
@@ -48480,7 +49169,7 @@
         <v>776</v>
       </c>
       <c r="R246" s="1">
-        <v>46026</v>
+        <v>46005</v>
       </c>
       <c r="T246">
         <v>1</v>
@@ -48494,27 +49183,24 @@
     </row>
     <row r="247" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A247" t="s">
-        <v>841</v>
+        <v>866</v>
       </c>
       <c r="D247" s="1">
-        <v>46006</v>
+        <v>45996</v>
       </c>
       <c r="E247" t="s">
-        <v>844</v>
-      </c>
-      <c r="H247" t="s">
-        <v>842</v>
+        <v>15</v>
       </c>
       <c r="I247" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J247" t="s">
         <v>402</v>
       </c>
       <c r="M247" t="s">
-        <v>843</v>
-      </c>
-      <c r="N247" t="e" vm="46">
+        <v>397</v>
+      </c>
+      <c r="N247" t="e" vm="47">
         <v>#VALUE!</v>
       </c>
       <c r="O247" t="s">
@@ -48524,7 +49210,7 @@
         <v>776</v>
       </c>
       <c r="R247" s="1">
-        <v>46022</v>
+        <v>46001</v>
       </c>
       <c r="T247">
         <v>1</v>
@@ -48538,27 +49224,33 @@
     </row>
     <row r="248" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A248" t="s">
-        <v>662</v>
+        <v>784</v>
       </c>
       <c r="D248" s="1">
-        <v>46011</v>
+        <v>46006</v>
       </c>
       <c r="E248" t="s">
-        <v>15</v>
-      </c>
-      <c r="H248" t="s">
-        <v>664</v>
+        <v>40</v>
+      </c>
+      <c r="F248" t="s">
+        <v>785</v>
       </c>
       <c r="I248" t="s">
-        <v>96</v>
+        <v>23</v>
       </c>
       <c r="J248" t="s">
         <v>402</v>
       </c>
+      <c r="K248" t="s">
+        <v>244</v>
+      </c>
+      <c r="L248" s="1">
+        <v>46027</v>
+      </c>
       <c r="M248" t="s">
-        <v>663</v>
-      </c>
-      <c r="N248" t="e" vm="45">
+        <v>786</v>
+      </c>
+      <c r="N248" t="e" vm="35">
         <v>#VALUE!</v>
       </c>
       <c r="O248" t="s">
@@ -48568,7 +49260,7 @@
         <v>776</v>
       </c>
       <c r="R248" s="1">
-        <v>46037</v>
+        <v>46026</v>
       </c>
       <c r="T248">
         <v>1</v>
@@ -48582,19 +49274,16 @@
     </row>
     <row r="249" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A249" t="s">
-        <v>722</v>
-      </c>
-      <c r="C249" t="s">
-        <v>723</v>
+        <v>838</v>
       </c>
       <c r="D249" s="1">
-        <v>46016</v>
+        <v>46006</v>
       </c>
       <c r="E249" t="s">
-        <v>15</v>
-      </c>
-      <c r="F249" t="s">
-        <v>721</v>
+        <v>841</v>
+      </c>
+      <c r="H249" t="s">
+        <v>839</v>
       </c>
       <c r="I249" t="s">
         <v>96</v>
@@ -48603,9 +49292,9 @@
         <v>402</v>
       </c>
       <c r="M249" t="s">
-        <v>720</v>
-      </c>
-      <c r="N249" t="e" vm="68">
+        <v>840</v>
+      </c>
+      <c r="N249" t="e" vm="46">
         <v>#VALUE!</v>
       </c>
       <c r="O249" t="s">
@@ -48615,7 +49304,7 @@
         <v>776</v>
       </c>
       <c r="R249" s="1">
-        <v>45992</v>
+        <v>46022</v>
       </c>
       <c r="T249">
         <v>1</v>
@@ -48628,21 +49317,17 @@
       </c>
     </row>
     <row r="250" spans="1:22" x14ac:dyDescent="0.4">
-      <c r="A250" s="4" t="s">
-        <v>719</v>
-      </c>
-      <c r="B250" s="19"/>
-      <c r="C250" t="s">
-        <v>783</v>
+      <c r="A250" t="s">
+        <v>662</v>
       </c>
       <c r="D250" s="1">
-        <v>46016</v>
+        <v>46011</v>
       </c>
       <c r="E250" t="s">
         <v>15</v>
       </c>
-      <c r="G250">
-        <v>3</v>
+      <c r="H250" t="s">
+        <v>664</v>
       </c>
       <c r="I250" t="s">
         <v>96</v>
@@ -48650,26 +49335,20 @@
       <c r="J250" t="s">
         <v>402</v>
       </c>
-      <c r="K250" t="s">
-        <v>309</v>
-      </c>
-      <c r="L250" s="1">
-        <v>45992</v>
-      </c>
-      <c r="M250" s="2" t="s">
-        <v>718</v>
+      <c r="M250" t="s">
+        <v>663</v>
       </c>
       <c r="N250" t="e" vm="45">
         <v>#VALUE!</v>
       </c>
       <c r="O250" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="Q250" t="s">
         <v>776</v>
       </c>
       <c r="R250" s="1">
-        <v>45996</v>
+        <v>46037</v>
       </c>
       <c r="T250">
         <v>1</v>
@@ -48683,7 +49362,10 @@
     </row>
     <row r="251" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A251" t="s">
-        <v>787</v>
+        <v>722</v>
+      </c>
+      <c r="C251" t="s">
+        <v>723</v>
       </c>
       <c r="D251" s="1">
         <v>46016</v>
@@ -48691,6 +49373,9 @@
       <c r="E251" t="s">
         <v>15</v>
       </c>
+      <c r="F251" t="s">
+        <v>721</v>
+      </c>
       <c r="I251" t="s">
         <v>96</v>
       </c>
@@ -48698,10 +49383,13 @@
         <v>402</v>
       </c>
       <c r="M251" t="s">
-        <v>788</v>
-      </c>
-      <c r="N251" t="e" vm="29">
+        <v>720</v>
+      </c>
+      <c r="N251" t="e" vm="68">
         <v>#VALUE!</v>
+      </c>
+      <c r="O251" t="s">
+        <v>26</v>
       </c>
       <c r="Q251" t="s">
         <v>776</v>
@@ -48710,7 +49398,7 @@
         <v>45992</v>
       </c>
       <c r="T251">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U251">
         <v>0</v>
@@ -48720,8 +49408,12 @@
       </c>
     </row>
     <row r="252" spans="1:22" x14ac:dyDescent="0.4">
-      <c r="A252" t="s">
-        <v>790</v>
+      <c r="A252" s="4" t="s">
+        <v>719</v>
+      </c>
+      <c r="B252" s="19"/>
+      <c r="C252" t="s">
+        <v>783</v>
       </c>
       <c r="D252" s="1">
         <v>46016</v>
@@ -48729,16 +49421,25 @@
       <c r="E252" t="s">
         <v>15</v>
       </c>
+      <c r="G252">
+        <v>3</v>
+      </c>
       <c r="I252" t="s">
         <v>96</v>
       </c>
       <c r="J252" t="s">
         <v>402</v>
       </c>
-      <c r="M252" t="s">
-        <v>789</v>
-      </c>
-      <c r="N252" t="e" vm="75">
+      <c r="K252" t="s">
+        <v>309</v>
+      </c>
+      <c r="L252" s="1">
+        <v>45992</v>
+      </c>
+      <c r="M252" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="N252" t="e" vm="45">
         <v>#VALUE!</v>
       </c>
       <c r="O252" t="s">
@@ -48748,7 +49449,7 @@
         <v>776</v>
       </c>
       <c r="R252" s="1">
-        <v>45992</v>
+        <v>45996</v>
       </c>
       <c r="T252">
         <v>1</v>
@@ -48762,16 +49463,13 @@
     </row>
     <row r="253" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A253" t="s">
-        <v>528</v>
-      </c>
-      <c r="C253" t="s">
-        <v>178</v>
+        <v>787</v>
       </c>
       <c r="D253" s="1">
-        <v>46023</v>
+        <v>46016</v>
       </c>
       <c r="E253" t="s">
-        <v>529</v>
+        <v>15</v>
       </c>
       <c r="I253" t="s">
         <v>96</v>
@@ -48780,39 +49478,36 @@
         <v>402</v>
       </c>
       <c r="M253" t="s">
-        <v>530</v>
-      </c>
-      <c r="N253" t="e" vm="102">
+        <v>788</v>
+      </c>
+      <c r="N253" t="e" vm="29">
         <v>#VALUE!</v>
-      </c>
-      <c r="O253" t="s">
-        <v>19</v>
       </c>
       <c r="Q253" t="s">
         <v>776</v>
       </c>
       <c r="R253" s="1">
-        <v>46041</v>
+        <v>45992</v>
       </c>
       <c r="T253">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U253">
         <v>0</v>
       </c>
       <c r="V253">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="254" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A254" t="s">
-        <v>564</v>
+        <v>790</v>
       </c>
       <c r="D254" s="1">
-        <v>46023</v>
+        <v>46016</v>
       </c>
       <c r="E254" t="s">
-        <v>565</v>
+        <v>15</v>
       </c>
       <c r="I254" t="s">
         <v>96</v>
@@ -48821,19 +49516,19 @@
         <v>402</v>
       </c>
       <c r="M254" t="s">
-        <v>566</v>
-      </c>
-      <c r="N254" t="e" vm="103">
+        <v>789</v>
+      </c>
+      <c r="N254" t="e" vm="75">
         <v>#VALUE!</v>
       </c>
       <c r="O254" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="Q254" t="s">
         <v>776</v>
       </c>
       <c r="R254" s="1">
-        <v>45664</v>
+        <v>45992</v>
       </c>
       <c r="T254">
         <v>1</v>
@@ -48847,37 +49542,37 @@
     </row>
     <row r="255" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A255" t="s">
-        <v>804</v>
+        <v>528</v>
+      </c>
+      <c r="C255" t="s">
+        <v>178</v>
       </c>
       <c r="D255" s="1">
         <v>46023</v>
       </c>
-      <c r="E255" s="2" t="s">
-        <v>803</v>
-      </c>
-      <c r="F255" s="2" t="s">
-        <v>806</v>
+      <c r="E255" t="s">
+        <v>529</v>
       </c>
       <c r="I255" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J255" t="s">
         <v>402</v>
       </c>
       <c r="M255" t="s">
-        <v>805</v>
-      </c>
-      <c r="N255" t="e" vm="35">
+        <v>530</v>
+      </c>
+      <c r="N255" t="e" vm="102">
         <v>#VALUE!</v>
       </c>
       <c r="O255" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="Q255" t="s">
         <v>776</v>
       </c>
       <c r="R255" s="1">
-        <v>46038</v>
+        <v>46041</v>
       </c>
       <c r="T255">
         <v>1</v>
@@ -48886,39 +49581,39 @@
         <v>0</v>
       </c>
       <c r="V255">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="256" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A256" t="s">
-        <v>807</v>
+        <v>564</v>
       </c>
       <c r="D256" s="1">
         <v>46023</v>
       </c>
       <c r="E256" t="s">
-        <v>15</v>
+        <v>565</v>
       </c>
       <c r="I256" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J256" t="s">
         <v>402</v>
       </c>
       <c r="M256" t="s">
-        <v>808</v>
-      </c>
-      <c r="N256" t="e" vm="54">
+        <v>566</v>
+      </c>
+      <c r="N256" t="e" vm="103">
         <v>#VALUE!</v>
       </c>
       <c r="O256" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="Q256" t="s">
         <v>776</v>
       </c>
       <c r="R256" s="1">
-        <v>46052</v>
+        <v>45664</v>
       </c>
       <c r="T256">
         <v>1</v>
@@ -48932,27 +49627,27 @@
     </row>
     <row r="257" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A257" t="s">
-        <v>809</v>
+        <v>804</v>
       </c>
       <c r="D257" s="1">
         <v>46023</v>
       </c>
-      <c r="E257" t="s">
-        <v>15</v>
-      </c>
-      <c r="H257" t="s">
-        <v>810</v>
+      <c r="E257" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="F257" s="2" t="s">
+        <v>806</v>
       </c>
       <c r="I257" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J257" t="s">
         <v>402</v>
       </c>
       <c r="M257" t="s">
-        <v>123</v>
-      </c>
-      <c r="N257" t="e" vm="25">
+        <v>805</v>
+      </c>
+      <c r="N257" t="e" vm="35">
         <v>#VALUE!</v>
       </c>
       <c r="O257" t="s">
@@ -48962,7 +49657,7 @@
         <v>776</v>
       </c>
       <c r="R257" s="1">
-        <v>46052</v>
+        <v>46038</v>
       </c>
       <c r="T257">
         <v>1</v>
@@ -48976,33 +49671,24 @@
     </row>
     <row r="258" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A258" t="s">
-        <v>811</v>
-      </c>
-      <c r="C258" t="s">
-        <v>814</v>
+        <v>807</v>
       </c>
       <c r="D258" s="1">
         <v>46023</v>
       </c>
       <c r="E258" t="s">
-        <v>40</v>
-      </c>
-      <c r="F258" t="s">
-        <v>813</v>
-      </c>
-      <c r="H258" t="s">
-        <v>815</v>
+        <v>15</v>
       </c>
       <c r="I258" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J258" t="s">
         <v>402</v>
       </c>
       <c r="M258" t="s">
-        <v>812</v>
-      </c>
-      <c r="N258" t="e" vm="35">
+        <v>808</v>
+      </c>
+      <c r="N258" t="e" vm="54">
         <v>#VALUE!</v>
       </c>
       <c r="O258" t="s">
@@ -49012,7 +49698,7 @@
         <v>776</v>
       </c>
       <c r="R258" s="1">
-        <v>46037</v>
+        <v>46052</v>
       </c>
       <c r="T258">
         <v>1</v>
@@ -49026,7 +49712,10 @@
     </row>
     <row r="259" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A259" t="s">
-        <v>816</v>
+        <v>809</v>
+      </c>
+      <c r="C259" t="s">
+        <v>812</v>
       </c>
       <c r="D259" s="1">
         <v>46023</v>
@@ -49034,17 +49723,20 @@
       <c r="E259" t="s">
         <v>40</v>
       </c>
-      <c r="F259" s="2" t="s">
-        <v>817</v>
+      <c r="F259" t="s">
+        <v>811</v>
+      </c>
+      <c r="H259" t="s">
+        <v>813</v>
       </c>
       <c r="I259" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J259" t="s">
         <v>402</v>
       </c>
       <c r="M259" t="s">
-        <v>818</v>
+        <v>810</v>
       </c>
       <c r="N259" t="e" vm="35">
         <v>#VALUE!</v>
@@ -49056,7 +49748,7 @@
         <v>776</v>
       </c>
       <c r="R259" s="1">
-        <v>46066</v>
+        <v>46037</v>
       </c>
       <c r="T259">
         <v>1</v>
@@ -49070,7 +49762,7 @@
     </row>
     <row r="260" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A260" t="s">
-        <v>819</v>
+        <v>814</v>
       </c>
       <c r="D260" s="1">
         <v>46023</v>
@@ -49078,19 +49770,19 @@
       <c r="E260" t="s">
         <v>40</v>
       </c>
-      <c r="F260" t="s">
-        <v>820</v>
+      <c r="F260" s="2" t="s">
+        <v>815</v>
       </c>
       <c r="I260" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J260" t="s">
         <v>402</v>
       </c>
       <c r="M260" t="s">
-        <v>821</v>
-      </c>
-      <c r="N260" t="e" vm="6">
+        <v>816</v>
+      </c>
+      <c r="N260" t="e" vm="35">
         <v>#VALUE!</v>
       </c>
       <c r="O260" t="s">
@@ -49100,7 +49792,7 @@
         <v>776</v>
       </c>
       <c r="R260" s="1">
-        <v>46052</v>
+        <v>46066</v>
       </c>
       <c r="T260">
         <v>1</v>
@@ -49114,7 +49806,7 @@
     </row>
     <row r="261" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A261" t="s">
-        <v>823</v>
+        <v>817</v>
       </c>
       <c r="D261" s="1">
         <v>46023</v>
@@ -49122,19 +49814,19 @@
       <c r="E261" t="s">
         <v>40</v>
       </c>
-      <c r="F261" s="2" t="s">
-        <v>824</v>
+      <c r="F261" t="s">
+        <v>818</v>
       </c>
       <c r="I261" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J261" t="s">
         <v>402</v>
       </c>
       <c r="M261" t="s">
-        <v>822</v>
-      </c>
-      <c r="N261" t="e" vm="35">
+        <v>819</v>
+      </c>
+      <c r="N261" t="e" vm="6">
         <v>#VALUE!</v>
       </c>
       <c r="O261" t="s">
@@ -49144,7 +49836,7 @@
         <v>776</v>
       </c>
       <c r="R261" s="1">
-        <v>46113</v>
+        <v>46052</v>
       </c>
       <c r="T261">
         <v>1</v>
@@ -49158,10 +49850,7 @@
     </row>
     <row r="262" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A262" t="s">
-        <v>825</v>
-      </c>
-      <c r="C262" t="s">
-        <v>831</v>
+        <v>821</v>
       </c>
       <c r="D262" s="1">
         <v>46023</v>
@@ -49170,28 +49859,28 @@
         <v>40</v>
       </c>
       <c r="F262" s="2" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="I262" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J262" t="s">
         <v>402</v>
       </c>
       <c r="M262" t="s">
-        <v>827</v>
+        <v>820</v>
       </c>
       <c r="N262" t="e" vm="35">
         <v>#VALUE!</v>
       </c>
       <c r="O262" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="Q262" t="s">
         <v>776</v>
       </c>
       <c r="R262" s="1">
-        <v>46038</v>
+        <v>46113</v>
       </c>
       <c r="T262">
         <v>1</v>
@@ -49205,10 +49894,10 @@
     </row>
     <row r="263" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A263" t="s">
-        <v>828</v>
+        <v>823</v>
       </c>
       <c r="C263" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="D263" s="1">
         <v>46023</v>
@@ -49216,29 +49905,29 @@
       <c r="E263" t="s">
         <v>40</v>
       </c>
-      <c r="F263" t="s">
-        <v>832</v>
+      <c r="F263" s="2" t="s">
+        <v>824</v>
       </c>
       <c r="I263" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J263" t="s">
         <v>402</v>
       </c>
       <c r="M263" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="N263" t="e" vm="35">
         <v>#VALUE!</v>
       </c>
       <c r="O263" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="Q263" t="s">
         <v>776</v>
       </c>
       <c r="R263" s="1">
-        <v>46143</v>
+        <v>46038</v>
       </c>
       <c r="T263">
         <v>1</v>
@@ -49252,10 +49941,10 @@
     </row>
     <row r="264" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A264" t="s">
-        <v>833</v>
+        <v>826</v>
       </c>
       <c r="C264" t="s">
-        <v>836</v>
+        <v>828</v>
       </c>
       <c r="D264" s="1">
         <v>46023</v>
@@ -49263,17 +49952,17 @@
       <c r="E264" t="s">
         <v>40</v>
       </c>
-      <c r="F264" s="2" t="s">
-        <v>835</v>
+      <c r="F264" t="s">
+        <v>830</v>
       </c>
       <c r="I264" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J264" t="s">
         <v>402</v>
       </c>
       <c r="M264" t="s">
-        <v>834</v>
+        <v>827</v>
       </c>
       <c r="N264" t="e" vm="35">
         <v>#VALUE!</v>
@@ -49285,7 +49974,7 @@
         <v>776</v>
       </c>
       <c r="R264" s="1">
-        <v>46027</v>
+        <v>46143</v>
       </c>
       <c r="T264">
         <v>1</v>
@@ -49299,22 +49988,28 @@
     </row>
     <row r="265" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A265" t="s">
-        <v>838</v>
+        <v>831</v>
+      </c>
+      <c r="C265" t="s">
+        <v>833</v>
       </c>
       <c r="D265" s="1">
         <v>46023</v>
       </c>
       <c r="E265" t="s">
-        <v>839</v>
+        <v>40</v>
+      </c>
+      <c r="F265" s="2" t="s">
+        <v>871</v>
       </c>
       <c r="I265" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J265" t="s">
         <v>402</v>
       </c>
       <c r="M265" t="s">
-        <v>840</v>
+        <v>832</v>
       </c>
       <c r="N265" t="e" vm="35">
         <v>#VALUE!</v>
@@ -49325,6 +50020,9 @@
       <c r="Q265" t="s">
         <v>776</v>
       </c>
+      <c r="R265" s="1">
+        <v>46027</v>
+      </c>
       <c r="T265">
         <v>1</v>
       </c>
@@ -49337,13 +50035,13 @@
     </row>
     <row r="266" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A266" t="s">
-        <v>845</v>
+        <v>835</v>
       </c>
       <c r="D266" s="1">
         <v>46023</v>
       </c>
       <c r="E266" t="s">
-        <v>846</v>
+        <v>836</v>
       </c>
       <c r="I266" t="s">
         <v>23</v>
@@ -49352,9 +50050,9 @@
         <v>402</v>
       </c>
       <c r="M266" t="s">
-        <v>847</v>
-      </c>
-      <c r="N266" t="e" vm="84">
+        <v>837</v>
+      </c>
+      <c r="N266" t="e" vm="35">
         <v>#VALUE!</v>
       </c>
       <c r="O266" t="s">
@@ -49363,9 +50061,6 @@
       <c r="Q266" t="s">
         <v>776</v>
       </c>
-      <c r="R266" s="1">
-        <v>46037</v>
-      </c>
       <c r="T266">
         <v>1</v>
       </c>
@@ -49378,16 +50073,13 @@
     </row>
     <row r="267" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A267" t="s">
-        <v>848</v>
-      </c>
-      <c r="C267" t="s">
-        <v>851</v>
+        <v>842</v>
       </c>
       <c r="D267" s="1">
         <v>46023</v>
       </c>
       <c r="E267" t="s">
-        <v>850</v>
+        <v>843</v>
       </c>
       <c r="I267" t="s">
         <v>23</v>
@@ -49396,19 +50088,19 @@
         <v>402</v>
       </c>
       <c r="M267" t="s">
-        <v>849</v>
-      </c>
-      <c r="N267" t="e" vm="35">
+        <v>844</v>
+      </c>
+      <c r="N267" t="e" vm="84">
         <v>#VALUE!</v>
       </c>
       <c r="O267" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="Q267" t="s">
         <v>776</v>
       </c>
       <c r="R267" s="1">
-        <v>46033</v>
+        <v>46037</v>
       </c>
       <c r="T267">
         <v>1</v>
@@ -49422,34 +50114,40 @@
     </row>
     <row r="268" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A268" t="s">
-        <v>255</v>
+        <v>845</v>
+      </c>
+      <c r="C268" t="s">
+        <v>848</v>
+      </c>
+      <c r="D268" s="1">
+        <v>46023</v>
       </c>
       <c r="E268" t="s">
-        <v>15</v>
-      </c>
-      <c r="F268" s="2" t="s">
-        <v>257</v>
+        <v>847</v>
       </c>
       <c r="I268" t="s">
-        <v>96</v>
+        <v>23</v>
       </c>
       <c r="J268" t="s">
         <v>402</v>
       </c>
       <c r="M268" t="s">
-        <v>256</v>
+        <v>846</v>
       </c>
       <c r="N268" t="e" vm="35">
         <v>#VALUE!</v>
       </c>
       <c r="O268" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="Q268" t="s">
         <v>776</v>
       </c>
+      <c r="R268" s="1">
+        <v>46033</v>
+      </c>
       <c r="T268">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U268">
         <v>0</v>
@@ -49458,93 +50156,376 @@
         <v>0</v>
       </c>
     </row>
+    <row r="269" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A269" t="s">
+        <v>850</v>
+      </c>
+      <c r="C269" t="s">
+        <v>853</v>
+      </c>
+      <c r="D269" s="1">
+        <v>46023</v>
+      </c>
+      <c r="E269" t="s">
+        <v>40</v>
+      </c>
+      <c r="F269" t="s">
+        <v>851</v>
+      </c>
+      <c r="I269" t="s">
+        <v>23</v>
+      </c>
+      <c r="J269" t="s">
+        <v>402</v>
+      </c>
+      <c r="M269" t="s">
+        <v>852</v>
+      </c>
+      <c r="N269" t="e" vm="35">
+        <v>#VALUE!</v>
+      </c>
+      <c r="O269" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q269" t="s">
+        <v>776</v>
+      </c>
+      <c r="R269" s="1">
+        <v>46173</v>
+      </c>
+      <c r="T269">
+        <v>1</v>
+      </c>
+      <c r="U269">
+        <v>0</v>
+      </c>
+      <c r="V269">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A270" t="s">
+        <v>854</v>
+      </c>
+      <c r="D270" s="1">
+        <v>46023</v>
+      </c>
+      <c r="E270" t="s">
+        <v>40</v>
+      </c>
+      <c r="F270" t="s">
+        <v>855</v>
+      </c>
+      <c r="I270" t="s">
+        <v>23</v>
+      </c>
+      <c r="J270" t="s">
+        <v>402</v>
+      </c>
+      <c r="M270" t="s">
+        <v>493</v>
+      </c>
+      <c r="N270" t="e" vm="35">
+        <v>#VALUE!</v>
+      </c>
+      <c r="O270" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q270" t="s">
+        <v>776</v>
+      </c>
+      <c r="R270" s="1">
+        <v>46028</v>
+      </c>
+      <c r="T270">
+        <v>1</v>
+      </c>
+      <c r="U270">
+        <v>0</v>
+      </c>
+      <c r="V270">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A271" t="s">
+        <v>856</v>
+      </c>
+      <c r="D271" s="1">
+        <v>46023</v>
+      </c>
+      <c r="E271" t="s">
+        <v>15</v>
+      </c>
+      <c r="F271" s="2" t="s">
+        <v>857</v>
+      </c>
+      <c r="H271" t="s">
+        <v>859</v>
+      </c>
+      <c r="I271" t="s">
+        <v>23</v>
+      </c>
+      <c r="J271" t="s">
+        <v>402</v>
+      </c>
+      <c r="M271" t="s">
+        <v>858</v>
+      </c>
+      <c r="N271" t="e" vm="70">
+        <v>#VALUE!</v>
+      </c>
+      <c r="O271" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q271" t="s">
+        <v>776</v>
+      </c>
+      <c r="R271" s="1">
+        <v>46055</v>
+      </c>
+      <c r="T271">
+        <v>1</v>
+      </c>
+      <c r="U271">
+        <v>0</v>
+      </c>
+      <c r="V271">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A272" t="s">
+        <v>860</v>
+      </c>
+      <c r="C272" t="s">
+        <v>862</v>
+      </c>
+      <c r="D272" s="1">
+        <v>46023</v>
+      </c>
+      <c r="E272" t="s">
+        <v>15</v>
+      </c>
+      <c r="F272" s="2" t="s">
+        <v>863</v>
+      </c>
+      <c r="I272" t="s">
+        <v>23</v>
+      </c>
+      <c r="J272" t="s">
+        <v>402</v>
+      </c>
+      <c r="M272" t="s">
+        <v>861</v>
+      </c>
+      <c r="N272" t="e" vm="93">
+        <v>#VALUE!</v>
+      </c>
+      <c r="O272" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q272" t="s">
+        <v>776</v>
+      </c>
+      <c r="R272" s="1">
+        <v>46026</v>
+      </c>
+      <c r="T272">
+        <v>1</v>
+      </c>
+      <c r="U272">
+        <v>0</v>
+      </c>
+      <c r="V272">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A273" t="s">
+        <v>867</v>
+      </c>
+      <c r="D273" s="1">
+        <v>46023</v>
+      </c>
+      <c r="E273" t="s">
+        <v>15</v>
+      </c>
+      <c r="I273" t="s">
+        <v>23</v>
+      </c>
+      <c r="J273" t="s">
+        <v>402</v>
+      </c>
+      <c r="M273" t="s">
+        <v>868</v>
+      </c>
+      <c r="N273" t="e" vm="104">
+        <v>#VALUE!</v>
+      </c>
+      <c r="O273" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q273" t="s">
+        <v>776</v>
+      </c>
+      <c r="R273" s="1">
+        <v>46036</v>
+      </c>
+      <c r="T273">
+        <v>1</v>
+      </c>
+      <c r="U273">
+        <v>0</v>
+      </c>
+      <c r="V273">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A274" t="s">
+        <v>869</v>
+      </c>
+      <c r="D274" s="1">
+        <v>46023</v>
+      </c>
+      <c r="E274" t="s">
+        <v>15</v>
+      </c>
+      <c r="I274" t="s">
+        <v>23</v>
+      </c>
+      <c r="J274" t="s">
+        <v>402</v>
+      </c>
+      <c r="M274" t="s">
+        <v>870</v>
+      </c>
+      <c r="N274" t="e" vm="94">
+        <v>#VALUE!</v>
+      </c>
+      <c r="O274" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q274" t="s">
+        <v>776</v>
+      </c>
+      <c r="R274" s="1">
+        <v>46053</v>
+      </c>
+      <c r="T274">
+        <v>1</v>
+      </c>
+      <c r="U274">
+        <v>0</v>
+      </c>
+      <c r="V274">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A275" t="s">
+        <v>255</v>
+      </c>
+      <c r="E275" t="s">
+        <v>15</v>
+      </c>
+      <c r="F275" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="I275" t="s">
+        <v>96</v>
+      </c>
+      <c r="J275" t="s">
+        <v>402</v>
+      </c>
+      <c r="M275" t="s">
+        <v>256</v>
+      </c>
+      <c r="N275" t="e" vm="35">
+        <v>#VALUE!</v>
+      </c>
+      <c r="O275" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q275" t="s">
+        <v>776</v>
+      </c>
+      <c r="T275">
+        <v>0</v>
+      </c>
+      <c r="U275">
+        <v>0</v>
+      </c>
+      <c r="V275">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V248" xr:uid="{F7772053-9363-CA4A-A53F-040B7C700753}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V268">
-      <sortCondition ref="D1:D248"/>
+  <autoFilter ref="A1:V267" xr:uid="{F7772053-9363-CA4A-A53F-040B7C700753}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V275">
+      <sortCondition ref="D1:D267"/>
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="A1:B208 A210:B1048576">
-    <cfRule type="duplicateValues" dxfId="207" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="213" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:B22">
-    <cfRule type="duplicateValues" dxfId="206" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="212" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A61:B61">
-    <cfRule type="duplicateValues" dxfId="205" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="211" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="containsText" dxfId="204" priority="15" operator="containsText" text="closed">
+    <cfRule type="containsText" dxfId="210" priority="15" operator="containsText" text="closed">
       <formula>NOT(ISERROR(SEARCH("closed",I1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="203" priority="16" operator="containsText" text="abandoned">
+    <cfRule type="containsText" dxfId="209" priority="16" operator="containsText" text="abandoned">
       <formula>NOT(ISERROR(SEARCH("abandoned",I1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="202" priority="18" operator="containsText" text="late app">
+    <cfRule type="containsText" dxfId="208" priority="18" operator="containsText" text="late app">
       <formula>NOT(ISERROR(SEARCH("late app",I1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:L1048576 O78:O80 O83:O89 O92:O112 O115:O124 O126:O181 R136 R153 R159 R166 R173 R178 O183:O205 O208:O211 O213:O218 O220:O233 R225 O235:O237 O239:O248 M248 O250:O255 I1:J1 M266 N267">
-    <cfRule type="containsText" dxfId="201" priority="21" operator="containsText" text="completed">
+  <conditionalFormatting sqref="I2:L1048576 O78:O80 O83:O89 O92:O112 O115:O124 O126:O181 R136 R153 R159 R166 R173 R178 O183:O205 O208:O211 O213:O218 O220:O233 R225 O235:O237 O239:O248 I1:J1">
+    <cfRule type="containsText" dxfId="207" priority="21" operator="containsText" text="completed">
       <formula>NOT(ISERROR(SEARCH("completed",I1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:J1048576">
-    <cfRule type="containsText" dxfId="200" priority="10" operator="containsText" text="no news">
+    <cfRule type="containsText" dxfId="206" priority="10" operator="containsText" text="no news">
       <formula>NOT(ISERROR(SEARCH("no news",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="199" priority="11" operator="containsText" text="offer">
+    <cfRule type="containsText" dxfId="205" priority="11" operator="containsText" text="offer">
       <formula>NOT(ISERROR(SEARCH("offer",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="198" priority="12" operator="containsText" text="fly out">
+    <cfRule type="containsText" dxfId="204" priority="12" operator="containsText" text="fly out">
       <formula>NOT(ISERROR(SEARCH("fly out",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="197" priority="13" operator="containsText" text="interview">
+    <cfRule type="containsText" dxfId="203" priority="13" operator="containsText" text="interview">
       <formula>NOT(ISERROR(SEARCH("interview",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="196" priority="14" operator="containsText" text="rejected">
+    <cfRule type="containsText" dxfId="202" priority="14" operator="containsText" text="rejected">
       <formula>NOT(ISERROR(SEARCH("rejected",J1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K1:L1048576 O78:O80 O83:O89 O92:O112 O115:O124 O126:O181 R136 R153 R159 R166 R173 R178 O183:O205 O208:O211 O213:O218 O220:O233 R225 O235:O237 O239:O248 M248 O250:O255 M266 N267">
-    <cfRule type="containsText" dxfId="195" priority="19" operator="containsText" text="NO">
+  <conditionalFormatting sqref="K1:L1048576 O78:O80 O83:O89 O92:O112 O115:O124 O126:O181 R136 R153 R159 R166 R173 R178 O183:O205 O208:O211 O213:O218 O220:O233 R225 O235:O237 O239:O248">
+    <cfRule type="containsText" dxfId="201" priority="19" operator="containsText" text="NO">
       <formula>NOT(ISERROR(SEARCH("NO",K1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="194" priority="20" operator="containsText" text="YES">
+    <cfRule type="containsText" dxfId="200" priority="20" operator="containsText" text="YES">
       <formula>NOT(ISERROR(SEARCH("YES",K1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N256:O264 O265 N266:O266 O267:O268">
-    <cfRule type="containsText" dxfId="193" priority="7" operator="containsText" text="NO">
-      <formula>NOT(ISERROR(SEARCH("NO",N256)))</formula>
+  <conditionalFormatting sqref="O250:O267">
+    <cfRule type="containsText" dxfId="199" priority="1" operator="containsText" text="NO">
+      <formula>NOT(ISERROR(SEARCH("NO",O250)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="192" priority="8" operator="containsText" text="YES">
-      <formula>NOT(ISERROR(SEARCH("YES",N256)))</formula>
+    <cfRule type="containsText" dxfId="198" priority="2" operator="containsText" text="YES">
+      <formula>NOT(ISERROR(SEARCH("YES",O250)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="191" priority="9" operator="containsText" text="completed">
-      <formula>NOT(ISERROR(SEARCH("completed",N256)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N265">
-    <cfRule type="containsText" dxfId="5" priority="4" operator="containsText" text="NO">
-      <formula>NOT(ISERROR(SEARCH("NO",N265)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="YES">
-      <formula>NOT(ISERROR(SEARCH("YES",N265)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="6" operator="containsText" text="completed">
-      <formula>NOT(ISERROR(SEARCH("completed",N265)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N268">
-    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="NO">
-      <formula>NOT(ISERROR(SEARCH("NO",N268)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="YES">
-      <formula>NOT(ISERROR(SEARCH("YES",N268)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="completed">
-      <formula>NOT(ISERROR(SEARCH("completed",N268)))</formula>
+    <cfRule type="containsText" dxfId="197" priority="3" operator="containsText" text="completed">
+      <formula>NOT(ISERROR(SEARCH("completed",O250)))</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
@@ -49629,7 +50610,7 @@
     <hyperlink ref="M17" r:id="rId79" xr:uid="{9A9A6BC9-B330-7842-A78C-4DCC88F5E19F}"/>
     <hyperlink ref="M32" r:id="rId80" xr:uid="{928CABEF-4FA6-E646-8140-7B6E43F8FB96}"/>
     <hyperlink ref="F177" r:id="rId81" xr:uid="{82BF1574-A6C6-1641-9FFE-615861E401FD}"/>
-    <hyperlink ref="F268" r:id="rId82" xr:uid="{3562807E-7FDA-F046-BA03-5DDD43072DB7}"/>
+    <hyperlink ref="F275" r:id="rId82" xr:uid="{3562807E-7FDA-F046-BA03-5DDD43072DB7}"/>
     <hyperlink ref="H215" r:id="rId83" display="mailto:ivanpaya@ua.es" xr:uid="{DEFB77A5-E57F-714C-BAB9-56DE82BA0B2E}"/>
     <hyperlink ref="H138" r:id="rId84" display="mailto:ari.hyytinen@hanken.fi" xr:uid="{7777B12A-FD99-4A43-A14B-A15661B760DC}"/>
     <hyperlink ref="H115" r:id="rId85" display="mailto:peter.haan@fu-berlin.de" xr:uid="{3D1A69ED-8F06-1246-B586-201CB349DB62}"/>
@@ -49647,23 +50628,25 @@
     <hyperlink ref="H240" r:id="rId97" display="mailto:ondrej.krcal@econ.muni.cz" xr:uid="{EDDEB1E6-5767-4FFB-A0AE-57A909D04E81}"/>
     <hyperlink ref="M218" r:id="rId98" display="https://www.ovgu.de/unimagdeburg/en/" xr:uid="{BCB3935D-2B6D-4090-86F5-762D762ED0E3}"/>
     <hyperlink ref="E152" r:id="rId99" xr:uid="{550520C0-1E25-41CD-9AEE-9A3C4D7D328C}"/>
-    <hyperlink ref="M250" r:id="rId100" xr:uid="{F0DD6D71-3FFD-4EAB-A251-AAF2DA8EF53C}"/>
+    <hyperlink ref="M252" r:id="rId100" xr:uid="{F0DD6D71-3FFD-4EAB-A251-AAF2DA8EF53C}"/>
     <hyperlink ref="F243" r:id="rId101" xr:uid="{BDBBC2E2-C3C5-4526-A621-853D22D99CCF}"/>
-    <hyperlink ref="F255" r:id="rId102" display="mailto:comap@northwestern.edu" xr:uid="{4DD04925-4C98-401C-B09E-A61B83C23B4E}"/>
-    <hyperlink ref="E255" r:id="rId103" xr:uid="{491ECAF5-1DC5-4C3F-B1BE-621395157776}"/>
-    <hyperlink ref="F259" r:id="rId104" xr:uid="{B084E08B-44BE-4FA5-A345-8036292B3E22}"/>
-    <hyperlink ref="F261" r:id="rId105" xr:uid="{F59B1D31-814A-4100-8601-8879ABB1E739}"/>
-    <hyperlink ref="F262" r:id="rId106" xr:uid="{C4BD89A9-F3F0-4E10-BAC5-751787E6C1A9}"/>
-    <hyperlink ref="F264" r:id="rId107" xr:uid="{64E2681C-F146-4414-BBE6-9DC59E57C615}"/>
+    <hyperlink ref="F257" r:id="rId102" display="mailto:comap@northwestern.edu" xr:uid="{4DD04925-4C98-401C-B09E-A61B83C23B4E}"/>
+    <hyperlink ref="E257" r:id="rId103" xr:uid="{491ECAF5-1DC5-4C3F-B1BE-621395157776}"/>
+    <hyperlink ref="F260" r:id="rId104" xr:uid="{B084E08B-44BE-4FA5-A345-8036292B3E22}"/>
+    <hyperlink ref="F262" r:id="rId105" xr:uid="{F59B1D31-814A-4100-8601-8879ABB1E739}"/>
+    <hyperlink ref="F263" r:id="rId106" xr:uid="{C4BD89A9-F3F0-4E10-BAC5-751787E6C1A9}"/>
+    <hyperlink ref="F271" r:id="rId107" xr:uid="{A8AE6398-5E3B-44CD-895F-D20F2BEC5279}"/>
+    <hyperlink ref="F272" r:id="rId108" xr:uid="{34317180-A8EC-4C92-AB27-7AD534355822}"/>
+    <hyperlink ref="F246" r:id="rId109" xr:uid="{81F56FF4-6BEE-4876-B897-D914C7668775}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId108"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId110"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923E81FA-B875-3C4E-A189-1A21268FA086}">
-  <dimension ref="A1:C274"/>
+  <dimension ref="A1:C292"/>
   <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="32.83203125" customWidth="1"/>
@@ -52591,7 +53574,7 @@
         <v>45993</v>
       </c>
       <c r="C272" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.4">
@@ -52610,538 +53593,772 @@
         <v>45994</v>
       </c>
       <c r="C274" t="s">
-        <v>852</v>
+        <v>849</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A275" s="1">
+        <v>45995</v>
+      </c>
+      <c r="B275" t="s">
+        <v>735</v>
+      </c>
+      <c r="C275" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A276" s="1">
+        <v>45995</v>
+      </c>
+      <c r="B276" t="s">
+        <v>767</v>
+      </c>
+      <c r="C276" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A277" s="1">
+        <v>45998</v>
+      </c>
+      <c r="B277" t="s">
+        <v>250</v>
+      </c>
+      <c r="C277" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A278" s="1">
+        <v>45999</v>
+      </c>
+      <c r="B278" t="s">
+        <v>864</v>
+      </c>
+      <c r="C278" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A279" s="1">
+        <v>45999</v>
+      </c>
+      <c r="B279" t="s">
+        <v>472</v>
+      </c>
+      <c r="C279" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A280" s="1">
+        <v>45999</v>
+      </c>
+      <c r="B280" t="s">
+        <v>804</v>
+      </c>
+      <c r="C280" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A281" s="1">
+        <v>46000</v>
+      </c>
+      <c r="B281" t="s">
+        <v>807</v>
+      </c>
+      <c r="C281" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A282" s="1">
+        <v>46000</v>
+      </c>
+      <c r="B282" t="s">
+        <v>557</v>
+      </c>
+      <c r="C282" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A283" s="1">
+        <v>46000</v>
+      </c>
+      <c r="B283" t="s">
+        <v>54</v>
+      </c>
+      <c r="C283" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A284" s="1">
+        <v>46000</v>
+      </c>
+      <c r="B284" t="s">
+        <v>807</v>
+      </c>
+      <c r="C284" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A285" s="1">
+        <v>46000</v>
+      </c>
+      <c r="B285" t="s">
+        <v>809</v>
+      </c>
+      <c r="C285" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A286" s="1">
+        <v>46000</v>
+      </c>
+      <c r="B286" t="s">
+        <v>814</v>
+      </c>
+      <c r="C286" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A287" s="1">
+        <v>46000</v>
+      </c>
+      <c r="B287" t="s">
+        <v>817</v>
+      </c>
+      <c r="C287" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A288" s="1">
+        <v>46000</v>
+      </c>
+      <c r="B288" t="s">
+        <v>821</v>
+      </c>
+      <c r="C288" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A289" s="1">
+        <v>46001</v>
+      </c>
+      <c r="B289" t="s">
+        <v>314</v>
+      </c>
+      <c r="C289" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A290" s="1">
+        <v>46001</v>
+      </c>
+      <c r="B290" t="s">
+        <v>144</v>
+      </c>
+      <c r="C290" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A291" s="1">
+        <v>46001</v>
+      </c>
+      <c r="B291" t="s">
+        <v>823</v>
+      </c>
+      <c r="C291" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A292" s="1">
+        <v>46001</v>
+      </c>
+      <c r="B292" t="s">
+        <v>831</v>
+      </c>
+      <c r="C292" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5">
-    <cfRule type="duplicateValues" dxfId="190" priority="191"/>
-    <cfRule type="duplicateValues" dxfId="189" priority="192"/>
+    <cfRule type="duplicateValues" dxfId="196" priority="204"/>
+    <cfRule type="duplicateValues" dxfId="195" priority="205"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B10">
-    <cfRule type="duplicateValues" dxfId="188" priority="190"/>
-    <cfRule type="duplicateValues" dxfId="187" priority="189"/>
+    <cfRule type="duplicateValues" dxfId="194" priority="203"/>
+    <cfRule type="duplicateValues" dxfId="193" priority="202"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B11">
-    <cfRule type="duplicateValues" dxfId="186" priority="188"/>
-    <cfRule type="duplicateValues" dxfId="185" priority="187"/>
+    <cfRule type="duplicateValues" dxfId="192" priority="201"/>
+    <cfRule type="duplicateValues" dxfId="191" priority="200"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12">
-    <cfRule type="duplicateValues" dxfId="184" priority="186"/>
-    <cfRule type="duplicateValues" dxfId="183" priority="185"/>
+    <cfRule type="duplicateValues" dxfId="190" priority="199"/>
+    <cfRule type="duplicateValues" dxfId="189" priority="198"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15">
-    <cfRule type="duplicateValues" dxfId="182" priority="184"/>
-    <cfRule type="duplicateValues" dxfId="181" priority="183"/>
+    <cfRule type="duplicateValues" dxfId="188" priority="196"/>
+    <cfRule type="duplicateValues" dxfId="187" priority="197"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16">
-    <cfRule type="duplicateValues" dxfId="180" priority="182"/>
+    <cfRule type="duplicateValues" dxfId="186" priority="195"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17">
-    <cfRule type="duplicateValues" dxfId="179" priority="181"/>
-    <cfRule type="duplicateValues" dxfId="178" priority="180"/>
+    <cfRule type="duplicateValues" dxfId="185" priority="194"/>
+    <cfRule type="duplicateValues" dxfId="184" priority="193"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B18">
-    <cfRule type="duplicateValues" dxfId="177" priority="179"/>
-    <cfRule type="duplicateValues" dxfId="176" priority="178"/>
+    <cfRule type="duplicateValues" dxfId="183" priority="192"/>
+    <cfRule type="duplicateValues" dxfId="182" priority="191"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B19">
-    <cfRule type="duplicateValues" dxfId="175" priority="177"/>
+    <cfRule type="duplicateValues" dxfId="181" priority="190"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:B23">
-    <cfRule type="duplicateValues" dxfId="174" priority="176"/>
-    <cfRule type="duplicateValues" dxfId="173" priority="175"/>
+    <cfRule type="duplicateValues" dxfId="180" priority="189"/>
+    <cfRule type="duplicateValues" dxfId="179" priority="188"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B24">
-    <cfRule type="duplicateValues" dxfId="172" priority="174"/>
-    <cfRule type="duplicateValues" dxfId="171" priority="173"/>
+    <cfRule type="duplicateValues" dxfId="178" priority="187"/>
+    <cfRule type="duplicateValues" dxfId="177" priority="186"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B27">
-    <cfRule type="duplicateValues" dxfId="170" priority="172"/>
-    <cfRule type="duplicateValues" dxfId="169" priority="171"/>
+    <cfRule type="duplicateValues" dxfId="176" priority="184"/>
+    <cfRule type="duplicateValues" dxfId="175" priority="185"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28">
-    <cfRule type="duplicateValues" dxfId="168" priority="170"/>
+    <cfRule type="duplicateValues" dxfId="174" priority="183"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29">
-    <cfRule type="duplicateValues" dxfId="167" priority="169"/>
-    <cfRule type="duplicateValues" dxfId="166" priority="168"/>
+    <cfRule type="duplicateValues" dxfId="173" priority="181"/>
+    <cfRule type="duplicateValues" dxfId="172" priority="182"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="165" priority="167"/>
+    <cfRule type="duplicateValues" dxfId="171" priority="180"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31">
-    <cfRule type="duplicateValues" dxfId="164" priority="166"/>
+    <cfRule type="duplicateValues" dxfId="170" priority="179"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="duplicateValues" dxfId="163" priority="165"/>
+    <cfRule type="duplicateValues" dxfId="169" priority="178"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33">
-    <cfRule type="duplicateValues" dxfId="162" priority="164"/>
+    <cfRule type="duplicateValues" dxfId="168" priority="177"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="161" priority="163"/>
+    <cfRule type="duplicateValues" dxfId="167" priority="176"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35">
-    <cfRule type="duplicateValues" dxfId="160" priority="162"/>
+    <cfRule type="duplicateValues" dxfId="166" priority="175"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37">
-    <cfRule type="duplicateValues" dxfId="159" priority="161"/>
+    <cfRule type="duplicateValues" dxfId="165" priority="174"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38">
-    <cfRule type="duplicateValues" dxfId="158" priority="160"/>
+    <cfRule type="duplicateValues" dxfId="164" priority="173"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B42">
-    <cfRule type="duplicateValues" dxfId="157" priority="159"/>
+    <cfRule type="duplicateValues" dxfId="163" priority="172"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43">
-    <cfRule type="duplicateValues" dxfId="156" priority="158"/>
+    <cfRule type="duplicateValues" dxfId="162" priority="171"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44:B45">
-    <cfRule type="duplicateValues" dxfId="155" priority="157"/>
+    <cfRule type="duplicateValues" dxfId="161" priority="170"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B46">
-    <cfRule type="duplicateValues" dxfId="154" priority="156"/>
+    <cfRule type="duplicateValues" dxfId="160" priority="169"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B48">
-    <cfRule type="duplicateValues" dxfId="153" priority="155"/>
+    <cfRule type="duplicateValues" dxfId="159" priority="168"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B49">
-    <cfRule type="duplicateValues" dxfId="152" priority="154"/>
+    <cfRule type="duplicateValues" dxfId="158" priority="167"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B51">
-    <cfRule type="duplicateValues" dxfId="151" priority="153"/>
+    <cfRule type="duplicateValues" dxfId="157" priority="166"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B52">
-    <cfRule type="duplicateValues" dxfId="150" priority="152"/>
+    <cfRule type="duplicateValues" dxfId="156" priority="165"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B58">
-    <cfRule type="duplicateValues" dxfId="149" priority="150"/>
+    <cfRule type="duplicateValues" dxfId="155" priority="163"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B59">
-    <cfRule type="duplicateValues" dxfId="148" priority="148"/>
+    <cfRule type="duplicateValues" dxfId="154" priority="161"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B63">
-    <cfRule type="duplicateValues" dxfId="147" priority="147"/>
+    <cfRule type="duplicateValues" dxfId="153" priority="160"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B64">
-    <cfRule type="duplicateValues" dxfId="146" priority="145"/>
+    <cfRule type="duplicateValues" dxfId="152" priority="158"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B66">
-    <cfRule type="duplicateValues" dxfId="145" priority="144"/>
+    <cfRule type="duplicateValues" dxfId="151" priority="157"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="144" priority="143"/>
-    <cfRule type="duplicateValues" dxfId="143" priority="142"/>
+    <cfRule type="duplicateValues" dxfId="150" priority="155"/>
+    <cfRule type="duplicateValues" dxfId="149" priority="156"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B68">
-    <cfRule type="duplicateValues" dxfId="142" priority="141"/>
+    <cfRule type="duplicateValues" dxfId="148" priority="154"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B69">
-    <cfRule type="duplicateValues" dxfId="141" priority="140"/>
+    <cfRule type="duplicateValues" dxfId="147" priority="153"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B70">
-    <cfRule type="duplicateValues" dxfId="140" priority="138"/>
+    <cfRule type="duplicateValues" dxfId="146" priority="151"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B72">
-    <cfRule type="duplicateValues" dxfId="139" priority="137"/>
+    <cfRule type="duplicateValues" dxfId="145" priority="150"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B73">
-    <cfRule type="duplicateValues" dxfId="138" priority="135"/>
+    <cfRule type="duplicateValues" dxfId="144" priority="148"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B74">
-    <cfRule type="duplicateValues" dxfId="137" priority="134"/>
+    <cfRule type="duplicateValues" dxfId="143" priority="147"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B75">
-    <cfRule type="duplicateValues" dxfId="136" priority="133"/>
+    <cfRule type="duplicateValues" dxfId="142" priority="146"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B76">
-    <cfRule type="duplicateValues" dxfId="135" priority="132"/>
+    <cfRule type="duplicateValues" dxfId="141" priority="145"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B77">
-    <cfRule type="duplicateValues" dxfId="134" priority="130"/>
+    <cfRule type="duplicateValues" dxfId="140" priority="143"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B78">
-    <cfRule type="duplicateValues" dxfId="133" priority="129"/>
+    <cfRule type="duplicateValues" dxfId="139" priority="142"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B83">
-    <cfRule type="duplicateValues" dxfId="132" priority="128"/>
+    <cfRule type="duplicateValues" dxfId="138" priority="141"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B84">
-    <cfRule type="duplicateValues" dxfId="131" priority="127"/>
+    <cfRule type="duplicateValues" dxfId="137" priority="140"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B85">
-    <cfRule type="duplicateValues" dxfId="130" priority="126"/>
+    <cfRule type="duplicateValues" dxfId="136" priority="139"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B87">
-    <cfRule type="duplicateValues" dxfId="129" priority="125"/>
+    <cfRule type="duplicateValues" dxfId="135" priority="138"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B88">
-    <cfRule type="duplicateValues" dxfId="128" priority="124"/>
+    <cfRule type="duplicateValues" dxfId="134" priority="137"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B89">
-    <cfRule type="duplicateValues" dxfId="127" priority="123"/>
+    <cfRule type="duplicateValues" dxfId="133" priority="136"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B90">
-    <cfRule type="duplicateValues" dxfId="126" priority="122"/>
+    <cfRule type="duplicateValues" dxfId="132" priority="135"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B91">
-    <cfRule type="duplicateValues" dxfId="125" priority="121"/>
+    <cfRule type="duplicateValues" dxfId="131" priority="134"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B92">
-    <cfRule type="duplicateValues" dxfId="124" priority="120"/>
+    <cfRule type="duplicateValues" dxfId="130" priority="133"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B93">
-    <cfRule type="duplicateValues" dxfId="123" priority="119"/>
+    <cfRule type="duplicateValues" dxfId="129" priority="132"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B94">
-    <cfRule type="duplicateValues" dxfId="122" priority="118"/>
+    <cfRule type="duplicateValues" dxfId="128" priority="131"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B95">
-    <cfRule type="duplicateValues" dxfId="121" priority="117"/>
+    <cfRule type="duplicateValues" dxfId="127" priority="130"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B96">
-    <cfRule type="duplicateValues" dxfId="120" priority="116"/>
+    <cfRule type="duplicateValues" dxfId="126" priority="129"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B97">
-    <cfRule type="duplicateValues" dxfId="119" priority="115"/>
+    <cfRule type="duplicateValues" dxfId="125" priority="128"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B98">
-    <cfRule type="duplicateValues" dxfId="118" priority="114"/>
+    <cfRule type="duplicateValues" dxfId="124" priority="127"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B99">
-    <cfRule type="duplicateValues" dxfId="117" priority="113"/>
+    <cfRule type="duplicateValues" dxfId="123" priority="126"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B100">
-    <cfRule type="duplicateValues" dxfId="116" priority="112"/>
+    <cfRule type="duplicateValues" dxfId="122" priority="125"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B101">
-    <cfRule type="duplicateValues" dxfId="115" priority="111"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="124"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B104">
-    <cfRule type="duplicateValues" dxfId="114" priority="110"/>
-    <cfRule type="duplicateValues" dxfId="113" priority="109"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="123"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="122"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B105:B106">
-    <cfRule type="duplicateValues" dxfId="112" priority="108"/>
+    <cfRule type="duplicateValues" dxfId="118" priority="121"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B107">
-    <cfRule type="duplicateValues" dxfId="111" priority="107"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="120"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B108">
-    <cfRule type="duplicateValues" dxfId="110" priority="106"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="119"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B109">
-    <cfRule type="duplicateValues" dxfId="109" priority="105"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="118"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B110">
-    <cfRule type="duplicateValues" dxfId="108" priority="104"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="117"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B111">
-    <cfRule type="duplicateValues" dxfId="107" priority="103"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="116"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B112">
-    <cfRule type="duplicateValues" dxfId="106" priority="102"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="115"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B113">
-    <cfRule type="duplicateValues" dxfId="105" priority="101"/>
+    <cfRule type="duplicateValues" dxfId="111" priority="114"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B114">
-    <cfRule type="duplicateValues" dxfId="104" priority="100"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="113"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B115">
-    <cfRule type="duplicateValues" dxfId="103" priority="99"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="112"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B116">
-    <cfRule type="duplicateValues" dxfId="102" priority="98"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="111"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B117">
-    <cfRule type="duplicateValues" dxfId="101" priority="97"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="110"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B118">
-    <cfRule type="duplicateValues" dxfId="100" priority="96"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="109"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B119">
-    <cfRule type="duplicateValues" dxfId="99" priority="95"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="108"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B120">
-    <cfRule type="duplicateValues" dxfId="98" priority="94"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="107"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B121">
-    <cfRule type="duplicateValues" dxfId="97" priority="93"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="106"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B122">
-    <cfRule type="duplicateValues" dxfId="96" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="105"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B126">
-    <cfRule type="duplicateValues" dxfId="95" priority="91"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="104"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B127">
-    <cfRule type="duplicateValues" dxfId="94" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="103"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B128">
-    <cfRule type="duplicateValues" dxfId="93" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="102"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B129">
-    <cfRule type="duplicateValues" dxfId="92" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="101"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B130">
-    <cfRule type="duplicateValues" dxfId="91" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="100"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B131">
-    <cfRule type="duplicateValues" dxfId="90" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="99"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B132">
-    <cfRule type="duplicateValues" dxfId="89" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="98"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B133">
-    <cfRule type="duplicateValues" dxfId="88" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="97"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B136">
-    <cfRule type="duplicateValues" dxfId="87" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="96"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B137">
-    <cfRule type="duplicateValues" dxfId="86" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="95"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B138">
-    <cfRule type="duplicateValues" dxfId="85" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="94"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B139">
-    <cfRule type="duplicateValues" dxfId="84" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="93"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B140">
-    <cfRule type="duplicateValues" dxfId="83" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="92"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B141">
-    <cfRule type="duplicateValues" dxfId="82" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="91"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B142">
-    <cfRule type="duplicateValues" dxfId="81" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="90"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B143">
-    <cfRule type="duplicateValues" dxfId="80" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="89"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B144">
-    <cfRule type="duplicateValues" dxfId="79" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="88"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B145">
-    <cfRule type="duplicateValues" dxfId="78" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="87"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B147">
-    <cfRule type="duplicateValues" dxfId="77" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="86"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B148">
-    <cfRule type="duplicateValues" dxfId="76" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="85"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B149">
-    <cfRule type="duplicateValues" dxfId="75" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="84"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B150">
-    <cfRule type="duplicateValues" dxfId="74" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="83"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B151">
-    <cfRule type="duplicateValues" dxfId="73" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="82"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B152">
-    <cfRule type="duplicateValues" dxfId="72" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="81"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B153">
-    <cfRule type="duplicateValues" dxfId="71" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="80"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B154">
-    <cfRule type="duplicateValues" dxfId="70" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="79"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B155">
-    <cfRule type="duplicateValues" dxfId="69" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="78"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B156">
-    <cfRule type="duplicateValues" dxfId="68" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="77"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B157">
-    <cfRule type="duplicateValues" dxfId="67" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="76"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B171">
-    <cfRule type="duplicateValues" dxfId="66" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="75"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B172">
-    <cfRule type="duplicateValues" dxfId="65" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="74"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B174">
-    <cfRule type="duplicateValues" dxfId="64" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="73"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B177:B178">
-    <cfRule type="duplicateValues" dxfId="63" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="72"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B181">
-    <cfRule type="duplicateValues" dxfId="62" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B182">
-    <cfRule type="duplicateValues" dxfId="61" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B183">
-    <cfRule type="duplicateValues" dxfId="60" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="69"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B184">
-    <cfRule type="duplicateValues" dxfId="59" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="68"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B185">
-    <cfRule type="duplicateValues" dxfId="58" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B186">
-    <cfRule type="duplicateValues" dxfId="57" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="66"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B188">
-    <cfRule type="duplicateValues" dxfId="56" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B189">
-    <cfRule type="duplicateValues" dxfId="55" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="64"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B190">
-    <cfRule type="duplicateValues" dxfId="54" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="63"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B191">
-    <cfRule type="duplicateValues" dxfId="53" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="62"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B192">
-    <cfRule type="duplicateValues" dxfId="52" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="61"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B193">
-    <cfRule type="duplicateValues" dxfId="51" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B195">
-    <cfRule type="duplicateValues" dxfId="50" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="59"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B196">
-    <cfRule type="duplicateValues" dxfId="49" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="58"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B197">
-    <cfRule type="duplicateValues" dxfId="48" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B198">
-    <cfRule type="duplicateValues" dxfId="47" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B199">
-    <cfRule type="duplicateValues" dxfId="46" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B200">
-    <cfRule type="duplicateValues" dxfId="45" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B201">
-    <cfRule type="duplicateValues" dxfId="44" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B202">
-    <cfRule type="duplicateValues" dxfId="43" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B203">
-    <cfRule type="duplicateValues" dxfId="42" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B204">
-    <cfRule type="duplicateValues" dxfId="41" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B205">
-    <cfRule type="duplicateValues" dxfId="40" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B206">
-    <cfRule type="duplicateValues" dxfId="39" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B207">
-    <cfRule type="duplicateValues" dxfId="38" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B215">
-    <cfRule type="duplicateValues" dxfId="37" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B218">
-    <cfRule type="duplicateValues" dxfId="36" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B220">
-    <cfRule type="duplicateValues" dxfId="35" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B222">
-    <cfRule type="duplicateValues" dxfId="34" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B223">
-    <cfRule type="duplicateValues" dxfId="33" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B224">
-    <cfRule type="duplicateValues" dxfId="32" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B225">
-    <cfRule type="duplicateValues" dxfId="31" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B227">
-    <cfRule type="duplicateValues" dxfId="30" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B229">
-    <cfRule type="duplicateValues" dxfId="29" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B230">
-    <cfRule type="duplicateValues" dxfId="28" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B232">
-    <cfRule type="duplicateValues" dxfId="27" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B233">
-    <cfRule type="duplicateValues" dxfId="26" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B234">
-    <cfRule type="duplicateValues" dxfId="25" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B235">
-    <cfRule type="duplicateValues" dxfId="24" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B236">
-    <cfRule type="duplicateValues" dxfId="23" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B237">
-    <cfRule type="duplicateValues" dxfId="22" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B239">
-    <cfRule type="duplicateValues" dxfId="21" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B240">
-    <cfRule type="duplicateValues" dxfId="20" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B241">
-    <cfRule type="duplicateValues" dxfId="19" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B242">
-    <cfRule type="duplicateValues" dxfId="18" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B243">
-    <cfRule type="duplicateValues" dxfId="17" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B250">
-    <cfRule type="duplicateValues" dxfId="16" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B251">
-    <cfRule type="duplicateValues" dxfId="15" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B253">
-    <cfRule type="duplicateValues" dxfId="14" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B255">
-    <cfRule type="duplicateValues" dxfId="13" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B258:B259">
-    <cfRule type="duplicateValues" dxfId="12" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B260">
-    <cfRule type="duplicateValues" dxfId="11" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B265:B267 B269">
-    <cfRule type="duplicateValues" dxfId="10" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B268">
-    <cfRule type="duplicateValues" dxfId="9" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B270">
-    <cfRule type="duplicateValues" dxfId="8" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B271">
-    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B273">
-    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B275">
+    <cfRule type="duplicateValues" dxfId="11" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B278">
+    <cfRule type="duplicateValues" dxfId="10" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B279">
+    <cfRule type="duplicateValues" dxfId="9" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B280">
+    <cfRule type="duplicateValues" dxfId="8" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B281">
+    <cfRule type="duplicateValues" dxfId="7" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B282">
+    <cfRule type="duplicateValues" dxfId="6" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B283">
+    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B284:B286">
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B287">
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B288">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B291">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B292">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -53163,15 +54380,15 @@
       </c>
       <c r="B1" s="15">
         <f>COUNTA(sum!A:A) -1</f>
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="C1" s="22">
         <f>COUNTIF(sum!I:I, "completed")/(B1-COUNTIF(sum!I:I, "abandoned")-COUNTIF(sum!I:I, "late app"))</f>
-        <v>0.94230769230769229</v>
+        <v>0.96254681647940077</v>
       </c>
       <c r="D1" s="21">
         <f>COUNTIF(sum!I:I, "completed")</f>
-        <v>245</v>
+        <v>257</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.4">
@@ -53206,7 +54423,7 @@
       </c>
       <c r="B5" s="15">
         <f>COUNTA(sum!J:J) -1</f>
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="C5" s="14">
         <f>B5/B1</f>
@@ -53219,11 +54436,11 @@
       </c>
       <c r="B6" s="16">
         <f>COUNTIFS(sum!J:J,"no news")</f>
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C6" s="10">
         <f>B6/$B$5</f>
-        <v>0.9550561797752809</v>
+        <v>0.93430656934306566</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
@@ -53232,11 +54449,11 @@
       </c>
       <c r="B7" s="16">
         <f>COUNTIFS(sum!J:J,"rejected")</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C7" s="10">
         <f t="shared" ref="C7:C10" si="0">B7/$B$5</f>
-        <v>4.1198501872659173E-2</v>
+        <v>4.7445255474452552E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">
@@ -53244,12 +54461,12 @@
         <v>404</v>
       </c>
       <c r="B8" s="16">
-        <f>COUNTIFS(sum!J:J,"interview")</f>
-        <v>1</v>
+        <f>COUNTIFS(sum!J:J,"interview") + COUNTIFS(sum!J:J,"fly out") + COUNTIFS(sum!J:J,"offer")</f>
+        <v>5</v>
       </c>
       <c r="C8" s="10">
         <f t="shared" si="0"/>
-        <v>3.7453183520599251E-3</v>
+        <v>1.824817518248175E-2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">
@@ -53257,12 +54474,12 @@
         <v>405</v>
       </c>
       <c r="B9" s="16">
-        <f>COUNTIFS(sum!J:J,"fly out")</f>
-        <v>0</v>
+        <f xml:space="preserve"> COUNTIFS(sum!J:J,"fly out") + COUNTIFS(sum!J:J,"offer")</f>
+        <v>1</v>
       </c>
       <c r="C9" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3.6496350364963502E-3</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.4">

--- a/EconJM_status.xlsx
+++ b/EconJM_status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\javie\Dropbox\Work\Job Search\2025 EconJM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2472ACC8-6AF5-40ED-BCEE-1A327BB2778B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D80B516F-7A6D-497D-9AA7-E31BF4D26662}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" xr2:uid="{6FE48536-7E5C-BF4C-9490-2A6392576298}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" activeTab="1" xr2:uid="{6FE48536-7E5C-BF4C-9490-2A6392576298}"/>
   </bookViews>
   <sheets>
     <sheet name="sum" sheetId="1" r:id="rId1"/>
@@ -1093,7 +1093,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2767" uniqueCount="872">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2769" uniqueCount="872">
   <si>
     <t>add_id</t>
   </si>
@@ -3926,7 +3926,17 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="214">
+  <dxfs count="215">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -46569,7 +46579,7 @@
         <v>96</v>
       </c>
       <c r="J187" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M187" t="s">
         <v>683</v>
@@ -50468,63 +50478,63 @@
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="A1:B208 A210:B1048576">
-    <cfRule type="duplicateValues" dxfId="213" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="214" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:B22">
-    <cfRule type="duplicateValues" dxfId="212" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="213" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A61:B61">
-    <cfRule type="duplicateValues" dxfId="211" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="212" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="containsText" dxfId="210" priority="15" operator="containsText" text="closed">
+    <cfRule type="containsText" dxfId="211" priority="15" operator="containsText" text="closed">
       <formula>NOT(ISERROR(SEARCH("closed",I1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="209" priority="16" operator="containsText" text="abandoned">
+    <cfRule type="containsText" dxfId="210" priority="16" operator="containsText" text="abandoned">
       <formula>NOT(ISERROR(SEARCH("abandoned",I1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="208" priority="18" operator="containsText" text="late app">
+    <cfRule type="containsText" dxfId="209" priority="18" operator="containsText" text="late app">
       <formula>NOT(ISERROR(SEARCH("late app",I1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:L1048576 O78:O80 O83:O89 O92:O112 O115:O124 O126:O181 R136 R153 R159 R166 R173 R178 O183:O205 O208:O211 O213:O218 O220:O233 R225 O235:O237 O239:O248 I1:J1">
-    <cfRule type="containsText" dxfId="207" priority="21" operator="containsText" text="completed">
+    <cfRule type="containsText" dxfId="208" priority="21" operator="containsText" text="completed">
       <formula>NOT(ISERROR(SEARCH("completed",I1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:J1048576">
-    <cfRule type="containsText" dxfId="206" priority="10" operator="containsText" text="no news">
+    <cfRule type="containsText" dxfId="207" priority="10" operator="containsText" text="no news">
       <formula>NOT(ISERROR(SEARCH("no news",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="205" priority="11" operator="containsText" text="offer">
+    <cfRule type="containsText" dxfId="206" priority="11" operator="containsText" text="offer">
       <formula>NOT(ISERROR(SEARCH("offer",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="204" priority="12" operator="containsText" text="fly out">
+    <cfRule type="containsText" dxfId="205" priority="12" operator="containsText" text="fly out">
       <formula>NOT(ISERROR(SEARCH("fly out",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="203" priority="13" operator="containsText" text="interview">
+    <cfRule type="containsText" dxfId="204" priority="13" operator="containsText" text="interview">
       <formula>NOT(ISERROR(SEARCH("interview",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="202" priority="14" operator="containsText" text="rejected">
+    <cfRule type="containsText" dxfId="203" priority="14" operator="containsText" text="rejected">
       <formula>NOT(ISERROR(SEARCH("rejected",J1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1:L1048576 O78:O80 O83:O89 O92:O112 O115:O124 O126:O181 R136 R153 R159 R166 R173 R178 O183:O205 O208:O211 O213:O218 O220:O233 R225 O235:O237 O239:O248">
-    <cfRule type="containsText" dxfId="201" priority="19" operator="containsText" text="NO">
+    <cfRule type="containsText" dxfId="202" priority="19" operator="containsText" text="NO">
       <formula>NOT(ISERROR(SEARCH("NO",K1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="200" priority="20" operator="containsText" text="YES">
+    <cfRule type="containsText" dxfId="201" priority="20" operator="containsText" text="YES">
       <formula>NOT(ISERROR(SEARCH("YES",K1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O250:O267">
-    <cfRule type="containsText" dxfId="199" priority="1" operator="containsText" text="NO">
+    <cfRule type="containsText" dxfId="200" priority="1" operator="containsText" text="NO">
       <formula>NOT(ISERROR(SEARCH("NO",O250)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="198" priority="2" operator="containsText" text="YES">
+    <cfRule type="containsText" dxfId="199" priority="2" operator="containsText" text="YES">
       <formula>NOT(ISERROR(SEARCH("YES",O250)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="197" priority="3" operator="containsText" text="completed">
+    <cfRule type="containsText" dxfId="198" priority="3" operator="containsText" text="completed">
       <formula>NOT(ISERROR(SEARCH("completed",O250)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -50646,7 +50656,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923E81FA-B875-3C4E-A189-1A21268FA086}">
-  <dimension ref="A1:C292"/>
+  <dimension ref="A1:C293"/>
   <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="32.83203125" customWidth="1"/>
@@ -53794,570 +53804,584 @@
         <v>97</v>
       </c>
     </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A293" s="1">
+        <v>46001</v>
+      </c>
+      <c r="B293" t="s">
+        <v>682</v>
+      </c>
+      <c r="C293" t="s">
+        <v>403</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="B5">
-    <cfRule type="duplicateValues" dxfId="196" priority="204"/>
-    <cfRule type="duplicateValues" dxfId="195" priority="205"/>
+    <cfRule type="duplicateValues" dxfId="197" priority="205"/>
+    <cfRule type="duplicateValues" dxfId="196" priority="206"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B10">
+    <cfRule type="duplicateValues" dxfId="195" priority="204"/>
     <cfRule type="duplicateValues" dxfId="194" priority="203"/>
-    <cfRule type="duplicateValues" dxfId="193" priority="202"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B11">
+    <cfRule type="duplicateValues" dxfId="193" priority="202"/>
     <cfRule type="duplicateValues" dxfId="192" priority="201"/>
-    <cfRule type="duplicateValues" dxfId="191" priority="200"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12">
+    <cfRule type="duplicateValues" dxfId="191" priority="200"/>
     <cfRule type="duplicateValues" dxfId="190" priority="199"/>
-    <cfRule type="duplicateValues" dxfId="189" priority="198"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15">
-    <cfRule type="duplicateValues" dxfId="188" priority="196"/>
-    <cfRule type="duplicateValues" dxfId="187" priority="197"/>
+    <cfRule type="duplicateValues" dxfId="189" priority="198"/>
+    <cfRule type="duplicateValues" dxfId="188" priority="197"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16">
-    <cfRule type="duplicateValues" dxfId="186" priority="195"/>
+    <cfRule type="duplicateValues" dxfId="187" priority="196"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17">
-    <cfRule type="duplicateValues" dxfId="185" priority="194"/>
-    <cfRule type="duplicateValues" dxfId="184" priority="193"/>
+    <cfRule type="duplicateValues" dxfId="186" priority="194"/>
+    <cfRule type="duplicateValues" dxfId="185" priority="195"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B18">
+    <cfRule type="duplicateValues" dxfId="184" priority="193"/>
     <cfRule type="duplicateValues" dxfId="183" priority="192"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B19">
     <cfRule type="duplicateValues" dxfId="182" priority="191"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B19">
+  <conditionalFormatting sqref="B22:B23">
     <cfRule type="duplicateValues" dxfId="181" priority="190"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B22:B23">
     <cfRule type="duplicateValues" dxfId="180" priority="189"/>
-    <cfRule type="duplicateValues" dxfId="179" priority="188"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B24">
+    <cfRule type="duplicateValues" dxfId="179" priority="188"/>
     <cfRule type="duplicateValues" dxfId="178" priority="187"/>
-    <cfRule type="duplicateValues" dxfId="177" priority="186"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B27">
-    <cfRule type="duplicateValues" dxfId="176" priority="184"/>
-    <cfRule type="duplicateValues" dxfId="175" priority="185"/>
+    <cfRule type="duplicateValues" dxfId="177" priority="186"/>
+    <cfRule type="duplicateValues" dxfId="176" priority="185"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28">
-    <cfRule type="duplicateValues" dxfId="174" priority="183"/>
+    <cfRule type="duplicateValues" dxfId="175" priority="184"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29">
-    <cfRule type="duplicateValues" dxfId="173" priority="181"/>
-    <cfRule type="duplicateValues" dxfId="172" priority="182"/>
+    <cfRule type="duplicateValues" dxfId="174" priority="182"/>
+    <cfRule type="duplicateValues" dxfId="173" priority="183"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30">
+    <cfRule type="duplicateValues" dxfId="172" priority="181"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31">
     <cfRule type="duplicateValues" dxfId="171" priority="180"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B31">
+  <conditionalFormatting sqref="B32">
     <cfRule type="duplicateValues" dxfId="170" priority="179"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B32">
+  <conditionalFormatting sqref="B33">
     <cfRule type="duplicateValues" dxfId="169" priority="178"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B33">
+  <conditionalFormatting sqref="B34">
     <cfRule type="duplicateValues" dxfId="168" priority="177"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B34">
+  <conditionalFormatting sqref="B35">
     <cfRule type="duplicateValues" dxfId="167" priority="176"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B35">
+  <conditionalFormatting sqref="B37">
     <cfRule type="duplicateValues" dxfId="166" priority="175"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B37">
+  <conditionalFormatting sqref="B38">
     <cfRule type="duplicateValues" dxfId="165" priority="174"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B38">
+  <conditionalFormatting sqref="B42">
     <cfRule type="duplicateValues" dxfId="164" priority="173"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B42">
+  <conditionalFormatting sqref="B43">
     <cfRule type="duplicateValues" dxfId="163" priority="172"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B43">
+  <conditionalFormatting sqref="B44:B45">
     <cfRule type="duplicateValues" dxfId="162" priority="171"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B44:B45">
+  <conditionalFormatting sqref="B46">
     <cfRule type="duplicateValues" dxfId="161" priority="170"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B46">
+  <conditionalFormatting sqref="B48">
     <cfRule type="duplicateValues" dxfId="160" priority="169"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B48">
+  <conditionalFormatting sqref="B49">
     <cfRule type="duplicateValues" dxfId="159" priority="168"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B49">
+  <conditionalFormatting sqref="B51">
     <cfRule type="duplicateValues" dxfId="158" priority="167"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B51">
+  <conditionalFormatting sqref="B52">
     <cfRule type="duplicateValues" dxfId="157" priority="166"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B52">
-    <cfRule type="duplicateValues" dxfId="156" priority="165"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B58">
-    <cfRule type="duplicateValues" dxfId="155" priority="163"/>
+    <cfRule type="duplicateValues" dxfId="156" priority="164"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B59">
+    <cfRule type="duplicateValues" dxfId="155" priority="162"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B63">
     <cfRule type="duplicateValues" dxfId="154" priority="161"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B63">
-    <cfRule type="duplicateValues" dxfId="153" priority="160"/>
+  <conditionalFormatting sqref="B64">
+    <cfRule type="duplicateValues" dxfId="153" priority="159"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B64">
+  <conditionalFormatting sqref="B66">
     <cfRule type="duplicateValues" dxfId="152" priority="158"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B66">
+  <conditionalFormatting sqref="B67">
     <cfRule type="duplicateValues" dxfId="151" priority="157"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="150" priority="155"/>
-    <cfRule type="duplicateValues" dxfId="149" priority="156"/>
+    <cfRule type="duplicateValues" dxfId="150" priority="156"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B68">
+    <cfRule type="duplicateValues" dxfId="149" priority="155"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B69">
     <cfRule type="duplicateValues" dxfId="148" priority="154"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B69">
-    <cfRule type="duplicateValues" dxfId="147" priority="153"/>
+  <conditionalFormatting sqref="B70">
+    <cfRule type="duplicateValues" dxfId="147" priority="152"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B70">
+  <conditionalFormatting sqref="B72">
     <cfRule type="duplicateValues" dxfId="146" priority="151"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B72">
-    <cfRule type="duplicateValues" dxfId="145" priority="150"/>
+  <conditionalFormatting sqref="B73">
+    <cfRule type="duplicateValues" dxfId="145" priority="149"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B73">
+  <conditionalFormatting sqref="B74">
     <cfRule type="duplicateValues" dxfId="144" priority="148"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B74">
+  <conditionalFormatting sqref="B75">
     <cfRule type="duplicateValues" dxfId="143" priority="147"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B75">
+  <conditionalFormatting sqref="B76">
     <cfRule type="duplicateValues" dxfId="142" priority="146"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B76">
-    <cfRule type="duplicateValues" dxfId="141" priority="145"/>
+  <conditionalFormatting sqref="B77">
+    <cfRule type="duplicateValues" dxfId="141" priority="144"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B77">
+  <conditionalFormatting sqref="B78">
     <cfRule type="duplicateValues" dxfId="140" priority="143"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B78">
+  <conditionalFormatting sqref="B83">
     <cfRule type="duplicateValues" dxfId="139" priority="142"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B83">
+  <conditionalFormatting sqref="B84">
     <cfRule type="duplicateValues" dxfId="138" priority="141"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B84">
+  <conditionalFormatting sqref="B85">
     <cfRule type="duplicateValues" dxfId="137" priority="140"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B85">
+  <conditionalFormatting sqref="B87">
     <cfRule type="duplicateValues" dxfId="136" priority="139"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B87">
+  <conditionalFormatting sqref="B88">
     <cfRule type="duplicateValues" dxfId="135" priority="138"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B88">
+  <conditionalFormatting sqref="B89">
     <cfRule type="duplicateValues" dxfId="134" priority="137"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B89">
+  <conditionalFormatting sqref="B90">
     <cfRule type="duplicateValues" dxfId="133" priority="136"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B90">
+  <conditionalFormatting sqref="B91">
     <cfRule type="duplicateValues" dxfId="132" priority="135"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B91">
+  <conditionalFormatting sqref="B92">
     <cfRule type="duplicateValues" dxfId="131" priority="134"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B92">
+  <conditionalFormatting sqref="B93">
     <cfRule type="duplicateValues" dxfId="130" priority="133"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B93">
+  <conditionalFormatting sqref="B94">
     <cfRule type="duplicateValues" dxfId="129" priority="132"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B94">
+  <conditionalFormatting sqref="B95">
     <cfRule type="duplicateValues" dxfId="128" priority="131"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B95">
+  <conditionalFormatting sqref="B96">
     <cfRule type="duplicateValues" dxfId="127" priority="130"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B96">
+  <conditionalFormatting sqref="B97">
     <cfRule type="duplicateValues" dxfId="126" priority="129"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B97">
+  <conditionalFormatting sqref="B98">
     <cfRule type="duplicateValues" dxfId="125" priority="128"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B98">
+  <conditionalFormatting sqref="B99">
     <cfRule type="duplicateValues" dxfId="124" priority="127"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B99">
+  <conditionalFormatting sqref="B100">
     <cfRule type="duplicateValues" dxfId="123" priority="126"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B100">
+  <conditionalFormatting sqref="B101">
     <cfRule type="duplicateValues" dxfId="122" priority="125"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B101">
+  <conditionalFormatting sqref="B104">
     <cfRule type="duplicateValues" dxfId="121" priority="124"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="123"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B104">
-    <cfRule type="duplicateValues" dxfId="120" priority="123"/>
+  <conditionalFormatting sqref="B105:B106">
     <cfRule type="duplicateValues" dxfId="119" priority="122"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B105:B106">
+  <conditionalFormatting sqref="B107">
     <cfRule type="duplicateValues" dxfId="118" priority="121"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B107">
+  <conditionalFormatting sqref="B108">
     <cfRule type="duplicateValues" dxfId="117" priority="120"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B108">
+  <conditionalFormatting sqref="B109">
     <cfRule type="duplicateValues" dxfId="116" priority="119"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B109">
+  <conditionalFormatting sqref="B110">
     <cfRule type="duplicateValues" dxfId="115" priority="118"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B110">
+  <conditionalFormatting sqref="B111">
     <cfRule type="duplicateValues" dxfId="114" priority="117"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B111">
+  <conditionalFormatting sqref="B112">
     <cfRule type="duplicateValues" dxfId="113" priority="116"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B112">
+  <conditionalFormatting sqref="B113">
     <cfRule type="duplicateValues" dxfId="112" priority="115"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B113">
+  <conditionalFormatting sqref="B114">
     <cfRule type="duplicateValues" dxfId="111" priority="114"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B114">
+  <conditionalFormatting sqref="B115">
     <cfRule type="duplicateValues" dxfId="110" priority="113"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B115">
+  <conditionalFormatting sqref="B116">
     <cfRule type="duplicateValues" dxfId="109" priority="112"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B116">
+  <conditionalFormatting sqref="B117">
     <cfRule type="duplicateValues" dxfId="108" priority="111"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B117">
+  <conditionalFormatting sqref="B118">
     <cfRule type="duplicateValues" dxfId="107" priority="110"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B118">
+  <conditionalFormatting sqref="B119">
     <cfRule type="duplicateValues" dxfId="106" priority="109"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B119">
+  <conditionalFormatting sqref="B120">
     <cfRule type="duplicateValues" dxfId="105" priority="108"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B120">
+  <conditionalFormatting sqref="B121">
     <cfRule type="duplicateValues" dxfId="104" priority="107"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B121">
+  <conditionalFormatting sqref="B122">
     <cfRule type="duplicateValues" dxfId="103" priority="106"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B122">
+  <conditionalFormatting sqref="B126">
     <cfRule type="duplicateValues" dxfId="102" priority="105"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B126">
+  <conditionalFormatting sqref="B127">
     <cfRule type="duplicateValues" dxfId="101" priority="104"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B127">
+  <conditionalFormatting sqref="B128">
     <cfRule type="duplicateValues" dxfId="100" priority="103"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B128">
+  <conditionalFormatting sqref="B129">
     <cfRule type="duplicateValues" dxfId="99" priority="102"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B129">
+  <conditionalFormatting sqref="B130">
     <cfRule type="duplicateValues" dxfId="98" priority="101"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B130">
+  <conditionalFormatting sqref="B131">
     <cfRule type="duplicateValues" dxfId="97" priority="100"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B131">
+  <conditionalFormatting sqref="B132">
     <cfRule type="duplicateValues" dxfId="96" priority="99"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B132">
+  <conditionalFormatting sqref="B133">
     <cfRule type="duplicateValues" dxfId="95" priority="98"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B133">
+  <conditionalFormatting sqref="B136">
     <cfRule type="duplicateValues" dxfId="94" priority="97"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B136">
+  <conditionalFormatting sqref="B137">
     <cfRule type="duplicateValues" dxfId="93" priority="96"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B137">
+  <conditionalFormatting sqref="B138">
     <cfRule type="duplicateValues" dxfId="92" priority="95"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B138">
+  <conditionalFormatting sqref="B139">
     <cfRule type="duplicateValues" dxfId="91" priority="94"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B139">
+  <conditionalFormatting sqref="B140">
     <cfRule type="duplicateValues" dxfId="90" priority="93"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B140">
+  <conditionalFormatting sqref="B141">
     <cfRule type="duplicateValues" dxfId="89" priority="92"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B141">
+  <conditionalFormatting sqref="B142">
     <cfRule type="duplicateValues" dxfId="88" priority="91"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B142">
+  <conditionalFormatting sqref="B143">
     <cfRule type="duplicateValues" dxfId="87" priority="90"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B143">
+  <conditionalFormatting sqref="B144">
     <cfRule type="duplicateValues" dxfId="86" priority="89"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B144">
+  <conditionalFormatting sqref="B145">
     <cfRule type="duplicateValues" dxfId="85" priority="88"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B145">
+  <conditionalFormatting sqref="B147">
     <cfRule type="duplicateValues" dxfId="84" priority="87"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B147">
+  <conditionalFormatting sqref="B148">
     <cfRule type="duplicateValues" dxfId="83" priority="86"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B148">
+  <conditionalFormatting sqref="B149">
     <cfRule type="duplicateValues" dxfId="82" priority="85"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B149">
+  <conditionalFormatting sqref="B150">
     <cfRule type="duplicateValues" dxfId="81" priority="84"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B150">
+  <conditionalFormatting sqref="B151">
     <cfRule type="duplicateValues" dxfId="80" priority="83"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B151">
+  <conditionalFormatting sqref="B152">
     <cfRule type="duplicateValues" dxfId="79" priority="82"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B152">
+  <conditionalFormatting sqref="B153">
     <cfRule type="duplicateValues" dxfId="78" priority="81"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B153">
+  <conditionalFormatting sqref="B154">
     <cfRule type="duplicateValues" dxfId="77" priority="80"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B154">
+  <conditionalFormatting sqref="B155">
     <cfRule type="duplicateValues" dxfId="76" priority="79"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B155">
+  <conditionalFormatting sqref="B156">
     <cfRule type="duplicateValues" dxfId="75" priority="78"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B156">
+  <conditionalFormatting sqref="B157">
     <cfRule type="duplicateValues" dxfId="74" priority="77"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B157">
+  <conditionalFormatting sqref="B171">
     <cfRule type="duplicateValues" dxfId="73" priority="76"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B171">
+  <conditionalFormatting sqref="B172">
     <cfRule type="duplicateValues" dxfId="72" priority="75"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B172">
+  <conditionalFormatting sqref="B174">
     <cfRule type="duplicateValues" dxfId="71" priority="74"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B174">
+  <conditionalFormatting sqref="B177:B178">
     <cfRule type="duplicateValues" dxfId="70" priority="73"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B177:B178">
+  <conditionalFormatting sqref="B181">
     <cfRule type="duplicateValues" dxfId="69" priority="72"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B181">
+  <conditionalFormatting sqref="B182">
     <cfRule type="duplicateValues" dxfId="68" priority="71"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B182">
+  <conditionalFormatting sqref="B183">
     <cfRule type="duplicateValues" dxfId="67" priority="70"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B183">
+  <conditionalFormatting sqref="B184">
     <cfRule type="duplicateValues" dxfId="66" priority="69"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B184">
+  <conditionalFormatting sqref="B185">
     <cfRule type="duplicateValues" dxfId="65" priority="68"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B185">
+  <conditionalFormatting sqref="B186">
     <cfRule type="duplicateValues" dxfId="64" priority="67"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B186">
+  <conditionalFormatting sqref="B188">
     <cfRule type="duplicateValues" dxfId="63" priority="66"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B188">
+  <conditionalFormatting sqref="B189">
     <cfRule type="duplicateValues" dxfId="62" priority="65"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B189">
+  <conditionalFormatting sqref="B190">
     <cfRule type="duplicateValues" dxfId="61" priority="64"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B190">
+  <conditionalFormatting sqref="B191">
     <cfRule type="duplicateValues" dxfId="60" priority="63"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B191">
+  <conditionalFormatting sqref="B192">
     <cfRule type="duplicateValues" dxfId="59" priority="62"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B192">
+  <conditionalFormatting sqref="B193">
     <cfRule type="duplicateValues" dxfId="58" priority="61"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B193">
+  <conditionalFormatting sqref="B195">
     <cfRule type="duplicateValues" dxfId="57" priority="60"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B195">
+  <conditionalFormatting sqref="B196">
     <cfRule type="duplicateValues" dxfId="56" priority="59"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B196">
+  <conditionalFormatting sqref="B197">
     <cfRule type="duplicateValues" dxfId="55" priority="58"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B197">
+  <conditionalFormatting sqref="B198">
     <cfRule type="duplicateValues" dxfId="54" priority="57"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B198">
+  <conditionalFormatting sqref="B199">
     <cfRule type="duplicateValues" dxfId="53" priority="56"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B199">
+  <conditionalFormatting sqref="B200">
     <cfRule type="duplicateValues" dxfId="52" priority="55"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B200">
+  <conditionalFormatting sqref="B201">
     <cfRule type="duplicateValues" dxfId="51" priority="54"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B201">
+  <conditionalFormatting sqref="B202">
     <cfRule type="duplicateValues" dxfId="50" priority="53"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B202">
+  <conditionalFormatting sqref="B203">
     <cfRule type="duplicateValues" dxfId="49" priority="52"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B203">
+  <conditionalFormatting sqref="B204">
     <cfRule type="duplicateValues" dxfId="48" priority="51"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B204">
+  <conditionalFormatting sqref="B205">
     <cfRule type="duplicateValues" dxfId="47" priority="50"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B205">
+  <conditionalFormatting sqref="B206">
     <cfRule type="duplicateValues" dxfId="46" priority="49"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B206">
+  <conditionalFormatting sqref="B207">
     <cfRule type="duplicateValues" dxfId="45" priority="48"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B207">
+  <conditionalFormatting sqref="B215">
     <cfRule type="duplicateValues" dxfId="44" priority="47"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B215">
+  <conditionalFormatting sqref="B218">
     <cfRule type="duplicateValues" dxfId="43" priority="46"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B218">
+  <conditionalFormatting sqref="B220">
     <cfRule type="duplicateValues" dxfId="42" priority="45"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B220">
+  <conditionalFormatting sqref="B222">
     <cfRule type="duplicateValues" dxfId="41" priority="44"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B222">
+  <conditionalFormatting sqref="B223">
     <cfRule type="duplicateValues" dxfId="40" priority="43"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B223">
+  <conditionalFormatting sqref="B224">
     <cfRule type="duplicateValues" dxfId="39" priority="42"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B224">
+  <conditionalFormatting sqref="B225">
     <cfRule type="duplicateValues" dxfId="38" priority="41"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B225">
+  <conditionalFormatting sqref="B227">
     <cfRule type="duplicateValues" dxfId="37" priority="40"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B227">
+  <conditionalFormatting sqref="B229">
     <cfRule type="duplicateValues" dxfId="36" priority="39"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B229">
+  <conditionalFormatting sqref="B230">
     <cfRule type="duplicateValues" dxfId="35" priority="38"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B230">
+  <conditionalFormatting sqref="B232">
     <cfRule type="duplicateValues" dxfId="34" priority="37"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B232">
+  <conditionalFormatting sqref="B233">
     <cfRule type="duplicateValues" dxfId="33" priority="36"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B233">
+  <conditionalFormatting sqref="B234">
     <cfRule type="duplicateValues" dxfId="32" priority="35"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B234">
+  <conditionalFormatting sqref="B235">
     <cfRule type="duplicateValues" dxfId="31" priority="34"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B235">
+  <conditionalFormatting sqref="B236">
     <cfRule type="duplicateValues" dxfId="30" priority="33"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B236">
+  <conditionalFormatting sqref="B237">
     <cfRule type="duplicateValues" dxfId="29" priority="32"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B237">
-    <cfRule type="duplicateValues" dxfId="28" priority="31"/>
+  <conditionalFormatting sqref="B239">
+    <cfRule type="duplicateValues" dxfId="28" priority="30"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B239">
+  <conditionalFormatting sqref="B240">
     <cfRule type="duplicateValues" dxfId="27" priority="29"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B240">
+  <conditionalFormatting sqref="B241">
     <cfRule type="duplicateValues" dxfId="26" priority="28"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B241">
+  <conditionalFormatting sqref="B242">
     <cfRule type="duplicateValues" dxfId="25" priority="27"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B242">
+  <conditionalFormatting sqref="B243">
     <cfRule type="duplicateValues" dxfId="24" priority="26"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B243">
+  <conditionalFormatting sqref="B250">
     <cfRule type="duplicateValues" dxfId="23" priority="25"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B250">
+  <conditionalFormatting sqref="B251">
     <cfRule type="duplicateValues" dxfId="22" priority="24"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B251">
+  <conditionalFormatting sqref="B253">
     <cfRule type="duplicateValues" dxfId="21" priority="23"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B253">
+  <conditionalFormatting sqref="B255">
     <cfRule type="duplicateValues" dxfId="20" priority="22"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B255">
+  <conditionalFormatting sqref="B258:B259">
     <cfRule type="duplicateValues" dxfId="19" priority="21"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B258:B259">
+  <conditionalFormatting sqref="B260">
     <cfRule type="duplicateValues" dxfId="18" priority="20"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B260">
+  <conditionalFormatting sqref="B265:B267 B269">
     <cfRule type="duplicateValues" dxfId="17" priority="19"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B265:B267 B269">
+  <conditionalFormatting sqref="B268">
     <cfRule type="duplicateValues" dxfId="16" priority="18"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B268">
+  <conditionalFormatting sqref="B270">
     <cfRule type="duplicateValues" dxfId="15" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B270">
+  <conditionalFormatting sqref="B271">
     <cfRule type="duplicateValues" dxfId="14" priority="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B271">
+  <conditionalFormatting sqref="B273">
     <cfRule type="duplicateValues" dxfId="13" priority="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B273">
+  <conditionalFormatting sqref="B275">
     <cfRule type="duplicateValues" dxfId="12" priority="14"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B275">
+  <conditionalFormatting sqref="B278">
     <cfRule type="duplicateValues" dxfId="11" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B278">
+  <conditionalFormatting sqref="B279">
     <cfRule type="duplicateValues" dxfId="10" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B279">
+  <conditionalFormatting sqref="B280">
     <cfRule type="duplicateValues" dxfId="9" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B280">
+  <conditionalFormatting sqref="B281">
     <cfRule type="duplicateValues" dxfId="8" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B281">
+  <conditionalFormatting sqref="B282">
     <cfRule type="duplicateValues" dxfId="7" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B282">
-    <cfRule type="duplicateValues" dxfId="6" priority="8"/>
+  <conditionalFormatting sqref="B283">
+    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B283">
+  <conditionalFormatting sqref="B284:B286">
     <cfRule type="duplicateValues" dxfId="5" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B284:B286">
+  <conditionalFormatting sqref="B287">
     <cfRule type="duplicateValues" dxfId="4" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B287">
+  <conditionalFormatting sqref="B288">
     <cfRule type="duplicateValues" dxfId="3" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B288">
+  <conditionalFormatting sqref="B291">
     <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B291">
+  <conditionalFormatting sqref="B292">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B292">
+  <conditionalFormatting sqref="B293">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -54436,11 +54460,11 @@
       </c>
       <c r="B6" s="16">
         <f>COUNTIFS(sum!J:J,"no news")</f>
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C6" s="10">
         <f>B6/$B$5</f>
-        <v>0.93430656934306566</v>
+        <v>0.93065693430656937</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
@@ -54449,11 +54473,11 @@
       </c>
       <c r="B7" s="16">
         <f>COUNTIFS(sum!J:J,"rejected")</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" s="10">
         <f t="shared" ref="C7:C10" si="0">B7/$B$5</f>
-        <v>4.7445255474452552E-2</v>
+        <v>5.1094890510948905E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">

--- a/EconJM_status.xlsx
+++ b/EconJM_status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\javie\Dropbox\Work\Job Search\2025 EconJM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D80B516F-7A6D-497D-9AA7-E31BF4D26662}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F6C8224-58DB-4FC4-9E56-D5083ED4DD72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" activeTab="1" xr2:uid="{6FE48536-7E5C-BF4C-9490-2A6392576298}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" xr2:uid="{6FE48536-7E5C-BF4C-9490-2A6392576298}"/>
   </bookViews>
   <sheets>
     <sheet name="sum" sheetId="1" r:id="rId1"/>
@@ -1093,7 +1093,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2769" uniqueCount="872">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2799" uniqueCount="878">
   <si>
     <t>add_id</t>
   </si>
@@ -3745,6 +3745,24 @@
   </si>
   <si>
     <t>https://careers.fiu.edu/</t>
+  </si>
+  <si>
+    <t>tcd</t>
+  </si>
+  <si>
+    <t>https://my.corehr.com/pls/trrecruit/core_document_api_2.view_erecruit_document?p_key_1=CB26AA2AFD844E702E8300F71615FD485BC43D74A5AAB9780031AD7075E81C90E6513048715BC22461A36B1EAA3E023D296A2289F631CA529DC264DD0ECF30E82908B43DC4E26E11669B19E4D2CD6D7937CD3A1F455C59A346519CA6ED25DF0A5AEA55F0F331F97B5557E15631AFFE70CD24F8C6261254157EBBFFD246B9731DBA2290C8462798283678FF3109A886FFDF736969AD17D9A049C27A7220C3D37C95ED008CF3A070DA8E957B2F39BC1ABF732359DABCE73E2E2E49E25099B8C67A&amp;p_key_2=AD3492EFB843B061088195B195E18CA2DECEAE63982E0CF4EF78491D2E81D188036665B4BD789DCF29AB94C2B6FDBC9CEE0FDF25F2739474708FD4658CD450D6FD856FC916740D29CBABFA1D4EDD51A15B7B5839C2FAD157A56CEAFF96CCBFCF1A845B3B27F3D720B67471703936D8D3BBCC8A5C1941C9B03054BD685B589B3A137E92E7C53CD7322B2E2A33F7EBBFB47E150C53669CF6F6ACFAA17C2AD0168A4EA8F1785CA53DB1673DC6ECFD2764A3F908FB0AE85025BF4C938FE465D44654</t>
+  </si>
+  <si>
+    <t>Trinity College Dublin</t>
+  </si>
+  <si>
+    <t>Ireland</t>
+  </si>
+  <si>
+    <t>http://jobs.tcd.ie</t>
+  </si>
+  <si>
+    <t>search for the econ AP position</t>
   </si>
 </sst>
 </file>
@@ -3926,7 +3944,107 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="215">
+  <dxfs count="225">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -38010,7 +38128,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7772053-9363-CA4A-A53F-040B7C700753}">
-  <dimension ref="A1:V275"/>
+  <dimension ref="A1:V276"/>
   <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="19.6640625" customWidth="1"/>
@@ -40222,7 +40340,7 @@
         <v>96</v>
       </c>
       <c r="J49" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M49" t="s">
         <v>369</v>
@@ -49246,7 +49364,7 @@
         <v>785</v>
       </c>
       <c r="I248" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J248" t="s">
         <v>402</v>
@@ -50054,7 +50172,7 @@
         <v>836</v>
       </c>
       <c r="I266" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J266" t="s">
         <v>402</v>
@@ -50092,7 +50210,7 @@
         <v>843</v>
       </c>
       <c r="I267" t="s">
-        <v>23</v>
+        <v>152</v>
       </c>
       <c r="J267" t="s">
         <v>402</v>
@@ -50136,7 +50254,7 @@
         <v>847</v>
       </c>
       <c r="I268" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J268" t="s">
         <v>402</v>
@@ -50183,7 +50301,7 @@
         <v>851</v>
       </c>
       <c r="I269" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J269" t="s">
         <v>402</v>
@@ -50227,7 +50345,7 @@
         <v>855</v>
       </c>
       <c r="I270" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J270" t="s">
         <v>402</v>
@@ -50274,7 +50392,7 @@
         <v>859</v>
       </c>
       <c r="I271" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J271" t="s">
         <v>402</v>
@@ -50362,7 +50480,7 @@
         <v>15</v>
       </c>
       <c r="I273" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J273" t="s">
         <v>402</v>
@@ -50403,7 +50521,7 @@
         <v>15</v>
       </c>
       <c r="I274" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="J274" t="s">
         <v>402</v>
@@ -50435,13 +50553,19 @@
     </row>
     <row r="275" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A275" t="s">
-        <v>255</v>
-      </c>
-      <c r="E275" t="s">
-        <v>15</v>
-      </c>
-      <c r="F275" s="2" t="s">
-        <v>257</v>
+        <v>872</v>
+      </c>
+      <c r="C275" t="s">
+        <v>877</v>
+      </c>
+      <c r="D275" s="1">
+        <v>46023</v>
+      </c>
+      <c r="E275" s="2" t="s">
+        <v>876</v>
+      </c>
+      <c r="F275" t="s">
+        <v>873</v>
       </c>
       <c r="I275" t="s">
         <v>96</v>
@@ -50450,10 +50574,10 @@
         <v>402</v>
       </c>
       <c r="M275" t="s">
-        <v>256</v>
-      </c>
-      <c r="N275" t="e" vm="35">
-        <v>#VALUE!</v>
+        <v>874</v>
+      </c>
+      <c r="N275" t="s">
+        <v>875</v>
       </c>
       <c r="O275" t="s">
         <v>11</v>
@@ -50461,8 +50585,11 @@
       <c r="Q275" t="s">
         <v>776</v>
       </c>
+      <c r="R275" s="1">
+        <v>46034</v>
+      </c>
       <c r="T275">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U275">
         <v>0</v>
@@ -50471,70 +50598,108 @@
         <v>0</v>
       </c>
     </row>
+    <row r="276" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A276" t="s">
+        <v>255</v>
+      </c>
+      <c r="E276" t="s">
+        <v>15</v>
+      </c>
+      <c r="F276" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="I276" t="s">
+        <v>96</v>
+      </c>
+      <c r="J276" t="s">
+        <v>402</v>
+      </c>
+      <c r="M276" t="s">
+        <v>256</v>
+      </c>
+      <c r="N276" t="e" vm="35">
+        <v>#VALUE!</v>
+      </c>
+      <c r="O276" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q276" t="s">
+        <v>776</v>
+      </c>
+      <c r="T276">
+        <v>0</v>
+      </c>
+      <c r="U276">
+        <v>0</v>
+      </c>
+      <c r="V276">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:V267" xr:uid="{F7772053-9363-CA4A-A53F-040B7C700753}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V275">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V276">
       <sortCondition ref="D1:D267"/>
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="A1:B208 A210:B1048576">
-    <cfRule type="duplicateValues" dxfId="214" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="224" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:B22">
-    <cfRule type="duplicateValues" dxfId="213" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="223" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A61:B61">
-    <cfRule type="duplicateValues" dxfId="212" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="222" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="containsText" dxfId="211" priority="15" operator="containsText" text="closed">
+    <cfRule type="containsText" dxfId="221" priority="15" operator="containsText" text="closed">
       <formula>NOT(ISERROR(SEARCH("closed",I1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="210" priority="16" operator="containsText" text="abandoned">
+    <cfRule type="containsText" dxfId="220" priority="16" operator="containsText" text="abandoned">
       <formula>NOT(ISERROR(SEARCH("abandoned",I1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="209" priority="18" operator="containsText" text="late app">
+    <cfRule type="containsText" dxfId="219" priority="18" operator="containsText" text="late app">
       <formula>NOT(ISERROR(SEARCH("late app",I1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:L1048576 O78:O80 O83:O89 O92:O112 O115:O124 O126:O181 R136 R153 R159 R166 R173 R178 O183:O205 O208:O211 O213:O218 O220:O233 R225 O235:O237 O239:O248 I1:J1">
-    <cfRule type="containsText" dxfId="208" priority="21" operator="containsText" text="completed">
+  <conditionalFormatting sqref="I2:L1048576 O78:O80 O83:O89 O92:O112 O115:O124 O126:O181 R136 R153 R159 R166 R173 R178 O183:O205 O208:O211 O213:O218 O220:O233 R225 O235:O237 O239:O248 N276:O276 Q276 I1:J1">
+    <cfRule type="containsText" dxfId="218" priority="21" operator="containsText" text="completed">
       <formula>NOT(ISERROR(SEARCH("completed",I1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:J1048576">
-    <cfRule type="containsText" dxfId="207" priority="10" operator="containsText" text="no news">
+    <cfRule type="containsText" dxfId="217" priority="10" operator="containsText" text="no news">
       <formula>NOT(ISERROR(SEARCH("no news",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="206" priority="11" operator="containsText" text="offer">
+    <cfRule type="containsText" dxfId="216" priority="11" operator="containsText" text="offer">
       <formula>NOT(ISERROR(SEARCH("offer",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="205" priority="12" operator="containsText" text="fly out">
+    <cfRule type="containsText" dxfId="215" priority="12" operator="containsText" text="fly out">
       <formula>NOT(ISERROR(SEARCH("fly out",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="204" priority="13" operator="containsText" text="interview">
+    <cfRule type="containsText" dxfId="214" priority="13" operator="containsText" text="interview">
       <formula>NOT(ISERROR(SEARCH("interview",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="203" priority="14" operator="containsText" text="rejected">
+    <cfRule type="containsText" dxfId="213" priority="14" operator="containsText" text="rejected">
       <formula>NOT(ISERROR(SEARCH("rejected",J1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K1:L1048576 O78:O80 O83:O89 O92:O112 O115:O124 O126:O181 R136 R153 R159 R166 R173 R178 O183:O205 O208:O211 O213:O218 O220:O233 R225 O235:O237 O239:O248">
-    <cfRule type="containsText" dxfId="202" priority="19" operator="containsText" text="NO">
+  <conditionalFormatting sqref="K1:L1048576 O78:O80 O83:O89 O92:O112 O115:O124 O126:O181 R136 R153 R159 R166 R173 R178 O183:O205 O208:O211 O213:O218 O220:O233 R225 O235:O237 O239:O248 N276:O276 Q276">
+    <cfRule type="containsText" dxfId="212" priority="19" operator="containsText" text="NO">
       <formula>NOT(ISERROR(SEARCH("NO",K1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="201" priority="20" operator="containsText" text="YES">
+    <cfRule type="containsText" dxfId="211" priority="20" operator="containsText" text="YES">
       <formula>NOT(ISERROR(SEARCH("YES",K1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O250:O267">
-    <cfRule type="containsText" dxfId="200" priority="1" operator="containsText" text="NO">
+    <cfRule type="containsText" dxfId="210" priority="1" operator="containsText" text="NO">
       <formula>NOT(ISERROR(SEARCH("NO",O250)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="199" priority="2" operator="containsText" text="YES">
+    <cfRule type="containsText" dxfId="209" priority="2" operator="containsText" text="YES">
       <formula>NOT(ISERROR(SEARCH("YES",O250)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="198" priority="3" operator="containsText" text="completed">
+    <cfRule type="containsText" dxfId="208" priority="3" operator="containsText" text="completed">
       <formula>NOT(ISERROR(SEARCH("completed",O250)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -50620,7 +50785,7 @@
     <hyperlink ref="M17" r:id="rId79" xr:uid="{9A9A6BC9-B330-7842-A78C-4DCC88F5E19F}"/>
     <hyperlink ref="M32" r:id="rId80" xr:uid="{928CABEF-4FA6-E646-8140-7B6E43F8FB96}"/>
     <hyperlink ref="F177" r:id="rId81" xr:uid="{82BF1574-A6C6-1641-9FFE-615861E401FD}"/>
-    <hyperlink ref="F275" r:id="rId82" xr:uid="{3562807E-7FDA-F046-BA03-5DDD43072DB7}"/>
+    <hyperlink ref="F276" r:id="rId82" xr:uid="{3562807E-7FDA-F046-BA03-5DDD43072DB7}"/>
     <hyperlink ref="H215" r:id="rId83" display="mailto:ivanpaya@ua.es" xr:uid="{DEFB77A5-E57F-714C-BAB9-56DE82BA0B2E}"/>
     <hyperlink ref="H138" r:id="rId84" display="mailto:ari.hyytinen@hanken.fi" xr:uid="{7777B12A-FD99-4A43-A14B-A15661B760DC}"/>
     <hyperlink ref="H115" r:id="rId85" display="mailto:peter.haan@fu-berlin.de" xr:uid="{3D1A69ED-8F06-1246-B586-201CB349DB62}"/>
@@ -50648,15 +50813,16 @@
     <hyperlink ref="F271" r:id="rId107" xr:uid="{A8AE6398-5E3B-44CD-895F-D20F2BEC5279}"/>
     <hyperlink ref="F272" r:id="rId108" xr:uid="{34317180-A8EC-4C92-AB27-7AD534355822}"/>
     <hyperlink ref="F246" r:id="rId109" xr:uid="{81F56FF4-6BEE-4876-B897-D914C7668775}"/>
+    <hyperlink ref="E275" r:id="rId110" xr:uid="{ACFEBBD7-5100-486E-81B2-AD29703033C3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId110"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId111"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923E81FA-B875-3C4E-A189-1A21268FA086}">
-  <dimension ref="A1:C293"/>
+  <dimension ref="A1:C303"/>
   <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="32.83203125" customWidth="1"/>
@@ -53815,573 +53981,713 @@
         <v>403</v>
       </c>
     </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A294" s="1">
+        <v>46003</v>
+      </c>
+      <c r="B294" t="s">
+        <v>784</v>
+      </c>
+      <c r="C294" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A295" s="1">
+        <v>46003</v>
+      </c>
+      <c r="B295" t="s">
+        <v>368</v>
+      </c>
+      <c r="C295" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A296" s="1">
+        <v>46005</v>
+      </c>
+      <c r="B296" t="s">
+        <v>835</v>
+      </c>
+      <c r="C296" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A297" s="1">
+        <v>46005</v>
+      </c>
+      <c r="B297" t="s">
+        <v>845</v>
+      </c>
+      <c r="C297" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A298" s="1">
+        <v>46005</v>
+      </c>
+      <c r="B298" t="s">
+        <v>850</v>
+      </c>
+      <c r="C298" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A299" s="1">
+        <v>46005</v>
+      </c>
+      <c r="B299" t="s">
+        <v>854</v>
+      </c>
+      <c r="C299" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A300" s="1">
+        <v>46005</v>
+      </c>
+      <c r="B300" t="s">
+        <v>856</v>
+      </c>
+      <c r="C300" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A301" s="1">
+        <v>46005</v>
+      </c>
+      <c r="B301" t="s">
+        <v>867</v>
+      </c>
+      <c r="C301" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A302" s="1">
+        <v>46005</v>
+      </c>
+      <c r="B302" t="s">
+        <v>869</v>
+      </c>
+      <c r="C302" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A303" s="1">
+        <v>46005</v>
+      </c>
+      <c r="B303" t="s">
+        <v>872</v>
+      </c>
+      <c r="C303" t="s">
+        <v>97</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="B5">
-    <cfRule type="duplicateValues" dxfId="197" priority="205"/>
-    <cfRule type="duplicateValues" dxfId="196" priority="206"/>
+    <cfRule type="duplicateValues" dxfId="207" priority="215"/>
+    <cfRule type="duplicateValues" dxfId="206" priority="216"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B10">
-    <cfRule type="duplicateValues" dxfId="195" priority="204"/>
-    <cfRule type="duplicateValues" dxfId="194" priority="203"/>
+    <cfRule type="duplicateValues" dxfId="205" priority="214"/>
+    <cfRule type="duplicateValues" dxfId="204" priority="213"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B11">
+    <cfRule type="duplicateValues" dxfId="203" priority="212"/>
+    <cfRule type="duplicateValues" dxfId="202" priority="211"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B12">
+    <cfRule type="duplicateValues" dxfId="201" priority="210"/>
+    <cfRule type="duplicateValues" dxfId="200" priority="209"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B15">
+    <cfRule type="duplicateValues" dxfId="199" priority="208"/>
+    <cfRule type="duplicateValues" dxfId="198" priority="207"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B16">
+    <cfRule type="duplicateValues" dxfId="197" priority="206"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B17">
+    <cfRule type="duplicateValues" dxfId="196" priority="205"/>
+    <cfRule type="duplicateValues" dxfId="195" priority="204"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B18">
+    <cfRule type="duplicateValues" dxfId="194" priority="203"/>
     <cfRule type="duplicateValues" dxfId="193" priority="202"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B19">
     <cfRule type="duplicateValues" dxfId="192" priority="201"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B12">
-    <cfRule type="duplicateValues" dxfId="191" priority="200"/>
-    <cfRule type="duplicateValues" dxfId="190" priority="199"/>
+  <conditionalFormatting sqref="B22:B23">
+    <cfRule type="duplicateValues" dxfId="191" priority="199"/>
+    <cfRule type="duplicateValues" dxfId="190" priority="200"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B15">
-    <cfRule type="duplicateValues" dxfId="189" priority="198"/>
-    <cfRule type="duplicateValues" dxfId="188" priority="197"/>
+  <conditionalFormatting sqref="B24">
+    <cfRule type="duplicateValues" dxfId="189" priority="197"/>
+    <cfRule type="duplicateValues" dxfId="188" priority="198"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B16">
+  <conditionalFormatting sqref="B27">
     <cfRule type="duplicateValues" dxfId="187" priority="196"/>
+    <cfRule type="duplicateValues" dxfId="186" priority="195"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B17">
-    <cfRule type="duplicateValues" dxfId="186" priority="194"/>
-    <cfRule type="duplicateValues" dxfId="185" priority="195"/>
+  <conditionalFormatting sqref="B28">
+    <cfRule type="duplicateValues" dxfId="185" priority="194"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B18">
+  <conditionalFormatting sqref="B29">
     <cfRule type="duplicateValues" dxfId="184" priority="193"/>
     <cfRule type="duplicateValues" dxfId="183" priority="192"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B19">
+  <conditionalFormatting sqref="B30">
     <cfRule type="duplicateValues" dxfId="182" priority="191"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B22:B23">
+  <conditionalFormatting sqref="B31">
     <cfRule type="duplicateValues" dxfId="181" priority="190"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B32">
     <cfRule type="duplicateValues" dxfId="180" priority="189"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B24">
+  <conditionalFormatting sqref="B33">
     <cfRule type="duplicateValues" dxfId="179" priority="188"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B34">
     <cfRule type="duplicateValues" dxfId="178" priority="187"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B27">
+  <conditionalFormatting sqref="B35">
     <cfRule type="duplicateValues" dxfId="177" priority="186"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B37">
     <cfRule type="duplicateValues" dxfId="176" priority="185"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B28">
+  <conditionalFormatting sqref="B38">
     <cfRule type="duplicateValues" dxfId="175" priority="184"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B29">
-    <cfRule type="duplicateValues" dxfId="174" priority="182"/>
-    <cfRule type="duplicateValues" dxfId="173" priority="183"/>
+  <conditionalFormatting sqref="B42">
+    <cfRule type="duplicateValues" dxfId="174" priority="183"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B30">
+  <conditionalFormatting sqref="B43">
+    <cfRule type="duplicateValues" dxfId="173" priority="182"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B44:B45">
     <cfRule type="duplicateValues" dxfId="172" priority="181"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B31">
+  <conditionalFormatting sqref="B46">
     <cfRule type="duplicateValues" dxfId="171" priority="180"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B32">
+  <conditionalFormatting sqref="B48">
     <cfRule type="duplicateValues" dxfId="170" priority="179"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B33">
+  <conditionalFormatting sqref="B49">
     <cfRule type="duplicateValues" dxfId="169" priority="178"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B34">
+  <conditionalFormatting sqref="B51">
     <cfRule type="duplicateValues" dxfId="168" priority="177"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B35">
+  <conditionalFormatting sqref="B52">
     <cfRule type="duplicateValues" dxfId="167" priority="176"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B37">
-    <cfRule type="duplicateValues" dxfId="166" priority="175"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B38">
-    <cfRule type="duplicateValues" dxfId="165" priority="174"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B42">
-    <cfRule type="duplicateValues" dxfId="164" priority="173"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B43">
-    <cfRule type="duplicateValues" dxfId="163" priority="172"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B44:B45">
-    <cfRule type="duplicateValues" dxfId="162" priority="171"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B46">
-    <cfRule type="duplicateValues" dxfId="161" priority="170"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B48">
-    <cfRule type="duplicateValues" dxfId="160" priority="169"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B49">
-    <cfRule type="duplicateValues" dxfId="159" priority="168"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B51">
-    <cfRule type="duplicateValues" dxfId="158" priority="167"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B52">
-    <cfRule type="duplicateValues" dxfId="157" priority="166"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B58">
-    <cfRule type="duplicateValues" dxfId="156" priority="164"/>
+    <cfRule type="duplicateValues" dxfId="166" priority="174"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B59">
-    <cfRule type="duplicateValues" dxfId="155" priority="162"/>
+    <cfRule type="duplicateValues" dxfId="165" priority="172"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B63">
-    <cfRule type="duplicateValues" dxfId="154" priority="161"/>
+    <cfRule type="duplicateValues" dxfId="164" priority="171"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B64">
-    <cfRule type="duplicateValues" dxfId="153" priority="159"/>
+    <cfRule type="duplicateValues" dxfId="163" priority="169"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B66">
-    <cfRule type="duplicateValues" dxfId="152" priority="158"/>
+    <cfRule type="duplicateValues" dxfId="162" priority="168"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="151" priority="157"/>
-    <cfRule type="duplicateValues" dxfId="150" priority="156"/>
+    <cfRule type="duplicateValues" dxfId="161" priority="167"/>
+    <cfRule type="duplicateValues" dxfId="160" priority="166"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B68">
-    <cfRule type="duplicateValues" dxfId="149" priority="155"/>
+    <cfRule type="duplicateValues" dxfId="159" priority="165"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B69">
-    <cfRule type="duplicateValues" dxfId="148" priority="154"/>
+    <cfRule type="duplicateValues" dxfId="158" priority="164"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B70">
-    <cfRule type="duplicateValues" dxfId="147" priority="152"/>
+    <cfRule type="duplicateValues" dxfId="157" priority="162"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B72">
-    <cfRule type="duplicateValues" dxfId="146" priority="151"/>
+    <cfRule type="duplicateValues" dxfId="156" priority="161"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B73">
-    <cfRule type="duplicateValues" dxfId="145" priority="149"/>
+    <cfRule type="duplicateValues" dxfId="155" priority="159"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B74">
-    <cfRule type="duplicateValues" dxfId="144" priority="148"/>
+    <cfRule type="duplicateValues" dxfId="154" priority="158"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B75">
-    <cfRule type="duplicateValues" dxfId="143" priority="147"/>
+    <cfRule type="duplicateValues" dxfId="153" priority="157"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B76">
-    <cfRule type="duplicateValues" dxfId="142" priority="146"/>
+    <cfRule type="duplicateValues" dxfId="152" priority="156"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B77">
+    <cfRule type="duplicateValues" dxfId="151" priority="154"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B78">
+    <cfRule type="duplicateValues" dxfId="150" priority="153"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B83">
+    <cfRule type="duplicateValues" dxfId="149" priority="152"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B84">
+    <cfRule type="duplicateValues" dxfId="148" priority="151"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B85">
+    <cfRule type="duplicateValues" dxfId="147" priority="150"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B87">
+    <cfRule type="duplicateValues" dxfId="146" priority="149"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B88">
+    <cfRule type="duplicateValues" dxfId="145" priority="148"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B89">
+    <cfRule type="duplicateValues" dxfId="144" priority="147"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B90">
+    <cfRule type="duplicateValues" dxfId="143" priority="146"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B91">
+    <cfRule type="duplicateValues" dxfId="142" priority="145"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B92">
     <cfRule type="duplicateValues" dxfId="141" priority="144"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B78">
+  <conditionalFormatting sqref="B93">
     <cfRule type="duplicateValues" dxfId="140" priority="143"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B83">
+  <conditionalFormatting sqref="B94">
     <cfRule type="duplicateValues" dxfId="139" priority="142"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B84">
+  <conditionalFormatting sqref="B95">
     <cfRule type="duplicateValues" dxfId="138" priority="141"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B85">
+  <conditionalFormatting sqref="B96">
     <cfRule type="duplicateValues" dxfId="137" priority="140"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B87">
+  <conditionalFormatting sqref="B97">
     <cfRule type="duplicateValues" dxfId="136" priority="139"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B88">
+  <conditionalFormatting sqref="B98">
     <cfRule type="duplicateValues" dxfId="135" priority="138"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B89">
+  <conditionalFormatting sqref="B99">
     <cfRule type="duplicateValues" dxfId="134" priority="137"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B90">
+  <conditionalFormatting sqref="B100">
     <cfRule type="duplicateValues" dxfId="133" priority="136"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B91">
+  <conditionalFormatting sqref="B101">
     <cfRule type="duplicateValues" dxfId="132" priority="135"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B92">
+  <conditionalFormatting sqref="B104">
     <cfRule type="duplicateValues" dxfId="131" priority="134"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B93">
     <cfRule type="duplicateValues" dxfId="130" priority="133"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B94">
+  <conditionalFormatting sqref="B105:B106">
     <cfRule type="duplicateValues" dxfId="129" priority="132"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B95">
+  <conditionalFormatting sqref="B107">
     <cfRule type="duplicateValues" dxfId="128" priority="131"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B96">
+  <conditionalFormatting sqref="B108">
     <cfRule type="duplicateValues" dxfId="127" priority="130"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B97">
+  <conditionalFormatting sqref="B109">
     <cfRule type="duplicateValues" dxfId="126" priority="129"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B98">
+  <conditionalFormatting sqref="B110">
     <cfRule type="duplicateValues" dxfId="125" priority="128"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B99">
+  <conditionalFormatting sqref="B111">
     <cfRule type="duplicateValues" dxfId="124" priority="127"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B100">
+  <conditionalFormatting sqref="B112">
     <cfRule type="duplicateValues" dxfId="123" priority="126"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B101">
+  <conditionalFormatting sqref="B113">
     <cfRule type="duplicateValues" dxfId="122" priority="125"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B104">
+  <conditionalFormatting sqref="B114">
     <cfRule type="duplicateValues" dxfId="121" priority="124"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B115">
     <cfRule type="duplicateValues" dxfId="120" priority="123"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B105:B106">
+  <conditionalFormatting sqref="B116">
     <cfRule type="duplicateValues" dxfId="119" priority="122"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B107">
+  <conditionalFormatting sqref="B117">
     <cfRule type="duplicateValues" dxfId="118" priority="121"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B108">
+  <conditionalFormatting sqref="B118">
     <cfRule type="duplicateValues" dxfId="117" priority="120"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B109">
+  <conditionalFormatting sqref="B119">
     <cfRule type="duplicateValues" dxfId="116" priority="119"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B110">
+  <conditionalFormatting sqref="B120">
     <cfRule type="duplicateValues" dxfId="115" priority="118"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B111">
+  <conditionalFormatting sqref="B121">
     <cfRule type="duplicateValues" dxfId="114" priority="117"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B112">
+  <conditionalFormatting sqref="B122">
     <cfRule type="duplicateValues" dxfId="113" priority="116"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B113">
+  <conditionalFormatting sqref="B126">
     <cfRule type="duplicateValues" dxfId="112" priority="115"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B114">
+  <conditionalFormatting sqref="B127">
     <cfRule type="duplicateValues" dxfId="111" priority="114"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B115">
+  <conditionalFormatting sqref="B128">
     <cfRule type="duplicateValues" dxfId="110" priority="113"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B116">
+  <conditionalFormatting sqref="B129">
     <cfRule type="duplicateValues" dxfId="109" priority="112"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B117">
+  <conditionalFormatting sqref="B130">
     <cfRule type="duplicateValues" dxfId="108" priority="111"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B118">
+  <conditionalFormatting sqref="B131">
     <cfRule type="duplicateValues" dxfId="107" priority="110"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B119">
+  <conditionalFormatting sqref="B132">
     <cfRule type="duplicateValues" dxfId="106" priority="109"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B120">
+  <conditionalFormatting sqref="B133">
     <cfRule type="duplicateValues" dxfId="105" priority="108"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B121">
+  <conditionalFormatting sqref="B136">
     <cfRule type="duplicateValues" dxfId="104" priority="107"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B122">
+  <conditionalFormatting sqref="B137">
     <cfRule type="duplicateValues" dxfId="103" priority="106"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B126">
+  <conditionalFormatting sqref="B138">
     <cfRule type="duplicateValues" dxfId="102" priority="105"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B127">
+  <conditionalFormatting sqref="B139">
     <cfRule type="duplicateValues" dxfId="101" priority="104"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B128">
+  <conditionalFormatting sqref="B140">
     <cfRule type="duplicateValues" dxfId="100" priority="103"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B129">
+  <conditionalFormatting sqref="B141">
     <cfRule type="duplicateValues" dxfId="99" priority="102"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B130">
+  <conditionalFormatting sqref="B142">
     <cfRule type="duplicateValues" dxfId="98" priority="101"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B131">
+  <conditionalFormatting sqref="B143">
     <cfRule type="duplicateValues" dxfId="97" priority="100"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B132">
+  <conditionalFormatting sqref="B144">
     <cfRule type="duplicateValues" dxfId="96" priority="99"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B133">
+  <conditionalFormatting sqref="B145">
     <cfRule type="duplicateValues" dxfId="95" priority="98"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B136">
+  <conditionalFormatting sqref="B147">
     <cfRule type="duplicateValues" dxfId="94" priority="97"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B137">
+  <conditionalFormatting sqref="B148">
     <cfRule type="duplicateValues" dxfId="93" priority="96"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B138">
+  <conditionalFormatting sqref="B149">
     <cfRule type="duplicateValues" dxfId="92" priority="95"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B139">
+  <conditionalFormatting sqref="B150">
     <cfRule type="duplicateValues" dxfId="91" priority="94"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B140">
+  <conditionalFormatting sqref="B151">
     <cfRule type="duplicateValues" dxfId="90" priority="93"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B141">
+  <conditionalFormatting sqref="B152">
     <cfRule type="duplicateValues" dxfId="89" priority="92"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B142">
+  <conditionalFormatting sqref="B153">
     <cfRule type="duplicateValues" dxfId="88" priority="91"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B143">
+  <conditionalFormatting sqref="B154">
     <cfRule type="duplicateValues" dxfId="87" priority="90"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B144">
+  <conditionalFormatting sqref="B155">
     <cfRule type="duplicateValues" dxfId="86" priority="89"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B145">
+  <conditionalFormatting sqref="B156">
     <cfRule type="duplicateValues" dxfId="85" priority="88"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B147">
+  <conditionalFormatting sqref="B157">
     <cfRule type="duplicateValues" dxfId="84" priority="87"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B148">
+  <conditionalFormatting sqref="B171">
     <cfRule type="duplicateValues" dxfId="83" priority="86"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B149">
+  <conditionalFormatting sqref="B172">
     <cfRule type="duplicateValues" dxfId="82" priority="85"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B150">
+  <conditionalFormatting sqref="B174">
     <cfRule type="duplicateValues" dxfId="81" priority="84"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B151">
+  <conditionalFormatting sqref="B177:B178">
     <cfRule type="duplicateValues" dxfId="80" priority="83"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B152">
+  <conditionalFormatting sqref="B181">
     <cfRule type="duplicateValues" dxfId="79" priority="82"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B153">
+  <conditionalFormatting sqref="B182">
     <cfRule type="duplicateValues" dxfId="78" priority="81"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B154">
+  <conditionalFormatting sqref="B183">
     <cfRule type="duplicateValues" dxfId="77" priority="80"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B155">
+  <conditionalFormatting sqref="B184">
     <cfRule type="duplicateValues" dxfId="76" priority="79"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B156">
+  <conditionalFormatting sqref="B185">
     <cfRule type="duplicateValues" dxfId="75" priority="78"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B157">
+  <conditionalFormatting sqref="B186">
     <cfRule type="duplicateValues" dxfId="74" priority="77"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B171">
+  <conditionalFormatting sqref="B188">
     <cfRule type="duplicateValues" dxfId="73" priority="76"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B172">
+  <conditionalFormatting sqref="B189">
     <cfRule type="duplicateValues" dxfId="72" priority="75"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B174">
+  <conditionalFormatting sqref="B190">
     <cfRule type="duplicateValues" dxfId="71" priority="74"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B177:B178">
+  <conditionalFormatting sqref="B191">
     <cfRule type="duplicateValues" dxfId="70" priority="73"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B181">
+  <conditionalFormatting sqref="B192">
     <cfRule type="duplicateValues" dxfId="69" priority="72"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B182">
+  <conditionalFormatting sqref="B193">
     <cfRule type="duplicateValues" dxfId="68" priority="71"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B183">
+  <conditionalFormatting sqref="B195">
     <cfRule type="duplicateValues" dxfId="67" priority="70"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B184">
+  <conditionalFormatting sqref="B196">
     <cfRule type="duplicateValues" dxfId="66" priority="69"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B185">
+  <conditionalFormatting sqref="B197">
     <cfRule type="duplicateValues" dxfId="65" priority="68"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B186">
+  <conditionalFormatting sqref="B198">
     <cfRule type="duplicateValues" dxfId="64" priority="67"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B188">
+  <conditionalFormatting sqref="B199">
     <cfRule type="duplicateValues" dxfId="63" priority="66"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B189">
+  <conditionalFormatting sqref="B200">
     <cfRule type="duplicateValues" dxfId="62" priority="65"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B190">
+  <conditionalFormatting sqref="B201">
     <cfRule type="duplicateValues" dxfId="61" priority="64"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B191">
+  <conditionalFormatting sqref="B202">
     <cfRule type="duplicateValues" dxfId="60" priority="63"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B192">
+  <conditionalFormatting sqref="B203">
     <cfRule type="duplicateValues" dxfId="59" priority="62"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B193">
+  <conditionalFormatting sqref="B204">
     <cfRule type="duplicateValues" dxfId="58" priority="61"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B195">
+  <conditionalFormatting sqref="B205">
     <cfRule type="duplicateValues" dxfId="57" priority="60"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B196">
+  <conditionalFormatting sqref="B206">
     <cfRule type="duplicateValues" dxfId="56" priority="59"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B197">
+  <conditionalFormatting sqref="B207">
     <cfRule type="duplicateValues" dxfId="55" priority="58"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B198">
+  <conditionalFormatting sqref="B215">
     <cfRule type="duplicateValues" dxfId="54" priority="57"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B199">
+  <conditionalFormatting sqref="B218">
     <cfRule type="duplicateValues" dxfId="53" priority="56"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B200">
+  <conditionalFormatting sqref="B220">
     <cfRule type="duplicateValues" dxfId="52" priority="55"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B201">
+  <conditionalFormatting sqref="B222">
     <cfRule type="duplicateValues" dxfId="51" priority="54"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B202">
+  <conditionalFormatting sqref="B223">
     <cfRule type="duplicateValues" dxfId="50" priority="53"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B203">
+  <conditionalFormatting sqref="B224">
     <cfRule type="duplicateValues" dxfId="49" priority="52"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B204">
+  <conditionalFormatting sqref="B225">
     <cfRule type="duplicateValues" dxfId="48" priority="51"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B205">
+  <conditionalFormatting sqref="B227">
     <cfRule type="duplicateValues" dxfId="47" priority="50"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B206">
+  <conditionalFormatting sqref="B229">
     <cfRule type="duplicateValues" dxfId="46" priority="49"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B207">
+  <conditionalFormatting sqref="B230">
     <cfRule type="duplicateValues" dxfId="45" priority="48"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B215">
+  <conditionalFormatting sqref="B232">
     <cfRule type="duplicateValues" dxfId="44" priority="47"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B218">
+  <conditionalFormatting sqref="B233">
     <cfRule type="duplicateValues" dxfId="43" priority="46"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B220">
+  <conditionalFormatting sqref="B234">
     <cfRule type="duplicateValues" dxfId="42" priority="45"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B222">
+  <conditionalFormatting sqref="B235">
     <cfRule type="duplicateValues" dxfId="41" priority="44"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B223">
+  <conditionalFormatting sqref="B236">
     <cfRule type="duplicateValues" dxfId="40" priority="43"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B224">
+  <conditionalFormatting sqref="B237">
     <cfRule type="duplicateValues" dxfId="39" priority="42"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B225">
-    <cfRule type="duplicateValues" dxfId="38" priority="41"/>
+  <conditionalFormatting sqref="B239">
+    <cfRule type="duplicateValues" dxfId="38" priority="40"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B227">
-    <cfRule type="duplicateValues" dxfId="37" priority="40"/>
+  <conditionalFormatting sqref="B240">
+    <cfRule type="duplicateValues" dxfId="37" priority="39"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B229">
-    <cfRule type="duplicateValues" dxfId="36" priority="39"/>
+  <conditionalFormatting sqref="B241">
+    <cfRule type="duplicateValues" dxfId="36" priority="38"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B230">
-    <cfRule type="duplicateValues" dxfId="35" priority="38"/>
+  <conditionalFormatting sqref="B242">
+    <cfRule type="duplicateValues" dxfId="35" priority="37"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B232">
-    <cfRule type="duplicateValues" dxfId="34" priority="37"/>
+  <conditionalFormatting sqref="B243">
+    <cfRule type="duplicateValues" dxfId="34" priority="36"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B233">
-    <cfRule type="duplicateValues" dxfId="33" priority="36"/>
+  <conditionalFormatting sqref="B250">
+    <cfRule type="duplicateValues" dxfId="33" priority="35"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B234">
-    <cfRule type="duplicateValues" dxfId="32" priority="35"/>
+  <conditionalFormatting sqref="B251">
+    <cfRule type="duplicateValues" dxfId="32" priority="34"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B235">
-    <cfRule type="duplicateValues" dxfId="31" priority="34"/>
+  <conditionalFormatting sqref="B253">
+    <cfRule type="duplicateValues" dxfId="31" priority="33"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B236">
-    <cfRule type="duplicateValues" dxfId="30" priority="33"/>
+  <conditionalFormatting sqref="B255">
+    <cfRule type="duplicateValues" dxfId="30" priority="32"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B237">
-    <cfRule type="duplicateValues" dxfId="29" priority="32"/>
+  <conditionalFormatting sqref="B258:B259">
+    <cfRule type="duplicateValues" dxfId="29" priority="31"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B239">
+  <conditionalFormatting sqref="B260">
     <cfRule type="duplicateValues" dxfId="28" priority="30"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B240">
+  <conditionalFormatting sqref="B265:B267 B269">
     <cfRule type="duplicateValues" dxfId="27" priority="29"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B241">
+  <conditionalFormatting sqref="B268">
     <cfRule type="duplicateValues" dxfId="26" priority="28"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B242">
+  <conditionalFormatting sqref="B270">
     <cfRule type="duplicateValues" dxfId="25" priority="27"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B243">
+  <conditionalFormatting sqref="B271">
     <cfRule type="duplicateValues" dxfId="24" priority="26"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B250">
+  <conditionalFormatting sqref="B273">
     <cfRule type="duplicateValues" dxfId="23" priority="25"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B251">
+  <conditionalFormatting sqref="B275">
     <cfRule type="duplicateValues" dxfId="22" priority="24"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B253">
+  <conditionalFormatting sqref="B278">
     <cfRule type="duplicateValues" dxfId="21" priority="23"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B255">
+  <conditionalFormatting sqref="B279">
     <cfRule type="duplicateValues" dxfId="20" priority="22"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B258:B259">
+  <conditionalFormatting sqref="B280">
     <cfRule type="duplicateValues" dxfId="19" priority="21"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B260">
+  <conditionalFormatting sqref="B281">
     <cfRule type="duplicateValues" dxfId="18" priority="20"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B265:B267 B269">
+  <conditionalFormatting sqref="B282">
     <cfRule type="duplicateValues" dxfId="17" priority="19"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B268">
-    <cfRule type="duplicateValues" dxfId="16" priority="18"/>
+  <conditionalFormatting sqref="B283">
+    <cfRule type="duplicateValues" dxfId="16" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B270">
-    <cfRule type="duplicateValues" dxfId="15" priority="17"/>
+  <conditionalFormatting sqref="B284:B286">
+    <cfRule type="duplicateValues" dxfId="15" priority="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B271">
-    <cfRule type="duplicateValues" dxfId="14" priority="16"/>
+  <conditionalFormatting sqref="B287">
+    <cfRule type="duplicateValues" dxfId="14" priority="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B273">
-    <cfRule type="duplicateValues" dxfId="13" priority="15"/>
+  <conditionalFormatting sqref="B288">
+    <cfRule type="duplicateValues" dxfId="13" priority="14"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B275">
-    <cfRule type="duplicateValues" dxfId="12" priority="14"/>
+  <conditionalFormatting sqref="B291">
+    <cfRule type="duplicateValues" dxfId="12" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B278">
-    <cfRule type="duplicateValues" dxfId="11" priority="13"/>
+  <conditionalFormatting sqref="B292">
+    <cfRule type="duplicateValues" dxfId="11" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B279">
-    <cfRule type="duplicateValues" dxfId="10" priority="12"/>
+  <conditionalFormatting sqref="B293">
+    <cfRule type="duplicateValues" dxfId="10" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B280">
-    <cfRule type="duplicateValues" dxfId="9" priority="11"/>
+  <conditionalFormatting sqref="B294">
+    <cfRule type="duplicateValues" dxfId="9" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B281">
-    <cfRule type="duplicateValues" dxfId="8" priority="10"/>
+  <conditionalFormatting sqref="B295">
+    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B282">
-    <cfRule type="duplicateValues" dxfId="7" priority="9"/>
+  <conditionalFormatting sqref="B296">
+    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B283">
+  <conditionalFormatting sqref="B297">
     <cfRule type="duplicateValues" dxfId="6" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B284:B286">
+  <conditionalFormatting sqref="B298">
     <cfRule type="duplicateValues" dxfId="5" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B287">
+  <conditionalFormatting sqref="B299">
     <cfRule type="duplicateValues" dxfId="4" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B288">
+  <conditionalFormatting sqref="B300">
     <cfRule type="duplicateValues" dxfId="3" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B291">
+  <conditionalFormatting sqref="B301">
     <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B292">
+  <conditionalFormatting sqref="B302">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B293">
+  <conditionalFormatting sqref="B303">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -54404,15 +54710,15 @@
       </c>
       <c r="B1" s="15">
         <f>COUNTA(sum!A:A) -1</f>
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C1" s="22">
         <f>COUNTIF(sum!I:I, "completed")/(B1-COUNTIF(sum!I:I, "abandoned")-COUNTIF(sum!I:I, "late app"))</f>
-        <v>0.96254681647940077</v>
+        <v>0.99625468164794007</v>
       </c>
       <c r="D1" s="21">
         <f>COUNTIF(sum!I:I, "completed")</f>
-        <v>257</v>
+        <v>266</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.4">
@@ -54438,7 +54744,7 @@
       </c>
       <c r="C3" s="10">
         <f>COUNTIFS(sum!I:I,"completed", sum!K:K, "&lt;&gt;") / B3</f>
-        <v>0.98305084745762716</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="26" x14ac:dyDescent="0.6">
@@ -54447,7 +54753,7 @@
       </c>
       <c r="B5" s="15">
         <f>COUNTA(sum!J:J) -1</f>
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C5" s="14">
         <f>B5/B1</f>
@@ -54464,7 +54770,7 @@
       </c>
       <c r="C6" s="10">
         <f>B6/$B$5</f>
-        <v>0.93065693430656937</v>
+        <v>0.92727272727272725</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
@@ -54473,11 +54779,11 @@
       </c>
       <c r="B7" s="16">
         <f>COUNTIFS(sum!J:J,"rejected")</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" s="10">
         <f t="shared" ref="C7:C10" si="0">B7/$B$5</f>
-        <v>5.1094890510948905E-2</v>
+        <v>5.4545454545454543E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">
@@ -54490,7 +54796,7 @@
       </c>
       <c r="C8" s="10">
         <f t="shared" si="0"/>
-        <v>1.824817518248175E-2</v>
+        <v>1.8181818181818181E-2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">
@@ -54503,7 +54809,7 @@
       </c>
       <c r="C9" s="10">
         <f t="shared" si="0"/>
-        <v>3.6496350364963502E-3</v>
+        <v>3.6363636363636364E-3</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.4">

--- a/EconJM_status.xlsx
+++ b/EconJM_status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\javie\Dropbox\Work\Job Search\2025 EconJM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E27037DE-BB5E-4FF5-A759-F0B52699730A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D04130B4-A7A5-4357-BA59-A6B368A572B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" activeTab="2" xr2:uid="{6FE48536-7E5C-BF4C-9490-2A6392576298}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" activeTab="1" xr2:uid="{6FE48536-7E5C-BF4C-9490-2A6392576298}"/>
   </bookViews>
   <sheets>
     <sheet name="sum" sheetId="1" r:id="rId1"/>
@@ -428,7 +428,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2808" uniqueCount="880">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2814" uniqueCount="880">
   <si>
     <t>add_id</t>
   </si>
@@ -3285,7 +3285,17 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="227">
+  <dxfs count="228">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -44688,7 +44698,7 @@
         <v>96</v>
       </c>
       <c r="J179" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="K179" t="s">
         <v>309</v>
@@ -47269,7 +47279,7 @@
         <v>96</v>
       </c>
       <c r="J233" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="K233" t="s">
         <v>309</v>
@@ -49398,63 +49408,63 @@
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="A1:B208 A210:B1048576">
-    <cfRule type="duplicateValues" dxfId="226" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="227" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:B22">
-    <cfRule type="duplicateValues" dxfId="225" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="226" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A61:B61">
-    <cfRule type="duplicateValues" dxfId="224" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="225" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="containsText" dxfId="223" priority="15" operator="containsText" text="closed">
+    <cfRule type="containsText" dxfId="224" priority="15" operator="containsText" text="closed">
       <formula>NOT(ISERROR(SEARCH("closed",I1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="222" priority="16" operator="containsText" text="abandoned">
+    <cfRule type="containsText" dxfId="223" priority="16" operator="containsText" text="abandoned">
       <formula>NOT(ISERROR(SEARCH("abandoned",I1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="221" priority="18" operator="containsText" text="late app">
+    <cfRule type="containsText" dxfId="222" priority="18" operator="containsText" text="late app">
       <formula>NOT(ISERROR(SEARCH("late app",I1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:L1048576 P78:P80 P83:P89 P92:P112 P115:P124 P126:P181 S136 S153 S159 S166 S173 S178 P183:P205 P208:P211 P213:P218 P220:P233 S225 P235:P237 P239:P248 P276 R276 I1:J1">
-    <cfRule type="containsText" dxfId="220" priority="21" operator="containsText" text="completed">
+    <cfRule type="containsText" dxfId="221" priority="21" operator="containsText" text="completed">
       <formula>NOT(ISERROR(SEARCH("completed",I1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:J1048576">
-    <cfRule type="containsText" dxfId="219" priority="10" operator="containsText" text="no news">
+    <cfRule type="containsText" dxfId="220" priority="10" operator="containsText" text="no news">
       <formula>NOT(ISERROR(SEARCH("no news",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="218" priority="11" operator="containsText" text="offer">
+    <cfRule type="containsText" dxfId="219" priority="11" operator="containsText" text="offer">
       <formula>NOT(ISERROR(SEARCH("offer",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="217" priority="12" operator="containsText" text="fly out">
+    <cfRule type="containsText" dxfId="218" priority="12" operator="containsText" text="fly out">
       <formula>NOT(ISERROR(SEARCH("fly out",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="216" priority="13" operator="containsText" text="interview">
+    <cfRule type="containsText" dxfId="217" priority="13" operator="containsText" text="interview">
       <formula>NOT(ISERROR(SEARCH("interview",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="215" priority="14" operator="containsText" text="rejected">
+    <cfRule type="containsText" dxfId="216" priority="14" operator="containsText" text="rejected">
       <formula>NOT(ISERROR(SEARCH("rejected",J1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1:L1048576 P78:P80 P83:P89 P92:P112 P115:P124 P126:P181 S136 S153 S159 S166 S173 S178 P183:P205 P208:P211 P213:P218 P220:P233 S225 P235:P237 P239:P248 P276 R276">
-    <cfRule type="containsText" dxfId="214" priority="19" operator="containsText" text="NO">
+    <cfRule type="containsText" dxfId="215" priority="19" operator="containsText" text="NO">
       <formula>NOT(ISERROR(SEARCH("NO",K1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="213" priority="20" operator="containsText" text="YES">
+    <cfRule type="containsText" dxfId="214" priority="20" operator="containsText" text="YES">
       <formula>NOT(ISERROR(SEARCH("YES",K1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P250:P267">
-    <cfRule type="containsText" dxfId="212" priority="1" operator="containsText" text="NO">
+    <cfRule type="containsText" dxfId="213" priority="1" operator="containsText" text="NO">
       <formula>NOT(ISERROR(SEARCH("NO",P250)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="211" priority="2" operator="containsText" text="YES">
+    <cfRule type="containsText" dxfId="212" priority="2" operator="containsText" text="YES">
       <formula>NOT(ISERROR(SEARCH("YES",P250)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="210" priority="3" operator="containsText" text="completed">
+    <cfRule type="containsText" dxfId="211" priority="3" operator="containsText" text="completed">
       <formula>NOT(ISERROR(SEARCH("completed",P250)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -49577,7 +49587,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923E81FA-B875-3C4E-A189-1A21268FA086}">
-  <dimension ref="A1:C306"/>
+  <dimension ref="A1:C309"/>
   <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="32.83203125" customWidth="1"/>
@@ -52879,609 +52889,645 @@
         <v>403</v>
       </c>
     </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A307" s="1">
+        <v>46010</v>
+      </c>
+      <c r="B307" t="s">
+        <v>578</v>
+      </c>
+      <c r="C307" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A308" s="1">
+        <v>46010</v>
+      </c>
+      <c r="B308" t="s">
+        <v>763</v>
+      </c>
+      <c r="C308" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A309" s="1">
+        <v>46010</v>
+      </c>
+      <c r="B309" t="s">
+        <v>430</v>
+      </c>
+      <c r="C309" t="s">
+        <v>403</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="B5">
-    <cfRule type="duplicateValues" dxfId="209" priority="217"/>
-    <cfRule type="duplicateValues" dxfId="208" priority="218"/>
+    <cfRule type="duplicateValues" dxfId="210" priority="218"/>
+    <cfRule type="duplicateValues" dxfId="209" priority="219"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B10">
+    <cfRule type="duplicateValues" dxfId="208" priority="217"/>
     <cfRule type="duplicateValues" dxfId="207" priority="216"/>
-    <cfRule type="duplicateValues" dxfId="206" priority="215"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B11">
-    <cfRule type="duplicateValues" dxfId="205" priority="213"/>
-    <cfRule type="duplicateValues" dxfId="204" priority="214"/>
+    <cfRule type="duplicateValues" dxfId="206" priority="214"/>
+    <cfRule type="duplicateValues" dxfId="205" priority="215"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12">
+    <cfRule type="duplicateValues" dxfId="204" priority="213"/>
     <cfRule type="duplicateValues" dxfId="203" priority="212"/>
-    <cfRule type="duplicateValues" dxfId="202" priority="211"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15">
+    <cfRule type="duplicateValues" dxfId="202" priority="211"/>
     <cfRule type="duplicateValues" dxfId="201" priority="210"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B16">
     <cfRule type="duplicateValues" dxfId="200" priority="209"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B16">
-    <cfRule type="duplicateValues" dxfId="199" priority="208"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B17">
-    <cfRule type="duplicateValues" dxfId="198" priority="206"/>
-    <cfRule type="duplicateValues" dxfId="197" priority="207"/>
+    <cfRule type="duplicateValues" dxfId="199" priority="207"/>
+    <cfRule type="duplicateValues" dxfId="198" priority="208"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B18">
+    <cfRule type="duplicateValues" dxfId="197" priority="206"/>
     <cfRule type="duplicateValues" dxfId="196" priority="205"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B19">
     <cfRule type="duplicateValues" dxfId="195" priority="204"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B19">
+  <conditionalFormatting sqref="B22:B23">
     <cfRule type="duplicateValues" dxfId="194" priority="203"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B22:B23">
     <cfRule type="duplicateValues" dxfId="193" priority="202"/>
-    <cfRule type="duplicateValues" dxfId="192" priority="201"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B24">
+    <cfRule type="duplicateValues" dxfId="192" priority="201"/>
     <cfRule type="duplicateValues" dxfId="191" priority="200"/>
-    <cfRule type="duplicateValues" dxfId="190" priority="199"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B27">
+    <cfRule type="duplicateValues" dxfId="190" priority="199"/>
     <cfRule type="duplicateValues" dxfId="189" priority="198"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B28">
     <cfRule type="duplicateValues" dxfId="188" priority="197"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B28">
-    <cfRule type="duplicateValues" dxfId="187" priority="196"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B29">
-    <cfRule type="duplicateValues" dxfId="186" priority="194"/>
-    <cfRule type="duplicateValues" dxfId="185" priority="195"/>
+    <cfRule type="duplicateValues" dxfId="187" priority="195"/>
+    <cfRule type="duplicateValues" dxfId="186" priority="196"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30">
+    <cfRule type="duplicateValues" dxfId="185" priority="194"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31">
     <cfRule type="duplicateValues" dxfId="184" priority="193"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B31">
+  <conditionalFormatting sqref="B32">
     <cfRule type="duplicateValues" dxfId="183" priority="192"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B32">
+  <conditionalFormatting sqref="B33">
     <cfRule type="duplicateValues" dxfId="182" priority="191"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B33">
+  <conditionalFormatting sqref="B34">
     <cfRule type="duplicateValues" dxfId="181" priority="190"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B34">
+  <conditionalFormatting sqref="B35">
     <cfRule type="duplicateValues" dxfId="180" priority="189"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B35">
+  <conditionalFormatting sqref="B37">
     <cfRule type="duplicateValues" dxfId="179" priority="188"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B37">
+  <conditionalFormatting sqref="B38">
     <cfRule type="duplicateValues" dxfId="178" priority="187"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B38">
+  <conditionalFormatting sqref="B42">
     <cfRule type="duplicateValues" dxfId="177" priority="186"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B42">
+  <conditionalFormatting sqref="B43">
     <cfRule type="duplicateValues" dxfId="176" priority="185"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B43">
+  <conditionalFormatting sqref="B44:B45">
     <cfRule type="duplicateValues" dxfId="175" priority="184"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B44:B45">
+  <conditionalFormatting sqref="B46">
     <cfRule type="duplicateValues" dxfId="174" priority="183"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B46">
+  <conditionalFormatting sqref="B48">
     <cfRule type="duplicateValues" dxfId="173" priority="182"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B48">
+  <conditionalFormatting sqref="B49">
     <cfRule type="duplicateValues" dxfId="172" priority="181"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B49">
+  <conditionalFormatting sqref="B51">
     <cfRule type="duplicateValues" dxfId="171" priority="180"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B51">
+  <conditionalFormatting sqref="B52">
     <cfRule type="duplicateValues" dxfId="170" priority="179"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B52">
-    <cfRule type="duplicateValues" dxfId="169" priority="178"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B58">
-    <cfRule type="duplicateValues" dxfId="168" priority="176"/>
+    <cfRule type="duplicateValues" dxfId="169" priority="177"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B59">
+    <cfRule type="duplicateValues" dxfId="168" priority="175"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B63">
     <cfRule type="duplicateValues" dxfId="167" priority="174"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B63">
-    <cfRule type="duplicateValues" dxfId="166" priority="173"/>
+  <conditionalFormatting sqref="B64">
+    <cfRule type="duplicateValues" dxfId="166" priority="172"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B64">
+  <conditionalFormatting sqref="B66">
     <cfRule type="duplicateValues" dxfId="165" priority="171"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B66">
+  <conditionalFormatting sqref="B67">
     <cfRule type="duplicateValues" dxfId="164" priority="170"/>
+    <cfRule type="duplicateValues" dxfId="163" priority="169"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="163" priority="169"/>
+  <conditionalFormatting sqref="B68">
     <cfRule type="duplicateValues" dxfId="162" priority="168"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B68">
+  <conditionalFormatting sqref="B69">
     <cfRule type="duplicateValues" dxfId="161" priority="167"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B69">
-    <cfRule type="duplicateValues" dxfId="160" priority="166"/>
+  <conditionalFormatting sqref="B70">
+    <cfRule type="duplicateValues" dxfId="160" priority="165"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B70">
+  <conditionalFormatting sqref="B72">
     <cfRule type="duplicateValues" dxfId="159" priority="164"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B72">
-    <cfRule type="duplicateValues" dxfId="158" priority="163"/>
+  <conditionalFormatting sqref="B73">
+    <cfRule type="duplicateValues" dxfId="158" priority="162"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B73">
+  <conditionalFormatting sqref="B74">
     <cfRule type="duplicateValues" dxfId="157" priority="161"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B74">
+  <conditionalFormatting sqref="B75">
     <cfRule type="duplicateValues" dxfId="156" priority="160"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B75">
+  <conditionalFormatting sqref="B76">
     <cfRule type="duplicateValues" dxfId="155" priority="159"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B76">
-    <cfRule type="duplicateValues" dxfId="154" priority="158"/>
+  <conditionalFormatting sqref="B77">
+    <cfRule type="duplicateValues" dxfId="154" priority="157"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B77">
+  <conditionalFormatting sqref="B78">
     <cfRule type="duplicateValues" dxfId="153" priority="156"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B78">
+  <conditionalFormatting sqref="B83">
     <cfRule type="duplicateValues" dxfId="152" priority="155"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B83">
+  <conditionalFormatting sqref="B84">
     <cfRule type="duplicateValues" dxfId="151" priority="154"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B84">
+  <conditionalFormatting sqref="B85">
     <cfRule type="duplicateValues" dxfId="150" priority="153"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B85">
+  <conditionalFormatting sqref="B87">
     <cfRule type="duplicateValues" dxfId="149" priority="152"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B87">
+  <conditionalFormatting sqref="B88">
     <cfRule type="duplicateValues" dxfId="148" priority="151"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B88">
+  <conditionalFormatting sqref="B89">
     <cfRule type="duplicateValues" dxfId="147" priority="150"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B89">
+  <conditionalFormatting sqref="B90">
     <cfRule type="duplicateValues" dxfId="146" priority="149"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B90">
+  <conditionalFormatting sqref="B91">
     <cfRule type="duplicateValues" dxfId="145" priority="148"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B91">
+  <conditionalFormatting sqref="B92">
     <cfRule type="duplicateValues" dxfId="144" priority="147"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B92">
+  <conditionalFormatting sqref="B93">
     <cfRule type="duplicateValues" dxfId="143" priority="146"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B93">
+  <conditionalFormatting sqref="B94">
     <cfRule type="duplicateValues" dxfId="142" priority="145"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B94">
+  <conditionalFormatting sqref="B95">
     <cfRule type="duplicateValues" dxfId="141" priority="144"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B95">
+  <conditionalFormatting sqref="B96">
     <cfRule type="duplicateValues" dxfId="140" priority="143"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B96">
+  <conditionalFormatting sqref="B97">
     <cfRule type="duplicateValues" dxfId="139" priority="142"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B97">
+  <conditionalFormatting sqref="B98">
     <cfRule type="duplicateValues" dxfId="138" priority="141"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B98">
+  <conditionalFormatting sqref="B99">
     <cfRule type="duplicateValues" dxfId="137" priority="140"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B99">
+  <conditionalFormatting sqref="B100">
     <cfRule type="duplicateValues" dxfId="136" priority="139"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B100">
+  <conditionalFormatting sqref="B101">
     <cfRule type="duplicateValues" dxfId="135" priority="138"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B101">
-    <cfRule type="duplicateValues" dxfId="134" priority="137"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B104">
-    <cfRule type="duplicateValues" dxfId="133" priority="135"/>
-    <cfRule type="duplicateValues" dxfId="132" priority="136"/>
+    <cfRule type="duplicateValues" dxfId="134" priority="136"/>
+    <cfRule type="duplicateValues" dxfId="133" priority="137"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B105:B106">
+    <cfRule type="duplicateValues" dxfId="132" priority="135"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B107">
     <cfRule type="duplicateValues" dxfId="131" priority="134"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B107">
+  <conditionalFormatting sqref="B108">
     <cfRule type="duplicateValues" dxfId="130" priority="133"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B108">
+  <conditionalFormatting sqref="B109">
     <cfRule type="duplicateValues" dxfId="129" priority="132"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B109">
+  <conditionalFormatting sqref="B110">
     <cfRule type="duplicateValues" dxfId="128" priority="131"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B110">
+  <conditionalFormatting sqref="B111">
     <cfRule type="duplicateValues" dxfId="127" priority="130"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B111">
+  <conditionalFormatting sqref="B112">
     <cfRule type="duplicateValues" dxfId="126" priority="129"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B112">
+  <conditionalFormatting sqref="B113">
     <cfRule type="duplicateValues" dxfId="125" priority="128"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B113">
+  <conditionalFormatting sqref="B114">
     <cfRule type="duplicateValues" dxfId="124" priority="127"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B114">
+  <conditionalFormatting sqref="B115">
     <cfRule type="duplicateValues" dxfId="123" priority="126"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B115">
+  <conditionalFormatting sqref="B116">
     <cfRule type="duplicateValues" dxfId="122" priority="125"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B116">
+  <conditionalFormatting sqref="B117">
     <cfRule type="duplicateValues" dxfId="121" priority="124"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B117">
+  <conditionalFormatting sqref="B118">
     <cfRule type="duplicateValues" dxfId="120" priority="123"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B118">
+  <conditionalFormatting sqref="B119">
     <cfRule type="duplicateValues" dxfId="119" priority="122"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B119">
+  <conditionalFormatting sqref="B120">
     <cfRule type="duplicateValues" dxfId="118" priority="121"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B120">
+  <conditionalFormatting sqref="B121">
     <cfRule type="duplicateValues" dxfId="117" priority="120"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B121">
+  <conditionalFormatting sqref="B122">
     <cfRule type="duplicateValues" dxfId="116" priority="119"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B122">
+  <conditionalFormatting sqref="B126">
     <cfRule type="duplicateValues" dxfId="115" priority="118"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B126">
+  <conditionalFormatting sqref="B127">
     <cfRule type="duplicateValues" dxfId="114" priority="117"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B127">
+  <conditionalFormatting sqref="B128">
     <cfRule type="duplicateValues" dxfId="113" priority="116"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B128">
+  <conditionalFormatting sqref="B129">
     <cfRule type="duplicateValues" dxfId="112" priority="115"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B129">
+  <conditionalFormatting sqref="B130">
     <cfRule type="duplicateValues" dxfId="111" priority="114"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B130">
+  <conditionalFormatting sqref="B131">
     <cfRule type="duplicateValues" dxfId="110" priority="113"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B131">
+  <conditionalFormatting sqref="B132">
     <cfRule type="duplicateValues" dxfId="109" priority="112"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B132">
+  <conditionalFormatting sqref="B133">
     <cfRule type="duplicateValues" dxfId="108" priority="111"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B133">
+  <conditionalFormatting sqref="B136">
     <cfRule type="duplicateValues" dxfId="107" priority="110"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B136">
+  <conditionalFormatting sqref="B137">
     <cfRule type="duplicateValues" dxfId="106" priority="109"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B137">
+  <conditionalFormatting sqref="B138">
     <cfRule type="duplicateValues" dxfId="105" priority="108"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B138">
+  <conditionalFormatting sqref="B139">
     <cfRule type="duplicateValues" dxfId="104" priority="107"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B139">
+  <conditionalFormatting sqref="B140">
     <cfRule type="duplicateValues" dxfId="103" priority="106"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B140">
+  <conditionalFormatting sqref="B141">
     <cfRule type="duplicateValues" dxfId="102" priority="105"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B141">
+  <conditionalFormatting sqref="B142">
     <cfRule type="duplicateValues" dxfId="101" priority="104"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B142">
+  <conditionalFormatting sqref="B143">
     <cfRule type="duplicateValues" dxfId="100" priority="103"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B143">
+  <conditionalFormatting sqref="B144">
     <cfRule type="duplicateValues" dxfId="99" priority="102"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B144">
+  <conditionalFormatting sqref="B145">
     <cfRule type="duplicateValues" dxfId="98" priority="101"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B145">
+  <conditionalFormatting sqref="B147">
     <cfRule type="duplicateValues" dxfId="97" priority="100"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B147">
+  <conditionalFormatting sqref="B148">
     <cfRule type="duplicateValues" dxfId="96" priority="99"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B148">
+  <conditionalFormatting sqref="B149">
     <cfRule type="duplicateValues" dxfId="95" priority="98"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B149">
+  <conditionalFormatting sqref="B150">
     <cfRule type="duplicateValues" dxfId="94" priority="97"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B150">
+  <conditionalFormatting sqref="B151">
     <cfRule type="duplicateValues" dxfId="93" priority="96"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B151">
+  <conditionalFormatting sqref="B152">
     <cfRule type="duplicateValues" dxfId="92" priority="95"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B152">
+  <conditionalFormatting sqref="B153">
     <cfRule type="duplicateValues" dxfId="91" priority="94"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B153">
+  <conditionalFormatting sqref="B154">
     <cfRule type="duplicateValues" dxfId="90" priority="93"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B154">
+  <conditionalFormatting sqref="B155">
     <cfRule type="duplicateValues" dxfId="89" priority="92"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B155">
+  <conditionalFormatting sqref="B156">
     <cfRule type="duplicateValues" dxfId="88" priority="91"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B156">
+  <conditionalFormatting sqref="B157">
     <cfRule type="duplicateValues" dxfId="87" priority="90"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B157">
+  <conditionalFormatting sqref="B171">
     <cfRule type="duplicateValues" dxfId="86" priority="89"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B171">
+  <conditionalFormatting sqref="B172">
     <cfRule type="duplicateValues" dxfId="85" priority="88"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B172">
+  <conditionalFormatting sqref="B174">
     <cfRule type="duplicateValues" dxfId="84" priority="87"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B174">
+  <conditionalFormatting sqref="B177:B178">
     <cfRule type="duplicateValues" dxfId="83" priority="86"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B177:B178">
+  <conditionalFormatting sqref="B181">
     <cfRule type="duplicateValues" dxfId="82" priority="85"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B181">
+  <conditionalFormatting sqref="B182">
     <cfRule type="duplicateValues" dxfId="81" priority="84"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B182">
+  <conditionalFormatting sqref="B183">
     <cfRule type="duplicateValues" dxfId="80" priority="83"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B183">
+  <conditionalFormatting sqref="B184">
     <cfRule type="duplicateValues" dxfId="79" priority="82"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B184">
+  <conditionalFormatting sqref="B185">
     <cfRule type="duplicateValues" dxfId="78" priority="81"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B185">
+  <conditionalFormatting sqref="B186">
     <cfRule type="duplicateValues" dxfId="77" priority="80"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B186">
+  <conditionalFormatting sqref="B188">
     <cfRule type="duplicateValues" dxfId="76" priority="79"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B188">
+  <conditionalFormatting sqref="B189">
     <cfRule type="duplicateValues" dxfId="75" priority="78"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B189">
+  <conditionalFormatting sqref="B190">
     <cfRule type="duplicateValues" dxfId="74" priority="77"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B190">
+  <conditionalFormatting sqref="B191">
     <cfRule type="duplicateValues" dxfId="73" priority="76"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B191">
+  <conditionalFormatting sqref="B192">
     <cfRule type="duplicateValues" dxfId="72" priority="75"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B192">
+  <conditionalFormatting sqref="B193">
     <cfRule type="duplicateValues" dxfId="71" priority="74"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B193">
+  <conditionalFormatting sqref="B195">
     <cfRule type="duplicateValues" dxfId="70" priority="73"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B195">
+  <conditionalFormatting sqref="B196">
     <cfRule type="duplicateValues" dxfId="69" priority="72"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B196">
+  <conditionalFormatting sqref="B197">
     <cfRule type="duplicateValues" dxfId="68" priority="71"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B197">
+  <conditionalFormatting sqref="B198">
     <cfRule type="duplicateValues" dxfId="67" priority="70"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B198">
+  <conditionalFormatting sqref="B199">
     <cfRule type="duplicateValues" dxfId="66" priority="69"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B199">
+  <conditionalFormatting sqref="B200">
     <cfRule type="duplicateValues" dxfId="65" priority="68"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B200">
+  <conditionalFormatting sqref="B201">
     <cfRule type="duplicateValues" dxfId="64" priority="67"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B201">
+  <conditionalFormatting sqref="B202">
     <cfRule type="duplicateValues" dxfId="63" priority="66"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B202">
+  <conditionalFormatting sqref="B203">
     <cfRule type="duplicateValues" dxfId="62" priority="65"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B203">
+  <conditionalFormatting sqref="B204">
     <cfRule type="duplicateValues" dxfId="61" priority="64"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B204">
+  <conditionalFormatting sqref="B205">
     <cfRule type="duplicateValues" dxfId="60" priority="63"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B205">
+  <conditionalFormatting sqref="B206">
     <cfRule type="duplicateValues" dxfId="59" priority="62"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B206">
+  <conditionalFormatting sqref="B207">
     <cfRule type="duplicateValues" dxfId="58" priority="61"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B207">
+  <conditionalFormatting sqref="B215">
     <cfRule type="duplicateValues" dxfId="57" priority="60"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B215">
+  <conditionalFormatting sqref="B218">
     <cfRule type="duplicateValues" dxfId="56" priority="59"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B218">
+  <conditionalFormatting sqref="B220">
     <cfRule type="duplicateValues" dxfId="55" priority="58"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B220">
+  <conditionalFormatting sqref="B222">
     <cfRule type="duplicateValues" dxfId="54" priority="57"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B222">
+  <conditionalFormatting sqref="B223">
     <cfRule type="duplicateValues" dxfId="53" priority="56"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B223">
+  <conditionalFormatting sqref="B224">
     <cfRule type="duplicateValues" dxfId="52" priority="55"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B224">
+  <conditionalFormatting sqref="B225">
     <cfRule type="duplicateValues" dxfId="51" priority="54"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B225">
+  <conditionalFormatting sqref="B227">
     <cfRule type="duplicateValues" dxfId="50" priority="53"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B227">
+  <conditionalFormatting sqref="B229">
     <cfRule type="duplicateValues" dxfId="49" priority="52"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B229">
+  <conditionalFormatting sqref="B230">
     <cfRule type="duplicateValues" dxfId="48" priority="51"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B230">
+  <conditionalFormatting sqref="B232">
     <cfRule type="duplicateValues" dxfId="47" priority="50"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B232">
+  <conditionalFormatting sqref="B233">
     <cfRule type="duplicateValues" dxfId="46" priority="49"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B233">
+  <conditionalFormatting sqref="B234">
     <cfRule type="duplicateValues" dxfId="45" priority="48"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B234">
+  <conditionalFormatting sqref="B235">
     <cfRule type="duplicateValues" dxfId="44" priority="47"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B235">
+  <conditionalFormatting sqref="B236">
     <cfRule type="duplicateValues" dxfId="43" priority="46"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B236">
+  <conditionalFormatting sqref="B237">
     <cfRule type="duplicateValues" dxfId="42" priority="45"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B237">
-    <cfRule type="duplicateValues" dxfId="41" priority="44"/>
+  <conditionalFormatting sqref="B239">
+    <cfRule type="duplicateValues" dxfId="41" priority="43"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B239">
+  <conditionalFormatting sqref="B240">
     <cfRule type="duplicateValues" dxfId="40" priority="42"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B240">
+  <conditionalFormatting sqref="B241">
     <cfRule type="duplicateValues" dxfId="39" priority="41"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B241">
+  <conditionalFormatting sqref="B242">
     <cfRule type="duplicateValues" dxfId="38" priority="40"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B242">
+  <conditionalFormatting sqref="B243">
     <cfRule type="duplicateValues" dxfId="37" priority="39"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B243">
+  <conditionalFormatting sqref="B250">
     <cfRule type="duplicateValues" dxfId="36" priority="38"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B250">
+  <conditionalFormatting sqref="B251">
     <cfRule type="duplicateValues" dxfId="35" priority="37"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B251">
+  <conditionalFormatting sqref="B253">
     <cfRule type="duplicateValues" dxfId="34" priority="36"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B253">
+  <conditionalFormatting sqref="B255">
     <cfRule type="duplicateValues" dxfId="33" priority="35"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B255">
+  <conditionalFormatting sqref="B258:B259">
     <cfRule type="duplicateValues" dxfId="32" priority="34"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B258:B259">
+  <conditionalFormatting sqref="B260">
     <cfRule type="duplicateValues" dxfId="31" priority="33"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B260">
+  <conditionalFormatting sqref="B265:B267 B269">
     <cfRule type="duplicateValues" dxfId="30" priority="32"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B265:B267 B269">
+  <conditionalFormatting sqref="B268">
     <cfRule type="duplicateValues" dxfId="29" priority="31"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B268">
+  <conditionalFormatting sqref="B270">
     <cfRule type="duplicateValues" dxfId="28" priority="30"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B270">
+  <conditionalFormatting sqref="B271">
     <cfRule type="duplicateValues" dxfId="27" priority="29"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B271">
+  <conditionalFormatting sqref="B273">
     <cfRule type="duplicateValues" dxfId="26" priority="28"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B273">
+  <conditionalFormatting sqref="B275">
     <cfRule type="duplicateValues" dxfId="25" priority="27"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B275">
+  <conditionalFormatting sqref="B278">
     <cfRule type="duplicateValues" dxfId="24" priority="26"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B278">
+  <conditionalFormatting sqref="B279">
     <cfRule type="duplicateValues" dxfId="23" priority="25"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B279">
+  <conditionalFormatting sqref="B280">
     <cfRule type="duplicateValues" dxfId="22" priority="24"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B280">
+  <conditionalFormatting sqref="B281">
     <cfRule type="duplicateValues" dxfId="21" priority="23"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B281">
+  <conditionalFormatting sqref="B282">
     <cfRule type="duplicateValues" dxfId="20" priority="22"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B282">
-    <cfRule type="duplicateValues" dxfId="19" priority="21"/>
+  <conditionalFormatting sqref="B283">
+    <cfRule type="duplicateValues" dxfId="19" priority="20"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B283">
+  <conditionalFormatting sqref="B284:B286">
     <cfRule type="duplicateValues" dxfId="18" priority="19"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B284:B286">
+  <conditionalFormatting sqref="B287">
     <cfRule type="duplicateValues" dxfId="17" priority="18"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B287">
+  <conditionalFormatting sqref="B288">
     <cfRule type="duplicateValues" dxfId="16" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B288">
+  <conditionalFormatting sqref="B291">
     <cfRule type="duplicateValues" dxfId="15" priority="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B291">
+  <conditionalFormatting sqref="B292">
     <cfRule type="duplicateValues" dxfId="14" priority="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B292">
+  <conditionalFormatting sqref="B293">
     <cfRule type="duplicateValues" dxfId="13" priority="14"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B293">
+  <conditionalFormatting sqref="B294">
     <cfRule type="duplicateValues" dxfId="12" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B294">
+  <conditionalFormatting sqref="B295">
     <cfRule type="duplicateValues" dxfId="11" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B295">
+  <conditionalFormatting sqref="B296">
     <cfRule type="duplicateValues" dxfId="10" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B296">
+  <conditionalFormatting sqref="B297">
     <cfRule type="duplicateValues" dxfId="9" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B297">
+  <conditionalFormatting sqref="B298">
     <cfRule type="duplicateValues" dxfId="8" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B298">
+  <conditionalFormatting sqref="B299">
     <cfRule type="duplicateValues" dxfId="7" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B299">
+  <conditionalFormatting sqref="B300">
     <cfRule type="duplicateValues" dxfId="6" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B300">
+  <conditionalFormatting sqref="B301">
     <cfRule type="duplicateValues" dxfId="5" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B301">
+  <conditionalFormatting sqref="B302">
     <cfRule type="duplicateValues" dxfId="4" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B302">
+  <conditionalFormatting sqref="B303">
     <cfRule type="duplicateValues" dxfId="3" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B303">
+  <conditionalFormatting sqref="B304">
     <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B304">
+  <conditionalFormatting sqref="B306">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B306">
+  <conditionalFormatting sqref="B309">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -53560,11 +53606,11 @@
       </c>
       <c r="B6" s="16">
         <f>COUNTIFS(sum!J:J,"no news")</f>
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C6" s="10">
         <f>B6/$B$5</f>
-        <v>0.92363636363636359</v>
+        <v>0.91636363636363638</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
@@ -53573,11 +53619,11 @@
       </c>
       <c r="B7" s="16">
         <f>COUNTIFS(sum!J:J,"rejected")</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C7" s="10">
         <f t="shared" ref="C7:C10" si="0">B7/$B$5</f>
-        <v>5.8181818181818182E-2</v>
+        <v>6.545454545454546E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">

--- a/EconJM_status.xlsx
+++ b/EconJM_status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\javie\Dropbox\Work\Job Search\2025 EconJM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D04130B4-A7A5-4357-BA59-A6B368A572B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19C8A08A-4746-408C-AC0F-23C4766CDB97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" activeTab="1" xr2:uid="{6FE48536-7E5C-BF4C-9490-2A6392576298}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" xr2:uid="{6FE48536-7E5C-BF4C-9490-2A6392576298}"/>
   </bookViews>
   <sheets>
     <sheet name="sum" sheetId="1" r:id="rId1"/>
@@ -52932,8 +52932,8 @@
     <cfRule type="duplicateValues" dxfId="207" priority="216"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B11">
-    <cfRule type="duplicateValues" dxfId="206" priority="214"/>
-    <cfRule type="duplicateValues" dxfId="205" priority="215"/>
+    <cfRule type="duplicateValues" dxfId="206" priority="215"/>
+    <cfRule type="duplicateValues" dxfId="205" priority="214"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12">
     <cfRule type="duplicateValues" dxfId="204" priority="213"/>
@@ -52947,8 +52947,8 @@
     <cfRule type="duplicateValues" dxfId="200" priority="209"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17">
-    <cfRule type="duplicateValues" dxfId="199" priority="207"/>
-    <cfRule type="duplicateValues" dxfId="198" priority="208"/>
+    <cfRule type="duplicateValues" dxfId="199" priority="208"/>
+    <cfRule type="duplicateValues" dxfId="198" priority="207"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B18">
     <cfRule type="duplicateValues" dxfId="197" priority="206"/>
@@ -52973,8 +52973,8 @@
     <cfRule type="duplicateValues" dxfId="188" priority="197"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29">
-    <cfRule type="duplicateValues" dxfId="187" priority="195"/>
-    <cfRule type="duplicateValues" dxfId="186" priority="196"/>
+    <cfRule type="duplicateValues" dxfId="187" priority="196"/>
+    <cfRule type="duplicateValues" dxfId="186" priority="195"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30">
     <cfRule type="duplicateValues" dxfId="185" priority="194"/>
@@ -53040,8 +53040,8 @@
     <cfRule type="duplicateValues" dxfId="165" priority="171"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="164" priority="170"/>
-    <cfRule type="duplicateValues" dxfId="163" priority="169"/>
+    <cfRule type="duplicateValues" dxfId="164" priority="169"/>
+    <cfRule type="duplicateValues" dxfId="163" priority="170"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B68">
     <cfRule type="duplicateValues" dxfId="162" priority="168"/>
@@ -53128,8 +53128,8 @@
     <cfRule type="duplicateValues" dxfId="135" priority="138"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B104">
-    <cfRule type="duplicateValues" dxfId="134" priority="136"/>
-    <cfRule type="duplicateValues" dxfId="133" priority="137"/>
+    <cfRule type="duplicateValues" dxfId="134" priority="137"/>
+    <cfRule type="duplicateValues" dxfId="133" priority="136"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B105:B106">
     <cfRule type="duplicateValues" dxfId="132" priority="135"/>

--- a/EconJM_status.xlsx
+++ b/EconJM_status.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\javie\Dropbox\Work\Job Search\2025 EconJM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19C8A08A-4746-408C-AC0F-23C4766CDB97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D543F11-740F-4D81-9925-3E2417C235D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" xr2:uid="{6FE48536-7E5C-BF4C-9490-2A6392576298}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" activeTab="1" xr2:uid="{6FE48536-7E5C-BF4C-9490-2A6392576298}"/>
   </bookViews>
   <sheets>
     <sheet name="sum" sheetId="1" r:id="rId1"/>
@@ -428,7 +428,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2814" uniqueCount="880">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2855" uniqueCount="881">
   <si>
     <t>add_id</t>
   </si>
@@ -3105,12 +3105,15 @@
   <si>
     <t>Ireland</t>
   </si>
+  <si>
+    <t>*may be not updated. See timeline for accurate status of applications</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -3190,6 +3193,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="6"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -3231,7 +3241,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
@@ -3279,13 +3289,126 @@
     <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="228">
+  <dxfs count="239">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -5655,6 +5778,7 @@
         </key>
         <key name="%IsRefreshable">
           <flag name="ShowInCardView" value="0"/>
+          <flag name="ShowInDotNotation" value="0"/>
           <flag name="ShowInAutoComplete" value="0"/>
           <flag name="ExcludeFromCalcComparison" value="1"/>
         </key>
@@ -36006,7 +36130,7 @@
         <v>96</v>
       </c>
       <c r="J4" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>16</v>
@@ -38578,7 +38702,7 @@
         <v>96</v>
       </c>
       <c r="J57" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M57" t="s">
         <v>422</v>
@@ -40679,7 +40803,7 @@
         <v>96</v>
       </c>
       <c r="J100" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="K100" t="s">
         <v>309</v>
@@ -41358,7 +41482,7 @@
         <v>96</v>
       </c>
       <c r="J112" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="K112" t="s">
         <v>309</v>
@@ -41414,7 +41538,7 @@
         <v>96</v>
       </c>
       <c r="J113" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="K113" t="s">
         <v>309</v>
@@ -42835,7 +42959,7 @@
         <v>96</v>
       </c>
       <c r="J142" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M142" t="s">
         <v>359</v>
@@ -43162,7 +43286,7 @@
         <v>96</v>
       </c>
       <c r="J149" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M149" t="s">
         <v>513</v>
@@ -43265,7 +43389,7 @@
         <v>96</v>
       </c>
       <c r="J151" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M151" t="s">
         <v>741</v>
@@ -45950,7 +46074,7 @@
         <v>96</v>
       </c>
       <c r="J205" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="M205" t="s">
         <v>253</v>
@@ -46229,7 +46353,7 @@
         <v>96</v>
       </c>
       <c r="J211" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M211" t="s">
         <v>352</v>
@@ -49278,7 +49402,7 @@
         <v>96</v>
       </c>
       <c r="J274" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="M274" t="s">
         <v>870</v>
@@ -49408,63 +49532,63 @@
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="A1:B208 A210:B1048576">
-    <cfRule type="duplicateValues" dxfId="227" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="238" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:B22">
-    <cfRule type="duplicateValues" dxfId="226" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="237" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A61:B61">
-    <cfRule type="duplicateValues" dxfId="225" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="236" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="containsText" dxfId="224" priority="15" operator="containsText" text="closed">
+    <cfRule type="containsText" dxfId="235" priority="15" operator="containsText" text="closed">
       <formula>NOT(ISERROR(SEARCH("closed",I1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="223" priority="16" operator="containsText" text="abandoned">
+    <cfRule type="containsText" dxfId="234" priority="16" operator="containsText" text="abandoned">
       <formula>NOT(ISERROR(SEARCH("abandoned",I1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="222" priority="18" operator="containsText" text="late app">
+    <cfRule type="containsText" dxfId="233" priority="18" operator="containsText" text="late app">
       <formula>NOT(ISERROR(SEARCH("late app",I1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:L1048576 P78:P80 P83:P89 P92:P112 P115:P124 P126:P181 S136 S153 S159 S166 S173 S178 P183:P205 P208:P211 P213:P218 P220:P233 S225 P235:P237 P239:P248 P276 R276 I1:J1">
-    <cfRule type="containsText" dxfId="221" priority="21" operator="containsText" text="completed">
+    <cfRule type="containsText" dxfId="232" priority="21" operator="containsText" text="completed">
       <formula>NOT(ISERROR(SEARCH("completed",I1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:J1048576">
-    <cfRule type="containsText" dxfId="220" priority="10" operator="containsText" text="no news">
+    <cfRule type="containsText" dxfId="231" priority="10" operator="containsText" text="no news">
       <formula>NOT(ISERROR(SEARCH("no news",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="219" priority="11" operator="containsText" text="offer">
+    <cfRule type="containsText" dxfId="230" priority="11" operator="containsText" text="offer">
       <formula>NOT(ISERROR(SEARCH("offer",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="218" priority="12" operator="containsText" text="fly out">
+    <cfRule type="containsText" dxfId="229" priority="12" operator="containsText" text="fly out">
       <formula>NOT(ISERROR(SEARCH("fly out",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="217" priority="13" operator="containsText" text="interview">
+    <cfRule type="containsText" dxfId="228" priority="13" operator="containsText" text="interview">
       <formula>NOT(ISERROR(SEARCH("interview",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="216" priority="14" operator="containsText" text="rejected">
+    <cfRule type="containsText" dxfId="227" priority="14" operator="containsText" text="rejected">
       <formula>NOT(ISERROR(SEARCH("rejected",J1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1:L1048576 P78:P80 P83:P89 P92:P112 P115:P124 P126:P181 S136 S153 S159 S166 S173 S178 P183:P205 P208:P211 P213:P218 P220:P233 S225 P235:P237 P239:P248 P276 R276">
-    <cfRule type="containsText" dxfId="215" priority="19" operator="containsText" text="NO">
+    <cfRule type="containsText" dxfId="226" priority="19" operator="containsText" text="NO">
       <formula>NOT(ISERROR(SEARCH("NO",K1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="214" priority="20" operator="containsText" text="YES">
+    <cfRule type="containsText" dxfId="225" priority="20" operator="containsText" text="YES">
       <formula>NOT(ISERROR(SEARCH("YES",K1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P250:P267">
-    <cfRule type="containsText" dxfId="213" priority="1" operator="containsText" text="NO">
+    <cfRule type="containsText" dxfId="224" priority="1" operator="containsText" text="NO">
       <formula>NOT(ISERROR(SEARCH("NO",P250)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="212" priority="2" operator="containsText" text="YES">
+    <cfRule type="containsText" dxfId="223" priority="2" operator="containsText" text="YES">
       <formula>NOT(ISERROR(SEARCH("YES",P250)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="211" priority="3" operator="containsText" text="completed">
+    <cfRule type="containsText" dxfId="222" priority="3" operator="containsText" text="completed">
       <formula>NOT(ISERROR(SEARCH("completed",P250)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -49587,7 +49711,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923E81FA-B875-3C4E-A189-1A21268FA086}">
-  <dimension ref="A1:C309"/>
+  <dimension ref="A1:C329"/>
   <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="32.83203125" customWidth="1"/>
@@ -52922,612 +53046,863 @@
         <v>403</v>
       </c>
     </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A310" s="1">
+        <v>46011</v>
+      </c>
+      <c r="B310" t="s">
+        <v>510</v>
+      </c>
+      <c r="C310" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A311" s="1">
+        <v>46012</v>
+      </c>
+      <c r="B311" t="s">
+        <v>24</v>
+      </c>
+      <c r="C311" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A312" s="1">
+        <v>46013</v>
+      </c>
+      <c r="B312" t="s">
+        <v>353</v>
+      </c>
+      <c r="C312" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A313" s="1">
+        <v>46013</v>
+      </c>
+      <c r="B313" t="s">
+        <v>17</v>
+      </c>
+      <c r="C313" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A314" s="1">
+        <v>46013</v>
+      </c>
+      <c r="B314" t="s">
+        <v>739</v>
+      </c>
+      <c r="C314" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A315" s="1">
+        <v>46013</v>
+      </c>
+      <c r="B315" t="s">
+        <v>388</v>
+      </c>
+      <c r="C315" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A316" s="1">
+        <v>46013</v>
+      </c>
+      <c r="B316" t="s">
+        <v>254</v>
+      </c>
+      <c r="C316" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A317" s="1">
+        <v>46014</v>
+      </c>
+      <c r="B317" t="s">
+        <v>238</v>
+      </c>
+      <c r="C317" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A318" s="1">
+        <v>46017</v>
+      </c>
+      <c r="B318" t="s">
+        <v>408</v>
+      </c>
+      <c r="C318" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A319" s="1">
+        <v>46028</v>
+      </c>
+      <c r="B319" t="s">
+        <v>869</v>
+      </c>
+      <c r="C319" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A320" s="1">
+        <v>46029</v>
+      </c>
+      <c r="B320" t="s">
+        <v>671</v>
+      </c>
+      <c r="C320" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A321" s="1">
+        <v>46029</v>
+      </c>
+      <c r="B321" t="s">
+        <v>421</v>
+      </c>
+      <c r="C321" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A322" s="1">
+        <v>46031</v>
+      </c>
+      <c r="B322" t="s">
+        <v>796</v>
+      </c>
+      <c r="C322" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A323" s="1">
+        <v>46031</v>
+      </c>
+      <c r="B323" t="s">
+        <v>408</v>
+      </c>
+      <c r="C323" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A324" s="1">
+        <v>46031</v>
+      </c>
+      <c r="B324" t="s">
+        <v>671</v>
+      </c>
+      <c r="C324" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A325" s="1">
+        <v>46034</v>
+      </c>
+      <c r="B325" t="s">
+        <v>44</v>
+      </c>
+      <c r="C325" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A326" s="1">
+        <v>46037</v>
+      </c>
+      <c r="B326" t="s">
+        <v>157</v>
+      </c>
+      <c r="C326" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A327" s="1">
+        <v>46038</v>
+      </c>
+      <c r="B327" t="s">
+        <v>360</v>
+      </c>
+      <c r="C327" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A328" s="1">
+        <v>46045</v>
+      </c>
+      <c r="B328" t="s">
+        <v>872</v>
+      </c>
+      <c r="C328" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A329" s="1">
+        <v>46045</v>
+      </c>
+      <c r="B329" t="s">
+        <v>348</v>
+      </c>
+      <c r="C329" t="s">
+        <v>403</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="B5">
-    <cfRule type="duplicateValues" dxfId="210" priority="218"/>
-    <cfRule type="duplicateValues" dxfId="209" priority="219"/>
+    <cfRule type="duplicateValues" dxfId="221" priority="230"/>
+    <cfRule type="duplicateValues" dxfId="220" priority="231"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B10">
-    <cfRule type="duplicateValues" dxfId="208" priority="217"/>
-    <cfRule type="duplicateValues" dxfId="207" priority="216"/>
+    <cfRule type="duplicateValues" dxfId="219" priority="229"/>
+    <cfRule type="duplicateValues" dxfId="218" priority="228"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B11">
-    <cfRule type="duplicateValues" dxfId="206" priority="215"/>
-    <cfRule type="duplicateValues" dxfId="205" priority="214"/>
+    <cfRule type="duplicateValues" dxfId="217" priority="227"/>
+    <cfRule type="duplicateValues" dxfId="216" priority="226"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12">
-    <cfRule type="duplicateValues" dxfId="204" priority="213"/>
-    <cfRule type="duplicateValues" dxfId="203" priority="212"/>
+    <cfRule type="duplicateValues" dxfId="215" priority="225"/>
+    <cfRule type="duplicateValues" dxfId="214" priority="224"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15">
-    <cfRule type="duplicateValues" dxfId="202" priority="211"/>
-    <cfRule type="duplicateValues" dxfId="201" priority="210"/>
+    <cfRule type="duplicateValues" dxfId="213" priority="223"/>
+    <cfRule type="duplicateValues" dxfId="212" priority="222"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16">
-    <cfRule type="duplicateValues" dxfId="200" priority="209"/>
+    <cfRule type="duplicateValues" dxfId="211" priority="221"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17">
-    <cfRule type="duplicateValues" dxfId="199" priority="208"/>
-    <cfRule type="duplicateValues" dxfId="198" priority="207"/>
+    <cfRule type="duplicateValues" dxfId="210" priority="219"/>
+    <cfRule type="duplicateValues" dxfId="209" priority="220"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B18">
-    <cfRule type="duplicateValues" dxfId="197" priority="206"/>
-    <cfRule type="duplicateValues" dxfId="196" priority="205"/>
+    <cfRule type="duplicateValues" dxfId="208" priority="218"/>
+    <cfRule type="duplicateValues" dxfId="207" priority="217"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B19">
-    <cfRule type="duplicateValues" dxfId="195" priority="204"/>
+    <cfRule type="duplicateValues" dxfId="206" priority="216"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:B23">
-    <cfRule type="duplicateValues" dxfId="194" priority="203"/>
-    <cfRule type="duplicateValues" dxfId="193" priority="202"/>
+    <cfRule type="duplicateValues" dxfId="205" priority="215"/>
+    <cfRule type="duplicateValues" dxfId="204" priority="214"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B24">
-    <cfRule type="duplicateValues" dxfId="192" priority="201"/>
-    <cfRule type="duplicateValues" dxfId="191" priority="200"/>
+    <cfRule type="duplicateValues" dxfId="203" priority="213"/>
+    <cfRule type="duplicateValues" dxfId="202" priority="212"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B27">
-    <cfRule type="duplicateValues" dxfId="190" priority="199"/>
-    <cfRule type="duplicateValues" dxfId="189" priority="198"/>
+    <cfRule type="duplicateValues" dxfId="201" priority="211"/>
+    <cfRule type="duplicateValues" dxfId="200" priority="210"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28">
-    <cfRule type="duplicateValues" dxfId="188" priority="197"/>
+    <cfRule type="duplicateValues" dxfId="199" priority="209"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29">
-    <cfRule type="duplicateValues" dxfId="187" priority="196"/>
-    <cfRule type="duplicateValues" dxfId="186" priority="195"/>
+    <cfRule type="duplicateValues" dxfId="198" priority="208"/>
+    <cfRule type="duplicateValues" dxfId="197" priority="207"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="185" priority="194"/>
+    <cfRule type="duplicateValues" dxfId="196" priority="206"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31">
-    <cfRule type="duplicateValues" dxfId="184" priority="193"/>
+    <cfRule type="duplicateValues" dxfId="195" priority="205"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="duplicateValues" dxfId="183" priority="192"/>
+    <cfRule type="duplicateValues" dxfId="194" priority="204"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33">
-    <cfRule type="duplicateValues" dxfId="182" priority="191"/>
+    <cfRule type="duplicateValues" dxfId="193" priority="203"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="181" priority="190"/>
+    <cfRule type="duplicateValues" dxfId="192" priority="202"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35">
+    <cfRule type="duplicateValues" dxfId="191" priority="201"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B37">
+    <cfRule type="duplicateValues" dxfId="190" priority="200"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B38">
+    <cfRule type="duplicateValues" dxfId="189" priority="199"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B42">
+    <cfRule type="duplicateValues" dxfId="188" priority="198"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B43">
+    <cfRule type="duplicateValues" dxfId="187" priority="197"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B44:B45">
+    <cfRule type="duplicateValues" dxfId="186" priority="196"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B46">
+    <cfRule type="duplicateValues" dxfId="185" priority="195"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B48">
+    <cfRule type="duplicateValues" dxfId="184" priority="194"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B49">
+    <cfRule type="duplicateValues" dxfId="183" priority="193"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B51">
+    <cfRule type="duplicateValues" dxfId="182" priority="192"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B52">
+    <cfRule type="duplicateValues" dxfId="181" priority="191"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B58">
     <cfRule type="duplicateValues" dxfId="180" priority="189"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B37">
-    <cfRule type="duplicateValues" dxfId="179" priority="188"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B38">
-    <cfRule type="duplicateValues" dxfId="178" priority="187"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B42">
-    <cfRule type="duplicateValues" dxfId="177" priority="186"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B43">
-    <cfRule type="duplicateValues" dxfId="176" priority="185"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B44:B45">
-    <cfRule type="duplicateValues" dxfId="175" priority="184"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B46">
-    <cfRule type="duplicateValues" dxfId="174" priority="183"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B48">
-    <cfRule type="duplicateValues" dxfId="173" priority="182"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B49">
-    <cfRule type="duplicateValues" dxfId="172" priority="181"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B51">
-    <cfRule type="duplicateValues" dxfId="171" priority="180"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B52">
-    <cfRule type="duplicateValues" dxfId="170" priority="179"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B58">
-    <cfRule type="duplicateValues" dxfId="169" priority="177"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B59">
-    <cfRule type="duplicateValues" dxfId="168" priority="175"/>
+    <cfRule type="duplicateValues" dxfId="179" priority="187"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B63">
-    <cfRule type="duplicateValues" dxfId="167" priority="174"/>
+    <cfRule type="duplicateValues" dxfId="178" priority="186"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B64">
-    <cfRule type="duplicateValues" dxfId="166" priority="172"/>
+    <cfRule type="duplicateValues" dxfId="177" priority="184"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B66">
-    <cfRule type="duplicateValues" dxfId="165" priority="171"/>
+    <cfRule type="duplicateValues" dxfId="176" priority="183"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="164" priority="169"/>
-    <cfRule type="duplicateValues" dxfId="163" priority="170"/>
+    <cfRule type="duplicateValues" dxfId="175" priority="182"/>
+    <cfRule type="duplicateValues" dxfId="174" priority="181"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B68">
-    <cfRule type="duplicateValues" dxfId="162" priority="168"/>
+    <cfRule type="duplicateValues" dxfId="173" priority="180"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B69">
-    <cfRule type="duplicateValues" dxfId="161" priority="167"/>
+    <cfRule type="duplicateValues" dxfId="172" priority="179"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B70">
-    <cfRule type="duplicateValues" dxfId="160" priority="165"/>
+    <cfRule type="duplicateValues" dxfId="171" priority="177"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B72">
-    <cfRule type="duplicateValues" dxfId="159" priority="164"/>
+    <cfRule type="duplicateValues" dxfId="170" priority="176"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B73">
+    <cfRule type="duplicateValues" dxfId="169" priority="174"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B74">
+    <cfRule type="duplicateValues" dxfId="168" priority="173"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B75">
+    <cfRule type="duplicateValues" dxfId="167" priority="172"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B76">
+    <cfRule type="duplicateValues" dxfId="166" priority="171"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B77">
+    <cfRule type="duplicateValues" dxfId="165" priority="169"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B78">
+    <cfRule type="duplicateValues" dxfId="164" priority="168"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B83">
+    <cfRule type="duplicateValues" dxfId="163" priority="167"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B84">
+    <cfRule type="duplicateValues" dxfId="162" priority="166"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B85">
+    <cfRule type="duplicateValues" dxfId="161" priority="165"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B87">
+    <cfRule type="duplicateValues" dxfId="160" priority="164"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B88">
+    <cfRule type="duplicateValues" dxfId="159" priority="163"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B89">
     <cfRule type="duplicateValues" dxfId="158" priority="162"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B74">
+  <conditionalFormatting sqref="B90">
     <cfRule type="duplicateValues" dxfId="157" priority="161"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B75">
+  <conditionalFormatting sqref="B91">
     <cfRule type="duplicateValues" dxfId="156" priority="160"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B76">
+  <conditionalFormatting sqref="B92">
     <cfRule type="duplicateValues" dxfId="155" priority="159"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B77">
-    <cfRule type="duplicateValues" dxfId="154" priority="157"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B78">
-    <cfRule type="duplicateValues" dxfId="153" priority="156"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B83">
-    <cfRule type="duplicateValues" dxfId="152" priority="155"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B84">
-    <cfRule type="duplicateValues" dxfId="151" priority="154"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B85">
-    <cfRule type="duplicateValues" dxfId="150" priority="153"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B87">
-    <cfRule type="duplicateValues" dxfId="149" priority="152"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B88">
-    <cfRule type="duplicateValues" dxfId="148" priority="151"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B89">
-    <cfRule type="duplicateValues" dxfId="147" priority="150"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B90">
-    <cfRule type="duplicateValues" dxfId="146" priority="149"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B91">
-    <cfRule type="duplicateValues" dxfId="145" priority="148"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B92">
-    <cfRule type="duplicateValues" dxfId="144" priority="147"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B93">
-    <cfRule type="duplicateValues" dxfId="143" priority="146"/>
+    <cfRule type="duplicateValues" dxfId="154" priority="158"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B94">
-    <cfRule type="duplicateValues" dxfId="142" priority="145"/>
+    <cfRule type="duplicateValues" dxfId="153" priority="157"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B95">
-    <cfRule type="duplicateValues" dxfId="141" priority="144"/>
+    <cfRule type="duplicateValues" dxfId="152" priority="156"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B96">
-    <cfRule type="duplicateValues" dxfId="140" priority="143"/>
+    <cfRule type="duplicateValues" dxfId="151" priority="155"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B97">
-    <cfRule type="duplicateValues" dxfId="139" priority="142"/>
+    <cfRule type="duplicateValues" dxfId="150" priority="154"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B98">
-    <cfRule type="duplicateValues" dxfId="138" priority="141"/>
+    <cfRule type="duplicateValues" dxfId="149" priority="153"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B99">
-    <cfRule type="duplicateValues" dxfId="137" priority="140"/>
+    <cfRule type="duplicateValues" dxfId="148" priority="152"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B100">
-    <cfRule type="duplicateValues" dxfId="136" priority="139"/>
+    <cfRule type="duplicateValues" dxfId="147" priority="151"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B101">
-    <cfRule type="duplicateValues" dxfId="135" priority="138"/>
+    <cfRule type="duplicateValues" dxfId="146" priority="150"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B104">
-    <cfRule type="duplicateValues" dxfId="134" priority="137"/>
-    <cfRule type="duplicateValues" dxfId="133" priority="136"/>
+    <cfRule type="duplicateValues" dxfId="145" priority="149"/>
+    <cfRule type="duplicateValues" dxfId="144" priority="148"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B105:B106">
-    <cfRule type="duplicateValues" dxfId="132" priority="135"/>
+    <cfRule type="duplicateValues" dxfId="143" priority="147"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B107">
-    <cfRule type="duplicateValues" dxfId="131" priority="134"/>
+    <cfRule type="duplicateValues" dxfId="142" priority="146"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B108">
-    <cfRule type="duplicateValues" dxfId="130" priority="133"/>
+    <cfRule type="duplicateValues" dxfId="141" priority="145"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B109">
-    <cfRule type="duplicateValues" dxfId="129" priority="132"/>
+    <cfRule type="duplicateValues" dxfId="140" priority="144"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B110">
-    <cfRule type="duplicateValues" dxfId="128" priority="131"/>
+    <cfRule type="duplicateValues" dxfId="139" priority="143"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B111">
-    <cfRule type="duplicateValues" dxfId="127" priority="130"/>
+    <cfRule type="duplicateValues" dxfId="138" priority="142"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B112">
-    <cfRule type="duplicateValues" dxfId="126" priority="129"/>
+    <cfRule type="duplicateValues" dxfId="137" priority="141"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B113">
-    <cfRule type="duplicateValues" dxfId="125" priority="128"/>
+    <cfRule type="duplicateValues" dxfId="136" priority="140"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B114">
-    <cfRule type="duplicateValues" dxfId="124" priority="127"/>
+    <cfRule type="duplicateValues" dxfId="135" priority="139"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B115">
-    <cfRule type="duplicateValues" dxfId="123" priority="126"/>
+    <cfRule type="duplicateValues" dxfId="134" priority="138"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B116">
-    <cfRule type="duplicateValues" dxfId="122" priority="125"/>
+    <cfRule type="duplicateValues" dxfId="133" priority="137"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B117">
-    <cfRule type="duplicateValues" dxfId="121" priority="124"/>
+    <cfRule type="duplicateValues" dxfId="132" priority="136"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B118">
-    <cfRule type="duplicateValues" dxfId="120" priority="123"/>
+    <cfRule type="duplicateValues" dxfId="131" priority="135"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B119">
-    <cfRule type="duplicateValues" dxfId="119" priority="122"/>
+    <cfRule type="duplicateValues" dxfId="130" priority="134"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B120">
-    <cfRule type="duplicateValues" dxfId="118" priority="121"/>
+    <cfRule type="duplicateValues" dxfId="129" priority="133"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B121">
-    <cfRule type="duplicateValues" dxfId="117" priority="120"/>
+    <cfRule type="duplicateValues" dxfId="128" priority="132"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B122">
-    <cfRule type="duplicateValues" dxfId="116" priority="119"/>
+    <cfRule type="duplicateValues" dxfId="127" priority="131"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B126">
-    <cfRule type="duplicateValues" dxfId="115" priority="118"/>
+    <cfRule type="duplicateValues" dxfId="126" priority="130"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B127">
-    <cfRule type="duplicateValues" dxfId="114" priority="117"/>
+    <cfRule type="duplicateValues" dxfId="125" priority="129"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B128">
-    <cfRule type="duplicateValues" dxfId="113" priority="116"/>
+    <cfRule type="duplicateValues" dxfId="124" priority="128"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B129">
-    <cfRule type="duplicateValues" dxfId="112" priority="115"/>
+    <cfRule type="duplicateValues" dxfId="123" priority="127"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B130">
-    <cfRule type="duplicateValues" dxfId="111" priority="114"/>
+    <cfRule type="duplicateValues" dxfId="122" priority="126"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B131">
-    <cfRule type="duplicateValues" dxfId="110" priority="113"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="125"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B132">
-    <cfRule type="duplicateValues" dxfId="109" priority="112"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="124"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B133">
-    <cfRule type="duplicateValues" dxfId="108" priority="111"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="123"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B136">
-    <cfRule type="duplicateValues" dxfId="107" priority="110"/>
+    <cfRule type="duplicateValues" dxfId="118" priority="122"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B137">
-    <cfRule type="duplicateValues" dxfId="106" priority="109"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="121"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B138">
-    <cfRule type="duplicateValues" dxfId="105" priority="108"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="120"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B139">
-    <cfRule type="duplicateValues" dxfId="104" priority="107"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="119"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B140">
-    <cfRule type="duplicateValues" dxfId="103" priority="106"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="118"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B141">
-    <cfRule type="duplicateValues" dxfId="102" priority="105"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="117"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B142">
-    <cfRule type="duplicateValues" dxfId="101" priority="104"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="116"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B143">
-    <cfRule type="duplicateValues" dxfId="100" priority="103"/>
+    <cfRule type="duplicateValues" dxfId="111" priority="115"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B144">
-    <cfRule type="duplicateValues" dxfId="99" priority="102"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="114"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B145">
-    <cfRule type="duplicateValues" dxfId="98" priority="101"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="113"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B147">
-    <cfRule type="duplicateValues" dxfId="97" priority="100"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="112"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B148">
-    <cfRule type="duplicateValues" dxfId="96" priority="99"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="111"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B149">
-    <cfRule type="duplicateValues" dxfId="95" priority="98"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="110"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B150">
-    <cfRule type="duplicateValues" dxfId="94" priority="97"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="109"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B151">
-    <cfRule type="duplicateValues" dxfId="93" priority="96"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="108"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B152">
-    <cfRule type="duplicateValues" dxfId="92" priority="95"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="107"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B153">
-    <cfRule type="duplicateValues" dxfId="91" priority="94"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="106"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B154">
-    <cfRule type="duplicateValues" dxfId="90" priority="93"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="105"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B155">
-    <cfRule type="duplicateValues" dxfId="89" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="104"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B156">
-    <cfRule type="duplicateValues" dxfId="88" priority="91"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="103"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B157">
-    <cfRule type="duplicateValues" dxfId="87" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="102"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B171">
-    <cfRule type="duplicateValues" dxfId="86" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="101"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B172">
-    <cfRule type="duplicateValues" dxfId="85" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="100"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B174">
-    <cfRule type="duplicateValues" dxfId="84" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="99"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B177:B178">
-    <cfRule type="duplicateValues" dxfId="83" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="98"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B181">
-    <cfRule type="duplicateValues" dxfId="82" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="97"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B182">
-    <cfRule type="duplicateValues" dxfId="81" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="96"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B183">
-    <cfRule type="duplicateValues" dxfId="80" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="95"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B184">
-    <cfRule type="duplicateValues" dxfId="79" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="94"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B185">
-    <cfRule type="duplicateValues" dxfId="78" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="93"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B186">
-    <cfRule type="duplicateValues" dxfId="77" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="92"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B188">
-    <cfRule type="duplicateValues" dxfId="76" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="91"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B189">
-    <cfRule type="duplicateValues" dxfId="75" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="90"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B190">
-    <cfRule type="duplicateValues" dxfId="74" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="89"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B191">
-    <cfRule type="duplicateValues" dxfId="73" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="88"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B192">
-    <cfRule type="duplicateValues" dxfId="72" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="87"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B193">
-    <cfRule type="duplicateValues" dxfId="71" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="86"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B195">
-    <cfRule type="duplicateValues" dxfId="70" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="85"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B196">
-    <cfRule type="duplicateValues" dxfId="69" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="84"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B197">
-    <cfRule type="duplicateValues" dxfId="68" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="83"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B198">
-    <cfRule type="duplicateValues" dxfId="67" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="82"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B199">
-    <cfRule type="duplicateValues" dxfId="66" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="81"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B200">
-    <cfRule type="duplicateValues" dxfId="65" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="80"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B201">
-    <cfRule type="duplicateValues" dxfId="64" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="79"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B202">
-    <cfRule type="duplicateValues" dxfId="63" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="78"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B203">
-    <cfRule type="duplicateValues" dxfId="62" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="77"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B204">
-    <cfRule type="duplicateValues" dxfId="61" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="76"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B205">
-    <cfRule type="duplicateValues" dxfId="60" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="75"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B206">
-    <cfRule type="duplicateValues" dxfId="59" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="74"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B207">
-    <cfRule type="duplicateValues" dxfId="58" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="73"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B215">
-    <cfRule type="duplicateValues" dxfId="57" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="72"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B218">
-    <cfRule type="duplicateValues" dxfId="56" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B220">
-    <cfRule type="duplicateValues" dxfId="55" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B222">
-    <cfRule type="duplicateValues" dxfId="54" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="69"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B223">
-    <cfRule type="duplicateValues" dxfId="53" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="68"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B224">
+    <cfRule type="duplicateValues" dxfId="63" priority="67"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B225">
+    <cfRule type="duplicateValues" dxfId="62" priority="66"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B227">
+    <cfRule type="duplicateValues" dxfId="61" priority="65"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B229">
+    <cfRule type="duplicateValues" dxfId="60" priority="64"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B230">
+    <cfRule type="duplicateValues" dxfId="59" priority="63"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B232">
+    <cfRule type="duplicateValues" dxfId="58" priority="62"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B233">
+    <cfRule type="duplicateValues" dxfId="57" priority="61"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B234">
+    <cfRule type="duplicateValues" dxfId="56" priority="60"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B235">
+    <cfRule type="duplicateValues" dxfId="55" priority="59"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B236">
+    <cfRule type="duplicateValues" dxfId="54" priority="58"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B237">
+    <cfRule type="duplicateValues" dxfId="53" priority="57"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B239">
     <cfRule type="duplicateValues" dxfId="52" priority="55"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B225">
+  <conditionalFormatting sqref="B240">
     <cfRule type="duplicateValues" dxfId="51" priority="54"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B227">
+  <conditionalFormatting sqref="B241">
     <cfRule type="duplicateValues" dxfId="50" priority="53"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B229">
+  <conditionalFormatting sqref="B242">
     <cfRule type="duplicateValues" dxfId="49" priority="52"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B230">
+  <conditionalFormatting sqref="B243">
     <cfRule type="duplicateValues" dxfId="48" priority="51"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B232">
+  <conditionalFormatting sqref="B250">
     <cfRule type="duplicateValues" dxfId="47" priority="50"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B233">
+  <conditionalFormatting sqref="B251">
     <cfRule type="duplicateValues" dxfId="46" priority="49"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B234">
+  <conditionalFormatting sqref="B253">
     <cfRule type="duplicateValues" dxfId="45" priority="48"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B235">
+  <conditionalFormatting sqref="B255">
     <cfRule type="duplicateValues" dxfId="44" priority="47"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B236">
+  <conditionalFormatting sqref="B258:B259">
     <cfRule type="duplicateValues" dxfId="43" priority="46"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B237">
+  <conditionalFormatting sqref="B260">
     <cfRule type="duplicateValues" dxfId="42" priority="45"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B239">
-    <cfRule type="duplicateValues" dxfId="41" priority="43"/>
+  <conditionalFormatting sqref="B265:B267 B269">
+    <cfRule type="duplicateValues" dxfId="41" priority="44"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B240">
-    <cfRule type="duplicateValues" dxfId="40" priority="42"/>
+  <conditionalFormatting sqref="B268">
+    <cfRule type="duplicateValues" dxfId="40" priority="43"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B241">
-    <cfRule type="duplicateValues" dxfId="39" priority="41"/>
+  <conditionalFormatting sqref="B270">
+    <cfRule type="duplicateValues" dxfId="39" priority="42"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B242">
-    <cfRule type="duplicateValues" dxfId="38" priority="40"/>
+  <conditionalFormatting sqref="B271">
+    <cfRule type="duplicateValues" dxfId="38" priority="41"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B243">
-    <cfRule type="duplicateValues" dxfId="37" priority="39"/>
+  <conditionalFormatting sqref="B273">
+    <cfRule type="duplicateValues" dxfId="37" priority="40"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B250">
-    <cfRule type="duplicateValues" dxfId="36" priority="38"/>
+  <conditionalFormatting sqref="B275">
+    <cfRule type="duplicateValues" dxfId="36" priority="39"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B251">
-    <cfRule type="duplicateValues" dxfId="35" priority="37"/>
+  <conditionalFormatting sqref="B278">
+    <cfRule type="duplicateValues" dxfId="35" priority="38"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B253">
-    <cfRule type="duplicateValues" dxfId="34" priority="36"/>
+  <conditionalFormatting sqref="B279">
+    <cfRule type="duplicateValues" dxfId="34" priority="37"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B255">
-    <cfRule type="duplicateValues" dxfId="33" priority="35"/>
+  <conditionalFormatting sqref="B280">
+    <cfRule type="duplicateValues" dxfId="33" priority="36"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B258:B259">
-    <cfRule type="duplicateValues" dxfId="32" priority="34"/>
+  <conditionalFormatting sqref="B281">
+    <cfRule type="duplicateValues" dxfId="32" priority="35"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B260">
-    <cfRule type="duplicateValues" dxfId="31" priority="33"/>
+  <conditionalFormatting sqref="B282">
+    <cfRule type="duplicateValues" dxfId="31" priority="34"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B265:B267 B269">
+  <conditionalFormatting sqref="B283">
     <cfRule type="duplicateValues" dxfId="30" priority="32"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B268">
+  <conditionalFormatting sqref="B284:B286">
     <cfRule type="duplicateValues" dxfId="29" priority="31"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B270">
+  <conditionalFormatting sqref="B287">
     <cfRule type="duplicateValues" dxfId="28" priority="30"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B271">
+  <conditionalFormatting sqref="B288">
     <cfRule type="duplicateValues" dxfId="27" priority="29"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B273">
+  <conditionalFormatting sqref="B291">
     <cfRule type="duplicateValues" dxfId="26" priority="28"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B275">
+  <conditionalFormatting sqref="B292">
     <cfRule type="duplicateValues" dxfId="25" priority="27"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B278">
+  <conditionalFormatting sqref="B293">
     <cfRule type="duplicateValues" dxfId="24" priority="26"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B279">
+  <conditionalFormatting sqref="B294">
     <cfRule type="duplicateValues" dxfId="23" priority="25"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B280">
+  <conditionalFormatting sqref="B295">
     <cfRule type="duplicateValues" dxfId="22" priority="24"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B281">
+  <conditionalFormatting sqref="B296">
     <cfRule type="duplicateValues" dxfId="21" priority="23"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B282">
+  <conditionalFormatting sqref="B297">
     <cfRule type="duplicateValues" dxfId="20" priority="22"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B283">
-    <cfRule type="duplicateValues" dxfId="19" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B284:B286">
-    <cfRule type="duplicateValues" dxfId="18" priority="19"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B287">
-    <cfRule type="duplicateValues" dxfId="17" priority="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B288">
-    <cfRule type="duplicateValues" dxfId="16" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B291">
-    <cfRule type="duplicateValues" dxfId="15" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B292">
-    <cfRule type="duplicateValues" dxfId="14" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B293">
-    <cfRule type="duplicateValues" dxfId="13" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B294">
-    <cfRule type="duplicateValues" dxfId="12" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B295">
-    <cfRule type="duplicateValues" dxfId="11" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B296">
-    <cfRule type="duplicateValues" dxfId="10" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B297">
-    <cfRule type="duplicateValues" dxfId="9" priority="10"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B298">
-    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B299">
-    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B300">
-    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B301">
-    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B302">
+    <cfRule type="duplicateValues" dxfId="15" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B303">
+    <cfRule type="duplicateValues" dxfId="14" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B304">
+    <cfRule type="duplicateValues" dxfId="13" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B306">
+    <cfRule type="duplicateValues" dxfId="12" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B309">
+    <cfRule type="duplicateValues" dxfId="11" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B310">
+    <cfRule type="duplicateValues" dxfId="10" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B313">
+    <cfRule type="duplicateValues" dxfId="9" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B314">
+    <cfRule type="duplicateValues" dxfId="7" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B316">
+    <cfRule type="duplicateValues" dxfId="6" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B319">
+    <cfRule type="duplicateValues" dxfId="5" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B321">
     <cfRule type="duplicateValues" dxfId="4" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B303">
+  <conditionalFormatting sqref="B322">
     <cfRule type="duplicateValues" dxfId="3" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B304">
+  <conditionalFormatting sqref="B325">
     <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B306">
+  <conditionalFormatting sqref="B327">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B309">
+  <conditionalFormatting sqref="B329">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -53536,10 +53911,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{852B2CA5-879F-3640-8AF9-56395EF3FA0F}">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="15.83203125" style="12" customWidth="1"/>
+    <col min="1" max="1" width="17.33203125" style="12" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" style="16"/>
     <col min="3" max="3" width="15.33203125" style="10" customWidth="1"/>
   </cols>
@@ -53606,11 +53981,11 @@
       </c>
       <c r="B6" s="16">
         <f>COUNTIFS(sum!J:J,"no news")</f>
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="C6" s="10">
         <f>B6/$B$5</f>
-        <v>0.91636363636363638</v>
+        <v>0.87636363636363634</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
@@ -53619,11 +53994,11 @@
       </c>
       <c r="B7" s="16">
         <f>COUNTIFS(sum!J:J,"rejected")</f>
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C7" s="10">
         <f t="shared" ref="C7:C10" si="0">B7/$B$5</f>
-        <v>6.545454545454546E-2</v>
+        <v>9.4545454545454544E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">
@@ -53632,11 +54007,11 @@
       </c>
       <c r="B8" s="16">
         <f>COUNTIFS(sum!J:J,"interview") + COUNTIFS(sum!J:J,"fly out") + COUNTIFS(sum!J:J,"offer")</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C8" s="10">
         <f t="shared" si="0"/>
-        <v>1.8181818181818181E-2</v>
+        <v>2.9090909090909091E-2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">
@@ -53663,6 +54038,11 @@
       <c r="C10" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A11" s="23" t="s">
+        <v>880</v>
       </c>
     </row>
   </sheetData>

--- a/EconJM_status.xlsx
+++ b/EconJM_status.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\javie\Dropbox\Work\Job Search\2025 EconJM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80043ACE-4A8F-4F83-A536-3C3D456B89FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{851EE1F0-9E31-4B99-A62B-5757413AF67B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" xr2:uid="{6FE48536-7E5C-BF4C-9490-2A6392576298}"/>
   </bookViews>
@@ -428,7 +428,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2928" uniqueCount="891">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3025" uniqueCount="919">
   <si>
     <t>add_id</t>
   </si>
@@ -3103,9 +3103,6 @@
     <t>Ireland</t>
   </si>
   <si>
-    <t>*may be not updated. See timeline for accurate status of applications</t>
-  </si>
-  <si>
     <t>purdue_post_sloan</t>
   </si>
   <si>
@@ -3137,6 +3134,93 @@
   </si>
   <si>
     <t>zurich_post_dig</t>
+  </si>
+  <si>
+    <t>andres_bello</t>
+  </si>
+  <si>
+    <t>https://www.aeaweb.org/joe/listing.php?JOE_ID=2026-01_111477201&amp;q=eNplj1EKwkAMRO-Sb4Uq6EcPIAjeYYm7sa7GbEm2lVwi3t0oFgT_wpvMJPOAQ7aapbNd0Ru0D8gSMNY8ErTQwAKuNN2LpmCEGs8OnRn5RhFoZWBewIV4HrPZ8Haum_V22ax8t2jusiDv_5RYBqk6BaXuXCfMcKQUToUTqc0woqScsFKwqHg7Ms2KUiSpoQhPM-Jvo-Bvk4ajC_Dx9sWqZ6Pf5r53unkX7LH7pj2fL5LLXFyZ</t>
+  </si>
+  <si>
+    <t>Universidad Andres Bello</t>
+  </si>
+  <si>
+    <t>hec_ine</t>
+  </si>
+  <si>
+    <t>generating docs</t>
+  </si>
+  <si>
+    <t>wheterall</t>
+  </si>
+  <si>
+    <t>Queens University</t>
+  </si>
+  <si>
+    <t>porto</t>
+  </si>
+  <si>
+    <t>University of Porto</t>
+  </si>
+  <si>
+    <t>lyon_post</t>
+  </si>
+  <si>
+    <t>École Normale Superieure de Lyon</t>
+  </si>
+  <si>
+    <t>uciii_post</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carlos III </t>
+  </si>
+  <si>
+    <t>added some other job postings</t>
+  </si>
+  <si>
+    <t>*may be not updated because I forgot to update the "sum" page. See timeline for accurate status of applications</t>
+  </si>
+  <si>
+    <t>fiu_teaching</t>
+  </si>
+  <si>
+    <t>https://search.careers.fiu.edu/?q=536746</t>
+  </si>
+  <si>
+    <t>reading</t>
+  </si>
+  <si>
+    <t>University of Reading</t>
+  </si>
+  <si>
+    <t>Simonetta Longhi (s.longhi@reading.ac.uk)</t>
+  </si>
+  <si>
+    <t>https://jobs.reading.ac.uk/Job/JobDetail?JobId=25073</t>
+  </si>
+  <si>
+    <t>n_iowa_teaching</t>
+  </si>
+  <si>
+    <t>https://uni.wd5.myworkdayjobs.com/en-US/UNI/job/Assistant-Professor-of-Instruction-or-Practice---Economics_JR1009</t>
+  </si>
+  <si>
+    <t>University of North Iowa</t>
+  </si>
+  <si>
+    <t>toronto_limited</t>
+  </si>
+  <si>
+    <t>https://jobs.utoronto.ca/job/Toronto-Assistant-Professor-Contractually-Limited-Term-Appointment-%28CLTA%29-EconomicsApplied-Economics-ON/599485817/</t>
+  </si>
+  <si>
+    <t>north_western</t>
+  </si>
+  <si>
+    <t>https://www.nwciowa.edu/employment/openings/402/visiting-faculty---economics</t>
+  </si>
+  <si>
+    <t>Northwestern College</t>
   </si>
 </sst>
 </file>
@@ -3328,27 +3412,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="263">
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="252">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3356,16 +3420,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3383,85 +3437,11 @@
       <font>
         <color rgb="FF9C0006"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <color theme="8" tint="-0.24994659260841701"/>
-      </font>
       <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="8" tint="-0.24994659260841701"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.24994659260841701"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="hair">
-          <color auto="1"/>
-        </left>
-        <right style="hair">
-          <color auto="1"/>
-        </right>
-        <top style="hair">
-          <color auto="1"/>
-        </top>
-        <bottom style="hair">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="2" tint="-0.24994659260841701"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <color theme="0" tint="-0.24994659260841701"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="5" tint="0.79998168889431442"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -36177,7 +36157,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7772053-9363-CA4A-A53F-040B7C700753}">
-  <dimension ref="A1:W283"/>
+  <dimension ref="A1:W294"/>
   <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="19.6640625" customWidth="1"/>
@@ -37622,7 +37602,7 @@
         <v>95</v>
       </c>
       <c r="J29" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M29" t="s">
         <v>477</v>
@@ -48558,7 +48538,7 @@
         <v>95</v>
       </c>
       <c r="J251" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M251" t="s">
         <v>719</v>
@@ -49791,13 +49771,13 @@
     </row>
     <row r="277" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A277" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="D277" s="1">
         <v>46068</v>
       </c>
       <c r="F277" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="I277" t="s">
         <v>95</v>
@@ -49836,13 +49816,13 @@
     </row>
     <row r="278" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A278" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="D278" s="1">
         <v>46054</v>
       </c>
       <c r="F278" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="I278" t="s">
         <v>95</v>
@@ -49881,7 +49861,7 @@
     </row>
     <row r="279" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A279" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="D279" s="1">
         <v>46052</v>
@@ -49926,7 +49906,7 @@
     </row>
     <row r="280" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A280" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="D280" s="1">
         <v>46054</v>
@@ -49941,7 +49921,7 @@
         <v>401</v>
       </c>
       <c r="M280" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="N280" t="e" vm="12">
         <v>#VALUE!</v>
@@ -49971,7 +49951,7 @@
     </row>
     <row r="281" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A281" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="D281" s="1">
         <v>46054</v>
@@ -49986,7 +49966,7 @@
         <v>401</v>
       </c>
       <c r="M281" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="N281" t="e" vm="1">
         <v>#VALUE!</v>
@@ -50016,7 +49996,7 @@
     </row>
     <row r="282" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A282" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="D282" s="1">
         <v>46054</v>
@@ -50061,7 +50041,7 @@
     </row>
     <row r="283" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A283" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="D283" s="1">
         <v>46054</v>
@@ -50101,6 +50081,482 @@
         <v>0</v>
       </c>
       <c r="W283">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="A284" t="s">
+        <v>890</v>
+      </c>
+      <c r="D284" s="1">
+        <v>46054</v>
+      </c>
+      <c r="E284" t="s">
+        <v>39</v>
+      </c>
+      <c r="F284" t="s">
+        <v>891</v>
+      </c>
+      <c r="I284" t="s">
+        <v>95</v>
+      </c>
+      <c r="J284" t="s">
+        <v>401</v>
+      </c>
+      <c r="M284" t="s">
+        <v>892</v>
+      </c>
+      <c r="N284" t="e" vm="5">
+        <v>#VALUE!</v>
+      </c>
+      <c r="O284" t="str" cm="1">
+        <f t="array" aca="1" ref="O284" ca="1">_FV(N284,"Name")</f>
+        <v>Chile</v>
+      </c>
+      <c r="P284" t="s">
+        <v>11</v>
+      </c>
+      <c r="R284" t="s">
+        <v>775</v>
+      </c>
+      <c r="S284" s="1">
+        <v>46054</v>
+      </c>
+      <c r="U284">
+        <v>1</v>
+      </c>
+      <c r="V284">
+        <v>0</v>
+      </c>
+      <c r="W284">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="A285" t="s">
+        <v>893</v>
+      </c>
+      <c r="D285" s="1">
+        <v>46082</v>
+      </c>
+      <c r="E285" t="s">
+        <v>15</v>
+      </c>
+      <c r="I285" t="s">
+        <v>894</v>
+      </c>
+      <c r="J285" t="s">
+        <v>401</v>
+      </c>
+      <c r="M285" t="s">
+        <v>807</v>
+      </c>
+      <c r="N285" t="e" vm="4">
+        <v>#VALUE!</v>
+      </c>
+      <c r="P285" t="s">
+        <v>25</v>
+      </c>
+      <c r="R285" t="s">
+        <v>775</v>
+      </c>
+      <c r="S285" s="1">
+        <v>46113</v>
+      </c>
+      <c r="U285">
+        <v>1</v>
+      </c>
+      <c r="V285">
+        <v>0</v>
+      </c>
+      <c r="W285">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="A286" t="s">
+        <v>895</v>
+      </c>
+      <c r="D286" s="1">
+        <v>46069</v>
+      </c>
+      <c r="E286" t="s">
+        <v>15</v>
+      </c>
+      <c r="I286" t="s">
+        <v>894</v>
+      </c>
+      <c r="J286" t="s">
+        <v>401</v>
+      </c>
+      <c r="M286" t="s">
+        <v>896</v>
+      </c>
+      <c r="N286" t="e" vm="10">
+        <v>#VALUE!</v>
+      </c>
+      <c r="P286" t="s">
+        <v>25</v>
+      </c>
+      <c r="R286" t="s">
+        <v>775</v>
+      </c>
+      <c r="S286" s="1">
+        <v>46107</v>
+      </c>
+      <c r="U286">
+        <v>1</v>
+      </c>
+      <c r="V286">
+        <v>0</v>
+      </c>
+      <c r="W286">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="A287" t="s">
+        <v>897</v>
+      </c>
+      <c r="D287" s="1">
+        <v>46081</v>
+      </c>
+      <c r="E287" t="s">
+        <v>15</v>
+      </c>
+      <c r="I287" t="s">
+        <v>894</v>
+      </c>
+      <c r="J287" t="s">
+        <v>401</v>
+      </c>
+      <c r="M287" t="s">
+        <v>898</v>
+      </c>
+      <c r="N287" t="e" vm="22">
+        <v>#VALUE!</v>
+      </c>
+      <c r="P287" t="s">
+        <v>11</v>
+      </c>
+      <c r="R287" t="s">
+        <v>775</v>
+      </c>
+      <c r="S287" s="1">
+        <v>46081</v>
+      </c>
+      <c r="U287">
+        <v>1</v>
+      </c>
+      <c r="V287">
+        <v>0</v>
+      </c>
+      <c r="W287">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="A288" t="s">
+        <v>899</v>
+      </c>
+      <c r="D288" s="1">
+        <v>46069</v>
+      </c>
+      <c r="E288" t="s">
+        <v>15</v>
+      </c>
+      <c r="I288" t="s">
+        <v>894</v>
+      </c>
+      <c r="J288" t="s">
+        <v>401</v>
+      </c>
+      <c r="M288" t="s">
+        <v>900</v>
+      </c>
+      <c r="N288" t="e" vm="4">
+        <v>#VALUE!</v>
+      </c>
+      <c r="P288" t="s">
+        <v>25</v>
+      </c>
+      <c r="R288" t="s">
+        <v>775</v>
+      </c>
+      <c r="S288" s="1">
+        <v>46082</v>
+      </c>
+      <c r="U288">
+        <v>1</v>
+      </c>
+      <c r="V288">
+        <v>0</v>
+      </c>
+      <c r="W288">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="A289" t="s">
+        <v>901</v>
+      </c>
+      <c r="D289" s="1">
+        <v>46069</v>
+      </c>
+      <c r="E289" t="s">
+        <v>15</v>
+      </c>
+      <c r="I289" t="s">
+        <v>894</v>
+      </c>
+      <c r="J289" t="s">
+        <v>401</v>
+      </c>
+      <c r="M289" t="s">
+        <v>902</v>
+      </c>
+      <c r="N289" t="e" vm="2">
+        <v>#VALUE!</v>
+      </c>
+      <c r="P289" t="s">
+        <v>25</v>
+      </c>
+      <c r="R289" t="s">
+        <v>775</v>
+      </c>
+      <c r="S289" s="1">
+        <v>46073</v>
+      </c>
+      <c r="U289">
+        <v>1</v>
+      </c>
+      <c r="V289">
+        <v>0</v>
+      </c>
+      <c r="W289">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="A290" t="s">
+        <v>905</v>
+      </c>
+      <c r="D290" s="1">
+        <v>46063</v>
+      </c>
+      <c r="E290" t="s">
+        <v>39</v>
+      </c>
+      <c r="F290" t="s">
+        <v>906</v>
+      </c>
+      <c r="I290" t="s">
+        <v>894</v>
+      </c>
+      <c r="J290" t="s">
+        <v>401</v>
+      </c>
+      <c r="M290" t="s">
+        <v>831</v>
+      </c>
+      <c r="N290" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="P290" t="s">
+        <v>19</v>
+      </c>
+      <c r="R290" t="s">
+        <v>19</v>
+      </c>
+      <c r="S290" s="1">
+        <v>46055</v>
+      </c>
+      <c r="U290">
+        <v>1</v>
+      </c>
+      <c r="V290">
+        <v>0</v>
+      </c>
+      <c r="W290">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="A291" t="s">
+        <v>907</v>
+      </c>
+      <c r="D291" s="1">
+        <v>46068</v>
+      </c>
+      <c r="E291" t="s">
+        <v>39</v>
+      </c>
+      <c r="F291" s="2" t="s">
+        <v>910</v>
+      </c>
+      <c r="H291" t="s">
+        <v>909</v>
+      </c>
+      <c r="I291" t="s">
+        <v>894</v>
+      </c>
+      <c r="J291" t="s">
+        <v>401</v>
+      </c>
+      <c r="M291" t="s">
+        <v>908</v>
+      </c>
+      <c r="N291" t="e" vm="21">
+        <v>#VALUE!</v>
+      </c>
+      <c r="P291" t="s">
+        <v>11</v>
+      </c>
+      <c r="R291" t="s">
+        <v>775</v>
+      </c>
+      <c r="S291" s="1">
+        <v>46068</v>
+      </c>
+      <c r="U291">
+        <v>1</v>
+      </c>
+      <c r="V291">
+        <v>0</v>
+      </c>
+      <c r="W291">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="A292" t="s">
+        <v>911</v>
+      </c>
+      <c r="D292" s="1">
+        <v>46069</v>
+      </c>
+      <c r="E292" t="s">
+        <v>39</v>
+      </c>
+      <c r="F292" t="s">
+        <v>912</v>
+      </c>
+      <c r="I292" t="s">
+        <v>894</v>
+      </c>
+      <c r="J292" t="s">
+        <v>401</v>
+      </c>
+      <c r="M292" t="s">
+        <v>913</v>
+      </c>
+      <c r="N292" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="P292" t="s">
+        <v>11</v>
+      </c>
+      <c r="R292" t="s">
+        <v>19</v>
+      </c>
+      <c r="S292" s="1">
+        <v>46080</v>
+      </c>
+      <c r="U292">
+        <v>1</v>
+      </c>
+      <c r="V292">
+        <v>0</v>
+      </c>
+      <c r="W292">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="A293" t="s">
+        <v>914</v>
+      </c>
+      <c r="D293" s="1">
+        <v>46069</v>
+      </c>
+      <c r="E293" t="s">
+        <v>39</v>
+      </c>
+      <c r="F293" t="s">
+        <v>915</v>
+      </c>
+      <c r="I293" t="s">
+        <v>894</v>
+      </c>
+      <c r="J293" t="s">
+        <v>401</v>
+      </c>
+      <c r="M293" t="s">
+        <v>198</v>
+      </c>
+      <c r="N293" t="e" vm="10">
+        <v>#VALUE!</v>
+      </c>
+      <c r="P293" t="s">
+        <v>11</v>
+      </c>
+      <c r="R293" t="s">
+        <v>19</v>
+      </c>
+      <c r="S293" s="1">
+        <v>46082</v>
+      </c>
+      <c r="U293">
+        <v>1</v>
+      </c>
+      <c r="V293">
+        <v>0</v>
+      </c>
+      <c r="W293">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="A294" t="s">
+        <v>916</v>
+      </c>
+      <c r="D294" s="1">
+        <v>46063</v>
+      </c>
+      <c r="E294" t="s">
+        <v>39</v>
+      </c>
+      <c r="F294" t="s">
+        <v>917</v>
+      </c>
+      <c r="I294" t="s">
+        <v>894</v>
+      </c>
+      <c r="J294" t="s">
+        <v>401</v>
+      </c>
+      <c r="M294" t="s">
+        <v>918</v>
+      </c>
+      <c r="N294" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="P294" t="s">
+        <v>11</v>
+      </c>
+      <c r="R294" t="s">
+        <v>775</v>
+      </c>
+      <c r="S294" s="1">
+        <v>46082</v>
+      </c>
+      <c r="U294">
+        <v>1</v>
+      </c>
+      <c r="V294">
+        <v>0</v>
+      </c>
+      <c r="W294">
         <v>0</v>
       </c>
     </row>
@@ -50110,64 +50566,64 @@
       <sortCondition ref="D1:D267"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="A1:B208 A210:B1048576">
-    <cfRule type="duplicateValues" dxfId="262" priority="23"/>
+  <conditionalFormatting sqref="A1:B208 A210:B283 A285:B1048576 B284">
+    <cfRule type="duplicateValues" dxfId="251" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:B22">
-    <cfRule type="duplicateValues" dxfId="261" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="250" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A61:B61">
-    <cfRule type="duplicateValues" dxfId="260" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="249" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="containsText" dxfId="259" priority="15" operator="containsText" text="closed">
+    <cfRule type="containsText" dxfId="248" priority="15" operator="containsText" text="closed">
       <formula>NOT(ISERROR(SEARCH("closed",I1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="258" priority="16" operator="containsText" text="abandoned">
+    <cfRule type="containsText" dxfId="247" priority="16" operator="containsText" text="abandoned">
       <formula>NOT(ISERROR(SEARCH("abandoned",I1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="257" priority="18" operator="containsText" text="late app">
+    <cfRule type="containsText" dxfId="246" priority="18" operator="containsText" text="late app">
       <formula>NOT(ISERROR(SEARCH("late app",I1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P78:P80 P83:P89 P92:P112 P115:P124 P126:P181 S136 S153 S159 S166 S173 S178 P183:P205 P208:P211 P213:P218 P220:P233 S225 P235:P237 P239:P248 I1:J1 P276:P283 R276:R283 I2:L1048576">
-    <cfRule type="containsText" dxfId="256" priority="21" operator="containsText" text="completed">
+  <conditionalFormatting sqref="I2:L1048576 P78:P80 P83:P89 P92:P112 P115:P124 P126:P181 S136 S153 S159 S166 S173 S178 P183:P205 P208:P211 P213:P218 P220:P233 S225 P235:P237 P239:P248 N284:N285 I1:J1 N291:N293 P276:P294 R276:R294">
+    <cfRule type="containsText" dxfId="245" priority="21" operator="containsText" text="completed">
       <formula>NOT(ISERROR(SEARCH("completed",I1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:J1048576">
-    <cfRule type="containsText" dxfId="255" priority="10" operator="containsText" text="no news">
+    <cfRule type="containsText" dxfId="244" priority="10" operator="containsText" text="no news">
       <formula>NOT(ISERROR(SEARCH("no news",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="254" priority="11" operator="containsText" text="offer">
+    <cfRule type="containsText" dxfId="243" priority="11" operator="containsText" text="offer">
       <formula>NOT(ISERROR(SEARCH("offer",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="253" priority="12" operator="containsText" text="fly out">
+    <cfRule type="containsText" dxfId="242" priority="12" operator="containsText" text="fly out">
       <formula>NOT(ISERROR(SEARCH("fly out",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="252" priority="13" operator="containsText" text="interview">
+    <cfRule type="containsText" dxfId="241" priority="13" operator="containsText" text="interview">
       <formula>NOT(ISERROR(SEARCH("interview",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="251" priority="14" operator="containsText" text="rejected">
+    <cfRule type="containsText" dxfId="240" priority="14" operator="containsText" text="rejected">
       <formula>NOT(ISERROR(SEARCH("rejected",J1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K1:L1048576 P78:P80 P83:P89 P92:P112 P115:P124 P126:P181 S136 S153 S159 S166 S173 S178 P183:P205 P208:P211 P213:P218 P220:P233 S225 P235:P237 P239:P248 P276:P283 R276:R283">
-    <cfRule type="containsText" dxfId="250" priority="19" operator="containsText" text="NO">
+  <conditionalFormatting sqref="K1:L1048576 P78:P80 P83:P89 P92:P112 P115:P124 P126:P181 S136 S153 S159 S166 S173 S178 P183:P205 P208:P211 P213:P218 P220:P233 S225 P235:P237 P239:P248 N284:N285 N291:N293 P276:P294 R276:R294">
+    <cfRule type="containsText" dxfId="239" priority="19" operator="containsText" text="NO">
       <formula>NOT(ISERROR(SEARCH("NO",K1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="249" priority="20" operator="containsText" text="YES">
+    <cfRule type="containsText" dxfId="238" priority="20" operator="containsText" text="YES">
       <formula>NOT(ISERROR(SEARCH("YES",K1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P250:P267">
-    <cfRule type="containsText" dxfId="248" priority="1" operator="containsText" text="NO">
+    <cfRule type="containsText" dxfId="237" priority="1" operator="containsText" text="NO">
       <formula>NOT(ISERROR(SEARCH("NO",P250)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="247" priority="2" operator="containsText" text="YES">
+    <cfRule type="containsText" dxfId="236" priority="2" operator="containsText" text="YES">
       <formula>NOT(ISERROR(SEARCH("YES",P250)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="246" priority="3" operator="containsText" text="completed">
+    <cfRule type="containsText" dxfId="235" priority="3" operator="containsText" text="completed">
       <formula>NOT(ISERROR(SEARCH("completed",P250)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -50282,19 +50738,20 @@
     <hyperlink ref="F272" r:id="rId108" xr:uid="{34317180-A8EC-4C92-AB27-7AD534355822}"/>
     <hyperlink ref="F246" r:id="rId109" xr:uid="{81F56FF4-6BEE-4876-B897-D914C7668775}"/>
     <hyperlink ref="E275" r:id="rId110" xr:uid="{ACFEBBD7-5100-486E-81B2-AD29703033C3}"/>
+    <hyperlink ref="F291" r:id="rId111" xr:uid="{311A156E-3561-465E-A136-460E4C083957}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId111"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId112"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923E81FA-B875-3C4E-A189-1A21268FA086}">
-  <dimension ref="A1:C341"/>
+  <dimension ref="A1:C348"/>
   <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="32.83203125" customWidth="1"/>
-    <col min="2" max="2" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21" customWidth="1"/>
   </cols>
   <sheetData>
@@ -53894,7 +54351,7 @@
         <v>46049</v>
       </c>
       <c r="B334" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="C334" t="s">
         <v>96</v>
@@ -53905,7 +54362,7 @@
         <v>46049</v>
       </c>
       <c r="B335" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="C335" t="s">
         <v>96</v>
@@ -53927,7 +54384,7 @@
         <v>46052</v>
       </c>
       <c r="B337" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="C337" t="s">
         <v>96</v>
@@ -53938,7 +54395,7 @@
         <v>46052</v>
       </c>
       <c r="B338" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="C338" t="s">
         <v>96</v>
@@ -53949,7 +54406,7 @@
         <v>46052</v>
       </c>
       <c r="B339" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="C339" t="s">
         <v>96</v>
@@ -53960,7 +54417,7 @@
         <v>46052</v>
       </c>
       <c r="B340" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="C340" t="s">
         <v>96</v>
@@ -53971,669 +54428,759 @@
         <v>46052</v>
       </c>
       <c r="B341" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C341" t="s">
         <v>96</v>
       </c>
     </row>
+    <row r="342" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A342" s="1">
+        <v>46055</v>
+      </c>
+      <c r="B342" t="s">
+        <v>721</v>
+      </c>
+      <c r="C342" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A343" s="1">
+        <v>46056</v>
+      </c>
+      <c r="B343" t="s">
+        <v>889</v>
+      </c>
+      <c r="C343" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A344" s="1">
+        <v>46056</v>
+      </c>
+      <c r="B344" t="s">
+        <v>224</v>
+      </c>
+      <c r="C344" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A345" s="1">
+        <v>46058</v>
+      </c>
+      <c r="B345" t="s">
+        <v>738</v>
+      </c>
+      <c r="C345" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A346" s="1">
+        <v>46058</v>
+      </c>
+      <c r="B346" t="s">
+        <v>478</v>
+      </c>
+      <c r="C346" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A347" s="1">
+        <v>46058</v>
+      </c>
+      <c r="B347" t="s">
+        <v>890</v>
+      </c>
+      <c r="C347" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A348" s="1">
+        <v>46059</v>
+      </c>
+      <c r="C348" t="s">
+        <v>903</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="B5">
-    <cfRule type="duplicateValues" dxfId="245" priority="237"/>
-    <cfRule type="duplicateValues" dxfId="244" priority="238"/>
+    <cfRule type="duplicateValues" dxfId="234" priority="243"/>
+    <cfRule type="duplicateValues" dxfId="233" priority="244"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B10">
-    <cfRule type="duplicateValues" dxfId="243" priority="236"/>
-    <cfRule type="duplicateValues" dxfId="242" priority="235"/>
+    <cfRule type="duplicateValues" dxfId="232" priority="242"/>
+    <cfRule type="duplicateValues" dxfId="231" priority="241"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B11">
-    <cfRule type="duplicateValues" dxfId="241" priority="233"/>
-    <cfRule type="duplicateValues" dxfId="240" priority="234"/>
+    <cfRule type="duplicateValues" dxfId="230" priority="239"/>
+    <cfRule type="duplicateValues" dxfId="229" priority="240"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12">
-    <cfRule type="duplicateValues" dxfId="239" priority="232"/>
-    <cfRule type="duplicateValues" dxfId="238" priority="231"/>
+    <cfRule type="duplicateValues" dxfId="228" priority="238"/>
+    <cfRule type="duplicateValues" dxfId="227" priority="237"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15">
-    <cfRule type="duplicateValues" dxfId="237" priority="230"/>
-    <cfRule type="duplicateValues" dxfId="236" priority="229"/>
+    <cfRule type="duplicateValues" dxfId="226" priority="236"/>
+    <cfRule type="duplicateValues" dxfId="225" priority="235"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16">
-    <cfRule type="duplicateValues" dxfId="235" priority="228"/>
+    <cfRule type="duplicateValues" dxfId="224" priority="234"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17">
-    <cfRule type="duplicateValues" dxfId="234" priority="227"/>
-    <cfRule type="duplicateValues" dxfId="233" priority="226"/>
+    <cfRule type="duplicateValues" dxfId="223" priority="233"/>
+    <cfRule type="duplicateValues" dxfId="222" priority="232"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B18">
-    <cfRule type="duplicateValues" dxfId="232" priority="225"/>
-    <cfRule type="duplicateValues" dxfId="231" priority="224"/>
+    <cfRule type="duplicateValues" dxfId="221" priority="230"/>
+    <cfRule type="duplicateValues" dxfId="220" priority="231"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B19">
-    <cfRule type="duplicateValues" dxfId="230" priority="223"/>
+    <cfRule type="duplicateValues" dxfId="219" priority="229"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:B23">
-    <cfRule type="duplicateValues" dxfId="229" priority="222"/>
-    <cfRule type="duplicateValues" dxfId="228" priority="221"/>
+    <cfRule type="duplicateValues" dxfId="218" priority="228"/>
+    <cfRule type="duplicateValues" dxfId="217" priority="227"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B24">
-    <cfRule type="duplicateValues" dxfId="227" priority="220"/>
-    <cfRule type="duplicateValues" dxfId="226" priority="219"/>
+    <cfRule type="duplicateValues" dxfId="216" priority="226"/>
+    <cfRule type="duplicateValues" dxfId="215" priority="225"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B27">
-    <cfRule type="duplicateValues" dxfId="225" priority="218"/>
-    <cfRule type="duplicateValues" dxfId="224" priority="217"/>
+    <cfRule type="duplicateValues" dxfId="214" priority="224"/>
+    <cfRule type="duplicateValues" dxfId="213" priority="223"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28">
-    <cfRule type="duplicateValues" dxfId="223" priority="216"/>
+    <cfRule type="duplicateValues" dxfId="212" priority="222"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29">
-    <cfRule type="duplicateValues" dxfId="222" priority="215"/>
-    <cfRule type="duplicateValues" dxfId="221" priority="214"/>
+    <cfRule type="duplicateValues" dxfId="211" priority="221"/>
+    <cfRule type="duplicateValues" dxfId="210" priority="220"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="220" priority="213"/>
+    <cfRule type="duplicateValues" dxfId="209" priority="219"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31">
-    <cfRule type="duplicateValues" dxfId="219" priority="212"/>
+    <cfRule type="duplicateValues" dxfId="208" priority="218"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="duplicateValues" dxfId="218" priority="211"/>
+    <cfRule type="duplicateValues" dxfId="207" priority="217"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33">
-    <cfRule type="duplicateValues" dxfId="217" priority="210"/>
+    <cfRule type="duplicateValues" dxfId="206" priority="216"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="duplicateValues" dxfId="216" priority="209"/>
+    <cfRule type="duplicateValues" dxfId="205" priority="215"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35">
-    <cfRule type="duplicateValues" dxfId="215" priority="208"/>
+    <cfRule type="duplicateValues" dxfId="204" priority="214"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37">
-    <cfRule type="duplicateValues" dxfId="214" priority="207"/>
+    <cfRule type="duplicateValues" dxfId="203" priority="213"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38">
-    <cfRule type="duplicateValues" dxfId="213" priority="206"/>
+    <cfRule type="duplicateValues" dxfId="202" priority="212"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B42">
-    <cfRule type="duplicateValues" dxfId="212" priority="205"/>
+    <cfRule type="duplicateValues" dxfId="201" priority="211"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43">
-    <cfRule type="duplicateValues" dxfId="211" priority="204"/>
+    <cfRule type="duplicateValues" dxfId="200" priority="210"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44:B45">
-    <cfRule type="duplicateValues" dxfId="210" priority="203"/>
+    <cfRule type="duplicateValues" dxfId="199" priority="209"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B46">
-    <cfRule type="duplicateValues" dxfId="209" priority="202"/>
+    <cfRule type="duplicateValues" dxfId="198" priority="208"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B48">
-    <cfRule type="duplicateValues" dxfId="208" priority="201"/>
+    <cfRule type="duplicateValues" dxfId="197" priority="207"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B49">
-    <cfRule type="duplicateValues" dxfId="207" priority="200"/>
+    <cfRule type="duplicateValues" dxfId="196" priority="206"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B51">
-    <cfRule type="duplicateValues" dxfId="206" priority="199"/>
+    <cfRule type="duplicateValues" dxfId="195" priority="205"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B52">
-    <cfRule type="duplicateValues" dxfId="205" priority="198"/>
+    <cfRule type="duplicateValues" dxfId="194" priority="204"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B58">
-    <cfRule type="duplicateValues" dxfId="204" priority="196"/>
+    <cfRule type="duplicateValues" dxfId="193" priority="202"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B59">
-    <cfRule type="duplicateValues" dxfId="203" priority="194"/>
+    <cfRule type="duplicateValues" dxfId="192" priority="200"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B63">
-    <cfRule type="duplicateValues" dxfId="202" priority="193"/>
+    <cfRule type="duplicateValues" dxfId="191" priority="199"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B64">
-    <cfRule type="duplicateValues" dxfId="201" priority="191"/>
+    <cfRule type="duplicateValues" dxfId="190" priority="197"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B66">
-    <cfRule type="duplicateValues" dxfId="200" priority="190"/>
+    <cfRule type="duplicateValues" dxfId="189" priority="196"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="199" priority="189"/>
-    <cfRule type="duplicateValues" dxfId="198" priority="188"/>
+    <cfRule type="duplicateValues" dxfId="188" priority="195"/>
+    <cfRule type="duplicateValues" dxfId="187" priority="194"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B68">
-    <cfRule type="duplicateValues" dxfId="197" priority="187"/>
+    <cfRule type="duplicateValues" dxfId="186" priority="193"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B69">
-    <cfRule type="duplicateValues" dxfId="196" priority="186"/>
+    <cfRule type="duplicateValues" dxfId="185" priority="192"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B70">
-    <cfRule type="duplicateValues" dxfId="195" priority="184"/>
+    <cfRule type="duplicateValues" dxfId="184" priority="190"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B72">
-    <cfRule type="duplicateValues" dxfId="194" priority="183"/>
+    <cfRule type="duplicateValues" dxfId="183" priority="189"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B73">
-    <cfRule type="duplicateValues" dxfId="193" priority="181"/>
+    <cfRule type="duplicateValues" dxfId="182" priority="187"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B74">
-    <cfRule type="duplicateValues" dxfId="192" priority="180"/>
+    <cfRule type="duplicateValues" dxfId="181" priority="186"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B75">
-    <cfRule type="duplicateValues" dxfId="191" priority="179"/>
+    <cfRule type="duplicateValues" dxfId="180" priority="185"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B76">
-    <cfRule type="duplicateValues" dxfId="190" priority="178"/>
+    <cfRule type="duplicateValues" dxfId="179" priority="184"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B77">
-    <cfRule type="duplicateValues" dxfId="189" priority="176"/>
+    <cfRule type="duplicateValues" dxfId="178" priority="182"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B78">
-    <cfRule type="duplicateValues" dxfId="188" priority="175"/>
+    <cfRule type="duplicateValues" dxfId="177" priority="181"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B83">
-    <cfRule type="duplicateValues" dxfId="187" priority="174"/>
+    <cfRule type="duplicateValues" dxfId="176" priority="180"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B84">
-    <cfRule type="duplicateValues" dxfId="186" priority="173"/>
+    <cfRule type="duplicateValues" dxfId="175" priority="179"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B85">
-    <cfRule type="duplicateValues" dxfId="185" priority="172"/>
+    <cfRule type="duplicateValues" dxfId="174" priority="178"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B87">
-    <cfRule type="duplicateValues" dxfId="184" priority="171"/>
+    <cfRule type="duplicateValues" dxfId="173" priority="177"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B88">
-    <cfRule type="duplicateValues" dxfId="183" priority="170"/>
+    <cfRule type="duplicateValues" dxfId="172" priority="176"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B89">
-    <cfRule type="duplicateValues" dxfId="182" priority="169"/>
+    <cfRule type="duplicateValues" dxfId="171" priority="175"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B90">
-    <cfRule type="duplicateValues" dxfId="181" priority="168"/>
+    <cfRule type="duplicateValues" dxfId="170" priority="174"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B91">
-    <cfRule type="duplicateValues" dxfId="180" priority="167"/>
+    <cfRule type="duplicateValues" dxfId="169" priority="173"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B92">
-    <cfRule type="duplicateValues" dxfId="179" priority="166"/>
+    <cfRule type="duplicateValues" dxfId="168" priority="172"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B93">
-    <cfRule type="duplicateValues" dxfId="178" priority="165"/>
+    <cfRule type="duplicateValues" dxfId="167" priority="171"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B94">
-    <cfRule type="duplicateValues" dxfId="177" priority="164"/>
+    <cfRule type="duplicateValues" dxfId="166" priority="170"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B95">
-    <cfRule type="duplicateValues" dxfId="176" priority="163"/>
+    <cfRule type="duplicateValues" dxfId="165" priority="169"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B96">
-    <cfRule type="duplicateValues" dxfId="175" priority="162"/>
+    <cfRule type="duplicateValues" dxfId="164" priority="168"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B97">
-    <cfRule type="duplicateValues" dxfId="174" priority="161"/>
+    <cfRule type="duplicateValues" dxfId="163" priority="167"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B98">
-    <cfRule type="duplicateValues" dxfId="173" priority="160"/>
+    <cfRule type="duplicateValues" dxfId="162" priority="166"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B99">
-    <cfRule type="duplicateValues" dxfId="172" priority="159"/>
+    <cfRule type="duplicateValues" dxfId="161" priority="165"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B100">
-    <cfRule type="duplicateValues" dxfId="171" priority="158"/>
+    <cfRule type="duplicateValues" dxfId="160" priority="164"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B101">
-    <cfRule type="duplicateValues" dxfId="170" priority="157"/>
+    <cfRule type="duplicateValues" dxfId="159" priority="163"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B104">
-    <cfRule type="duplicateValues" dxfId="169" priority="156"/>
-    <cfRule type="duplicateValues" dxfId="168" priority="155"/>
+    <cfRule type="duplicateValues" dxfId="158" priority="162"/>
+    <cfRule type="duplicateValues" dxfId="157" priority="161"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B105:B106">
-    <cfRule type="duplicateValues" dxfId="167" priority="154"/>
+    <cfRule type="duplicateValues" dxfId="156" priority="160"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B107">
-    <cfRule type="duplicateValues" dxfId="166" priority="153"/>
+    <cfRule type="duplicateValues" dxfId="155" priority="159"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B108">
-    <cfRule type="duplicateValues" dxfId="165" priority="152"/>
+    <cfRule type="duplicateValues" dxfId="154" priority="158"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B109">
-    <cfRule type="duplicateValues" dxfId="164" priority="151"/>
+    <cfRule type="duplicateValues" dxfId="153" priority="157"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B110">
-    <cfRule type="duplicateValues" dxfId="163" priority="150"/>
+    <cfRule type="duplicateValues" dxfId="152" priority="156"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B111">
-    <cfRule type="duplicateValues" dxfId="162" priority="149"/>
+    <cfRule type="duplicateValues" dxfId="151" priority="155"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B112">
-    <cfRule type="duplicateValues" dxfId="161" priority="148"/>
+    <cfRule type="duplicateValues" dxfId="150" priority="154"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B113">
-    <cfRule type="duplicateValues" dxfId="160" priority="147"/>
+    <cfRule type="duplicateValues" dxfId="149" priority="153"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B114">
-    <cfRule type="duplicateValues" dxfId="159" priority="146"/>
+    <cfRule type="duplicateValues" dxfId="148" priority="152"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B115">
-    <cfRule type="duplicateValues" dxfId="158" priority="145"/>
+    <cfRule type="duplicateValues" dxfId="147" priority="151"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B116">
-    <cfRule type="duplicateValues" dxfId="157" priority="144"/>
+    <cfRule type="duplicateValues" dxfId="146" priority="150"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B117">
-    <cfRule type="duplicateValues" dxfId="156" priority="143"/>
+    <cfRule type="duplicateValues" dxfId="145" priority="149"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B118">
-    <cfRule type="duplicateValues" dxfId="155" priority="142"/>
+    <cfRule type="duplicateValues" dxfId="144" priority="148"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B119">
-    <cfRule type="duplicateValues" dxfId="154" priority="141"/>
+    <cfRule type="duplicateValues" dxfId="143" priority="147"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B120">
-    <cfRule type="duplicateValues" dxfId="153" priority="140"/>
+    <cfRule type="duplicateValues" dxfId="142" priority="146"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B121">
-    <cfRule type="duplicateValues" dxfId="152" priority="139"/>
+    <cfRule type="duplicateValues" dxfId="141" priority="145"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B122">
-    <cfRule type="duplicateValues" dxfId="151" priority="138"/>
+    <cfRule type="duplicateValues" dxfId="140" priority="144"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B126">
-    <cfRule type="duplicateValues" dxfId="150" priority="137"/>
+    <cfRule type="duplicateValues" dxfId="139" priority="143"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B127">
-    <cfRule type="duplicateValues" dxfId="149" priority="136"/>
+    <cfRule type="duplicateValues" dxfId="138" priority="142"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B128">
-    <cfRule type="duplicateValues" dxfId="148" priority="135"/>
+    <cfRule type="duplicateValues" dxfId="137" priority="141"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B129">
-    <cfRule type="duplicateValues" dxfId="147" priority="134"/>
+    <cfRule type="duplicateValues" dxfId="136" priority="140"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B130">
-    <cfRule type="duplicateValues" dxfId="146" priority="133"/>
+    <cfRule type="duplicateValues" dxfId="135" priority="139"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B131">
-    <cfRule type="duplicateValues" dxfId="145" priority="132"/>
+    <cfRule type="duplicateValues" dxfId="134" priority="138"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B132">
-    <cfRule type="duplicateValues" dxfId="144" priority="131"/>
+    <cfRule type="duplicateValues" dxfId="133" priority="137"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B133">
-    <cfRule type="duplicateValues" dxfId="143" priority="130"/>
+    <cfRule type="duplicateValues" dxfId="132" priority="136"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B136">
-    <cfRule type="duplicateValues" dxfId="142" priority="129"/>
+    <cfRule type="duplicateValues" dxfId="131" priority="135"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B137">
-    <cfRule type="duplicateValues" dxfId="141" priority="128"/>
+    <cfRule type="duplicateValues" dxfId="130" priority="134"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B138">
-    <cfRule type="duplicateValues" dxfId="140" priority="127"/>
+    <cfRule type="duplicateValues" dxfId="129" priority="133"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B139">
-    <cfRule type="duplicateValues" dxfId="139" priority="126"/>
+    <cfRule type="duplicateValues" dxfId="128" priority="132"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B140">
-    <cfRule type="duplicateValues" dxfId="138" priority="125"/>
+    <cfRule type="duplicateValues" dxfId="127" priority="131"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B141">
-    <cfRule type="duplicateValues" dxfId="137" priority="124"/>
+    <cfRule type="duplicateValues" dxfId="126" priority="130"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B142">
-    <cfRule type="duplicateValues" dxfId="136" priority="123"/>
+    <cfRule type="duplicateValues" dxfId="125" priority="129"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B143">
-    <cfRule type="duplicateValues" dxfId="135" priority="122"/>
+    <cfRule type="duplicateValues" dxfId="124" priority="128"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B144">
-    <cfRule type="duplicateValues" dxfId="134" priority="121"/>
+    <cfRule type="duplicateValues" dxfId="123" priority="127"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B145">
-    <cfRule type="duplicateValues" dxfId="133" priority="120"/>
+    <cfRule type="duplicateValues" dxfId="122" priority="126"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B147">
-    <cfRule type="duplicateValues" dxfId="132" priority="119"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="125"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B148">
-    <cfRule type="duplicateValues" dxfId="131" priority="118"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="124"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B149">
-    <cfRule type="duplicateValues" dxfId="130" priority="117"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="123"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B150">
-    <cfRule type="duplicateValues" dxfId="129" priority="116"/>
+    <cfRule type="duplicateValues" dxfId="118" priority="122"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B151">
-    <cfRule type="duplicateValues" dxfId="128" priority="115"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="121"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B152">
-    <cfRule type="duplicateValues" dxfId="127" priority="114"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="120"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B153">
-    <cfRule type="duplicateValues" dxfId="126" priority="113"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="119"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B154">
-    <cfRule type="duplicateValues" dxfId="125" priority="112"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="118"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B155">
-    <cfRule type="duplicateValues" dxfId="124" priority="111"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="117"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B156">
-    <cfRule type="duplicateValues" dxfId="123" priority="110"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="116"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B157">
-    <cfRule type="duplicateValues" dxfId="122" priority="109"/>
+    <cfRule type="duplicateValues" dxfId="111" priority="115"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B171">
-    <cfRule type="duplicateValues" dxfId="121" priority="108"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="114"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B172">
-    <cfRule type="duplicateValues" dxfId="120" priority="107"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="113"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B174">
-    <cfRule type="duplicateValues" dxfId="119" priority="106"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="112"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B177:B178">
-    <cfRule type="duplicateValues" dxfId="118" priority="105"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="111"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B181">
-    <cfRule type="duplicateValues" dxfId="117" priority="104"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="110"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B182">
-    <cfRule type="duplicateValues" dxfId="116" priority="103"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="109"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B183">
-    <cfRule type="duplicateValues" dxfId="115" priority="102"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="108"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B184">
-    <cfRule type="duplicateValues" dxfId="114" priority="101"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="107"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B185">
-    <cfRule type="duplicateValues" dxfId="113" priority="100"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="106"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B186">
-    <cfRule type="duplicateValues" dxfId="112" priority="99"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="105"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B188">
-    <cfRule type="duplicateValues" dxfId="111" priority="98"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="104"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B189">
-    <cfRule type="duplicateValues" dxfId="110" priority="97"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="103"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B190">
-    <cfRule type="duplicateValues" dxfId="109" priority="96"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="102"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B191">
-    <cfRule type="duplicateValues" dxfId="108" priority="95"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="101"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B192">
-    <cfRule type="duplicateValues" dxfId="107" priority="94"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="100"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B193">
-    <cfRule type="duplicateValues" dxfId="106" priority="93"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="99"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B195">
-    <cfRule type="duplicateValues" dxfId="105" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="98"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B196">
-    <cfRule type="duplicateValues" dxfId="104" priority="91"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="97"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B197">
-    <cfRule type="duplicateValues" dxfId="103" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="96"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B198">
-    <cfRule type="duplicateValues" dxfId="102" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="95"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B199">
-    <cfRule type="duplicateValues" dxfId="101" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="94"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B200">
-    <cfRule type="duplicateValues" dxfId="100" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="93"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B201">
-    <cfRule type="duplicateValues" dxfId="99" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="92"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B202">
-    <cfRule type="duplicateValues" dxfId="98" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="91"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B203">
-    <cfRule type="duplicateValues" dxfId="97" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="90"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B204">
-    <cfRule type="duplicateValues" dxfId="96" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="89"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B205">
-    <cfRule type="duplicateValues" dxfId="95" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="88"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B206">
-    <cfRule type="duplicateValues" dxfId="94" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="87"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B207">
-    <cfRule type="duplicateValues" dxfId="93" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="86"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B215">
-    <cfRule type="duplicateValues" dxfId="92" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="85"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B218">
-    <cfRule type="duplicateValues" dxfId="91" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="84"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B220">
-    <cfRule type="duplicateValues" dxfId="90" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="83"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B222">
-    <cfRule type="duplicateValues" dxfId="89" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="82"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B223">
-    <cfRule type="duplicateValues" dxfId="88" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="81"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B224">
-    <cfRule type="duplicateValues" dxfId="87" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="80"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B225">
-    <cfRule type="duplicateValues" dxfId="86" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="79"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B227">
-    <cfRule type="duplicateValues" dxfId="85" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="78"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B229">
-    <cfRule type="duplicateValues" dxfId="84" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="77"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B230">
-    <cfRule type="duplicateValues" dxfId="83" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="76"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B232">
-    <cfRule type="duplicateValues" dxfId="82" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="75"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B233">
-    <cfRule type="duplicateValues" dxfId="81" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="74"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B234">
-    <cfRule type="duplicateValues" dxfId="80" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="73"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B235">
-    <cfRule type="duplicateValues" dxfId="79" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="72"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B236">
-    <cfRule type="duplicateValues" dxfId="78" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B237">
-    <cfRule type="duplicateValues" dxfId="77" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B239">
-    <cfRule type="duplicateValues" dxfId="76" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="68"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B240">
-    <cfRule type="duplicateValues" dxfId="75" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B241">
-    <cfRule type="duplicateValues" dxfId="74" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="66"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B242">
-    <cfRule type="duplicateValues" dxfId="73" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B243">
-    <cfRule type="duplicateValues" dxfId="72" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="64"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B250">
-    <cfRule type="duplicateValues" dxfId="71" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="63"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B251">
-    <cfRule type="duplicateValues" dxfId="70" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="62"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B253">
-    <cfRule type="duplicateValues" dxfId="69" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="61"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B255">
-    <cfRule type="duplicateValues" dxfId="68" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B258:B259">
-    <cfRule type="duplicateValues" dxfId="67" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="59"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B260">
-    <cfRule type="duplicateValues" dxfId="66" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="58"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B265:B267 B269">
-    <cfRule type="duplicateValues" dxfId="65" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B268">
-    <cfRule type="duplicateValues" dxfId="64" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B270">
-    <cfRule type="duplicateValues" dxfId="63" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B271">
-    <cfRule type="duplicateValues" dxfId="62" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B273">
-    <cfRule type="duplicateValues" dxfId="61" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B275">
-    <cfRule type="duplicateValues" dxfId="60" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B278">
-    <cfRule type="duplicateValues" dxfId="59" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B279">
-    <cfRule type="duplicateValues" dxfId="58" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B280">
-    <cfRule type="duplicateValues" dxfId="57" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B281">
-    <cfRule type="duplicateValues" dxfId="56" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B282">
-    <cfRule type="duplicateValues" dxfId="55" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B283">
-    <cfRule type="duplicateValues" dxfId="54" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B284:B286">
-    <cfRule type="duplicateValues" dxfId="53" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B287">
-    <cfRule type="duplicateValues" dxfId="52" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B288">
-    <cfRule type="duplicateValues" dxfId="51" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B291">
-    <cfRule type="duplicateValues" dxfId="50" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B292">
-    <cfRule type="duplicateValues" dxfId="49" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B293">
-    <cfRule type="duplicateValues" dxfId="48" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B294">
-    <cfRule type="duplicateValues" dxfId="47" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B295">
-    <cfRule type="duplicateValues" dxfId="46" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B296">
-    <cfRule type="duplicateValues" dxfId="45" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B297">
-    <cfRule type="duplicateValues" dxfId="44" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B298">
-    <cfRule type="duplicateValues" dxfId="43" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B299">
-    <cfRule type="duplicateValues" dxfId="42" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B300">
-    <cfRule type="duplicateValues" dxfId="41" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B301">
-    <cfRule type="duplicateValues" dxfId="40" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B302">
-    <cfRule type="duplicateValues" dxfId="39" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B303">
-    <cfRule type="duplicateValues" dxfId="38" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B304">
-    <cfRule type="duplicateValues" dxfId="37" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B306">
-    <cfRule type="duplicateValues" dxfId="36" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B309">
-    <cfRule type="duplicateValues" dxfId="35" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B310">
-    <cfRule type="duplicateValues" dxfId="34" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B313">
-    <cfRule type="duplicateValues" dxfId="33" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B314">
-    <cfRule type="duplicateValues" dxfId="31" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B316">
-    <cfRule type="duplicateValues" dxfId="30" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B319">
-    <cfRule type="duplicateValues" dxfId="29" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B321">
-    <cfRule type="duplicateValues" dxfId="28" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B322">
-    <cfRule type="duplicateValues" dxfId="27" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B325">
-    <cfRule type="duplicateValues" dxfId="26" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B327">
-    <cfRule type="duplicateValues" dxfId="25" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B329">
-    <cfRule type="duplicateValues" dxfId="24" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B330">
-    <cfRule type="duplicateValues" dxfId="23" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B332">
-    <cfRule type="duplicateValues" dxfId="22" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B333">
-    <cfRule type="duplicateValues" dxfId="21" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B334">
-    <cfRule type="duplicateValues" dxfId="19" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B335">
-    <cfRule type="duplicateValues" dxfId="18" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B337:B341">
-    <cfRule type="duplicateValues" dxfId="17" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B342">
+    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B343">
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B344">
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B345">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B346">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -54655,15 +55202,15 @@
       </c>
       <c r="B1" s="15">
         <f>COUNTA(sum!A:A) -1</f>
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="C1" s="22">
         <f>COUNTIF(sum!I:I, "completed")/(B1-COUNTIF(sum!I:I, "abandoned")-COUNTIF(sum!I:I, "late app"))</f>
-        <v>1</v>
+        <v>0.96478873239436624</v>
       </c>
       <c r="D1" s="21">
         <f>COUNTIF(sum!I:I, "completed")</f>
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.4">
@@ -54698,7 +55245,7 @@
       </c>
       <c r="B5" s="15">
         <f>COUNTA(sum!J:J) -1</f>
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="C5" s="14">
         <f>B5/B1</f>
@@ -54711,11 +55258,11 @@
       </c>
       <c r="B6" s="16">
         <f>COUNTIFS(sum!J:J,"no news")</f>
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="C6" s="10">
         <f>B6/$B$5</f>
-        <v>0.87943262411347523</v>
+        <v>0.87713310580204773</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
@@ -54724,11 +55271,11 @@
       </c>
       <c r="B7" s="16">
         <f>COUNTIFS(sum!J:J,"rejected")</f>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C7" s="10">
         <f t="shared" ref="C7:C10" si="0">B7/$B$5</f>
-        <v>9.2198581560283682E-2</v>
+        <v>9.556313993174062E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">
@@ -54741,7 +55288,7 @@
       </c>
       <c r="C8" s="10">
         <f t="shared" si="0"/>
-        <v>2.8368794326241134E-2</v>
+        <v>2.7303754266211604E-2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">
@@ -54754,7 +55301,7 @@
       </c>
       <c r="C9" s="10">
         <f t="shared" si="0"/>
-        <v>3.5460992907801418E-3</v>
+        <v>3.4129692832764505E-3</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.4">
@@ -54772,7 +55319,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A11" s="23" t="s">
-        <v>879</v>
+        <v>904</v>
       </c>
     </row>
   </sheetData>

--- a/EconJM_status.xlsx
+++ b/EconJM_status.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\javie\Dropbox\Work\Job Search\2025 EconJM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{851EE1F0-9E31-4B99-A62B-5757413AF67B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CB7AFDA-2E68-45BA-8FD0-E8E046281AFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" xr2:uid="{6FE48536-7E5C-BF4C-9490-2A6392576298}"/>
   </bookViews>
@@ -428,7 +428,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3025" uniqueCount="919">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3063" uniqueCount="925">
   <si>
     <t>add_id</t>
   </si>
@@ -3221,6 +3221,24 @@
   </si>
   <si>
     <t>Northwestern College</t>
+  </si>
+  <si>
+    <t>tilurg_postdoc</t>
+  </si>
+  <si>
+    <t>Tilurg University</t>
+  </si>
+  <si>
+    <t>south_denmark</t>
+  </si>
+  <si>
+    <t>https://fa-eosd-saasfaprod1.fa.ocs.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1001/job/3205</t>
+  </si>
+  <si>
+    <t>Danish Institute for Advanced Study</t>
+  </si>
+  <si>
+    <t>full</t>
   </si>
 </sst>
 </file>
@@ -3412,7 +3430,67 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="252">
+  <dxfs count="258">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -36157,7 +36235,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7772053-9363-CA4A-A53F-040B7C700753}">
-  <dimension ref="A1:W294"/>
+  <dimension ref="A1:W296"/>
   <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="19.6640625" customWidth="1"/>
@@ -50143,7 +50221,7 @@
         <v>15</v>
       </c>
       <c r="I285" t="s">
-        <v>894</v>
+        <v>95</v>
       </c>
       <c r="J285" t="s">
         <v>401</v>
@@ -50153,6 +50231,10 @@
       </c>
       <c r="N285" t="e" vm="4">
         <v>#VALUE!</v>
+      </c>
+      <c r="O285" t="str" cm="1">
+        <f t="array" aca="1" ref="O285" ca="1">_FV(N285,"Name")</f>
+        <v>France</v>
       </c>
       <c r="P285" t="s">
         <v>25</v>
@@ -50184,7 +50266,7 @@
         <v>15</v>
       </c>
       <c r="I286" t="s">
-        <v>894</v>
+        <v>95</v>
       </c>
       <c r="J286" t="s">
         <v>401</v>
@@ -50194,6 +50276,10 @@
       </c>
       <c r="N286" t="e" vm="10">
         <v>#VALUE!</v>
+      </c>
+      <c r="O286" t="str" cm="1">
+        <f t="array" aca="1" ref="O286" ca="1">_FV(N286,"Name")</f>
+        <v>Canada</v>
       </c>
       <c r="P286" t="s">
         <v>25</v>
@@ -50225,7 +50311,7 @@
         <v>15</v>
       </c>
       <c r="I287" t="s">
-        <v>894</v>
+        <v>95</v>
       </c>
       <c r="J287" t="s">
         <v>401</v>
@@ -50235,6 +50321,10 @@
       </c>
       <c r="N287" t="e" vm="22">
         <v>#VALUE!</v>
+      </c>
+      <c r="O287" t="str" cm="1">
+        <f t="array" aca="1" ref="O287" ca="1">_FV(N287,"Name")</f>
+        <v>Portugal</v>
       </c>
       <c r="P287" t="s">
         <v>11</v>
@@ -50266,7 +50356,7 @@
         <v>15</v>
       </c>
       <c r="I288" t="s">
-        <v>894</v>
+        <v>95</v>
       </c>
       <c r="J288" t="s">
         <v>401</v>
@@ -50276,6 +50366,10 @@
       </c>
       <c r="N288" t="e" vm="4">
         <v>#VALUE!</v>
+      </c>
+      <c r="O288" t="str" cm="1">
+        <f t="array" aca="1" ref="O288" ca="1">_FV(N288,"Name")</f>
+        <v>France</v>
       </c>
       <c r="P288" t="s">
         <v>25</v>
@@ -50307,7 +50401,7 @@
         <v>15</v>
       </c>
       <c r="I289" t="s">
-        <v>894</v>
+        <v>95</v>
       </c>
       <c r="J289" t="s">
         <v>401</v>
@@ -50317,6 +50411,10 @@
       </c>
       <c r="N289" t="e" vm="2">
         <v>#VALUE!</v>
+      </c>
+      <c r="O289" t="str" cm="1">
+        <f t="array" aca="1" ref="O289" ca="1">_FV(N289,"Name")</f>
+        <v>Spain</v>
       </c>
       <c r="P289" t="s">
         <v>25</v>
@@ -50351,7 +50449,7 @@
         <v>906</v>
       </c>
       <c r="I290" t="s">
-        <v>894</v>
+        <v>95</v>
       </c>
       <c r="J290" t="s">
         <v>401</v>
@@ -50361,6 +50459,10 @@
       </c>
       <c r="N290" t="e" vm="1">
         <v>#VALUE!</v>
+      </c>
+      <c r="O290" t="str" cm="1">
+        <f t="array" aca="1" ref="O290" ca="1">_FV(N290,"Name")</f>
+        <v>United States</v>
       </c>
       <c r="P290" t="s">
         <v>19</v>
@@ -50398,7 +50500,7 @@
         <v>909</v>
       </c>
       <c r="I291" t="s">
-        <v>894</v>
+        <v>95</v>
       </c>
       <c r="J291" t="s">
         <v>401</v>
@@ -50408,6 +50510,10 @@
       </c>
       <c r="N291" t="e" vm="21">
         <v>#VALUE!</v>
+      </c>
+      <c r="O291" t="str" cm="1">
+        <f t="array" aca="1" ref="O291" ca="1">_FV(N291,"Name")</f>
+        <v>United Kingdom</v>
       </c>
       <c r="P291" t="s">
         <v>11</v>
@@ -50453,6 +50559,10 @@
       <c r="N292" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
+      <c r="O292" t="str" cm="1">
+        <f t="array" aca="1" ref="O292" ca="1">_FV(N292,"Name")</f>
+        <v>United States</v>
+      </c>
       <c r="P292" t="s">
         <v>11</v>
       </c>
@@ -50497,6 +50607,10 @@
       <c r="N293" t="e" vm="10">
         <v>#VALUE!</v>
       </c>
+      <c r="O293" t="str" cm="1">
+        <f t="array" aca="1" ref="O293" ca="1">_FV(N293,"Name")</f>
+        <v>Canada</v>
+      </c>
       <c r="P293" t="s">
         <v>11</v>
       </c>
@@ -50541,6 +50655,10 @@
       <c r="N294" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
+      <c r="O294" t="str" cm="1">
+        <f t="array" aca="1" ref="O294" ca="1">_FV(N294,"Name")</f>
+        <v>United States</v>
+      </c>
       <c r="P294" t="s">
         <v>11</v>
       </c>
@@ -50557,6 +50675,96 @@
         <v>0</v>
       </c>
       <c r="W294">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="A295" t="s">
+        <v>919</v>
+      </c>
+      <c r="D295" s="1">
+        <v>46068</v>
+      </c>
+      <c r="E295" t="s">
+        <v>15</v>
+      </c>
+      <c r="I295" t="s">
+        <v>95</v>
+      </c>
+      <c r="J295" t="s">
+        <v>401</v>
+      </c>
+      <c r="M295" t="s">
+        <v>920</v>
+      </c>
+      <c r="N295" t="e" vm="6">
+        <v>#VALUE!</v>
+      </c>
+      <c r="O295" t="str" cm="1">
+        <f t="array" aca="1" ref="O295" ca="1">_FV(N295,"Name")</f>
+        <v>Netherlands</v>
+      </c>
+      <c r="P295" t="s">
+        <v>25</v>
+      </c>
+      <c r="R295" t="s">
+        <v>775</v>
+      </c>
+      <c r="S295" s="1">
+        <v>46068</v>
+      </c>
+      <c r="U295">
+        <v>1</v>
+      </c>
+      <c r="V295">
+        <v>0</v>
+      </c>
+      <c r="W295">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="A296" t="s">
+        <v>921</v>
+      </c>
+      <c r="D296" s="1">
+        <v>46069</v>
+      </c>
+      <c r="F296" s="2" t="s">
+        <v>922</v>
+      </c>
+      <c r="I296" t="s">
+        <v>95</v>
+      </c>
+      <c r="J296" t="s">
+        <v>401</v>
+      </c>
+      <c r="M296" t="s">
+        <v>923</v>
+      </c>
+      <c r="N296" t="e" vm="20">
+        <v>#VALUE!</v>
+      </c>
+      <c r="O296" t="str" cm="1">
+        <f t="array" aca="1" ref="O296" ca="1">_FV(N296,"Name")</f>
+        <v>Denmark</v>
+      </c>
+      <c r="P296" t="s">
+        <v>924</v>
+      </c>
+      <c r="R296" t="s">
+        <v>775</v>
+      </c>
+      <c r="S296" s="1">
+        <v>46082</v>
+      </c>
+      <c r="U296">
+        <v>1</v>
+      </c>
+      <c r="V296">
+        <v>0</v>
+      </c>
+      <c r="W296">
         <v>0</v>
       </c>
     </row>
@@ -50567,63 +50775,63 @@
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="A1:B208 A210:B283 A285:B1048576 B284">
-    <cfRule type="duplicateValues" dxfId="251" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="257" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:B22">
-    <cfRule type="duplicateValues" dxfId="250" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="256" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A61:B61">
-    <cfRule type="duplicateValues" dxfId="249" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="255" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="containsText" dxfId="248" priority="15" operator="containsText" text="closed">
+    <cfRule type="containsText" dxfId="254" priority="15" operator="containsText" text="closed">
       <formula>NOT(ISERROR(SEARCH("closed",I1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="247" priority="16" operator="containsText" text="abandoned">
+    <cfRule type="containsText" dxfId="253" priority="16" operator="containsText" text="abandoned">
       <formula>NOT(ISERROR(SEARCH("abandoned",I1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="246" priority="18" operator="containsText" text="late app">
+    <cfRule type="containsText" dxfId="252" priority="18" operator="containsText" text="late app">
       <formula>NOT(ISERROR(SEARCH("late app",I1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:L1048576 P78:P80 P83:P89 P92:P112 P115:P124 P126:P181 S136 S153 S159 S166 S173 S178 P183:P205 P208:P211 P213:P218 P220:P233 S225 P235:P237 P239:P248 N284:N285 I1:J1 N291:N293 P276:P294 R276:R294">
-    <cfRule type="containsText" dxfId="245" priority="21" operator="containsText" text="completed">
+  <conditionalFormatting sqref="P78:P80 P83:P89 P92:P112 P115:P124 P126:P181 S136 S153 S159 S166 S173 S178 P183:P205 P208:P211 P213:P218 P220:P233 S225 P235:P237 P239:P248 N284:N285 N291:N293 I1:J1 N295:N296 P276:P296 R276:R296 I2:L1048576">
+    <cfRule type="containsText" dxfId="251" priority="21" operator="containsText" text="completed">
       <formula>NOT(ISERROR(SEARCH("completed",I1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:J1048576">
-    <cfRule type="containsText" dxfId="244" priority="10" operator="containsText" text="no news">
+    <cfRule type="containsText" dxfId="250" priority="10" operator="containsText" text="no news">
       <formula>NOT(ISERROR(SEARCH("no news",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="243" priority="11" operator="containsText" text="offer">
+    <cfRule type="containsText" dxfId="249" priority="11" operator="containsText" text="offer">
       <formula>NOT(ISERROR(SEARCH("offer",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="242" priority="12" operator="containsText" text="fly out">
+    <cfRule type="containsText" dxfId="248" priority="12" operator="containsText" text="fly out">
       <formula>NOT(ISERROR(SEARCH("fly out",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="241" priority="13" operator="containsText" text="interview">
+    <cfRule type="containsText" dxfId="247" priority="13" operator="containsText" text="interview">
       <formula>NOT(ISERROR(SEARCH("interview",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="240" priority="14" operator="containsText" text="rejected">
+    <cfRule type="containsText" dxfId="246" priority="14" operator="containsText" text="rejected">
       <formula>NOT(ISERROR(SEARCH("rejected",J1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K1:L1048576 P78:P80 P83:P89 P92:P112 P115:P124 P126:P181 S136 S153 S159 S166 S173 S178 P183:P205 P208:P211 P213:P218 P220:P233 S225 P235:P237 P239:P248 N284:N285 N291:N293 P276:P294 R276:R294">
-    <cfRule type="containsText" dxfId="239" priority="19" operator="containsText" text="NO">
+  <conditionalFormatting sqref="K1:L1048576 P78:P80 P83:P89 P92:P112 P115:P124 P126:P181 S136 S153 S159 S166 S173 S178 P183:P205 P208:P211 P213:P218 P220:P233 S225 P235:P237 P239:P248 N284:N285 N291:N293 N295:N296 P276:P296 R276:R296">
+    <cfRule type="containsText" dxfId="245" priority="19" operator="containsText" text="NO">
       <formula>NOT(ISERROR(SEARCH("NO",K1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="238" priority="20" operator="containsText" text="YES">
+    <cfRule type="containsText" dxfId="244" priority="20" operator="containsText" text="YES">
       <formula>NOT(ISERROR(SEARCH("YES",K1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P250:P267">
-    <cfRule type="containsText" dxfId="237" priority="1" operator="containsText" text="NO">
+    <cfRule type="containsText" dxfId="243" priority="1" operator="containsText" text="NO">
       <formula>NOT(ISERROR(SEARCH("NO",P250)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="236" priority="2" operator="containsText" text="YES">
+    <cfRule type="containsText" dxfId="242" priority="2" operator="containsText" text="YES">
       <formula>NOT(ISERROR(SEARCH("YES",P250)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="235" priority="3" operator="containsText" text="completed">
+    <cfRule type="containsText" dxfId="241" priority="3" operator="containsText" text="completed">
       <formula>NOT(ISERROR(SEARCH("completed",P250)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -50739,15 +50947,16 @@
     <hyperlink ref="F246" r:id="rId109" xr:uid="{81F56FF4-6BEE-4876-B897-D914C7668775}"/>
     <hyperlink ref="E275" r:id="rId110" xr:uid="{ACFEBBD7-5100-486E-81B2-AD29703033C3}"/>
     <hyperlink ref="F291" r:id="rId111" xr:uid="{311A156E-3561-465E-A136-460E4C083957}"/>
+    <hyperlink ref="F296" r:id="rId112" xr:uid="{6122D6CC-37C2-48AE-B198-BBEB4D956A30}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId112"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId113"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923E81FA-B875-3C4E-A189-1A21268FA086}">
-  <dimension ref="A1:C348"/>
+  <dimension ref="A1:C360"/>
   <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="32.83203125" customWidth="1"/>
@@ -54508,678 +54717,828 @@
         <v>903</v>
       </c>
     </row>
+    <row r="349" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A349" s="1">
+        <v>46062</v>
+      </c>
+      <c r="B349" t="s">
+        <v>893</v>
+      </c>
+      <c r="C349" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A350" s="1">
+        <v>46062</v>
+      </c>
+      <c r="B350" t="s">
+        <v>895</v>
+      </c>
+      <c r="C350" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A351" s="1">
+        <v>46062</v>
+      </c>
+      <c r="B351" t="s">
+        <v>897</v>
+      </c>
+      <c r="C351" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A352" s="1">
+        <v>46062</v>
+      </c>
+      <c r="B352" t="s">
+        <v>899</v>
+      </c>
+      <c r="C352" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A353" s="1">
+        <v>46062</v>
+      </c>
+      <c r="B353" t="s">
+        <v>901</v>
+      </c>
+      <c r="C353" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A354" s="1">
+        <v>46062</v>
+      </c>
+      <c r="B354" t="s">
+        <v>919</v>
+      </c>
+      <c r="C354" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A355" s="1">
+        <v>46062</v>
+      </c>
+      <c r="B355" t="s">
+        <v>905</v>
+      </c>
+      <c r="C355" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="356" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A356" s="1">
+        <v>46062</v>
+      </c>
+      <c r="B356" t="s">
+        <v>907</v>
+      </c>
+      <c r="C356" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="357" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A357" s="1">
+        <v>46062</v>
+      </c>
+      <c r="B357" t="s">
+        <v>911</v>
+      </c>
+      <c r="C357" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="358" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A358" s="1">
+        <v>46062</v>
+      </c>
+      <c r="B358" t="s">
+        <v>914</v>
+      </c>
+      <c r="C358" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="359" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A359" s="1">
+        <v>46062</v>
+      </c>
+      <c r="B359" t="s">
+        <v>916</v>
+      </c>
+      <c r="C359" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A360" s="1">
+        <v>46062</v>
+      </c>
+      <c r="B360" t="s">
+        <v>921</v>
+      </c>
+      <c r="C360" t="s">
+        <v>96</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="B5">
-    <cfRule type="duplicateValues" dxfId="234" priority="243"/>
-    <cfRule type="duplicateValues" dxfId="233" priority="244"/>
+    <cfRule type="duplicateValues" dxfId="240" priority="249"/>
+    <cfRule type="duplicateValues" dxfId="239" priority="250"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B10">
+    <cfRule type="duplicateValues" dxfId="238" priority="248"/>
+    <cfRule type="duplicateValues" dxfId="237" priority="247"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B11">
+    <cfRule type="duplicateValues" dxfId="236" priority="245"/>
+    <cfRule type="duplicateValues" dxfId="235" priority="246"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B12">
+    <cfRule type="duplicateValues" dxfId="234" priority="244"/>
+    <cfRule type="duplicateValues" dxfId="233" priority="243"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B15">
     <cfRule type="duplicateValues" dxfId="232" priority="242"/>
     <cfRule type="duplicateValues" dxfId="231" priority="241"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B11">
-    <cfRule type="duplicateValues" dxfId="230" priority="239"/>
-    <cfRule type="duplicateValues" dxfId="229" priority="240"/>
+  <conditionalFormatting sqref="B16">
+    <cfRule type="duplicateValues" dxfId="230" priority="240"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B12">
+  <conditionalFormatting sqref="B17">
+    <cfRule type="duplicateValues" dxfId="229" priority="239"/>
     <cfRule type="duplicateValues" dxfId="228" priority="238"/>
-    <cfRule type="duplicateValues" dxfId="227" priority="237"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B15">
-    <cfRule type="duplicateValues" dxfId="226" priority="236"/>
+  <conditionalFormatting sqref="B18">
+    <cfRule type="duplicateValues" dxfId="227" priority="236"/>
+    <cfRule type="duplicateValues" dxfId="226" priority="237"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B19">
     <cfRule type="duplicateValues" dxfId="225" priority="235"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B16">
+  <conditionalFormatting sqref="B22:B23">
     <cfRule type="duplicateValues" dxfId="224" priority="234"/>
+    <cfRule type="duplicateValues" dxfId="223" priority="233"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B17">
-    <cfRule type="duplicateValues" dxfId="223" priority="233"/>
+  <conditionalFormatting sqref="B24">
     <cfRule type="duplicateValues" dxfId="222" priority="232"/>
+    <cfRule type="duplicateValues" dxfId="221" priority="231"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B18">
-    <cfRule type="duplicateValues" dxfId="221" priority="230"/>
-    <cfRule type="duplicateValues" dxfId="220" priority="231"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B19">
+  <conditionalFormatting sqref="B27">
+    <cfRule type="duplicateValues" dxfId="220" priority="230"/>
     <cfRule type="duplicateValues" dxfId="219" priority="229"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B22:B23">
+  <conditionalFormatting sqref="B28">
     <cfRule type="duplicateValues" dxfId="218" priority="228"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B29">
     <cfRule type="duplicateValues" dxfId="217" priority="227"/>
+    <cfRule type="duplicateValues" dxfId="216" priority="226"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B24">
-    <cfRule type="duplicateValues" dxfId="216" priority="226"/>
+  <conditionalFormatting sqref="B30">
     <cfRule type="duplicateValues" dxfId="215" priority="225"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B27">
+  <conditionalFormatting sqref="B31">
     <cfRule type="duplicateValues" dxfId="214" priority="224"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B32">
     <cfRule type="duplicateValues" dxfId="213" priority="223"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B28">
+  <conditionalFormatting sqref="B33">
     <cfRule type="duplicateValues" dxfId="212" priority="222"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B29">
+  <conditionalFormatting sqref="B34">
     <cfRule type="duplicateValues" dxfId="211" priority="221"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B35">
     <cfRule type="duplicateValues" dxfId="210" priority="220"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B30">
+  <conditionalFormatting sqref="B37">
     <cfRule type="duplicateValues" dxfId="209" priority="219"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B31">
+  <conditionalFormatting sqref="B38">
     <cfRule type="duplicateValues" dxfId="208" priority="218"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B32">
+  <conditionalFormatting sqref="B42">
     <cfRule type="duplicateValues" dxfId="207" priority="217"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B33">
+  <conditionalFormatting sqref="B43">
     <cfRule type="duplicateValues" dxfId="206" priority="216"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B34">
+  <conditionalFormatting sqref="B44:B45">
     <cfRule type="duplicateValues" dxfId="205" priority="215"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B35">
+  <conditionalFormatting sqref="B46">
     <cfRule type="duplicateValues" dxfId="204" priority="214"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B37">
+  <conditionalFormatting sqref="B48">
     <cfRule type="duplicateValues" dxfId="203" priority="213"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B38">
+  <conditionalFormatting sqref="B49">
     <cfRule type="duplicateValues" dxfId="202" priority="212"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B42">
+  <conditionalFormatting sqref="B51">
     <cfRule type="duplicateValues" dxfId="201" priority="211"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B43">
+  <conditionalFormatting sqref="B52">
     <cfRule type="duplicateValues" dxfId="200" priority="210"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B44:B45">
-    <cfRule type="duplicateValues" dxfId="199" priority="209"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B46">
-    <cfRule type="duplicateValues" dxfId="198" priority="208"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B48">
-    <cfRule type="duplicateValues" dxfId="197" priority="207"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B49">
-    <cfRule type="duplicateValues" dxfId="196" priority="206"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B51">
-    <cfRule type="duplicateValues" dxfId="195" priority="205"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B52">
-    <cfRule type="duplicateValues" dxfId="194" priority="204"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B58">
-    <cfRule type="duplicateValues" dxfId="193" priority="202"/>
+    <cfRule type="duplicateValues" dxfId="199" priority="208"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B59">
-    <cfRule type="duplicateValues" dxfId="192" priority="200"/>
+    <cfRule type="duplicateValues" dxfId="198" priority="206"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B63">
-    <cfRule type="duplicateValues" dxfId="191" priority="199"/>
+    <cfRule type="duplicateValues" dxfId="197" priority="205"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B64">
-    <cfRule type="duplicateValues" dxfId="190" priority="197"/>
+    <cfRule type="duplicateValues" dxfId="196" priority="203"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B66">
-    <cfRule type="duplicateValues" dxfId="189" priority="196"/>
+    <cfRule type="duplicateValues" dxfId="195" priority="202"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="188" priority="195"/>
-    <cfRule type="duplicateValues" dxfId="187" priority="194"/>
+    <cfRule type="duplicateValues" dxfId="194" priority="201"/>
+    <cfRule type="duplicateValues" dxfId="193" priority="200"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B68">
-    <cfRule type="duplicateValues" dxfId="186" priority="193"/>
+    <cfRule type="duplicateValues" dxfId="192" priority="199"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B69">
-    <cfRule type="duplicateValues" dxfId="185" priority="192"/>
+    <cfRule type="duplicateValues" dxfId="191" priority="198"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B70">
-    <cfRule type="duplicateValues" dxfId="184" priority="190"/>
+    <cfRule type="duplicateValues" dxfId="190" priority="196"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B72">
-    <cfRule type="duplicateValues" dxfId="183" priority="189"/>
+    <cfRule type="duplicateValues" dxfId="189" priority="195"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B73">
-    <cfRule type="duplicateValues" dxfId="182" priority="187"/>
+    <cfRule type="duplicateValues" dxfId="188" priority="193"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B74">
-    <cfRule type="duplicateValues" dxfId="181" priority="186"/>
+    <cfRule type="duplicateValues" dxfId="187" priority="192"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B75">
-    <cfRule type="duplicateValues" dxfId="180" priority="185"/>
+    <cfRule type="duplicateValues" dxfId="186" priority="191"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B76">
-    <cfRule type="duplicateValues" dxfId="179" priority="184"/>
+    <cfRule type="duplicateValues" dxfId="185" priority="190"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B77">
+    <cfRule type="duplicateValues" dxfId="184" priority="188"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B78">
+    <cfRule type="duplicateValues" dxfId="183" priority="187"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B83">
+    <cfRule type="duplicateValues" dxfId="182" priority="186"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B84">
+    <cfRule type="duplicateValues" dxfId="181" priority="185"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B85">
+    <cfRule type="duplicateValues" dxfId="180" priority="184"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B87">
+    <cfRule type="duplicateValues" dxfId="179" priority="183"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B88">
     <cfRule type="duplicateValues" dxfId="178" priority="182"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B78">
+  <conditionalFormatting sqref="B89">
     <cfRule type="duplicateValues" dxfId="177" priority="181"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B83">
+  <conditionalFormatting sqref="B90">
     <cfRule type="duplicateValues" dxfId="176" priority="180"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B84">
+  <conditionalFormatting sqref="B91">
     <cfRule type="duplicateValues" dxfId="175" priority="179"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B85">
+  <conditionalFormatting sqref="B92">
     <cfRule type="duplicateValues" dxfId="174" priority="178"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B87">
+  <conditionalFormatting sqref="B93">
     <cfRule type="duplicateValues" dxfId="173" priority="177"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B88">
+  <conditionalFormatting sqref="B94">
     <cfRule type="duplicateValues" dxfId="172" priority="176"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B89">
+  <conditionalFormatting sqref="B95">
     <cfRule type="duplicateValues" dxfId="171" priority="175"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B90">
+  <conditionalFormatting sqref="B96">
     <cfRule type="duplicateValues" dxfId="170" priority="174"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B91">
+  <conditionalFormatting sqref="B97">
     <cfRule type="duplicateValues" dxfId="169" priority="173"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B92">
+  <conditionalFormatting sqref="B98">
     <cfRule type="duplicateValues" dxfId="168" priority="172"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B93">
+  <conditionalFormatting sqref="B99">
     <cfRule type="duplicateValues" dxfId="167" priority="171"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B94">
+  <conditionalFormatting sqref="B100">
     <cfRule type="duplicateValues" dxfId="166" priority="170"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B95">
+  <conditionalFormatting sqref="B101">
     <cfRule type="duplicateValues" dxfId="165" priority="169"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B96">
+  <conditionalFormatting sqref="B104">
     <cfRule type="duplicateValues" dxfId="164" priority="168"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B97">
     <cfRule type="duplicateValues" dxfId="163" priority="167"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B98">
+  <conditionalFormatting sqref="B105:B106">
     <cfRule type="duplicateValues" dxfId="162" priority="166"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B99">
+  <conditionalFormatting sqref="B107">
     <cfRule type="duplicateValues" dxfId="161" priority="165"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B100">
+  <conditionalFormatting sqref="B108">
     <cfRule type="duplicateValues" dxfId="160" priority="164"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B101">
+  <conditionalFormatting sqref="B109">
     <cfRule type="duplicateValues" dxfId="159" priority="163"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B104">
+  <conditionalFormatting sqref="B110">
     <cfRule type="duplicateValues" dxfId="158" priority="162"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B111">
     <cfRule type="duplicateValues" dxfId="157" priority="161"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B105:B106">
+  <conditionalFormatting sqref="B112">
     <cfRule type="duplicateValues" dxfId="156" priority="160"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B107">
+  <conditionalFormatting sqref="B113">
     <cfRule type="duplicateValues" dxfId="155" priority="159"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B108">
+  <conditionalFormatting sqref="B114">
     <cfRule type="duplicateValues" dxfId="154" priority="158"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B109">
+  <conditionalFormatting sqref="B115">
     <cfRule type="duplicateValues" dxfId="153" priority="157"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B110">
+  <conditionalFormatting sqref="B116">
     <cfRule type="duplicateValues" dxfId="152" priority="156"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B111">
+  <conditionalFormatting sqref="B117">
     <cfRule type="duplicateValues" dxfId="151" priority="155"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B112">
+  <conditionalFormatting sqref="B118">
     <cfRule type="duplicateValues" dxfId="150" priority="154"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B113">
+  <conditionalFormatting sqref="B119">
     <cfRule type="duplicateValues" dxfId="149" priority="153"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B114">
+  <conditionalFormatting sqref="B120">
     <cfRule type="duplicateValues" dxfId="148" priority="152"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B115">
+  <conditionalFormatting sqref="B121">
     <cfRule type="duplicateValues" dxfId="147" priority="151"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B116">
+  <conditionalFormatting sqref="B122">
     <cfRule type="duplicateValues" dxfId="146" priority="150"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B117">
+  <conditionalFormatting sqref="B126">
     <cfRule type="duplicateValues" dxfId="145" priority="149"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B118">
+  <conditionalFormatting sqref="B127">
     <cfRule type="duplicateValues" dxfId="144" priority="148"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B119">
+  <conditionalFormatting sqref="B128">
     <cfRule type="duplicateValues" dxfId="143" priority="147"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B120">
+  <conditionalFormatting sqref="B129">
     <cfRule type="duplicateValues" dxfId="142" priority="146"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B121">
+  <conditionalFormatting sqref="B130">
     <cfRule type="duplicateValues" dxfId="141" priority="145"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B122">
+  <conditionalFormatting sqref="B131">
     <cfRule type="duplicateValues" dxfId="140" priority="144"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B126">
+  <conditionalFormatting sqref="B132">
     <cfRule type="duplicateValues" dxfId="139" priority="143"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B127">
+  <conditionalFormatting sqref="B133">
     <cfRule type="duplicateValues" dxfId="138" priority="142"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B128">
+  <conditionalFormatting sqref="B136">
     <cfRule type="duplicateValues" dxfId="137" priority="141"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B129">
+  <conditionalFormatting sqref="B137">
     <cfRule type="duplicateValues" dxfId="136" priority="140"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B130">
+  <conditionalFormatting sqref="B138">
     <cfRule type="duplicateValues" dxfId="135" priority="139"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B131">
+  <conditionalFormatting sqref="B139">
     <cfRule type="duplicateValues" dxfId="134" priority="138"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B132">
+  <conditionalFormatting sqref="B140">
     <cfRule type="duplicateValues" dxfId="133" priority="137"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B133">
+  <conditionalFormatting sqref="B141">
     <cfRule type="duplicateValues" dxfId="132" priority="136"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B136">
+  <conditionalFormatting sqref="B142">
     <cfRule type="duplicateValues" dxfId="131" priority="135"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B137">
+  <conditionalFormatting sqref="B143">
     <cfRule type="duplicateValues" dxfId="130" priority="134"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B138">
+  <conditionalFormatting sqref="B144">
     <cfRule type="duplicateValues" dxfId="129" priority="133"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B139">
+  <conditionalFormatting sqref="B145">
     <cfRule type="duplicateValues" dxfId="128" priority="132"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B140">
+  <conditionalFormatting sqref="B147">
     <cfRule type="duplicateValues" dxfId="127" priority="131"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B141">
+  <conditionalFormatting sqref="B148">
     <cfRule type="duplicateValues" dxfId="126" priority="130"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B142">
+  <conditionalFormatting sqref="B149">
     <cfRule type="duplicateValues" dxfId="125" priority="129"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B143">
+  <conditionalFormatting sqref="B150">
     <cfRule type="duplicateValues" dxfId="124" priority="128"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B144">
+  <conditionalFormatting sqref="B151">
     <cfRule type="duplicateValues" dxfId="123" priority="127"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B145">
+  <conditionalFormatting sqref="B152">
     <cfRule type="duplicateValues" dxfId="122" priority="126"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B147">
+  <conditionalFormatting sqref="B153">
     <cfRule type="duplicateValues" dxfId="121" priority="125"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B148">
+  <conditionalFormatting sqref="B154">
     <cfRule type="duplicateValues" dxfId="120" priority="124"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B149">
+  <conditionalFormatting sqref="B155">
     <cfRule type="duplicateValues" dxfId="119" priority="123"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B150">
+  <conditionalFormatting sqref="B156">
     <cfRule type="duplicateValues" dxfId="118" priority="122"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B151">
+  <conditionalFormatting sqref="B157">
     <cfRule type="duplicateValues" dxfId="117" priority="121"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B152">
+  <conditionalFormatting sqref="B171">
     <cfRule type="duplicateValues" dxfId="116" priority="120"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B153">
+  <conditionalFormatting sqref="B172">
     <cfRule type="duplicateValues" dxfId="115" priority="119"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B154">
+  <conditionalFormatting sqref="B174">
     <cfRule type="duplicateValues" dxfId="114" priority="118"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B155">
+  <conditionalFormatting sqref="B177:B178">
     <cfRule type="duplicateValues" dxfId="113" priority="117"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B156">
+  <conditionalFormatting sqref="B181">
     <cfRule type="duplicateValues" dxfId="112" priority="116"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B157">
+  <conditionalFormatting sqref="B182">
     <cfRule type="duplicateValues" dxfId="111" priority="115"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B171">
+  <conditionalFormatting sqref="B183">
     <cfRule type="duplicateValues" dxfId="110" priority="114"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B172">
+  <conditionalFormatting sqref="B184">
     <cfRule type="duplicateValues" dxfId="109" priority="113"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B174">
+  <conditionalFormatting sqref="B185">
     <cfRule type="duplicateValues" dxfId="108" priority="112"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B177:B178">
+  <conditionalFormatting sqref="B186">
     <cfRule type="duplicateValues" dxfId="107" priority="111"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B181">
+  <conditionalFormatting sqref="B188">
     <cfRule type="duplicateValues" dxfId="106" priority="110"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B182">
+  <conditionalFormatting sqref="B189">
     <cfRule type="duplicateValues" dxfId="105" priority="109"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B183">
+  <conditionalFormatting sqref="B190">
     <cfRule type="duplicateValues" dxfId="104" priority="108"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B184">
+  <conditionalFormatting sqref="B191">
     <cfRule type="duplicateValues" dxfId="103" priority="107"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B185">
+  <conditionalFormatting sqref="B192">
     <cfRule type="duplicateValues" dxfId="102" priority="106"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B186">
+  <conditionalFormatting sqref="B193">
     <cfRule type="duplicateValues" dxfId="101" priority="105"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B188">
+  <conditionalFormatting sqref="B195">
     <cfRule type="duplicateValues" dxfId="100" priority="104"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B189">
+  <conditionalFormatting sqref="B196">
     <cfRule type="duplicateValues" dxfId="99" priority="103"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B190">
+  <conditionalFormatting sqref="B197">
     <cfRule type="duplicateValues" dxfId="98" priority="102"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B191">
+  <conditionalFormatting sqref="B198">
     <cfRule type="duplicateValues" dxfId="97" priority="101"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B192">
+  <conditionalFormatting sqref="B199">
     <cfRule type="duplicateValues" dxfId="96" priority="100"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B193">
+  <conditionalFormatting sqref="B200">
     <cfRule type="duplicateValues" dxfId="95" priority="99"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B195">
+  <conditionalFormatting sqref="B201">
     <cfRule type="duplicateValues" dxfId="94" priority="98"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B196">
+  <conditionalFormatting sqref="B202">
     <cfRule type="duplicateValues" dxfId="93" priority="97"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B197">
+  <conditionalFormatting sqref="B203">
     <cfRule type="duplicateValues" dxfId="92" priority="96"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B198">
+  <conditionalFormatting sqref="B204">
     <cfRule type="duplicateValues" dxfId="91" priority="95"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B199">
+  <conditionalFormatting sqref="B205">
     <cfRule type="duplicateValues" dxfId="90" priority="94"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B200">
+  <conditionalFormatting sqref="B206">
     <cfRule type="duplicateValues" dxfId="89" priority="93"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B201">
+  <conditionalFormatting sqref="B207">
     <cfRule type="duplicateValues" dxfId="88" priority="92"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B202">
+  <conditionalFormatting sqref="B215">
     <cfRule type="duplicateValues" dxfId="87" priority="91"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B203">
+  <conditionalFormatting sqref="B218">
     <cfRule type="duplicateValues" dxfId="86" priority="90"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B204">
+  <conditionalFormatting sqref="B220">
     <cfRule type="duplicateValues" dxfId="85" priority="89"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B205">
+  <conditionalFormatting sqref="B222">
     <cfRule type="duplicateValues" dxfId="84" priority="88"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B206">
+  <conditionalFormatting sqref="B223">
     <cfRule type="duplicateValues" dxfId="83" priority="87"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B207">
+  <conditionalFormatting sqref="B224">
     <cfRule type="duplicateValues" dxfId="82" priority="86"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B215">
+  <conditionalFormatting sqref="B225">
     <cfRule type="duplicateValues" dxfId="81" priority="85"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B218">
+  <conditionalFormatting sqref="B227">
     <cfRule type="duplicateValues" dxfId="80" priority="84"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B220">
+  <conditionalFormatting sqref="B229">
     <cfRule type="duplicateValues" dxfId="79" priority="83"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B222">
+  <conditionalFormatting sqref="B230">
     <cfRule type="duplicateValues" dxfId="78" priority="82"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B223">
+  <conditionalFormatting sqref="B232">
     <cfRule type="duplicateValues" dxfId="77" priority="81"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B224">
+  <conditionalFormatting sqref="B233">
     <cfRule type="duplicateValues" dxfId="76" priority="80"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B225">
+  <conditionalFormatting sqref="B234">
     <cfRule type="duplicateValues" dxfId="75" priority="79"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B227">
+  <conditionalFormatting sqref="B235">
     <cfRule type="duplicateValues" dxfId="74" priority="78"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B229">
+  <conditionalFormatting sqref="B236">
     <cfRule type="duplicateValues" dxfId="73" priority="77"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B230">
+  <conditionalFormatting sqref="B237">
     <cfRule type="duplicateValues" dxfId="72" priority="76"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B232">
-    <cfRule type="duplicateValues" dxfId="71" priority="75"/>
+  <conditionalFormatting sqref="B239">
+    <cfRule type="duplicateValues" dxfId="71" priority="74"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B233">
-    <cfRule type="duplicateValues" dxfId="70" priority="74"/>
+  <conditionalFormatting sqref="B240">
+    <cfRule type="duplicateValues" dxfId="70" priority="73"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B234">
-    <cfRule type="duplicateValues" dxfId="69" priority="73"/>
+  <conditionalFormatting sqref="B241">
+    <cfRule type="duplicateValues" dxfId="69" priority="72"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B235">
-    <cfRule type="duplicateValues" dxfId="68" priority="72"/>
+  <conditionalFormatting sqref="B242">
+    <cfRule type="duplicateValues" dxfId="68" priority="71"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B236">
-    <cfRule type="duplicateValues" dxfId="67" priority="71"/>
+  <conditionalFormatting sqref="B243">
+    <cfRule type="duplicateValues" dxfId="67" priority="70"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B237">
-    <cfRule type="duplicateValues" dxfId="66" priority="70"/>
+  <conditionalFormatting sqref="B250">
+    <cfRule type="duplicateValues" dxfId="66" priority="69"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B239">
+  <conditionalFormatting sqref="B251">
     <cfRule type="duplicateValues" dxfId="65" priority="68"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B240">
+  <conditionalFormatting sqref="B253">
     <cfRule type="duplicateValues" dxfId="64" priority="67"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B241">
+  <conditionalFormatting sqref="B255">
     <cfRule type="duplicateValues" dxfId="63" priority="66"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B242">
+  <conditionalFormatting sqref="B258:B259">
     <cfRule type="duplicateValues" dxfId="62" priority="65"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B243">
+  <conditionalFormatting sqref="B260">
     <cfRule type="duplicateValues" dxfId="61" priority="64"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B250">
+  <conditionalFormatting sqref="B265:B267 B269">
     <cfRule type="duplicateValues" dxfId="60" priority="63"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B251">
+  <conditionalFormatting sqref="B268">
     <cfRule type="duplicateValues" dxfId="59" priority="62"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B253">
+  <conditionalFormatting sqref="B270">
     <cfRule type="duplicateValues" dxfId="58" priority="61"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B255">
+  <conditionalFormatting sqref="B271">
     <cfRule type="duplicateValues" dxfId="57" priority="60"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B258:B259">
+  <conditionalFormatting sqref="B273">
     <cfRule type="duplicateValues" dxfId="56" priority="59"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B260">
+  <conditionalFormatting sqref="B275">
     <cfRule type="duplicateValues" dxfId="55" priority="58"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B265:B267 B269">
+  <conditionalFormatting sqref="B278">
     <cfRule type="duplicateValues" dxfId="54" priority="57"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B268">
+  <conditionalFormatting sqref="B279">
     <cfRule type="duplicateValues" dxfId="53" priority="56"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B270">
+  <conditionalFormatting sqref="B280">
     <cfRule type="duplicateValues" dxfId="52" priority="55"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B271">
+  <conditionalFormatting sqref="B281">
     <cfRule type="duplicateValues" dxfId="51" priority="54"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B273">
+  <conditionalFormatting sqref="B282">
     <cfRule type="duplicateValues" dxfId="50" priority="53"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B275">
-    <cfRule type="duplicateValues" dxfId="49" priority="52"/>
+  <conditionalFormatting sqref="B283">
+    <cfRule type="duplicateValues" dxfId="49" priority="51"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B278">
-    <cfRule type="duplicateValues" dxfId="48" priority="51"/>
+  <conditionalFormatting sqref="B284:B286">
+    <cfRule type="duplicateValues" dxfId="48" priority="50"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B279">
-    <cfRule type="duplicateValues" dxfId="47" priority="50"/>
+  <conditionalFormatting sqref="B287">
+    <cfRule type="duplicateValues" dxfId="47" priority="49"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B280">
-    <cfRule type="duplicateValues" dxfId="46" priority="49"/>
+  <conditionalFormatting sqref="B288">
+    <cfRule type="duplicateValues" dxfId="46" priority="48"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B281">
-    <cfRule type="duplicateValues" dxfId="45" priority="48"/>
+  <conditionalFormatting sqref="B291">
+    <cfRule type="duplicateValues" dxfId="45" priority="47"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B282">
-    <cfRule type="duplicateValues" dxfId="44" priority="47"/>
+  <conditionalFormatting sqref="B292">
+    <cfRule type="duplicateValues" dxfId="44" priority="46"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B283">
+  <conditionalFormatting sqref="B293">
     <cfRule type="duplicateValues" dxfId="43" priority="45"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B284:B286">
+  <conditionalFormatting sqref="B294">
     <cfRule type="duplicateValues" dxfId="42" priority="44"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B287">
+  <conditionalFormatting sqref="B295">
     <cfRule type="duplicateValues" dxfId="41" priority="43"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B288">
+  <conditionalFormatting sqref="B296">
     <cfRule type="duplicateValues" dxfId="40" priority="42"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B291">
+  <conditionalFormatting sqref="B297">
     <cfRule type="duplicateValues" dxfId="39" priority="41"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B292">
+  <conditionalFormatting sqref="B298">
     <cfRule type="duplicateValues" dxfId="38" priority="40"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B293">
+  <conditionalFormatting sqref="B299">
     <cfRule type="duplicateValues" dxfId="37" priority="39"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B294">
+  <conditionalFormatting sqref="B300">
     <cfRule type="duplicateValues" dxfId="36" priority="38"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B295">
+  <conditionalFormatting sqref="B301">
     <cfRule type="duplicateValues" dxfId="35" priority="37"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B296">
+  <conditionalFormatting sqref="B302">
     <cfRule type="duplicateValues" dxfId="34" priority="36"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B297">
+  <conditionalFormatting sqref="B303">
     <cfRule type="duplicateValues" dxfId="33" priority="35"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B298">
+  <conditionalFormatting sqref="B304">
     <cfRule type="duplicateValues" dxfId="32" priority="34"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B299">
+  <conditionalFormatting sqref="B306">
     <cfRule type="duplicateValues" dxfId="31" priority="33"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B300">
+  <conditionalFormatting sqref="B309">
     <cfRule type="duplicateValues" dxfId="30" priority="32"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B301">
+  <conditionalFormatting sqref="B310">
     <cfRule type="duplicateValues" dxfId="29" priority="31"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B302">
+  <conditionalFormatting sqref="B313">
     <cfRule type="duplicateValues" dxfId="28" priority="30"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B303">
     <cfRule type="duplicateValues" dxfId="27" priority="29"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B304">
+  <conditionalFormatting sqref="B314">
     <cfRule type="duplicateValues" dxfId="26" priority="28"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B306">
+  <conditionalFormatting sqref="B316">
     <cfRule type="duplicateValues" dxfId="25" priority="27"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B309">
+  <conditionalFormatting sqref="B319">
     <cfRule type="duplicateValues" dxfId="24" priority="26"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B310">
-    <cfRule type="duplicateValues" dxfId="23" priority="25"/>
+  <conditionalFormatting sqref="B321">
+    <cfRule type="duplicateValues" dxfId="23" priority="24"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B313">
-    <cfRule type="duplicateValues" dxfId="22" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="23"/>
+  <conditionalFormatting sqref="B322">
+    <cfRule type="duplicateValues" dxfId="22" priority="23"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B314">
-    <cfRule type="duplicateValues" dxfId="20" priority="22"/>
+  <conditionalFormatting sqref="B325">
+    <cfRule type="duplicateValues" dxfId="21" priority="22"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B316">
-    <cfRule type="duplicateValues" dxfId="19" priority="21"/>
+  <conditionalFormatting sqref="B327">
+    <cfRule type="duplicateValues" dxfId="20" priority="21"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B319">
-    <cfRule type="duplicateValues" dxfId="18" priority="20"/>
+  <conditionalFormatting sqref="B329">
+    <cfRule type="duplicateValues" dxfId="19" priority="20"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B321">
+  <conditionalFormatting sqref="B330">
+    <cfRule type="duplicateValues" dxfId="18" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B332">
     <cfRule type="duplicateValues" dxfId="17" priority="18"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B322">
-    <cfRule type="duplicateValues" dxfId="16" priority="17"/>
+  <conditionalFormatting sqref="B333">
+    <cfRule type="duplicateValues" dxfId="16" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B325">
-    <cfRule type="duplicateValues" dxfId="15" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B327">
+  <conditionalFormatting sqref="B334">
     <cfRule type="duplicateValues" dxfId="14" priority="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B329">
+  <conditionalFormatting sqref="B335">
     <cfRule type="duplicateValues" dxfId="13" priority="14"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B330">
+  <conditionalFormatting sqref="B337:B341">
     <cfRule type="duplicateValues" dxfId="12" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B332">
+  <conditionalFormatting sqref="B342">
     <cfRule type="duplicateValues" dxfId="11" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B333">
-    <cfRule type="duplicateValues" dxfId="10" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="11"/>
+  <conditionalFormatting sqref="B343">
+    <cfRule type="duplicateValues" dxfId="10" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B334">
+  <conditionalFormatting sqref="B344">
+    <cfRule type="duplicateValues" dxfId="9" priority="10"/>
     <cfRule type="duplicateValues" dxfId="8" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B335">
+  <conditionalFormatting sqref="B345">
     <cfRule type="duplicateValues" dxfId="7" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B337:B341">
+  <conditionalFormatting sqref="B346">
     <cfRule type="duplicateValues" dxfId="6" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B342">
+  <conditionalFormatting sqref="B349:B350">
     <cfRule type="duplicateValues" dxfId="5" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B343">
+  <conditionalFormatting sqref="B351:B353">
     <cfRule type="duplicateValues" dxfId="4" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B344">
+  <conditionalFormatting sqref="B354">
     <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B355">
     <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B345">
+  <conditionalFormatting sqref="B356:B359">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B346">
+  <conditionalFormatting sqref="B360">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -55202,15 +55561,15 @@
       </c>
       <c r="B1" s="15">
         <f>COUNTA(sum!A:A) -1</f>
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C1" s="22">
         <f>COUNTIF(sum!I:I, "completed")/(B1-COUNTIF(sum!I:I, "abandoned")-COUNTIF(sum!I:I, "late app"))</f>
-        <v>0.96478873239436624</v>
+        <v>0.98951048951048948</v>
       </c>
       <c r="D1" s="21">
         <f>COUNTIF(sum!I:I, "completed")</f>
-        <v>274</v>
+        <v>283</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.4">
@@ -55245,7 +55604,7 @@
       </c>
       <c r="B5" s="15">
         <f>COUNTA(sum!J:J) -1</f>
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C5" s="14">
         <f>B5/B1</f>
@@ -55258,11 +55617,11 @@
       </c>
       <c r="B6" s="16">
         <f>COUNTIFS(sum!J:J,"no news")</f>
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C6" s="10">
         <f>B6/$B$5</f>
-        <v>0.87713310580204773</v>
+        <v>0.87796610169491529</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
@@ -55275,7 +55634,7 @@
       </c>
       <c r="C7" s="10">
         <f t="shared" ref="C7:C10" si="0">B7/$B$5</f>
-        <v>9.556313993174062E-2</v>
+        <v>9.4915254237288138E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">
@@ -55288,7 +55647,7 @@
       </c>
       <c r="C8" s="10">
         <f t="shared" si="0"/>
-        <v>2.7303754266211604E-2</v>
+        <v>2.7118644067796609E-2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">
@@ -55301,7 +55660,7 @@
       </c>
       <c r="C9" s="10">
         <f t="shared" si="0"/>
-        <v>3.4129692832764505E-3</v>
+        <v>3.3898305084745762E-3</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.4">

--- a/EconJM_status.xlsx
+++ b/EconJM_status.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\javie\Dropbox\Work\Job Search\2025 EconJM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CDF8CA5-636E-4A97-BC79-CC6E28A305ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0065D0FC-DCA2-451B-BC93-36394C3F0ADD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" activeTab="1" xr2:uid="{6FE48536-7E5C-BF4C-9490-2A6392576298}"/>
   </bookViews>
@@ -438,7 +438,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3211" uniqueCount="967">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3227" uniqueCount="967">
   <si>
     <t>add_id</t>
   </si>
@@ -3566,7 +3566,67 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="23">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -49737,63 +49797,63 @@
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="A1:B208 A210:B283 A285:B1048576 B284">
-    <cfRule type="duplicateValues" dxfId="16" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:B22">
-    <cfRule type="duplicateValues" dxfId="15" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A61:B61">
-    <cfRule type="duplicateValues" dxfId="14" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="containsText" dxfId="13" priority="15" operator="containsText" text="closed">
+    <cfRule type="containsText" dxfId="19" priority="15" operator="containsText" text="closed">
       <formula>NOT(ISERROR(SEARCH("closed",I1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="16" operator="containsText" text="abandoned">
+    <cfRule type="containsText" dxfId="18" priority="16" operator="containsText" text="abandoned">
       <formula>NOT(ISERROR(SEARCH("abandoned",I1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="11" priority="18" operator="containsText" text="late app">
+    <cfRule type="containsText" dxfId="17" priority="18" operator="containsText" text="late app">
       <formula>NOT(ISERROR(SEARCH("late app",I1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:L1048576 P78:P80 P83:P89 P92:P112 P115:P124 P126:P181 S136 S153 S159 S166 S173 S178 P183:P205 P208:P211 P213:P218 P220:P233 S225 P235:P237 P239:P248 P276:P309 R276:R309 I1:J1">
-    <cfRule type="containsText" dxfId="10" priority="21" operator="containsText" text="completed">
+    <cfRule type="containsText" dxfId="16" priority="21" operator="containsText" text="completed">
       <formula>NOT(ISERROR(SEARCH("completed",I1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:J1048576">
-    <cfRule type="containsText" dxfId="9" priority="10" operator="containsText" text="no news">
+    <cfRule type="containsText" dxfId="15" priority="10" operator="containsText" text="no news">
       <formula>NOT(ISERROR(SEARCH("no news",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="11" operator="containsText" text="offer">
+    <cfRule type="containsText" dxfId="14" priority="11" operator="containsText" text="offer">
       <formula>NOT(ISERROR(SEARCH("offer",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="7" priority="12" operator="containsText" text="fly out">
+    <cfRule type="containsText" dxfId="13" priority="12" operator="containsText" text="fly out">
       <formula>NOT(ISERROR(SEARCH("fly out",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="13" operator="containsText" text="interview">
+    <cfRule type="containsText" dxfId="12" priority="13" operator="containsText" text="interview">
       <formula>NOT(ISERROR(SEARCH("interview",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="14" operator="containsText" text="rejected">
+    <cfRule type="containsText" dxfId="11" priority="14" operator="containsText" text="rejected">
       <formula>NOT(ISERROR(SEARCH("rejected",J1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1:L1048576 P78:P80 P83:P89 P92:P112 P115:P124 P126:P181 S136 S153 S159 S166 S173 S178 P183:P205 P208:P211 P213:P218 P220:P233 S225 P235:P237 P239:P248 P276:P309 R276:R309">
-    <cfRule type="containsText" dxfId="4" priority="19" operator="containsText" text="NO">
+    <cfRule type="containsText" dxfId="10" priority="19" operator="containsText" text="NO">
       <formula>NOT(ISERROR(SEARCH("NO",K1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="20" operator="containsText" text="YES">
+    <cfRule type="containsText" dxfId="9" priority="20" operator="containsText" text="YES">
       <formula>NOT(ISERROR(SEARCH("YES",K1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P250:P267">
-    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="NO">
+    <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="NO">
       <formula>NOT(ISERROR(SEARCH("NO",P250)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="YES">
+    <cfRule type="containsText" dxfId="7" priority="2" operator="containsText" text="YES">
       <formula>NOT(ISERROR(SEARCH("YES",P250)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="completed">
+    <cfRule type="containsText" dxfId="6" priority="3" operator="containsText" text="completed">
       <formula>NOT(ISERROR(SEARCH("completed",P250)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -49923,7 +49983,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923E81FA-B875-3C4E-A189-1A21268FA086}">
-  <dimension ref="A1:C382"/>
+  <dimension ref="A1:C390"/>
   <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="32.83203125" customWidth="1"/>
@@ -54055,7 +54115,113 @@
         <v>405</v>
       </c>
     </row>
+    <row r="383" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A383" s="1">
+        <v>46076</v>
+      </c>
+      <c r="B383" t="s">
+        <v>598</v>
+      </c>
+      <c r="C383" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="384" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A384" s="1">
+        <v>46076</v>
+      </c>
+      <c r="B384" t="s">
+        <v>825</v>
+      </c>
+      <c r="C384" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="385" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A385" s="1">
+        <v>46076</v>
+      </c>
+      <c r="B385" t="s">
+        <v>88</v>
+      </c>
+      <c r="C385" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="386" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A386" s="1">
+        <v>46079</v>
+      </c>
+      <c r="B386" t="s">
+        <v>277</v>
+      </c>
+      <c r="C386" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="387" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A387" s="1">
+        <v>46079</v>
+      </c>
+      <c r="B387" t="s">
+        <v>65</v>
+      </c>
+      <c r="C387" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="388" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A388" s="1">
+        <v>46080</v>
+      </c>
+      <c r="B388" t="s">
+        <v>723</v>
+      </c>
+      <c r="C388" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="389" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A389" s="1">
+        <v>46083</v>
+      </c>
+      <c r="B389" t="s">
+        <v>593</v>
+      </c>
+      <c r="C389" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="390" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A390" s="1">
+        <v>46083</v>
+      </c>
+      <c r="B390" t="s">
+        <v>855</v>
+      </c>
+      <c r="C390" t="s">
+        <v>402</v>
+      </c>
+    </row>
   </sheetData>
+  <conditionalFormatting sqref="B383">
+    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B384">
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B385">
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B387">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B389">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B390">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/EconJM_status.xlsx
+++ b/EconJM_status.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\javie\Dropbox\Work\Job Search\2025 EconJM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0065D0FC-DCA2-451B-BC93-36394C3F0ADD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B14633BD-299C-40C7-B140-944B478BAF0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" activeTab="1" xr2:uid="{6FE48536-7E5C-BF4C-9490-2A6392576298}"/>
   </bookViews>
@@ -438,7 +438,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3227" uniqueCount="967">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3231" uniqueCount="967">
   <si>
     <t>add_id</t>
   </si>
@@ -3566,7 +3566,27 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="23">
+  <dxfs count="25">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -49797,63 +49817,63 @@
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="A1:B208 A210:B283 A285:B1048576 B284">
-    <cfRule type="duplicateValues" dxfId="22" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:B22">
-    <cfRule type="duplicateValues" dxfId="21" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A61:B61">
-    <cfRule type="duplicateValues" dxfId="20" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="containsText" dxfId="19" priority="15" operator="containsText" text="closed">
+    <cfRule type="containsText" dxfId="21" priority="15" operator="containsText" text="closed">
       <formula>NOT(ISERROR(SEARCH("closed",I1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="16" operator="containsText" text="abandoned">
+    <cfRule type="containsText" dxfId="20" priority="16" operator="containsText" text="abandoned">
       <formula>NOT(ISERROR(SEARCH("abandoned",I1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="17" priority="18" operator="containsText" text="late app">
+    <cfRule type="containsText" dxfId="19" priority="18" operator="containsText" text="late app">
       <formula>NOT(ISERROR(SEARCH("late app",I1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:L1048576 P78:P80 P83:P89 P92:P112 P115:P124 P126:P181 S136 S153 S159 S166 S173 S178 P183:P205 P208:P211 P213:P218 P220:P233 S225 P235:P237 P239:P248 P276:P309 R276:R309 I1:J1">
-    <cfRule type="containsText" dxfId="16" priority="21" operator="containsText" text="completed">
+    <cfRule type="containsText" dxfId="18" priority="21" operator="containsText" text="completed">
       <formula>NOT(ISERROR(SEARCH("completed",I1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:J1048576">
-    <cfRule type="containsText" dxfId="15" priority="10" operator="containsText" text="no news">
+    <cfRule type="containsText" dxfId="17" priority="10" operator="containsText" text="no news">
       <formula>NOT(ISERROR(SEARCH("no news",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="11" operator="containsText" text="offer">
+    <cfRule type="containsText" dxfId="16" priority="11" operator="containsText" text="offer">
       <formula>NOT(ISERROR(SEARCH("offer",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="13" priority="12" operator="containsText" text="fly out">
+    <cfRule type="containsText" dxfId="15" priority="12" operator="containsText" text="fly out">
       <formula>NOT(ISERROR(SEARCH("fly out",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="13" operator="containsText" text="interview">
+    <cfRule type="containsText" dxfId="14" priority="13" operator="containsText" text="interview">
       <formula>NOT(ISERROR(SEARCH("interview",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="11" priority="14" operator="containsText" text="rejected">
+    <cfRule type="containsText" dxfId="13" priority="14" operator="containsText" text="rejected">
       <formula>NOT(ISERROR(SEARCH("rejected",J1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1:L1048576 P78:P80 P83:P89 P92:P112 P115:P124 P126:P181 S136 S153 S159 S166 S173 S178 P183:P205 P208:P211 P213:P218 P220:P233 S225 P235:P237 P239:P248 P276:P309 R276:R309">
-    <cfRule type="containsText" dxfId="10" priority="19" operator="containsText" text="NO">
+    <cfRule type="containsText" dxfId="12" priority="19" operator="containsText" text="NO">
       <formula>NOT(ISERROR(SEARCH("NO",K1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="9" priority="20" operator="containsText" text="YES">
+    <cfRule type="containsText" dxfId="11" priority="20" operator="containsText" text="YES">
       <formula>NOT(ISERROR(SEARCH("YES",K1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P250:P267">
-    <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="NO">
+    <cfRule type="containsText" dxfId="10" priority="1" operator="containsText" text="NO">
       <formula>NOT(ISERROR(SEARCH("NO",P250)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="7" priority="2" operator="containsText" text="YES">
+    <cfRule type="containsText" dxfId="9" priority="2" operator="containsText" text="YES">
       <formula>NOT(ISERROR(SEARCH("YES",P250)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="3" operator="containsText" text="completed">
+    <cfRule type="containsText" dxfId="8" priority="3" operator="containsText" text="completed">
       <formula>NOT(ISERROR(SEARCH("completed",P250)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -49983,7 +50003,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923E81FA-B875-3C4E-A189-1A21268FA086}">
-  <dimension ref="A1:C390"/>
+  <dimension ref="A1:C392"/>
   <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="32.83203125" customWidth="1"/>
@@ -54203,23 +54223,51 @@
         <v>402</v>
       </c>
     </row>
+    <row r="391" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A391" s="1">
+        <v>46084</v>
+      </c>
+      <c r="B391" t="s">
+        <v>721</v>
+      </c>
+      <c r="C391" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="392" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A392" s="1">
+        <v>46084</v>
+      </c>
+      <c r="B392" t="s">
+        <v>619</v>
+      </c>
+      <c r="C392" t="s">
+        <v>402</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="B383">
+    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B384">
+    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B385">
     <cfRule type="duplicateValues" dxfId="5" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B384">
+  <conditionalFormatting sqref="B387">
     <cfRule type="duplicateValues" dxfId="4" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B385">
+  <conditionalFormatting sqref="B389">
     <cfRule type="duplicateValues" dxfId="3" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B387">
+  <conditionalFormatting sqref="B390">
     <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B389">
+  <conditionalFormatting sqref="B391">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B390">
+  <conditionalFormatting sqref="B392">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/EconJM_status.xlsx
+++ b/EconJM_status.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\javie\Dropbox\Work\Job Search\2025 EconJM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B14633BD-299C-40C7-B140-944B478BAF0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F04C0E7-4484-4656-9AE9-6822A5AFDD1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" activeTab="1" xr2:uid="{6FE48536-7E5C-BF4C-9490-2A6392576298}"/>
   </bookViews>
@@ -438,7 +438,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3231" uniqueCount="967">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3235" uniqueCount="967">
   <si>
     <t>add_id</t>
   </si>
@@ -3566,7 +3566,27 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="25">
+  <dxfs count="27">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -49817,63 +49837,63 @@
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="A1:B208 A210:B283 A285:B1048576 B284">
-    <cfRule type="duplicateValues" dxfId="24" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:B22">
-    <cfRule type="duplicateValues" dxfId="23" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A61:B61">
-    <cfRule type="duplicateValues" dxfId="22" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="containsText" dxfId="21" priority="15" operator="containsText" text="closed">
+    <cfRule type="containsText" dxfId="23" priority="15" operator="containsText" text="closed">
       <formula>NOT(ISERROR(SEARCH("closed",I1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="20" priority="16" operator="containsText" text="abandoned">
+    <cfRule type="containsText" dxfId="22" priority="16" operator="containsText" text="abandoned">
       <formula>NOT(ISERROR(SEARCH("abandoned",I1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="19" priority="18" operator="containsText" text="late app">
+    <cfRule type="containsText" dxfId="21" priority="18" operator="containsText" text="late app">
       <formula>NOT(ISERROR(SEARCH("late app",I1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:L1048576 P78:P80 P83:P89 P92:P112 P115:P124 P126:P181 S136 S153 S159 S166 S173 S178 P183:P205 P208:P211 P213:P218 P220:P233 S225 P235:P237 P239:P248 P276:P309 R276:R309 I1:J1">
-    <cfRule type="containsText" dxfId="18" priority="21" operator="containsText" text="completed">
+    <cfRule type="containsText" dxfId="20" priority="21" operator="containsText" text="completed">
       <formula>NOT(ISERROR(SEARCH("completed",I1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:J1048576">
-    <cfRule type="containsText" dxfId="17" priority="10" operator="containsText" text="no news">
+    <cfRule type="containsText" dxfId="19" priority="10" operator="containsText" text="no news">
       <formula>NOT(ISERROR(SEARCH("no news",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="11" operator="containsText" text="offer">
+    <cfRule type="containsText" dxfId="18" priority="11" operator="containsText" text="offer">
       <formula>NOT(ISERROR(SEARCH("offer",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="15" priority="12" operator="containsText" text="fly out">
+    <cfRule type="containsText" dxfId="17" priority="12" operator="containsText" text="fly out">
       <formula>NOT(ISERROR(SEARCH("fly out",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="13" operator="containsText" text="interview">
+    <cfRule type="containsText" dxfId="16" priority="13" operator="containsText" text="interview">
       <formula>NOT(ISERROR(SEARCH("interview",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="13" priority="14" operator="containsText" text="rejected">
+    <cfRule type="containsText" dxfId="15" priority="14" operator="containsText" text="rejected">
       <formula>NOT(ISERROR(SEARCH("rejected",J1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1:L1048576 P78:P80 P83:P89 P92:P112 P115:P124 P126:P181 S136 S153 S159 S166 S173 S178 P183:P205 P208:P211 P213:P218 P220:P233 S225 P235:P237 P239:P248 P276:P309 R276:R309">
-    <cfRule type="containsText" dxfId="12" priority="19" operator="containsText" text="NO">
+    <cfRule type="containsText" dxfId="14" priority="19" operator="containsText" text="NO">
       <formula>NOT(ISERROR(SEARCH("NO",K1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="11" priority="20" operator="containsText" text="YES">
+    <cfRule type="containsText" dxfId="13" priority="20" operator="containsText" text="YES">
       <formula>NOT(ISERROR(SEARCH("YES",K1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P250:P267">
-    <cfRule type="containsText" dxfId="10" priority="1" operator="containsText" text="NO">
+    <cfRule type="containsText" dxfId="12" priority="1" operator="containsText" text="NO">
       <formula>NOT(ISERROR(SEARCH("NO",P250)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="9" priority="2" operator="containsText" text="YES">
+    <cfRule type="containsText" dxfId="11" priority="2" operator="containsText" text="YES">
       <formula>NOT(ISERROR(SEARCH("YES",P250)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="3" operator="containsText" text="completed">
+    <cfRule type="containsText" dxfId="10" priority="3" operator="containsText" text="completed">
       <formula>NOT(ISERROR(SEARCH("completed",P250)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -50003,7 +50023,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923E81FA-B875-3C4E-A189-1A21268FA086}">
-  <dimension ref="A1:C392"/>
+  <dimension ref="A1:C394"/>
   <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="32.83203125" customWidth="1"/>
@@ -54245,29 +54265,57 @@
         <v>402</v>
       </c>
     </row>
+    <row r="393" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A393" s="1">
+        <v>46086</v>
+      </c>
+      <c r="B393" t="s">
+        <v>820</v>
+      </c>
+      <c r="C393" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="394" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A394" s="1">
+        <v>46086</v>
+      </c>
+      <c r="B394" t="s">
+        <v>808</v>
+      </c>
+      <c r="C394" t="s">
+        <v>402</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="B383">
+    <cfRule type="duplicateValues" dxfId="9" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B384">
+    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B385">
     <cfRule type="duplicateValues" dxfId="7" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B384">
+  <conditionalFormatting sqref="B387">
     <cfRule type="duplicateValues" dxfId="6" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B385">
+  <conditionalFormatting sqref="B389">
     <cfRule type="duplicateValues" dxfId="5" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B387">
+  <conditionalFormatting sqref="B390">
     <cfRule type="duplicateValues" dxfId="4" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B389">
+  <conditionalFormatting sqref="B391">
     <cfRule type="duplicateValues" dxfId="3" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B390">
+  <conditionalFormatting sqref="B392">
     <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B391">
+  <conditionalFormatting sqref="B393">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B392">
+  <conditionalFormatting sqref="B394">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/EconJM_status.xlsx
+++ b/EconJM_status.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\javie\Dropbox\Work\Job Search\2025 EconJM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F04C0E7-4484-4656-9AE9-6822A5AFDD1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF0415E7-3901-434A-91EB-A78A4840DAF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" activeTab="1" xr2:uid="{6FE48536-7E5C-BF4C-9490-2A6392576298}"/>
   </bookViews>
@@ -438,7 +438,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3235" uniqueCount="967">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3248" uniqueCount="967">
   <si>
     <t>add_id</t>
   </si>
@@ -3566,7 +3566,67 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="27">
+  <dxfs count="33">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -49837,63 +49897,63 @@
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="A1:B208 A210:B283 A285:B1048576 B284">
-    <cfRule type="duplicateValues" dxfId="26" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:B22">
-    <cfRule type="duplicateValues" dxfId="25" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A61:B61">
-    <cfRule type="duplicateValues" dxfId="24" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="containsText" dxfId="23" priority="15" operator="containsText" text="closed">
+    <cfRule type="containsText" dxfId="29" priority="15" operator="containsText" text="closed">
       <formula>NOT(ISERROR(SEARCH("closed",I1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="22" priority="16" operator="containsText" text="abandoned">
+    <cfRule type="containsText" dxfId="28" priority="16" operator="containsText" text="abandoned">
       <formula>NOT(ISERROR(SEARCH("abandoned",I1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="21" priority="18" operator="containsText" text="late app">
+    <cfRule type="containsText" dxfId="27" priority="18" operator="containsText" text="late app">
       <formula>NOT(ISERROR(SEARCH("late app",I1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:L1048576 P78:P80 P83:P89 P92:P112 P115:P124 P126:P181 S136 S153 S159 S166 S173 S178 P183:P205 P208:P211 P213:P218 P220:P233 S225 P235:P237 P239:P248 P276:P309 R276:R309 I1:J1">
-    <cfRule type="containsText" dxfId="20" priority="21" operator="containsText" text="completed">
+    <cfRule type="containsText" dxfId="26" priority="21" operator="containsText" text="completed">
       <formula>NOT(ISERROR(SEARCH("completed",I1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:J1048576">
-    <cfRule type="containsText" dxfId="19" priority="10" operator="containsText" text="no news">
+    <cfRule type="containsText" dxfId="25" priority="10" operator="containsText" text="no news">
       <formula>NOT(ISERROR(SEARCH("no news",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="11" operator="containsText" text="offer">
+    <cfRule type="containsText" dxfId="24" priority="11" operator="containsText" text="offer">
       <formula>NOT(ISERROR(SEARCH("offer",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="17" priority="12" operator="containsText" text="fly out">
+    <cfRule type="containsText" dxfId="23" priority="12" operator="containsText" text="fly out">
       <formula>NOT(ISERROR(SEARCH("fly out",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="13" operator="containsText" text="interview">
+    <cfRule type="containsText" dxfId="22" priority="13" operator="containsText" text="interview">
       <formula>NOT(ISERROR(SEARCH("interview",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="15" priority="14" operator="containsText" text="rejected">
+    <cfRule type="containsText" dxfId="21" priority="14" operator="containsText" text="rejected">
       <formula>NOT(ISERROR(SEARCH("rejected",J1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1:L1048576 P78:P80 P83:P89 P92:P112 P115:P124 P126:P181 S136 S153 S159 S166 S173 S178 P183:P205 P208:P211 P213:P218 P220:P233 S225 P235:P237 P239:P248 P276:P309 R276:R309">
-    <cfRule type="containsText" dxfId="14" priority="19" operator="containsText" text="NO">
+    <cfRule type="containsText" dxfId="20" priority="19" operator="containsText" text="NO">
       <formula>NOT(ISERROR(SEARCH("NO",K1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="13" priority="20" operator="containsText" text="YES">
+    <cfRule type="containsText" dxfId="19" priority="20" operator="containsText" text="YES">
       <formula>NOT(ISERROR(SEARCH("YES",K1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P250:P267">
-    <cfRule type="containsText" dxfId="12" priority="1" operator="containsText" text="NO">
+    <cfRule type="containsText" dxfId="18" priority="1" operator="containsText" text="NO">
       <formula>NOT(ISERROR(SEARCH("NO",P250)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="11" priority="2" operator="containsText" text="YES">
+    <cfRule type="containsText" dxfId="17" priority="2" operator="containsText" text="YES">
       <formula>NOT(ISERROR(SEARCH("YES",P250)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="3" operator="containsText" text="completed">
+    <cfRule type="containsText" dxfId="16" priority="3" operator="containsText" text="completed">
       <formula>NOT(ISERROR(SEARCH("completed",P250)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -50023,7 +50083,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923E81FA-B875-3C4E-A189-1A21268FA086}">
-  <dimension ref="A1:C394"/>
+  <dimension ref="A1:C401"/>
   <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="32.83203125" customWidth="1"/>
@@ -54287,35 +54347,125 @@
         <v>402</v>
       </c>
     </row>
+    <row r="395" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A395" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B395" t="s">
+        <v>635</v>
+      </c>
+      <c r="C395" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="396" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A396" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B396" t="s">
+        <v>487</v>
+      </c>
+      <c r="C396" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="397" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A397" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B397" t="s">
+        <v>440</v>
+      </c>
+      <c r="C397" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="398" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A398" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B398" t="s">
+        <v>496</v>
+      </c>
+      <c r="C398" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="399" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A399" s="1">
+        <v>46094</v>
+      </c>
+      <c r="C399" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="400" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A400" s="1">
+        <v>46099</v>
+      </c>
+      <c r="B400" t="s">
+        <v>920</v>
+      </c>
+      <c r="C400" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="401" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A401" s="1">
+        <v>46100</v>
+      </c>
+      <c r="B401" t="s">
+        <v>906</v>
+      </c>
+      <c r="C401" t="s">
+        <v>402</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="B383">
+    <cfRule type="duplicateValues" dxfId="15" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B384">
+    <cfRule type="duplicateValues" dxfId="14" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B385">
+    <cfRule type="duplicateValues" dxfId="13" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B387">
+    <cfRule type="duplicateValues" dxfId="12" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B389">
+    <cfRule type="duplicateValues" dxfId="11" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B390">
+    <cfRule type="duplicateValues" dxfId="10" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B391">
     <cfRule type="duplicateValues" dxfId="9" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B384">
+  <conditionalFormatting sqref="B392">
     <cfRule type="duplicateValues" dxfId="8" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B385">
+  <conditionalFormatting sqref="B393">
     <cfRule type="duplicateValues" dxfId="7" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B387">
+  <conditionalFormatting sqref="B394">
     <cfRule type="duplicateValues" dxfId="6" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B389">
+  <conditionalFormatting sqref="B396">
     <cfRule type="duplicateValues" dxfId="5" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B390">
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+  <conditionalFormatting sqref="B397">
+    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B391">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B392">
+  <conditionalFormatting sqref="B398">
     <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B393">
+  <conditionalFormatting sqref="B400">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B394">
+  <conditionalFormatting sqref="B401">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/EconJM_status.xlsx
+++ b/EconJM_status.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\javie\Dropbox\Work\Job Search\2025 EconJM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF0415E7-3901-434A-91EB-A78A4840DAF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E6D2ABF-EA20-49C4-A64E-8C8901E19753}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" activeTab="1" xr2:uid="{6FE48536-7E5C-BF4C-9490-2A6392576298}"/>
   </bookViews>
@@ -438,7 +438,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3248" uniqueCount="967">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3264" uniqueCount="967">
   <si>
     <t>add_id</t>
   </si>
@@ -3566,7 +3566,77 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="33">
+  <dxfs count="40">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -49897,63 +49967,63 @@
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="A1:B208 A210:B283 A285:B1048576 B284">
-    <cfRule type="duplicateValues" dxfId="32" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:B22">
-    <cfRule type="duplicateValues" dxfId="31" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A61:B61">
-    <cfRule type="duplicateValues" dxfId="30" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="containsText" dxfId="29" priority="15" operator="containsText" text="closed">
+    <cfRule type="containsText" dxfId="36" priority="15" operator="containsText" text="closed">
       <formula>NOT(ISERROR(SEARCH("closed",I1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="28" priority="16" operator="containsText" text="abandoned">
+    <cfRule type="containsText" dxfId="35" priority="16" operator="containsText" text="abandoned">
       <formula>NOT(ISERROR(SEARCH("abandoned",I1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="27" priority="18" operator="containsText" text="late app">
+    <cfRule type="containsText" dxfId="34" priority="18" operator="containsText" text="late app">
       <formula>NOT(ISERROR(SEARCH("late app",I1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:L1048576 P78:P80 P83:P89 P92:P112 P115:P124 P126:P181 S136 S153 S159 S166 S173 S178 P183:P205 P208:P211 P213:P218 P220:P233 S225 P235:P237 P239:P248 P276:P309 R276:R309 I1:J1">
-    <cfRule type="containsText" dxfId="26" priority="21" operator="containsText" text="completed">
+    <cfRule type="containsText" dxfId="33" priority="21" operator="containsText" text="completed">
       <formula>NOT(ISERROR(SEARCH("completed",I1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:J1048576">
-    <cfRule type="containsText" dxfId="25" priority="10" operator="containsText" text="no news">
+    <cfRule type="containsText" dxfId="32" priority="10" operator="containsText" text="no news">
       <formula>NOT(ISERROR(SEARCH("no news",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="24" priority="11" operator="containsText" text="offer">
+    <cfRule type="containsText" dxfId="31" priority="11" operator="containsText" text="offer">
       <formula>NOT(ISERROR(SEARCH("offer",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="23" priority="12" operator="containsText" text="fly out">
+    <cfRule type="containsText" dxfId="30" priority="12" operator="containsText" text="fly out">
       <formula>NOT(ISERROR(SEARCH("fly out",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="22" priority="13" operator="containsText" text="interview">
+    <cfRule type="containsText" dxfId="29" priority="13" operator="containsText" text="interview">
       <formula>NOT(ISERROR(SEARCH("interview",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="21" priority="14" operator="containsText" text="rejected">
+    <cfRule type="containsText" dxfId="28" priority="14" operator="containsText" text="rejected">
       <formula>NOT(ISERROR(SEARCH("rejected",J1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1:L1048576 P78:P80 P83:P89 P92:P112 P115:P124 P126:P181 S136 S153 S159 S166 S173 S178 P183:P205 P208:P211 P213:P218 P220:P233 S225 P235:P237 P239:P248 P276:P309 R276:R309">
-    <cfRule type="containsText" dxfId="20" priority="19" operator="containsText" text="NO">
+    <cfRule type="containsText" dxfId="27" priority="19" operator="containsText" text="NO">
       <formula>NOT(ISERROR(SEARCH("NO",K1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="19" priority="20" operator="containsText" text="YES">
+    <cfRule type="containsText" dxfId="26" priority="20" operator="containsText" text="YES">
       <formula>NOT(ISERROR(SEARCH("YES",K1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P250:P267">
-    <cfRule type="containsText" dxfId="18" priority="1" operator="containsText" text="NO">
+    <cfRule type="containsText" dxfId="25" priority="1" operator="containsText" text="NO">
       <formula>NOT(ISERROR(SEARCH("NO",P250)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="17" priority="2" operator="containsText" text="YES">
+    <cfRule type="containsText" dxfId="24" priority="2" operator="containsText" text="YES">
       <formula>NOT(ISERROR(SEARCH("YES",P250)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="3" operator="containsText" text="completed">
+    <cfRule type="containsText" dxfId="23" priority="3" operator="containsText" text="completed">
       <formula>NOT(ISERROR(SEARCH("completed",P250)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -50083,7 +50153,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923E81FA-B875-3C4E-A189-1A21268FA086}">
-  <dimension ref="A1:C401"/>
+  <dimension ref="A1:C409"/>
   <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="32.83203125" customWidth="1"/>
@@ -54421,51 +54491,158 @@
         <v>402</v>
       </c>
     </row>
+    <row r="402" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A402" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B402" t="s">
+        <v>183</v>
+      </c>
+      <c r="C402" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="403" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A403" s="1">
+        <v>46105</v>
+      </c>
+      <c r="B403" t="s">
+        <v>713</v>
+      </c>
+      <c r="C403" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="404" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A404" s="1">
+        <v>46105</v>
+      </c>
+      <c r="B404" t="s">
+        <v>955</v>
+      </c>
+      <c r="C404" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="405" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A405" s="1">
+        <v>46106</v>
+      </c>
+      <c r="B405" t="s">
+        <v>233</v>
+      </c>
+      <c r="C405" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="406" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A406" s="1">
+        <v>46106</v>
+      </c>
+      <c r="B406" t="s">
+        <v>918</v>
+      </c>
+      <c r="C406" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="407" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A407" s="1">
+        <v>46107</v>
+      </c>
+      <c r="B407" t="s">
+        <v>224</v>
+      </c>
+      <c r="C407" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="408" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A408" s="1">
+        <v>46112</v>
+      </c>
+      <c r="B408" t="s">
+        <v>415</v>
+      </c>
+      <c r="C408" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="409" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A409" s="1">
+        <v>46115</v>
+      </c>
+      <c r="B409" t="s">
+        <v>466</v>
+      </c>
+      <c r="C409" t="s">
+        <v>402</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="B383">
+    <cfRule type="duplicateValues" dxfId="22" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B384">
+    <cfRule type="duplicateValues" dxfId="21" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B385">
+    <cfRule type="duplicateValues" dxfId="20" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B387">
+    <cfRule type="duplicateValues" dxfId="19" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B389">
+    <cfRule type="duplicateValues" dxfId="18" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B390">
+    <cfRule type="duplicateValues" dxfId="17" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B391">
+    <cfRule type="duplicateValues" dxfId="16" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B392">
     <cfRule type="duplicateValues" dxfId="15" priority="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B384">
+  <conditionalFormatting sqref="B393">
     <cfRule type="duplicateValues" dxfId="14" priority="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B385">
+  <conditionalFormatting sqref="B394">
     <cfRule type="duplicateValues" dxfId="13" priority="14"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B387">
+  <conditionalFormatting sqref="B396">
     <cfRule type="duplicateValues" dxfId="12" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B389">
-    <cfRule type="duplicateValues" dxfId="11" priority="12"/>
+  <conditionalFormatting sqref="B397">
+    <cfRule type="duplicateValues" dxfId="11" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B390">
-    <cfRule type="duplicateValues" dxfId="10" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B391">
+  <conditionalFormatting sqref="B398">
     <cfRule type="duplicateValues" dxfId="9" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B392">
+  <conditionalFormatting sqref="B400">
     <cfRule type="duplicateValues" dxfId="8" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B393">
+  <conditionalFormatting sqref="B401">
     <cfRule type="duplicateValues" dxfId="7" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B394">
+  <conditionalFormatting sqref="B402">
     <cfRule type="duplicateValues" dxfId="6" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B396">
+  <conditionalFormatting sqref="B404">
     <cfRule type="duplicateValues" dxfId="5" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B397">
-    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="5"/>
+  <conditionalFormatting sqref="B405">
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B398">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  <conditionalFormatting sqref="B406">
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B400">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  <conditionalFormatting sqref="B407">
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B401">
+  <conditionalFormatting sqref="B408">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/EconJM_status.xlsx
+++ b/EconJM_status.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\javie\Dropbox\Work\Job Search\2025 EconJM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E6D2ABF-EA20-49C4-A64E-8C8901E19753}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0073BD6-B0F7-4D8C-953D-AEFAB13E4FEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" activeTab="1" xr2:uid="{6FE48536-7E5C-BF4C-9490-2A6392576298}"/>
   </bookViews>
@@ -438,7 +438,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3264" uniqueCount="967">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3272" uniqueCount="968">
   <si>
     <t>add_id</t>
   </si>
@@ -3375,6 +3375,9 @@
   </si>
   <si>
     <t>Brown University</t>
+  </si>
+  <si>
+    <t>viena</t>
   </si>
 </sst>
 </file>
@@ -3566,7 +3569,37 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="40">
+  <dxfs count="43">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -49967,63 +50000,63 @@
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="A1:B208 A210:B283 A285:B1048576 B284">
-    <cfRule type="duplicateValues" dxfId="39" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:B22">
-    <cfRule type="duplicateValues" dxfId="38" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A61:B61">
-    <cfRule type="duplicateValues" dxfId="37" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="containsText" dxfId="36" priority="15" operator="containsText" text="closed">
+    <cfRule type="containsText" dxfId="39" priority="15" operator="containsText" text="closed">
       <formula>NOT(ISERROR(SEARCH("closed",I1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="35" priority="16" operator="containsText" text="abandoned">
+    <cfRule type="containsText" dxfId="38" priority="16" operator="containsText" text="abandoned">
       <formula>NOT(ISERROR(SEARCH("abandoned",I1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="34" priority="18" operator="containsText" text="late app">
+    <cfRule type="containsText" dxfId="37" priority="18" operator="containsText" text="late app">
       <formula>NOT(ISERROR(SEARCH("late app",I1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:L1048576 P78:P80 P83:P89 P92:P112 P115:P124 P126:P181 S136 S153 S159 S166 S173 S178 P183:P205 P208:P211 P213:P218 P220:P233 S225 P235:P237 P239:P248 P276:P309 R276:R309 I1:J1">
-    <cfRule type="containsText" dxfId="33" priority="21" operator="containsText" text="completed">
+    <cfRule type="containsText" dxfId="36" priority="21" operator="containsText" text="completed">
       <formula>NOT(ISERROR(SEARCH("completed",I1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:J1048576">
-    <cfRule type="containsText" dxfId="32" priority="10" operator="containsText" text="no news">
+    <cfRule type="containsText" dxfId="35" priority="10" operator="containsText" text="no news">
       <formula>NOT(ISERROR(SEARCH("no news",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="31" priority="11" operator="containsText" text="offer">
+    <cfRule type="containsText" dxfId="34" priority="11" operator="containsText" text="offer">
       <formula>NOT(ISERROR(SEARCH("offer",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="30" priority="12" operator="containsText" text="fly out">
+    <cfRule type="containsText" dxfId="33" priority="12" operator="containsText" text="fly out">
       <formula>NOT(ISERROR(SEARCH("fly out",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="29" priority="13" operator="containsText" text="interview">
+    <cfRule type="containsText" dxfId="32" priority="13" operator="containsText" text="interview">
       <formula>NOT(ISERROR(SEARCH("interview",J1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="28" priority="14" operator="containsText" text="rejected">
+    <cfRule type="containsText" dxfId="31" priority="14" operator="containsText" text="rejected">
       <formula>NOT(ISERROR(SEARCH("rejected",J1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1:L1048576 P78:P80 P83:P89 P92:P112 P115:P124 P126:P181 S136 S153 S159 S166 S173 S178 P183:P205 P208:P211 P213:P218 P220:P233 S225 P235:P237 P239:P248 P276:P309 R276:R309">
-    <cfRule type="containsText" dxfId="27" priority="19" operator="containsText" text="NO">
+    <cfRule type="containsText" dxfId="30" priority="19" operator="containsText" text="NO">
       <formula>NOT(ISERROR(SEARCH("NO",K1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="26" priority="20" operator="containsText" text="YES">
+    <cfRule type="containsText" dxfId="29" priority="20" operator="containsText" text="YES">
       <formula>NOT(ISERROR(SEARCH("YES",K1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P250:P267">
-    <cfRule type="containsText" dxfId="25" priority="1" operator="containsText" text="NO">
+    <cfRule type="containsText" dxfId="28" priority="1" operator="containsText" text="NO">
       <formula>NOT(ISERROR(SEARCH("NO",P250)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="24" priority="2" operator="containsText" text="YES">
+    <cfRule type="containsText" dxfId="27" priority="2" operator="containsText" text="YES">
       <formula>NOT(ISERROR(SEARCH("YES",P250)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="23" priority="3" operator="containsText" text="completed">
+    <cfRule type="containsText" dxfId="26" priority="3" operator="containsText" text="completed">
       <formula>NOT(ISERROR(SEARCH("completed",P250)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -50153,7 +50186,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923E81FA-B875-3C4E-A189-1A21268FA086}">
-  <dimension ref="A1:C409"/>
+  <dimension ref="A1:C413"/>
   <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="32.83203125" customWidth="1"/>
@@ -54579,70 +54612,123 @@
         <v>402</v>
       </c>
     </row>
+    <row r="410" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A410" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B410" t="s">
+        <v>913</v>
+      </c>
+      <c r="C410" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="411" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A411" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B411" t="s">
+        <v>621</v>
+      </c>
+      <c r="C411" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="412" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A412" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B412" t="s">
+        <v>431</v>
+      </c>
+      <c r="C412" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="413" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A413" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B413" t="s">
+        <v>967</v>
+      </c>
+      <c r="C413" t="s">
+        <v>402</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="B383">
+    <cfRule type="duplicateValues" dxfId="25" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B384">
+    <cfRule type="duplicateValues" dxfId="24" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B385">
+    <cfRule type="duplicateValues" dxfId="23" priority="24"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B387">
     <cfRule type="duplicateValues" dxfId="22" priority="23"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B384">
+  <conditionalFormatting sqref="B389">
     <cfRule type="duplicateValues" dxfId="21" priority="22"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B385">
+  <conditionalFormatting sqref="B390">
     <cfRule type="duplicateValues" dxfId="20" priority="21"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B387">
+  <conditionalFormatting sqref="B391">
     <cfRule type="duplicateValues" dxfId="19" priority="20"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B389">
+  <conditionalFormatting sqref="B392">
     <cfRule type="duplicateValues" dxfId="18" priority="19"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B390">
+  <conditionalFormatting sqref="B393">
     <cfRule type="duplicateValues" dxfId="17" priority="18"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B391">
+  <conditionalFormatting sqref="B394">
     <cfRule type="duplicateValues" dxfId="16" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B392">
+  <conditionalFormatting sqref="B396">
     <cfRule type="duplicateValues" dxfId="15" priority="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B393">
-    <cfRule type="duplicateValues" dxfId="14" priority="15"/>
+  <conditionalFormatting sqref="B397">
+    <cfRule type="duplicateValues" dxfId="14" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B394">
-    <cfRule type="duplicateValues" dxfId="13" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B396">
+  <conditionalFormatting sqref="B398">
     <cfRule type="duplicateValues" dxfId="12" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B397">
-    <cfRule type="duplicateValues" dxfId="11" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="12"/>
+  <conditionalFormatting sqref="B400">
+    <cfRule type="duplicateValues" dxfId="11" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B398">
+  <conditionalFormatting sqref="B401">
+    <cfRule type="duplicateValues" dxfId="10" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B402">
     <cfRule type="duplicateValues" dxfId="9" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B400">
+  <conditionalFormatting sqref="B404">
     <cfRule type="duplicateValues" dxfId="8" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B401">
+  <conditionalFormatting sqref="B405">
     <cfRule type="duplicateValues" dxfId="7" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B402">
+  <conditionalFormatting sqref="B406">
     <cfRule type="duplicateValues" dxfId="6" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B404">
-    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+  <conditionalFormatting sqref="B407">
+    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B405">
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B406">
+  <conditionalFormatting sqref="B408">
     <cfRule type="duplicateValues" dxfId="3" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B407">
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+  <conditionalFormatting sqref="B410">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B408">
+  <conditionalFormatting sqref="B411">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B412">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
